--- a/j-busqueda clientes/j-clientes-gle.xlsx
+++ b/j-busqueda clientes/j-clientes-gle.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88153b17ae7a9f01/documentos/TRABAJOS AUTONOMOS/JURADA/j-busqueda clientes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="686" documentId="11_A9F854B1BC61342BED428D976AB7AEFF89D0661B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEB1D1AE-8907-5784-80C4-B6F8128DDC02}"/>
+  <xr:revisionPtr revIDLastSave="1347" documentId="11_A9F854B1BC61342BED428D976AB7AEFF89D0661B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2980377-10DC-42A0-BBAB-1369BD199A61}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="-110" windowWidth="24900" windowHeight="14500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="810" yWindow="-110" windowWidth="24900" windowHeight="14500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="clientes" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,6 @@
     <definedName name="DatosExternos_1" localSheetId="0">clientes!$A$1:$X$58</definedName>
   </definedNames>
   <calcPr calcId="0" iterateDelta="1E-4"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -54,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3649" uniqueCount="2101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3712" uniqueCount="2100">
   <si>
     <t>fechaEmail</t>
   </si>
@@ -6112,12 +6111,6 @@
     <t>sudáfrica</t>
   </si>
   <si>
-    <t>ANÁLISIS DE FACTORES DE RESPUESTA</t>
-  </si>
-  <si>
-    <t>Actualizado: 19/02/2026</t>
-  </si>
-  <si>
     <t>HITOS CLAVE</t>
   </si>
   <si>
@@ -6127,33 +6120,15 @@
     <t>~29/01/2026: CV con 2 recomendaciones de clientes (1 de visados)</t>
   </si>
   <si>
-    <t>Análisis previo (nov 2025): email particular 46% vs genérico 36% respuesta</t>
-  </si>
-  <si>
-    <t>CLASIFICACIÓN DE RESPUESTAS USADA EN ESTE ANÁLISIS</t>
-  </si>
-  <si>
-    <t>POSITIVO REAL (interés comercial concreto):</t>
-  </si>
-  <si>
     <t>PT, PIDE PRES, PP, PPE, QG, R, R-C, TW</t>
   </si>
   <si>
-    <t>POSITIVO BLANDO (buena disposición sin acción):</t>
-  </si>
-  <si>
-    <t>POSITIVA, POSITIVO, PV, NP, AP, MP, MR, ME RECOMIENDA, ME REDIRIGE</t>
-  </si>
-  <si>
     <t>NEGATIVO:</t>
   </si>
   <si>
     <t>N, negativa, "ya tienen gente"</t>
   </si>
   <si>
-    <t>SIN EFECTO (email no llegó):</t>
-  </si>
-  <si>
     <t>SIN RESPUESTA:</t>
   </si>
   <si>
@@ -6193,18 +6168,12 @@
     <t>TIEMPO DE RESPUESTA</t>
   </si>
   <si>
-    <t>Media: 20 días | Mediana: 4 días</t>
-  </si>
-  <si>
     <t>DETALLE: RESPUESTAS POSITIVO REAL</t>
   </si>
   <si>
     <t>Empresa</t>
   </si>
   <si>
-    <t>Fecha email</t>
-  </si>
-  <si>
     <t>Email único</t>
   </si>
   <si>
@@ -6268,9 +6237,6 @@
     <t>FACTOR: PERSONALIZADO (col E): ¿mensaje personalizado?</t>
   </si>
   <si>
-    <t>medio</t>
-  </si>
-  <si>
     <t>FACTOR: IDIOMA (col M): ¿en inglés o español?</t>
   </si>
   <si>
@@ -6295,100 +6261,130 @@
     <t>FACTOR: REMINDER (col B): ¿se envió follow-up?</t>
   </si>
   <si>
-    <t>CONCLUSIONES</t>
-  </si>
-  <si>
-    <t>1. IDIOMA: DATO NO FIABLE — la columna M solo está rellenada en 90 de 271 filas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Los 3 PT (dan trabajo): 2 escritos en español (col M vacía), 1 en inglés.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   El análisis mostraba en&gt;es, pero es un espejismo por datos incompletos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   No se puede concluir nada sobre idioma hasta rellenar la columna M.</t>
-  </si>
-  <si>
-    <t>2. REGIÓN: España concentra los mejores resultados reales.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Los 3 clientes que han dado trabajo (PT) operan en España.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   5 de 7 Positivo Real con región conocida son de España.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   UK: 23% responde pero 0% Positivo Real (prefieren traductores locales).</t>
-  </si>
-  <si>
-    <t>3. REMINDERS: Los follow-up aumentan el Positivo Real (4.9% vs 2.2% sin reminder).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Insistir funciona para convertir interés latente en acción.</t>
-  </si>
-  <si>
-    <t>4. EMAIL PERSONAL vs GENÉRICO: Confirma análisis previo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Email personal: 26.7% positivo total vs genérico: 17.5%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Pero el % de Positivo Real es similar (~4%). La ventaja está en respuestas blandas.</t>
-  </si>
-  <si>
-    <t>5. PERSONALIZACIÓN: Los emails personalizados funcionan mejor (23.5% vs 15.8%).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Dado que casi todos son personalizados, este factor es difícil de aislar.</t>
-  </si>
-  <si>
-    <t>6. PERIODO TEMPORAL: Aún no se ve efecto claro de los cambios recientes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Antes ene-2026: 26.7% positivo (5.7% Real) — mejor tasa global.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Desde 29-ene (tarifa+recomendaciones): 20.4% (1.9% Real) — peor, pero...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   CAVEAT: los emails recientes no han tenido tiempo suficiente para generar respuestas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Este dato debe revisarse en 1-2 meses.</t>
-  </si>
-  <si>
-    <t>7. TASA GENERAL: 29% responde, 4% genera interés comercial real.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   De 271 contactadas, solo 11 mostraron interés real y 3 dieron trabajo.</t>
-  </si>
-  <si>
-    <t>CALIDAD DE DATOS — COLUMNAS CON MUCHOS VACÍOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Col M (idioma): solo 90/271 rellenadas (33%). Conclusiones no fiables.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Col N (adecuada): solo 25/271 rellenadas (9%). Muestra insuficiente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Col L (ubicación): 204/271 rellenadas (75%). Razonablemente fiable.</t>
-  </si>
-  <si>
-    <t>RECOMENDACIONES</t>
-  </si>
-  <si>
-    <t>• Priorizar empresas en España (o que operen en España)</t>
-  </si>
-  <si>
-    <t>• Seguir enviando reminders (aumentan conversión real)</t>
-  </si>
-  <si>
-    <t>• Rellenar col M (idioma) para poder evaluar ese factor con fiabilidad</t>
-  </si>
-  <si>
-    <t>• Revisar este análisis en abril 2026 para evaluar efecto de tarifa+recomendaciones</t>
+    <t>ANÁLISIS AMPLIADO DE FACTORES DE RESPUESTA</t>
+  </si>
+  <si>
+    <t>Actualizado: 21/02/2026</t>
+  </si>
+  <si>
+    <t>Incluye columnas Y (tipoPersonalización) y Z (tamañoEmpresa)</t>
+  </si>
+  <si>
+    <t>Feb 2026: análisis ampliado con datos de personalización y tamaño empresa</t>
+  </si>
+  <si>
+    <t>CLASIFICACIÓN DE RESPUESTAS</t>
+  </si>
+  <si>
+    <t>POSITIVO REAL:</t>
+  </si>
+  <si>
+    <t>POSITIVO BLANDO:</t>
+  </si>
+  <si>
+    <t>PV, NP, AP, MP, MR, ME RECOMIENDA, ME REDIRIGE</t>
+  </si>
+  <si>
+    <t>SIN EFECTO:</t>
+  </si>
+  <si>
+    <t>NE (email no llegó)</t>
+  </si>
+  <si>
+    <t>CALIDAD DE DATOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Col M (idioma)</t>
+  </si>
+  <si>
+    <t>261/274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Col Y (tipoPersonalización)</t>
+  </si>
+  <si>
+    <t>203/274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Col Z (tamañoEmpresa)</t>
+  </si>
+  <si>
+    <t>108/274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Col N (adecuada)</t>
+  </si>
+  <si>
+    <t>28/274</t>
+  </si>
+  <si>
+    <t>Media: 20 días | Mediana: 3 días</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Tipo pers.</t>
+  </si>
+  <si>
+    <t>Tamaño</t>
+  </si>
+  <si>
+    <t>FACTOR: TIPO PERSONALIZACIÓN (col Y): tipo de personalización usada</t>
+  </si>
+  <si>
+    <t>FACTOR: TAMAÑO EMPRESA (col Z): tamaño estimado</t>
+  </si>
+  <si>
+    <t>FACTOR: GENÉRICO vs PERSONALIZADO REAL (basado en col Y)</t>
+  </si>
+  <si>
+    <t>Genérico (GN)</t>
+  </si>
+  <si>
+    <t>Personalizado real</t>
+  </si>
+  <si>
+    <t>CONCLUSIONES (generadas automáticamente a partir de los datos)</t>
+  </si>
+  <si>
+    <t>⚠ Col Z (tamañoEmpresa): solo 39.4% rellenada. Conclusiones sobre este factor NO son fiables.</t>
+  </si>
+  <si>
+    <t>⚠ Col N (adecuada): solo 10.2% rellenada. Conclusiones sobre este factor NO son fiables.</t>
+  </si>
+  <si>
+    <t>• EMAIL ÚNICO (col D): mejor resultado = no (4.2% Pos.Real) vs peor = sí (3.3%)</t>
+  </si>
+  <si>
+    <t>• PERSONALIZADO (col E): mejor resultado = sí (4.7% Pos.Real) vs peor = no (3.1%)</t>
+  </si>
+  <si>
+    <t>• IDIOMA (col M): mejor resultado = en (4.5% Pos.Real) vs peor = es (4.0%)</t>
+  </si>
+  <si>
+    <t>• ADECUACIÓN (col N): mejor resultado = ADECUADA (12.5% Pos.Real) vs peor = MUY ADECUADA (0.0%)</t>
+  </si>
+  <si>
+    <t>• REGIÓN: mejor resultado = Otro (3.8% Pos.Real) vs peor = Irlanda (0.0%)</t>
+  </si>
+  <si>
+    <t>• PERIODO TEMPORAL: mejor resultado = Antes ene-2026 (5.7% Pos.Real) vs peor = Desde 29-ene (+ recomendaciones) (1.8%)</t>
+  </si>
+  <si>
+    <t>• REMINDER (col B): mejor resultado = True (4.9% Pos.Real) vs peor = False (2.2%)</t>
+  </si>
+  <si>
+    <t>• TIPO PERSONALIZACIÓN (col Y): mejor resultado = JV (12.5% Pos.Real) vs peor = MLT (0.0%)</t>
+  </si>
+  <si>
+    <t>• TAMAÑO EMPRESA (col Z): mejor resultado = BT (15.9% Pos.Real) vs peor = GR (0.0%)</t>
+  </si>
+  <si>
+    <t>• GENÉRICO vs PERSONALIZADO REAL (basado en col Y): mejor resultado = Personalizado real (4.8% Pos.Real) vs peor = Genérico (GN) (3.5%)</t>
+  </si>
+  <si>
+    <t>NOTA: Las conclusiones anteriores son orientativas. Verificar que la muestra de cada factor es suficiente.</t>
   </si>
 </sst>
 </file>
@@ -64848,601 +64844,592 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15" customHeight="1">
       <c r="A1" s="408" t="s">
-        <v>2008</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1">
       <c r="A2" t="s">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="12.65" customHeight="1"/>
-    <row r="4" spans="1:2" ht="12.65" customHeight="1">
-      <c r="A4" s="408" t="s">
-        <v>2010</v>
-      </c>
-    </row>
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="12.65" customHeight="1">
+      <c r="A3" t="s">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="5" spans="1:2" ht="12.65" customHeight="1">
-      <c r="A5" t="s">
-        <v>2011</v>
+      <c r="A5" s="408" t="s">
+        <v>2008</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" customHeight="1">
       <c r="A6" t="s">
-        <v>2012</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="12.65" customHeight="1">
-      <c r="A7" s="408" t="s">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="12.65" customHeight="1"/>
-    <row r="9" spans="1:2" ht="12.65" customHeight="1">
-      <c r="A9" s="408" t="s">
-        <v>2014</v>
-      </c>
-    </row>
+      <c r="A7" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="12.65" customHeight="1">
+      <c r="A8" s="408" t="s">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="10" spans="1:2" ht="12.65" customHeight="1">
-      <c r="A10" t="s">
-        <v>2015</v>
-      </c>
-      <c r="B10" t="s">
-        <v>2016</v>
+      <c r="A10" s="408" t="s">
+        <v>2062</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="12.65" customHeight="1">
       <c r="A11" t="s">
-        <v>2017</v>
+        <v>2063</v>
       </c>
       <c r="B11" t="s">
-        <v>2018</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="12.65" customHeight="1">
       <c r="A12" t="s">
-        <v>2019</v>
+        <v>2064</v>
       </c>
       <c r="B12" t="s">
-        <v>2020</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="52" customHeight="1">
       <c r="A13" t="s">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="B13" t="s">
-        <v>765</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="12.65" customHeight="1">
       <c r="A14" t="s">
+        <v>2066</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="12.65" customHeight="1">
+      <c r="A15" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="12.65" customHeight="1"/>
+    <row r="17" spans="1:3" ht="12.65" customHeight="1">
+      <c r="A17" s="408" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="12.65" customHeight="1">
+      <c r="B18" t="s">
+        <v>2017</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="25" customHeight="1">
+      <c r="A19" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B19">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="12.65" customHeight="1">
+      <c r="A20" t="s">
+        <v>2020</v>
+      </c>
+      <c r="B20">
+        <v>81</v>
+      </c>
+      <c r="C20" s="406">
+        <v>0.29599999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="25" customHeight="1">
+      <c r="A21" t="s">
+        <v>2021</v>
+      </c>
+      <c r="B21">
+        <v>11</v>
+      </c>
+      <c r="C21" s="406">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="12.65" customHeight="1">
+      <c r="A22" t="s">
         <v>2022</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B22">
+        <v>51</v>
+      </c>
+      <c r="C22" s="406">
+        <v>0.186</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="25" customHeight="1">
+      <c r="A23" t="s">
         <v>2023</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="12.65" customHeight="1"/>
-    <row r="16" spans="1:2" ht="12.65" customHeight="1">
-      <c r="A16" s="408" t="s">
+      <c r="B23">
+        <v>14</v>
+      </c>
+      <c r="C23" s="406">
+        <v>5.0999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="12.65" customHeight="1">
+      <c r="A24" t="s">
         <v>2024</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="12.65" customHeight="1">
-      <c r="B17" t="s">
+      <c r="B24">
+        <v>5</v>
+      </c>
+      <c r="C24" s="406">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="12.65" customHeight="1">
+      <c r="A25" t="s">
         <v>2025</v>
       </c>
-      <c r="C17" t="s">
+      <c r="B25">
+        <v>193</v>
+      </c>
+      <c r="C25" s="406">
+        <v>0.70399999999999996</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="12.65" customHeight="1"/>
+    <row r="27" spans="1:3" ht="12.65" customHeight="1">
+      <c r="A27" s="408" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="12.65" customHeight="1">
+      <c r="A28" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2070</v>
+      </c>
+      <c r="C28" s="406">
+        <v>0.95299999999999996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="12.65" customHeight="1">
+      <c r="A29" t="s">
+        <v>2071</v>
+      </c>
+      <c r="B29" t="s">
+        <v>2072</v>
+      </c>
+      <c r="C29" s="406">
+        <v>0.74099999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="12.65" customHeight="1">
+      <c r="A30" t="s">
+        <v>2073</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C30" s="406">
+        <v>0.39400000000000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="12.65" customHeight="1">
+      <c r="A31" t="s">
+        <v>2075</v>
+      </c>
+      <c r="B31" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C31" s="406">
+        <v>0.10199999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="12.65" customHeight="1"/>
+    <row r="33" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A33" s="408" t="s">
         <v>2026</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="12.65" customHeight="1">
-      <c r="A18" t="s">
-        <v>2027</v>
-      </c>
-      <c r="B18">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="25" customHeight="1">
-      <c r="A19" t="s">
-        <v>2028</v>
-      </c>
-      <c r="B19">
-        <v>79</v>
-      </c>
-      <c r="C19" s="406">
-        <v>0.29199999999999998</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="12.65" customHeight="1">
-      <c r="A20" t="s">
-        <v>2029</v>
-      </c>
-      <c r="B20">
-        <v>11</v>
-      </c>
-      <c r="C20" s="406">
-        <v>4.1000000000000002E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="25" customHeight="1">
-      <c r="A21" t="s">
-        <v>2030</v>
-      </c>
-      <c r="B21">
-        <v>50</v>
-      </c>
-      <c r="C21" s="406">
-        <v>0.185</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="12.65" customHeight="1">
-      <c r="A22" t="s">
-        <v>2031</v>
-      </c>
-      <c r="B22">
-        <v>12</v>
-      </c>
-      <c r="C22" s="406">
-        <v>4.3999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="25" customHeight="1">
-      <c r="A23" t="s">
-        <v>2032</v>
-      </c>
-      <c r="B23">
-        <v>6</v>
-      </c>
-      <c r="C23" s="406">
-        <v>2.1999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="12.65" customHeight="1">
-      <c r="A24" t="s">
-        <v>2033</v>
-      </c>
-      <c r="B24">
-        <v>192</v>
-      </c>
-      <c r="C24" s="406">
-        <v>0.70799999999999996</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="12.65" customHeight="1"/>
-    <row r="26" spans="1:7" ht="12.65" customHeight="1">
-      <c r="A26" s="408" t="s">
-        <v>2034</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="12.65" customHeight="1">
-      <c r="A27" t="s">
-        <v>2035</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="12.65" customHeight="1"/>
-    <row r="29" spans="1:7" ht="12.65" customHeight="1">
-      <c r="A29" s="408" t="s">
-        <v>2036</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="12.65" customHeight="1">
-      <c r="A30" t="s">
-        <v>2037</v>
-      </c>
-      <c r="B30" t="s">
-        <v>2038</v>
-      </c>
-      <c r="C30" t="s">
-        <v>2039</v>
-      </c>
-      <c r="D30" t="s">
-        <v>2040</v>
-      </c>
-      <c r="E30" t="s">
-        <v>2041</v>
-      </c>
-      <c r="F30" t="s">
-        <v>2042</v>
-      </c>
-      <c r="G30" t="s">
-        <v>2043</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="12.65" customHeight="1">
-      <c r="A31" t="s">
-        <v>138</v>
-      </c>
-      <c r="B31" t="s">
-        <v>2044</v>
-      </c>
-      <c r="D31" t="s">
-        <v>2045</v>
-      </c>
-      <c r="G31" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="12.65" customHeight="1">
-      <c r="A32" t="s">
-        <v>144</v>
-      </c>
-      <c r="B32" t="s">
-        <v>2044</v>
-      </c>
-      <c r="D32" t="s">
-        <v>2045</v>
-      </c>
-      <c r="F32" t="s">
-        <v>781</v>
-      </c>
-      <c r="G32" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="12.65" customHeight="1">
-      <c r="B33" t="s">
-        <v>2046</v>
-      </c>
-      <c r="C33" t="s">
-        <v>2045</v>
-      </c>
-      <c r="D33" t="s">
-        <v>2045</v>
-      </c>
-      <c r="G33" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="12.65" customHeight="1">
       <c r="A34" t="s">
-        <v>583</v>
-      </c>
-      <c r="B34" t="s">
-        <v>2046</v>
-      </c>
-      <c r="C34" t="s">
-        <v>1426</v>
-      </c>
-      <c r="D34" t="s">
-        <v>2045</v>
-      </c>
-      <c r="G34" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="12.65" customHeight="1">
-      <c r="A35" t="s">
-        <v>626</v>
-      </c>
-      <c r="B35" s="407">
-        <v>45788</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1426</v>
-      </c>
-      <c r="D35" t="s">
-        <v>2045</v>
-      </c>
-      <c r="F35" t="s">
-        <v>781</v>
-      </c>
-      <c r="G35" t="s">
-        <v>625</v>
-      </c>
-    </row>
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="36" spans="1:9" ht="12.65" customHeight="1">
-      <c r="A36" t="s">
-        <v>677</v>
-      </c>
-      <c r="B36" t="s">
-        <v>2047</v>
-      </c>
-      <c r="C36" t="s">
-        <v>1426</v>
-      </c>
-      <c r="D36" t="s">
-        <v>1426</v>
-      </c>
-      <c r="E36" t="s">
-        <v>48</v>
-      </c>
-      <c r="G36" t="s">
-        <v>137</v>
+      <c r="A36" s="408" t="s">
+        <v>2027</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="12.65" customHeight="1">
       <c r="A37" t="s">
-        <v>928</v>
+        <v>2028</v>
       </c>
       <c r="B37" t="s">
-        <v>2048</v>
+        <v>2078</v>
       </c>
       <c r="C37" t="s">
-        <v>1426</v>
+        <v>2029</v>
       </c>
       <c r="D37" t="s">
-        <v>2045</v>
+        <v>2030</v>
       </c>
       <c r="E37" t="s">
-        <v>48</v>
+        <v>2031</v>
       </c>
       <c r="F37" t="s">
-        <v>781</v>
+        <v>2032</v>
       </c>
       <c r="G37" t="s">
-        <v>927</v>
+        <v>2079</v>
+      </c>
+      <c r="H37" t="s">
+        <v>2080</v>
+      </c>
+      <c r="I37" t="s">
+        <v>2033</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="12.65" customHeight="1">
       <c r="A38" t="s">
-        <v>1106</v>
+        <v>138</v>
       </c>
       <c r="B38" t="s">
-        <v>2048</v>
-      </c>
-      <c r="C38" t="s">
-        <v>2045</v>
+        <v>2034</v>
       </c>
       <c r="D38" t="s">
-        <v>2045</v>
+        <v>2035</v>
       </c>
       <c r="E38" t="s">
-        <v>48</v>
-      </c>
-      <c r="F38" t="s">
-        <v>2049</v>
+        <v>31</v>
       </c>
       <c r="G38" t="s">
-        <v>143</v>
+        <v>136</v>
+      </c>
+      <c r="H38" t="s">
+        <v>33</v>
+      </c>
+      <c r="I38" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="12.65" customHeight="1">
       <c r="A39" t="s">
-        <v>1111</v>
+        <v>144</v>
       </c>
       <c r="B39" t="s">
-        <v>2048</v>
-      </c>
-      <c r="C39" t="s">
-        <v>2045</v>
+        <v>2034</v>
       </c>
       <c r="D39" t="s">
-        <v>2045</v>
+        <v>1426</v>
       </c>
       <c r="E39" t="s">
         <v>48</v>
       </c>
       <c r="F39" t="s">
-        <v>2049</v>
+        <v>781</v>
       </c>
       <c r="G39" t="s">
+        <v>32</v>
+      </c>
+      <c r="H39" t="s">
+        <v>33</v>
+      </c>
+      <c r="I39" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="12.65" customHeight="1">
-      <c r="A40" t="s">
-        <v>1528</v>
-      </c>
-      <c r="B40" s="407">
-        <v>46114</v>
+      <c r="B40" t="s">
+        <v>2036</v>
       </c>
       <c r="C40" t="s">
-        <v>1426</v>
+        <v>2035</v>
       </c>
       <c r="D40" t="s">
-        <v>2045</v>
-      </c>
-      <c r="F40" t="s">
-        <v>781</v>
+        <v>2035</v>
+      </c>
+      <c r="E40" t="s">
+        <v>31</v>
       </c>
       <c r="G40" t="s">
-        <v>137</v>
+        <v>387</v>
+      </c>
+      <c r="H40" t="s">
+        <v>33</v>
+      </c>
+      <c r="I40" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="12.65" customHeight="1">
       <c r="A41" t="s">
-        <v>1686</v>
-      </c>
-      <c r="B41" s="407">
-        <v>46144</v>
+        <v>583</v>
+      </c>
+      <c r="B41" t="s">
+        <v>2036</v>
       </c>
       <c r="C41" t="s">
         <v>1426</v>
       </c>
       <c r="D41" t="s">
-        <v>2045</v>
+        <v>2035</v>
       </c>
       <c r="E41" t="s">
         <v>48</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
+        <v>387</v>
+      </c>
+      <c r="H41" t="s">
+        <v>41</v>
+      </c>
+      <c r="I41" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A42" t="s">
+        <v>626</v>
+      </c>
+      <c r="B42" s="407">
+        <v>45788</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D42" t="s">
+        <v>2035</v>
+      </c>
+      <c r="E42" t="s">
+        <v>31</v>
+      </c>
+      <c r="F42" t="s">
         <v>781</v>
       </c>
-      <c r="G41" t="s">
+      <c r="G42" t="s">
+        <v>387</v>
+      </c>
+      <c r="H42" t="s">
+        <v>33</v>
+      </c>
+      <c r="I42" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A43" t="s">
+        <v>677</v>
+      </c>
+      <c r="B43" t="s">
+        <v>2037</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D43" t="s">
+        <v>1426</v>
+      </c>
+      <c r="E43" t="s">
+        <v>48</v>
+      </c>
+      <c r="G43" t="s">
+        <v>32</v>
+      </c>
+      <c r="H43" t="s">
+        <v>33</v>
+      </c>
+      <c r="I43" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A44" t="s">
+        <v>928</v>
+      </c>
+      <c r="B44" t="s">
+        <v>2038</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D44" t="s">
+        <v>2035</v>
+      </c>
+      <c r="E44" t="s">
+        <v>31</v>
+      </c>
+      <c r="F44" t="s">
+        <v>781</v>
+      </c>
+      <c r="G44" t="s">
+        <v>59</v>
+      </c>
+      <c r="H44" t="s">
+        <v>33</v>
+      </c>
+      <c r="I44" t="s">
         <v>927</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="12.65" customHeight="1"/>
-    <row r="43" spans="1:9" ht="12.65" customHeight="1">
-      <c r="A43" s="408" t="s">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="12.65" customHeight="1">
-      <c r="B44" t="s">
-        <v>2051</v>
-      </c>
-      <c r="C44" t="s">
-        <v>2052</v>
-      </c>
-      <c r="D44" t="s">
-        <v>2053</v>
-      </c>
-      <c r="E44" t="s">
-        <v>2054</v>
-      </c>
-      <c r="F44" t="s">
-        <v>2055</v>
-      </c>
-      <c r="G44" t="s">
-        <v>2056</v>
-      </c>
-      <c r="H44" t="s">
-        <v>2057</v>
-      </c>
-      <c r="I44" t="s">
-        <v>2058</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="12.65" customHeight="1">
       <c r="A45" t="s">
-        <v>1426</v>
-      </c>
-      <c r="B45">
-        <v>6</v>
-      </c>
-      <c r="C45">
-        <v>19</v>
-      </c>
-      <c r="D45">
-        <v>8</v>
-      </c>
-      <c r="E45">
-        <v>2</v>
-      </c>
-      <c r="F45">
-        <v>108</v>
-      </c>
-      <c r="G45">
+        <v>1106</v>
+      </c>
+      <c r="B45" t="s">
+        <v>2038</v>
+      </c>
+      <c r="C45" t="s">
+        <v>2035</v>
+      </c>
+      <c r="D45" t="s">
+        <v>2035</v>
+      </c>
+      <c r="E45" t="s">
+        <v>48</v>
+      </c>
+      <c r="F45" t="s">
+        <v>2039</v>
+      </c>
+      <c r="G45" t="s">
+        <v>237</v>
+      </c>
+      <c r="H45" t="s">
+        <v>33</v>
+      </c>
+      <c r="I45" t="s">
         <v>143</v>
-      </c>
-      <c r="H45">
-        <v>17.5</v>
-      </c>
-      <c r="I45">
-        <v>4.2</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="12.65" customHeight="1">
       <c r="A46" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B46">
-        <v>3</v>
-      </c>
-      <c r="C46">
-        <v>21</v>
-      </c>
-      <c r="D46">
-        <v>4</v>
-      </c>
-      <c r="E46">
-        <v>2</v>
-      </c>
-      <c r="F46">
-        <v>60</v>
-      </c>
-      <c r="G46">
-        <v>90</v>
-      </c>
-      <c r="H46">
-        <v>26.7</v>
-      </c>
-      <c r="I46">
-        <v>3.3</v>
+        <v>1111</v>
+      </c>
+      <c r="B46" t="s">
+        <v>2038</v>
+      </c>
+      <c r="C46" t="s">
+        <v>2035</v>
+      </c>
+      <c r="D46" t="s">
+        <v>2035</v>
+      </c>
+      <c r="E46" t="s">
+        <v>48</v>
+      </c>
+      <c r="F46" t="s">
+        <v>2039</v>
+      </c>
+      <c r="G46" t="s">
+        <v>136</v>
+      </c>
+      <c r="H46" t="s">
+        <v>33</v>
+      </c>
+      <c r="I46" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="12.65" customHeight="1">
       <c r="A47" t="s">
-        <v>2056</v>
-      </c>
-      <c r="B47">
-        <v>9</v>
-      </c>
-      <c r="C47">
-        <v>40</v>
-      </c>
-      <c r="D47">
-        <v>12</v>
-      </c>
-      <c r="E47">
-        <v>4</v>
-      </c>
-      <c r="F47">
-        <v>168</v>
-      </c>
-      <c r="G47">
-        <v>233</v>
-      </c>
-      <c r="H47">
-        <v>21</v>
-      </c>
-      <c r="I47">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="12.65" customHeight="1"/>
-    <row r="49" spans="1:9" ht="12.65" customHeight="1">
-      <c r="A49" s="408" t="s">
-        <v>2059</v>
-      </c>
-    </row>
+        <v>1528</v>
+      </c>
+      <c r="B47" s="407">
+        <v>46114</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D47" t="s">
+        <v>2035</v>
+      </c>
+      <c r="E47" t="s">
+        <v>31</v>
+      </c>
+      <c r="F47" t="s">
+        <v>781</v>
+      </c>
+      <c r="H47" t="s">
+        <v>33</v>
+      </c>
+      <c r="I47" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A48" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B48" s="407">
+        <v>46144</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D48" t="s">
+        <v>2035</v>
+      </c>
+      <c r="E48" t="s">
+        <v>31</v>
+      </c>
+      <c r="F48" t="s">
+        <v>781</v>
+      </c>
+      <c r="H48" t="s">
+        <v>33</v>
+      </c>
+      <c r="I48" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="50" spans="1:9" ht="12.65" customHeight="1">
-      <c r="B50" t="s">
-        <v>2051</v>
-      </c>
-      <c r="C50" t="s">
-        <v>2052</v>
-      </c>
-      <c r="D50" t="s">
-        <v>2053</v>
-      </c>
-      <c r="E50" t="s">
-        <v>2054</v>
-      </c>
-      <c r="F50" t="s">
-        <v>2055</v>
-      </c>
-      <c r="G50" t="s">
-        <v>2056</v>
-      </c>
-      <c r="H50" t="s">
-        <v>2057</v>
-      </c>
-      <c r="I50" t="s">
-        <v>2058</v>
+      <c r="A50" s="408" t="s">
+        <v>2040</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="12.65" customHeight="1">
-      <c r="A51" t="s">
-        <v>2060</v>
-      </c>
-      <c r="B51">
-        <v>0</v>
-      </c>
-      <c r="C51">
-        <v>2</v>
-      </c>
-      <c r="D51">
-        <v>0</v>
-      </c>
-      <c r="E51">
-        <v>0</v>
-      </c>
-      <c r="F51">
-        <v>16</v>
-      </c>
-      <c r="G51">
-        <v>18</v>
-      </c>
-      <c r="H51">
-        <v>11.1</v>
-      </c>
-      <c r="I51">
-        <v>0</v>
+      <c r="B51" t="s">
+        <v>2041</v>
+      </c>
+      <c r="C51" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D51" t="s">
+        <v>2043</v>
+      </c>
+      <c r="E51" t="s">
+        <v>2044</v>
+      </c>
+      <c r="F51" t="s">
+        <v>2045</v>
+      </c>
+      <c r="G51" t="s">
+        <v>2046</v>
+      </c>
+      <c r="H51" t="s">
+        <v>2047</v>
+      </c>
+      <c r="I51" t="s">
+        <v>2048</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="12.65" customHeight="1">
@@ -65450,425 +65437,425 @@
         <v>1426</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C52">
+        <v>19</v>
+      </c>
+      <c r="D52">
+        <v>8</v>
+      </c>
+      <c r="E52">
         <v>2</v>
       </c>
-      <c r="D52">
-        <v>3</v>
-      </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
       <c r="F52">
-        <v>13</v>
+        <v>109</v>
       </c>
       <c r="G52">
-        <v>19</v>
+        <v>144</v>
       </c>
       <c r="H52">
-        <v>15.8</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="I52">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="12.65" customHeight="1">
       <c r="A53" t="s">
-        <v>2045</v>
+        <v>2035</v>
       </c>
       <c r="B53">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C53">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D53">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E53">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F53">
-        <v>152</v>
+        <v>61</v>
       </c>
       <c r="G53">
-        <v>217</v>
+        <v>91</v>
       </c>
       <c r="H53">
-        <v>23.5</v>
+        <v>26.4</v>
       </c>
       <c r="I53">
-        <v>4.5999999999999996</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="12.65" customHeight="1">
       <c r="A54" t="s">
-        <v>2056</v>
+        <v>2046</v>
       </c>
       <c r="B54">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C54">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D54">
         <v>12</v>
       </c>
       <c r="E54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F54">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="G54">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="H54">
-        <v>22</v>
+        <v>20.9</v>
       </c>
       <c r="I54">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="56" spans="1:9" ht="12.65" customHeight="1">
       <c r="A56" s="408" t="s">
-        <v>2061</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="12.65" customHeight="1">
       <c r="B57" t="s">
-        <v>2051</v>
+        <v>2041</v>
       </c>
       <c r="C57" t="s">
-        <v>2052</v>
+        <v>2042</v>
       </c>
       <c r="D57" t="s">
-        <v>2053</v>
+        <v>2043</v>
       </c>
       <c r="E57" t="s">
-        <v>2054</v>
+        <v>2044</v>
       </c>
       <c r="F57" t="s">
-        <v>2055</v>
+        <v>2045</v>
       </c>
       <c r="G57" t="s">
-        <v>2056</v>
+        <v>2046</v>
       </c>
       <c r="H57" t="s">
-        <v>2057</v>
+        <v>2047</v>
       </c>
       <c r="I57" t="s">
-        <v>2058</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="12.65" customHeight="1">
       <c r="A58" t="s">
-        <v>48</v>
+        <v>1426</v>
       </c>
       <c r="B58">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C58">
         <v>8</v>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G58">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="H58">
-        <v>22.8</v>
+        <v>15.6</v>
       </c>
       <c r="I58">
-        <v>8.8000000000000007</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="12.65" customHeight="1">
       <c r="A59" t="s">
-        <v>31</v>
+        <v>2035</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C59">
+        <v>37</v>
+      </c>
+      <c r="D59">
+        <v>8</v>
+      </c>
+      <c r="E59">
         <v>4</v>
       </c>
-      <c r="D59">
-        <v>3</v>
-      </c>
-      <c r="E59">
-        <v>0</v>
-      </c>
       <c r="F59">
-        <v>26</v>
+        <v>134</v>
       </c>
       <c r="G59">
-        <v>33</v>
+        <v>192</v>
       </c>
       <c r="H59">
-        <v>12.1</v>
+        <v>24</v>
       </c>
       <c r="I59">
-        <v>0</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="12.65" customHeight="1">
       <c r="A60" t="s">
-        <v>2056</v>
+        <v>2046</v>
       </c>
       <c r="B60">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C60">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="D60">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F60">
-        <v>67</v>
+        <v>183</v>
       </c>
       <c r="G60">
-        <v>90</v>
+        <v>256</v>
       </c>
       <c r="H60">
-        <v>18.899999999999999</v>
+        <v>21.9</v>
       </c>
       <c r="I60">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="62" spans="1:9" ht="12.65" customHeight="1">
       <c r="A62" s="408" t="s">
-        <v>2062</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="12.65" customHeight="1">
       <c r="B63" t="s">
-        <v>2051</v>
+        <v>2041</v>
       </c>
       <c r="C63" t="s">
-        <v>2052</v>
+        <v>2042</v>
       </c>
       <c r="D63" t="s">
-        <v>2053</v>
+        <v>2043</v>
       </c>
       <c r="E63" t="s">
-        <v>2054</v>
+        <v>2044</v>
       </c>
       <c r="F63" t="s">
-        <v>2055</v>
+        <v>2045</v>
       </c>
       <c r="G63" t="s">
-        <v>2056</v>
+        <v>2046</v>
       </c>
       <c r="H63" t="s">
-        <v>2057</v>
+        <v>2047</v>
       </c>
       <c r="I63" t="s">
-        <v>2058</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="12.65" customHeight="1">
       <c r="A64" t="s">
-        <v>1752</v>
+        <v>48</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F64">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="G64">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="H64">
-        <v>28.6</v>
+        <v>21.6</v>
       </c>
       <c r="I64">
-        <v>14.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="12.65" customHeight="1">
       <c r="A65" t="s">
-        <v>1631</v>
+        <v>31</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F65">
-        <v>9</v>
+        <v>103</v>
       </c>
       <c r="G65">
-        <v>9</v>
+        <v>150</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>24.7</v>
       </c>
       <c r="I65">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="12.65" customHeight="1">
       <c r="A66" t="s">
-        <v>1616</v>
+        <v>2046</v>
       </c>
       <c r="B66">
+        <v>11</v>
+      </c>
+      <c r="C66">
+        <v>50</v>
+      </c>
+      <c r="D66">
+        <v>13</v>
+      </c>
+      <c r="E66">
+        <v>5</v>
+      </c>
+      <c r="F66">
+        <v>182</v>
+      </c>
+      <c r="G66">
+        <v>261</v>
+      </c>
+      <c r="H66">
+        <v>23.4</v>
+      </c>
+      <c r="I66">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="68" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A68" s="408" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="12.65" customHeight="1">
+      <c r="B69" t="s">
+        <v>2041</v>
+      </c>
+      <c r="C69" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D69" t="s">
+        <v>2043</v>
+      </c>
+      <c r="E69" t="s">
+        <v>2044</v>
+      </c>
+      <c r="F69" t="s">
+        <v>2045</v>
+      </c>
+      <c r="G69" t="s">
+        <v>2046</v>
+      </c>
+      <c r="H69" t="s">
+        <v>2047</v>
+      </c>
+      <c r="I69" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A70" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70">
         <v>0</v>
       </c>
-      <c r="C66">
+      <c r="E70">
         <v>0</v>
       </c>
-      <c r="D66">
-        <v>0</v>
-      </c>
-      <c r="E66">
-        <v>0</v>
-      </c>
-      <c r="F66">
-        <v>9</v>
-      </c>
-      <c r="G66">
-        <v>9</v>
-      </c>
-      <c r="H66">
-        <v>0</v>
-      </c>
-      <c r="I66">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="12.65" customHeight="1">
-      <c r="A67" t="s">
-        <v>2056</v>
-      </c>
-      <c r="B67">
-        <v>1</v>
-      </c>
-      <c r="C67">
-        <v>1</v>
-      </c>
-      <c r="D67">
-        <v>0</v>
-      </c>
-      <c r="E67">
-        <v>0</v>
-      </c>
-      <c r="F67">
-        <v>23</v>
-      </c>
-      <c r="G67">
+      <c r="F70">
+        <v>6</v>
+      </c>
+      <c r="G70">
+        <v>8</v>
+      </c>
+      <c r="H70">
         <v>25</v>
       </c>
-      <c r="H67">
-        <v>8</v>
-      </c>
-      <c r="I67">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="12.65" customHeight="1"/>
-    <row r="69" spans="1:9" ht="12.65" customHeight="1">
-      <c r="A69" s="408" t="s">
-        <v>2063</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="12.65" customHeight="1">
-      <c r="B70" t="s">
-        <v>2051</v>
-      </c>
-      <c r="C70" t="s">
-        <v>2052</v>
-      </c>
-      <c r="D70" t="s">
-        <v>2053</v>
-      </c>
-      <c r="E70" t="s">
-        <v>2054</v>
-      </c>
-      <c r="F70" t="s">
-        <v>2055</v>
-      </c>
-      <c r="G70" t="s">
-        <v>2056</v>
-      </c>
-      <c r="H70" t="s">
-        <v>2057</v>
-      </c>
-      <c r="I70" t="s">
-        <v>2058</v>
+      <c r="I70">
+        <v>12.5</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="12.65" customHeight="1">
       <c r="A71" t="s">
-        <v>781</v>
+        <v>1631</v>
       </c>
       <c r="B71">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C71">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D71">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="G71">
-        <v>136</v>
+        <v>11</v>
       </c>
       <c r="H71">
-        <v>22.1</v>
+        <v>9.1</v>
       </c>
       <c r="I71">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="12.65" customHeight="1">
       <c r="A72" t="s">
-        <v>1105</v>
+        <v>1616</v>
       </c>
       <c r="B72">
         <v>0</v>
       </c>
       <c r="C72">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -65877,13 +65864,13 @@
         <v>0</v>
       </c>
       <c r="F72">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G72">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H72">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -65891,274 +65878,274 @@
     </row>
     <row r="73" spans="1:9" ht="12.65" customHeight="1">
       <c r="A73" t="s">
-        <v>2049</v>
+        <v>2046</v>
       </c>
       <c r="B73">
+        <v>1</v>
+      </c>
+      <c r="C73">
         <v>2</v>
       </c>
-      <c r="C73">
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>25</v>
+      </c>
+      <c r="G73">
+        <v>28</v>
+      </c>
+      <c r="H73">
+        <v>10.7</v>
+      </c>
+      <c r="I73">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="75" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A75" s="408" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="12.65" customHeight="1">
+      <c r="B76" t="s">
+        <v>2041</v>
+      </c>
+      <c r="C76" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D76" t="s">
+        <v>2043</v>
+      </c>
+      <c r="E76" t="s">
+        <v>2044</v>
+      </c>
+      <c r="F76" t="s">
+        <v>2045</v>
+      </c>
+      <c r="G76" t="s">
+        <v>2046</v>
+      </c>
+      <c r="H76" t="s">
+        <v>2047</v>
+      </c>
+      <c r="I76" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A77" t="s">
+        <v>781</v>
+      </c>
+      <c r="B77">
+        <v>5</v>
+      </c>
+      <c r="C77">
+        <v>25</v>
+      </c>
+      <c r="D77">
         <v>6</v>
       </c>
-      <c r="D73">
-        <v>3</v>
-      </c>
-      <c r="E73">
+      <c r="E77">
+        <v>1</v>
+      </c>
+      <c r="F77">
+        <v>100</v>
+      </c>
+      <c r="G77">
+        <v>137</v>
+      </c>
+      <c r="H77">
+        <v>21.9</v>
+      </c>
+      <c r="I77">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A78" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B78">
+        <v>0</v>
+      </c>
+      <c r="C78">
         <v>2</v>
       </c>
-      <c r="F73">
-        <v>38</v>
-      </c>
-      <c r="G73">
-        <v>51</v>
-      </c>
-      <c r="H73">
-        <v>15.7</v>
-      </c>
-      <c r="I73">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="12.65" customHeight="1">
-      <c r="A74" t="s">
-        <v>1458</v>
-      </c>
-      <c r="B74">
+      <c r="D78">
         <v>0</v>
       </c>
-      <c r="C74">
-        <v>3</v>
-      </c>
-      <c r="D74">
+      <c r="E78">
         <v>0</v>
       </c>
-      <c r="E74">
+      <c r="F78">
+        <v>2</v>
+      </c>
+      <c r="G78">
+        <v>4</v>
+      </c>
+      <c r="H78">
+        <v>50</v>
+      </c>
+      <c r="I78">
         <v>0</v>
-      </c>
-      <c r="F74">
-        <v>10</v>
-      </c>
-      <c r="G74">
-        <v>13</v>
-      </c>
-      <c r="H74">
-        <v>23.1</v>
-      </c>
-      <c r="I74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="12.65" customHeight="1">
-      <c r="A75" t="s">
-        <v>2056</v>
-      </c>
-      <c r="B75">
-        <v>7</v>
-      </c>
-      <c r="C75">
-        <v>36</v>
-      </c>
-      <c r="D75">
-        <v>9</v>
-      </c>
-      <c r="E75">
-        <v>3</v>
-      </c>
-      <c r="F75">
-        <v>149</v>
-      </c>
-      <c r="G75">
-        <v>204</v>
-      </c>
-      <c r="H75">
-        <v>21.1</v>
-      </c>
-      <c r="I75">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="12.65" customHeight="1"/>
-    <row r="77" spans="1:9" ht="12.65" customHeight="1">
-      <c r="A77" s="408" t="s">
-        <v>2064</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="12.65" customHeight="1">
-      <c r="B78" t="s">
-        <v>2051</v>
-      </c>
-      <c r="C78" t="s">
-        <v>2052</v>
-      </c>
-      <c r="D78" t="s">
-        <v>2053</v>
-      </c>
-      <c r="E78" t="s">
-        <v>2054</v>
-      </c>
-      <c r="F78" t="s">
-        <v>2055</v>
-      </c>
-      <c r="G78" t="s">
-        <v>2056</v>
-      </c>
-      <c r="H78" t="s">
-        <v>2057</v>
-      </c>
-      <c r="I78" t="s">
-        <v>2058</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="12.65" customHeight="1">
       <c r="A79" t="s">
-        <v>2065</v>
+        <v>2039</v>
       </c>
       <c r="B79">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C79">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D79">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E79">
         <v>2</v>
       </c>
       <c r="F79">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="G79">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="H79">
-        <v>26.7</v>
+        <v>17.3</v>
       </c>
       <c r="I79">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="12.65" customHeight="1">
       <c r="A80" t="s">
-        <v>2066</v>
+        <v>1458</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C80">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D80">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E80">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F80">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="G80">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="H80">
-        <v>20.399999999999999</v>
+        <v>23.1</v>
       </c>
       <c r="I80">
-        <v>1.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="12.65" customHeight="1">
       <c r="A81" t="s">
-        <v>2067</v>
+        <v>2046</v>
       </c>
       <c r="B81">
+        <v>7</v>
+      </c>
+      <c r="C81">
+        <v>37</v>
+      </c>
+      <c r="D81">
+        <v>9</v>
+      </c>
+      <c r="E81">
         <v>3</v>
       </c>
-      <c r="C81">
+      <c r="F81">
+        <v>150</v>
+      </c>
+      <c r="G81">
+        <v>206</v>
+      </c>
+      <c r="H81">
+        <v>21.4</v>
+      </c>
+      <c r="I81">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="83" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A83" s="408" t="s">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="12.65" customHeight="1">
+      <c r="B84" t="s">
+        <v>2041</v>
+      </c>
+      <c r="C84" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D84" t="s">
+        <v>2043</v>
+      </c>
+      <c r="E84" t="s">
+        <v>2044</v>
+      </c>
+      <c r="F84" t="s">
+        <v>2045</v>
+      </c>
+      <c r="G84" t="s">
+        <v>2046</v>
+      </c>
+      <c r="H84" t="s">
+        <v>2047</v>
+      </c>
+      <c r="I84" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A85" t="s">
+        <v>2054</v>
+      </c>
+      <c r="B85">
+        <v>6</v>
+      </c>
+      <c r="C85">
+        <v>22</v>
+      </c>
+      <c r="D85">
         <v>8</v>
       </c>
-      <c r="D81">
-        <v>2</v>
-      </c>
-      <c r="E81">
+      <c r="E85">
         <v>1</v>
       </c>
-      <c r="F81">
-        <v>44</v>
-      </c>
-      <c r="G81">
-        <v>58</v>
-      </c>
-      <c r="H81">
-        <v>19</v>
-      </c>
-      <c r="I81">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ht="12.65" customHeight="1">
-      <c r="A82" t="s">
-        <v>2056</v>
-      </c>
-      <c r="B82">
-        <v>11</v>
-      </c>
-      <c r="C82">
-        <v>50</v>
-      </c>
-      <c r="D82">
-        <v>12</v>
-      </c>
-      <c r="E82">
-        <v>6</v>
-      </c>
-      <c r="F82">
-        <v>192</v>
-      </c>
-      <c r="G82">
-        <v>271</v>
-      </c>
-      <c r="H82">
-        <v>22.5</v>
-      </c>
-      <c r="I82">
-        <v>4.0999999999999996</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" ht="12.65" customHeight="1"/>
-    <row r="84" spans="1:9" ht="12.65" customHeight="1">
-      <c r="A84" s="408" t="s">
-        <v>2068</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" ht="12.65" customHeight="1">
-      <c r="B85" t="s">
-        <v>2051</v>
-      </c>
-      <c r="C85" t="s">
-        <v>2052</v>
-      </c>
-      <c r="D85" t="s">
-        <v>2053</v>
-      </c>
-      <c r="E85" t="s">
-        <v>2054</v>
-      </c>
-      <c r="F85" t="s">
+      <c r="F85">
+        <v>68</v>
+      </c>
+      <c r="G85">
+        <v>105</v>
+      </c>
+      <c r="H85">
+        <v>26.7</v>
+      </c>
+      <c r="I85">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A86" t="s">
         <v>2055</v>
-      </c>
-      <c r="G85" t="s">
-        <v>2056</v>
-      </c>
-      <c r="H85" t="s">
-        <v>2057</v>
-      </c>
-      <c r="I85" t="s">
-        <v>2058</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" ht="12.65" customHeight="1">
-      <c r="A86" t="b">
-        <v>0</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -66170,257 +66157,861 @@
         <v>4</v>
       </c>
       <c r="E86">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F86">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="G86">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="H86">
-        <v>25.8</v>
+        <v>20.7</v>
       </c>
       <c r="I86">
-        <v>2.2000000000000002</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="12.65" customHeight="1">
-      <c r="A87" t="b">
-        <v>1</v>
+      <c r="A87" t="s">
+        <v>2056</v>
       </c>
       <c r="B87">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C87">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="D87">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E87">
         <v>1</v>
       </c>
       <c r="F87">
-        <v>135</v>
+        <v>44</v>
       </c>
       <c r="G87">
-        <v>182</v>
+        <v>58</v>
       </c>
       <c r="H87">
-        <v>20.9</v>
+        <v>19</v>
       </c>
       <c r="I87">
-        <v>4.9000000000000004</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="12.65" customHeight="1">
       <c r="A88" t="s">
-        <v>2056</v>
+        <v>2046</v>
       </c>
       <c r="B88">
         <v>11</v>
       </c>
       <c r="C88">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D88">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E88">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F88">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G88">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="H88">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="I88">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="90" spans="1:9" ht="12.65" customHeight="1">
       <c r="A90" s="408" t="s">
-        <v>2069</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" ht="12.65" customHeight="1"/>
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="12.65" customHeight="1">
+      <c r="B91" t="s">
+        <v>2041</v>
+      </c>
+      <c r="C91" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D91" t="s">
+        <v>2043</v>
+      </c>
+      <c r="E91" t="s">
+        <v>2044</v>
+      </c>
+      <c r="F91" t="s">
+        <v>2045</v>
+      </c>
+      <c r="G91" t="s">
+        <v>2046</v>
+      </c>
+      <c r="H91" t="s">
+        <v>2047</v>
+      </c>
+      <c r="I91" t="s">
+        <v>2048</v>
+      </c>
+    </row>
     <row r="92" spans="1:9" ht="12.65" customHeight="1">
-      <c r="A92" t="s">
-        <v>2070</v>
+      <c r="A92" t="b">
+        <v>0</v>
+      </c>
+      <c r="B92">
+        <v>2</v>
+      </c>
+      <c r="C92">
+        <v>22</v>
+      </c>
+      <c r="D92">
+        <v>5</v>
+      </c>
+      <c r="E92">
+        <v>4</v>
+      </c>
+      <c r="F92">
+        <v>58</v>
+      </c>
+      <c r="G92">
+        <v>91</v>
+      </c>
+      <c r="H92">
+        <v>26.4</v>
+      </c>
+      <c r="I92">
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="12.65" customHeight="1">
-      <c r="A93" t="s">
-        <v>2071</v>
+      <c r="A93" t="b">
+        <v>1</v>
+      </c>
+      <c r="B93">
+        <v>9</v>
+      </c>
+      <c r="C93">
+        <v>29</v>
+      </c>
+      <c r="D93">
+        <v>9</v>
+      </c>
+      <c r="E93">
+        <v>1</v>
+      </c>
+      <c r="F93">
+        <v>135</v>
+      </c>
+      <c r="G93">
+        <v>183</v>
+      </c>
+      <c r="H93">
+        <v>20.8</v>
+      </c>
+      <c r="I93">
+        <v>4.9000000000000004</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="12.65" customHeight="1">
-      <c r="A94" s="408" t="s">
-        <v>2072</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" ht="12.65" customHeight="1">
-      <c r="A95" t="s">
-        <v>2073</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" ht="12.65" customHeight="1"/>
-    <row r="97" spans="1:1" ht="12.65" customHeight="1">
-      <c r="A97" t="s">
-        <v>2074</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" ht="12.65" customHeight="1">
+      <c r="A94" t="s">
+        <v>2046</v>
+      </c>
+      <c r="B94">
+        <v>11</v>
+      </c>
+      <c r="C94">
+        <v>51</v>
+      </c>
+      <c r="D94">
+        <v>14</v>
+      </c>
+      <c r="E94">
+        <v>5</v>
+      </c>
+      <c r="F94">
+        <v>193</v>
+      </c>
+      <c r="G94">
+        <v>274</v>
+      </c>
+      <c r="H94">
+        <v>22.6</v>
+      </c>
+      <c r="I94">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="96" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A96" s="408" t="s">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="12.65" customHeight="1">
+      <c r="B97" t="s">
+        <v>2041</v>
+      </c>
+      <c r="C97" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D97" t="s">
+        <v>2043</v>
+      </c>
+      <c r="E97" t="s">
+        <v>2044</v>
+      </c>
+      <c r="F97" t="s">
+        <v>2045</v>
+      </c>
+      <c r="G97" t="s">
+        <v>2046</v>
+      </c>
+      <c r="H97" t="s">
+        <v>2047</v>
+      </c>
+      <c r="I97" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="12.65" customHeight="1">
       <c r="A98" t="s">
-        <v>2075</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" ht="12.65" customHeight="1">
+        <v>32</v>
+      </c>
+      <c r="B98">
+        <v>2</v>
+      </c>
+      <c r="C98">
+        <v>8</v>
+      </c>
+      <c r="D98">
+        <v>5</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98">
+        <v>42</v>
+      </c>
+      <c r="G98">
+        <v>57</v>
+      </c>
+      <c r="H98">
+        <v>17.5</v>
+      </c>
+      <c r="I98">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="12.65" customHeight="1">
       <c r="A99" t="s">
-        <v>2076</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" ht="12.65" customHeight="1">
+        <v>237</v>
+      </c>
+      <c r="B99">
+        <v>1</v>
+      </c>
+      <c r="C99">
+        <v>4</v>
+      </c>
+      <c r="D99">
+        <v>1</v>
+      </c>
+      <c r="E99">
+        <v>2</v>
+      </c>
+      <c r="F99">
+        <v>20</v>
+      </c>
+      <c r="G99">
+        <v>28</v>
+      </c>
+      <c r="H99">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="I99">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="12.65" customHeight="1">
       <c r="A100" t="s">
-        <v>2077</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" ht="12.65" customHeight="1"/>
-    <row r="102" spans="1:1" ht="12.65" customHeight="1">
+        <v>59</v>
+      </c>
+      <c r="B100">
+        <v>1</v>
+      </c>
+      <c r="C100">
+        <v>3</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <v>4</v>
+      </c>
+      <c r="G100">
+        <v>8</v>
+      </c>
+      <c r="H100">
+        <v>50</v>
+      </c>
+      <c r="I100">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A101" t="s">
+        <v>174</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <v>2</v>
+      </c>
+      <c r="G101">
+        <v>2</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="12.65" customHeight="1">
       <c r="A102" t="s">
-        <v>2078</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" ht="12.65" customHeight="1">
+        <v>136</v>
+      </c>
+      <c r="B102">
+        <v>2</v>
+      </c>
+      <c r="C102">
+        <v>13</v>
+      </c>
+      <c r="D102">
+        <v>3</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102">
+        <v>44</v>
+      </c>
+      <c r="G102">
+        <v>62</v>
+      </c>
+      <c r="H102">
+        <v>24.2</v>
+      </c>
+      <c r="I102">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="12.65" customHeight="1">
       <c r="A103" t="s">
-        <v>2079</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" ht="12.65" customHeight="1"/>
-    <row r="105" spans="1:1" ht="12.65" customHeight="1">
-      <c r="A105" s="408" t="s">
-        <v>2080</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" ht="12.65" customHeight="1">
+        <v>1036</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+      <c r="C103">
+        <v>1</v>
+      </c>
+      <c r="D103">
+        <v>1</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>4</v>
+      </c>
+      <c r="G103">
+        <v>6</v>
+      </c>
+      <c r="H103">
+        <v>16.7</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A104" t="s">
+        <v>160</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+      <c r="C104">
+        <v>5</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="E104">
+        <v>1</v>
+      </c>
+      <c r="F104">
+        <v>8</v>
+      </c>
+      <c r="G104">
+        <v>14</v>
+      </c>
+      <c r="H104">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A105" t="s">
+        <v>387</v>
+      </c>
+      <c r="B105">
+        <v>3</v>
+      </c>
+      <c r="C105">
+        <v>6</v>
+      </c>
+      <c r="D105">
+        <v>2</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>15</v>
+      </c>
+      <c r="G105">
+        <v>26</v>
+      </c>
+      <c r="H105">
+        <v>34.6</v>
+      </c>
+      <c r="I105">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="12.65" customHeight="1">
       <c r="A106" t="s">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" ht="12.65" customHeight="1">
-      <c r="A107" t="s">
+        <v>2046</v>
+      </c>
+      <c r="B106">
+        <v>9</v>
+      </c>
+      <c r="C106">
+        <v>40</v>
+      </c>
+      <c r="D106">
+        <v>12</v>
+      </c>
+      <c r="E106">
+        <v>3</v>
+      </c>
+      <c r="F106">
+        <v>139</v>
+      </c>
+      <c r="G106">
+        <v>203</v>
+      </c>
+      <c r="H106">
+        <v>24.1</v>
+      </c>
+      <c r="I106">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="108" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A108" s="408" t="s">
         <v>2082</v>
       </c>
     </row>
-    <row r="108" spans="1:1" ht="12.65" customHeight="1"/>
-    <row r="109" spans="1:1" ht="12.65" customHeight="1">
-      <c r="A109" t="s">
+    <row r="109" spans="1:9" ht="12.65" customHeight="1">
+      <c r="B109" t="s">
+        <v>2041</v>
+      </c>
+      <c r="C109" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D109" t="s">
+        <v>2043</v>
+      </c>
+      <c r="E109" t="s">
+        <v>2044</v>
+      </c>
+      <c r="F109" t="s">
+        <v>2045</v>
+      </c>
+      <c r="G109" t="s">
+        <v>2046</v>
+      </c>
+      <c r="H109" t="s">
+        <v>2047</v>
+      </c>
+      <c r="I109" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A110" t="s">
+        <v>33</v>
+      </c>
+      <c r="B110">
+        <v>10</v>
+      </c>
+      <c r="C110">
+        <v>16</v>
+      </c>
+      <c r="D110">
+        <v>3</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>34</v>
+      </c>
+      <c r="G110">
+        <v>63</v>
+      </c>
+      <c r="H110">
+        <v>41.3</v>
+      </c>
+      <c r="I110">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A111" t="s">
+        <v>49</v>
+      </c>
+      <c r="B111">
+        <v>0</v>
+      </c>
+      <c r="C111">
+        <v>5</v>
+      </c>
+      <c r="D111">
+        <v>2</v>
+      </c>
+      <c r="E111">
+        <v>1</v>
+      </c>
+      <c r="F111">
+        <v>5</v>
+      </c>
+      <c r="G111">
+        <v>13</v>
+      </c>
+      <c r="H111">
+        <v>38.5</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A112" t="s">
+        <v>112</v>
+      </c>
+      <c r="B112">
+        <v>0</v>
+      </c>
+      <c r="C112">
+        <v>4</v>
+      </c>
+      <c r="D112">
+        <v>1</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112">
+        <v>5</v>
+      </c>
+      <c r="G112">
+        <v>10</v>
+      </c>
+      <c r="H112">
+        <v>40</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A113" t="s">
+        <v>41</v>
+      </c>
+      <c r="B113">
+        <v>1</v>
+      </c>
+      <c r="C113">
+        <v>5</v>
+      </c>
+      <c r="D113">
+        <v>3</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113">
+        <v>13</v>
+      </c>
+      <c r="G113">
+        <v>22</v>
+      </c>
+      <c r="H113">
+        <v>27.3</v>
+      </c>
+      <c r="I113">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A114" t="s">
+        <v>2046</v>
+      </c>
+      <c r="B114">
+        <v>11</v>
+      </c>
+      <c r="C114">
+        <v>30</v>
+      </c>
+      <c r="D114">
+        <v>9</v>
+      </c>
+      <c r="E114">
+        <v>1</v>
+      </c>
+      <c r="F114">
+        <v>57</v>
+      </c>
+      <c r="G114">
+        <v>108</v>
+      </c>
+      <c r="H114">
+        <v>38</v>
+      </c>
+      <c r="I114">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="116" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A116" s="408" t="s">
         <v>2083</v>
       </c>
     </row>
-    <row r="110" spans="1:1" ht="12.65" customHeight="1">
-      <c r="A110" s="408" t="s">
+    <row r="117" spans="1:9" ht="12.65" customHeight="1">
+      <c r="B117" t="s">
+        <v>2041</v>
+      </c>
+      <c r="C117" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D117" t="s">
+        <v>2043</v>
+      </c>
+      <c r="E117" t="s">
+        <v>2044</v>
+      </c>
+      <c r="F117" t="s">
+        <v>2045</v>
+      </c>
+      <c r="G117" t="s">
+        <v>2046</v>
+      </c>
+      <c r="H117" t="s">
+        <v>2047</v>
+      </c>
+      <c r="I117" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A118" t="s">
         <v>2084</v>
       </c>
-    </row>
-    <row r="111" spans="1:1" ht="12.65" customHeight="1"/>
-    <row r="112" spans="1:1" ht="12.65" customHeight="1">
-      <c r="A112" t="s">
+      <c r="B118">
+        <v>2</v>
+      </c>
+      <c r="C118">
+        <v>8</v>
+      </c>
+      <c r="D118">
+        <v>5</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <v>42</v>
+      </c>
+      <c r="G118">
+        <v>57</v>
+      </c>
+      <c r="H118">
+        <v>17.5</v>
+      </c>
+      <c r="I118">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A119" t="s">
         <v>2085</v>
       </c>
-    </row>
-    <row r="113" spans="1:1" ht="12.65" customHeight="1">
-      <c r="A113" t="s">
+      <c r="B119">
+        <v>7</v>
+      </c>
+      <c r="C119">
+        <v>32</v>
+      </c>
+      <c r="D119">
+        <v>7</v>
+      </c>
+      <c r="E119">
+        <v>3</v>
+      </c>
+      <c r="F119">
+        <v>97</v>
+      </c>
+      <c r="G119">
+        <v>146</v>
+      </c>
+      <c r="H119">
+        <v>26.7</v>
+      </c>
+      <c r="I119">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A120" t="s">
+        <v>2046</v>
+      </c>
+      <c r="B120">
+        <v>9</v>
+      </c>
+      <c r="C120">
+        <v>40</v>
+      </c>
+      <c r="D120">
+        <v>12</v>
+      </c>
+      <c r="E120">
+        <v>3</v>
+      </c>
+      <c r="F120">
+        <v>139</v>
+      </c>
+      <c r="G120">
+        <v>203</v>
+      </c>
+      <c r="H120">
+        <v>24.1</v>
+      </c>
+      <c r="I120">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="122" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A122" s="408" t="s">
         <v>2086</v>
       </c>
     </row>
-    <row r="114" spans="1:1" ht="12.65" customHeight="1">
-      <c r="A114" t="s">
+    <row r="123" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="124" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A124" s="408" t="s">
         <v>2087</v>
       </c>
     </row>
-    <row r="115" spans="1:1" ht="12.65" customHeight="1">
-      <c r="A115" s="408" t="s">
+    <row r="125" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A125" s="408" t="s">
         <v>2088</v>
       </c>
     </row>
-    <row r="116" spans="1:1" ht="12.65" customHeight="1">
-      <c r="A116" t="s">
+    <row r="126" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="127" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A127" t="s">
         <v>2089</v>
       </c>
     </row>
-    <row r="117" spans="1:1" ht="12.65" customHeight="1"/>
-    <row r="118" spans="1:1" ht="12.65" customHeight="1">
-      <c r="A118" t="s">
+    <row r="128" spans="1:9" ht="12.65" customHeight="1">
+      <c r="A128" t="s">
         <v>2090</v>
       </c>
     </row>
-    <row r="119" spans="1:1" ht="12.65" customHeight="1">
-      <c r="A119" t="s">
+    <row r="129" spans="1:1" ht="12.65" customHeight="1">
+      <c r="A129" t="s">
         <v>2091</v>
       </c>
     </row>
-    <row r="120" spans="1:1" ht="12.65" customHeight="1"/>
-    <row r="121" spans="1:1" ht="12.65" customHeight="1">
-      <c r="A121" t="s">
+    <row r="130" spans="1:1" ht="12.65" customHeight="1">
+      <c r="A130" t="s">
         <v>2092</v>
       </c>
     </row>
-    <row r="122" spans="1:1" ht="12.65" customHeight="1">
-      <c r="A122" s="408" t="s">
+    <row r="131" spans="1:1" ht="12.65" customHeight="1">
+      <c r="A131" t="s">
         <v>2093</v>
       </c>
     </row>
-    <row r="123" spans="1:1" ht="12.65" customHeight="1">
-      <c r="A123" t="s">
+    <row r="132" spans="1:1" ht="12.65" customHeight="1">
+      <c r="A132" t="s">
         <v>2094</v>
       </c>
     </row>
-    <row r="124" spans="1:1" ht="12.65" customHeight="1">
-      <c r="A124" t="s">
+    <row r="133" spans="1:1" ht="12.65" customHeight="1">
+      <c r="A133" t="s">
         <v>2095</v>
       </c>
     </row>
-    <row r="125" spans="1:1" ht="12.65" customHeight="1"/>
-    <row r="126" spans="1:1" ht="12.65" customHeight="1">
-      <c r="A126" t="s">
+    <row r="134" spans="1:1" ht="12.65" customHeight="1">
+      <c r="A134" t="s">
         <v>2096</v>
       </c>
     </row>
-    <row r="127" spans="1:1" ht="12.65" customHeight="1">
-      <c r="A127" t="s">
+    <row r="135" spans="1:1" ht="12.65" customHeight="1">
+      <c r="A135" t="s">
         <v>2097</v>
       </c>
     </row>
-    <row r="128" spans="1:1" ht="12.65" customHeight="1">
-      <c r="A128" t="s">
+    <row r="136" spans="1:1" ht="12.65" customHeight="1">
+      <c r="A136" t="s">
         <v>2098</v>
       </c>
     </row>
-    <row r="129" spans="1:1" ht="12.65" customHeight="1">
-      <c r="A129" s="408" t="s">
+    <row r="137" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="138" spans="1:1" ht="12.65" customHeight="1">
+      <c r="A138" s="408" t="s">
         <v>2099</v>
       </c>
     </row>
-    <row r="130" spans="1:1" ht="12.65" customHeight="1">
-      <c r="A130" s="408" t="s">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1" ht="12.65" customHeight="1"/>
-    <row r="132" spans="1:1" ht="12.65" customHeight="1"/>
-    <row r="133" spans="1:1" ht="12.65" customHeight="1"/>
-    <row r="134" spans="1:1" ht="12.65" customHeight="1"/>
-    <row r="135" spans="1:1" ht="12.65" customHeight="1"/>
-    <row r="136" spans="1:1" ht="12.65" customHeight="1"/>
-    <row r="137" spans="1:1" ht="12.65" customHeight="1"/>
-    <row r="138" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="139" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="140" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="141" spans="1:1" ht="12.65" customHeight="1"/>

--- a/j-busqueda clientes/j-clientes-gle.xlsx
+++ b/j-busqueda clientes/j-clientes-gle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88153b17ae7a9f01/documentos/TRABAJOS AUTONOMOS/JURADA/j-busqueda clientes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1398" documentId="13_ncr:1_{DF388099-A258-48E4-8A4C-6C022E777824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57F3A1CB-0EF8-42A6-BA25-0394A92EFD2F}"/>
+  <xr:revisionPtr revIDLastSave="1416" documentId="13_ncr:1_{DF388099-A258-48E4-8A4C-6C022E777824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DF9117F-7C92-49CB-84D9-AA2BCC5880B1}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="-110" windowWidth="24900" windowHeight="14900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   <definedNames>
     <definedName name="DatosExternos_1" localSheetId="0">clientes!$A$1:$Y$58</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3784" uniqueCount="2156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3794" uniqueCount="2160">
   <si>
     <t>fechaEmail</t>
   </si>
@@ -6555,6 +6555,18 @@
   </si>
   <si>
     <t>Web 403. Traductores inglés/árabe/francés, colaboradores países árabes. Versión francesa del sitio. Clientela principal árabe/francófona. Inglés secundario, sin evidencia clientes UK/US.</t>
+  </si>
+  <si>
+    <t>info@perezdevargas.es / marbella@perezdevargas.com / estepona@perezdevargas.com</t>
+  </si>
+  <si>
+    <t>FBERNAL Abogados</t>
+  </si>
+  <si>
+    <t>Pedro Fernández</t>
+  </si>
+  <si>
+    <t>pedrofernandez@abogaciaextranjeria.es</t>
   </si>
 </sst>
 </file>
@@ -26801,12 +26813,18 @@
       <c r="AG313" s="84"/>
     </row>
     <row r="314" spans="1:33" ht="11.5" customHeight="1">
-      <c r="A314" s="414"/>
+      <c r="A314" s="412">
+        <v>46077</v>
+      </c>
       <c r="B314" s="289"/>
       <c r="C314" s="289"/>
       <c r="D314" s="86"/>
-      <c r="E314" s="87"/>
-      <c r="F314" s="87"/>
+      <c r="E314" s="87" t="s">
+        <v>26</v>
+      </c>
+      <c r="F314" s="87" t="s">
+        <v>55</v>
+      </c>
       <c r="G314" s="87"/>
       <c r="H314" s="201" t="s">
         <v>2096</v>
@@ -27025,12 +27043,18 @@
       <c r="AG318" s="97"/>
     </row>
     <row r="319" spans="1:33" ht="11.5" customHeight="1">
-      <c r="A319" s="412"/>
+      <c r="A319" s="412">
+        <v>46077</v>
+      </c>
       <c r="B319" s="288"/>
       <c r="C319" s="288"/>
       <c r="D319" s="81"/>
-      <c r="E319" s="82"/>
-      <c r="F319" s="82"/>
+      <c r="E319" s="82" t="s">
+        <v>26</v>
+      </c>
+      <c r="F319" s="82" t="s">
+        <v>55</v>
+      </c>
       <c r="G319" s="82"/>
       <c r="H319" s="199" t="s">
         <v>2109</v>
@@ -27127,6 +27151,9 @@
         <v>2114</v>
       </c>
       <c r="J321" s="201"/>
+      <c r="K321" s="200" t="s">
+        <v>2156</v>
+      </c>
       <c r="L321" s="201" t="s">
         <v>2120</v>
       </c>
@@ -27157,19 +27184,33 @@
       <c r="AG321" s="87"/>
     </row>
     <row r="322" spans="1:33" ht="11.5" customHeight="1">
-      <c r="A322" s="425"/>
+      <c r="A322" s="412">
+        <v>46077</v>
+      </c>
       <c r="B322" s="290"/>
       <c r="C322" s="290"/>
       <c r="D322" s="88"/>
       <c r="E322" s="89"/>
       <c r="F322" s="89"/>
       <c r="G322" s="89"/>
-      <c r="H322" s="198"/>
-      <c r="J322" s="198"/>
+      <c r="H322" s="198" t="s">
+        <v>2157</v>
+      </c>
+      <c r="I322" s="200" t="s">
+        <v>1729</v>
+      </c>
+      <c r="J322" s="198" t="s">
+        <v>2158</v>
+      </c>
+      <c r="K322" s="200" t="s">
+        <v>2159</v>
+      </c>
       <c r="L322" s="198"/>
       <c r="M322" s="256"/>
       <c r="N322" s="89"/>
-      <c r="O322" s="89"/>
+      <c r="O322" s="89" t="s">
+        <v>1703</v>
+      </c>
       <c r="P322" s="89"/>
       <c r="Q322" s="89"/>
       <c r="R322" s="89"/>

--- a/j-busqueda clientes/j-clientes-gle.xlsx
+++ b/j-busqueda clientes/j-clientes-gle.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88153b17ae7a9f01/documentos/TRABAJOS AUTONOMOS/JURADA/j-busqueda clientes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="11_A7EF37BD59B216A1919E58397C9D2DAA6E9EA21E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9538D6FD-5157-4423-957F-0B85042B97DC}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{0AFA8464-F26A-41CE-9FAC-2E395A515B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4925D569-AD13-4800-8678-F6DA847A4DA4}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="-110" windowWidth="24900" windowHeight="14500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5267" uniqueCount="3070">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5269" uniqueCount="3070">
   <si>
     <t>fechaEmail</t>
   </si>
@@ -9310,7 +9310,7 @@
     <numFmt numFmtId="167" formatCode="d\-m\-yy;@"/>
     <numFmt numFmtId="168" formatCode="d\-m\-yyyy"/>
   </numFmts>
-  <fonts count="57">
+  <fonts count="58">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -9662,6 +9662,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="26">
     <fill>
@@ -9906,7 +9913,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="454">
+  <cellXfs count="456">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -11209,6 +11216,12 @@
     <xf numFmtId="0" fontId="55" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="57" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -11225,10 +11238,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20239,7 +20248,7 @@
       <c r="F149" s="104" t="s">
         <v>58</v>
       </c>
-      <c r="G149" s="113" t="s">
+      <c r="G149" s="455" t="s">
         <v>97</v>
       </c>
       <c r="H149" s="143" t="s">
@@ -20443,14 +20452,18 @@
       <c r="C153" s="365" t="s">
         <v>776</v>
       </c>
-      <c r="D153" s="108"/>
+      <c r="D153" s="108">
+        <v>46086</v>
+      </c>
       <c r="E153" s="81" t="s">
         <v>27</v>
       </c>
       <c r="F153" s="81" t="s">
         <v>58</v>
       </c>
-      <c r="G153" s="81"/>
+      <c r="G153" s="416" t="s">
+        <v>97</v>
+      </c>
       <c r="H153" s="142" t="s">
         <v>913</v>
       </c>
@@ -31718,14 +31731,18 @@
       </c>
       <c r="B344" s="204"/>
       <c r="C344" s="380"/>
-      <c r="D344" s="86"/>
+      <c r="D344" s="86">
+        <v>46080</v>
+      </c>
       <c r="E344" s="88" t="s">
         <v>27</v>
       </c>
       <c r="F344" s="88" t="s">
         <v>58</v>
       </c>
-      <c r="G344" s="88"/>
+      <c r="G344" s="403" t="s">
+        <v>27</v>
+      </c>
       <c r="H344" s="122" t="s">
         <v>2095</v>
       </c>
@@ -32491,7 +32508,7 @@
         <v>1780</v>
       </c>
       <c r="P354" s="420"/>
-      <c r="Q354" s="420" t="s">
+      <c r="Q354" s="402" t="s">
         <v>2228</v>
       </c>
       <c r="R354" s="420"/>
@@ -32749,7 +32766,7 @@
       <c r="J358" s="119" t="s">
         <v>2300</v>
       </c>
-      <c r="K358" s="120" t="s">
+      <c r="K358" s="454" t="s">
         <v>2301</v>
       </c>
       <c r="L358" s="119" t="s">

--- a/j-busqueda clientes/j-clientes-gle.xlsx
+++ b/j-busqueda clientes/j-clientes-gle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rocio\OneDrive\documentos\TRABAJOS AUTONOMOS\JURADA\j-busqueda clientes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A2029E-8E0C-4E20-9F58-3C284BA7BF17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0691193-CE52-40CA-AC12-5DD3C742F909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1260" yWindow="-120" windowWidth="27660" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5266" uniqueCount="3069">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5268" uniqueCount="3071">
   <si>
     <t>fechaEmail</t>
   </si>
@@ -9294,6 +9294,12 @@
   </si>
   <si>
     <t>1-1n</t>
+  </si>
+  <si>
+    <t>tarifas ofrecidas</t>
+  </si>
+  <si>
+    <t>0,11/ pal / 30-40 por doc</t>
   </si>
 </sst>
 </file>
@@ -9910,7 +9916,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="456">
+  <cellXfs count="457">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -11219,6 +11225,9 @@
     <xf numFmtId="0" fontId="55" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -11546,7 +11555,9 @@
       <c r="AA1" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="26"/>
+      <c r="AB1" s="415" t="s">
+        <v>3069</v>
+      </c>
       <c r="AC1" s="26"/>
       <c r="AD1" s="26"/>
       <c r="AE1" s="26"/>
@@ -27266,7 +27277,9 @@
       <c r="AA270" s="360" t="s">
         <v>34</v>
       </c>
-      <c r="AB270" s="360"/>
+      <c r="AB270" s="456" t="s">
+        <v>3070</v>
+      </c>
       <c r="AC270" s="360"/>
       <c r="AD270" s="360"/>
       <c r="AE270" s="360"/>

--- a/j-busqueda clientes/j-clientes-gle.xlsx
+++ b/j-busqueda clientes/j-clientes-gle.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rocio\OneDrive\documentos\TRABAJOS AUTONOMOS\JURADA\j-busqueda clientes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0691193-CE52-40CA-AC12-5DD3C742F909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F773AF29-691D-415A-A88F-79748947A016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1260" yWindow="-120" windowWidth="27660" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5268" uniqueCount="3071">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5269" uniqueCount="3071">
   <si>
     <t>fechaEmail</t>
   </si>
@@ -18320,14 +18320,18 @@
         <v>45987</v>
       </c>
       <c r="C115" s="365"/>
-      <c r="D115" s="109"/>
+      <c r="D115" s="109">
+        <v>46114</v>
+      </c>
       <c r="E115" s="102" t="s">
         <v>27</v>
       </c>
       <c r="F115" s="102" t="s">
         <v>27</v>
       </c>
-      <c r="G115" s="102"/>
+      <c r="G115" s="85" t="s">
+        <v>939</v>
+      </c>
       <c r="H115" s="124" t="s">
         <v>726</v>
       </c>

--- a/j-busqueda clientes/j-clientes-gle.xlsx
+++ b/j-busqueda clientes/j-clientes-gle.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rocio\OneDrive\documentos\TRABAJOS AUTONOMOS\JURADA\j-busqueda clientes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88153b17ae7a9f01/documentos/TRABAJOS AUTONOMOS/JURADA/j-busqueda clientes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F773AF29-691D-415A-A88F-79748947A016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{F773AF29-691D-415A-A88F-79748947A016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FDA778A-416F-4906-B6BE-1896C6F37542}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="-120" windowWidth="27660" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="810" yWindow="-110" windowWidth="24900" windowHeight="14500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="clientes" sheetId="1" r:id="rId1"/>
@@ -11446,31 +11446,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:AG534"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="11.45" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="11.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.140625" style="411" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" style="350" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" style="390" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" style="75" customWidth="1"/>
-    <col min="5" max="5" width="4.42578125" style="75" customWidth="1"/>
-    <col min="6" max="6" width="4.140625" style="75" customWidth="1"/>
-    <col min="7" max="7" width="5.140625" style="75" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" style="125" customWidth="1"/>
+    <col min="1" max="1" width="10.1796875" style="411" customWidth="1"/>
+    <col min="2" max="2" width="10.26953125" style="350" customWidth="1"/>
+    <col min="3" max="3" width="9.54296875" style="390" customWidth="1"/>
+    <col min="4" max="4" width="13.26953125" style="75" customWidth="1"/>
+    <col min="5" max="5" width="4.453125" style="75" customWidth="1"/>
+    <col min="6" max="6" width="4.1796875" style="75" customWidth="1"/>
+    <col min="7" max="7" width="5.1796875" style="75" customWidth="1"/>
+    <col min="8" max="8" width="16.54296875" style="125" customWidth="1"/>
     <col min="9" max="9" width="18" style="120" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" style="125" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" style="120" customWidth="1"/>
-    <col min="12" max="12" width="13.85546875" style="125" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" style="198" customWidth="1"/>
-    <col min="14" max="14" width="3.7109375" style="75" customWidth="1"/>
-    <col min="15" max="15" width="4.5703125" style="75" customWidth="1"/>
-    <col min="16" max="16" width="7.85546875" style="75" customWidth="1"/>
-    <col min="17" max="17" width="17.5703125" style="435" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="75" customWidth="1"/>
-    <col min="19" max="23" width="7.28515625" style="75" customWidth="1"/>
-    <col min="24" max="25" width="7.28515625" style="75" hidden="1" customWidth="1"/>
-    <col min="26" max="33" width="7.28515625" style="75" customWidth="1"/>
-    <col min="34" max="45" width="14.42578125" style="75" customWidth="1"/>
-    <col min="46" max="16384" width="14.42578125" style="75"/>
+    <col min="10" max="10" width="9.54296875" style="125" customWidth="1"/>
+    <col min="11" max="11" width="15.81640625" style="120" customWidth="1"/>
+    <col min="12" max="12" width="13.81640625" style="125" customWidth="1"/>
+    <col min="13" max="13" width="6.81640625" style="198" customWidth="1"/>
+    <col min="14" max="14" width="3.7265625" style="75" customWidth="1"/>
+    <col min="15" max="15" width="4.54296875" style="75" customWidth="1"/>
+    <col min="16" max="16" width="7.81640625" style="75" customWidth="1"/>
+    <col min="17" max="17" width="17.54296875" style="435" customWidth="1"/>
+    <col min="18" max="18" width="14.453125" style="75" customWidth="1"/>
+    <col min="19" max="23" width="7.26953125" style="75" customWidth="1"/>
+    <col min="24" max="25" width="7.26953125" style="75" hidden="1" customWidth="1"/>
+    <col min="26" max="33" width="7.26953125" style="75" customWidth="1"/>
+    <col min="34" max="45" width="14.453125" style="75" customWidth="1"/>
+    <col min="46" max="16384" width="14.453125" style="75"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="26.25" customHeight="1">
@@ -11564,7 +11564,7 @@
       <c r="AF1" s="26"/>
       <c r="AG1" s="26"/>
     </row>
-    <row r="2" spans="1:33" ht="11.45" customHeight="1">
+    <row r="2" spans="1:33" ht="11.5" customHeight="1">
       <c r="A2" s="209">
         <v>45770</v>
       </c>
@@ -11621,7 +11621,7 @@
       <c r="AF2" s="102"/>
       <c r="AG2" s="102"/>
     </row>
-    <row r="3" spans="1:33" ht="11.45" customHeight="1">
+    <row r="3" spans="1:33" ht="11.5" customHeight="1">
       <c r="A3" s="205">
         <v>46000</v>
       </c>
@@ -11676,7 +11676,7 @@
       <c r="AF3" s="104"/>
       <c r="AG3" s="104"/>
     </row>
-    <row r="4" spans="1:33" ht="11.45" customHeight="1">
+    <row r="4" spans="1:33" ht="11.5" customHeight="1">
       <c r="A4" s="207">
         <v>45776</v>
       </c>
@@ -11733,7 +11733,7 @@
       <c r="AF4" s="106"/>
       <c r="AG4" s="106"/>
     </row>
-    <row r="5" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="5" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A5" s="267">
         <v>45756</v>
       </c>
@@ -11792,7 +11792,7 @@
       <c r="AF5" s="263"/>
       <c r="AG5" s="263"/>
     </row>
-    <row r="6" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="6" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A6" s="270">
         <v>46000</v>
       </c>
@@ -11843,7 +11843,7 @@
       <c r="AF6" s="272"/>
       <c r="AG6" s="272"/>
     </row>
-    <row r="7" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="7" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A7" s="230">
         <v>46000</v>
       </c>
@@ -11896,7 +11896,7 @@
       <c r="AF7" s="274"/>
       <c r="AG7" s="274"/>
     </row>
-    <row r="8" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="8" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A8" s="275"/>
       <c r="B8" s="275"/>
       <c r="C8" s="371"/>
@@ -11939,7 +11939,7 @@
       <c r="AF8" s="277"/>
       <c r="AG8" s="277"/>
     </row>
-    <row r="9" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="9" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A9" s="278"/>
       <c r="B9" s="278"/>
       <c r="C9" s="372"/>
@@ -11982,7 +11982,7 @@
       <c r="AF9" s="248"/>
       <c r="AG9" s="248"/>
     </row>
-    <row r="10" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="10" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A10" s="280"/>
       <c r="B10" s="280"/>
       <c r="C10" s="373"/>
@@ -12023,7 +12023,7 @@
       <c r="AF10" s="282"/>
       <c r="AG10" s="282"/>
     </row>
-    <row r="11" spans="1:33" s="286" customFormat="1" ht="11.45" customHeight="1">
+    <row r="11" spans="1:33" s="286" customFormat="1" ht="11.5" customHeight="1">
       <c r="A11" s="283">
         <v>45756</v>
       </c>
@@ -12086,7 +12086,7 @@
       <c r="AF11" s="285"/>
       <c r="AG11" s="285"/>
     </row>
-    <row r="12" spans="1:33" s="286" customFormat="1" ht="11.45" customHeight="1">
+    <row r="12" spans="1:33" s="286" customFormat="1" ht="11.5" customHeight="1">
       <c r="A12" s="283">
         <v>46059</v>
       </c>
@@ -12139,7 +12139,7 @@
       <c r="AF12" s="285"/>
       <c r="AG12" s="285"/>
     </row>
-    <row r="13" spans="1:33" s="286" customFormat="1" ht="11.45" customHeight="1">
+    <row r="13" spans="1:33" s="286" customFormat="1" ht="11.5" customHeight="1">
       <c r="A13" s="289">
         <v>46001</v>
       </c>
@@ -12190,7 +12190,7 @@
       <c r="AF13" s="291"/>
       <c r="AG13" s="291"/>
     </row>
-    <row r="14" spans="1:33" s="286" customFormat="1" ht="11.45" customHeight="1">
+    <row r="14" spans="1:33" s="286" customFormat="1" ht="11.5" customHeight="1">
       <c r="A14" s="289" t="s">
         <v>89</v>
       </c>
@@ -12239,7 +12239,7 @@
       <c r="AF14" s="291"/>
       <c r="AG14" s="291"/>
     </row>
-    <row r="15" spans="1:33" ht="11.45" customHeight="1">
+    <row r="15" spans="1:33" ht="11.5" customHeight="1">
       <c r="A15" s="203">
         <v>46000</v>
       </c>
@@ -12283,7 +12283,7 @@
       <c r="AF15" s="56"/>
       <c r="AG15" s="56"/>
     </row>
-    <row r="16" spans="1:33" ht="11.45" customHeight="1">
+    <row r="16" spans="1:33" ht="11.5" customHeight="1">
       <c r="A16" s="214">
         <v>46056</v>
       </c>
@@ -12330,7 +12330,7 @@
       <c r="AF16" s="81"/>
       <c r="AG16" s="81"/>
     </row>
-    <row r="17" spans="1:33" ht="11.45" customHeight="1">
+    <row r="17" spans="1:33" ht="11.5" customHeight="1">
       <c r="A17" s="209">
         <v>45757</v>
       </c>
@@ -12391,7 +12391,7 @@
       <c r="AF17" s="102"/>
       <c r="AG17" s="102"/>
     </row>
-    <row r="18" spans="1:33" ht="11.45" customHeight="1">
+    <row r="18" spans="1:33" ht="11.5" customHeight="1">
       <c r="A18" s="205">
         <v>45770</v>
       </c>
@@ -12447,7 +12447,7 @@
       <c r="AF18" s="104"/>
       <c r="AG18" s="104"/>
     </row>
-    <row r="19" spans="1:33" ht="11.45" customHeight="1">
+    <row r="19" spans="1:33" ht="11.5" customHeight="1">
       <c r="A19" s="207">
         <v>45770</v>
       </c>
@@ -12504,7 +12504,7 @@
       <c r="AF19" s="106"/>
       <c r="AG19" s="106"/>
     </row>
-    <row r="20" spans="1:33" ht="11.45" customHeight="1">
+    <row r="20" spans="1:33" ht="11.5" customHeight="1">
       <c r="A20" s="203">
         <v>46351</v>
       </c>
@@ -12567,7 +12567,7 @@
       <c r="AF20" s="56"/>
       <c r="AG20" s="56"/>
     </row>
-    <row r="21" spans="1:33" ht="11.45" customHeight="1">
+    <row r="21" spans="1:33" ht="11.5" customHeight="1">
       <c r="A21" s="206">
         <v>45770</v>
       </c>
@@ -12632,7 +12632,7 @@
       <c r="AF21" s="78"/>
       <c r="AG21" s="78"/>
     </row>
-    <row r="22" spans="1:33" ht="11.45" customHeight="1">
+    <row r="22" spans="1:33" ht="11.5" customHeight="1">
       <c r="A22" s="204">
         <v>45924</v>
       </c>
@@ -12694,7 +12694,7 @@
       <c r="AF22" s="88"/>
       <c r="AG22" s="88"/>
     </row>
-    <row r="23" spans="1:33" s="302" customFormat="1" ht="11.45" customHeight="1">
+    <row r="23" spans="1:33" s="302" customFormat="1" ht="11.5" customHeight="1">
       <c r="A23" s="298">
         <v>45770</v>
       </c>
@@ -12755,7 +12755,7 @@
       <c r="AF23" s="300"/>
       <c r="AG23" s="300"/>
     </row>
-    <row r="24" spans="1:33" ht="11.45" customHeight="1">
+    <row r="24" spans="1:33" ht="11.5" customHeight="1">
       <c r="A24" s="214">
         <v>45770</v>
       </c>
@@ -12820,7 +12820,7 @@
       <c r="AF24" s="81"/>
       <c r="AG24" s="81"/>
     </row>
-    <row r="25" spans="1:33" ht="11.45" customHeight="1">
+    <row r="25" spans="1:33" ht="11.5" customHeight="1">
       <c r="A25" s="209">
         <v>45770</v>
       </c>
@@ -12885,7 +12885,7 @@
       <c r="AF25" s="102"/>
       <c r="AG25" s="102"/>
     </row>
-    <row r="26" spans="1:33" ht="11.45" customHeight="1">
+    <row r="26" spans="1:33" ht="11.5" customHeight="1">
       <c r="A26" s="205">
         <v>45930</v>
       </c>
@@ -12946,7 +12946,7 @@
       <c r="AF26" s="104"/>
       <c r="AG26" s="104"/>
     </row>
-    <row r="27" spans="1:33" ht="11.45" customHeight="1">
+    <row r="27" spans="1:33" ht="11.5" customHeight="1">
       <c r="A27" s="207"/>
       <c r="B27" s="207"/>
       <c r="C27" s="367"/>
@@ -12989,7 +12989,7 @@
       <c r="AF27" s="106"/>
       <c r="AG27" s="106"/>
     </row>
-    <row r="28" spans="1:33" ht="11.45" customHeight="1">
+    <row r="28" spans="1:33" ht="11.5" customHeight="1">
       <c r="A28" s="206">
         <v>45790</v>
       </c>
@@ -13054,7 +13054,7 @@
       <c r="AF28" s="78"/>
       <c r="AG28" s="78"/>
     </row>
-    <row r="29" spans="1:33" ht="11.45" customHeight="1">
+    <row r="29" spans="1:33" ht="11.5" customHeight="1">
       <c r="A29" s="204">
         <v>45778</v>
       </c>
@@ -13123,7 +13123,7 @@
       <c r="AF29" s="88"/>
       <c r="AG29" s="88"/>
     </row>
-    <row r="30" spans="1:33" ht="11.45" customHeight="1">
+    <row r="30" spans="1:33" ht="11.5" customHeight="1">
       <c r="A30" s="203">
         <v>45814</v>
       </c>
@@ -13198,7 +13198,7 @@
       <c r="AF30" s="56"/>
       <c r="AG30" s="56"/>
     </row>
-    <row r="31" spans="1:33" ht="11.45" customHeight="1">
+    <row r="31" spans="1:33" ht="11.5" customHeight="1">
       <c r="A31" s="214">
         <v>45924</v>
       </c>
@@ -13259,7 +13259,7 @@
       <c r="AF31" s="81"/>
       <c r="AG31" s="81"/>
     </row>
-    <row r="32" spans="1:33" ht="11.45" customHeight="1">
+    <row r="32" spans="1:33" ht="11.5" customHeight="1">
       <c r="A32" s="209">
         <v>45924</v>
       </c>
@@ -13314,7 +13314,7 @@
       <c r="AF32" s="102"/>
       <c r="AG32" s="102"/>
     </row>
-    <row r="33" spans="1:33" ht="11.45" customHeight="1">
+    <row r="33" spans="1:33" ht="11.5" customHeight="1">
       <c r="A33" s="205"/>
       <c r="B33" s="205"/>
       <c r="C33" s="366"/>
@@ -13358,7 +13358,7 @@
       <c r="AF33" s="104"/>
       <c r="AG33" s="104"/>
     </row>
-    <row r="34" spans="1:33" ht="11.45" customHeight="1">
+    <row r="34" spans="1:33" ht="11.5" customHeight="1">
       <c r="A34" s="207">
         <v>45805</v>
       </c>
@@ -13421,7 +13421,7 @@
       <c r="AF34" s="106"/>
       <c r="AG34" s="106"/>
     </row>
-    <row r="35" spans="1:33" ht="11.45" customHeight="1">
+    <row r="35" spans="1:33" ht="11.5" customHeight="1">
       <c r="A35" s="206"/>
       <c r="B35" s="206">
         <v>46001</v>
@@ -13484,7 +13484,7 @@
       <c r="AF35" s="78"/>
       <c r="AG35" s="78"/>
     </row>
-    <row r="36" spans="1:33" ht="11.45" customHeight="1">
+    <row r="36" spans="1:33" ht="11.5" customHeight="1">
       <c r="A36" s="203"/>
       <c r="B36" s="203"/>
       <c r="C36" s="377"/>
@@ -13531,7 +13531,7 @@
       <c r="AF36" s="56"/>
       <c r="AG36" s="56"/>
     </row>
-    <row r="37" spans="1:33" ht="11.45" customHeight="1">
+    <row r="37" spans="1:33" ht="11.5" customHeight="1">
       <c r="A37" s="214">
         <v>45924</v>
       </c>
@@ -13596,7 +13596,7 @@
       <c r="AF37" s="81"/>
       <c r="AG37" s="81"/>
     </row>
-    <row r="38" spans="1:33" ht="11.45" customHeight="1">
+    <row r="38" spans="1:33" ht="11.5" customHeight="1">
       <c r="A38" s="209">
         <v>45810</v>
       </c>
@@ -13649,7 +13649,7 @@
       <c r="AF38" s="102"/>
       <c r="AG38" s="102"/>
     </row>
-    <row r="39" spans="1:33" ht="11.45" customHeight="1">
+    <row r="39" spans="1:33" ht="11.5" customHeight="1">
       <c r="A39" s="205">
         <v>45909</v>
       </c>
@@ -13708,7 +13708,7 @@
       <c r="AF39" s="104"/>
       <c r="AG39" s="104"/>
     </row>
-    <row r="40" spans="1:33" ht="11.45" customHeight="1">
+    <row r="40" spans="1:33" ht="11.5" customHeight="1">
       <c r="A40" s="207"/>
       <c r="B40" s="207">
         <v>45924</v>
@@ -13748,7 +13748,7 @@
       <c r="AF40" s="106"/>
       <c r="AG40" s="106"/>
     </row>
-    <row r="41" spans="1:33" ht="11.45" customHeight="1">
+    <row r="41" spans="1:33" ht="11.5" customHeight="1">
       <c r="A41" s="206"/>
       <c r="B41" s="206"/>
       <c r="C41" s="382"/>
@@ -13795,7 +13795,7 @@
       <c r="AF41" s="78"/>
       <c r="AG41" s="78"/>
     </row>
-    <row r="42" spans="1:33" ht="11.45" customHeight="1">
+    <row r="42" spans="1:33" ht="11.5" customHeight="1">
       <c r="A42" s="304">
         <v>45833</v>
       </c>
@@ -13860,7 +13860,7 @@
       <c r="AF42" s="306"/>
       <c r="AG42" s="306"/>
     </row>
-    <row r="43" spans="1:33" ht="11.45" customHeight="1">
+    <row r="43" spans="1:33" ht="11.5" customHeight="1">
       <c r="A43" s="203">
         <v>45812</v>
       </c>
@@ -13927,7 +13927,7 @@
       <c r="AF43" s="56"/>
       <c r="AG43" s="56"/>
     </row>
-    <row r="44" spans="1:33" ht="11.45" customHeight="1">
+    <row r="44" spans="1:33" ht="11.5" customHeight="1">
       <c r="A44" s="214"/>
       <c r="B44" s="214"/>
       <c r="C44" s="378"/>
@@ -13974,7 +13974,7 @@
       <c r="AF44" s="81"/>
       <c r="AG44" s="81"/>
     </row>
-    <row r="45" spans="1:33" ht="11.45" customHeight="1">
+    <row r="45" spans="1:33" ht="11.5" customHeight="1">
       <c r="A45" s="209">
         <v>45826</v>
       </c>
@@ -14037,7 +14037,7 @@
       <c r="AF45" s="102"/>
       <c r="AG45" s="102"/>
     </row>
-    <row r="46" spans="1:33" ht="11.45" customHeight="1">
+    <row r="46" spans="1:33" ht="11.5" customHeight="1">
       <c r="A46" s="205">
         <v>45840</v>
       </c>
@@ -14100,7 +14100,7 @@
       <c r="AF46" s="104"/>
       <c r="AG46" s="104"/>
     </row>
-    <row r="47" spans="1:33" ht="11.45" customHeight="1">
+    <row r="47" spans="1:33" ht="11.5" customHeight="1">
       <c r="A47" s="207">
         <v>45840</v>
       </c>
@@ -14157,7 +14157,7 @@
       <c r="AF47" s="106"/>
       <c r="AG47" s="106"/>
     </row>
-    <row r="48" spans="1:33" ht="11.45" customHeight="1">
+    <row r="48" spans="1:33" ht="11.5" customHeight="1">
       <c r="A48" s="206">
         <v>45840</v>
       </c>
@@ -14214,7 +14214,7 @@
       <c r="AF48" s="78"/>
       <c r="AG48" s="78"/>
     </row>
-    <row r="49" spans="1:33" ht="11.45" customHeight="1">
+    <row r="49" spans="1:33" ht="11.5" customHeight="1">
       <c r="A49" s="204">
         <v>45840</v>
       </c>
@@ -14277,7 +14277,7 @@
       <c r="AF49" s="88"/>
       <c r="AG49" s="88"/>
     </row>
-    <row r="50" spans="1:33" ht="11.45" customHeight="1" thickBot="1">
+    <row r="50" spans="1:33" ht="11.5" customHeight="1" thickBot="1">
       <c r="A50" s="203">
         <v>45846</v>
       </c>
@@ -14336,7 +14336,7 @@
       <c r="AF50" s="56"/>
       <c r="AG50" s="56"/>
     </row>
-    <row r="51" spans="1:33" ht="11.45" customHeight="1" thickBot="1">
+    <row r="51" spans="1:33" ht="11.5" customHeight="1" thickBot="1">
       <c r="A51" s="214"/>
       <c r="B51" s="214"/>
       <c r="C51" s="378"/>
@@ -14383,7 +14383,7 @@
       <c r="AF51" s="81"/>
       <c r="AG51" s="81"/>
     </row>
-    <row r="52" spans="1:33" ht="11.45" customHeight="1">
+    <row r="52" spans="1:33" ht="11.5" customHeight="1">
       <c r="A52" s="209">
         <v>45846</v>
       </c>
@@ -14444,7 +14444,7 @@
       <c r="AF52" s="102"/>
       <c r="AG52" s="102"/>
     </row>
-    <row r="53" spans="1:33" ht="11.45" customHeight="1">
+    <row r="53" spans="1:33" ht="11.5" customHeight="1">
       <c r="A53" s="205">
         <v>45909</v>
       </c>
@@ -14501,7 +14501,7 @@
       <c r="AF53" s="104"/>
       <c r="AG53" s="104"/>
     </row>
-    <row r="54" spans="1:33" ht="11.45" customHeight="1">
+    <row r="54" spans="1:33" ht="11.5" customHeight="1">
       <c r="A54" s="207"/>
       <c r="B54" s="207"/>
       <c r="C54" s="367"/>
@@ -14543,7 +14543,7 @@
       <c r="AF54" s="106"/>
       <c r="AG54" s="106"/>
     </row>
-    <row r="55" spans="1:33" ht="11.45" customHeight="1">
+    <row r="55" spans="1:33" ht="11.5" customHeight="1">
       <c r="A55" s="206">
         <v>45909</v>
       </c>
@@ -14604,7 +14604,7 @@
       <c r="AF55" s="78"/>
       <c r="AG55" s="78"/>
     </row>
-    <row r="56" spans="1:33" ht="11.45" customHeight="1">
+    <row r="56" spans="1:33" ht="11.5" customHeight="1">
       <c r="A56" s="204"/>
       <c r="B56" s="204"/>
       <c r="C56" s="380"/>
@@ -14653,7 +14653,7 @@
       <c r="AF56" s="88"/>
       <c r="AG56" s="88"/>
     </row>
-    <row r="57" spans="1:33" ht="11.45" customHeight="1">
+    <row r="57" spans="1:33" ht="11.5" customHeight="1">
       <c r="A57" s="203">
         <v>45909</v>
       </c>
@@ -14718,7 +14718,7 @@
       <c r="AF57" s="56"/>
       <c r="AG57" s="56"/>
     </row>
-    <row r="58" spans="1:33" ht="11.45" customHeight="1">
+    <row r="58" spans="1:33" ht="11.5" customHeight="1">
       <c r="A58" s="214">
         <v>45959</v>
       </c>
@@ -14777,7 +14777,7 @@
       <c r="AF58" s="81"/>
       <c r="AG58" s="81"/>
     </row>
-    <row r="59" spans="1:33" ht="11.45" customHeight="1">
+    <row r="59" spans="1:33" ht="11.5" customHeight="1">
       <c r="A59" s="209">
         <v>45909</v>
       </c>
@@ -14842,7 +14842,7 @@
       <c r="AF59" s="102"/>
       <c r="AG59" s="102"/>
     </row>
-    <row r="60" spans="1:33" ht="11.45" customHeight="1">
+    <row r="60" spans="1:33" ht="11.5" customHeight="1">
       <c r="A60" s="205">
         <v>45819</v>
       </c>
@@ -14907,7 +14907,7 @@
       <c r="AF60" s="104"/>
       <c r="AG60" s="104"/>
     </row>
-    <row r="61" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="61" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A61" s="267">
         <v>45909</v>
       </c>
@@ -14964,7 +14964,7 @@
       <c r="AF61" s="263"/>
       <c r="AG61" s="263"/>
     </row>
-    <row r="62" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="62" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A62" s="270">
         <v>45909</v>
       </c>
@@ -15019,7 +15019,7 @@
       <c r="AF62" s="272"/>
       <c r="AG62" s="272"/>
     </row>
-    <row r="63" spans="1:33" ht="11.45" customHeight="1">
+    <row r="63" spans="1:33" ht="11.5" customHeight="1">
       <c r="A63" s="203">
         <v>45909</v>
       </c>
@@ -15090,7 +15090,7 @@
       <c r="AF63" s="56"/>
       <c r="AG63" s="56"/>
     </row>
-    <row r="64" spans="1:33" ht="11.45" customHeight="1">
+    <row r="64" spans="1:33" ht="11.5" customHeight="1">
       <c r="A64" s="214">
         <v>45909</v>
       </c>
@@ -15157,7 +15157,7 @@
       <c r="AF64" s="81"/>
       <c r="AG64" s="81"/>
     </row>
-    <row r="65" spans="1:33" ht="11.45" customHeight="1">
+    <row r="65" spans="1:33" ht="11.5" customHeight="1">
       <c r="A65" s="209"/>
       <c r="B65" s="209"/>
       <c r="C65" s="365"/>
@@ -15197,7 +15197,7 @@
       <c r="AF65" s="102"/>
       <c r="AG65" s="102"/>
     </row>
-    <row r="66" spans="1:33" ht="11.45" customHeight="1">
+    <row r="66" spans="1:33" ht="11.5" customHeight="1">
       <c r="A66" s="205">
         <v>45909</v>
       </c>
@@ -15270,7 +15270,7 @@
       <c r="AF66" s="104"/>
       <c r="AG66" s="104"/>
     </row>
-    <row r="67" spans="1:33" ht="11.45" customHeight="1">
+    <row r="67" spans="1:33" ht="11.5" customHeight="1">
       <c r="A67" s="207">
         <v>45874</v>
       </c>
@@ -15339,7 +15339,7 @@
       <c r="AF67" s="106"/>
       <c r="AG67" s="106"/>
     </row>
-    <row r="68" spans="1:33" ht="11.45" customHeight="1">
+    <row r="68" spans="1:33" ht="11.5" customHeight="1">
       <c r="A68" s="206">
         <v>45909</v>
       </c>
@@ -15408,7 +15408,7 @@
       <c r="AF68" s="78"/>
       <c r="AG68" s="78"/>
     </row>
-    <row r="69" spans="1:33" ht="11.45" customHeight="1">
+    <row r="69" spans="1:33" ht="11.5" customHeight="1">
       <c r="A69" s="204">
         <v>45909</v>
       </c>
@@ -15479,7 +15479,7 @@
       <c r="AF69" s="88"/>
       <c r="AG69" s="88"/>
     </row>
-    <row r="70" spans="1:33" ht="11.45" customHeight="1">
+    <row r="70" spans="1:33" ht="11.5" customHeight="1">
       <c r="A70" s="203">
         <v>45909</v>
       </c>
@@ -15542,7 +15542,7 @@
       <c r="AF70" s="56"/>
       <c r="AG70" s="56"/>
     </row>
-    <row r="71" spans="1:33" ht="11.45" customHeight="1">
+    <row r="71" spans="1:33" ht="11.5" customHeight="1">
       <c r="A71" s="214">
         <v>45909</v>
       </c>
@@ -15603,7 +15603,7 @@
       <c r="AF71" s="81"/>
       <c r="AG71" s="81"/>
     </row>
-    <row r="72" spans="1:33" ht="11.45" customHeight="1">
+    <row r="72" spans="1:33" ht="11.5" customHeight="1">
       <c r="A72" s="209">
         <v>45909</v>
       </c>
@@ -15662,7 +15662,7 @@
       <c r="AF72" s="102"/>
       <c r="AG72" s="102"/>
     </row>
-    <row r="73" spans="1:33" ht="11.45" customHeight="1">
+    <row r="73" spans="1:33" ht="11.5" customHeight="1">
       <c r="A73" s="205">
         <v>45909</v>
       </c>
@@ -15729,7 +15729,7 @@
       <c r="AF73" s="104"/>
       <c r="AG73" s="104"/>
     </row>
-    <row r="74" spans="1:33" ht="11.45" customHeight="1">
+    <row r="74" spans="1:33" ht="11.5" customHeight="1">
       <c r="A74" s="207">
         <v>45909</v>
       </c>
@@ -15785,7 +15785,7 @@
       <c r="AF74" s="106"/>
       <c r="AG74" s="106"/>
     </row>
-    <row r="75" spans="1:33" ht="11.45" customHeight="1">
+    <row r="75" spans="1:33" ht="11.5" customHeight="1">
       <c r="A75" s="206">
         <v>45909</v>
       </c>
@@ -15856,7 +15856,7 @@
       <c r="AF75" s="78"/>
       <c r="AG75" s="78"/>
     </row>
-    <row r="76" spans="1:33" ht="11.45" customHeight="1">
+    <row r="76" spans="1:33" ht="11.5" customHeight="1">
       <c r="A76" s="204">
         <v>45921</v>
       </c>
@@ -15919,7 +15919,7 @@
       <c r="AF76" s="88"/>
       <c r="AG76" s="88"/>
     </row>
-    <row r="77" spans="1:33" ht="11.45" customHeight="1">
+    <row r="77" spans="1:33" ht="11.5" customHeight="1">
       <c r="A77" s="203"/>
       <c r="B77" s="203"/>
       <c r="C77" s="377"/>
@@ -15964,7 +15964,7 @@
       <c r="AF77" s="56"/>
       <c r="AG77" s="56"/>
     </row>
-    <row r="78" spans="1:33" ht="11.45" customHeight="1">
+    <row r="78" spans="1:33" ht="11.5" customHeight="1">
       <c r="A78" s="214">
         <v>45924</v>
       </c>
@@ -16031,7 +16031,7 @@
       <c r="AF78" s="81"/>
       <c r="AG78" s="81"/>
     </row>
-    <row r="79" spans="1:33" s="166" customFormat="1" ht="11.45" customHeight="1">
+    <row r="79" spans="1:33" s="166" customFormat="1" ht="11.5" customHeight="1">
       <c r="A79" s="208">
         <v>45924</v>
       </c>
@@ -16108,7 +16108,7 @@
       <c r="AF79" s="85"/>
       <c r="AG79" s="85"/>
     </row>
-    <row r="80" spans="1:33" ht="11.45" customHeight="1">
+    <row r="80" spans="1:33" ht="11.5" customHeight="1">
       <c r="A80" s="207">
         <v>45924</v>
       </c>
@@ -16169,7 +16169,7 @@
       <c r="AF80" s="106"/>
       <c r="AG80" s="106"/>
     </row>
-    <row r="81" spans="1:33" ht="11.45" customHeight="1">
+    <row r="81" spans="1:33" ht="11.5" customHeight="1">
       <c r="A81" s="206">
         <v>45924</v>
       </c>
@@ -16240,7 +16240,7 @@
       <c r="AF81" s="78"/>
       <c r="AG81" s="78"/>
     </row>
-    <row r="82" spans="1:33" ht="11.45" customHeight="1">
+    <row r="82" spans="1:33" ht="11.5" customHeight="1">
       <c r="A82" s="204">
         <v>45924</v>
       </c>
@@ -16311,7 +16311,7 @@
       <c r="AF82" s="88"/>
       <c r="AG82" s="88"/>
     </row>
-    <row r="83" spans="1:33" ht="11.45" customHeight="1">
+    <row r="83" spans="1:33" ht="11.5" customHeight="1">
       <c r="A83" s="203">
         <v>45924</v>
       </c>
@@ -16380,7 +16380,7 @@
       <c r="AF83" s="56"/>
       <c r="AG83" s="56"/>
     </row>
-    <row r="84" spans="1:33" ht="11.45" customHeight="1">
+    <row r="84" spans="1:33" ht="11.5" customHeight="1">
       <c r="A84" s="214">
         <v>45924</v>
       </c>
@@ -16453,7 +16453,7 @@
       <c r="AF84" s="81"/>
       <c r="AG84" s="81"/>
     </row>
-    <row r="85" spans="1:33" ht="11.45" customHeight="1">
+    <row r="85" spans="1:33" ht="11.5" customHeight="1">
       <c r="A85" s="209">
         <v>45930</v>
       </c>
@@ -16518,7 +16518,7 @@
       <c r="AF85" s="102"/>
       <c r="AG85" s="102"/>
     </row>
-    <row r="86" spans="1:33" ht="11.45" customHeight="1">
+    <row r="86" spans="1:33" ht="11.5" customHeight="1">
       <c r="A86" s="410">
         <v>45930</v>
       </c>
@@ -16578,7 +16578,7 @@
       <c r="AF86" s="104"/>
       <c r="AG86" s="104"/>
     </row>
-    <row r="87" spans="1:33" ht="11.45" customHeight="1">
+    <row r="87" spans="1:33" ht="11.5" customHeight="1">
       <c r="A87" s="207">
         <v>45924</v>
       </c>
@@ -16631,7 +16631,7 @@
       <c r="AF87" s="106"/>
       <c r="AG87" s="106"/>
     </row>
-    <row r="88" spans="1:33" ht="11.45" customHeight="1">
+    <row r="88" spans="1:33" ht="11.5" customHeight="1">
       <c r="A88" s="206">
         <v>45930</v>
       </c>
@@ -16692,7 +16692,7 @@
       <c r="AF88" s="78"/>
       <c r="AG88" s="78"/>
     </row>
-    <row r="89" spans="1:33" ht="11.45" customHeight="1">
+    <row r="89" spans="1:33" ht="11.5" customHeight="1">
       <c r="A89" s="204">
         <v>45930</v>
       </c>
@@ -16759,7 +16759,7 @@
       <c r="AF89" s="88"/>
       <c r="AG89" s="88"/>
     </row>
-    <row r="90" spans="1:33" ht="11.45" customHeight="1">
+    <row r="90" spans="1:33" ht="11.5" customHeight="1">
       <c r="A90" s="203">
         <v>45930</v>
       </c>
@@ -16822,7 +16822,7 @@
       <c r="AF90" s="56"/>
       <c r="AG90" s="56"/>
     </row>
-    <row r="91" spans="1:33" ht="11.45" customHeight="1">
+    <row r="91" spans="1:33" ht="11.5" customHeight="1">
       <c r="A91" s="214">
         <v>45930</v>
       </c>
@@ -16891,7 +16891,7 @@
       <c r="AF91" s="81"/>
       <c r="AG91" s="81"/>
     </row>
-    <row r="92" spans="1:33" ht="11.45" customHeight="1">
+    <row r="92" spans="1:33" ht="11.5" customHeight="1">
       <c r="A92" s="214">
         <v>45930</v>
       </c>
@@ -16943,7 +16943,7 @@
       <c r="AF92" s="81"/>
       <c r="AG92" s="81"/>
     </row>
-    <row r="93" spans="1:33" ht="11.45" customHeight="1">
+    <row r="93" spans="1:33" ht="11.5" customHeight="1">
       <c r="A93" s="209">
         <v>45930</v>
       </c>
@@ -17008,7 +17008,7 @@
       <c r="AF93" s="102"/>
       <c r="AG93" s="102"/>
     </row>
-    <row r="94" spans="1:33" ht="11.45" customHeight="1">
+    <row r="94" spans="1:33" ht="11.5" customHeight="1">
       <c r="A94" s="205">
         <v>45930</v>
       </c>
@@ -17071,7 +17071,7 @@
       <c r="AF94" s="104"/>
       <c r="AG94" s="104"/>
     </row>
-    <row r="95" spans="1:33" ht="11.45" customHeight="1">
+    <row r="95" spans="1:33" ht="11.5" customHeight="1">
       <c r="A95" s="207">
         <v>45930</v>
       </c>
@@ -17132,7 +17132,7 @@
       <c r="AF95" s="106"/>
       <c r="AG95" s="106"/>
     </row>
-    <row r="96" spans="1:33" ht="11.45" customHeight="1">
+    <row r="96" spans="1:33" ht="11.5" customHeight="1">
       <c r="A96" s="206">
         <v>45930</v>
       </c>
@@ -17193,7 +17193,7 @@
       <c r="AF96" s="78"/>
       <c r="AG96" s="78"/>
     </row>
-    <row r="97" spans="1:33" ht="11.45" customHeight="1">
+    <row r="97" spans="1:33" ht="11.5" customHeight="1">
       <c r="A97" s="204">
         <v>45938</v>
       </c>
@@ -17252,7 +17252,7 @@
       <c r="AF97" s="88"/>
       <c r="AG97" s="88"/>
     </row>
-    <row r="98" spans="1:33" ht="11.45" customHeight="1">
+    <row r="98" spans="1:33" ht="11.5" customHeight="1">
       <c r="A98" s="203">
         <v>45966</v>
       </c>
@@ -17323,7 +17323,7 @@
       <c r="AF98" s="56"/>
       <c r="AG98" s="56"/>
     </row>
-    <row r="99" spans="1:33" ht="11.45" customHeight="1">
+    <row r="99" spans="1:33" ht="11.5" customHeight="1">
       <c r="A99" s="214">
         <v>45966</v>
       </c>
@@ -17392,7 +17392,7 @@
       <c r="AF99" s="81"/>
       <c r="AG99" s="81"/>
     </row>
-    <row r="100" spans="1:33" ht="11.45" customHeight="1">
+    <row r="100" spans="1:33" ht="11.5" customHeight="1">
       <c r="A100" s="209">
         <v>45966</v>
       </c>
@@ -17446,7 +17446,7 @@
       <c r="AF100" s="102"/>
       <c r="AG100" s="102"/>
     </row>
-    <row r="101" spans="1:33" ht="11.45" customHeight="1">
+    <row r="101" spans="1:33" ht="11.5" customHeight="1">
       <c r="A101" s="205">
         <v>45966</v>
       </c>
@@ -17505,7 +17505,7 @@
       <c r="AF101" s="104"/>
       <c r="AG101" s="104"/>
     </row>
-    <row r="102" spans="1:33" ht="11.45" customHeight="1">
+    <row r="102" spans="1:33" ht="11.5" customHeight="1">
       <c r="A102" s="207">
         <v>45972</v>
       </c>
@@ -17568,7 +17568,7 @@
       <c r="AF102" s="106"/>
       <c r="AG102" s="106"/>
     </row>
-    <row r="103" spans="1:33" ht="11.45" customHeight="1">
+    <row r="103" spans="1:33" ht="11.5" customHeight="1">
       <c r="A103" s="206">
         <v>45972</v>
       </c>
@@ -17631,7 +17631,7 @@
       <c r="AF103" s="78"/>
       <c r="AG103" s="78"/>
     </row>
-    <row r="104" spans="1:33" ht="11.45" customHeight="1">
+    <row r="104" spans="1:33" ht="11.5" customHeight="1">
       <c r="A104" s="204">
         <v>45972</v>
       </c>
@@ -17689,7 +17689,7 @@
       <c r="AF104" s="88"/>
       <c r="AG104" s="88"/>
     </row>
-    <row r="105" spans="1:33" ht="11.45" customHeight="1">
+    <row r="105" spans="1:33" ht="11.5" customHeight="1">
       <c r="A105" s="203">
         <v>45979</v>
       </c>
@@ -17760,7 +17760,7 @@
       <c r="AF105" s="56"/>
       <c r="AG105" s="56"/>
     </row>
-    <row r="106" spans="1:33" ht="11.45" customHeight="1">
+    <row r="106" spans="1:33" ht="11.5" customHeight="1">
       <c r="A106" s="214">
         <v>45979</v>
       </c>
@@ -17829,7 +17829,7 @@
       <c r="AF106" s="81"/>
       <c r="AG106" s="81"/>
     </row>
-    <row r="107" spans="1:33" ht="11.45" customHeight="1">
+    <row r="107" spans="1:33" ht="11.5" customHeight="1">
       <c r="A107" s="205">
         <v>45980</v>
       </c>
@@ -17894,7 +17894,7 @@
       <c r="AF107" s="104"/>
       <c r="AG107" s="104"/>
     </row>
-    <row r="108" spans="1:33" s="302" customFormat="1" ht="11.45" customHeight="1">
+    <row r="108" spans="1:33" s="302" customFormat="1" ht="11.5" customHeight="1">
       <c r="A108" s="250">
         <v>45980</v>
       </c>
@@ -17955,7 +17955,7 @@
       <c r="AF108" s="333"/>
       <c r="AG108" s="333"/>
     </row>
-    <row r="109" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="109" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A109" s="222">
         <v>46035</v>
       </c>
@@ -18011,7 +18011,7 @@
       <c r="AF109" s="335"/>
       <c r="AG109" s="335"/>
     </row>
-    <row r="110" spans="1:33" ht="11.45" customHeight="1">
+    <row r="110" spans="1:33" ht="11.5" customHeight="1">
       <c r="A110" s="206">
         <v>45981</v>
       </c>
@@ -18074,7 +18074,7 @@
       <c r="AF110" s="78"/>
       <c r="AG110" s="78"/>
     </row>
-    <row r="111" spans="1:33" ht="11.45" customHeight="1">
+    <row r="111" spans="1:33" ht="11.5" customHeight="1">
       <c r="A111" s="203">
         <v>46035</v>
       </c>
@@ -18135,7 +18135,7 @@
       <c r="AF111" s="56"/>
       <c r="AG111" s="56"/>
     </row>
-    <row r="112" spans="1:33" ht="11.45" customHeight="1">
+    <row r="112" spans="1:33" ht="11.5" customHeight="1">
       <c r="A112" s="204">
         <v>45981</v>
       </c>
@@ -18192,7 +18192,7 @@
       <c r="AF112" s="88"/>
       <c r="AG112" s="88"/>
     </row>
-    <row r="113" spans="1:33" ht="11.45" customHeight="1">
+    <row r="113" spans="1:33" ht="11.5" customHeight="1">
       <c r="A113" s="203">
         <v>45981</v>
       </c>
@@ -18251,7 +18251,7 @@
       <c r="AF113" s="56"/>
       <c r="AG113" s="56"/>
     </row>
-    <row r="114" spans="1:33" ht="11.45" customHeight="1">
+    <row r="114" spans="1:33" ht="11.5" customHeight="1">
       <c r="A114" s="214">
         <v>45981</v>
       </c>
@@ -18312,7 +18312,7 @@
       <c r="AF114" s="81"/>
       <c r="AG114" s="81"/>
     </row>
-    <row r="115" spans="1:33" ht="11.45" customHeight="1">
+    <row r="115" spans="1:33" ht="11.5" customHeight="1">
       <c r="A115" s="209">
         <v>45981</v>
       </c>
@@ -18375,7 +18375,7 @@
       <c r="AF115" s="102"/>
       <c r="AG115" s="102"/>
     </row>
-    <row r="116" spans="1:33" ht="11.45" customHeight="1">
+    <row r="116" spans="1:33" ht="11.5" customHeight="1">
       <c r="A116" s="205">
         <v>45981</v>
       </c>
@@ -18438,7 +18438,7 @@
       <c r="AF116" s="104"/>
       <c r="AG116" s="104"/>
     </row>
-    <row r="117" spans="1:33" ht="11.45" customHeight="1">
+    <row r="117" spans="1:33" ht="11.5" customHeight="1">
       <c r="A117" s="207">
         <v>45986</v>
       </c>
@@ -18497,7 +18497,7 @@
       <c r="AF117" s="106"/>
       <c r="AG117" s="106"/>
     </row>
-    <row r="118" spans="1:33" ht="11.45" customHeight="1">
+    <row r="118" spans="1:33" ht="11.5" customHeight="1">
       <c r="A118" s="206">
         <v>45986</v>
       </c>
@@ -18560,7 +18560,7 @@
       <c r="AF118" s="78"/>
       <c r="AG118" s="78"/>
     </row>
-    <row r="119" spans="1:33" ht="11.45" customHeight="1">
+    <row r="119" spans="1:33" ht="11.5" customHeight="1">
       <c r="A119" s="204">
         <v>45986</v>
       </c>
@@ -18621,7 +18621,7 @@
       <c r="AF119" s="88"/>
       <c r="AG119" s="88"/>
     </row>
-    <row r="120" spans="1:33" ht="11.45" customHeight="1">
+    <row r="120" spans="1:33" ht="11.5" customHeight="1">
       <c r="A120" s="214">
         <v>45986</v>
       </c>
@@ -18737,7 +18737,7 @@
       <c r="AF121" s="102"/>
       <c r="AG121" s="102"/>
     </row>
-    <row r="122" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="122" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A122" s="280">
         <v>45986</v>
       </c>
@@ -18798,7 +18798,7 @@
       <c r="AF122" s="282"/>
       <c r="AG122" s="282"/>
     </row>
-    <row r="123" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="123" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A123" s="222">
         <v>45986</v>
       </c>
@@ -18857,7 +18857,7 @@
       <c r="AF123" s="335"/>
       <c r="AG123" s="335"/>
     </row>
-    <row r="124" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="124" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A124" s="267">
         <v>46072</v>
       </c>
@@ -18912,7 +18912,7 @@
       <c r="AF124" s="263"/>
       <c r="AG124" s="263"/>
     </row>
-    <row r="125" spans="1:33" ht="11.45" customHeight="1">
+    <row r="125" spans="1:33" ht="11.5" customHeight="1">
       <c r="A125" s="204">
         <v>45986</v>
       </c>
@@ -18975,7 +18975,7 @@
       <c r="AF125" s="88"/>
       <c r="AG125" s="88"/>
     </row>
-    <row r="126" spans="1:33" ht="11.45" customHeight="1">
+    <row r="126" spans="1:33" ht="11.5" customHeight="1">
       <c r="A126" s="203"/>
       <c r="B126" s="203"/>
       <c r="C126" s="377"/>
@@ -19021,7 +19021,7 @@
       <c r="AF126" s="56"/>
       <c r="AG126" s="56"/>
     </row>
-    <row r="127" spans="1:33" ht="11.45" customHeight="1">
+    <row r="127" spans="1:33" ht="11.5" customHeight="1">
       <c r="A127" s="214">
         <v>45986</v>
       </c>
@@ -19076,7 +19076,7 @@
       <c r="AF127" s="81"/>
       <c r="AG127" s="81"/>
     </row>
-    <row r="128" spans="1:33" ht="11.45" customHeight="1">
+    <row r="128" spans="1:33" ht="11.5" customHeight="1">
       <c r="A128" s="209">
         <v>46051</v>
       </c>
@@ -19130,7 +19130,7 @@
       <c r="AF128" s="102"/>
       <c r="AG128" s="102"/>
     </row>
-    <row r="129" spans="1:33" ht="11.45" customHeight="1">
+    <row r="129" spans="1:33" ht="11.5" customHeight="1">
       <c r="A129" s="205">
         <v>45987</v>
       </c>
@@ -19185,7 +19185,7 @@
       <c r="AF129" s="104"/>
       <c r="AG129" s="104"/>
     </row>
-    <row r="130" spans="1:33" ht="11.45" customHeight="1">
+    <row r="130" spans="1:33" ht="11.5" customHeight="1">
       <c r="A130" s="207">
         <v>46000</v>
       </c>
@@ -19236,7 +19236,7 @@
       <c r="AF130" s="106"/>
       <c r="AG130" s="106"/>
     </row>
-    <row r="131" spans="1:33" ht="11.45" customHeight="1">
+    <row r="131" spans="1:33" ht="11.5" customHeight="1">
       <c r="A131" s="206">
         <v>46001</v>
       </c>
@@ -19295,7 +19295,7 @@
       <c r="AF131" s="78"/>
       <c r="AG131" s="78"/>
     </row>
-    <row r="132" spans="1:33" ht="11.45" customHeight="1">
+    <row r="132" spans="1:33" ht="11.5" customHeight="1">
       <c r="A132" s="204"/>
       <c r="B132" s="204"/>
       <c r="C132" s="380"/>
@@ -19331,7 +19331,7 @@
       <c r="AF132" s="88"/>
       <c r="AG132" s="88"/>
     </row>
-    <row r="133" spans="1:33" ht="11.45" customHeight="1">
+    <row r="133" spans="1:33" ht="11.5" customHeight="1">
       <c r="A133" s="203"/>
       <c r="B133" s="203">
         <v>46058</v>
@@ -19371,7 +19371,7 @@
       <c r="AF133" s="56"/>
       <c r="AG133" s="56"/>
     </row>
-    <row r="134" spans="1:33" ht="11.45" customHeight="1">
+    <row r="134" spans="1:33" ht="11.5" customHeight="1">
       <c r="A134" s="214">
         <v>46035</v>
       </c>
@@ -19434,7 +19434,7 @@
       <c r="AF134" s="81"/>
       <c r="AG134" s="81"/>
     </row>
-    <row r="135" spans="1:33" ht="11.45" customHeight="1">
+    <row r="135" spans="1:33" ht="11.5" customHeight="1">
       <c r="A135" s="209">
         <v>46035</v>
       </c>
@@ -19497,7 +19497,7 @@
       <c r="AF135" s="102"/>
       <c r="AG135" s="102"/>
     </row>
-    <row r="136" spans="1:33" ht="11.45" customHeight="1">
+    <row r="136" spans="1:33" ht="11.5" customHeight="1">
       <c r="A136" s="205"/>
       <c r="B136" s="205"/>
       <c r="C136" s="366"/>
@@ -19543,7 +19543,7 @@
       <c r="AF136" s="104"/>
       <c r="AG136" s="104"/>
     </row>
-    <row r="137" spans="1:33" ht="11.45" customHeight="1">
+    <row r="137" spans="1:33" ht="11.5" customHeight="1">
       <c r="A137" s="206">
         <v>46035</v>
       </c>
@@ -19600,7 +19600,7 @@
       <c r="AF137" s="78"/>
       <c r="AG137" s="78"/>
     </row>
-    <row r="138" spans="1:33" ht="11.45" customHeight="1">
+    <row r="138" spans="1:33" ht="11.5" customHeight="1">
       <c r="A138" s="203">
         <v>46029</v>
       </c>
@@ -19665,7 +19665,7 @@
       <c r="AF138" s="56"/>
       <c r="AG138" s="56"/>
     </row>
-    <row r="139" spans="1:33" ht="11.45" customHeight="1">
+    <row r="139" spans="1:33" ht="11.5" customHeight="1">
       <c r="A139" s="214">
         <v>46029</v>
       </c>
@@ -19724,7 +19724,7 @@
       <c r="AF139" s="81"/>
       <c r="AG139" s="81"/>
     </row>
-    <row r="140" spans="1:33" ht="11.45" customHeight="1">
+    <row r="140" spans="1:33" ht="11.5" customHeight="1">
       <c r="A140" s="214">
         <v>46035</v>
       </c>
@@ -19773,7 +19773,7 @@
       <c r="AF140" s="81"/>
       <c r="AG140" s="81"/>
     </row>
-    <row r="141" spans="1:33" ht="11.45" customHeight="1">
+    <row r="141" spans="1:33" ht="11.5" customHeight="1">
       <c r="A141" s="209">
         <v>46029</v>
       </c>
@@ -19832,7 +19832,7 @@
       <c r="AF141" s="102"/>
       <c r="AG141" s="102"/>
     </row>
-    <row r="142" spans="1:33" ht="11.45" customHeight="1">
+    <row r="142" spans="1:33" ht="11.5" customHeight="1">
       <c r="A142" s="205">
         <v>46035</v>
       </c>
@@ -19891,7 +19891,7 @@
       <c r="AF142" s="104"/>
       <c r="AG142" s="104"/>
     </row>
-    <row r="143" spans="1:33" ht="11.45" customHeight="1">
+    <row r="143" spans="1:33" ht="11.5" customHeight="1">
       <c r="A143" s="207">
         <v>46035</v>
       </c>
@@ -19948,7 +19948,7 @@
       <c r="AF143" s="106"/>
       <c r="AG143" s="106"/>
     </row>
-    <row r="144" spans="1:33" ht="11.45" customHeight="1">
+    <row r="144" spans="1:33" ht="11.5" customHeight="1">
       <c r="A144" s="206">
         <v>46035</v>
       </c>
@@ -20007,7 +20007,7 @@
       <c r="AF144" s="78"/>
       <c r="AG144" s="78"/>
     </row>
-    <row r="145" spans="1:33" ht="11.45" customHeight="1">
+    <row r="145" spans="1:33" ht="11.5" customHeight="1">
       <c r="A145" s="204">
         <v>46035</v>
       </c>
@@ -20068,7 +20068,7 @@
       <c r="AF145" s="88"/>
       <c r="AG145" s="88"/>
     </row>
-    <row r="146" spans="1:33" ht="11.45" customHeight="1">
+    <row r="146" spans="1:33" ht="11.5" customHeight="1">
       <c r="A146" s="203">
         <v>46030</v>
       </c>
@@ -20127,7 +20127,7 @@
       <c r="AF146" s="56"/>
       <c r="AG146" s="56"/>
     </row>
-    <row r="147" spans="1:33" ht="11.45" customHeight="1">
+    <row r="147" spans="1:33" ht="11.5" customHeight="1">
       <c r="A147" s="214">
         <v>46035</v>
       </c>
@@ -20186,7 +20186,7 @@
       <c r="AF147" s="81"/>
       <c r="AG147" s="81"/>
     </row>
-    <row r="148" spans="1:33" ht="11.45" customHeight="1">
+    <row r="148" spans="1:33" ht="11.5" customHeight="1">
       <c r="A148" s="209">
         <v>46029</v>
       </c>
@@ -20245,7 +20245,7 @@
       <c r="AF148" s="102"/>
       <c r="AG148" s="102"/>
     </row>
-    <row r="149" spans="1:33" ht="11.45" customHeight="1">
+    <row r="149" spans="1:33" ht="11.5" customHeight="1">
       <c r="A149" s="205">
         <v>46029</v>
       </c>
@@ -20306,7 +20306,7 @@
       <c r="AF149" s="104"/>
       <c r="AG149" s="104"/>
     </row>
-    <row r="150" spans="1:33" ht="11.45" customHeight="1">
+    <row r="150" spans="1:33" ht="11.5" customHeight="1">
       <c r="A150" s="207">
         <v>46029</v>
       </c>
@@ -20366,7 +20366,7 @@
       <c r="AF150" s="326"/>
       <c r="AG150" s="326"/>
     </row>
-    <row r="151" spans="1:33" ht="11.45" customHeight="1">
+    <row r="151" spans="1:33" ht="11.5" customHeight="1">
       <c r="A151" s="204"/>
       <c r="B151" s="204"/>
       <c r="C151" s="380"/>
@@ -20413,7 +20413,7 @@
       <c r="AF151" s="88"/>
       <c r="AG151" s="88"/>
     </row>
-    <row r="152" spans="1:33" ht="11.45" customHeight="1">
+    <row r="152" spans="1:33" ht="11.5" customHeight="1">
       <c r="A152" s="203"/>
       <c r="B152" s="203"/>
       <c r="C152" s="377"/>
@@ -20454,7 +20454,7 @@
       <c r="AF152" s="56"/>
       <c r="AG152" s="56"/>
     </row>
-    <row r="153" spans="1:33" ht="11.45" customHeight="1">
+    <row r="153" spans="1:33" ht="11.5" customHeight="1">
       <c r="A153" s="214">
         <v>46035</v>
       </c>
@@ -20519,7 +20519,7 @@
       <c r="AF153" s="81"/>
       <c r="AG153" s="81"/>
     </row>
-    <row r="154" spans="1:33" ht="11.45" customHeight="1">
+    <row r="154" spans="1:33" ht="11.5" customHeight="1">
       <c r="A154" s="209">
         <v>46035</v>
       </c>
@@ -20580,7 +20580,7 @@
       <c r="AF154" s="102"/>
       <c r="AG154" s="102"/>
     </row>
-    <row r="155" spans="1:33" ht="11.45" customHeight="1">
+    <row r="155" spans="1:33" ht="11.5" customHeight="1">
       <c r="A155" s="205">
         <v>46035</v>
       </c>
@@ -20647,7 +20647,7 @@
       <c r="AF155" s="104"/>
       <c r="AG155" s="104"/>
     </row>
-    <row r="156" spans="1:33" ht="11.45" customHeight="1">
+    <row r="156" spans="1:33" ht="11.5" customHeight="1">
       <c r="A156" s="207">
         <v>46035</v>
       </c>
@@ -20704,7 +20704,7 @@
       <c r="AF156" s="106"/>
       <c r="AG156" s="106"/>
     </row>
-    <row r="157" spans="1:33" ht="11.45" customHeight="1">
+    <row r="157" spans="1:33" ht="11.5" customHeight="1">
       <c r="A157" s="206"/>
       <c r="B157" s="206"/>
       <c r="C157" s="382"/>
@@ -20747,7 +20747,7 @@
       <c r="AF157" s="78"/>
       <c r="AG157" s="78"/>
     </row>
-    <row r="158" spans="1:33" ht="11.45" customHeight="1">
+    <row r="158" spans="1:33" ht="11.5" customHeight="1">
       <c r="A158" s="204">
         <v>46035</v>
       </c>
@@ -20810,7 +20810,7 @@
       <c r="AF158" s="88"/>
       <c r="AG158" s="88"/>
     </row>
-    <row r="159" spans="1:33" ht="11.45" customHeight="1">
+    <row r="159" spans="1:33" ht="11.5" customHeight="1">
       <c r="A159" s="203">
         <v>46035</v>
       </c>
@@ -20867,7 +20867,7 @@
       <c r="AF159" s="56"/>
       <c r="AG159" s="56"/>
     </row>
-    <row r="160" spans="1:33" ht="11.45" customHeight="1">
+    <row r="160" spans="1:33" ht="11.5" customHeight="1">
       <c r="A160" s="214">
         <v>46035</v>
       </c>
@@ -20934,7 +20934,7 @@
       <c r="AF160" s="81"/>
       <c r="AG160" s="81"/>
     </row>
-    <row r="161" spans="1:33" ht="11.45" customHeight="1">
+    <row r="161" spans="1:33" ht="11.5" customHeight="1">
       <c r="A161" s="209">
         <v>46035</v>
       </c>
@@ -20995,7 +20995,7 @@
       <c r="AF161" s="102"/>
       <c r="AG161" s="102"/>
     </row>
-    <row r="162" spans="1:33" ht="11.45" customHeight="1">
+    <row r="162" spans="1:33" ht="11.5" customHeight="1">
       <c r="A162" s="205"/>
       <c r="B162" s="205"/>
       <c r="C162" s="366"/>
@@ -21033,7 +21033,7 @@
       <c r="AF162" s="104"/>
       <c r="AG162" s="104"/>
     </row>
-    <row r="163" spans="1:33" ht="11.45" customHeight="1">
+    <row r="163" spans="1:33" ht="11.5" customHeight="1">
       <c r="A163" s="204">
         <v>46035</v>
       </c>
@@ -21090,7 +21090,7 @@
       <c r="AF163" s="88"/>
       <c r="AG163" s="88"/>
     </row>
-    <row r="164" spans="1:33" ht="11.45" customHeight="1">
+    <row r="164" spans="1:33" ht="11.5" customHeight="1">
       <c r="A164" s="206">
         <v>46035</v>
       </c>
@@ -21151,7 +21151,7 @@
       <c r="AF164" s="78"/>
       <c r="AG164" s="78"/>
     </row>
-    <row r="165" spans="1:33" ht="11.45" customHeight="1">
+    <row r="165" spans="1:33" ht="11.5" customHeight="1">
       <c r="A165" s="204"/>
       <c r="B165" s="204"/>
       <c r="C165" s="380"/>
@@ -21187,7 +21187,7 @@
       <c r="AF165" s="88"/>
       <c r="AG165" s="88"/>
     </row>
-    <row r="166" spans="1:33" ht="11.45" customHeight="1">
+    <row r="166" spans="1:33" ht="11.5" customHeight="1">
       <c r="A166" s="203">
         <v>46052</v>
       </c>
@@ -21246,7 +21246,7 @@
       <c r="AF166" s="56"/>
       <c r="AG166" s="56"/>
     </row>
-    <row r="167" spans="1:33" ht="11.45" customHeight="1">
+    <row r="167" spans="1:33" ht="11.5" customHeight="1">
       <c r="A167" s="214">
         <v>46029</v>
       </c>
@@ -21305,7 +21305,7 @@
       <c r="AF167" s="81"/>
       <c r="AG167" s="81"/>
     </row>
-    <row r="168" spans="1:33" ht="11.45" customHeight="1">
+    <row r="168" spans="1:33" ht="11.5" customHeight="1">
       <c r="A168" s="209">
         <v>46035</v>
       </c>
@@ -21364,7 +21364,7 @@
       <c r="AF168" s="102"/>
       <c r="AG168" s="102"/>
     </row>
-    <row r="169" spans="1:33" ht="11.45" customHeight="1">
+    <row r="169" spans="1:33" ht="11.5" customHeight="1">
       <c r="A169" s="205">
         <v>46035</v>
       </c>
@@ -21427,7 +21427,7 @@
       <c r="AF169" s="104"/>
       <c r="AG169" s="104"/>
     </row>
-    <row r="170" spans="1:33" ht="11.45" customHeight="1">
+    <row r="170" spans="1:33" ht="11.5" customHeight="1">
       <c r="A170" s="412">
         <v>46035</v>
       </c>
@@ -21476,7 +21476,7 @@
       <c r="AF170" s="106"/>
       <c r="AG170" s="106"/>
     </row>
-    <row r="171" spans="1:33" ht="11.45" customHeight="1">
+    <row r="171" spans="1:33" ht="11.5" customHeight="1">
       <c r="A171" s="206">
         <v>46035</v>
       </c>
@@ -21539,7 +21539,7 @@
       <c r="AF171" s="78"/>
       <c r="AG171" s="78"/>
     </row>
-    <row r="172" spans="1:33" ht="11.45" customHeight="1">
+    <row r="172" spans="1:33" ht="11.5" customHeight="1">
       <c r="A172" s="204"/>
       <c r="B172" s="204"/>
       <c r="C172" s="380"/>
@@ -21579,7 +21579,7 @@
       <c r="AF172" s="88"/>
       <c r="AG172" s="88"/>
     </row>
-    <row r="173" spans="1:33" ht="11.45" customHeight="1">
+    <row r="173" spans="1:33" ht="11.5" customHeight="1">
       <c r="A173" s="203">
         <v>46035</v>
       </c>
@@ -21636,7 +21636,7 @@
       <c r="AF173" s="56"/>
       <c r="AG173" s="56"/>
     </row>
-    <row r="174" spans="1:33" ht="11.45" customHeight="1">
+    <row r="174" spans="1:33" ht="11.5" customHeight="1">
       <c r="A174" s="214">
         <v>46035</v>
       </c>
@@ -21695,7 +21695,7 @@
       <c r="AF174" s="81"/>
       <c r="AG174" s="81"/>
     </row>
-    <row r="175" spans="1:33" ht="11.45" customHeight="1">
+    <row r="175" spans="1:33" ht="11.5" customHeight="1">
       <c r="A175" s="209">
         <v>46035</v>
       </c>
@@ -21756,7 +21756,7 @@
       <c r="AF175" s="102"/>
       <c r="AG175" s="102"/>
     </row>
-    <row r="176" spans="1:33" ht="11.45" customHeight="1">
+    <row r="176" spans="1:33" ht="11.5" customHeight="1">
       <c r="A176" s="205">
         <v>46035</v>
       </c>
@@ -21817,7 +21817,7 @@
       <c r="AF176" s="104"/>
       <c r="AG176" s="104"/>
     </row>
-    <row r="177" spans="1:33" ht="11.45" customHeight="1">
+    <row r="177" spans="1:33" ht="11.5" customHeight="1">
       <c r="A177" s="207">
         <v>46035</v>
       </c>
@@ -21876,7 +21876,7 @@
       <c r="AF177" s="106"/>
       <c r="AG177" s="106"/>
     </row>
-    <row r="178" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="178" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A178" s="267">
         <v>46035</v>
       </c>
@@ -21939,7 +21939,7 @@
       <c r="AF178" s="263"/>
       <c r="AG178" s="263"/>
     </row>
-    <row r="179" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="179" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A179" s="267"/>
       <c r="B179" s="222"/>
       <c r="C179" s="388"/>
@@ -21980,7 +21980,7 @@
       <c r="AF179" s="263"/>
       <c r="AG179" s="263"/>
     </row>
-    <row r="180" spans="1:33" ht="11.45" customHeight="1">
+    <row r="180" spans="1:33" ht="11.5" customHeight="1">
       <c r="A180" s="204">
         <v>46035</v>
       </c>
@@ -22039,7 +22039,7 @@
       <c r="AF180" s="88"/>
       <c r="AG180" s="88"/>
     </row>
-    <row r="181" spans="1:33" ht="11.45" customHeight="1">
+    <row r="181" spans="1:33" ht="11.5" customHeight="1">
       <c r="A181" s="203">
         <v>46035</v>
       </c>
@@ -22098,7 +22098,7 @@
       <c r="AF181" s="56"/>
       <c r="AG181" s="56"/>
     </row>
-    <row r="182" spans="1:33" ht="11.45" customHeight="1">
+    <row r="182" spans="1:33" ht="11.5" customHeight="1">
       <c r="A182" s="214">
         <v>46035</v>
       </c>
@@ -22157,7 +22157,7 @@
       <c r="AF182" s="81"/>
       <c r="AG182" s="81"/>
     </row>
-    <row r="183" spans="1:33" ht="11.45" customHeight="1">
+    <row r="183" spans="1:33" ht="11.5" customHeight="1">
       <c r="A183" s="209">
         <v>46035</v>
       </c>
@@ -22218,7 +22218,7 @@
       <c r="AF183" s="102"/>
       <c r="AG183" s="102"/>
     </row>
-    <row r="184" spans="1:33" ht="11.45" customHeight="1">
+    <row r="184" spans="1:33" ht="11.5" customHeight="1">
       <c r="A184" s="205">
         <v>46035</v>
       </c>
@@ -22277,7 +22277,7 @@
       <c r="AF184" s="104"/>
       <c r="AG184" s="104"/>
     </row>
-    <row r="185" spans="1:33" ht="11.45" customHeight="1">
+    <row r="185" spans="1:33" ht="11.5" customHeight="1">
       <c r="A185" s="207">
         <v>46035</v>
       </c>
@@ -22336,7 +22336,7 @@
       <c r="AF185" s="106"/>
       <c r="AG185" s="106"/>
     </row>
-    <row r="186" spans="1:33" ht="11.45" customHeight="1">
+    <row r="186" spans="1:33" ht="11.5" customHeight="1">
       <c r="A186" s="206">
         <v>46035</v>
       </c>
@@ -22395,7 +22395,7 @@
       <c r="AF186" s="78"/>
       <c r="AG186" s="78"/>
     </row>
-    <row r="187" spans="1:33" ht="11.45" customHeight="1">
+    <row r="187" spans="1:33" ht="11.5" customHeight="1">
       <c r="A187" s="204">
         <v>46035</v>
       </c>
@@ -22456,7 +22456,7 @@
       <c r="AF187" s="88"/>
       <c r="AG187" s="88"/>
     </row>
-    <row r="188" spans="1:33" ht="11.45" customHeight="1">
+    <row r="188" spans="1:33" ht="11.5" customHeight="1">
       <c r="A188" s="203"/>
       <c r="B188" s="203"/>
       <c r="C188" s="377"/>
@@ -22505,7 +22505,7 @@
       <c r="AF188" s="56"/>
       <c r="AG188" s="56"/>
     </row>
-    <row r="189" spans="1:33" ht="11.45" customHeight="1">
+    <row r="189" spans="1:33" ht="11.5" customHeight="1">
       <c r="A189" s="209">
         <v>46035</v>
       </c>
@@ -22562,7 +22562,7 @@
       <c r="AF189" s="102"/>
       <c r="AG189" s="102"/>
     </row>
-    <row r="190" spans="1:33" ht="11.45" customHeight="1">
+    <row r="190" spans="1:33" ht="11.5" customHeight="1">
       <c r="A190" s="203">
         <v>46035</v>
       </c>
@@ -22627,7 +22627,7 @@
       <c r="AF190" s="56"/>
       <c r="AG190" s="56"/>
     </row>
-    <row r="191" spans="1:33" ht="11.45" customHeight="1">
+    <row r="191" spans="1:33" ht="11.5" customHeight="1">
       <c r="A191" s="214">
         <v>46035</v>
       </c>
@@ -22686,7 +22686,7 @@
       <c r="AF191" s="81"/>
       <c r="AG191" s="81"/>
     </row>
-    <row r="192" spans="1:33" ht="11.45" customHeight="1">
+    <row r="192" spans="1:33" ht="11.5" customHeight="1">
       <c r="A192" s="209">
         <v>46035</v>
       </c>
@@ -22753,7 +22753,7 @@
       <c r="AF192" s="102"/>
       <c r="AG192" s="102"/>
     </row>
-    <row r="193" spans="1:33" ht="11.45" customHeight="1">
+    <row r="193" spans="1:33" ht="11.5" customHeight="1">
       <c r="A193" s="205">
         <v>46035</v>
       </c>
@@ -22771,7 +22771,7 @@
         <v>58</v>
       </c>
       <c r="G193" s="113" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="H193" s="120" t="s">
         <v>1120</v>
@@ -22818,7 +22818,7 @@
       <c r="AF193" s="104"/>
       <c r="AG193" s="104"/>
     </row>
-    <row r="194" spans="1:33" ht="11.45" customHeight="1">
+    <row r="194" spans="1:33" ht="11.5" customHeight="1">
       <c r="A194" s="205">
         <v>46035</v>
       </c>
@@ -22860,7 +22860,7 @@
       <c r="AF194" s="104"/>
       <c r="AG194" s="104"/>
     </row>
-    <row r="195" spans="1:33" ht="11.45" customHeight="1">
+    <row r="195" spans="1:33" ht="11.5" customHeight="1">
       <c r="A195" s="207">
         <v>46035</v>
       </c>
@@ -22917,7 +22917,7 @@
       <c r="AF195" s="106"/>
       <c r="AG195" s="106"/>
     </row>
-    <row r="196" spans="1:33" ht="11.45" customHeight="1">
+    <row r="196" spans="1:33" ht="11.5" customHeight="1">
       <c r="A196" s="206">
         <v>46035</v>
       </c>
@@ -22976,7 +22976,7 @@
       <c r="AF196" s="78"/>
       <c r="AG196" s="78"/>
     </row>
-    <row r="197" spans="1:33" ht="11.45" customHeight="1">
+    <row r="197" spans="1:33" ht="11.5" customHeight="1">
       <c r="A197" s="204">
         <v>46057</v>
       </c>
@@ -23035,7 +23035,7 @@
       <c r="AF197" s="88"/>
       <c r="AG197" s="88"/>
     </row>
-    <row r="198" spans="1:33" ht="11.45" customHeight="1">
+    <row r="198" spans="1:33" ht="11.5" customHeight="1">
       <c r="A198" s="203">
         <v>46057</v>
       </c>
@@ -23094,7 +23094,7 @@
       <c r="AF198" s="56"/>
       <c r="AG198" s="56"/>
     </row>
-    <row r="199" spans="1:33" ht="11.45" customHeight="1">
+    <row r="199" spans="1:33" ht="11.5" customHeight="1">
       <c r="A199" s="214">
         <v>46035</v>
       </c>
@@ -23151,7 +23151,7 @@
       <c r="AF199" s="81"/>
       <c r="AG199" s="81"/>
     </row>
-    <row r="200" spans="1:33" ht="11.45" customHeight="1">
+    <row r="200" spans="1:33" ht="11.5" customHeight="1">
       <c r="A200" s="214">
         <v>46058</v>
       </c>
@@ -23204,7 +23204,7 @@
       <c r="AF200" s="81"/>
       <c r="AG200" s="81"/>
     </row>
-    <row r="201" spans="1:33" ht="11.45" customHeight="1">
+    <row r="201" spans="1:33" ht="11.5" customHeight="1">
       <c r="A201" s="209">
         <v>46051</v>
       </c>
@@ -23261,7 +23261,7 @@
       <c r="AF201" s="102"/>
       <c r="AG201" s="102"/>
     </row>
-    <row r="202" spans="1:33" ht="11.45" customHeight="1">
+    <row r="202" spans="1:33" ht="11.5" customHeight="1">
       <c r="A202" s="205">
         <v>46051</v>
       </c>
@@ -23320,7 +23320,7 @@
       <c r="AF202" s="104"/>
       <c r="AG202" s="104"/>
     </row>
-    <row r="203" spans="1:33" ht="11.45" customHeight="1">
+    <row r="203" spans="1:33" ht="11.5" customHeight="1">
       <c r="A203" s="207">
         <v>46051</v>
       </c>
@@ -23383,7 +23383,7 @@
       <c r="AF203" s="106"/>
       <c r="AG203" s="106"/>
     </row>
-    <row r="204" spans="1:33" ht="11.45" customHeight="1">
+    <row r="204" spans="1:33" ht="11.5" customHeight="1">
       <c r="A204" s="206">
         <v>46051</v>
       </c>
@@ -23440,7 +23440,7 @@
       <c r="AF204" s="78"/>
       <c r="AG204" s="78"/>
     </row>
-    <row r="205" spans="1:33" ht="11.45" customHeight="1">
+    <row r="205" spans="1:33" ht="11.5" customHeight="1">
       <c r="A205" s="203">
         <v>46051</v>
       </c>
@@ -23499,7 +23499,7 @@
       <c r="AF205" s="56"/>
       <c r="AG205" s="56"/>
     </row>
-    <row r="206" spans="1:33" ht="11.45" customHeight="1">
+    <row r="206" spans="1:33" ht="11.5" customHeight="1">
       <c r="A206" s="214">
         <v>46051</v>
       </c>
@@ -23558,7 +23558,7 @@
       <c r="AF206" s="81"/>
       <c r="AG206" s="81"/>
     </row>
-    <row r="207" spans="1:33" ht="11.45" customHeight="1">
+    <row r="207" spans="1:33" ht="11.5" customHeight="1">
       <c r="A207" s="209">
         <v>46051</v>
       </c>
@@ -23615,7 +23615,7 @@
       <c r="AF207" s="102"/>
       <c r="AG207" s="102"/>
     </row>
-    <row r="208" spans="1:33" ht="11.45" customHeight="1">
+    <row r="208" spans="1:33" ht="11.5" customHeight="1">
       <c r="A208" s="205">
         <v>46051</v>
       </c>
@@ -23672,7 +23672,7 @@
       <c r="AF208" s="104"/>
       <c r="AG208" s="104"/>
     </row>
-    <row r="209" spans="1:33" ht="11.45" customHeight="1">
+    <row r="209" spans="1:33" ht="11.5" customHeight="1">
       <c r="A209" s="207">
         <v>46051</v>
       </c>
@@ -23722,7 +23722,7 @@
       <c r="AF209" s="106"/>
       <c r="AG209" s="106"/>
     </row>
-    <row r="210" spans="1:33" ht="11.45" customHeight="1">
+    <row r="210" spans="1:33" ht="11.5" customHeight="1">
       <c r="A210" s="206">
         <v>46051</v>
       </c>
@@ -23779,7 +23779,7 @@
       <c r="AF210" s="78"/>
       <c r="AG210" s="78"/>
     </row>
-    <row r="211" spans="1:33" ht="11.45" customHeight="1">
+    <row r="211" spans="1:33" ht="11.5" customHeight="1">
       <c r="A211" s="204">
         <v>46051</v>
       </c>
@@ -23833,7 +23833,7 @@
       <c r="AF211" s="88"/>
       <c r="AG211" s="88"/>
     </row>
-    <row r="212" spans="1:33" ht="11.45" customHeight="1">
+    <row r="212" spans="1:33" ht="11.5" customHeight="1">
       <c r="A212" s="203">
         <v>46051</v>
       </c>
@@ -23890,7 +23890,7 @@
       <c r="AF212" s="56"/>
       <c r="AG212" s="56"/>
     </row>
-    <row r="213" spans="1:33" ht="11.45" customHeight="1">
+    <row r="213" spans="1:33" ht="11.5" customHeight="1">
       <c r="A213" s="214">
         <v>46051</v>
       </c>
@@ -23949,7 +23949,7 @@
       <c r="AF213" s="81"/>
       <c r="AG213" s="81"/>
     </row>
-    <row r="214" spans="1:33" ht="11.45" customHeight="1">
+    <row r="214" spans="1:33" ht="11.5" customHeight="1">
       <c r="A214" s="209">
         <v>46051</v>
       </c>
@@ -24006,7 +24006,7 @@
       <c r="AF214" s="102"/>
       <c r="AG214" s="102"/>
     </row>
-    <row r="215" spans="1:33" ht="11.45" customHeight="1">
+    <row r="215" spans="1:33" ht="11.5" customHeight="1">
       <c r="A215" s="205">
         <v>46051</v>
       </c>
@@ -24065,7 +24065,7 @@
       <c r="AF215" s="104"/>
       <c r="AG215" s="104"/>
     </row>
-    <row r="216" spans="1:33" ht="11.45" customHeight="1">
+    <row r="216" spans="1:33" ht="11.5" customHeight="1">
       <c r="A216" s="207">
         <v>46051</v>
       </c>
@@ -24122,7 +24122,7 @@
       <c r="AF216" s="106"/>
       <c r="AG216" s="106"/>
     </row>
-    <row r="217" spans="1:33" ht="11.45" customHeight="1">
+    <row r="217" spans="1:33" ht="11.5" customHeight="1">
       <c r="A217" s="206">
         <v>46051</v>
       </c>
@@ -24185,7 +24185,7 @@
       <c r="AF217" s="78"/>
       <c r="AG217" s="78"/>
     </row>
-    <row r="218" spans="1:33" ht="11.45" customHeight="1">
+    <row r="218" spans="1:33" ht="11.5" customHeight="1">
       <c r="A218" s="204">
         <v>46051</v>
       </c>
@@ -24244,7 +24244,7 @@
       <c r="AF218" s="88"/>
       <c r="AG218" s="88"/>
     </row>
-    <row r="219" spans="1:33" ht="11.45" customHeight="1">
+    <row r="219" spans="1:33" ht="11.5" customHeight="1">
       <c r="A219" s="203">
         <v>46051</v>
       </c>
@@ -24303,7 +24303,7 @@
       <c r="AF219" s="56"/>
       <c r="AG219" s="56"/>
     </row>
-    <row r="220" spans="1:33" ht="11.45" customHeight="1">
+    <row r="220" spans="1:33" ht="11.5" customHeight="1">
       <c r="A220" s="214">
         <v>46051</v>
       </c>
@@ -24360,7 +24360,7 @@
       <c r="AF220" s="81"/>
       <c r="AG220" s="81"/>
     </row>
-    <row r="221" spans="1:33" ht="11.45" customHeight="1">
+    <row r="221" spans="1:33" ht="11.5" customHeight="1">
       <c r="A221" s="209">
         <v>46051</v>
       </c>
@@ -24423,7 +24423,7 @@
       <c r="AF221" s="102"/>
       <c r="AG221" s="102"/>
     </row>
-    <row r="222" spans="1:33" ht="11.45" customHeight="1">
+    <row r="222" spans="1:33" ht="11.5" customHeight="1">
       <c r="A222" s="205">
         <v>46051</v>
       </c>
@@ -24486,7 +24486,7 @@
       <c r="AF222" s="104"/>
       <c r="AG222" s="104"/>
     </row>
-    <row r="223" spans="1:33" ht="11.45" customHeight="1">
+    <row r="223" spans="1:33" ht="11.5" customHeight="1">
       <c r="A223" s="207">
         <v>46051</v>
       </c>
@@ -24543,7 +24543,7 @@
       <c r="AF223" s="106"/>
       <c r="AG223" s="106"/>
     </row>
-    <row r="224" spans="1:33" ht="11.45" customHeight="1">
+    <row r="224" spans="1:33" ht="11.5" customHeight="1">
       <c r="A224" s="206">
         <v>46051</v>
       </c>
@@ -24602,7 +24602,7 @@
       <c r="AF224" s="78"/>
       <c r="AG224" s="78"/>
     </row>
-    <row r="225" spans="1:33" ht="11.45" customHeight="1">
+    <row r="225" spans="1:33" ht="11.5" customHeight="1">
       <c r="A225" s="204">
         <v>46051</v>
       </c>
@@ -24659,7 +24659,7 @@
       <c r="AF225" s="88"/>
       <c r="AG225" s="88"/>
     </row>
-    <row r="226" spans="1:33" ht="11.45" customHeight="1">
+    <row r="226" spans="1:33" ht="11.5" customHeight="1">
       <c r="A226" s="203">
         <v>46051</v>
       </c>
@@ -24712,7 +24712,7 @@
       <c r="AF226" s="56"/>
       <c r="AG226" s="56"/>
     </row>
-    <row r="227" spans="1:33" ht="11.45" customHeight="1">
+    <row r="227" spans="1:33" ht="11.5" customHeight="1">
       <c r="A227" s="214">
         <v>46051</v>
       </c>
@@ -24777,7 +24777,7 @@
       <c r="AF227" s="81"/>
       <c r="AG227" s="81"/>
     </row>
-    <row r="228" spans="1:33" ht="11.45" customHeight="1">
+    <row r="228" spans="1:33" ht="11.5" customHeight="1">
       <c r="A228" s="209">
         <v>46056</v>
       </c>
@@ -24840,7 +24840,7 @@
       <c r="AF228" s="102"/>
       <c r="AG228" s="102"/>
     </row>
-    <row r="229" spans="1:33" ht="11.45" customHeight="1">
+    <row r="229" spans="1:33" ht="11.5" customHeight="1">
       <c r="A229" s="205">
         <v>46056</v>
       </c>
@@ -24897,7 +24897,7 @@
       <c r="AF229" s="104"/>
       <c r="AG229" s="104"/>
     </row>
-    <row r="230" spans="1:33" ht="11.45" customHeight="1">
+    <row r="230" spans="1:33" ht="11.5" customHeight="1">
       <c r="A230" s="207">
         <v>46056</v>
       </c>
@@ -24952,7 +24952,7 @@
       <c r="AF230" s="106"/>
       <c r="AG230" s="106"/>
     </row>
-    <row r="231" spans="1:33" ht="11.45" customHeight="1">
+    <row r="231" spans="1:33" ht="11.5" customHeight="1">
       <c r="A231" s="206">
         <v>46051</v>
       </c>
@@ -25013,7 +25013,7 @@
       <c r="AF231" s="78"/>
       <c r="AG231" s="78"/>
     </row>
-    <row r="232" spans="1:33" ht="11.45" customHeight="1">
+    <row r="232" spans="1:33" ht="11.5" customHeight="1">
       <c r="G232" s="102"/>
       <c r="H232" s="119" t="s">
         <v>167</v>
@@ -25053,7 +25053,7 @@
       <c r="AF232" s="102"/>
       <c r="AG232" s="102"/>
     </row>
-    <row r="233" spans="1:33" ht="11.45" customHeight="1">
+    <row r="233" spans="1:33" ht="11.5" customHeight="1">
       <c r="A233" s="204">
         <v>46056</v>
       </c>
@@ -25110,7 +25110,7 @@
       <c r="AF233" s="88"/>
       <c r="AG233" s="88"/>
     </row>
-    <row r="234" spans="1:33" ht="11.45" customHeight="1">
+    <row r="234" spans="1:33" ht="11.5" customHeight="1">
       <c r="A234" s="203">
         <v>46056</v>
       </c>
@@ -25167,7 +25167,7 @@
       <c r="AF234" s="56"/>
       <c r="AG234" s="56"/>
     </row>
-    <row r="235" spans="1:33" ht="11.45" customHeight="1">
+    <row r="235" spans="1:33" ht="11.5" customHeight="1">
       <c r="A235" s="214">
         <v>46051</v>
       </c>
@@ -25232,7 +25232,7 @@
       <c r="AF235" s="81"/>
       <c r="AG235" s="81"/>
     </row>
-    <row r="236" spans="1:33" ht="11.45" customHeight="1">
+    <row r="236" spans="1:33" ht="11.5" customHeight="1">
       <c r="A236" s="209">
         <v>46051</v>
       </c>
@@ -25297,7 +25297,7 @@
       <c r="AF236" s="102"/>
       <c r="AG236" s="102"/>
     </row>
-    <row r="237" spans="1:33" ht="11.45" customHeight="1">
+    <row r="237" spans="1:33" ht="11.5" customHeight="1">
       <c r="A237" s="205">
         <v>46056</v>
       </c>
@@ -25358,7 +25358,7 @@
       <c r="AF237" s="104"/>
       <c r="AG237" s="104"/>
     </row>
-    <row r="238" spans="1:33" ht="11.45" customHeight="1">
+    <row r="238" spans="1:33" ht="11.5" customHeight="1">
       <c r="A238" s="207">
         <v>46056</v>
       </c>
@@ -25421,7 +25421,7 @@
       <c r="AF238" s="106"/>
       <c r="AG238" s="106"/>
     </row>
-    <row r="239" spans="1:33" ht="11.45" customHeight="1">
+    <row r="239" spans="1:33" ht="11.5" customHeight="1">
       <c r="A239" s="206">
         <v>46056</v>
       </c>
@@ -25482,7 +25482,7 @@
       <c r="AF239" s="78"/>
       <c r="AG239" s="78"/>
     </row>
-    <row r="240" spans="1:33" ht="11.45" customHeight="1">
+    <row r="240" spans="1:33" ht="11.5" customHeight="1">
       <c r="A240" s="204">
         <v>46056</v>
       </c>
@@ -25541,7 +25541,7 @@
       <c r="AF240" s="88"/>
       <c r="AG240" s="88"/>
     </row>
-    <row r="241" spans="1:33" ht="11.45" customHeight="1">
+    <row r="241" spans="1:33" ht="11.5" customHeight="1">
       <c r="A241" s="203">
         <v>46056</v>
       </c>
@@ -25596,7 +25596,7 @@
       <c r="AF241" s="56"/>
       <c r="AG241" s="56"/>
     </row>
-    <row r="242" spans="1:33" ht="11.45" customHeight="1">
+    <row r="242" spans="1:33" ht="11.5" customHeight="1">
       <c r="A242" s="214">
         <v>46051</v>
       </c>
@@ -25655,7 +25655,7 @@
       <c r="AF242" s="81"/>
       <c r="AG242" s="81"/>
     </row>
-    <row r="243" spans="1:33" ht="11.45" customHeight="1">
+    <row r="243" spans="1:33" ht="11.5" customHeight="1">
       <c r="A243" s="413" t="s">
         <v>1375</v>
       </c>
@@ -25702,7 +25702,7 @@
       <c r="AF243" s="102"/>
       <c r="AG243" s="102"/>
     </row>
-    <row r="244" spans="1:33" ht="11.45" customHeight="1">
+    <row r="244" spans="1:33" ht="11.5" customHeight="1">
       <c r="A244" s="205">
         <v>46056</v>
       </c>
@@ -25761,7 +25761,7 @@
       <c r="AF244" s="104"/>
       <c r="AG244" s="104"/>
     </row>
-    <row r="245" spans="1:33" ht="11.45" customHeight="1">
+    <row r="245" spans="1:33" ht="11.5" customHeight="1">
       <c r="A245" s="207">
         <v>46056</v>
       </c>
@@ -25822,7 +25822,7 @@
       <c r="AF245" s="106"/>
       <c r="AG245" s="106"/>
     </row>
-    <row r="246" spans="1:33" ht="11.45" customHeight="1" thickBot="1">
+    <row r="246" spans="1:33" ht="11.5" customHeight="1" thickBot="1">
       <c r="A246" s="206">
         <v>46056</v>
       </c>
@@ -25885,7 +25885,7 @@
       <c r="AF246" s="78"/>
       <c r="AG246" s="78"/>
     </row>
-    <row r="247" spans="1:33" ht="11.45" customHeight="1" thickBot="1">
+    <row r="247" spans="1:33" ht="11.5" customHeight="1" thickBot="1">
       <c r="A247" s="204">
         <v>46056</v>
       </c>
@@ -25942,7 +25942,7 @@
       <c r="AF247" s="88"/>
       <c r="AG247" s="88"/>
     </row>
-    <row r="248" spans="1:33" ht="11.45" customHeight="1" thickBot="1">
+    <row r="248" spans="1:33" ht="11.5" customHeight="1" thickBot="1">
       <c r="A248" s="203">
         <v>46051</v>
       </c>
@@ -26005,7 +26005,7 @@
       <c r="AF248" s="56"/>
       <c r="AG248" s="56"/>
     </row>
-    <row r="249" spans="1:33" ht="11.45" customHeight="1" thickBot="1">
+    <row r="249" spans="1:33" ht="11.5" customHeight="1" thickBot="1">
       <c r="A249" s="214">
         <v>46056</v>
       </c>
@@ -26064,7 +26064,7 @@
       <c r="AF249" s="81"/>
       <c r="AG249" s="81"/>
     </row>
-    <row r="250" spans="1:33" ht="11.45" customHeight="1">
+    <row r="250" spans="1:33" ht="11.5" customHeight="1">
       <c r="A250" s="209">
         <v>46056</v>
       </c>
@@ -26121,7 +26121,7 @@
       <c r="AF250" s="102"/>
       <c r="AG250" s="102"/>
     </row>
-    <row r="251" spans="1:33" ht="11.45" customHeight="1">
+    <row r="251" spans="1:33" ht="11.5" customHeight="1">
       <c r="A251" s="205">
         <v>46051</v>
       </c>
@@ -26182,7 +26182,7 @@
       <c r="AF251" s="104"/>
       <c r="AG251" s="104"/>
     </row>
-    <row r="252" spans="1:33" ht="11.45" customHeight="1">
+    <row r="252" spans="1:33" ht="11.5" customHeight="1">
       <c r="A252" s="207">
         <v>46056</v>
       </c>
@@ -26239,7 +26239,7 @@
       <c r="AF252" s="106"/>
       <c r="AG252" s="106"/>
     </row>
-    <row r="253" spans="1:33" ht="11.45" customHeight="1">
+    <row r="253" spans="1:33" ht="11.5" customHeight="1">
       <c r="A253" s="206">
         <v>46056</v>
       </c>
@@ -26294,7 +26294,7 @@
       <c r="AF253" s="78"/>
       <c r="AG253" s="78"/>
     </row>
-    <row r="254" spans="1:33" ht="11.45" customHeight="1">
+    <row r="254" spans="1:33" ht="11.5" customHeight="1">
       <c r="A254" s="204">
         <v>46056</v>
       </c>
@@ -26349,7 +26349,7 @@
       <c r="AF254" s="88"/>
       <c r="AG254" s="88"/>
     </row>
-    <row r="255" spans="1:33" ht="11.45" customHeight="1">
+    <row r="255" spans="1:33" ht="11.5" customHeight="1">
       <c r="A255" s="204">
         <v>46058</v>
       </c>
@@ -26397,7 +26397,7 @@
       <c r="AF255" s="88"/>
       <c r="AG255" s="88"/>
     </row>
-    <row r="256" spans="1:33" ht="11.45" customHeight="1">
+    <row r="256" spans="1:33" ht="11.5" customHeight="1">
       <c r="A256" s="203">
         <v>46056</v>
       </c>
@@ -26462,7 +26462,7 @@
       <c r="AF256" s="56"/>
       <c r="AG256" s="56"/>
     </row>
-    <row r="257" spans="1:33" ht="11.45" customHeight="1">
+    <row r="257" spans="1:33" ht="11.5" customHeight="1">
       <c r="A257" s="214">
         <v>46057</v>
       </c>
@@ -26519,7 +26519,7 @@
       <c r="AF257" s="81"/>
       <c r="AG257" s="81"/>
     </row>
-    <row r="258" spans="1:33" ht="11.45" customHeight="1">
+    <row r="258" spans="1:33" ht="11.5" customHeight="1">
       <c r="A258" s="209">
         <v>46051</v>
       </c>
@@ -26578,7 +26578,7 @@
       <c r="AF258" s="102"/>
       <c r="AG258" s="102"/>
     </row>
-    <row r="259" spans="1:33" ht="11.45" customHeight="1">
+    <row r="259" spans="1:33" ht="11.5" customHeight="1">
       <c r="A259" s="205">
         <v>46057</v>
       </c>
@@ -26639,7 +26639,7 @@
       <c r="AF259" s="104"/>
       <c r="AG259" s="104"/>
     </row>
-    <row r="260" spans="1:33" ht="11.45" customHeight="1">
+    <row r="260" spans="1:33" ht="11.5" customHeight="1">
       <c r="A260" s="207">
         <v>46057</v>
       </c>
@@ -26698,7 +26698,7 @@
       <c r="AF260" s="106"/>
       <c r="AG260" s="106"/>
     </row>
-    <row r="261" spans="1:33" ht="11.45" customHeight="1">
+    <row r="261" spans="1:33" ht="11.5" customHeight="1">
       <c r="A261" s="204">
         <v>46057</v>
       </c>
@@ -26757,7 +26757,7 @@
       <c r="AF261" s="88"/>
       <c r="AG261" s="88"/>
     </row>
-    <row r="262" spans="1:33" ht="11.45" customHeight="1">
+    <row r="262" spans="1:33" ht="11.5" customHeight="1">
       <c r="A262" s="203">
         <v>46057</v>
       </c>
@@ -26816,7 +26816,7 @@
       <c r="AF262" s="56"/>
       <c r="AG262" s="56"/>
     </row>
-    <row r="263" spans="1:33" ht="11.45" customHeight="1">
+    <row r="263" spans="1:33" ht="11.5" customHeight="1">
       <c r="A263" s="214">
         <v>46051</v>
       </c>
@@ -26873,7 +26873,7 @@
       <c r="AF263" s="81"/>
       <c r="AG263" s="81"/>
     </row>
-    <row r="264" spans="1:33" ht="11.45" customHeight="1">
+    <row r="264" spans="1:33" ht="11.5" customHeight="1">
       <c r="A264" s="209">
         <v>46051</v>
       </c>
@@ -26930,7 +26930,7 @@
       <c r="AF264" s="102"/>
       <c r="AG264" s="102"/>
     </row>
-    <row r="265" spans="1:33" ht="11.45" customHeight="1">
+    <row r="265" spans="1:33" ht="11.5" customHeight="1">
       <c r="A265" s="205">
         <v>46051</v>
       </c>
@@ -26987,7 +26987,7 @@
       <c r="AF265" s="104"/>
       <c r="AG265" s="104"/>
     </row>
-    <row r="266" spans="1:33" ht="11.45" customHeight="1">
+    <row r="266" spans="1:33" ht="11.5" customHeight="1">
       <c r="A266" s="207">
         <v>46051</v>
       </c>
@@ -27044,7 +27044,7 @@
       <c r="AF266" s="106"/>
       <c r="AG266" s="106"/>
     </row>
-    <row r="267" spans="1:33" ht="11.45" customHeight="1">
+    <row r="267" spans="1:33" ht="11.5" customHeight="1">
       <c r="A267" s="204">
         <v>46057</v>
       </c>
@@ -27105,7 +27105,7 @@
       <c r="AF267" s="88"/>
       <c r="AG267" s="88"/>
     </row>
-    <row r="268" spans="1:33" ht="11.45" customHeight="1">
+    <row r="268" spans="1:33" ht="11.5" customHeight="1">
       <c r="A268" s="203">
         <v>46057</v>
       </c>
@@ -27166,7 +27166,7 @@
       <c r="AF268" s="56"/>
       <c r="AG268" s="56"/>
     </row>
-    <row r="269" spans="1:33" ht="11.45" customHeight="1">
+    <row r="269" spans="1:33" ht="11.5" customHeight="1">
       <c r="A269" s="209">
         <v>46057</v>
       </c>
@@ -27227,7 +27227,7 @@
       <c r="AF269" s="102"/>
       <c r="AG269" s="102"/>
     </row>
-    <row r="270" spans="1:33" s="302" customFormat="1" ht="11.45" customHeight="1">
+    <row r="270" spans="1:33" s="302" customFormat="1" ht="11.5" customHeight="1">
       <c r="A270" s="358">
         <v>46057</v>
       </c>
@@ -27290,7 +27290,7 @@
       <c r="AF270" s="360"/>
       <c r="AG270" s="360"/>
     </row>
-    <row r="271" spans="1:33" ht="11.45" customHeight="1">
+    <row r="271" spans="1:33" ht="11.5" customHeight="1">
       <c r="A271" s="209">
         <v>46057</v>
       </c>
@@ -27347,7 +27347,7 @@
       <c r="AF271" s="102"/>
       <c r="AG271" s="102"/>
     </row>
-    <row r="272" spans="1:33" ht="11.45" customHeight="1">
+    <row r="272" spans="1:33" ht="11.5" customHeight="1">
       <c r="A272" s="205">
         <v>46057</v>
       </c>
@@ -27402,7 +27402,7 @@
       <c r="AF272" s="104"/>
       <c r="AG272" s="104"/>
     </row>
-    <row r="273" spans="1:33" ht="11.45" customHeight="1">
+    <row r="273" spans="1:33" ht="11.5" customHeight="1">
       <c r="A273" s="204">
         <v>46057</v>
       </c>
@@ -27459,7 +27459,7 @@
       <c r="AF273" s="88"/>
       <c r="AG273" s="88"/>
     </row>
-    <row r="274" spans="1:33" ht="11.45" customHeight="1">
+    <row r="274" spans="1:33" ht="11.5" customHeight="1">
       <c r="A274" s="209">
         <v>46057</v>
       </c>
@@ -27514,7 +27514,7 @@
       <c r="AF274" s="81"/>
       <c r="AG274" s="81"/>
     </row>
-    <row r="275" spans="1:33" ht="11.45" customHeight="1">
+    <row r="275" spans="1:33" ht="11.5" customHeight="1">
       <c r="A275" s="205">
         <v>46057</v>
       </c>
@@ -27571,7 +27571,7 @@
       <c r="AF275" s="104"/>
       <c r="AG275" s="104"/>
     </row>
-    <row r="276" spans="1:33" ht="11.45" customHeight="1">
+    <row r="276" spans="1:33" ht="11.5" customHeight="1">
       <c r="A276" s="207">
         <v>46057</v>
       </c>
@@ -27627,7 +27627,7 @@
       <c r="AF276" s="106"/>
       <c r="AG276" s="106"/>
     </row>
-    <row r="277" spans="1:33" ht="11.45" customHeight="1">
+    <row r="277" spans="1:33" ht="11.5" customHeight="1">
       <c r="A277" s="209">
         <v>46057</v>
       </c>
@@ -27688,7 +27688,7 @@
       <c r="AF277" s="102"/>
       <c r="AG277" s="102"/>
     </row>
-    <row r="278" spans="1:33" ht="11.45" customHeight="1">
+    <row r="278" spans="1:33" ht="11.5" customHeight="1">
       <c r="A278" s="209">
         <v>46057</v>
       </c>
@@ -27745,7 +27745,7 @@
       <c r="AF278" s="106"/>
       <c r="AG278" s="106"/>
     </row>
-    <row r="279" spans="1:33" ht="11.45" customHeight="1">
+    <row r="279" spans="1:33" ht="11.5" customHeight="1">
       <c r="A279" s="209"/>
       <c r="B279" s="209"/>
       <c r="C279" s="365"/>
@@ -27804,7 +27804,7 @@
       <c r="AF279" s="78"/>
       <c r="AG279" s="78"/>
     </row>
-    <row r="280" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="280" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A280" s="278">
         <v>46057</v>
       </c>
@@ -27863,7 +27863,7 @@
       <c r="AF280" s="274"/>
       <c r="AG280" s="274"/>
     </row>
-    <row r="281" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="281" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A281" s="278"/>
       <c r="B281" s="278">
         <v>46072</v>
@@ -27906,7 +27906,7 @@
       <c r="AF281" s="274"/>
       <c r="AG281" s="274"/>
     </row>
-    <row r="282" spans="1:33" ht="11.45" customHeight="1">
+    <row r="282" spans="1:33" ht="11.5" customHeight="1">
       <c r="A282" s="205">
         <v>46035</v>
       </c>
@@ -27963,7 +27963,7 @@
       <c r="AF282" s="104"/>
       <c r="AG282" s="104"/>
     </row>
-    <row r="283" spans="1:33" ht="11.45" customHeight="1">
+    <row r="283" spans="1:33" ht="11.5" customHeight="1">
       <c r="A283" s="203">
         <v>46057</v>
       </c>
@@ -28020,7 +28020,7 @@
       <c r="AF283" s="56"/>
       <c r="AG283" s="56"/>
     </row>
-    <row r="284" spans="1:33" ht="11.45" customHeight="1">
+    <row r="284" spans="1:33" ht="11.5" customHeight="1">
       <c r="A284" s="209">
         <v>46057</v>
       </c>
@@ -28075,7 +28075,7 @@
       <c r="AF284" s="102"/>
       <c r="AG284" s="102"/>
     </row>
-    <row r="285" spans="1:33" ht="11.45" customHeight="1">
+    <row r="285" spans="1:33" ht="11.5" customHeight="1">
       <c r="A285" s="206">
         <v>46057</v>
       </c>
@@ -28134,7 +28134,7 @@
       <c r="AF285" s="78"/>
       <c r="AG285" s="78"/>
     </row>
-    <row r="286" spans="1:33" ht="11.45" customHeight="1">
+    <row r="286" spans="1:33" ht="11.5" customHeight="1">
       <c r="A286" s="207">
         <v>46057</v>
       </c>
@@ -28195,7 +28195,7 @@
       <c r="AF286" s="106"/>
       <c r="AG286" s="106"/>
     </row>
-    <row r="287" spans="1:33" ht="11.45" customHeight="1">
+    <row r="287" spans="1:33" ht="11.5" customHeight="1">
       <c r="A287" s="206">
         <v>46057</v>
       </c>
@@ -28254,7 +28254,7 @@
       <c r="AF287" s="78"/>
       <c r="AG287" s="78"/>
     </row>
-    <row r="288" spans="1:33" ht="11.45" customHeight="1">
+    <row r="288" spans="1:33" ht="11.5" customHeight="1">
       <c r="A288" s="204">
         <v>46056</v>
       </c>
@@ -28313,7 +28313,7 @@
       <c r="AF288" s="56"/>
       <c r="AG288" s="56"/>
     </row>
-    <row r="289" spans="1:33" ht="11.45" customHeight="1">
+    <row r="289" spans="1:33" ht="11.5" customHeight="1">
       <c r="A289" s="214">
         <v>46057</v>
       </c>
@@ -28372,7 +28372,7 @@
       <c r="AF289" s="81"/>
       <c r="AG289" s="81"/>
     </row>
-    <row r="290" spans="1:33" ht="11.45" customHeight="1">
+    <row r="290" spans="1:33" ht="11.5" customHeight="1">
       <c r="A290" s="204">
         <v>46057</v>
       </c>
@@ -28433,7 +28433,7 @@
       <c r="AF290" s="88"/>
       <c r="AG290" s="88"/>
     </row>
-    <row r="291" spans="1:33" ht="11.45" customHeight="1">
+    <row r="291" spans="1:33" ht="11.5" customHeight="1">
       <c r="A291" s="203">
         <v>46057</v>
       </c>
@@ -28496,7 +28496,7 @@
       <c r="AF291" s="56"/>
       <c r="AG291" s="56"/>
     </row>
-    <row r="292" spans="1:33" ht="11.45" customHeight="1">
+    <row r="292" spans="1:33" ht="11.5" customHeight="1">
       <c r="A292" s="209">
         <v>46057</v>
       </c>
@@ -28557,7 +28557,7 @@
       <c r="AF292" s="102"/>
       <c r="AG292" s="102"/>
     </row>
-    <row r="293" spans="1:33" ht="11.45" customHeight="1">
+    <row r="293" spans="1:33" ht="11.5" customHeight="1">
       <c r="A293" s="205">
         <v>46057</v>
       </c>
@@ -28618,7 +28618,7 @@
       <c r="AF293" s="104"/>
       <c r="AG293" s="104"/>
     </row>
-    <row r="294" spans="1:33" ht="11.45" customHeight="1">
+    <row r="294" spans="1:33" ht="11.5" customHeight="1">
       <c r="A294" s="205">
         <v>46057</v>
       </c>
@@ -28675,7 +28675,7 @@
       <c r="AF294" s="104"/>
       <c r="AG294" s="104"/>
     </row>
-    <row r="295" spans="1:33" ht="11.45" customHeight="1">
+    <row r="295" spans="1:33" ht="11.5" customHeight="1">
       <c r="A295" s="207">
         <v>46051</v>
       </c>
@@ -28734,7 +28734,7 @@
       <c r="AF295" s="106"/>
       <c r="AG295" s="106"/>
     </row>
-    <row r="296" spans="1:33" ht="11.45" customHeight="1">
+    <row r="296" spans="1:33" ht="11.5" customHeight="1">
       <c r="A296" s="206">
         <v>46058</v>
       </c>
@@ -28797,7 +28797,7 @@
       <c r="AF296" s="78"/>
       <c r="AG296" s="78"/>
     </row>
-    <row r="297" spans="1:33" ht="11.45" customHeight="1">
+    <row r="297" spans="1:33" ht="11.5" customHeight="1">
       <c r="A297" s="204">
         <v>46057</v>
       </c>
@@ -28858,7 +28858,7 @@
       <c r="AF297" s="88"/>
       <c r="AG297" s="88"/>
     </row>
-    <row r="298" spans="1:33" ht="11.45" customHeight="1">
+    <row r="298" spans="1:33" ht="11.5" customHeight="1">
       <c r="A298" s="205">
         <v>46063</v>
       </c>
@@ -28917,7 +28917,7 @@
       <c r="AF298" s="104"/>
       <c r="AG298" s="104"/>
     </row>
-    <row r="299" spans="1:33" ht="11.45" customHeight="1">
+    <row r="299" spans="1:33" ht="11.5" customHeight="1">
       <c r="A299" s="207">
         <v>46063</v>
       </c>
@@ -28974,7 +28974,7 @@
       <c r="AF299" s="106"/>
       <c r="AG299" s="106"/>
     </row>
-    <row r="300" spans="1:33" ht="11.45" customHeight="1">
+    <row r="300" spans="1:33" ht="11.5" customHeight="1">
       <c r="A300" s="206">
         <v>46063</v>
       </c>
@@ -29033,7 +29033,7 @@
       <c r="AF300" s="78"/>
       <c r="AG300" s="78"/>
     </row>
-    <row r="301" spans="1:33" ht="11.45" customHeight="1">
+    <row r="301" spans="1:33" ht="11.5" customHeight="1">
       <c r="A301" s="204">
         <v>46063</v>
       </c>
@@ -29092,7 +29092,7 @@
       <c r="AF301" s="88"/>
       <c r="AG301" s="88"/>
     </row>
-    <row r="302" spans="1:33" ht="11.45" customHeight="1">
+    <row r="302" spans="1:33" ht="11.5" customHeight="1">
       <c r="A302" s="203">
         <v>46063</v>
       </c>
@@ -29153,7 +29153,7 @@
       <c r="AF302" s="56"/>
       <c r="AG302" s="56"/>
     </row>
-    <row r="303" spans="1:33" ht="11.45" customHeight="1">
+    <row r="303" spans="1:33" ht="11.5" customHeight="1">
       <c r="A303" s="214"/>
       <c r="B303" s="214"/>
       <c r="C303" s="378"/>
@@ -29202,7 +29202,7 @@
       <c r="AF303" s="81"/>
       <c r="AG303" s="81"/>
     </row>
-    <row r="304" spans="1:33" ht="11.45" customHeight="1">
+    <row r="304" spans="1:33" ht="11.5" customHeight="1">
       <c r="A304" s="209"/>
       <c r="B304" s="209"/>
       <c r="C304" s="365"/>
@@ -29251,7 +29251,7 @@
       <c r="AF304" s="102"/>
       <c r="AG304" s="102"/>
     </row>
-    <row r="305" spans="1:33" ht="11.45" customHeight="1">
+    <row r="305" spans="1:33" ht="11.5" customHeight="1">
       <c r="A305" s="205">
         <v>46058</v>
       </c>
@@ -29310,7 +29310,7 @@
       <c r="AF305" s="104"/>
       <c r="AG305" s="104"/>
     </row>
-    <row r="306" spans="1:33" s="121" customFormat="1" ht="11.45" customHeight="1">
+    <row r="306" spans="1:33" s="121" customFormat="1" ht="11.5" customHeight="1">
       <c r="A306" s="414">
         <v>46066</v>
       </c>
@@ -29347,7 +29347,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="307" spans="1:33" ht="11.45" customHeight="1">
+    <row r="307" spans="1:33" ht="11.5" customHeight="1">
       <c r="A307" s="414">
         <v>46077</v>
       </c>
@@ -29397,7 +29397,7 @@
       <c r="AF307" s="81"/>
       <c r="AG307" s="81"/>
     </row>
-    <row r="308" spans="1:33" ht="11.45" customHeight="1">
+    <row r="308" spans="1:33" ht="11.5" customHeight="1">
       <c r="A308" s="414">
         <v>46077</v>
       </c>
@@ -29454,7 +29454,7 @@
       <c r="AF308" s="56"/>
       <c r="AG308" s="56"/>
     </row>
-    <row r="309" spans="1:33" ht="11.45" customHeight="1">
+    <row r="309" spans="1:33" ht="11.5" customHeight="1">
       <c r="A309" s="209">
         <v>46077</v>
       </c>
@@ -29499,7 +29499,7 @@
       <c r="AF309" s="102"/>
       <c r="AG309" s="102"/>
     </row>
-    <row r="310" spans="1:33" ht="11.45" customHeight="1">
+    <row r="310" spans="1:33" ht="11.5" customHeight="1">
       <c r="A310" s="209">
         <v>46077</v>
       </c>
@@ -29551,7 +29551,7 @@
       <c r="AF310" s="104"/>
       <c r="AG310" s="104"/>
     </row>
-    <row r="311" spans="1:33" ht="11.45" customHeight="1">
+    <row r="311" spans="1:33" ht="11.5" customHeight="1">
       <c r="A311" s="209">
         <v>46077</v>
       </c>
@@ -29603,7 +29603,7 @@
       <c r="AF311" s="106"/>
       <c r="AG311" s="106"/>
     </row>
-    <row r="312" spans="1:33" ht="11.45" customHeight="1">
+    <row r="312" spans="1:33" ht="11.5" customHeight="1">
       <c r="A312" s="205">
         <v>46077</v>
       </c>
@@ -29658,7 +29658,7 @@
       <c r="AF312" s="78"/>
       <c r="AG312" s="78"/>
     </row>
-    <row r="313" spans="1:33" ht="11.45" customHeight="1">
+    <row r="313" spans="1:33" ht="11.5" customHeight="1">
       <c r="A313" s="204">
         <v>46077</v>
       </c>
@@ -29713,7 +29713,7 @@
       <c r="AF313" s="88"/>
       <c r="AG313" s="88"/>
     </row>
-    <row r="314" spans="1:33" ht="11.45" customHeight="1">
+    <row r="314" spans="1:33" ht="11.5" customHeight="1">
       <c r="A314" s="203">
         <v>46077</v>
       </c>
@@ -29788,7 +29788,7 @@
       <c r="AF314" s="56"/>
       <c r="AG314" s="56"/>
     </row>
-    <row r="315" spans="1:33" ht="11.45" customHeight="1">
+    <row r="315" spans="1:33" ht="11.5" customHeight="1">
       <c r="A315" s="209">
         <v>46077</v>
       </c>
@@ -29842,7 +29842,7 @@
       <c r="AF315" s="102"/>
       <c r="AG315" s="102"/>
     </row>
-    <row r="316" spans="1:33" ht="11.45" customHeight="1">
+    <row r="316" spans="1:33" ht="11.5" customHeight="1">
       <c r="A316" s="207">
         <v>46077</v>
       </c>
@@ -29921,7 +29921,7 @@
       <c r="AF316" s="106"/>
       <c r="AG316" s="106"/>
     </row>
-    <row r="317" spans="1:33" ht="11.45" customHeight="1">
+    <row r="317" spans="1:33" ht="11.5" customHeight="1">
       <c r="A317" s="209">
         <v>46077</v>
       </c>
@@ -29972,7 +29972,7 @@
       <c r="AF317" s="78"/>
       <c r="AG317" s="78"/>
     </row>
-    <row r="318" spans="1:33" ht="11.45" customHeight="1">
+    <row r="318" spans="1:33" ht="11.5" customHeight="1">
       <c r="A318" s="204">
         <v>46079</v>
       </c>
@@ -30025,7 +30025,7 @@
       <c r="AF318" s="88"/>
       <c r="AG318" s="88"/>
     </row>
-    <row r="319" spans="1:33" ht="11.45" customHeight="1">
+    <row r="319" spans="1:33" ht="11.5" customHeight="1">
       <c r="A319" s="204">
         <v>46079</v>
       </c>
@@ -30080,7 +30080,7 @@
       <c r="AF319" s="56"/>
       <c r="AG319" s="56"/>
     </row>
-    <row r="320" spans="1:33" ht="11.45" customHeight="1">
+    <row r="320" spans="1:33" ht="11.5" customHeight="1">
       <c r="A320" s="204">
         <v>46079</v>
       </c>
@@ -30139,7 +30139,7 @@
       <c r="AF320" s="81"/>
       <c r="AG320" s="81"/>
     </row>
-    <row r="321" spans="1:33" ht="11.45" customHeight="1">
+    <row r="321" spans="1:33" ht="11.5" customHeight="1">
       <c r="A321" s="204">
         <v>46079</v>
       </c>
@@ -30194,7 +30194,7 @@
       <c r="AF321" s="102"/>
       <c r="AG321" s="102"/>
     </row>
-    <row r="322" spans="1:33" ht="11.45" customHeight="1">
+    <row r="322" spans="1:33" ht="11.5" customHeight="1">
       <c r="A322" s="204">
         <v>46079</v>
       </c>
@@ -30247,7 +30247,7 @@
       <c r="AF322" s="104"/>
       <c r="AG322" s="104"/>
     </row>
-    <row r="323" spans="1:33" ht="11.45" customHeight="1">
+    <row r="323" spans="1:33" ht="11.5" customHeight="1">
       <c r="A323" s="214">
         <v>46079</v>
       </c>
@@ -30324,7 +30324,7 @@
       <c r="AF323" s="81"/>
       <c r="AG323" s="81"/>
     </row>
-    <row r="324" spans="1:33" ht="11.45" customHeight="1">
+    <row r="324" spans="1:33" ht="11.5" customHeight="1">
       <c r="A324" s="214">
         <v>46079</v>
       </c>
@@ -30403,7 +30403,7 @@
       <c r="AF324" s="81"/>
       <c r="AG324" s="81"/>
     </row>
-    <row r="325" spans="1:33" ht="11.45" customHeight="1">
+    <row r="325" spans="1:33" ht="11.5" customHeight="1">
       <c r="A325" s="204">
         <v>46079</v>
       </c>
@@ -30480,7 +30480,7 @@
       <c r="AF325" s="88"/>
       <c r="AG325" s="88"/>
     </row>
-    <row r="326" spans="1:33" ht="11.45" customHeight="1">
+    <row r="326" spans="1:33" ht="11.5" customHeight="1">
       <c r="A326" s="206">
         <v>46079</v>
       </c>
@@ -30561,7 +30561,7 @@
       <c r="AF326" s="78"/>
       <c r="AG326" s="78"/>
     </row>
-    <row r="327" spans="1:33" ht="11.45" customHeight="1">
+    <row r="327" spans="1:33" ht="11.5" customHeight="1">
       <c r="A327" s="204">
         <v>46079</v>
       </c>
@@ -30636,7 +30636,7 @@
       <c r="AF327" s="88"/>
       <c r="AG327" s="88"/>
     </row>
-    <row r="328" spans="1:33" ht="11.45" customHeight="1">
+    <row r="328" spans="1:33" ht="11.5" customHeight="1">
       <c r="A328" s="209">
         <v>46079</v>
       </c>
@@ -30715,7 +30715,7 @@
       <c r="AF328" s="102"/>
       <c r="AG328" s="102"/>
     </row>
-    <row r="329" spans="1:33" ht="11.45" customHeight="1">
+    <row r="329" spans="1:33" ht="11.5" customHeight="1">
       <c r="A329" s="204">
         <v>46079</v>
       </c>
@@ -30794,7 +30794,7 @@
       <c r="AF329" s="88"/>
       <c r="AG329" s="88"/>
     </row>
-    <row r="330" spans="1:33" ht="11.45" customHeight="1">
+    <row r="330" spans="1:33" ht="11.5" customHeight="1">
       <c r="A330" s="209">
         <v>46079</v>
       </c>
@@ -30871,7 +30871,7 @@
       <c r="AF330" s="102"/>
       <c r="AG330" s="102"/>
     </row>
-    <row r="331" spans="1:33" ht="11.45" customHeight="1">
+    <row r="331" spans="1:33" ht="11.5" customHeight="1">
       <c r="A331" s="207">
         <v>46079</v>
       </c>
@@ -30952,7 +30952,7 @@
       <c r="AF331" s="106"/>
       <c r="AG331" s="106"/>
     </row>
-    <row r="332" spans="1:33" ht="11.45" customHeight="1">
+    <row r="332" spans="1:33" ht="11.5" customHeight="1">
       <c r="A332" s="204" t="s">
         <v>1965</v>
       </c>
@@ -31027,7 +31027,7 @@
       <c r="AF332" s="88"/>
       <c r="AG332" s="88"/>
     </row>
-    <row r="333" spans="1:33" ht="11.45" customHeight="1">
+    <row r="333" spans="1:33" ht="11.5" customHeight="1">
       <c r="A333" s="205">
         <v>46079</v>
       </c>
@@ -31100,7 +31100,7 @@
       <c r="AF333" s="104"/>
       <c r="AG333" s="104"/>
     </row>
-    <row r="334" spans="1:33" ht="11.45" customHeight="1">
+    <row r="334" spans="1:33" ht="11.5" customHeight="1">
       <c r="A334" s="207">
         <v>46079</v>
       </c>
@@ -31177,7 +31177,7 @@
       <c r="AF334" s="106"/>
       <c r="AG334" s="106"/>
     </row>
-    <row r="335" spans="1:33" ht="11.45" customHeight="1">
+    <row r="335" spans="1:33" ht="11.5" customHeight="1">
       <c r="A335" s="203">
         <v>46079</v>
       </c>
@@ -31254,7 +31254,7 @@
       <c r="AF335" s="56"/>
       <c r="AG335" s="56"/>
     </row>
-    <row r="336" spans="1:33" ht="11.45" customHeight="1">
+    <row r="336" spans="1:33" ht="11.5" customHeight="1">
       <c r="A336" s="214">
         <v>46079</v>
       </c>
@@ -31335,7 +31335,7 @@
       <c r="AF336" s="81"/>
       <c r="AG336" s="81"/>
     </row>
-    <row r="337" spans="1:33" ht="11.45" customHeight="1">
+    <row r="337" spans="1:33" ht="11.5" customHeight="1">
       <c r="A337" s="214">
         <v>46079</v>
       </c>
@@ -31392,7 +31392,7 @@
       <c r="AF337" s="56"/>
       <c r="AG337" s="56"/>
     </row>
-    <row r="338" spans="1:33" ht="11.45" customHeight="1">
+    <row r="338" spans="1:33" ht="11.5" customHeight="1">
       <c r="A338" s="204">
         <v>46079</v>
       </c>
@@ -31471,7 +31471,7 @@
       <c r="AF338" s="88"/>
       <c r="AG338" s="88"/>
     </row>
-    <row r="339" spans="1:33" ht="11.45" customHeight="1">
+    <row r="339" spans="1:33" ht="11.5" customHeight="1">
       <c r="A339" s="214">
         <v>46079</v>
       </c>
@@ -31546,7 +31546,7 @@
       <c r="AF339" s="81"/>
       <c r="AG339" s="81"/>
     </row>
-    <row r="340" spans="1:33" ht="11.45" customHeight="1">
+    <row r="340" spans="1:33" ht="11.5" customHeight="1">
       <c r="A340" s="209">
         <v>46079</v>
       </c>
@@ -31623,7 +31623,7 @@
       <c r="AF340" s="102"/>
       <c r="AG340" s="102"/>
     </row>
-    <row r="341" spans="1:33" ht="11.45" customHeight="1">
+    <row r="341" spans="1:33" ht="11.5" customHeight="1">
       <c r="A341" s="205" t="s">
         <v>1965</v>
       </c>
@@ -31700,7 +31700,7 @@
       <c r="AF341" s="104"/>
       <c r="AG341" s="104"/>
     </row>
-    <row r="342" spans="1:33" ht="11.45" customHeight="1">
+    <row r="342" spans="1:33" ht="11.5" customHeight="1">
       <c r="A342" s="204" t="s">
         <v>1965</v>
       </c>
@@ -31781,7 +31781,7 @@
       <c r="AF342" s="88"/>
       <c r="AG342" s="88"/>
     </row>
-    <row r="343" spans="1:33" ht="11.45" customHeight="1">
+    <row r="343" spans="1:33" ht="11.5" customHeight="1">
       <c r="A343" s="214" t="s">
         <v>1965</v>
       </c>
@@ -31858,7 +31858,7 @@
       <c r="AF343" s="81"/>
       <c r="AG343" s="81"/>
     </row>
-    <row r="344" spans="1:33" ht="11.45" customHeight="1">
+    <row r="344" spans="1:33" ht="11.5" customHeight="1">
       <c r="A344" s="411" t="s">
         <v>1965</v>
       </c>
@@ -31920,7 +31920,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="345" spans="1:33" s="122" customFormat="1" ht="12.6" customHeight="1">
+    <row r="345" spans="1:33" s="122" customFormat="1" ht="12.65" customHeight="1">
       <c r="A345" s="122" t="s">
         <v>1965</v>
       </c>
@@ -31988,7 +31988,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="346" spans="1:33" ht="11.45" customHeight="1">
+    <row r="346" spans="1:33" ht="11.5" customHeight="1">
       <c r="A346" s="205" t="s">
         <v>1965</v>
       </c>
@@ -32067,7 +32067,7 @@
       <c r="AF346" s="104"/>
       <c r="AG346" s="104"/>
     </row>
-    <row r="347" spans="1:33" ht="11.45" customHeight="1">
+    <row r="347" spans="1:33" ht="11.5" customHeight="1">
       <c r="A347" s="207" t="s">
         <v>1965</v>
       </c>
@@ -32146,7 +32146,7 @@
       <c r="AF347" s="106"/>
       <c r="AG347" s="106"/>
     </row>
-    <row r="348" spans="1:33" ht="11.45" customHeight="1">
+    <row r="348" spans="1:33" ht="11.5" customHeight="1">
       <c r="A348" s="204" t="s">
         <v>1965</v>
       </c>
@@ -32217,7 +32217,7 @@
       <c r="AF348" s="88"/>
       <c r="AG348" s="88"/>
     </row>
-    <row r="349" spans="1:33" ht="11.45" customHeight="1">
+    <row r="349" spans="1:33" ht="11.5" customHeight="1">
       <c r="A349" s="209" t="s">
         <v>1965</v>
       </c>
@@ -32292,7 +32292,7 @@
       <c r="AF349" s="102"/>
       <c r="AG349" s="102"/>
     </row>
-    <row r="350" spans="1:33" ht="11.45" customHeight="1">
+    <row r="350" spans="1:33" ht="11.5" customHeight="1">
       <c r="A350" s="206" t="s">
         <v>1965</v>
       </c>
@@ -32367,7 +32367,7 @@
       <c r="AF350" s="78"/>
       <c r="AG350" s="78"/>
     </row>
-    <row r="351" spans="1:33" ht="11.45" customHeight="1">
+    <row r="351" spans="1:33" ht="11.5" customHeight="1">
       <c r="A351" s="204" t="s">
         <v>1965</v>
       </c>
@@ -32444,7 +32444,7 @@
       <c r="AF351" s="88"/>
       <c r="AG351" s="88"/>
     </row>
-    <row r="352" spans="1:33" s="421" customFormat="1" ht="11.45" customHeight="1">
+    <row r="352" spans="1:33" s="421" customFormat="1" ht="11.5" customHeight="1">
       <c r="A352" s="417">
         <v>46084</v>
       </c>
@@ -32519,7 +32519,7 @@
       <c r="AF352" s="420"/>
       <c r="AG352" s="420"/>
     </row>
-    <row r="353" spans="1:33" ht="11.45" customHeight="1">
+    <row r="353" spans="1:33" ht="11.5" customHeight="1">
       <c r="A353" s="205">
         <v>46084.458333333343</v>
       </c>
@@ -32594,7 +32594,7 @@
       <c r="AF353" s="104"/>
       <c r="AG353" s="104"/>
     </row>
-    <row r="354" spans="1:33" ht="11.45" customHeight="1">
+    <row r="354" spans="1:33" ht="11.5" customHeight="1">
       <c r="A354" s="204">
         <v>46084</v>
       </c>
@@ -32667,7 +32667,7 @@
       <c r="AF354" s="88"/>
       <c r="AG354" s="88"/>
     </row>
-    <row r="355" spans="1:33" ht="11.45" customHeight="1">
+    <row r="355" spans="1:33" ht="11.5" customHeight="1">
       <c r="A355" s="205"/>
       <c r="B355" s="205"/>
       <c r="C355" s="366"/>
@@ -32724,7 +32724,7 @@
       <c r="AF355" s="104"/>
       <c r="AG355" s="104"/>
     </row>
-    <row r="356" spans="1:33" ht="11.45" customHeight="1">
+    <row r="356" spans="1:33" ht="11.5" customHeight="1">
       <c r="A356" s="209"/>
       <c r="B356" s="209"/>
       <c r="C356" s="365"/>
@@ -32779,7 +32779,7 @@
       <c r="AF356" s="102"/>
       <c r="AG356" s="102"/>
     </row>
-    <row r="357" spans="1:33" ht="11.45" customHeight="1">
+    <row r="357" spans="1:33" ht="11.5" customHeight="1">
       <c r="A357" s="206"/>
       <c r="B357" s="206"/>
       <c r="C357" s="382"/>
@@ -32834,7 +32834,7 @@
       <c r="AF357" s="78"/>
       <c r="AG357" s="78"/>
     </row>
-    <row r="358" spans="1:33" ht="11.45" customHeight="1">
+    <row r="358" spans="1:33" ht="11.5" customHeight="1">
       <c r="A358" s="204"/>
       <c r="B358" s="204"/>
       <c r="C358" s="380"/>
@@ -32889,7 +32889,7 @@
       <c r="AF358" s="88"/>
       <c r="AG358" s="88"/>
     </row>
-    <row r="359" spans="1:33" ht="11.45" customHeight="1">
+    <row r="359" spans="1:33" ht="11.5" customHeight="1">
       <c r="A359" s="203"/>
       <c r="B359" s="203"/>
       <c r="C359" s="377"/>
@@ -32922,7 +32922,7 @@
       <c r="AF359" s="56"/>
       <c r="AG359" s="56"/>
     </row>
-    <row r="360" spans="1:33" ht="11.45" customHeight="1">
+    <row r="360" spans="1:33" ht="11.5" customHeight="1">
       <c r="A360" s="214"/>
       <c r="B360" s="214"/>
       <c r="C360" s="378"/>
@@ -32955,7 +32955,7 @@
       <c r="AF360" s="81"/>
       <c r="AG360" s="81"/>
     </row>
-    <row r="361" spans="1:33" ht="11.45" customHeight="1">
+    <row r="361" spans="1:33" ht="11.5" customHeight="1">
       <c r="A361" s="209"/>
       <c r="B361" s="209"/>
       <c r="C361" s="365"/>
@@ -32988,7 +32988,7 @@
       <c r="AF361" s="102"/>
       <c r="AG361" s="102"/>
     </row>
-    <row r="362" spans="1:33" ht="11.45" customHeight="1">
+    <row r="362" spans="1:33" ht="11.5" customHeight="1">
       <c r="A362" s="205"/>
       <c r="B362" s="205"/>
       <c r="C362" s="366"/>
@@ -33021,7 +33021,7 @@
       <c r="AF362" s="104"/>
       <c r="AG362" s="104"/>
     </row>
-    <row r="363" spans="1:33" ht="11.45" customHeight="1">
+    <row r="363" spans="1:33" ht="11.5" customHeight="1">
       <c r="A363" s="207"/>
       <c r="B363" s="207"/>
       <c r="C363" s="367"/>
@@ -33054,7 +33054,7 @@
       <c r="AF363" s="106"/>
       <c r="AG363" s="106"/>
     </row>
-    <row r="364" spans="1:33" ht="11.45" customHeight="1">
+    <row r="364" spans="1:33" ht="11.5" customHeight="1">
       <c r="A364" s="206"/>
       <c r="B364" s="206"/>
       <c r="C364" s="382"/>
@@ -33087,7 +33087,7 @@
       <c r="AF364" s="78"/>
       <c r="AG364" s="78"/>
     </row>
-    <row r="365" spans="1:33" ht="11.45" customHeight="1">
+    <row r="365" spans="1:33" ht="11.5" customHeight="1">
       <c r="A365" s="204"/>
       <c r="B365" s="204"/>
       <c r="C365" s="380"/>
@@ -33120,7 +33120,7 @@
       <c r="AF365" s="88"/>
       <c r="AG365" s="88"/>
     </row>
-    <row r="366" spans="1:33" ht="11.45" customHeight="1">
+    <row r="366" spans="1:33" ht="11.5" customHeight="1">
       <c r="A366" s="203"/>
       <c r="B366" s="203"/>
       <c r="C366" s="377"/>
@@ -33153,7 +33153,7 @@
       <c r="AF366" s="56"/>
       <c r="AG366" s="56"/>
     </row>
-    <row r="367" spans="1:33" ht="11.45" customHeight="1">
+    <row r="367" spans="1:33" ht="11.5" customHeight="1">
       <c r="A367" s="214"/>
       <c r="B367" s="214"/>
       <c r="C367" s="378"/>
@@ -33186,7 +33186,7 @@
       <c r="AF367" s="81"/>
       <c r="AG367" s="81"/>
     </row>
-    <row r="368" spans="1:33" ht="11.45" customHeight="1">
+    <row r="368" spans="1:33" ht="11.5" customHeight="1">
       <c r="A368" s="209"/>
       <c r="B368" s="209"/>
       <c r="C368" s="365"/>
@@ -33219,7 +33219,7 @@
       <c r="AF368" s="102"/>
       <c r="AG368" s="102"/>
     </row>
-    <row r="369" spans="1:33" ht="11.45" customHeight="1">
+    <row r="369" spans="1:33" ht="11.5" customHeight="1">
       <c r="A369" s="205"/>
       <c r="B369" s="205"/>
       <c r="C369" s="366"/>
@@ -33252,7 +33252,7 @@
       <c r="AF369" s="104"/>
       <c r="AG369" s="104"/>
     </row>
-    <row r="370" spans="1:33" ht="11.45" customHeight="1">
+    <row r="370" spans="1:33" ht="11.5" customHeight="1">
       <c r="A370" s="207"/>
       <c r="B370" s="207"/>
       <c r="C370" s="367"/>
@@ -33285,7 +33285,7 @@
       <c r="AF370" s="106"/>
       <c r="AG370" s="106"/>
     </row>
-    <row r="371" spans="1:33" ht="11.45" customHeight="1">
+    <row r="371" spans="1:33" ht="11.5" customHeight="1">
       <c r="A371" s="206"/>
       <c r="B371" s="206"/>
       <c r="C371" s="382"/>
@@ -33318,7 +33318,7 @@
       <c r="AF371" s="78"/>
       <c r="AG371" s="78"/>
     </row>
-    <row r="372" spans="1:33" ht="11.45" customHeight="1">
+    <row r="372" spans="1:33" ht="11.5" customHeight="1">
       <c r="A372" s="204"/>
       <c r="B372" s="204"/>
       <c r="C372" s="380"/>
@@ -33351,7 +33351,7 @@
       <c r="AF372" s="88"/>
       <c r="AG372" s="88"/>
     </row>
-    <row r="373" spans="1:33" ht="11.45" customHeight="1">
+    <row r="373" spans="1:33" ht="11.5" customHeight="1">
       <c r="A373" s="203"/>
       <c r="B373" s="203"/>
       <c r="C373" s="377"/>
@@ -33384,7 +33384,7 @@
       <c r="AF373" s="56"/>
       <c r="AG373" s="56"/>
     </row>
-    <row r="374" spans="1:33" ht="11.45" customHeight="1">
+    <row r="374" spans="1:33" ht="11.5" customHeight="1">
       <c r="A374" s="214"/>
       <c r="B374" s="214"/>
       <c r="C374" s="378"/>
@@ -33417,7 +33417,7 @@
       <c r="AF374" s="81"/>
       <c r="AG374" s="81"/>
     </row>
-    <row r="375" spans="1:33" ht="11.45" customHeight="1">
+    <row r="375" spans="1:33" ht="11.5" customHeight="1">
       <c r="A375" s="209"/>
       <c r="B375" s="209"/>
       <c r="C375" s="365"/>
@@ -33450,7 +33450,7 @@
       <c r="AF375" s="102"/>
       <c r="AG375" s="102"/>
     </row>
-    <row r="376" spans="1:33" ht="11.45" customHeight="1">
+    <row r="376" spans="1:33" ht="11.5" customHeight="1">
       <c r="A376" s="205"/>
       <c r="B376" s="205"/>
       <c r="C376" s="366"/>
@@ -33483,7 +33483,7 @@
       <c r="AF376" s="104"/>
       <c r="AG376" s="104"/>
     </row>
-    <row r="377" spans="1:33" ht="11.45" customHeight="1">
+    <row r="377" spans="1:33" ht="11.5" customHeight="1">
       <c r="A377" s="207"/>
       <c r="B377" s="207"/>
       <c r="C377" s="367"/>
@@ -33516,7 +33516,7 @@
       <c r="AF377" s="106"/>
       <c r="AG377" s="106"/>
     </row>
-    <row r="378" spans="1:33" ht="11.45" customHeight="1">
+    <row r="378" spans="1:33" ht="11.5" customHeight="1">
       <c r="A378" s="206"/>
       <c r="B378" s="206"/>
       <c r="C378" s="382"/>
@@ -33549,7 +33549,7 @@
       <c r="AF378" s="78"/>
       <c r="AG378" s="78"/>
     </row>
-    <row r="379" spans="1:33" ht="11.45" customHeight="1">
+    <row r="379" spans="1:33" ht="11.5" customHeight="1">
       <c r="A379" s="204"/>
       <c r="B379" s="204"/>
       <c r="C379" s="380"/>
@@ -33582,7 +33582,7 @@
       <c r="AF379" s="88"/>
       <c r="AG379" s="88"/>
     </row>
-    <row r="380" spans="1:33" ht="11.45" customHeight="1">
+    <row r="380" spans="1:33" ht="11.5" customHeight="1">
       <c r="A380" s="203"/>
       <c r="B380" s="203"/>
       <c r="C380" s="377"/>
@@ -33615,7 +33615,7 @@
       <c r="AF380" s="56"/>
       <c r="AG380" s="56"/>
     </row>
-    <row r="381" spans="1:33" ht="11.45" customHeight="1">
+    <row r="381" spans="1:33" ht="11.5" customHeight="1">
       <c r="A381" s="214"/>
       <c r="B381" s="214"/>
       <c r="C381" s="378"/>
@@ -33648,7 +33648,7 @@
       <c r="AF381" s="81"/>
       <c r="AG381" s="81"/>
     </row>
-    <row r="382" spans="1:33" ht="11.45" customHeight="1">
+    <row r="382" spans="1:33" ht="11.5" customHeight="1">
       <c r="A382" s="209"/>
       <c r="B382" s="209"/>
       <c r="C382" s="365"/>
@@ -33681,7 +33681,7 @@
       <c r="AF382" s="102"/>
       <c r="AG382" s="102"/>
     </row>
-    <row r="383" spans="1:33" ht="11.45" customHeight="1">
+    <row r="383" spans="1:33" ht="11.5" customHeight="1">
       <c r="A383" s="205"/>
       <c r="B383" s="205"/>
       <c r="C383" s="366"/>
@@ -33714,7 +33714,7 @@
       <c r="AF383" s="104"/>
       <c r="AG383" s="104"/>
     </row>
-    <row r="384" spans="1:33" ht="11.45" customHeight="1">
+    <row r="384" spans="1:33" ht="11.5" customHeight="1">
       <c r="A384" s="207"/>
       <c r="B384" s="207"/>
       <c r="C384" s="367"/>
@@ -33747,7 +33747,7 @@
       <c r="AF384" s="106"/>
       <c r="AG384" s="106"/>
     </row>
-    <row r="385" spans="1:33" ht="11.45" customHeight="1">
+    <row r="385" spans="1:33" ht="11.5" customHeight="1">
       <c r="A385" s="206"/>
       <c r="B385" s="206"/>
       <c r="C385" s="382"/>
@@ -33780,7 +33780,7 @@
       <c r="AF385" s="78"/>
       <c r="AG385" s="78"/>
     </row>
-    <row r="386" spans="1:33" ht="11.45" customHeight="1">
+    <row r="386" spans="1:33" ht="11.5" customHeight="1">
       <c r="A386" s="204"/>
       <c r="B386" s="204"/>
       <c r="C386" s="380"/>
@@ -33813,7 +33813,7 @@
       <c r="AF386" s="88"/>
       <c r="AG386" s="88"/>
     </row>
-    <row r="387" spans="1:33" ht="11.45" customHeight="1">
+    <row r="387" spans="1:33" ht="11.5" customHeight="1">
       <c r="A387" s="203"/>
       <c r="B387" s="203"/>
       <c r="C387" s="377"/>
@@ -33846,7 +33846,7 @@
       <c r="AF387" s="56"/>
       <c r="AG387" s="56"/>
     </row>
-    <row r="388" spans="1:33" ht="11.45" customHeight="1">
+    <row r="388" spans="1:33" ht="11.5" customHeight="1">
       <c r="A388" s="214"/>
       <c r="B388" s="214"/>
       <c r="C388" s="378"/>
@@ -33879,7 +33879,7 @@
       <c r="AF388" s="81"/>
       <c r="AG388" s="81"/>
     </row>
-    <row r="389" spans="1:33" ht="11.45" customHeight="1">
+    <row r="389" spans="1:33" ht="11.5" customHeight="1">
       <c r="A389" s="209"/>
       <c r="B389" s="209"/>
       <c r="C389" s="365"/>
@@ -33912,7 +33912,7 @@
       <c r="AF389" s="102"/>
       <c r="AG389" s="102"/>
     </row>
-    <row r="390" spans="1:33" ht="11.45" customHeight="1">
+    <row r="390" spans="1:33" ht="11.5" customHeight="1">
       <c r="A390" s="205"/>
       <c r="B390" s="205"/>
       <c r="C390" s="366"/>
@@ -33945,7 +33945,7 @@
       <c r="AF390" s="104"/>
       <c r="AG390" s="104"/>
     </row>
-    <row r="391" spans="1:33" ht="11.45" customHeight="1">
+    <row r="391" spans="1:33" ht="11.5" customHeight="1">
       <c r="A391" s="207"/>
       <c r="B391" s="207"/>
       <c r="C391" s="367"/>
@@ -33978,7 +33978,7 @@
       <c r="AF391" s="106"/>
       <c r="AG391" s="106"/>
     </row>
-    <row r="392" spans="1:33" ht="11.45" customHeight="1">
+    <row r="392" spans="1:33" ht="11.5" customHeight="1">
       <c r="A392" s="206"/>
       <c r="B392" s="206"/>
       <c r="C392" s="382"/>
@@ -34011,7 +34011,7 @@
       <c r="AF392" s="78"/>
       <c r="AG392" s="78"/>
     </row>
-    <row r="393" spans="1:33" ht="11.45" customHeight="1">
+    <row r="393" spans="1:33" ht="11.5" customHeight="1">
       <c r="A393" s="204"/>
       <c r="B393" s="204"/>
       <c r="C393" s="380"/>
@@ -34044,7 +34044,7 @@
       <c r="AF393" s="88"/>
       <c r="AG393" s="88"/>
     </row>
-    <row r="394" spans="1:33" ht="11.45" customHeight="1">
+    <row r="394" spans="1:33" ht="11.5" customHeight="1">
       <c r="A394" s="203"/>
       <c r="B394" s="203"/>
       <c r="C394" s="377"/>
@@ -34077,7 +34077,7 @@
       <c r="AF394" s="56"/>
       <c r="AG394" s="56"/>
     </row>
-    <row r="395" spans="1:33" ht="11.45" customHeight="1">
+    <row r="395" spans="1:33" ht="11.5" customHeight="1">
       <c r="A395" s="214"/>
       <c r="B395" s="214"/>
       <c r="C395" s="378"/>
@@ -34110,7 +34110,7 @@
       <c r="AF395" s="81"/>
       <c r="AG395" s="81"/>
     </row>
-    <row r="396" spans="1:33" ht="11.45" customHeight="1">
+    <row r="396" spans="1:33" ht="11.5" customHeight="1">
       <c r="A396" s="209"/>
       <c r="B396" s="209"/>
       <c r="C396" s="365"/>
@@ -34143,7 +34143,7 @@
       <c r="AF396" s="102"/>
       <c r="AG396" s="102"/>
     </row>
-    <row r="397" spans="1:33" ht="11.45" customHeight="1">
+    <row r="397" spans="1:33" ht="11.5" customHeight="1">
       <c r="A397" s="205"/>
       <c r="B397" s="205"/>
       <c r="C397" s="366"/>
@@ -34176,7 +34176,7 @@
       <c r="AF397" s="104"/>
       <c r="AG397" s="104"/>
     </row>
-    <row r="398" spans="1:33" ht="11.45" customHeight="1">
+    <row r="398" spans="1:33" ht="11.5" customHeight="1">
       <c r="A398" s="207"/>
       <c r="B398" s="207"/>
       <c r="C398" s="367"/>
@@ -34209,7 +34209,7 @@
       <c r="AF398" s="106"/>
       <c r="AG398" s="106"/>
     </row>
-    <row r="399" spans="1:33" ht="11.45" customHeight="1">
+    <row r="399" spans="1:33" ht="11.5" customHeight="1">
       <c r="A399" s="206"/>
       <c r="B399" s="206"/>
       <c r="C399" s="382"/>
@@ -34242,7 +34242,7 @@
       <c r="AF399" s="78"/>
       <c r="AG399" s="78"/>
     </row>
-    <row r="400" spans="1:33" ht="11.45" customHeight="1">
+    <row r="400" spans="1:33" ht="11.5" customHeight="1">
       <c r="A400" s="204"/>
       <c r="B400" s="204"/>
       <c r="C400" s="380"/>
@@ -34275,7 +34275,7 @@
       <c r="AF400" s="88"/>
       <c r="AG400" s="88"/>
     </row>
-    <row r="401" spans="1:33" ht="11.45" customHeight="1">
+    <row r="401" spans="1:33" ht="11.5" customHeight="1">
       <c r="A401" s="203"/>
       <c r="B401" s="203"/>
       <c r="C401" s="377"/>
@@ -34308,7 +34308,7 @@
       <c r="AF401" s="56"/>
       <c r="AG401" s="56"/>
     </row>
-    <row r="402" spans="1:33" ht="11.45" customHeight="1">
+    <row r="402" spans="1:33" ht="11.5" customHeight="1">
       <c r="A402" s="214"/>
       <c r="B402" s="214"/>
       <c r="C402" s="378"/>
@@ -34341,7 +34341,7 @@
       <c r="AF402" s="81"/>
       <c r="AG402" s="81"/>
     </row>
-    <row r="403" spans="1:33" ht="11.45" customHeight="1">
+    <row r="403" spans="1:33" ht="11.5" customHeight="1">
       <c r="A403" s="209"/>
       <c r="B403" s="209"/>
       <c r="C403" s="365"/>
@@ -34374,7 +34374,7 @@
       <c r="AF403" s="102"/>
       <c r="AG403" s="102"/>
     </row>
-    <row r="404" spans="1:33" ht="11.45" customHeight="1">
+    <row r="404" spans="1:33" ht="11.5" customHeight="1">
       <c r="A404" s="205"/>
       <c r="B404" s="205"/>
       <c r="C404" s="366"/>
@@ -34407,7 +34407,7 @@
       <c r="AF404" s="104"/>
       <c r="AG404" s="104"/>
     </row>
-    <row r="405" spans="1:33" ht="11.45" customHeight="1">
+    <row r="405" spans="1:33" ht="11.5" customHeight="1">
       <c r="A405" s="207"/>
       <c r="B405" s="207"/>
       <c r="C405" s="367"/>
@@ -34440,7 +34440,7 @@
       <c r="AF405" s="106"/>
       <c r="AG405" s="106"/>
     </row>
-    <row r="406" spans="1:33" ht="11.45" customHeight="1">
+    <row r="406" spans="1:33" ht="11.5" customHeight="1">
       <c r="A406" s="206"/>
       <c r="B406" s="206"/>
       <c r="C406" s="382"/>
@@ -34473,7 +34473,7 @@
       <c r="AF406" s="78"/>
       <c r="AG406" s="78"/>
     </row>
-    <row r="407" spans="1:33" ht="11.45" customHeight="1">
+    <row r="407" spans="1:33" ht="11.5" customHeight="1">
       <c r="A407" s="204"/>
       <c r="B407" s="204"/>
       <c r="C407" s="380"/>
@@ -34506,7 +34506,7 @@
       <c r="AF407" s="88"/>
       <c r="AG407" s="88"/>
     </row>
-    <row r="408" spans="1:33" ht="11.45" customHeight="1">
+    <row r="408" spans="1:33" ht="11.5" customHeight="1">
       <c r="A408" s="203"/>
       <c r="B408" s="203"/>
       <c r="C408" s="377"/>
@@ -34539,7 +34539,7 @@
       <c r="AF408" s="56"/>
       <c r="AG408" s="56"/>
     </row>
-    <row r="409" spans="1:33" ht="11.45" customHeight="1">
+    <row r="409" spans="1:33" ht="11.5" customHeight="1">
       <c r="A409" s="214"/>
       <c r="B409" s="214"/>
       <c r="C409" s="378"/>
@@ -34572,7 +34572,7 @@
       <c r="AF409" s="81"/>
       <c r="AG409" s="81"/>
     </row>
-    <row r="410" spans="1:33" ht="11.45" customHeight="1">
+    <row r="410" spans="1:33" ht="11.5" customHeight="1">
       <c r="A410" s="209"/>
       <c r="B410" s="209"/>
       <c r="C410" s="365"/>
@@ -34605,7 +34605,7 @@
       <c r="AF410" s="102"/>
       <c r="AG410" s="102"/>
     </row>
-    <row r="411" spans="1:33" ht="11.45" customHeight="1">
+    <row r="411" spans="1:33" ht="11.5" customHeight="1">
       <c r="A411" s="205"/>
       <c r="B411" s="205"/>
       <c r="C411" s="366"/>
@@ -34638,7 +34638,7 @@
       <c r="AF411" s="104"/>
       <c r="AG411" s="104"/>
     </row>
-    <row r="412" spans="1:33" ht="11.45" customHeight="1">
+    <row r="412" spans="1:33" ht="11.5" customHeight="1">
       <c r="A412" s="207"/>
       <c r="B412" s="207"/>
       <c r="C412" s="367"/>
@@ -34671,7 +34671,7 @@
       <c r="AF412" s="106"/>
       <c r="AG412" s="106"/>
     </row>
-    <row r="413" spans="1:33" ht="11.45" customHeight="1">
+    <row r="413" spans="1:33" ht="11.5" customHeight="1">
       <c r="A413" s="206"/>
       <c r="B413" s="206"/>
       <c r="C413" s="382"/>
@@ -34704,7 +34704,7 @@
       <c r="AF413" s="78"/>
       <c r="AG413" s="78"/>
     </row>
-    <row r="414" spans="1:33" ht="11.45" customHeight="1">
+    <row r="414" spans="1:33" ht="11.5" customHeight="1">
       <c r="A414" s="204"/>
       <c r="B414" s="204"/>
       <c r="C414" s="380"/>
@@ -34737,7 +34737,7 @@
       <c r="AF414" s="88"/>
       <c r="AG414" s="88"/>
     </row>
-    <row r="415" spans="1:33" ht="11.45" customHeight="1">
+    <row r="415" spans="1:33" ht="11.5" customHeight="1">
       <c r="A415" s="203"/>
       <c r="B415" s="203"/>
       <c r="C415" s="377"/>
@@ -34770,7 +34770,7 @@
       <c r="AF415" s="56"/>
       <c r="AG415" s="56"/>
     </row>
-    <row r="416" spans="1:33" ht="11.45" customHeight="1">
+    <row r="416" spans="1:33" ht="11.5" customHeight="1">
       <c r="A416" s="214"/>
       <c r="B416" s="214"/>
       <c r="C416" s="378"/>
@@ -34803,7 +34803,7 @@
       <c r="AF416" s="81"/>
       <c r="AG416" s="81"/>
     </row>
-    <row r="417" spans="1:33" ht="11.45" customHeight="1">
+    <row r="417" spans="1:33" ht="11.5" customHeight="1">
       <c r="A417" s="209"/>
       <c r="B417" s="209"/>
       <c r="C417" s="365"/>
@@ -34836,7 +34836,7 @@
       <c r="AF417" s="102"/>
       <c r="AG417" s="102"/>
     </row>
-    <row r="418" spans="1:33" ht="11.45" customHeight="1">
+    <row r="418" spans="1:33" ht="11.5" customHeight="1">
       <c r="A418" s="205"/>
       <c r="B418" s="205"/>
       <c r="C418" s="366"/>
@@ -34869,7 +34869,7 @@
       <c r="AF418" s="104"/>
       <c r="AG418" s="104"/>
     </row>
-    <row r="419" spans="1:33" ht="11.45" customHeight="1">
+    <row r="419" spans="1:33" ht="11.5" customHeight="1">
       <c r="A419" s="207"/>
       <c r="B419" s="207"/>
       <c r="C419" s="367"/>
@@ -34902,7 +34902,7 @@
       <c r="AF419" s="106"/>
       <c r="AG419" s="106"/>
     </row>
-    <row r="420" spans="1:33" ht="11.45" customHeight="1">
+    <row r="420" spans="1:33" ht="11.5" customHeight="1">
       <c r="A420" s="206"/>
       <c r="B420" s="206"/>
       <c r="C420" s="382"/>
@@ -34935,7 +34935,7 @@
       <c r="AF420" s="78"/>
       <c r="AG420" s="78"/>
     </row>
-    <row r="421" spans="1:33" ht="11.45" customHeight="1">
+    <row r="421" spans="1:33" ht="11.5" customHeight="1">
       <c r="A421" s="204"/>
       <c r="B421" s="204"/>
       <c r="C421" s="380"/>
@@ -34968,7 +34968,7 @@
       <c r="AF421" s="88"/>
       <c r="AG421" s="88"/>
     </row>
-    <row r="422" spans="1:33" ht="11.45" customHeight="1">
+    <row r="422" spans="1:33" ht="11.5" customHeight="1">
       <c r="A422" s="203"/>
       <c r="B422" s="203"/>
       <c r="C422" s="377"/>
@@ -35001,7 +35001,7 @@
       <c r="AF422" s="56"/>
       <c r="AG422" s="56"/>
     </row>
-    <row r="423" spans="1:33" ht="11.45" customHeight="1">
+    <row r="423" spans="1:33" ht="11.5" customHeight="1">
       <c r="A423" s="214"/>
       <c r="B423" s="214"/>
       <c r="C423" s="378"/>
@@ -35034,7 +35034,7 @@
       <c r="AF423" s="81"/>
       <c r="AG423" s="81"/>
     </row>
-    <row r="424" spans="1:33" ht="11.45" customHeight="1">
+    <row r="424" spans="1:33" ht="11.5" customHeight="1">
       <c r="A424" s="209"/>
       <c r="B424" s="209"/>
       <c r="C424" s="365"/>
@@ -35067,7 +35067,7 @@
       <c r="AF424" s="102"/>
       <c r="AG424" s="102"/>
     </row>
-    <row r="425" spans="1:33" ht="11.45" customHeight="1">
+    <row r="425" spans="1:33" ht="11.5" customHeight="1">
       <c r="A425" s="205"/>
       <c r="B425" s="205"/>
       <c r="C425" s="366"/>
@@ -35100,7 +35100,7 @@
       <c r="AF425" s="104"/>
       <c r="AG425" s="104"/>
     </row>
-    <row r="426" spans="1:33" ht="11.45" customHeight="1">
+    <row r="426" spans="1:33" ht="11.5" customHeight="1">
       <c r="A426" s="207"/>
       <c r="B426" s="207"/>
       <c r="C426" s="367"/>
@@ -35133,7 +35133,7 @@
       <c r="AF426" s="106"/>
       <c r="AG426" s="106"/>
     </row>
-    <row r="427" spans="1:33" ht="11.45" customHeight="1">
+    <row r="427" spans="1:33" ht="11.5" customHeight="1">
       <c r="A427" s="206"/>
       <c r="B427" s="206"/>
       <c r="C427" s="382"/>
@@ -35166,7 +35166,7 @@
       <c r="AF427" s="78"/>
       <c r="AG427" s="78"/>
     </row>
-    <row r="428" spans="1:33" ht="11.45" customHeight="1">
+    <row r="428" spans="1:33" ht="11.5" customHeight="1">
       <c r="A428" s="204"/>
       <c r="B428" s="204"/>
       <c r="C428" s="380"/>
@@ -35199,7 +35199,7 @@
       <c r="AF428" s="88"/>
       <c r="AG428" s="88"/>
     </row>
-    <row r="429" spans="1:33" ht="11.45" customHeight="1">
+    <row r="429" spans="1:33" ht="11.5" customHeight="1">
       <c r="A429" s="203"/>
       <c r="B429" s="203"/>
       <c r="C429" s="377"/>
@@ -35232,7 +35232,7 @@
       <c r="AF429" s="56"/>
       <c r="AG429" s="56"/>
     </row>
-    <row r="430" spans="1:33" ht="11.45" customHeight="1">
+    <row r="430" spans="1:33" ht="11.5" customHeight="1">
       <c r="A430" s="214"/>
       <c r="B430" s="214"/>
       <c r="C430" s="378"/>
@@ -35265,7 +35265,7 @@
       <c r="AF430" s="81"/>
       <c r="AG430" s="81"/>
     </row>
-    <row r="431" spans="1:33" ht="11.45" customHeight="1">
+    <row r="431" spans="1:33" ht="11.5" customHeight="1">
       <c r="A431" s="209"/>
       <c r="B431" s="209"/>
       <c r="C431" s="365"/>
@@ -35298,7 +35298,7 @@
       <c r="AF431" s="102"/>
       <c r="AG431" s="102"/>
     </row>
-    <row r="432" spans="1:33" ht="11.45" customHeight="1">
+    <row r="432" spans="1:33" ht="11.5" customHeight="1">
       <c r="A432" s="205"/>
       <c r="B432" s="205"/>
       <c r="C432" s="366"/>
@@ -35331,7 +35331,7 @@
       <c r="AF432" s="104"/>
       <c r="AG432" s="104"/>
     </row>
-    <row r="433" spans="1:33" ht="11.45" customHeight="1">
+    <row r="433" spans="1:33" ht="11.5" customHeight="1">
       <c r="A433" s="207"/>
       <c r="B433" s="207"/>
       <c r="C433" s="367"/>
@@ -35364,7 +35364,7 @@
       <c r="AF433" s="106"/>
       <c r="AG433" s="106"/>
     </row>
-    <row r="434" spans="1:33" ht="11.45" customHeight="1">
+    <row r="434" spans="1:33" ht="11.5" customHeight="1">
       <c r="A434" s="206"/>
       <c r="B434" s="206"/>
       <c r="C434" s="382"/>
@@ -35397,7 +35397,7 @@
       <c r="AF434" s="78"/>
       <c r="AG434" s="78"/>
     </row>
-    <row r="435" spans="1:33" ht="11.45" customHeight="1">
+    <row r="435" spans="1:33" ht="11.5" customHeight="1">
       <c r="A435" s="204"/>
       <c r="B435" s="204"/>
       <c r="C435" s="380"/>
@@ -35430,7 +35430,7 @@
       <c r="AF435" s="88"/>
       <c r="AG435" s="88"/>
     </row>
-    <row r="436" spans="1:33" ht="11.45" customHeight="1">
+    <row r="436" spans="1:33" ht="11.5" customHeight="1">
       <c r="A436" s="203"/>
       <c r="B436" s="203"/>
       <c r="C436" s="377"/>
@@ -35463,7 +35463,7 @@
       <c r="AF436" s="56"/>
       <c r="AG436" s="56"/>
     </row>
-    <row r="437" spans="1:33" ht="11.45" customHeight="1">
+    <row r="437" spans="1:33" ht="11.5" customHeight="1">
       <c r="A437" s="214"/>
       <c r="B437" s="214"/>
       <c r="C437" s="378"/>
@@ -35496,7 +35496,7 @@
       <c r="AF437" s="81"/>
       <c r="AG437" s="81"/>
     </row>
-    <row r="438" spans="1:33" ht="11.45" customHeight="1">
+    <row r="438" spans="1:33" ht="11.5" customHeight="1">
       <c r="A438" s="209"/>
       <c r="B438" s="209"/>
       <c r="C438" s="365"/>
@@ -35529,7 +35529,7 @@
       <c r="AF438" s="102"/>
       <c r="AG438" s="102"/>
     </row>
-    <row r="439" spans="1:33" ht="11.45" customHeight="1">
+    <row r="439" spans="1:33" ht="11.5" customHeight="1">
       <c r="A439" s="205"/>
       <c r="B439" s="205"/>
       <c r="C439" s="366"/>
@@ -35562,7 +35562,7 @@
       <c r="AF439" s="104"/>
       <c r="AG439" s="104"/>
     </row>
-    <row r="440" spans="1:33" ht="11.45" customHeight="1">
+    <row r="440" spans="1:33" ht="11.5" customHeight="1">
       <c r="A440" s="207"/>
       <c r="B440" s="207"/>
       <c r="C440" s="367"/>
@@ -35595,7 +35595,7 @@
       <c r="AF440" s="106"/>
       <c r="AG440" s="106"/>
     </row>
-    <row r="441" spans="1:33" ht="11.45" customHeight="1">
+    <row r="441" spans="1:33" ht="11.5" customHeight="1">
       <c r="A441" s="206"/>
       <c r="B441" s="206"/>
       <c r="C441" s="382"/>
@@ -35628,7 +35628,7 @@
       <c r="AF441" s="78"/>
       <c r="AG441" s="78"/>
     </row>
-    <row r="442" spans="1:33" ht="11.45" customHeight="1">
+    <row r="442" spans="1:33" ht="11.5" customHeight="1">
       <c r="A442" s="204"/>
       <c r="B442" s="204"/>
       <c r="C442" s="380"/>
@@ -35661,7 +35661,7 @@
       <c r="AF442" s="88"/>
       <c r="AG442" s="88"/>
     </row>
-    <row r="443" spans="1:33" ht="11.45" customHeight="1">
+    <row r="443" spans="1:33" ht="11.5" customHeight="1">
       <c r="A443" s="203"/>
       <c r="B443" s="203"/>
       <c r="C443" s="377"/>
@@ -35694,7 +35694,7 @@
       <c r="AF443" s="56"/>
       <c r="AG443" s="56"/>
     </row>
-    <row r="444" spans="1:33" ht="11.45" customHeight="1">
+    <row r="444" spans="1:33" ht="11.5" customHeight="1">
       <c r="A444" s="214"/>
       <c r="B444" s="214"/>
       <c r="C444" s="378"/>
@@ -35727,7 +35727,7 @@
       <c r="AF444" s="81"/>
       <c r="AG444" s="81"/>
     </row>
-    <row r="445" spans="1:33" ht="11.45" customHeight="1">
+    <row r="445" spans="1:33" ht="11.5" customHeight="1">
       <c r="A445" s="209"/>
       <c r="B445" s="209"/>
       <c r="C445" s="365"/>
@@ -35760,7 +35760,7 @@
       <c r="AF445" s="102"/>
       <c r="AG445" s="102"/>
     </row>
-    <row r="446" spans="1:33" ht="11.45" customHeight="1">
+    <row r="446" spans="1:33" ht="11.5" customHeight="1">
       <c r="A446" s="205"/>
       <c r="B446" s="205"/>
       <c r="C446" s="366"/>
@@ -35793,7 +35793,7 @@
       <c r="AF446" s="104"/>
       <c r="AG446" s="104"/>
     </row>
-    <row r="447" spans="1:33" ht="11.45" customHeight="1">
+    <row r="447" spans="1:33" ht="11.5" customHeight="1">
       <c r="A447" s="207"/>
       <c r="B447" s="207"/>
       <c r="C447" s="367"/>
@@ -35826,7 +35826,7 @@
       <c r="AF447" s="106"/>
       <c r="AG447" s="106"/>
     </row>
-    <row r="448" spans="1:33" ht="11.45" customHeight="1">
+    <row r="448" spans="1:33" ht="11.5" customHeight="1">
       <c r="A448" s="206"/>
       <c r="B448" s="206"/>
       <c r="C448" s="382"/>
@@ -35859,7 +35859,7 @@
       <c r="AF448" s="78"/>
       <c r="AG448" s="78"/>
     </row>
-    <row r="449" spans="1:33" ht="11.45" customHeight="1">
+    <row r="449" spans="1:33" ht="11.5" customHeight="1">
       <c r="A449" s="204"/>
       <c r="B449" s="204"/>
       <c r="C449" s="380"/>
@@ -35892,7 +35892,7 @@
       <c r="AF449" s="88"/>
       <c r="AG449" s="88"/>
     </row>
-    <row r="450" spans="1:33" ht="11.45" customHeight="1">
+    <row r="450" spans="1:33" ht="11.5" customHeight="1">
       <c r="A450" s="203"/>
       <c r="B450" s="203"/>
       <c r="C450" s="377"/>
@@ -35925,7 +35925,7 @@
       <c r="AF450" s="56"/>
       <c r="AG450" s="56"/>
     </row>
-    <row r="451" spans="1:33" ht="11.45" customHeight="1">
+    <row r="451" spans="1:33" ht="11.5" customHeight="1">
       <c r="A451" s="214"/>
       <c r="B451" s="214"/>
       <c r="C451" s="378"/>
@@ -35958,7 +35958,7 @@
       <c r="AF451" s="81"/>
       <c r="AG451" s="81"/>
     </row>
-    <row r="452" spans="1:33" ht="11.45" customHeight="1">
+    <row r="452" spans="1:33" ht="11.5" customHeight="1">
       <c r="A452" s="209"/>
       <c r="B452" s="209"/>
       <c r="C452" s="365"/>
@@ -35991,7 +35991,7 @@
       <c r="AF452" s="102"/>
       <c r="AG452" s="102"/>
     </row>
-    <row r="453" spans="1:33" ht="11.45" customHeight="1">
+    <row r="453" spans="1:33" ht="11.5" customHeight="1">
       <c r="A453" s="205"/>
       <c r="B453" s="205"/>
       <c r="C453" s="366"/>
@@ -36024,7 +36024,7 @@
       <c r="AF453" s="104"/>
       <c r="AG453" s="104"/>
     </row>
-    <row r="454" spans="1:33" ht="11.45" customHeight="1">
+    <row r="454" spans="1:33" ht="11.5" customHeight="1">
       <c r="A454" s="207"/>
       <c r="B454" s="207"/>
       <c r="C454" s="367"/>
@@ -36057,7 +36057,7 @@
       <c r="AF454" s="106"/>
       <c r="AG454" s="106"/>
     </row>
-    <row r="455" spans="1:33" ht="11.45" customHeight="1">
+    <row r="455" spans="1:33" ht="11.5" customHeight="1">
       <c r="A455" s="206"/>
       <c r="B455" s="206"/>
       <c r="C455" s="382"/>
@@ -36090,7 +36090,7 @@
       <c r="AF455" s="78"/>
       <c r="AG455" s="78"/>
     </row>
-    <row r="456" spans="1:33" ht="11.45" customHeight="1">
+    <row r="456" spans="1:33" ht="11.5" customHeight="1">
       <c r="A456" s="204"/>
       <c r="B456" s="204"/>
       <c r="C456" s="380"/>
@@ -36123,7 +36123,7 @@
       <c r="AF456" s="88"/>
       <c r="AG456" s="88"/>
     </row>
-    <row r="457" spans="1:33" ht="11.45" customHeight="1">
+    <row r="457" spans="1:33" ht="11.5" customHeight="1">
       <c r="A457" s="203"/>
       <c r="B457" s="203"/>
       <c r="C457" s="377"/>
@@ -36156,7 +36156,7 @@
       <c r="AF457" s="56"/>
       <c r="AG457" s="56"/>
     </row>
-    <row r="458" spans="1:33" ht="11.45" customHeight="1">
+    <row r="458" spans="1:33" ht="11.5" customHeight="1">
       <c r="A458" s="214"/>
       <c r="B458" s="214"/>
       <c r="C458" s="378"/>
@@ -36189,7 +36189,7 @@
       <c r="AF458" s="81"/>
       <c r="AG458" s="81"/>
     </row>
-    <row r="459" spans="1:33" ht="11.45" customHeight="1">
+    <row r="459" spans="1:33" ht="11.5" customHeight="1">
       <c r="A459" s="209"/>
       <c r="B459" s="209"/>
       <c r="C459" s="365"/>
@@ -36222,7 +36222,7 @@
       <c r="AF459" s="102"/>
       <c r="AG459" s="102"/>
     </row>
-    <row r="460" spans="1:33" ht="11.45" customHeight="1">
+    <row r="460" spans="1:33" ht="11.5" customHeight="1">
       <c r="A460" s="205"/>
       <c r="B460" s="205"/>
       <c r="C460" s="366"/>
@@ -36255,7 +36255,7 @@
       <c r="AF460" s="104"/>
       <c r="AG460" s="104"/>
     </row>
-    <row r="461" spans="1:33" ht="11.45" customHeight="1">
+    <row r="461" spans="1:33" ht="11.5" customHeight="1">
       <c r="A461" s="207"/>
       <c r="B461" s="207"/>
       <c r="C461" s="367"/>
@@ -36288,7 +36288,7 @@
       <c r="AF461" s="106"/>
       <c r="AG461" s="106"/>
     </row>
-    <row r="462" spans="1:33" ht="11.45" customHeight="1">
+    <row r="462" spans="1:33" ht="11.5" customHeight="1">
       <c r="A462" s="206"/>
       <c r="B462" s="206"/>
       <c r="C462" s="382"/>
@@ -36321,7 +36321,7 @@
       <c r="AF462" s="78"/>
       <c r="AG462" s="78"/>
     </row>
-    <row r="463" spans="1:33" ht="11.45" customHeight="1">
+    <row r="463" spans="1:33" ht="11.5" customHeight="1">
       <c r="A463" s="204"/>
       <c r="B463" s="204"/>
       <c r="C463" s="380"/>
@@ -36354,7 +36354,7 @@
       <c r="AF463" s="88"/>
       <c r="AG463" s="88"/>
     </row>
-    <row r="464" spans="1:33" ht="11.45" customHeight="1">
+    <row r="464" spans="1:33" ht="11.5" customHeight="1">
       <c r="A464" s="203"/>
       <c r="B464" s="203"/>
       <c r="C464" s="377"/>
@@ -36387,7 +36387,7 @@
       <c r="AF464" s="56"/>
       <c r="AG464" s="56"/>
     </row>
-    <row r="465" spans="1:33" ht="11.45" customHeight="1">
+    <row r="465" spans="1:33" ht="11.5" customHeight="1">
       <c r="A465" s="214"/>
       <c r="B465" s="214"/>
       <c r="C465" s="378"/>
@@ -36420,7 +36420,7 @@
       <c r="AF465" s="81"/>
       <c r="AG465" s="81"/>
     </row>
-    <row r="466" spans="1:33" ht="11.45" customHeight="1">
+    <row r="466" spans="1:33" ht="11.5" customHeight="1">
       <c r="A466" s="209"/>
       <c r="B466" s="209"/>
       <c r="C466" s="365"/>
@@ -36453,7 +36453,7 @@
       <c r="AF466" s="102"/>
       <c r="AG466" s="102"/>
     </row>
-    <row r="467" spans="1:33" ht="11.45" customHeight="1">
+    <row r="467" spans="1:33" ht="11.5" customHeight="1">
       <c r="A467" s="205"/>
       <c r="B467" s="205"/>
       <c r="C467" s="366"/>
@@ -36486,7 +36486,7 @@
       <c r="AF467" s="104"/>
       <c r="AG467" s="104"/>
     </row>
-    <row r="468" spans="1:33" ht="11.45" customHeight="1">
+    <row r="468" spans="1:33" ht="11.5" customHeight="1">
       <c r="A468" s="207"/>
       <c r="B468" s="207"/>
       <c r="C468" s="367"/>
@@ -36519,7 +36519,7 @@
       <c r="AF468" s="106"/>
       <c r="AG468" s="106"/>
     </row>
-    <row r="469" spans="1:33" ht="11.45" customHeight="1">
+    <row r="469" spans="1:33" ht="11.5" customHeight="1">
       <c r="A469" s="206"/>
       <c r="B469" s="206"/>
       <c r="C469" s="382"/>
@@ -36552,7 +36552,7 @@
       <c r="AF469" s="78"/>
       <c r="AG469" s="78"/>
     </row>
-    <row r="470" spans="1:33" ht="11.45" customHeight="1">
+    <row r="470" spans="1:33" ht="11.5" customHeight="1">
       <c r="A470" s="204"/>
       <c r="B470" s="204"/>
       <c r="C470" s="380"/>
@@ -36585,7 +36585,7 @@
       <c r="AF470" s="88"/>
       <c r="AG470" s="88"/>
     </row>
-    <row r="471" spans="1:33" ht="11.45" customHeight="1">
+    <row r="471" spans="1:33" ht="11.5" customHeight="1">
       <c r="A471" s="203"/>
       <c r="B471" s="203"/>
       <c r="C471" s="377"/>
@@ -36618,7 +36618,7 @@
       <c r="AF471" s="56"/>
       <c r="AG471" s="56"/>
     </row>
-    <row r="472" spans="1:33" ht="11.45" customHeight="1">
+    <row r="472" spans="1:33" ht="11.5" customHeight="1">
       <c r="A472" s="214"/>
       <c r="B472" s="214"/>
       <c r="C472" s="378"/>
@@ -36651,7 +36651,7 @@
       <c r="AF472" s="81"/>
       <c r="AG472" s="81"/>
     </row>
-    <row r="473" spans="1:33" ht="11.45" customHeight="1">
+    <row r="473" spans="1:33" ht="11.5" customHeight="1">
       <c r="A473" s="209"/>
       <c r="B473" s="209"/>
       <c r="C473" s="365"/>
@@ -36684,7 +36684,7 @@
       <c r="AF473" s="102"/>
       <c r="AG473" s="102"/>
     </row>
-    <row r="474" spans="1:33" ht="11.45" customHeight="1">
+    <row r="474" spans="1:33" ht="11.5" customHeight="1">
       <c r="A474" s="205"/>
       <c r="B474" s="205"/>
       <c r="C474" s="366"/>
@@ -36717,7 +36717,7 @@
       <c r="AF474" s="104"/>
       <c r="AG474" s="104"/>
     </row>
-    <row r="475" spans="1:33" ht="11.45" customHeight="1">
+    <row r="475" spans="1:33" ht="11.5" customHeight="1">
       <c r="A475" s="207"/>
       <c r="B475" s="207"/>
       <c r="C475" s="367"/>
@@ -36750,7 +36750,7 @@
       <c r="AF475" s="106"/>
       <c r="AG475" s="106"/>
     </row>
-    <row r="476" spans="1:33" ht="11.45" customHeight="1">
+    <row r="476" spans="1:33" ht="11.5" customHeight="1">
       <c r="A476" s="206"/>
       <c r="B476" s="206"/>
       <c r="C476" s="382"/>
@@ -36783,7 +36783,7 @@
       <c r="AF476" s="78"/>
       <c r="AG476" s="78"/>
     </row>
-    <row r="477" spans="1:33" ht="11.45" customHeight="1">
+    <row r="477" spans="1:33" ht="11.5" customHeight="1">
       <c r="A477" s="204"/>
       <c r="B477" s="204"/>
       <c r="C477" s="380"/>
@@ -36816,7 +36816,7 @@
       <c r="AF477" s="88"/>
       <c r="AG477" s="88"/>
     </row>
-    <row r="478" spans="1:33" ht="11.45" customHeight="1">
+    <row r="478" spans="1:33" ht="11.5" customHeight="1">
       <c r="A478" s="203"/>
       <c r="B478" s="203"/>
       <c r="C478" s="377"/>
@@ -36849,7 +36849,7 @@
       <c r="AF478" s="56"/>
       <c r="AG478" s="56"/>
     </row>
-    <row r="479" spans="1:33" ht="11.45" customHeight="1">
+    <row r="479" spans="1:33" ht="11.5" customHeight="1">
       <c r="A479" s="214"/>
       <c r="B479" s="214"/>
       <c r="C479" s="378"/>
@@ -36882,7 +36882,7 @@
       <c r="AF479" s="81"/>
       <c r="AG479" s="81"/>
     </row>
-    <row r="480" spans="1:33" ht="11.45" customHeight="1">
+    <row r="480" spans="1:33" ht="11.5" customHeight="1">
       <c r="A480" s="209"/>
       <c r="B480" s="209"/>
       <c r="C480" s="365"/>
@@ -36915,7 +36915,7 @@
       <c r="AF480" s="102"/>
       <c r="AG480" s="102"/>
     </row>
-    <row r="481" spans="1:33" ht="11.45" customHeight="1">
+    <row r="481" spans="1:33" ht="11.5" customHeight="1">
       <c r="A481" s="205"/>
       <c r="B481" s="205"/>
       <c r="C481" s="366"/>
@@ -36948,7 +36948,7 @@
       <c r="AF481" s="104"/>
       <c r="AG481" s="104"/>
     </row>
-    <row r="482" spans="1:33" ht="11.45" customHeight="1">
+    <row r="482" spans="1:33" ht="11.5" customHeight="1">
       <c r="A482" s="207"/>
       <c r="B482" s="207"/>
       <c r="C482" s="367"/>
@@ -36981,7 +36981,7 @@
       <c r="AF482" s="106"/>
       <c r="AG482" s="106"/>
     </row>
-    <row r="483" spans="1:33" ht="11.45" customHeight="1">
+    <row r="483" spans="1:33" ht="11.5" customHeight="1">
       <c r="A483" s="206"/>
       <c r="B483" s="206"/>
       <c r="C483" s="382"/>
@@ -37014,7 +37014,7 @@
       <c r="AF483" s="78"/>
       <c r="AG483" s="78"/>
     </row>
-    <row r="484" spans="1:33" ht="11.45" customHeight="1">
+    <row r="484" spans="1:33" ht="11.5" customHeight="1">
       <c r="A484" s="204"/>
       <c r="B484" s="204"/>
       <c r="C484" s="380"/>
@@ -37047,7 +37047,7 @@
       <c r="AF484" s="88"/>
       <c r="AG484" s="88"/>
     </row>
-    <row r="485" spans="1:33" ht="11.45" customHeight="1">
+    <row r="485" spans="1:33" ht="11.5" customHeight="1">
       <c r="A485" s="203"/>
       <c r="B485" s="203"/>
       <c r="C485" s="377"/>
@@ -37080,7 +37080,7 @@
       <c r="AF485" s="56"/>
       <c r="AG485" s="56"/>
     </row>
-    <row r="486" spans="1:33" ht="11.45" customHeight="1">
+    <row r="486" spans="1:33" ht="11.5" customHeight="1">
       <c r="A486" s="214"/>
       <c r="B486" s="214"/>
       <c r="C486" s="378"/>
@@ -37113,7 +37113,7 @@
       <c r="AF486" s="81"/>
       <c r="AG486" s="81"/>
     </row>
-    <row r="487" spans="1:33" ht="11.45" customHeight="1">
+    <row r="487" spans="1:33" ht="11.5" customHeight="1">
       <c r="A487" s="209"/>
       <c r="B487" s="209"/>
       <c r="C487" s="365"/>
@@ -37146,7 +37146,7 @@
       <c r="AF487" s="102"/>
       <c r="AG487" s="102"/>
     </row>
-    <row r="488" spans="1:33" ht="11.45" customHeight="1">
+    <row r="488" spans="1:33" ht="11.5" customHeight="1">
       <c r="A488" s="205"/>
       <c r="B488" s="205"/>
       <c r="C488" s="366"/>
@@ -37179,7 +37179,7 @@
       <c r="AF488" s="104"/>
       <c r="AG488" s="104"/>
     </row>
-    <row r="489" spans="1:33" ht="11.45" customHeight="1">
+    <row r="489" spans="1:33" ht="11.5" customHeight="1">
       <c r="A489" s="207"/>
       <c r="B489" s="207"/>
       <c r="C489" s="367"/>
@@ -37212,7 +37212,7 @@
       <c r="AF489" s="106"/>
       <c r="AG489" s="106"/>
     </row>
-    <row r="490" spans="1:33" ht="11.45" customHeight="1">
+    <row r="490" spans="1:33" ht="11.5" customHeight="1">
       <c r="A490" s="206"/>
       <c r="B490" s="206"/>
       <c r="C490" s="382"/>
@@ -37245,7 +37245,7 @@
       <c r="AF490" s="78"/>
       <c r="AG490" s="78"/>
     </row>
-    <row r="491" spans="1:33" ht="11.45" customHeight="1">
+    <row r="491" spans="1:33" ht="11.5" customHeight="1">
       <c r="A491" s="204"/>
       <c r="B491" s="204"/>
       <c r="C491" s="380"/>
@@ -37278,7 +37278,7 @@
       <c r="AF491" s="88"/>
       <c r="AG491" s="88"/>
     </row>
-    <row r="492" spans="1:33" ht="11.45" customHeight="1">
+    <row r="492" spans="1:33" ht="11.5" customHeight="1">
       <c r="A492" s="203"/>
       <c r="B492" s="203"/>
       <c r="C492" s="377"/>
@@ -37311,7 +37311,7 @@
       <c r="AF492" s="56"/>
       <c r="AG492" s="56"/>
     </row>
-    <row r="493" spans="1:33" ht="11.45" customHeight="1">
+    <row r="493" spans="1:33" ht="11.5" customHeight="1">
       <c r="A493" s="214"/>
       <c r="B493" s="214"/>
       <c r="C493" s="378"/>
@@ -37344,7 +37344,7 @@
       <c r="AF493" s="81"/>
       <c r="AG493" s="81"/>
     </row>
-    <row r="494" spans="1:33" ht="11.45" customHeight="1">
+    <row r="494" spans="1:33" ht="11.5" customHeight="1">
       <c r="A494" s="209"/>
       <c r="B494" s="209"/>
       <c r="C494" s="365"/>
@@ -37377,7 +37377,7 @@
       <c r="AF494" s="102"/>
       <c r="AG494" s="102"/>
     </row>
-    <row r="495" spans="1:33" ht="11.45" customHeight="1">
+    <row r="495" spans="1:33" ht="11.5" customHeight="1">
       <c r="A495" s="205"/>
       <c r="B495" s="205"/>
       <c r="C495" s="366"/>
@@ -37410,7 +37410,7 @@
       <c r="AF495" s="104"/>
       <c r="AG495" s="104"/>
     </row>
-    <row r="496" spans="1:33" ht="11.45" customHeight="1">
+    <row r="496" spans="1:33" ht="11.5" customHeight="1">
       <c r="A496" s="207"/>
       <c r="B496" s="207"/>
       <c r="C496" s="367"/>
@@ -37443,7 +37443,7 @@
       <c r="AF496" s="106"/>
       <c r="AG496" s="106"/>
     </row>
-    <row r="497" spans="1:33" ht="11.45" customHeight="1">
+    <row r="497" spans="1:33" ht="11.5" customHeight="1">
       <c r="A497" s="206"/>
       <c r="B497" s="206"/>
       <c r="C497" s="382"/>
@@ -37476,7 +37476,7 @@
       <c r="AF497" s="78"/>
       <c r="AG497" s="78"/>
     </row>
-    <row r="498" spans="1:33" ht="11.45" customHeight="1">
+    <row r="498" spans="1:33" ht="11.5" customHeight="1">
       <c r="A498" s="204"/>
       <c r="B498" s="204"/>
       <c r="C498" s="380"/>
@@ -37509,7 +37509,7 @@
       <c r="AF498" s="88"/>
       <c r="AG498" s="88"/>
     </row>
-    <row r="499" spans="1:33" ht="11.45" customHeight="1">
+    <row r="499" spans="1:33" ht="11.5" customHeight="1">
       <c r="A499" s="203"/>
       <c r="B499" s="203"/>
       <c r="C499" s="377"/>
@@ -37542,7 +37542,7 @@
       <c r="AF499" s="56"/>
       <c r="AG499" s="56"/>
     </row>
-    <row r="500" spans="1:33" ht="11.45" customHeight="1">
+    <row r="500" spans="1:33" ht="11.5" customHeight="1">
       <c r="A500" s="214"/>
       <c r="B500" s="214"/>
       <c r="C500" s="378"/>
@@ -37575,7 +37575,7 @@
       <c r="AF500" s="81"/>
       <c r="AG500" s="81"/>
     </row>
-    <row r="501" spans="1:33" ht="11.45" customHeight="1">
+    <row r="501" spans="1:33" ht="11.5" customHeight="1">
       <c r="A501" s="209"/>
       <c r="B501" s="209"/>
       <c r="C501" s="365"/>
@@ -37608,7 +37608,7 @@
       <c r="AF501" s="102"/>
       <c r="AG501" s="102"/>
     </row>
-    <row r="502" spans="1:33" ht="11.45" customHeight="1">
+    <row r="502" spans="1:33" ht="11.5" customHeight="1">
       <c r="A502" s="205"/>
       <c r="B502" s="205"/>
       <c r="C502" s="366"/>
@@ -37641,7 +37641,7 @@
       <c r="AF502" s="104"/>
       <c r="AG502" s="104"/>
     </row>
-    <row r="503" spans="1:33" ht="11.45" customHeight="1">
+    <row r="503" spans="1:33" ht="11.5" customHeight="1">
       <c r="A503" s="207"/>
       <c r="B503" s="207"/>
       <c r="C503" s="367"/>
@@ -37674,7 +37674,7 @@
       <c r="AF503" s="106"/>
       <c r="AG503" s="106"/>
     </row>
-    <row r="504" spans="1:33" ht="11.45" customHeight="1">
+    <row r="504" spans="1:33" ht="11.5" customHeight="1">
       <c r="A504" s="206"/>
       <c r="B504" s="206"/>
       <c r="C504" s="382"/>
@@ -37707,7 +37707,7 @@
       <c r="AF504" s="78"/>
       <c r="AG504" s="78"/>
     </row>
-    <row r="505" spans="1:33" ht="11.45" customHeight="1">
+    <row r="505" spans="1:33" ht="11.5" customHeight="1">
       <c r="A505" s="204"/>
       <c r="B505" s="204"/>
       <c r="C505" s="380"/>
@@ -37740,7 +37740,7 @@
       <c r="AF505" s="88"/>
       <c r="AG505" s="88"/>
     </row>
-    <row r="506" spans="1:33" ht="11.45" customHeight="1">
+    <row r="506" spans="1:33" ht="11.5" customHeight="1">
       <c r="A506" s="203"/>
       <c r="B506" s="203"/>
       <c r="C506" s="377"/>
@@ -37773,7 +37773,7 @@
       <c r="AF506" s="56"/>
       <c r="AG506" s="56"/>
     </row>
-    <row r="507" spans="1:33" ht="11.45" customHeight="1">
+    <row r="507" spans="1:33" ht="11.5" customHeight="1">
       <c r="A507" s="214"/>
       <c r="B507" s="214"/>
       <c r="C507" s="378"/>
@@ -37806,7 +37806,7 @@
       <c r="AF507" s="81"/>
       <c r="AG507" s="81"/>
     </row>
-    <row r="508" spans="1:33" ht="11.45" customHeight="1">
+    <row r="508" spans="1:33" ht="11.5" customHeight="1">
       <c r="A508" s="209"/>
       <c r="B508" s="209"/>
       <c r="C508" s="365"/>
@@ -37839,7 +37839,7 @@
       <c r="AF508" s="102"/>
       <c r="AG508" s="102"/>
     </row>
-    <row r="509" spans="1:33" ht="11.45" customHeight="1">
+    <row r="509" spans="1:33" ht="11.5" customHeight="1">
       <c r="A509" s="205"/>
       <c r="B509" s="205"/>
       <c r="C509" s="366"/>
@@ -37872,7 +37872,7 @@
       <c r="AF509" s="104"/>
       <c r="AG509" s="104"/>
     </row>
-    <row r="510" spans="1:33" ht="11.45" customHeight="1">
+    <row r="510" spans="1:33" ht="11.5" customHeight="1">
       <c r="A510" s="207"/>
       <c r="B510" s="207"/>
       <c r="C510" s="367"/>
@@ -37905,7 +37905,7 @@
       <c r="AF510" s="106"/>
       <c r="AG510" s="106"/>
     </row>
-    <row r="511" spans="1:33" ht="11.45" customHeight="1">
+    <row r="511" spans="1:33" ht="11.5" customHeight="1">
       <c r="A511" s="206"/>
       <c r="B511" s="206"/>
       <c r="C511" s="382"/>
@@ -37938,7 +37938,7 @@
       <c r="AF511" s="78"/>
       <c r="AG511" s="78"/>
     </row>
-    <row r="512" spans="1:33" ht="11.45" customHeight="1">
+    <row r="512" spans="1:33" ht="11.5" customHeight="1">
       <c r="A512" s="204"/>
       <c r="B512" s="204"/>
       <c r="C512" s="380"/>
@@ -37971,7 +37971,7 @@
       <c r="AF512" s="88"/>
       <c r="AG512" s="88"/>
     </row>
-    <row r="513" spans="1:33" ht="11.45" customHeight="1">
+    <row r="513" spans="1:33" ht="11.5" customHeight="1">
       <c r="A513" s="203"/>
       <c r="B513" s="203"/>
       <c r="C513" s="377"/>
@@ -38004,7 +38004,7 @@
       <c r="AF513" s="56"/>
       <c r="AG513" s="56"/>
     </row>
-    <row r="514" spans="1:33" ht="11.45" customHeight="1">
+    <row r="514" spans="1:33" ht="11.5" customHeight="1">
       <c r="A514" s="214"/>
       <c r="B514" s="214"/>
       <c r="C514" s="378"/>
@@ -38037,7 +38037,7 @@
       <c r="AF514" s="81"/>
       <c r="AG514" s="81"/>
     </row>
-    <row r="515" spans="1:33" ht="11.45" customHeight="1">
+    <row r="515" spans="1:33" ht="11.5" customHeight="1">
       <c r="A515" s="209"/>
       <c r="B515" s="209"/>
       <c r="C515" s="365"/>
@@ -38070,7 +38070,7 @@
       <c r="AF515" s="102"/>
       <c r="AG515" s="102"/>
     </row>
-    <row r="516" spans="1:33" ht="11.45" customHeight="1">
+    <row r="516" spans="1:33" ht="11.5" customHeight="1">
       <c r="A516" s="205"/>
       <c r="B516" s="205"/>
       <c r="C516" s="366"/>
@@ -38103,7 +38103,7 @@
       <c r="AF516" s="104"/>
       <c r="AG516" s="104"/>
     </row>
-    <row r="517" spans="1:33" ht="11.45" customHeight="1">
+    <row r="517" spans="1:33" ht="11.5" customHeight="1">
       <c r="A517" s="207"/>
       <c r="B517" s="207"/>
       <c r="C517" s="367"/>
@@ -38136,7 +38136,7 @@
       <c r="AF517" s="106"/>
       <c r="AG517" s="106"/>
     </row>
-    <row r="518" spans="1:33" ht="11.45" customHeight="1">
+    <row r="518" spans="1:33" ht="11.5" customHeight="1">
       <c r="A518" s="206"/>
       <c r="B518" s="206"/>
       <c r="C518" s="382"/>
@@ -38169,7 +38169,7 @@
       <c r="AF518" s="78"/>
       <c r="AG518" s="78"/>
     </row>
-    <row r="519" spans="1:33" ht="11.45" customHeight="1">
+    <row r="519" spans="1:33" ht="11.5" customHeight="1">
       <c r="A519" s="204"/>
       <c r="B519" s="204"/>
       <c r="C519" s="380"/>
@@ -38202,7 +38202,7 @@
       <c r="AF519" s="88"/>
       <c r="AG519" s="88"/>
     </row>
-    <row r="520" spans="1:33" ht="11.45" customHeight="1">
+    <row r="520" spans="1:33" ht="11.5" customHeight="1">
       <c r="A520" s="203"/>
       <c r="B520" s="203"/>
       <c r="C520" s="377"/>
@@ -38235,7 +38235,7 @@
       <c r="AF520" s="56"/>
       <c r="AG520" s="56"/>
     </row>
-    <row r="521" spans="1:33" ht="11.45" customHeight="1">
+    <row r="521" spans="1:33" ht="11.5" customHeight="1">
       <c r="A521" s="214"/>
       <c r="B521" s="214"/>
       <c r="C521" s="378"/>
@@ -38268,7 +38268,7 @@
       <c r="AF521" s="81"/>
       <c r="AG521" s="81"/>
     </row>
-    <row r="522" spans="1:33" ht="11.45" customHeight="1">
+    <row r="522" spans="1:33" ht="11.5" customHeight="1">
       <c r="A522" s="209"/>
       <c r="B522" s="209"/>
       <c r="C522" s="365"/>
@@ -38301,7 +38301,7 @@
       <c r="AF522" s="102"/>
       <c r="AG522" s="102"/>
     </row>
-    <row r="523" spans="1:33" ht="11.45" customHeight="1">
+    <row r="523" spans="1:33" ht="11.5" customHeight="1">
       <c r="A523" s="205"/>
       <c r="B523" s="205"/>
       <c r="C523" s="366"/>
@@ -38334,7 +38334,7 @@
       <c r="AF523" s="104"/>
       <c r="AG523" s="104"/>
     </row>
-    <row r="524" spans="1:33" ht="11.45" customHeight="1">
+    <row r="524" spans="1:33" ht="11.5" customHeight="1">
       <c r="A524" s="207"/>
       <c r="B524" s="207"/>
       <c r="C524" s="367"/>
@@ -38367,7 +38367,7 @@
       <c r="AF524" s="106"/>
       <c r="AG524" s="106"/>
     </row>
-    <row r="525" spans="1:33" ht="11.45" customHeight="1">
+    <row r="525" spans="1:33" ht="11.5" customHeight="1">
       <c r="A525" s="206"/>
       <c r="B525" s="206"/>
       <c r="C525" s="382"/>
@@ -38400,7 +38400,7 @@
       <c r="AF525" s="78"/>
       <c r="AG525" s="78"/>
     </row>
-    <row r="526" spans="1:33" ht="11.45" customHeight="1">
+    <row r="526" spans="1:33" ht="11.5" customHeight="1">
       <c r="A526" s="204"/>
       <c r="B526" s="204"/>
       <c r="C526" s="380"/>
@@ -38433,7 +38433,7 @@
       <c r="AF526" s="88"/>
       <c r="AG526" s="88"/>
     </row>
-    <row r="527" spans="1:33" ht="11.45" customHeight="1">
+    <row r="527" spans="1:33" ht="11.5" customHeight="1">
       <c r="A527" s="203"/>
       <c r="B527" s="203"/>
       <c r="C527" s="377"/>
@@ -38466,7 +38466,7 @@
       <c r="AF527" s="56"/>
       <c r="AG527" s="56"/>
     </row>
-    <row r="528" spans="1:33" ht="11.45" customHeight="1">
+    <row r="528" spans="1:33" ht="11.5" customHeight="1">
       <c r="A528" s="214"/>
       <c r="B528" s="214"/>
       <c r="C528" s="378"/>
@@ -38499,7 +38499,7 @@
       <c r="AF528" s="81"/>
       <c r="AG528" s="81"/>
     </row>
-    <row r="529" spans="1:33" ht="11.45" customHeight="1">
+    <row r="529" spans="1:33" ht="11.5" customHeight="1">
       <c r="A529" s="209"/>
       <c r="B529" s="209"/>
       <c r="C529" s="365"/>
@@ -38532,7 +38532,7 @@
       <c r="AF529" s="102"/>
       <c r="AG529" s="102"/>
     </row>
-    <row r="530" spans="1:33" ht="11.45" customHeight="1">
+    <row r="530" spans="1:33" ht="11.5" customHeight="1">
       <c r="A530" s="205"/>
       <c r="B530" s="205"/>
       <c r="C530" s="366"/>
@@ -38565,7 +38565,7 @@
       <c r="AF530" s="104"/>
       <c r="AG530" s="104"/>
     </row>
-    <row r="531" spans="1:33" ht="11.45" customHeight="1">
+    <row r="531" spans="1:33" ht="11.5" customHeight="1">
       <c r="A531" s="207"/>
       <c r="B531" s="207"/>
       <c r="C531" s="367"/>
@@ -38598,7 +38598,7 @@
       <c r="AF531" s="106"/>
       <c r="AG531" s="106"/>
     </row>
-    <row r="532" spans="1:33" ht="11.45" customHeight="1">
+    <row r="532" spans="1:33" ht="11.5" customHeight="1">
       <c r="A532" s="206"/>
       <c r="B532" s="206"/>
       <c r="C532" s="382"/>
@@ -38631,7 +38631,7 @@
       <c r="AF532" s="78"/>
       <c r="AG532" s="78"/>
     </row>
-    <row r="533" spans="1:33" ht="11.45" customHeight="1">
+    <row r="533" spans="1:33" ht="11.5" customHeight="1">
       <c r="A533" s="204"/>
       <c r="B533" s="204"/>
       <c r="C533" s="380"/>
@@ -38664,7 +38664,7 @@
       <c r="AF533" s="88"/>
       <c r="AG533" s="88"/>
     </row>
-    <row r="534" spans="1:33" ht="11.45" customHeight="1">
+    <row r="534" spans="1:33" ht="11.5" customHeight="1">
       <c r="H534" s="125" t="s">
         <v>2324</v>
       </c>
@@ -38721,37 +38721,37 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AU142"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="5.140625" customWidth="1"/>
-    <col min="3" max="4" width="4.5703125" customWidth="1"/>
-    <col min="5" max="5" width="4.140625" customWidth="1"/>
-    <col min="6" max="6" width="2.42578125" customWidth="1"/>
-    <col min="7" max="7" width="4.42578125" customWidth="1"/>
-    <col min="8" max="8" width="51.7109375" customWidth="1"/>
+    <col min="1" max="2" width="5.1796875" customWidth="1"/>
+    <col min="3" max="4" width="4.54296875" customWidth="1"/>
+    <col min="5" max="5" width="4.1796875" customWidth="1"/>
+    <col min="6" max="6" width="2.453125" customWidth="1"/>
+    <col min="7" max="7" width="4.453125" customWidth="1"/>
+    <col min="8" max="8" width="51.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="8:15" ht="12.6" customHeight="1">
+    <row r="1" spans="8:15" ht="12.65" customHeight="1">
       <c r="H1" s="5" t="s">
         <v>2331</v>
       </c>
     </row>
-    <row r="2" spans="8:15" ht="12.6" customHeight="1">
+    <row r="2" spans="8:15" ht="12.65" customHeight="1">
       <c r="H2" s="20" t="s">
         <v>2332</v>
       </c>
     </row>
-    <row r="3" spans="8:15" ht="12.6" customHeight="1">
+    <row r="3" spans="8:15" ht="12.65" customHeight="1">
       <c r="H3" s="20" t="s">
         <v>2333</v>
       </c>
     </row>
-    <row r="4" spans="8:15" ht="12.6" customHeight="1">
+    <row r="4" spans="8:15" ht="12.65" customHeight="1">
       <c r="H4" s="21" t="s">
         <v>2334</v>
       </c>
     </row>
-    <row r="5" spans="8:15" ht="12.6" customHeight="1">
+    <row r="5" spans="8:15" ht="12.65" customHeight="1">
       <c r="H5" s="6" t="s">
         <v>2335</v>
       </c>
@@ -38775,7 +38775,7 @@
         <v>2339</v>
       </c>
     </row>
-    <row r="6" spans="8:15" ht="12.6" customHeight="1">
+    <row r="6" spans="8:15" ht="12.65" customHeight="1">
       <c r="H6" s="6" t="s">
         <v>2274</v>
       </c>
@@ -38867,7 +38867,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="8:15" ht="12.6" customHeight="1">
+    <row r="10" spans="8:15" ht="12.65" customHeight="1">
       <c r="H10" s="5" t="s">
         <v>2351</v>
       </c>
@@ -40092,7 +40092,7 @@
       <c r="AT41" s="39"/>
       <c r="AU41" s="39"/>
     </row>
-    <row r="42" spans="1:47" s="75" customFormat="1" ht="11.45" customHeight="1">
+    <row r="42" spans="1:47" s="75" customFormat="1" ht="11.5" customHeight="1">
       <c r="A42" s="265"/>
       <c r="B42" s="206"/>
       <c r="C42" s="382"/>
@@ -40421,7 +40421,7 @@
         <v>1624</v>
       </c>
     </row>
-    <row r="70" spans="8:27" ht="11.45" customHeight="1">
+    <row r="70" spans="8:27" ht="11.5" customHeight="1">
       <c r="H70" t="s">
         <v>2548</v>
       </c>
@@ -41222,7 +41222,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="100" spans="8:27" ht="11.45" customHeight="1">
+    <row r="100" spans="8:27" ht="11.5" customHeight="1">
       <c r="H100" t="s">
         <v>2690</v>
       </c>
@@ -41254,7 +41254,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="101" spans="8:27" ht="11.45" customHeight="1">
+    <row r="101" spans="8:27" ht="11.5" customHeight="1">
       <c r="H101" t="s">
         <v>2697</v>
       </c>
@@ -41277,7 +41277,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="102" spans="8:27" ht="11.45" customHeight="1">
+    <row r="102" spans="8:27" ht="11.5" customHeight="1">
       <c r="H102" t="s">
         <v>2702</v>
       </c>
@@ -41297,7 +41297,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="103" spans="8:27" ht="11.45" customHeight="1">
+    <row r="103" spans="8:27" ht="11.5" customHeight="1">
       <c r="H103" t="s">
         <v>2706</v>
       </c>
@@ -41320,7 +41320,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="104" spans="8:27" ht="11.45" customHeight="1">
+    <row r="104" spans="8:27" ht="11.5" customHeight="1">
       <c r="H104" t="s">
         <v>2421</v>
       </c>
@@ -41576,7 +41576,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="115" spans="8:27" ht="11.45" customHeight="1">
+    <row r="115" spans="8:27" ht="11.5" customHeight="1">
       <c r="H115" t="s">
         <v>2753</v>
       </c>
@@ -41599,7 +41599,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="116" spans="8:27" ht="11.45" customHeight="1">
+    <row r="116" spans="8:27" ht="11.5" customHeight="1">
       <c r="H116" t="s">
         <v>2757</v>
       </c>
@@ -41622,7 +41622,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="117" spans="8:27" ht="11.45" customHeight="1">
+    <row r="117" spans="8:27" ht="11.5" customHeight="1">
       <c r="H117" t="s">
         <v>2761</v>
       </c>
@@ -41654,7 +41654,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="118" spans="8:27" ht="11.45" customHeight="1">
+    <row r="118" spans="8:27" ht="11.5" customHeight="1">
       <c r="H118" t="s">
         <v>2769</v>
       </c>
@@ -41686,7 +41686,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="119" spans="8:27" ht="11.45" customHeight="1">
+    <row r="119" spans="8:27" ht="11.5" customHeight="1">
       <c r="H119" t="s">
         <v>2777</v>
       </c>
@@ -41718,7 +41718,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="120" spans="8:27" ht="11.45" customHeight="1">
+    <row r="120" spans="8:27" ht="11.5" customHeight="1">
       <c r="H120" t="s">
         <v>2785</v>
       </c>
@@ -41747,7 +41747,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="121" spans="8:27" ht="11.45" customHeight="1">
+    <row r="121" spans="8:27" ht="11.5" customHeight="1">
       <c r="H121" t="s">
         <v>2791</v>
       </c>
@@ -41773,7 +41773,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="122" spans="8:27" ht="11.45" customHeight="1">
+    <row r="122" spans="8:27" ht="11.5" customHeight="1">
       <c r="H122" t="s">
         <v>2796</v>
       </c>
@@ -42071,7 +42071,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="133" spans="1:33" s="75" customFormat="1" ht="11.45" customHeight="1">
+    <row r="133" spans="1:33" s="75" customFormat="1" ht="11.5" customHeight="1">
       <c r="A133" s="214">
         <v>46079</v>
       </c>
@@ -42466,23 +42466,23 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:C204"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="30" style="69" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="142.5703125" style="70" customWidth="1"/>
-    <col min="3" max="3" width="41.42578125" style="28" customWidth="1"/>
-    <col min="4" max="9" width="14.42578125" style="28" customWidth="1"/>
-    <col min="10" max="16384" width="14.42578125" style="28"/>
+    <col min="2" max="2" width="142.54296875" style="70" customWidth="1"/>
+    <col min="3" max="3" width="41.453125" style="28" customWidth="1"/>
+    <col min="4" max="9" width="14.453125" style="28" customWidth="1"/>
+    <col min="10" max="16384" width="14.453125" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="12.95" customHeight="1">
+    <row r="1" spans="1:3" ht="13" customHeight="1">
       <c r="A1" s="27" t="s">
         <v>2881</v>
       </c>
       <c r="B1" s="58"/>
       <c r="C1" s="59"/>
     </row>
-    <row r="2" spans="1:3" s="63" customFormat="1" ht="12.95" customHeight="1">
+    <row r="2" spans="1:3" s="63" customFormat="1" ht="13" customHeight="1">
       <c r="A2" s="60" t="s">
         <v>2882</v>
       </c>
@@ -42491,7 +42491,7 @@
       </c>
       <c r="C2" s="62"/>
     </row>
-    <row r="3" spans="1:3" ht="12.95" customHeight="1">
+    <row r="3" spans="1:3" ht="13" customHeight="1">
       <c r="A3" s="215" t="s">
         <v>143</v>
       </c>
@@ -42500,7 +42500,7 @@
       </c>
       <c r="C3" s="59"/>
     </row>
-    <row r="4" spans="1:3" ht="12.95" customHeight="1">
+    <row r="4" spans="1:3" ht="13" customHeight="1">
       <c r="A4" s="27" t="s">
         <v>2885</v>
       </c>
@@ -42509,7 +42509,7 @@
       </c>
       <c r="C4" s="59"/>
     </row>
-    <row r="5" spans="1:3" ht="12.95" customHeight="1">
+    <row r="5" spans="1:3" ht="13" customHeight="1">
       <c r="A5" s="27" t="s">
         <v>758</v>
       </c>
@@ -42518,7 +42518,7 @@
       </c>
       <c r="C5" s="59"/>
     </row>
-    <row r="6" spans="1:3" ht="12.95" customHeight="1">
+    <row r="6" spans="1:3" ht="13" customHeight="1">
       <c r="A6" s="27" t="s">
         <v>601</v>
       </c>
@@ -42619,7 +42619,7 @@
       <c r="A18" s="65"/>
       <c r="B18" s="66"/>
     </row>
-    <row r="19" spans="1:2" ht="12.95" customHeight="1">
+    <row r="19" spans="1:2" ht="13" customHeight="1">
       <c r="A19" s="216" t="s">
         <v>2905</v>
       </c>
@@ -42659,7 +42659,7 @@
         <v>2909</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="12.95" customHeight="1">
+    <row r="29" spans="1:2" ht="13" customHeight="1">
       <c r="A29" s="71"/>
       <c r="B29" s="70" t="s">
         <v>2910</v>
@@ -42775,7 +42775,7 @@
         <v>2935</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="42.95" customHeight="1">
+    <row r="46" spans="1:2" ht="43" customHeight="1">
       <c r="A46" s="216" t="s">
         <v>2936</v>
       </c>
@@ -42783,7 +42783,7 @@
         <v>2937</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="12.95" customHeight="1">
+    <row r="49" spans="1:2" ht="13" customHeight="1">
       <c r="A49" s="71" t="s">
         <v>2938</v>
       </c>
@@ -42923,11 +42923,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:X983"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="26.5703125" customWidth="1"/>
-    <col min="2" max="2" width="181.28515625" customWidth="1"/>
-    <col min="3" max="24" width="40.5703125" customWidth="1"/>
+    <col min="1" max="1" width="26.54296875" customWidth="1"/>
+    <col min="2" max="2" width="181.26953125" customWidth="1"/>
+    <col min="3" max="24" width="40.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="29.25" customHeight="1">
@@ -68504,7 +68504,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="5" t="s">
@@ -68594,11 +68594,11 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:I993"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="43.42578125" customWidth="1"/>
-    <col min="2" max="2" width="35.42578125" customWidth="1"/>
-    <col min="3" max="3" width="25.28515625" customWidth="1"/>
+    <col min="1" max="1" width="43.453125" customWidth="1"/>
+    <col min="2" max="2" width="35.453125" customWidth="1"/>
+    <col min="3" max="3" width="25.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15" customHeight="1">
@@ -68611,13 +68611,13 @@
         <v>2971</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="12.6" customHeight="1">
+    <row r="3" spans="1:2" ht="12.65" customHeight="1">
       <c r="A3" t="s">
         <v>2972</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="12.6" customHeight="1"/>
-    <row r="5" spans="1:2" ht="12.6" customHeight="1">
+    <row r="4" spans="1:2" ht="12.65" customHeight="1"/>
+    <row r="5" spans="1:2" ht="12.65" customHeight="1">
       <c r="A5" s="262" t="s">
         <v>2973</v>
       </c>
@@ -68627,23 +68627,23 @@
         <v>2974</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="12.6" customHeight="1">
+    <row r="7" spans="1:2" ht="12.65" customHeight="1">
       <c r="A7" t="s">
         <v>2975</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="12.6" customHeight="1">
+    <row r="8" spans="1:2" ht="12.65" customHeight="1">
       <c r="A8" s="262" t="s">
         <v>2976</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="12.6" customHeight="1"/>
-    <row r="10" spans="1:2" ht="12.6" customHeight="1">
+    <row r="9" spans="1:2" ht="12.65" customHeight="1"/>
+    <row r="10" spans="1:2" ht="12.65" customHeight="1">
       <c r="A10" s="262" t="s">
         <v>2977</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="12.6" customHeight="1">
+    <row r="11" spans="1:2" ht="12.65" customHeight="1">
       <c r="A11" t="s">
         <v>2978</v>
       </c>
@@ -68651,7 +68651,7 @@
         <v>2979</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="12.6" customHeight="1">
+    <row r="12" spans="1:2" ht="12.65" customHeight="1">
       <c r="A12" t="s">
         <v>2980</v>
       </c>
@@ -68659,7 +68659,7 @@
         <v>2981</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="51.95" customHeight="1">
+    <row r="13" spans="1:2" ht="52" customHeight="1">
       <c r="A13" t="s">
         <v>2982</v>
       </c>
@@ -68667,7 +68667,7 @@
         <v>2983</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="12.6" customHeight="1">
+    <row r="14" spans="1:2" ht="12.65" customHeight="1">
       <c r="A14" t="s">
         <v>2984</v>
       </c>
@@ -68675,7 +68675,7 @@
         <v>2985</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="12.6" customHeight="1">
+    <row r="15" spans="1:2" ht="12.65" customHeight="1">
       <c r="A15" t="s">
         <v>2986</v>
       </c>
@@ -68683,13 +68683,13 @@
         <v>2987</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="12.6" customHeight="1"/>
-    <row r="17" spans="1:3" ht="12.6" customHeight="1">
+    <row r="16" spans="1:2" ht="12.65" customHeight="1"/>
+    <row r="17" spans="1:3" ht="12.65" customHeight="1">
       <c r="A17" s="262" t="s">
         <v>2988</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="12.6" customHeight="1">
+    <row r="18" spans="1:3" ht="12.65" customHeight="1">
       <c r="B18" t="s">
         <v>2989</v>
       </c>
@@ -68697,7 +68697,7 @@
         <v>2990</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="24.95" customHeight="1">
+    <row r="19" spans="1:3" ht="25" customHeight="1">
       <c r="A19" t="s">
         <v>2991</v>
       </c>
@@ -68705,7 +68705,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="12.6" customHeight="1">
+    <row r="20" spans="1:3" ht="12.65" customHeight="1">
       <c r="A20" t="s">
         <v>2992</v>
       </c>
@@ -68716,7 +68716,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="24.95" customHeight="1">
+    <row r="21" spans="1:3" ht="25" customHeight="1">
       <c r="A21" t="s">
         <v>2993</v>
       </c>
@@ -68727,7 +68727,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="12.6" customHeight="1">
+    <row r="22" spans="1:3" ht="12.65" customHeight="1">
       <c r="A22" t="s">
         <v>2994</v>
       </c>
@@ -68738,7 +68738,7 @@
         <v>0.188</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="24.95" customHeight="1">
+    <row r="23" spans="1:3" ht="25" customHeight="1">
       <c r="A23" t="s">
         <v>2995</v>
       </c>
@@ -68749,7 +68749,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="12.6" customHeight="1">
+    <row r="24" spans="1:3" ht="12.65" customHeight="1">
       <c r="A24" t="s">
         <v>2996</v>
       </c>
@@ -68760,7 +68760,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="12.6" customHeight="1">
+    <row r="25" spans="1:3" ht="12.65" customHeight="1">
       <c r="A25" t="s">
         <v>2997</v>
       </c>
@@ -68771,13 +68771,13 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="12.6" customHeight="1"/>
-    <row r="27" spans="1:3" ht="12.6" customHeight="1">
+    <row r="26" spans="1:3" ht="12.65" customHeight="1"/>
+    <row r="27" spans="1:3" ht="12.65" customHeight="1">
       <c r="A27" s="262" t="s">
         <v>2998</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="12.6" customHeight="1">
+    <row r="28" spans="1:3" ht="12.65" customHeight="1">
       <c r="A28" t="s">
         <v>2999</v>
       </c>
@@ -68788,7 +68788,7 @@
         <v>0.94199999999999995</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="12.6" customHeight="1">
+    <row r="29" spans="1:3" ht="12.65" customHeight="1">
       <c r="A29" t="s">
         <v>3001</v>
       </c>
@@ -68799,7 +68799,7 @@
         <v>0.73299999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="12.6" customHeight="1">
+    <row r="30" spans="1:3" ht="12.65" customHeight="1">
       <c r="A30" t="s">
         <v>3003</v>
       </c>
@@ -68810,7 +68810,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="12.6" customHeight="1">
+    <row r="31" spans="1:3" ht="12.65" customHeight="1">
       <c r="A31" t="s">
         <v>3005</v>
       </c>
@@ -68821,24 +68821,24 @@
         <v>0.108</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="12.6" customHeight="1"/>
-    <row r="33" spans="1:9" ht="12.6" customHeight="1">
+    <row r="32" spans="1:3" ht="12.65" customHeight="1"/>
+    <row r="33" spans="1:9" ht="12.65" customHeight="1">
       <c r="A33" s="262" t="s">
         <v>3007</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="12.6" customHeight="1">
+    <row r="34" spans="1:9" ht="12.65" customHeight="1">
       <c r="A34" t="s">
         <v>3008</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="36" spans="1:9" ht="12.6" customHeight="1">
+    <row r="35" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="36" spans="1:9" ht="12.65" customHeight="1">
       <c r="A36" s="262" t="s">
         <v>3009</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="12.6" customHeight="1">
+    <row r="37" spans="1:9" ht="12.65" customHeight="1">
       <c r="A37" t="s">
         <v>3010</v>
       </c>
@@ -68867,7 +68867,7 @@
         <v>3018</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="12.6" customHeight="1">
+    <row r="38" spans="1:9" ht="12.65" customHeight="1">
       <c r="A38" t="s">
         <v>144</v>
       </c>
@@ -68890,7 +68890,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="12.6" customHeight="1">
+    <row r="39" spans="1:9" ht="12.65" customHeight="1">
       <c r="A39" t="s">
         <v>150</v>
       </c>
@@ -68916,7 +68916,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="12.6" customHeight="1">
+    <row r="40" spans="1:9" ht="12.65" customHeight="1">
       <c r="B40" t="s">
         <v>3021</v>
       </c>
@@ -68939,7 +68939,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="12.6" customHeight="1">
+    <row r="41" spans="1:9" ht="12.65" customHeight="1">
       <c r="A41" t="s">
         <v>167</v>
       </c>
@@ -68953,7 +68953,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="12.6" customHeight="1">
+    <row r="42" spans="1:9" ht="12.65" customHeight="1">
       <c r="A42" t="s">
         <v>642</v>
       </c>
@@ -68982,7 +68982,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="12.6" customHeight="1">
+    <row r="43" spans="1:9" ht="12.65" customHeight="1">
       <c r="A43" t="s">
         <v>694</v>
       </c>
@@ -69008,7 +69008,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="12.6" customHeight="1">
+    <row r="44" spans="1:9" ht="12.65" customHeight="1">
       <c r="A44" t="s">
         <v>940</v>
       </c>
@@ -69037,7 +69037,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="12.6" customHeight="1">
+    <row r="45" spans="1:9" ht="12.65" customHeight="1">
       <c r="A45" t="s">
         <v>1115</v>
       </c>
@@ -69066,7 +69066,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="12.6" customHeight="1">
+    <row r="46" spans="1:9" ht="12.65" customHeight="1">
       <c r="A46" t="s">
         <v>1120</v>
       </c>
@@ -69095,7 +69095,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="12.6" customHeight="1">
+    <row r="47" spans="1:9" ht="12.65" customHeight="1">
       <c r="A47" t="s">
         <v>1536</v>
       </c>
@@ -69121,7 +69121,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="12.6" customHeight="1">
+    <row r="48" spans="1:9" ht="12.65" customHeight="1">
       <c r="A48" t="s">
         <v>1694</v>
       </c>
@@ -69147,13 +69147,13 @@
         <v>939</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="50" spans="1:9" ht="12.6" customHeight="1">
+    <row r="49" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="50" spans="1:9" ht="12.65" customHeight="1">
       <c r="A50" s="262" t="s">
         <v>3025</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="12.6" customHeight="1">
+    <row r="51" spans="1:9" ht="12.65" customHeight="1">
       <c r="B51" t="s">
         <v>3026</v>
       </c>
@@ -69179,7 +69179,7 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="12.6" customHeight="1">
+    <row r="52" spans="1:9" ht="12.65" customHeight="1">
       <c r="A52" t="s">
         <v>1434</v>
       </c>
@@ -69208,7 +69208,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="12.6" customHeight="1">
+    <row r="53" spans="1:9" ht="12.65" customHeight="1">
       <c r="A53" t="s">
         <v>3020</v>
       </c>
@@ -69237,7 +69237,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="12.6" customHeight="1">
+    <row r="54" spans="1:9" ht="12.65" customHeight="1">
       <c r="A54" t="s">
         <v>3031</v>
       </c>
@@ -69266,13 +69266,13 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="56" spans="1:9" ht="12.6" customHeight="1">
+    <row r="55" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="56" spans="1:9" ht="12.65" customHeight="1">
       <c r="A56" s="262" t="s">
         <v>3034</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="12.6" customHeight="1">
+    <row r="57" spans="1:9" ht="12.65" customHeight="1">
       <c r="B57" t="s">
         <v>3026</v>
       </c>
@@ -69298,7 +69298,7 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="12.6" customHeight="1">
+    <row r="58" spans="1:9" ht="12.65" customHeight="1">
       <c r="A58" t="s">
         <v>1434</v>
       </c>
@@ -69327,7 +69327,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="12.6" customHeight="1">
+    <row r="59" spans="1:9" ht="12.65" customHeight="1">
       <c r="A59" t="s">
         <v>3020</v>
       </c>
@@ -69356,7 +69356,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="12.6" customHeight="1">
+    <row r="60" spans="1:9" ht="12.65" customHeight="1">
       <c r="A60" t="s">
         <v>3031</v>
       </c>
@@ -69385,13 +69385,13 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="62" spans="1:9" ht="12.6" customHeight="1">
+    <row r="61" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="62" spans="1:9" ht="12.65" customHeight="1">
       <c r="A62" s="262" t="s">
         <v>3035</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="12.6" customHeight="1">
+    <row r="63" spans="1:9" ht="12.65" customHeight="1">
       <c r="B63" t="s">
         <v>3026</v>
       </c>
@@ -69417,7 +69417,7 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="12.6" customHeight="1">
+    <row r="64" spans="1:9" ht="12.65" customHeight="1">
       <c r="A64" t="s">
         <v>51</v>
       </c>
@@ -69446,7 +69446,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="12.6" customHeight="1">
+    <row r="65" spans="1:9" ht="12.65" customHeight="1">
       <c r="A65" t="s">
         <v>32</v>
       </c>
@@ -69475,7 +69475,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="12.6" customHeight="1">
+    <row r="66" spans="1:9" ht="12.65" customHeight="1">
       <c r="A66" t="s">
         <v>3031</v>
       </c>
@@ -69504,13 +69504,13 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="68" spans="1:9" ht="12.6" customHeight="1">
+    <row r="67" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="68" spans="1:9" ht="12.65" customHeight="1">
       <c r="A68" s="262" t="s">
         <v>3036</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="12.6" customHeight="1">
+    <row r="69" spans="1:9" ht="12.65" customHeight="1">
       <c r="B69" t="s">
         <v>3026</v>
       </c>
@@ -69536,7 +69536,7 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="12.6" customHeight="1">
+    <row r="70" spans="1:9" ht="12.65" customHeight="1">
       <c r="A70" t="s">
         <v>1775</v>
       </c>
@@ -69565,7 +69565,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="12.6" customHeight="1">
+    <row r="71" spans="1:9" ht="12.65" customHeight="1">
       <c r="A71" t="s">
         <v>1639</v>
       </c>
@@ -69594,7 +69594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="12.6" customHeight="1">
+    <row r="72" spans="1:9" ht="12.65" customHeight="1">
       <c r="A72" t="s">
         <v>1624</v>
       </c>
@@ -69623,7 +69623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="12.6" customHeight="1">
+    <row r="73" spans="1:9" ht="12.65" customHeight="1">
       <c r="A73" t="s">
         <v>3031</v>
       </c>
@@ -69652,13 +69652,13 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="75" spans="1:9" ht="12.6" customHeight="1">
+    <row r="74" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="75" spans="1:9" ht="12.65" customHeight="1">
       <c r="A75" s="262" t="s">
         <v>3037</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="12.6" customHeight="1">
+    <row r="76" spans="1:9" ht="12.65" customHeight="1">
       <c r="B76" t="s">
         <v>3026</v>
       </c>
@@ -69684,7 +69684,7 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="12.6" customHeight="1">
+    <row r="77" spans="1:9" ht="12.65" customHeight="1">
       <c r="A77" t="s">
         <v>798</v>
       </c>
@@ -69713,7 +69713,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="12.6" customHeight="1">
+    <row r="78" spans="1:9" ht="12.65" customHeight="1">
       <c r="A78" t="s">
         <v>1113</v>
       </c>
@@ -69742,7 +69742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="12.6" customHeight="1">
+    <row r="79" spans="1:9" ht="12.65" customHeight="1">
       <c r="A79" t="s">
         <v>3024</v>
       </c>
@@ -69771,7 +69771,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="12.6" customHeight="1">
+    <row r="80" spans="1:9" ht="12.65" customHeight="1">
       <c r="A80" t="s">
         <v>1466</v>
       </c>
@@ -69800,7 +69800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="12.6" customHeight="1">
+    <row r="81" spans="1:9" ht="12.65" customHeight="1">
       <c r="A81" t="s">
         <v>3031</v>
       </c>
@@ -69829,13 +69829,13 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="83" spans="1:9" ht="12.6" customHeight="1">
+    <row r="82" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="83" spans="1:9" ht="12.65" customHeight="1">
       <c r="A83" s="262" t="s">
         <v>3038</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="12.6" customHeight="1">
+    <row r="84" spans="1:9" ht="12.65" customHeight="1">
       <c r="B84" t="s">
         <v>3026</v>
       </c>
@@ -69861,7 +69861,7 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="12.6" customHeight="1">
+    <row r="85" spans="1:9" ht="12.65" customHeight="1">
       <c r="A85" t="s">
         <v>3039</v>
       </c>
@@ -69890,7 +69890,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="12.6" customHeight="1">
+    <row r="86" spans="1:9" ht="12.65" customHeight="1">
       <c r="A86" t="s">
         <v>3040</v>
       </c>
@@ -69919,7 +69919,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="12.6" customHeight="1">
+    <row r="87" spans="1:9" ht="12.65" customHeight="1">
       <c r="A87" t="s">
         <v>3041</v>
       </c>
@@ -69948,7 +69948,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="12.6" customHeight="1">
+    <row r="88" spans="1:9" ht="12.65" customHeight="1">
       <c r="A88" t="s">
         <v>3031</v>
       </c>
@@ -69977,13 +69977,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="90" spans="1:9" ht="12.6" customHeight="1">
+    <row r="89" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="90" spans="1:9" ht="12.65" customHeight="1">
       <c r="A90" s="262" t="s">
         <v>3042</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="12.6" customHeight="1">
+    <row r="91" spans="1:9" ht="12.65" customHeight="1">
       <c r="B91" t="s">
         <v>3026</v>
       </c>
@@ -70009,7 +70009,7 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="12.6" customHeight="1">
+    <row r="92" spans="1:9" ht="12.65" customHeight="1">
       <c r="A92" t="b">
         <v>0</v>
       </c>
@@ -70038,7 +70038,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="12.6" customHeight="1">
+    <row r="93" spans="1:9" ht="12.65" customHeight="1">
       <c r="A93" t="b">
         <v>1</v>
       </c>
@@ -70067,7 +70067,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="12.6" customHeight="1">
+    <row r="94" spans="1:9" ht="12.65" customHeight="1">
       <c r="A94" t="s">
         <v>3031</v>
       </c>
@@ -70096,13 +70096,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="96" spans="1:9" ht="12.6" customHeight="1">
+    <row r="95" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="96" spans="1:9" ht="12.65" customHeight="1">
       <c r="A96" s="262" t="s">
         <v>3043</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="12.6" customHeight="1">
+    <row r="97" spans="1:9" ht="12.65" customHeight="1">
       <c r="B97" t="s">
         <v>3026</v>
       </c>
@@ -70128,7 +70128,7 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="12.6" customHeight="1">
+    <row r="98" spans="1:9" ht="12.65" customHeight="1">
       <c r="A98" t="s">
         <v>33</v>
       </c>
@@ -70157,7 +70157,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="12.6" customHeight="1">
+    <row r="99" spans="1:9" ht="12.65" customHeight="1">
       <c r="A99" t="s">
         <v>244</v>
       </c>
@@ -70186,7 +70186,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="12.6" customHeight="1">
+    <row r="100" spans="1:9" ht="12.65" customHeight="1">
       <c r="A100" t="s">
         <v>62</v>
       </c>
@@ -70215,7 +70215,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="12.6" customHeight="1">
+    <row r="101" spans="1:9" ht="12.65" customHeight="1">
       <c r="A101" t="s">
         <v>181</v>
       </c>
@@ -70244,7 +70244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="12.6" customHeight="1">
+    <row r="102" spans="1:9" ht="12.65" customHeight="1">
       <c r="A102" t="s">
         <v>142</v>
       </c>
@@ -70273,7 +70273,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="12.6" customHeight="1">
+    <row r="103" spans="1:9" ht="12.65" customHeight="1">
       <c r="A103" t="s">
         <v>1044</v>
       </c>
@@ -70302,7 +70302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="12.6" customHeight="1">
+    <row r="104" spans="1:9" ht="12.65" customHeight="1">
       <c r="A104" t="s">
         <v>166</v>
       </c>
@@ -70331,7 +70331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="12.6" customHeight="1">
+    <row r="105" spans="1:9" ht="12.65" customHeight="1">
       <c r="A105" t="s">
         <v>395</v>
       </c>
@@ -70360,7 +70360,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="12.6" customHeight="1">
+    <row r="106" spans="1:9" ht="12.65" customHeight="1">
       <c r="A106" t="s">
         <v>3031</v>
       </c>
@@ -70389,13 +70389,13 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="108" spans="1:9" ht="12.6" customHeight="1">
+    <row r="107" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="108" spans="1:9" ht="12.65" customHeight="1">
       <c r="A108" s="262" t="s">
         <v>3044</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="12.6" customHeight="1">
+    <row r="109" spans="1:9" ht="12.65" customHeight="1">
       <c r="B109" t="s">
         <v>3026</v>
       </c>
@@ -70421,7 +70421,7 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="12.6" customHeight="1">
+    <row r="110" spans="1:9" ht="12.65" customHeight="1">
       <c r="A110" t="s">
         <v>34</v>
       </c>
@@ -70450,7 +70450,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="12.6" customHeight="1">
+    <row r="111" spans="1:9" ht="12.65" customHeight="1">
       <c r="A111" t="s">
         <v>52</v>
       </c>
@@ -70479,7 +70479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="12.6" customHeight="1">
+    <row r="112" spans="1:9" ht="12.65" customHeight="1">
       <c r="A112" t="s">
         <v>117</v>
       </c>
@@ -70508,7 +70508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="12.6" customHeight="1">
+    <row r="113" spans="1:9" ht="12.65" customHeight="1">
       <c r="A113" t="s">
         <v>44</v>
       </c>
@@ -70537,7 +70537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="12.6" customHeight="1">
+    <row r="114" spans="1:9" ht="12.65" customHeight="1">
       <c r="A114" t="s">
         <v>3031</v>
       </c>
@@ -70566,13 +70566,13 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="116" spans="1:9" ht="12.6" customHeight="1">
+    <row r="115" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="116" spans="1:9" ht="12.65" customHeight="1">
       <c r="A116" s="262" t="s">
         <v>3045</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="12.6" customHeight="1">
+    <row r="117" spans="1:9" ht="12.65" customHeight="1">
       <c r="B117" t="s">
         <v>3026</v>
       </c>
@@ -70598,7 +70598,7 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="12.6" customHeight="1">
+    <row r="118" spans="1:9" ht="12.65" customHeight="1">
       <c r="A118" t="s">
         <v>3046</v>
       </c>
@@ -70627,7 +70627,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="12.6" customHeight="1">
+    <row r="119" spans="1:9" ht="12.65" customHeight="1">
       <c r="A119" t="s">
         <v>3047</v>
       </c>
@@ -70656,7 +70656,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="12.6" customHeight="1">
+    <row r="120" spans="1:9" ht="12.65" customHeight="1">
       <c r="A120" t="s">
         <v>3031</v>
       </c>
@@ -70685,935 +70685,935 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="122" spans="1:9" ht="12.6" customHeight="1">
+    <row r="121" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="122" spans="1:9" ht="12.65" customHeight="1">
       <c r="A122" s="262" t="s">
         <v>3048</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="124" spans="1:9" ht="12.6" customHeight="1">
+    <row r="123" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="124" spans="1:9" ht="12.65" customHeight="1">
       <c r="A124" s="262" t="s">
         <v>3049</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="12.6" customHeight="1">
+    <row r="125" spans="1:9" ht="12.65" customHeight="1">
       <c r="A125" s="262" t="s">
         <v>3050</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="127" spans="1:9" ht="12.6" customHeight="1">
+    <row r="126" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="127" spans="1:9" ht="12.65" customHeight="1">
       <c r="A127" t="s">
         <v>3051</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="12.6" customHeight="1">
+    <row r="128" spans="1:9" ht="12.65" customHeight="1">
       <c r="A128" t="s">
         <v>3052</v>
       </c>
     </row>
-    <row r="129" spans="1:1" ht="12.6" customHeight="1">
+    <row r="129" spans="1:1" ht="12.65" customHeight="1">
       <c r="A129" t="s">
         <v>3053</v>
       </c>
     </row>
-    <row r="130" spans="1:1" ht="12.6" customHeight="1">
+    <row r="130" spans="1:1" ht="12.65" customHeight="1">
       <c r="A130" t="s">
         <v>3054</v>
       </c>
     </row>
-    <row r="131" spans="1:1" ht="12.6" customHeight="1">
+    <row r="131" spans="1:1" ht="12.65" customHeight="1">
       <c r="A131" t="s">
         <v>3055</v>
       </c>
     </row>
-    <row r="132" spans="1:1" ht="12.6" customHeight="1">
+    <row r="132" spans="1:1" ht="12.65" customHeight="1">
       <c r="A132" t="s">
         <v>3056</v>
       </c>
     </row>
-    <row r="133" spans="1:1" ht="12.6" customHeight="1">
+    <row r="133" spans="1:1" ht="12.65" customHeight="1">
       <c r="A133" t="s">
         <v>3057</v>
       </c>
     </row>
-    <row r="134" spans="1:1" ht="12.6" customHeight="1">
+    <row r="134" spans="1:1" ht="12.65" customHeight="1">
       <c r="A134" t="s">
         <v>3058</v>
       </c>
     </row>
-    <row r="135" spans="1:1" ht="12.6" customHeight="1">
+    <row r="135" spans="1:1" ht="12.65" customHeight="1">
       <c r="A135" t="s">
         <v>3059</v>
       </c>
     </row>
-    <row r="136" spans="1:1" ht="12.6" customHeight="1">
+    <row r="136" spans="1:1" ht="12.65" customHeight="1">
       <c r="A136" t="s">
         <v>3060</v>
       </c>
     </row>
-    <row r="137" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="138" spans="1:1" ht="12.6" customHeight="1">
+    <row r="137" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="138" spans="1:1" ht="12.65" customHeight="1">
       <c r="A138" s="262" t="s">
         <v>3061</v>
       </c>
     </row>
-    <row r="139" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="140" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="141" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="142" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="143" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="144" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="145" ht="12.6" customHeight="1"/>
-    <row r="146" ht="12.6" customHeight="1"/>
-    <row r="147" ht="12.6" customHeight="1"/>
-    <row r="148" ht="12.6" customHeight="1"/>
-    <row r="149" ht="12.6" customHeight="1"/>
-    <row r="150" ht="12.6" customHeight="1"/>
-    <row r="151" ht="12.6" customHeight="1"/>
-    <row r="152" ht="12.6" customHeight="1"/>
-    <row r="153" ht="12.6" customHeight="1"/>
-    <row r="154" ht="12.6" customHeight="1"/>
-    <row r="155" ht="12.6" customHeight="1"/>
-    <row r="156" ht="12.6" customHeight="1"/>
-    <row r="157" ht="12.6" customHeight="1"/>
-    <row r="158" ht="12.6" customHeight="1"/>
-    <row r="159" ht="12.6" customHeight="1"/>
-    <row r="160" ht="12.6" customHeight="1"/>
-    <row r="161" ht="12.6" customHeight="1"/>
-    <row r="162" ht="12.6" customHeight="1"/>
-    <row r="163" ht="12.6" customHeight="1"/>
-    <row r="164" ht="12.6" customHeight="1"/>
-    <row r="165" ht="12.6" customHeight="1"/>
-    <row r="166" ht="12.6" customHeight="1"/>
-    <row r="167" ht="12.6" customHeight="1"/>
-    <row r="168" ht="12.6" customHeight="1"/>
-    <row r="169" ht="12.6" customHeight="1"/>
-    <row r="170" ht="12.6" customHeight="1"/>
-    <row r="171" ht="12.6" customHeight="1"/>
-    <row r="172" ht="12.6" customHeight="1"/>
-    <row r="173" ht="12.6" customHeight="1"/>
-    <row r="174" ht="12.6" customHeight="1"/>
-    <row r="175" ht="12.6" customHeight="1"/>
-    <row r="176" ht="12.6" customHeight="1"/>
-    <row r="177" ht="12.6" customHeight="1"/>
-    <row r="178" ht="12.6" customHeight="1"/>
-    <row r="179" ht="12.6" customHeight="1"/>
-    <row r="180" ht="12.6" customHeight="1"/>
-    <row r="181" ht="12.6" customHeight="1"/>
-    <row r="182" ht="12.6" customHeight="1"/>
-    <row r="183" ht="12.6" customHeight="1"/>
-    <row r="184" ht="12.6" customHeight="1"/>
-    <row r="185" ht="12.6" customHeight="1"/>
-    <row r="186" ht="12.6" customHeight="1"/>
-    <row r="187" ht="12.6" customHeight="1"/>
-    <row r="188" ht="12.6" customHeight="1"/>
-    <row r="189" ht="12.6" customHeight="1"/>
-    <row r="190" ht="12.6" customHeight="1"/>
-    <row r="191" ht="12.6" customHeight="1"/>
-    <row r="192" ht="12.6" customHeight="1"/>
-    <row r="193" ht="12.6" customHeight="1"/>
-    <row r="194" ht="12.6" customHeight="1"/>
-    <row r="195" ht="12.6" customHeight="1"/>
-    <row r="196" ht="12.6" customHeight="1"/>
-    <row r="197" ht="12.6" customHeight="1"/>
-    <row r="198" ht="12.6" customHeight="1"/>
-    <row r="199" ht="12.6" customHeight="1"/>
-    <row r="200" ht="12.6" customHeight="1"/>
-    <row r="201" ht="12.6" customHeight="1"/>
-    <row r="202" ht="12.6" customHeight="1"/>
-    <row r="203" ht="12.6" customHeight="1"/>
-    <row r="204" ht="12.6" customHeight="1"/>
-    <row r="205" ht="12.6" customHeight="1"/>
-    <row r="206" ht="12.6" customHeight="1"/>
-    <row r="207" ht="12.6" customHeight="1"/>
-    <row r="208" ht="12.6" customHeight="1"/>
-    <row r="209" ht="12.6" customHeight="1"/>
-    <row r="210" ht="12.6" customHeight="1"/>
-    <row r="211" ht="12.6" customHeight="1"/>
-    <row r="212" ht="12.6" customHeight="1"/>
-    <row r="213" ht="12.6" customHeight="1"/>
-    <row r="214" ht="12.6" customHeight="1"/>
-    <row r="215" ht="12.6" customHeight="1"/>
-    <row r="216" ht="12.6" customHeight="1"/>
-    <row r="217" ht="12.6" customHeight="1"/>
-    <row r="218" ht="12.6" customHeight="1"/>
-    <row r="219" ht="12.6" customHeight="1"/>
-    <row r="220" ht="12.6" customHeight="1"/>
-    <row r="221" ht="12.6" customHeight="1"/>
-    <row r="222" ht="12.6" customHeight="1"/>
-    <row r="223" ht="12.6" customHeight="1"/>
-    <row r="224" ht="12.6" customHeight="1"/>
-    <row r="225" ht="12.6" customHeight="1"/>
-    <row r="226" ht="12.6" customHeight="1"/>
-    <row r="227" ht="12.6" customHeight="1"/>
-    <row r="228" ht="12.6" customHeight="1"/>
-    <row r="229" ht="12.6" customHeight="1"/>
-    <row r="230" ht="12.6" customHeight="1"/>
-    <row r="231" ht="12.6" customHeight="1"/>
-    <row r="232" ht="12.6" customHeight="1"/>
-    <row r="233" ht="12.6" customHeight="1"/>
-    <row r="234" ht="12.6" customHeight="1"/>
-    <row r="235" ht="12.6" customHeight="1"/>
-    <row r="236" ht="12.6" customHeight="1"/>
-    <row r="237" ht="12.6" customHeight="1"/>
-    <row r="238" ht="12.6" customHeight="1"/>
-    <row r="239" ht="12.6" customHeight="1"/>
-    <row r="240" ht="12.6" customHeight="1"/>
-    <row r="241" ht="12.6" customHeight="1"/>
-    <row r="242" ht="12.6" customHeight="1"/>
-    <row r="243" ht="12.6" customHeight="1"/>
-    <row r="244" ht="12.6" customHeight="1"/>
-    <row r="245" ht="12.6" customHeight="1"/>
-    <row r="246" ht="12.6" customHeight="1"/>
-    <row r="247" ht="12.6" customHeight="1"/>
-    <row r="248" ht="12.6" customHeight="1"/>
-    <row r="249" ht="12.6" customHeight="1"/>
-    <row r="250" ht="12.6" customHeight="1"/>
-    <row r="251" ht="12.6" customHeight="1"/>
-    <row r="252" ht="12.6" customHeight="1"/>
-    <row r="253" ht="12.6" customHeight="1"/>
-    <row r="254" ht="12.6" customHeight="1"/>
-    <row r="255" ht="12.6" customHeight="1"/>
-    <row r="256" ht="12.6" customHeight="1"/>
-    <row r="257" ht="12.6" customHeight="1"/>
-    <row r="258" ht="12.6" customHeight="1"/>
-    <row r="259" ht="12.6" customHeight="1"/>
-    <row r="260" ht="12.6" customHeight="1"/>
-    <row r="261" ht="12.6" customHeight="1"/>
-    <row r="262" ht="12.6" customHeight="1"/>
-    <row r="263" ht="12.6" customHeight="1"/>
-    <row r="264" ht="12.6" customHeight="1"/>
-    <row r="265" ht="12.6" customHeight="1"/>
-    <row r="266" ht="12.6" customHeight="1"/>
-    <row r="267" ht="12.6" customHeight="1"/>
-    <row r="268" ht="12.6" customHeight="1"/>
-    <row r="269" ht="12.6" customHeight="1"/>
-    <row r="270" ht="12.6" customHeight="1"/>
-    <row r="271" ht="12.6" customHeight="1"/>
-    <row r="272" ht="12.6" customHeight="1"/>
-    <row r="273" ht="12.6" customHeight="1"/>
-    <row r="274" ht="12.6" customHeight="1"/>
-    <row r="275" ht="12.6" customHeight="1"/>
-    <row r="276" ht="12.6" customHeight="1"/>
-    <row r="277" ht="12.6" customHeight="1"/>
-    <row r="278" ht="12.6" customHeight="1"/>
-    <row r="279" ht="12.6" customHeight="1"/>
-    <row r="280" ht="12.6" customHeight="1"/>
-    <row r="281" ht="12.6" customHeight="1"/>
-    <row r="282" ht="12.6" customHeight="1"/>
-    <row r="283" ht="12.6" customHeight="1"/>
-    <row r="284" ht="12.6" customHeight="1"/>
-    <row r="285" ht="12.6" customHeight="1"/>
-    <row r="286" ht="12.6" customHeight="1"/>
-    <row r="287" ht="12.6" customHeight="1"/>
-    <row r="288" ht="12.6" customHeight="1"/>
-    <row r="289" ht="12.6" customHeight="1"/>
-    <row r="290" ht="12.6" customHeight="1"/>
-    <row r="291" ht="12.6" customHeight="1"/>
-    <row r="292" ht="12.6" customHeight="1"/>
-    <row r="293" ht="12.6" customHeight="1"/>
-    <row r="294" ht="12.6" customHeight="1"/>
-    <row r="295" ht="12.6" customHeight="1"/>
-    <row r="296" ht="12.6" customHeight="1"/>
-    <row r="297" ht="12.6" customHeight="1"/>
-    <row r="298" ht="12.6" customHeight="1"/>
-    <row r="299" ht="12.6" customHeight="1"/>
-    <row r="300" ht="12.6" customHeight="1"/>
-    <row r="301" ht="12.6" customHeight="1"/>
-    <row r="302" ht="12.6" customHeight="1"/>
-    <row r="303" ht="12.6" customHeight="1"/>
-    <row r="304" ht="12.6" customHeight="1"/>
-    <row r="305" ht="12.6" customHeight="1"/>
-    <row r="306" ht="12.6" customHeight="1"/>
-    <row r="307" ht="12.6" customHeight="1"/>
-    <row r="308" ht="12.6" customHeight="1"/>
-    <row r="309" ht="12.6" customHeight="1"/>
-    <row r="310" ht="12.6" customHeight="1"/>
-    <row r="311" ht="12.6" customHeight="1"/>
-    <row r="312" ht="12.6" customHeight="1"/>
-    <row r="313" ht="12.6" customHeight="1"/>
-    <row r="314" ht="12.6" customHeight="1"/>
-    <row r="315" ht="12.6" customHeight="1"/>
-    <row r="316" ht="12.6" customHeight="1"/>
-    <row r="317" ht="12.6" customHeight="1"/>
-    <row r="318" ht="12.6" customHeight="1"/>
-    <row r="319" ht="12.6" customHeight="1"/>
-    <row r="320" ht="12.6" customHeight="1"/>
-    <row r="321" ht="12.6" customHeight="1"/>
-    <row r="322" ht="12.6" customHeight="1"/>
-    <row r="323" ht="12.6" customHeight="1"/>
-    <row r="324" ht="12.6" customHeight="1"/>
-    <row r="325" ht="12.6" customHeight="1"/>
-    <row r="326" ht="12.6" customHeight="1"/>
-    <row r="327" ht="12.6" customHeight="1"/>
-    <row r="328" ht="12.6" customHeight="1"/>
-    <row r="329" ht="12.6" customHeight="1"/>
-    <row r="330" ht="12.6" customHeight="1"/>
-    <row r="331" ht="12.6" customHeight="1"/>
-    <row r="332" ht="12.6" customHeight="1"/>
-    <row r="333" ht="12.6" customHeight="1"/>
-    <row r="334" ht="12.6" customHeight="1"/>
-    <row r="335" ht="12.6" customHeight="1"/>
-    <row r="336" ht="12.6" customHeight="1"/>
-    <row r="337" ht="12.6" customHeight="1"/>
-    <row r="338" ht="12.6" customHeight="1"/>
-    <row r="339" ht="12.6" customHeight="1"/>
-    <row r="340" ht="12.6" customHeight="1"/>
-    <row r="341" ht="12.6" customHeight="1"/>
-    <row r="342" ht="12.6" customHeight="1"/>
-    <row r="343" ht="12.6" customHeight="1"/>
-    <row r="344" ht="12.6" customHeight="1"/>
-    <row r="345" ht="12.6" customHeight="1"/>
-    <row r="346" ht="12.6" customHeight="1"/>
-    <row r="347" ht="12.6" customHeight="1"/>
-    <row r="348" ht="12.6" customHeight="1"/>
-    <row r="349" ht="12.6" customHeight="1"/>
-    <row r="350" ht="12.6" customHeight="1"/>
-    <row r="351" ht="12.6" customHeight="1"/>
-    <row r="352" ht="12.6" customHeight="1"/>
-    <row r="353" ht="12.6" customHeight="1"/>
-    <row r="354" ht="12.6" customHeight="1"/>
-    <row r="355" ht="12.6" customHeight="1"/>
-    <row r="356" ht="12.6" customHeight="1"/>
-    <row r="357" ht="12.6" customHeight="1"/>
-    <row r="358" ht="12.6" customHeight="1"/>
-    <row r="359" ht="12.6" customHeight="1"/>
-    <row r="360" ht="12.6" customHeight="1"/>
-    <row r="361" ht="12.6" customHeight="1"/>
-    <row r="362" ht="12.6" customHeight="1"/>
-    <row r="363" ht="12.6" customHeight="1"/>
-    <row r="364" ht="12.6" customHeight="1"/>
-    <row r="365" ht="12.6" customHeight="1"/>
-    <row r="366" ht="12.6" customHeight="1"/>
-    <row r="367" ht="12.6" customHeight="1"/>
-    <row r="368" ht="12.6" customHeight="1"/>
-    <row r="369" ht="12.6" customHeight="1"/>
-    <row r="370" ht="12.6" customHeight="1"/>
-    <row r="371" ht="12.6" customHeight="1"/>
-    <row r="372" ht="12.6" customHeight="1"/>
-    <row r="373" ht="12.6" customHeight="1"/>
-    <row r="374" ht="12.6" customHeight="1"/>
-    <row r="375" ht="12.6" customHeight="1"/>
-    <row r="376" ht="12.6" customHeight="1"/>
-    <row r="377" ht="12.6" customHeight="1"/>
-    <row r="378" ht="12.6" customHeight="1"/>
-    <row r="379" ht="12.6" customHeight="1"/>
-    <row r="380" ht="12.6" customHeight="1"/>
-    <row r="381" ht="12.6" customHeight="1"/>
-    <row r="382" ht="12.6" customHeight="1"/>
-    <row r="383" ht="12.6" customHeight="1"/>
-    <row r="384" ht="12.6" customHeight="1"/>
-    <row r="385" ht="12.6" customHeight="1"/>
-    <row r="386" ht="12.6" customHeight="1"/>
-    <row r="387" ht="12.6" customHeight="1"/>
-    <row r="388" ht="12.6" customHeight="1"/>
-    <row r="389" ht="12.6" customHeight="1"/>
-    <row r="390" ht="12.6" customHeight="1"/>
-    <row r="391" ht="12.6" customHeight="1"/>
-    <row r="392" ht="12.6" customHeight="1"/>
-    <row r="393" ht="12.6" customHeight="1"/>
-    <row r="394" ht="12.6" customHeight="1"/>
-    <row r="395" ht="12.6" customHeight="1"/>
-    <row r="396" ht="12.6" customHeight="1"/>
-    <row r="397" ht="12.6" customHeight="1"/>
-    <row r="398" ht="12.6" customHeight="1"/>
-    <row r="399" ht="12.6" customHeight="1"/>
-    <row r="400" ht="12.6" customHeight="1"/>
-    <row r="401" ht="12.6" customHeight="1"/>
-    <row r="402" ht="12.6" customHeight="1"/>
-    <row r="403" ht="12.6" customHeight="1"/>
-    <row r="404" ht="12.6" customHeight="1"/>
-    <row r="405" ht="12.6" customHeight="1"/>
-    <row r="406" ht="12.6" customHeight="1"/>
-    <row r="407" ht="12.6" customHeight="1"/>
-    <row r="408" ht="12.6" customHeight="1"/>
-    <row r="409" ht="12.6" customHeight="1"/>
-    <row r="410" ht="12.6" customHeight="1"/>
-    <row r="411" ht="12.6" customHeight="1"/>
-    <row r="412" ht="12.6" customHeight="1"/>
-    <row r="413" ht="12.6" customHeight="1"/>
-    <row r="414" ht="12.6" customHeight="1"/>
-    <row r="415" ht="12.6" customHeight="1"/>
-    <row r="416" ht="12.6" customHeight="1"/>
-    <row r="417" ht="12.6" customHeight="1"/>
-    <row r="418" ht="12.6" customHeight="1"/>
-    <row r="419" ht="12.6" customHeight="1"/>
-    <row r="420" ht="12.6" customHeight="1"/>
-    <row r="421" ht="12.6" customHeight="1"/>
-    <row r="422" ht="12.6" customHeight="1"/>
-    <row r="423" ht="12.6" customHeight="1"/>
-    <row r="424" ht="12.6" customHeight="1"/>
-    <row r="425" ht="12.6" customHeight="1"/>
-    <row r="426" ht="12.6" customHeight="1"/>
-    <row r="427" ht="12.6" customHeight="1"/>
-    <row r="428" ht="12.6" customHeight="1"/>
-    <row r="429" ht="12.6" customHeight="1"/>
-    <row r="430" ht="12.6" customHeight="1"/>
-    <row r="431" ht="12.6" customHeight="1"/>
-    <row r="432" ht="12.6" customHeight="1"/>
-    <row r="433" ht="12.6" customHeight="1"/>
-    <row r="434" ht="12.6" customHeight="1"/>
-    <row r="435" ht="12.6" customHeight="1"/>
-    <row r="436" ht="12.6" customHeight="1"/>
-    <row r="437" ht="12.6" customHeight="1"/>
-    <row r="438" ht="12.6" customHeight="1"/>
-    <row r="439" ht="12.6" customHeight="1"/>
-    <row r="440" ht="12.6" customHeight="1"/>
-    <row r="441" ht="12.6" customHeight="1"/>
-    <row r="442" ht="12.6" customHeight="1"/>
-    <row r="443" ht="12.6" customHeight="1"/>
-    <row r="444" ht="12.6" customHeight="1"/>
-    <row r="445" ht="12.6" customHeight="1"/>
-    <row r="446" ht="12.6" customHeight="1"/>
-    <row r="447" ht="12.6" customHeight="1"/>
-    <row r="448" ht="12.6" customHeight="1"/>
-    <row r="449" ht="12.6" customHeight="1"/>
-    <row r="450" ht="12.6" customHeight="1"/>
-    <row r="451" ht="12.6" customHeight="1"/>
-    <row r="452" ht="12.6" customHeight="1"/>
-    <row r="453" ht="12.6" customHeight="1"/>
-    <row r="454" ht="12.6" customHeight="1"/>
-    <row r="455" ht="12.6" customHeight="1"/>
-    <row r="456" ht="12.6" customHeight="1"/>
-    <row r="457" ht="12.6" customHeight="1"/>
-    <row r="458" ht="12.6" customHeight="1"/>
-    <row r="459" ht="12.6" customHeight="1"/>
-    <row r="460" ht="12.6" customHeight="1"/>
-    <row r="461" ht="12.6" customHeight="1"/>
-    <row r="462" ht="12.6" customHeight="1"/>
-    <row r="463" ht="12.6" customHeight="1"/>
-    <row r="464" ht="12.6" customHeight="1"/>
-    <row r="465" ht="12.6" customHeight="1"/>
-    <row r="466" ht="12.6" customHeight="1"/>
-    <row r="467" ht="12.6" customHeight="1"/>
-    <row r="468" ht="12.6" customHeight="1"/>
-    <row r="469" ht="12.6" customHeight="1"/>
-    <row r="470" ht="12.6" customHeight="1"/>
-    <row r="471" ht="12.6" customHeight="1"/>
-    <row r="472" ht="12.6" customHeight="1"/>
-    <row r="473" ht="12.6" customHeight="1"/>
-    <row r="474" ht="12.6" customHeight="1"/>
-    <row r="475" ht="12.6" customHeight="1"/>
-    <row r="476" ht="12.6" customHeight="1"/>
-    <row r="477" ht="12.6" customHeight="1"/>
-    <row r="478" ht="12.6" customHeight="1"/>
-    <row r="479" ht="12.6" customHeight="1"/>
-    <row r="480" ht="12.6" customHeight="1"/>
-    <row r="481" ht="12.6" customHeight="1"/>
-    <row r="482" ht="12.6" customHeight="1"/>
-    <row r="483" ht="12.6" customHeight="1"/>
-    <row r="484" ht="12.6" customHeight="1"/>
-    <row r="485" ht="12.6" customHeight="1"/>
-    <row r="486" ht="12.6" customHeight="1"/>
-    <row r="487" ht="12.6" customHeight="1"/>
-    <row r="488" ht="12.6" customHeight="1"/>
-    <row r="489" ht="12.6" customHeight="1"/>
-    <row r="490" ht="12.6" customHeight="1"/>
-    <row r="491" ht="12.6" customHeight="1"/>
-    <row r="492" ht="12.6" customHeight="1"/>
-    <row r="493" ht="12.6" customHeight="1"/>
-    <row r="494" ht="12.6" customHeight="1"/>
-    <row r="495" ht="12.6" customHeight="1"/>
-    <row r="496" ht="12.6" customHeight="1"/>
-    <row r="497" ht="12.6" customHeight="1"/>
-    <row r="498" ht="12.6" customHeight="1"/>
-    <row r="499" ht="12.6" customHeight="1"/>
-    <row r="500" ht="12.6" customHeight="1"/>
-    <row r="501" ht="12.6" customHeight="1"/>
-    <row r="502" ht="12.6" customHeight="1"/>
-    <row r="503" ht="12.6" customHeight="1"/>
-    <row r="504" ht="12.6" customHeight="1"/>
-    <row r="505" ht="12.6" customHeight="1"/>
-    <row r="506" ht="12.6" customHeight="1"/>
-    <row r="507" ht="12.6" customHeight="1"/>
-    <row r="508" ht="12.6" customHeight="1"/>
-    <row r="509" ht="12.6" customHeight="1"/>
-    <row r="510" ht="12.6" customHeight="1"/>
-    <row r="511" ht="12.6" customHeight="1"/>
-    <row r="512" ht="12.6" customHeight="1"/>
-    <row r="513" ht="12.6" customHeight="1"/>
-    <row r="514" ht="12.6" customHeight="1"/>
-    <row r="515" ht="12.6" customHeight="1"/>
-    <row r="516" ht="12.6" customHeight="1"/>
-    <row r="517" ht="12.6" customHeight="1"/>
-    <row r="518" ht="12.6" customHeight="1"/>
-    <row r="519" ht="12.6" customHeight="1"/>
-    <row r="520" ht="12.6" customHeight="1"/>
-    <row r="521" ht="12.6" customHeight="1"/>
-    <row r="522" ht="12.6" customHeight="1"/>
-    <row r="523" ht="12.6" customHeight="1"/>
-    <row r="524" ht="12.6" customHeight="1"/>
-    <row r="525" ht="12.6" customHeight="1"/>
-    <row r="526" ht="12.6" customHeight="1"/>
-    <row r="527" ht="12.6" customHeight="1"/>
-    <row r="528" ht="12.6" customHeight="1"/>
-    <row r="529" ht="12.6" customHeight="1"/>
-    <row r="530" ht="12.6" customHeight="1"/>
-    <row r="531" ht="12.6" customHeight="1"/>
-    <row r="532" ht="12.6" customHeight="1"/>
-    <row r="533" ht="12.6" customHeight="1"/>
-    <row r="534" ht="12.6" customHeight="1"/>
-    <row r="535" ht="12.6" customHeight="1"/>
-    <row r="536" ht="12.6" customHeight="1"/>
-    <row r="537" ht="12.6" customHeight="1"/>
-    <row r="538" ht="12.6" customHeight="1"/>
-    <row r="539" ht="12.6" customHeight="1"/>
-    <row r="540" ht="12.6" customHeight="1"/>
-    <row r="541" ht="12.6" customHeight="1"/>
-    <row r="542" ht="12.6" customHeight="1"/>
-    <row r="543" ht="12.6" customHeight="1"/>
-    <row r="544" ht="12.6" customHeight="1"/>
-    <row r="545" ht="12.6" customHeight="1"/>
-    <row r="546" ht="12.6" customHeight="1"/>
-    <row r="547" ht="12.6" customHeight="1"/>
-    <row r="548" ht="12.6" customHeight="1"/>
-    <row r="549" ht="12.6" customHeight="1"/>
-    <row r="550" ht="12.6" customHeight="1"/>
-    <row r="551" ht="12.6" customHeight="1"/>
-    <row r="552" ht="12.6" customHeight="1"/>
-    <row r="553" ht="12.6" customHeight="1"/>
-    <row r="554" ht="12.6" customHeight="1"/>
-    <row r="555" ht="12.6" customHeight="1"/>
-    <row r="556" ht="12.6" customHeight="1"/>
-    <row r="557" ht="12.6" customHeight="1"/>
-    <row r="558" ht="12.6" customHeight="1"/>
-    <row r="559" ht="12.6" customHeight="1"/>
-    <row r="560" ht="12.6" customHeight="1"/>
-    <row r="561" ht="12.6" customHeight="1"/>
-    <row r="562" ht="12.6" customHeight="1"/>
-    <row r="563" ht="12.6" customHeight="1"/>
-    <row r="564" ht="12.6" customHeight="1"/>
-    <row r="565" ht="12.6" customHeight="1"/>
-    <row r="566" ht="12.6" customHeight="1"/>
-    <row r="567" ht="12.6" customHeight="1"/>
-    <row r="568" ht="12.6" customHeight="1"/>
-    <row r="569" ht="12.6" customHeight="1"/>
-    <row r="570" ht="12.6" customHeight="1"/>
-    <row r="571" ht="12.6" customHeight="1"/>
-    <row r="572" ht="12.6" customHeight="1"/>
-    <row r="573" ht="12.6" customHeight="1"/>
-    <row r="574" ht="12.6" customHeight="1"/>
-    <row r="575" ht="12.6" customHeight="1"/>
-    <row r="576" ht="12.6" customHeight="1"/>
-    <row r="577" ht="12.6" customHeight="1"/>
-    <row r="578" ht="12.6" customHeight="1"/>
-    <row r="579" ht="12.6" customHeight="1"/>
-    <row r="580" ht="12.6" customHeight="1"/>
-    <row r="581" ht="12.6" customHeight="1"/>
-    <row r="582" ht="12.6" customHeight="1"/>
-    <row r="583" ht="12.6" customHeight="1"/>
-    <row r="584" ht="12.6" customHeight="1"/>
-    <row r="585" ht="12.6" customHeight="1"/>
-    <row r="586" ht="12.6" customHeight="1"/>
-    <row r="587" ht="12.6" customHeight="1"/>
-    <row r="588" ht="12.6" customHeight="1"/>
-    <row r="589" ht="12.6" customHeight="1"/>
-    <row r="590" ht="12.6" customHeight="1"/>
-    <row r="591" ht="12.6" customHeight="1"/>
-    <row r="592" ht="12.6" customHeight="1"/>
-    <row r="593" ht="12.6" customHeight="1"/>
-    <row r="594" ht="12.6" customHeight="1"/>
-    <row r="595" ht="12.6" customHeight="1"/>
-    <row r="596" ht="12.6" customHeight="1"/>
-    <row r="597" ht="12.6" customHeight="1"/>
-    <row r="598" ht="12.6" customHeight="1"/>
-    <row r="599" ht="12.6" customHeight="1"/>
-    <row r="600" ht="12.6" customHeight="1"/>
-    <row r="601" ht="12.6" customHeight="1"/>
-    <row r="602" ht="12.6" customHeight="1"/>
-    <row r="603" ht="12.6" customHeight="1"/>
-    <row r="604" ht="12.6" customHeight="1"/>
-    <row r="605" ht="12.6" customHeight="1"/>
-    <row r="606" ht="12.6" customHeight="1"/>
-    <row r="607" ht="12.6" customHeight="1"/>
-    <row r="608" ht="12.6" customHeight="1"/>
-    <row r="609" ht="12.6" customHeight="1"/>
-    <row r="610" ht="12.6" customHeight="1"/>
-    <row r="611" ht="12.6" customHeight="1"/>
-    <row r="612" ht="12.6" customHeight="1"/>
-    <row r="613" ht="12.6" customHeight="1"/>
-    <row r="614" ht="12.6" customHeight="1"/>
-    <row r="615" ht="12.6" customHeight="1"/>
-    <row r="616" ht="12.6" customHeight="1"/>
-    <row r="617" ht="12.6" customHeight="1"/>
-    <row r="618" ht="12.6" customHeight="1"/>
-    <row r="619" ht="12.6" customHeight="1"/>
-    <row r="620" ht="12.6" customHeight="1"/>
-    <row r="621" ht="12.6" customHeight="1"/>
-    <row r="622" ht="12.6" customHeight="1"/>
-    <row r="623" ht="12.6" customHeight="1"/>
-    <row r="624" ht="12.6" customHeight="1"/>
-    <row r="625" ht="12.6" customHeight="1"/>
-    <row r="626" ht="12.6" customHeight="1"/>
-    <row r="627" ht="12.6" customHeight="1"/>
-    <row r="628" ht="12.6" customHeight="1"/>
-    <row r="629" ht="12.6" customHeight="1"/>
-    <row r="630" ht="12.6" customHeight="1"/>
-    <row r="631" ht="12.6" customHeight="1"/>
-    <row r="632" ht="12.6" customHeight="1"/>
-    <row r="633" ht="12.6" customHeight="1"/>
-    <row r="634" ht="12.6" customHeight="1"/>
-    <row r="635" ht="12.6" customHeight="1"/>
-    <row r="636" ht="12.6" customHeight="1"/>
-    <row r="637" ht="12.6" customHeight="1"/>
-    <row r="638" ht="12.6" customHeight="1"/>
-    <row r="639" ht="12.6" customHeight="1"/>
-    <row r="640" ht="12.6" customHeight="1"/>
-    <row r="641" ht="12.6" customHeight="1"/>
-    <row r="642" ht="12.6" customHeight="1"/>
-    <row r="643" ht="12.6" customHeight="1"/>
-    <row r="644" ht="12.6" customHeight="1"/>
-    <row r="645" ht="12.6" customHeight="1"/>
-    <row r="646" ht="12.6" customHeight="1"/>
-    <row r="647" ht="12.6" customHeight="1"/>
-    <row r="648" ht="12.6" customHeight="1"/>
-    <row r="649" ht="12.6" customHeight="1"/>
-    <row r="650" ht="12.6" customHeight="1"/>
-    <row r="651" ht="12.6" customHeight="1"/>
-    <row r="652" ht="12.6" customHeight="1"/>
-    <row r="653" ht="12.6" customHeight="1"/>
-    <row r="654" ht="12.6" customHeight="1"/>
-    <row r="655" ht="12.6" customHeight="1"/>
-    <row r="656" ht="12.6" customHeight="1"/>
-    <row r="657" ht="12.6" customHeight="1"/>
-    <row r="658" ht="12.6" customHeight="1"/>
-    <row r="659" ht="12.6" customHeight="1"/>
-    <row r="660" ht="12.6" customHeight="1"/>
-    <row r="661" ht="12.6" customHeight="1"/>
-    <row r="662" ht="12.6" customHeight="1"/>
-    <row r="663" ht="12.6" customHeight="1"/>
-    <row r="664" ht="12.6" customHeight="1"/>
-    <row r="665" ht="12.6" customHeight="1"/>
-    <row r="666" ht="12.6" customHeight="1"/>
-    <row r="667" ht="12.6" customHeight="1"/>
-    <row r="668" ht="12.6" customHeight="1"/>
-    <row r="669" ht="12.6" customHeight="1"/>
-    <row r="670" ht="12.6" customHeight="1"/>
-    <row r="671" ht="12.6" customHeight="1"/>
-    <row r="672" ht="12.6" customHeight="1"/>
-    <row r="673" ht="12.6" customHeight="1"/>
-    <row r="674" ht="12.6" customHeight="1"/>
-    <row r="675" ht="12.6" customHeight="1"/>
-    <row r="676" ht="12.6" customHeight="1"/>
-    <row r="677" ht="12.6" customHeight="1"/>
-    <row r="678" ht="12.6" customHeight="1"/>
-    <row r="679" ht="12.6" customHeight="1"/>
-    <row r="680" ht="12.6" customHeight="1"/>
-    <row r="681" ht="12.6" customHeight="1"/>
-    <row r="682" ht="12.6" customHeight="1"/>
-    <row r="683" ht="12.6" customHeight="1"/>
-    <row r="684" ht="12.6" customHeight="1"/>
-    <row r="685" ht="12.6" customHeight="1"/>
-    <row r="686" ht="12.6" customHeight="1"/>
-    <row r="687" ht="12.6" customHeight="1"/>
-    <row r="688" ht="12.6" customHeight="1"/>
-    <row r="689" ht="12.6" customHeight="1"/>
-    <row r="690" ht="12.6" customHeight="1"/>
-    <row r="691" ht="12.6" customHeight="1"/>
-    <row r="692" ht="12.6" customHeight="1"/>
-    <row r="693" ht="12.6" customHeight="1"/>
-    <row r="694" ht="12.6" customHeight="1"/>
-    <row r="695" ht="12.6" customHeight="1"/>
-    <row r="696" ht="12.6" customHeight="1"/>
-    <row r="697" ht="12.6" customHeight="1"/>
-    <row r="698" ht="12.6" customHeight="1"/>
-    <row r="699" ht="12.6" customHeight="1"/>
-    <row r="700" ht="12.6" customHeight="1"/>
-    <row r="701" ht="12.6" customHeight="1"/>
-    <row r="702" ht="12.6" customHeight="1"/>
-    <row r="703" ht="12.6" customHeight="1"/>
-    <row r="704" ht="12.6" customHeight="1"/>
-    <row r="705" ht="12.6" customHeight="1"/>
-    <row r="706" ht="12.6" customHeight="1"/>
-    <row r="707" ht="12.6" customHeight="1"/>
-    <row r="708" ht="12.6" customHeight="1"/>
-    <row r="709" ht="12.6" customHeight="1"/>
-    <row r="710" ht="12.6" customHeight="1"/>
-    <row r="711" ht="12.6" customHeight="1"/>
-    <row r="712" ht="12.6" customHeight="1"/>
-    <row r="713" ht="12.6" customHeight="1"/>
-    <row r="714" ht="12.6" customHeight="1"/>
-    <row r="715" ht="12.6" customHeight="1"/>
-    <row r="716" ht="12.6" customHeight="1"/>
-    <row r="717" ht="12.6" customHeight="1"/>
-    <row r="718" ht="12.6" customHeight="1"/>
-    <row r="719" ht="12.6" customHeight="1"/>
-    <row r="720" ht="12.6" customHeight="1"/>
-    <row r="721" ht="12.6" customHeight="1"/>
-    <row r="722" ht="12.6" customHeight="1"/>
-    <row r="723" ht="12.6" customHeight="1"/>
-    <row r="724" ht="12.6" customHeight="1"/>
-    <row r="725" ht="12.6" customHeight="1"/>
-    <row r="726" ht="12.6" customHeight="1"/>
-    <row r="727" ht="12.6" customHeight="1"/>
-    <row r="728" ht="12.6" customHeight="1"/>
-    <row r="729" ht="12.6" customHeight="1"/>
-    <row r="730" ht="12.6" customHeight="1"/>
-    <row r="731" ht="12.6" customHeight="1"/>
-    <row r="732" ht="12.6" customHeight="1"/>
-    <row r="733" ht="12.6" customHeight="1"/>
-    <row r="734" ht="12.6" customHeight="1"/>
-    <row r="735" ht="12.6" customHeight="1"/>
-    <row r="736" ht="12.6" customHeight="1"/>
-    <row r="737" ht="12.6" customHeight="1"/>
-    <row r="738" ht="12.6" customHeight="1"/>
-    <row r="739" ht="12.6" customHeight="1"/>
-    <row r="740" ht="12.6" customHeight="1"/>
-    <row r="741" ht="12.6" customHeight="1"/>
-    <row r="742" ht="12.6" customHeight="1"/>
-    <row r="743" ht="12.6" customHeight="1"/>
-    <row r="744" ht="12.6" customHeight="1"/>
-    <row r="745" ht="12.6" customHeight="1"/>
-    <row r="746" ht="12.6" customHeight="1"/>
-    <row r="747" ht="12.6" customHeight="1"/>
-    <row r="748" ht="12.6" customHeight="1"/>
-    <row r="749" ht="12.6" customHeight="1"/>
-    <row r="750" ht="12.6" customHeight="1"/>
-    <row r="751" ht="12.6" customHeight="1"/>
-    <row r="752" ht="12.6" customHeight="1"/>
-    <row r="753" ht="12.6" customHeight="1"/>
-    <row r="754" ht="12.6" customHeight="1"/>
-    <row r="755" ht="12.6" customHeight="1"/>
-    <row r="756" ht="12.6" customHeight="1"/>
-    <row r="757" ht="12.6" customHeight="1"/>
-    <row r="758" ht="12.6" customHeight="1"/>
-    <row r="759" ht="12.6" customHeight="1"/>
-    <row r="760" ht="12.6" customHeight="1"/>
-    <row r="761" ht="12.6" customHeight="1"/>
-    <row r="762" ht="12.6" customHeight="1"/>
-    <row r="763" ht="12.6" customHeight="1"/>
-    <row r="764" ht="12.6" customHeight="1"/>
-    <row r="765" ht="12.6" customHeight="1"/>
-    <row r="766" ht="12.6" customHeight="1"/>
-    <row r="767" ht="12.6" customHeight="1"/>
-    <row r="768" ht="12.6" customHeight="1"/>
-    <row r="769" ht="12.6" customHeight="1"/>
-    <row r="770" ht="12.6" customHeight="1"/>
-    <row r="771" ht="12.6" customHeight="1"/>
-    <row r="772" ht="12.6" customHeight="1"/>
-    <row r="773" ht="12.6" customHeight="1"/>
-    <row r="774" ht="12.6" customHeight="1"/>
-    <row r="775" ht="12.6" customHeight="1"/>
-    <row r="776" ht="12.6" customHeight="1"/>
-    <row r="777" ht="12.6" customHeight="1"/>
-    <row r="778" ht="12.6" customHeight="1"/>
-    <row r="779" ht="12.6" customHeight="1"/>
-    <row r="780" ht="12.6" customHeight="1"/>
-    <row r="781" ht="12.6" customHeight="1"/>
-    <row r="782" ht="12.6" customHeight="1"/>
-    <row r="783" ht="12.6" customHeight="1"/>
-    <row r="784" ht="12.6" customHeight="1"/>
-    <row r="785" ht="12.6" customHeight="1"/>
-    <row r="786" ht="12.6" customHeight="1"/>
-    <row r="787" ht="12.6" customHeight="1"/>
-    <row r="788" ht="12.6" customHeight="1"/>
-    <row r="789" ht="12.6" customHeight="1"/>
-    <row r="790" ht="12.6" customHeight="1"/>
-    <row r="791" ht="12.6" customHeight="1"/>
-    <row r="792" ht="12.6" customHeight="1"/>
-    <row r="793" ht="12.6" customHeight="1"/>
-    <row r="794" ht="12.6" customHeight="1"/>
-    <row r="795" ht="12.6" customHeight="1"/>
-    <row r="796" ht="12.6" customHeight="1"/>
-    <row r="797" ht="12.6" customHeight="1"/>
-    <row r="798" ht="12.6" customHeight="1"/>
-    <row r="799" ht="12.6" customHeight="1"/>
-    <row r="800" ht="12.6" customHeight="1"/>
-    <row r="801" ht="12.6" customHeight="1"/>
-    <row r="802" ht="12.6" customHeight="1"/>
-    <row r="803" ht="12.6" customHeight="1"/>
-    <row r="804" ht="12.6" customHeight="1"/>
-    <row r="805" ht="12.6" customHeight="1"/>
-    <row r="806" ht="12.6" customHeight="1"/>
-    <row r="807" ht="12.6" customHeight="1"/>
-    <row r="808" ht="12.6" customHeight="1"/>
-    <row r="809" ht="12.6" customHeight="1"/>
-    <row r="810" ht="12.6" customHeight="1"/>
-    <row r="811" ht="12.6" customHeight="1"/>
-    <row r="812" ht="12.6" customHeight="1"/>
-    <row r="813" ht="12.6" customHeight="1"/>
-    <row r="814" ht="12.6" customHeight="1"/>
-    <row r="815" ht="12.6" customHeight="1"/>
-    <row r="816" ht="12.6" customHeight="1"/>
-    <row r="817" ht="12.6" customHeight="1"/>
-    <row r="818" ht="12.6" customHeight="1"/>
-    <row r="819" ht="12.6" customHeight="1"/>
-    <row r="820" ht="12.6" customHeight="1"/>
-    <row r="821" ht="12.6" customHeight="1"/>
-    <row r="822" ht="12.6" customHeight="1"/>
-    <row r="823" ht="12.6" customHeight="1"/>
-    <row r="824" ht="12.6" customHeight="1"/>
-    <row r="825" ht="12.6" customHeight="1"/>
-    <row r="826" ht="12.6" customHeight="1"/>
-    <row r="827" ht="12.6" customHeight="1"/>
-    <row r="828" ht="12.6" customHeight="1"/>
-    <row r="829" ht="12.6" customHeight="1"/>
-    <row r="830" ht="12.6" customHeight="1"/>
-    <row r="831" ht="12.6" customHeight="1"/>
-    <row r="832" ht="12.6" customHeight="1"/>
-    <row r="833" ht="12.6" customHeight="1"/>
-    <row r="834" ht="12.6" customHeight="1"/>
-    <row r="835" ht="12.6" customHeight="1"/>
-    <row r="836" ht="12.6" customHeight="1"/>
-    <row r="837" ht="12.6" customHeight="1"/>
-    <row r="838" ht="12.6" customHeight="1"/>
-    <row r="839" ht="12.6" customHeight="1"/>
-    <row r="840" ht="12.6" customHeight="1"/>
-    <row r="841" ht="12.6" customHeight="1"/>
-    <row r="842" ht="12.6" customHeight="1"/>
-    <row r="843" ht="12.6" customHeight="1"/>
-    <row r="844" ht="12.6" customHeight="1"/>
-    <row r="845" ht="12.6" customHeight="1"/>
-    <row r="846" ht="12.6" customHeight="1"/>
-    <row r="847" ht="12.6" customHeight="1"/>
-    <row r="848" ht="12.6" customHeight="1"/>
-    <row r="849" ht="12.6" customHeight="1"/>
-    <row r="850" ht="12.6" customHeight="1"/>
-    <row r="851" ht="12.6" customHeight="1"/>
-    <row r="852" ht="12.6" customHeight="1"/>
-    <row r="853" ht="12.6" customHeight="1"/>
-    <row r="854" ht="12.6" customHeight="1"/>
-    <row r="855" ht="12.6" customHeight="1"/>
-    <row r="856" ht="12.6" customHeight="1"/>
-    <row r="857" ht="12.6" customHeight="1"/>
-    <row r="858" ht="12.6" customHeight="1"/>
-    <row r="859" ht="12.6" customHeight="1"/>
-    <row r="860" ht="12.6" customHeight="1"/>
-    <row r="861" ht="12.6" customHeight="1"/>
-    <row r="862" ht="12.6" customHeight="1"/>
-    <row r="863" ht="12.6" customHeight="1"/>
-    <row r="864" ht="12.6" customHeight="1"/>
-    <row r="865" ht="12.6" customHeight="1"/>
-    <row r="866" ht="12.6" customHeight="1"/>
-    <row r="867" ht="12.6" customHeight="1"/>
-    <row r="868" ht="12.6" customHeight="1"/>
-    <row r="869" ht="12.6" customHeight="1"/>
-    <row r="870" ht="12.6" customHeight="1"/>
-    <row r="871" ht="12.6" customHeight="1"/>
-    <row r="872" ht="12.6" customHeight="1"/>
-    <row r="873" ht="12.6" customHeight="1"/>
-    <row r="874" ht="12.6" customHeight="1"/>
-    <row r="875" ht="12.6" customHeight="1"/>
-    <row r="876" ht="12.6" customHeight="1"/>
-    <row r="877" ht="12.6" customHeight="1"/>
-    <row r="878" ht="12.6" customHeight="1"/>
-    <row r="879" ht="12.6" customHeight="1"/>
-    <row r="880" ht="12.6" customHeight="1"/>
-    <row r="881" ht="12.6" customHeight="1"/>
-    <row r="882" ht="12.6" customHeight="1"/>
-    <row r="883" ht="12.6" customHeight="1"/>
-    <row r="884" ht="12.6" customHeight="1"/>
-    <row r="885" ht="12.6" customHeight="1"/>
-    <row r="886" ht="12.6" customHeight="1"/>
-    <row r="887" ht="12.6" customHeight="1"/>
-    <row r="888" ht="12.6" customHeight="1"/>
-    <row r="889" ht="12.6" customHeight="1"/>
-    <row r="890" ht="12.6" customHeight="1"/>
-    <row r="891" ht="12.6" customHeight="1"/>
-    <row r="892" ht="12.6" customHeight="1"/>
-    <row r="893" ht="12.6" customHeight="1"/>
-    <row r="894" ht="12.6" customHeight="1"/>
-    <row r="895" ht="12.6" customHeight="1"/>
-    <row r="896" ht="12.6" customHeight="1"/>
-    <row r="897" ht="12.6" customHeight="1"/>
-    <row r="898" ht="12.6" customHeight="1"/>
-    <row r="899" ht="12.6" customHeight="1"/>
-    <row r="900" ht="12.6" customHeight="1"/>
-    <row r="901" ht="12.6" customHeight="1"/>
-    <row r="902" ht="12.6" customHeight="1"/>
-    <row r="903" ht="12.6" customHeight="1"/>
-    <row r="904" ht="12.6" customHeight="1"/>
-    <row r="905" ht="12.6" customHeight="1"/>
-    <row r="906" ht="12.6" customHeight="1"/>
-    <row r="907" ht="12.6" customHeight="1"/>
-    <row r="908" ht="12.6" customHeight="1"/>
-    <row r="909" ht="12.6" customHeight="1"/>
-    <row r="910" ht="12.6" customHeight="1"/>
-    <row r="911" ht="12.6" customHeight="1"/>
-    <row r="912" ht="12.6" customHeight="1"/>
-    <row r="913" ht="12.6" customHeight="1"/>
-    <row r="914" ht="12.6" customHeight="1"/>
-    <row r="915" ht="12.6" customHeight="1"/>
-    <row r="916" ht="12.6" customHeight="1"/>
-    <row r="917" ht="12.6" customHeight="1"/>
-    <row r="918" ht="12.6" customHeight="1"/>
-    <row r="919" ht="12.6" customHeight="1"/>
-    <row r="920" ht="12.6" customHeight="1"/>
-    <row r="921" ht="12.6" customHeight="1"/>
-    <row r="922" ht="12.6" customHeight="1"/>
-    <row r="923" ht="12.6" customHeight="1"/>
-    <row r="924" ht="12.6" customHeight="1"/>
-    <row r="925" ht="12.6" customHeight="1"/>
-    <row r="926" ht="12.6" customHeight="1"/>
-    <row r="927" ht="12.6" customHeight="1"/>
-    <row r="928" ht="12.6" customHeight="1"/>
-    <row r="929" ht="12.6" customHeight="1"/>
-    <row r="930" ht="12.6" customHeight="1"/>
-    <row r="931" ht="12.6" customHeight="1"/>
-    <row r="932" ht="12.6" customHeight="1"/>
-    <row r="933" ht="12.6" customHeight="1"/>
-    <row r="934" ht="12.6" customHeight="1"/>
-    <row r="935" ht="12.6" customHeight="1"/>
-    <row r="936" ht="12.6" customHeight="1"/>
-    <row r="937" ht="12.6" customHeight="1"/>
-    <row r="938" ht="12.6" customHeight="1"/>
-    <row r="939" ht="12.6" customHeight="1"/>
-    <row r="940" ht="12.6" customHeight="1"/>
-    <row r="941" ht="12.6" customHeight="1"/>
-    <row r="942" ht="12.6" customHeight="1"/>
-    <row r="943" ht="12.6" customHeight="1"/>
-    <row r="944" ht="12.6" customHeight="1"/>
-    <row r="945" ht="12.6" customHeight="1"/>
-    <row r="946" ht="12.6" customHeight="1"/>
-    <row r="947" ht="12.6" customHeight="1"/>
-    <row r="948" ht="12.6" customHeight="1"/>
-    <row r="949" ht="12.6" customHeight="1"/>
-    <row r="950" ht="12.6" customHeight="1"/>
-    <row r="951" ht="12.6" customHeight="1"/>
-    <row r="952" ht="12.6" customHeight="1"/>
-    <row r="953" ht="12.6" customHeight="1"/>
-    <row r="954" ht="12.6" customHeight="1"/>
-    <row r="955" ht="12.6" customHeight="1"/>
-    <row r="956" ht="12.6" customHeight="1"/>
-    <row r="957" ht="12.6" customHeight="1"/>
-    <row r="958" ht="12.6" customHeight="1"/>
-    <row r="959" ht="12.6" customHeight="1"/>
-    <row r="960" ht="12.6" customHeight="1"/>
-    <row r="961" ht="12.6" customHeight="1"/>
-    <row r="962" ht="12.6" customHeight="1"/>
-    <row r="963" ht="12.6" customHeight="1"/>
-    <row r="964" ht="12.6" customHeight="1"/>
-    <row r="965" ht="12.6" customHeight="1"/>
-    <row r="966" ht="12.6" customHeight="1"/>
-    <row r="967" ht="12.6" customHeight="1"/>
-    <row r="968" ht="12.6" customHeight="1"/>
-    <row r="969" ht="12.6" customHeight="1"/>
-    <row r="970" ht="12.6" customHeight="1"/>
-    <row r="971" ht="12.6" customHeight="1"/>
-    <row r="972" ht="12.6" customHeight="1"/>
-    <row r="973" ht="12.6" customHeight="1"/>
-    <row r="974" ht="12.6" customHeight="1"/>
-    <row r="975" ht="12.6" customHeight="1"/>
-    <row r="976" ht="12.6" customHeight="1"/>
-    <row r="977" ht="12.6" customHeight="1"/>
-    <row r="978" ht="12.6" customHeight="1"/>
-    <row r="979" ht="12.6" customHeight="1"/>
-    <row r="980" ht="12.6" customHeight="1"/>
-    <row r="981" ht="12.6" customHeight="1"/>
-    <row r="982" ht="12.6" customHeight="1"/>
-    <row r="983" ht="12.6" customHeight="1"/>
-    <row r="984" ht="12.6" customHeight="1"/>
-    <row r="985" ht="12.6" customHeight="1"/>
-    <row r="986" ht="12.6" customHeight="1"/>
-    <row r="987" ht="12.6" customHeight="1"/>
-    <row r="988" ht="12.6" customHeight="1"/>
-    <row r="989" ht="12.6" customHeight="1"/>
-    <row r="990" ht="12.6" customHeight="1"/>
-    <row r="991" ht="12.6" customHeight="1"/>
-    <row r="992" ht="12.6" customHeight="1"/>
-    <row r="993" ht="12.6" customHeight="1"/>
+    <row r="139" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="140" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="141" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="142" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="143" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="144" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="145" ht="12.65" customHeight="1"/>
+    <row r="146" ht="12.65" customHeight="1"/>
+    <row r="147" ht="12.65" customHeight="1"/>
+    <row r="148" ht="12.65" customHeight="1"/>
+    <row r="149" ht="12.65" customHeight="1"/>
+    <row r="150" ht="12.65" customHeight="1"/>
+    <row r="151" ht="12.65" customHeight="1"/>
+    <row r="152" ht="12.65" customHeight="1"/>
+    <row r="153" ht="12.65" customHeight="1"/>
+    <row r="154" ht="12.65" customHeight="1"/>
+    <row r="155" ht="12.65" customHeight="1"/>
+    <row r="156" ht="12.65" customHeight="1"/>
+    <row r="157" ht="12.65" customHeight="1"/>
+    <row r="158" ht="12.65" customHeight="1"/>
+    <row r="159" ht="12.65" customHeight="1"/>
+    <row r="160" ht="12.65" customHeight="1"/>
+    <row r="161" ht="12.65" customHeight="1"/>
+    <row r="162" ht="12.65" customHeight="1"/>
+    <row r="163" ht="12.65" customHeight="1"/>
+    <row r="164" ht="12.65" customHeight="1"/>
+    <row r="165" ht="12.65" customHeight="1"/>
+    <row r="166" ht="12.65" customHeight="1"/>
+    <row r="167" ht="12.65" customHeight="1"/>
+    <row r="168" ht="12.65" customHeight="1"/>
+    <row r="169" ht="12.65" customHeight="1"/>
+    <row r="170" ht="12.65" customHeight="1"/>
+    <row r="171" ht="12.65" customHeight="1"/>
+    <row r="172" ht="12.65" customHeight="1"/>
+    <row r="173" ht="12.65" customHeight="1"/>
+    <row r="174" ht="12.65" customHeight="1"/>
+    <row r="175" ht="12.65" customHeight="1"/>
+    <row r="176" ht="12.65" customHeight="1"/>
+    <row r="177" ht="12.65" customHeight="1"/>
+    <row r="178" ht="12.65" customHeight="1"/>
+    <row r="179" ht="12.65" customHeight="1"/>
+    <row r="180" ht="12.65" customHeight="1"/>
+    <row r="181" ht="12.65" customHeight="1"/>
+    <row r="182" ht="12.65" customHeight="1"/>
+    <row r="183" ht="12.65" customHeight="1"/>
+    <row r="184" ht="12.65" customHeight="1"/>
+    <row r="185" ht="12.65" customHeight="1"/>
+    <row r="186" ht="12.65" customHeight="1"/>
+    <row r="187" ht="12.65" customHeight="1"/>
+    <row r="188" ht="12.65" customHeight="1"/>
+    <row r="189" ht="12.65" customHeight="1"/>
+    <row r="190" ht="12.65" customHeight="1"/>
+    <row r="191" ht="12.65" customHeight="1"/>
+    <row r="192" ht="12.65" customHeight="1"/>
+    <row r="193" ht="12.65" customHeight="1"/>
+    <row r="194" ht="12.65" customHeight="1"/>
+    <row r="195" ht="12.65" customHeight="1"/>
+    <row r="196" ht="12.65" customHeight="1"/>
+    <row r="197" ht="12.65" customHeight="1"/>
+    <row r="198" ht="12.65" customHeight="1"/>
+    <row r="199" ht="12.65" customHeight="1"/>
+    <row r="200" ht="12.65" customHeight="1"/>
+    <row r="201" ht="12.65" customHeight="1"/>
+    <row r="202" ht="12.65" customHeight="1"/>
+    <row r="203" ht="12.65" customHeight="1"/>
+    <row r="204" ht="12.65" customHeight="1"/>
+    <row r="205" ht="12.65" customHeight="1"/>
+    <row r="206" ht="12.65" customHeight="1"/>
+    <row r="207" ht="12.65" customHeight="1"/>
+    <row r="208" ht="12.65" customHeight="1"/>
+    <row r="209" ht="12.65" customHeight="1"/>
+    <row r="210" ht="12.65" customHeight="1"/>
+    <row r="211" ht="12.65" customHeight="1"/>
+    <row r="212" ht="12.65" customHeight="1"/>
+    <row r="213" ht="12.65" customHeight="1"/>
+    <row r="214" ht="12.65" customHeight="1"/>
+    <row r="215" ht="12.65" customHeight="1"/>
+    <row r="216" ht="12.65" customHeight="1"/>
+    <row r="217" ht="12.65" customHeight="1"/>
+    <row r="218" ht="12.65" customHeight="1"/>
+    <row r="219" ht="12.65" customHeight="1"/>
+    <row r="220" ht="12.65" customHeight="1"/>
+    <row r="221" ht="12.65" customHeight="1"/>
+    <row r="222" ht="12.65" customHeight="1"/>
+    <row r="223" ht="12.65" customHeight="1"/>
+    <row r="224" ht="12.65" customHeight="1"/>
+    <row r="225" ht="12.65" customHeight="1"/>
+    <row r="226" ht="12.65" customHeight="1"/>
+    <row r="227" ht="12.65" customHeight="1"/>
+    <row r="228" ht="12.65" customHeight="1"/>
+    <row r="229" ht="12.65" customHeight="1"/>
+    <row r="230" ht="12.65" customHeight="1"/>
+    <row r="231" ht="12.65" customHeight="1"/>
+    <row r="232" ht="12.65" customHeight="1"/>
+    <row r="233" ht="12.65" customHeight="1"/>
+    <row r="234" ht="12.65" customHeight="1"/>
+    <row r="235" ht="12.65" customHeight="1"/>
+    <row r="236" ht="12.65" customHeight="1"/>
+    <row r="237" ht="12.65" customHeight="1"/>
+    <row r="238" ht="12.65" customHeight="1"/>
+    <row r="239" ht="12.65" customHeight="1"/>
+    <row r="240" ht="12.65" customHeight="1"/>
+    <row r="241" ht="12.65" customHeight="1"/>
+    <row r="242" ht="12.65" customHeight="1"/>
+    <row r="243" ht="12.65" customHeight="1"/>
+    <row r="244" ht="12.65" customHeight="1"/>
+    <row r="245" ht="12.65" customHeight="1"/>
+    <row r="246" ht="12.65" customHeight="1"/>
+    <row r="247" ht="12.65" customHeight="1"/>
+    <row r="248" ht="12.65" customHeight="1"/>
+    <row r="249" ht="12.65" customHeight="1"/>
+    <row r="250" ht="12.65" customHeight="1"/>
+    <row r="251" ht="12.65" customHeight="1"/>
+    <row r="252" ht="12.65" customHeight="1"/>
+    <row r="253" ht="12.65" customHeight="1"/>
+    <row r="254" ht="12.65" customHeight="1"/>
+    <row r="255" ht="12.65" customHeight="1"/>
+    <row r="256" ht="12.65" customHeight="1"/>
+    <row r="257" ht="12.65" customHeight="1"/>
+    <row r="258" ht="12.65" customHeight="1"/>
+    <row r="259" ht="12.65" customHeight="1"/>
+    <row r="260" ht="12.65" customHeight="1"/>
+    <row r="261" ht="12.65" customHeight="1"/>
+    <row r="262" ht="12.65" customHeight="1"/>
+    <row r="263" ht="12.65" customHeight="1"/>
+    <row r="264" ht="12.65" customHeight="1"/>
+    <row r="265" ht="12.65" customHeight="1"/>
+    <row r="266" ht="12.65" customHeight="1"/>
+    <row r="267" ht="12.65" customHeight="1"/>
+    <row r="268" ht="12.65" customHeight="1"/>
+    <row r="269" ht="12.65" customHeight="1"/>
+    <row r="270" ht="12.65" customHeight="1"/>
+    <row r="271" ht="12.65" customHeight="1"/>
+    <row r="272" ht="12.65" customHeight="1"/>
+    <row r="273" ht="12.65" customHeight="1"/>
+    <row r="274" ht="12.65" customHeight="1"/>
+    <row r="275" ht="12.65" customHeight="1"/>
+    <row r="276" ht="12.65" customHeight="1"/>
+    <row r="277" ht="12.65" customHeight="1"/>
+    <row r="278" ht="12.65" customHeight="1"/>
+    <row r="279" ht="12.65" customHeight="1"/>
+    <row r="280" ht="12.65" customHeight="1"/>
+    <row r="281" ht="12.65" customHeight="1"/>
+    <row r="282" ht="12.65" customHeight="1"/>
+    <row r="283" ht="12.65" customHeight="1"/>
+    <row r="284" ht="12.65" customHeight="1"/>
+    <row r="285" ht="12.65" customHeight="1"/>
+    <row r="286" ht="12.65" customHeight="1"/>
+    <row r="287" ht="12.65" customHeight="1"/>
+    <row r="288" ht="12.65" customHeight="1"/>
+    <row r="289" ht="12.65" customHeight="1"/>
+    <row r="290" ht="12.65" customHeight="1"/>
+    <row r="291" ht="12.65" customHeight="1"/>
+    <row r="292" ht="12.65" customHeight="1"/>
+    <row r="293" ht="12.65" customHeight="1"/>
+    <row r="294" ht="12.65" customHeight="1"/>
+    <row r="295" ht="12.65" customHeight="1"/>
+    <row r="296" ht="12.65" customHeight="1"/>
+    <row r="297" ht="12.65" customHeight="1"/>
+    <row r="298" ht="12.65" customHeight="1"/>
+    <row r="299" ht="12.65" customHeight="1"/>
+    <row r="300" ht="12.65" customHeight="1"/>
+    <row r="301" ht="12.65" customHeight="1"/>
+    <row r="302" ht="12.65" customHeight="1"/>
+    <row r="303" ht="12.65" customHeight="1"/>
+    <row r="304" ht="12.65" customHeight="1"/>
+    <row r="305" ht="12.65" customHeight="1"/>
+    <row r="306" ht="12.65" customHeight="1"/>
+    <row r="307" ht="12.65" customHeight="1"/>
+    <row r="308" ht="12.65" customHeight="1"/>
+    <row r="309" ht="12.65" customHeight="1"/>
+    <row r="310" ht="12.65" customHeight="1"/>
+    <row r="311" ht="12.65" customHeight="1"/>
+    <row r="312" ht="12.65" customHeight="1"/>
+    <row r="313" ht="12.65" customHeight="1"/>
+    <row r="314" ht="12.65" customHeight="1"/>
+    <row r="315" ht="12.65" customHeight="1"/>
+    <row r="316" ht="12.65" customHeight="1"/>
+    <row r="317" ht="12.65" customHeight="1"/>
+    <row r="318" ht="12.65" customHeight="1"/>
+    <row r="319" ht="12.65" customHeight="1"/>
+    <row r="320" ht="12.65" customHeight="1"/>
+    <row r="321" ht="12.65" customHeight="1"/>
+    <row r="322" ht="12.65" customHeight="1"/>
+    <row r="323" ht="12.65" customHeight="1"/>
+    <row r="324" ht="12.65" customHeight="1"/>
+    <row r="325" ht="12.65" customHeight="1"/>
+    <row r="326" ht="12.65" customHeight="1"/>
+    <row r="327" ht="12.65" customHeight="1"/>
+    <row r="328" ht="12.65" customHeight="1"/>
+    <row r="329" ht="12.65" customHeight="1"/>
+    <row r="330" ht="12.65" customHeight="1"/>
+    <row r="331" ht="12.65" customHeight="1"/>
+    <row r="332" ht="12.65" customHeight="1"/>
+    <row r="333" ht="12.65" customHeight="1"/>
+    <row r="334" ht="12.65" customHeight="1"/>
+    <row r="335" ht="12.65" customHeight="1"/>
+    <row r="336" ht="12.65" customHeight="1"/>
+    <row r="337" ht="12.65" customHeight="1"/>
+    <row r="338" ht="12.65" customHeight="1"/>
+    <row r="339" ht="12.65" customHeight="1"/>
+    <row r="340" ht="12.65" customHeight="1"/>
+    <row r="341" ht="12.65" customHeight="1"/>
+    <row r="342" ht="12.65" customHeight="1"/>
+    <row r="343" ht="12.65" customHeight="1"/>
+    <row r="344" ht="12.65" customHeight="1"/>
+    <row r="345" ht="12.65" customHeight="1"/>
+    <row r="346" ht="12.65" customHeight="1"/>
+    <row r="347" ht="12.65" customHeight="1"/>
+    <row r="348" ht="12.65" customHeight="1"/>
+    <row r="349" ht="12.65" customHeight="1"/>
+    <row r="350" ht="12.65" customHeight="1"/>
+    <row r="351" ht="12.65" customHeight="1"/>
+    <row r="352" ht="12.65" customHeight="1"/>
+    <row r="353" ht="12.65" customHeight="1"/>
+    <row r="354" ht="12.65" customHeight="1"/>
+    <row r="355" ht="12.65" customHeight="1"/>
+    <row r="356" ht="12.65" customHeight="1"/>
+    <row r="357" ht="12.65" customHeight="1"/>
+    <row r="358" ht="12.65" customHeight="1"/>
+    <row r="359" ht="12.65" customHeight="1"/>
+    <row r="360" ht="12.65" customHeight="1"/>
+    <row r="361" ht="12.65" customHeight="1"/>
+    <row r="362" ht="12.65" customHeight="1"/>
+    <row r="363" ht="12.65" customHeight="1"/>
+    <row r="364" ht="12.65" customHeight="1"/>
+    <row r="365" ht="12.65" customHeight="1"/>
+    <row r="366" ht="12.65" customHeight="1"/>
+    <row r="367" ht="12.65" customHeight="1"/>
+    <row r="368" ht="12.65" customHeight="1"/>
+    <row r="369" ht="12.65" customHeight="1"/>
+    <row r="370" ht="12.65" customHeight="1"/>
+    <row r="371" ht="12.65" customHeight="1"/>
+    <row r="372" ht="12.65" customHeight="1"/>
+    <row r="373" ht="12.65" customHeight="1"/>
+    <row r="374" ht="12.65" customHeight="1"/>
+    <row r="375" ht="12.65" customHeight="1"/>
+    <row r="376" ht="12.65" customHeight="1"/>
+    <row r="377" ht="12.65" customHeight="1"/>
+    <row r="378" ht="12.65" customHeight="1"/>
+    <row r="379" ht="12.65" customHeight="1"/>
+    <row r="380" ht="12.65" customHeight="1"/>
+    <row r="381" ht="12.65" customHeight="1"/>
+    <row r="382" ht="12.65" customHeight="1"/>
+    <row r="383" ht="12.65" customHeight="1"/>
+    <row r="384" ht="12.65" customHeight="1"/>
+    <row r="385" ht="12.65" customHeight="1"/>
+    <row r="386" ht="12.65" customHeight="1"/>
+    <row r="387" ht="12.65" customHeight="1"/>
+    <row r="388" ht="12.65" customHeight="1"/>
+    <row r="389" ht="12.65" customHeight="1"/>
+    <row r="390" ht="12.65" customHeight="1"/>
+    <row r="391" ht="12.65" customHeight="1"/>
+    <row r="392" ht="12.65" customHeight="1"/>
+    <row r="393" ht="12.65" customHeight="1"/>
+    <row r="394" ht="12.65" customHeight="1"/>
+    <row r="395" ht="12.65" customHeight="1"/>
+    <row r="396" ht="12.65" customHeight="1"/>
+    <row r="397" ht="12.65" customHeight="1"/>
+    <row r="398" ht="12.65" customHeight="1"/>
+    <row r="399" ht="12.65" customHeight="1"/>
+    <row r="400" ht="12.65" customHeight="1"/>
+    <row r="401" ht="12.65" customHeight="1"/>
+    <row r="402" ht="12.65" customHeight="1"/>
+    <row r="403" ht="12.65" customHeight="1"/>
+    <row r="404" ht="12.65" customHeight="1"/>
+    <row r="405" ht="12.65" customHeight="1"/>
+    <row r="406" ht="12.65" customHeight="1"/>
+    <row r="407" ht="12.65" customHeight="1"/>
+    <row r="408" ht="12.65" customHeight="1"/>
+    <row r="409" ht="12.65" customHeight="1"/>
+    <row r="410" ht="12.65" customHeight="1"/>
+    <row r="411" ht="12.65" customHeight="1"/>
+    <row r="412" ht="12.65" customHeight="1"/>
+    <row r="413" ht="12.65" customHeight="1"/>
+    <row r="414" ht="12.65" customHeight="1"/>
+    <row r="415" ht="12.65" customHeight="1"/>
+    <row r="416" ht="12.65" customHeight="1"/>
+    <row r="417" ht="12.65" customHeight="1"/>
+    <row r="418" ht="12.65" customHeight="1"/>
+    <row r="419" ht="12.65" customHeight="1"/>
+    <row r="420" ht="12.65" customHeight="1"/>
+    <row r="421" ht="12.65" customHeight="1"/>
+    <row r="422" ht="12.65" customHeight="1"/>
+    <row r="423" ht="12.65" customHeight="1"/>
+    <row r="424" ht="12.65" customHeight="1"/>
+    <row r="425" ht="12.65" customHeight="1"/>
+    <row r="426" ht="12.65" customHeight="1"/>
+    <row r="427" ht="12.65" customHeight="1"/>
+    <row r="428" ht="12.65" customHeight="1"/>
+    <row r="429" ht="12.65" customHeight="1"/>
+    <row r="430" ht="12.65" customHeight="1"/>
+    <row r="431" ht="12.65" customHeight="1"/>
+    <row r="432" ht="12.65" customHeight="1"/>
+    <row r="433" ht="12.65" customHeight="1"/>
+    <row r="434" ht="12.65" customHeight="1"/>
+    <row r="435" ht="12.65" customHeight="1"/>
+    <row r="436" ht="12.65" customHeight="1"/>
+    <row r="437" ht="12.65" customHeight="1"/>
+    <row r="438" ht="12.65" customHeight="1"/>
+    <row r="439" ht="12.65" customHeight="1"/>
+    <row r="440" ht="12.65" customHeight="1"/>
+    <row r="441" ht="12.65" customHeight="1"/>
+    <row r="442" ht="12.65" customHeight="1"/>
+    <row r="443" ht="12.65" customHeight="1"/>
+    <row r="444" ht="12.65" customHeight="1"/>
+    <row r="445" ht="12.65" customHeight="1"/>
+    <row r="446" ht="12.65" customHeight="1"/>
+    <row r="447" ht="12.65" customHeight="1"/>
+    <row r="448" ht="12.65" customHeight="1"/>
+    <row r="449" ht="12.65" customHeight="1"/>
+    <row r="450" ht="12.65" customHeight="1"/>
+    <row r="451" ht="12.65" customHeight="1"/>
+    <row r="452" ht="12.65" customHeight="1"/>
+    <row r="453" ht="12.65" customHeight="1"/>
+    <row r="454" ht="12.65" customHeight="1"/>
+    <row r="455" ht="12.65" customHeight="1"/>
+    <row r="456" ht="12.65" customHeight="1"/>
+    <row r="457" ht="12.65" customHeight="1"/>
+    <row r="458" ht="12.65" customHeight="1"/>
+    <row r="459" ht="12.65" customHeight="1"/>
+    <row r="460" ht="12.65" customHeight="1"/>
+    <row r="461" ht="12.65" customHeight="1"/>
+    <row r="462" ht="12.65" customHeight="1"/>
+    <row r="463" ht="12.65" customHeight="1"/>
+    <row r="464" ht="12.65" customHeight="1"/>
+    <row r="465" ht="12.65" customHeight="1"/>
+    <row r="466" ht="12.65" customHeight="1"/>
+    <row r="467" ht="12.65" customHeight="1"/>
+    <row r="468" ht="12.65" customHeight="1"/>
+    <row r="469" ht="12.65" customHeight="1"/>
+    <row r="470" ht="12.65" customHeight="1"/>
+    <row r="471" ht="12.65" customHeight="1"/>
+    <row r="472" ht="12.65" customHeight="1"/>
+    <row r="473" ht="12.65" customHeight="1"/>
+    <row r="474" ht="12.65" customHeight="1"/>
+    <row r="475" ht="12.65" customHeight="1"/>
+    <row r="476" ht="12.65" customHeight="1"/>
+    <row r="477" ht="12.65" customHeight="1"/>
+    <row r="478" ht="12.65" customHeight="1"/>
+    <row r="479" ht="12.65" customHeight="1"/>
+    <row r="480" ht="12.65" customHeight="1"/>
+    <row r="481" ht="12.65" customHeight="1"/>
+    <row r="482" ht="12.65" customHeight="1"/>
+    <row r="483" ht="12.65" customHeight="1"/>
+    <row r="484" ht="12.65" customHeight="1"/>
+    <row r="485" ht="12.65" customHeight="1"/>
+    <row r="486" ht="12.65" customHeight="1"/>
+    <row r="487" ht="12.65" customHeight="1"/>
+    <row r="488" ht="12.65" customHeight="1"/>
+    <row r="489" ht="12.65" customHeight="1"/>
+    <row r="490" ht="12.65" customHeight="1"/>
+    <row r="491" ht="12.65" customHeight="1"/>
+    <row r="492" ht="12.65" customHeight="1"/>
+    <row r="493" ht="12.65" customHeight="1"/>
+    <row r="494" ht="12.65" customHeight="1"/>
+    <row r="495" ht="12.65" customHeight="1"/>
+    <row r="496" ht="12.65" customHeight="1"/>
+    <row r="497" ht="12.65" customHeight="1"/>
+    <row r="498" ht="12.65" customHeight="1"/>
+    <row r="499" ht="12.65" customHeight="1"/>
+    <row r="500" ht="12.65" customHeight="1"/>
+    <row r="501" ht="12.65" customHeight="1"/>
+    <row r="502" ht="12.65" customHeight="1"/>
+    <row r="503" ht="12.65" customHeight="1"/>
+    <row r="504" ht="12.65" customHeight="1"/>
+    <row r="505" ht="12.65" customHeight="1"/>
+    <row r="506" ht="12.65" customHeight="1"/>
+    <row r="507" ht="12.65" customHeight="1"/>
+    <row r="508" ht="12.65" customHeight="1"/>
+    <row r="509" ht="12.65" customHeight="1"/>
+    <row r="510" ht="12.65" customHeight="1"/>
+    <row r="511" ht="12.65" customHeight="1"/>
+    <row r="512" ht="12.65" customHeight="1"/>
+    <row r="513" ht="12.65" customHeight="1"/>
+    <row r="514" ht="12.65" customHeight="1"/>
+    <row r="515" ht="12.65" customHeight="1"/>
+    <row r="516" ht="12.65" customHeight="1"/>
+    <row r="517" ht="12.65" customHeight="1"/>
+    <row r="518" ht="12.65" customHeight="1"/>
+    <row r="519" ht="12.65" customHeight="1"/>
+    <row r="520" ht="12.65" customHeight="1"/>
+    <row r="521" ht="12.65" customHeight="1"/>
+    <row r="522" ht="12.65" customHeight="1"/>
+    <row r="523" ht="12.65" customHeight="1"/>
+    <row r="524" ht="12.65" customHeight="1"/>
+    <row r="525" ht="12.65" customHeight="1"/>
+    <row r="526" ht="12.65" customHeight="1"/>
+    <row r="527" ht="12.65" customHeight="1"/>
+    <row r="528" ht="12.65" customHeight="1"/>
+    <row r="529" ht="12.65" customHeight="1"/>
+    <row r="530" ht="12.65" customHeight="1"/>
+    <row r="531" ht="12.65" customHeight="1"/>
+    <row r="532" ht="12.65" customHeight="1"/>
+    <row r="533" ht="12.65" customHeight="1"/>
+    <row r="534" ht="12.65" customHeight="1"/>
+    <row r="535" ht="12.65" customHeight="1"/>
+    <row r="536" ht="12.65" customHeight="1"/>
+    <row r="537" ht="12.65" customHeight="1"/>
+    <row r="538" ht="12.65" customHeight="1"/>
+    <row r="539" ht="12.65" customHeight="1"/>
+    <row r="540" ht="12.65" customHeight="1"/>
+    <row r="541" ht="12.65" customHeight="1"/>
+    <row r="542" ht="12.65" customHeight="1"/>
+    <row r="543" ht="12.65" customHeight="1"/>
+    <row r="544" ht="12.65" customHeight="1"/>
+    <row r="545" ht="12.65" customHeight="1"/>
+    <row r="546" ht="12.65" customHeight="1"/>
+    <row r="547" ht="12.65" customHeight="1"/>
+    <row r="548" ht="12.65" customHeight="1"/>
+    <row r="549" ht="12.65" customHeight="1"/>
+    <row r="550" ht="12.65" customHeight="1"/>
+    <row r="551" ht="12.65" customHeight="1"/>
+    <row r="552" ht="12.65" customHeight="1"/>
+    <row r="553" ht="12.65" customHeight="1"/>
+    <row r="554" ht="12.65" customHeight="1"/>
+    <row r="555" ht="12.65" customHeight="1"/>
+    <row r="556" ht="12.65" customHeight="1"/>
+    <row r="557" ht="12.65" customHeight="1"/>
+    <row r="558" ht="12.65" customHeight="1"/>
+    <row r="559" ht="12.65" customHeight="1"/>
+    <row r="560" ht="12.65" customHeight="1"/>
+    <row r="561" ht="12.65" customHeight="1"/>
+    <row r="562" ht="12.65" customHeight="1"/>
+    <row r="563" ht="12.65" customHeight="1"/>
+    <row r="564" ht="12.65" customHeight="1"/>
+    <row r="565" ht="12.65" customHeight="1"/>
+    <row r="566" ht="12.65" customHeight="1"/>
+    <row r="567" ht="12.65" customHeight="1"/>
+    <row r="568" ht="12.65" customHeight="1"/>
+    <row r="569" ht="12.65" customHeight="1"/>
+    <row r="570" ht="12.65" customHeight="1"/>
+    <row r="571" ht="12.65" customHeight="1"/>
+    <row r="572" ht="12.65" customHeight="1"/>
+    <row r="573" ht="12.65" customHeight="1"/>
+    <row r="574" ht="12.65" customHeight="1"/>
+    <row r="575" ht="12.65" customHeight="1"/>
+    <row r="576" ht="12.65" customHeight="1"/>
+    <row r="577" ht="12.65" customHeight="1"/>
+    <row r="578" ht="12.65" customHeight="1"/>
+    <row r="579" ht="12.65" customHeight="1"/>
+    <row r="580" ht="12.65" customHeight="1"/>
+    <row r="581" ht="12.65" customHeight="1"/>
+    <row r="582" ht="12.65" customHeight="1"/>
+    <row r="583" ht="12.65" customHeight="1"/>
+    <row r="584" ht="12.65" customHeight="1"/>
+    <row r="585" ht="12.65" customHeight="1"/>
+    <row r="586" ht="12.65" customHeight="1"/>
+    <row r="587" ht="12.65" customHeight="1"/>
+    <row r="588" ht="12.65" customHeight="1"/>
+    <row r="589" ht="12.65" customHeight="1"/>
+    <row r="590" ht="12.65" customHeight="1"/>
+    <row r="591" ht="12.65" customHeight="1"/>
+    <row r="592" ht="12.65" customHeight="1"/>
+    <row r="593" ht="12.65" customHeight="1"/>
+    <row r="594" ht="12.65" customHeight="1"/>
+    <row r="595" ht="12.65" customHeight="1"/>
+    <row r="596" ht="12.65" customHeight="1"/>
+    <row r="597" ht="12.65" customHeight="1"/>
+    <row r="598" ht="12.65" customHeight="1"/>
+    <row r="599" ht="12.65" customHeight="1"/>
+    <row r="600" ht="12.65" customHeight="1"/>
+    <row r="601" ht="12.65" customHeight="1"/>
+    <row r="602" ht="12.65" customHeight="1"/>
+    <row r="603" ht="12.65" customHeight="1"/>
+    <row r="604" ht="12.65" customHeight="1"/>
+    <row r="605" ht="12.65" customHeight="1"/>
+    <row r="606" ht="12.65" customHeight="1"/>
+    <row r="607" ht="12.65" customHeight="1"/>
+    <row r="608" ht="12.65" customHeight="1"/>
+    <row r="609" ht="12.65" customHeight="1"/>
+    <row r="610" ht="12.65" customHeight="1"/>
+    <row r="611" ht="12.65" customHeight="1"/>
+    <row r="612" ht="12.65" customHeight="1"/>
+    <row r="613" ht="12.65" customHeight="1"/>
+    <row r="614" ht="12.65" customHeight="1"/>
+    <row r="615" ht="12.65" customHeight="1"/>
+    <row r="616" ht="12.65" customHeight="1"/>
+    <row r="617" ht="12.65" customHeight="1"/>
+    <row r="618" ht="12.65" customHeight="1"/>
+    <row r="619" ht="12.65" customHeight="1"/>
+    <row r="620" ht="12.65" customHeight="1"/>
+    <row r="621" ht="12.65" customHeight="1"/>
+    <row r="622" ht="12.65" customHeight="1"/>
+    <row r="623" ht="12.65" customHeight="1"/>
+    <row r="624" ht="12.65" customHeight="1"/>
+    <row r="625" ht="12.65" customHeight="1"/>
+    <row r="626" ht="12.65" customHeight="1"/>
+    <row r="627" ht="12.65" customHeight="1"/>
+    <row r="628" ht="12.65" customHeight="1"/>
+    <row r="629" ht="12.65" customHeight="1"/>
+    <row r="630" ht="12.65" customHeight="1"/>
+    <row r="631" ht="12.65" customHeight="1"/>
+    <row r="632" ht="12.65" customHeight="1"/>
+    <row r="633" ht="12.65" customHeight="1"/>
+    <row r="634" ht="12.65" customHeight="1"/>
+    <row r="635" ht="12.65" customHeight="1"/>
+    <row r="636" ht="12.65" customHeight="1"/>
+    <row r="637" ht="12.65" customHeight="1"/>
+    <row r="638" ht="12.65" customHeight="1"/>
+    <row r="639" ht="12.65" customHeight="1"/>
+    <row r="640" ht="12.65" customHeight="1"/>
+    <row r="641" ht="12.65" customHeight="1"/>
+    <row r="642" ht="12.65" customHeight="1"/>
+    <row r="643" ht="12.65" customHeight="1"/>
+    <row r="644" ht="12.65" customHeight="1"/>
+    <row r="645" ht="12.65" customHeight="1"/>
+    <row r="646" ht="12.65" customHeight="1"/>
+    <row r="647" ht="12.65" customHeight="1"/>
+    <row r="648" ht="12.65" customHeight="1"/>
+    <row r="649" ht="12.65" customHeight="1"/>
+    <row r="650" ht="12.65" customHeight="1"/>
+    <row r="651" ht="12.65" customHeight="1"/>
+    <row r="652" ht="12.65" customHeight="1"/>
+    <row r="653" ht="12.65" customHeight="1"/>
+    <row r="654" ht="12.65" customHeight="1"/>
+    <row r="655" ht="12.65" customHeight="1"/>
+    <row r="656" ht="12.65" customHeight="1"/>
+    <row r="657" ht="12.65" customHeight="1"/>
+    <row r="658" ht="12.65" customHeight="1"/>
+    <row r="659" ht="12.65" customHeight="1"/>
+    <row r="660" ht="12.65" customHeight="1"/>
+    <row r="661" ht="12.65" customHeight="1"/>
+    <row r="662" ht="12.65" customHeight="1"/>
+    <row r="663" ht="12.65" customHeight="1"/>
+    <row r="664" ht="12.65" customHeight="1"/>
+    <row r="665" ht="12.65" customHeight="1"/>
+    <row r="666" ht="12.65" customHeight="1"/>
+    <row r="667" ht="12.65" customHeight="1"/>
+    <row r="668" ht="12.65" customHeight="1"/>
+    <row r="669" ht="12.65" customHeight="1"/>
+    <row r="670" ht="12.65" customHeight="1"/>
+    <row r="671" ht="12.65" customHeight="1"/>
+    <row r="672" ht="12.65" customHeight="1"/>
+    <row r="673" ht="12.65" customHeight="1"/>
+    <row r="674" ht="12.65" customHeight="1"/>
+    <row r="675" ht="12.65" customHeight="1"/>
+    <row r="676" ht="12.65" customHeight="1"/>
+    <row r="677" ht="12.65" customHeight="1"/>
+    <row r="678" ht="12.65" customHeight="1"/>
+    <row r="679" ht="12.65" customHeight="1"/>
+    <row r="680" ht="12.65" customHeight="1"/>
+    <row r="681" ht="12.65" customHeight="1"/>
+    <row r="682" ht="12.65" customHeight="1"/>
+    <row r="683" ht="12.65" customHeight="1"/>
+    <row r="684" ht="12.65" customHeight="1"/>
+    <row r="685" ht="12.65" customHeight="1"/>
+    <row r="686" ht="12.65" customHeight="1"/>
+    <row r="687" ht="12.65" customHeight="1"/>
+    <row r="688" ht="12.65" customHeight="1"/>
+    <row r="689" ht="12.65" customHeight="1"/>
+    <row r="690" ht="12.65" customHeight="1"/>
+    <row r="691" ht="12.65" customHeight="1"/>
+    <row r="692" ht="12.65" customHeight="1"/>
+    <row r="693" ht="12.65" customHeight="1"/>
+    <row r="694" ht="12.65" customHeight="1"/>
+    <row r="695" ht="12.65" customHeight="1"/>
+    <row r="696" ht="12.65" customHeight="1"/>
+    <row r="697" ht="12.65" customHeight="1"/>
+    <row r="698" ht="12.65" customHeight="1"/>
+    <row r="699" ht="12.65" customHeight="1"/>
+    <row r="700" ht="12.65" customHeight="1"/>
+    <row r="701" ht="12.65" customHeight="1"/>
+    <row r="702" ht="12.65" customHeight="1"/>
+    <row r="703" ht="12.65" customHeight="1"/>
+    <row r="704" ht="12.65" customHeight="1"/>
+    <row r="705" ht="12.65" customHeight="1"/>
+    <row r="706" ht="12.65" customHeight="1"/>
+    <row r="707" ht="12.65" customHeight="1"/>
+    <row r="708" ht="12.65" customHeight="1"/>
+    <row r="709" ht="12.65" customHeight="1"/>
+    <row r="710" ht="12.65" customHeight="1"/>
+    <row r="711" ht="12.65" customHeight="1"/>
+    <row r="712" ht="12.65" customHeight="1"/>
+    <row r="713" ht="12.65" customHeight="1"/>
+    <row r="714" ht="12.65" customHeight="1"/>
+    <row r="715" ht="12.65" customHeight="1"/>
+    <row r="716" ht="12.65" customHeight="1"/>
+    <row r="717" ht="12.65" customHeight="1"/>
+    <row r="718" ht="12.65" customHeight="1"/>
+    <row r="719" ht="12.65" customHeight="1"/>
+    <row r="720" ht="12.65" customHeight="1"/>
+    <row r="721" ht="12.65" customHeight="1"/>
+    <row r="722" ht="12.65" customHeight="1"/>
+    <row r="723" ht="12.65" customHeight="1"/>
+    <row r="724" ht="12.65" customHeight="1"/>
+    <row r="725" ht="12.65" customHeight="1"/>
+    <row r="726" ht="12.65" customHeight="1"/>
+    <row r="727" ht="12.65" customHeight="1"/>
+    <row r="728" ht="12.65" customHeight="1"/>
+    <row r="729" ht="12.65" customHeight="1"/>
+    <row r="730" ht="12.65" customHeight="1"/>
+    <row r="731" ht="12.65" customHeight="1"/>
+    <row r="732" ht="12.65" customHeight="1"/>
+    <row r="733" ht="12.65" customHeight="1"/>
+    <row r="734" ht="12.65" customHeight="1"/>
+    <row r="735" ht="12.65" customHeight="1"/>
+    <row r="736" ht="12.65" customHeight="1"/>
+    <row r="737" ht="12.65" customHeight="1"/>
+    <row r="738" ht="12.65" customHeight="1"/>
+    <row r="739" ht="12.65" customHeight="1"/>
+    <row r="740" ht="12.65" customHeight="1"/>
+    <row r="741" ht="12.65" customHeight="1"/>
+    <row r="742" ht="12.65" customHeight="1"/>
+    <row r="743" ht="12.65" customHeight="1"/>
+    <row r="744" ht="12.65" customHeight="1"/>
+    <row r="745" ht="12.65" customHeight="1"/>
+    <row r="746" ht="12.65" customHeight="1"/>
+    <row r="747" ht="12.65" customHeight="1"/>
+    <row r="748" ht="12.65" customHeight="1"/>
+    <row r="749" ht="12.65" customHeight="1"/>
+    <row r="750" ht="12.65" customHeight="1"/>
+    <row r="751" ht="12.65" customHeight="1"/>
+    <row r="752" ht="12.65" customHeight="1"/>
+    <row r="753" ht="12.65" customHeight="1"/>
+    <row r="754" ht="12.65" customHeight="1"/>
+    <row r="755" ht="12.65" customHeight="1"/>
+    <row r="756" ht="12.65" customHeight="1"/>
+    <row r="757" ht="12.65" customHeight="1"/>
+    <row r="758" ht="12.65" customHeight="1"/>
+    <row r="759" ht="12.65" customHeight="1"/>
+    <row r="760" ht="12.65" customHeight="1"/>
+    <row r="761" ht="12.65" customHeight="1"/>
+    <row r="762" ht="12.65" customHeight="1"/>
+    <row r="763" ht="12.65" customHeight="1"/>
+    <row r="764" ht="12.65" customHeight="1"/>
+    <row r="765" ht="12.65" customHeight="1"/>
+    <row r="766" ht="12.65" customHeight="1"/>
+    <row r="767" ht="12.65" customHeight="1"/>
+    <row r="768" ht="12.65" customHeight="1"/>
+    <row r="769" ht="12.65" customHeight="1"/>
+    <row r="770" ht="12.65" customHeight="1"/>
+    <row r="771" ht="12.65" customHeight="1"/>
+    <row r="772" ht="12.65" customHeight="1"/>
+    <row r="773" ht="12.65" customHeight="1"/>
+    <row r="774" ht="12.65" customHeight="1"/>
+    <row r="775" ht="12.65" customHeight="1"/>
+    <row r="776" ht="12.65" customHeight="1"/>
+    <row r="777" ht="12.65" customHeight="1"/>
+    <row r="778" ht="12.65" customHeight="1"/>
+    <row r="779" ht="12.65" customHeight="1"/>
+    <row r="780" ht="12.65" customHeight="1"/>
+    <row r="781" ht="12.65" customHeight="1"/>
+    <row r="782" ht="12.65" customHeight="1"/>
+    <row r="783" ht="12.65" customHeight="1"/>
+    <row r="784" ht="12.65" customHeight="1"/>
+    <row r="785" ht="12.65" customHeight="1"/>
+    <row r="786" ht="12.65" customHeight="1"/>
+    <row r="787" ht="12.65" customHeight="1"/>
+    <row r="788" ht="12.65" customHeight="1"/>
+    <row r="789" ht="12.65" customHeight="1"/>
+    <row r="790" ht="12.65" customHeight="1"/>
+    <row r="791" ht="12.65" customHeight="1"/>
+    <row r="792" ht="12.65" customHeight="1"/>
+    <row r="793" ht="12.65" customHeight="1"/>
+    <row r="794" ht="12.65" customHeight="1"/>
+    <row r="795" ht="12.65" customHeight="1"/>
+    <row r="796" ht="12.65" customHeight="1"/>
+    <row r="797" ht="12.65" customHeight="1"/>
+    <row r="798" ht="12.65" customHeight="1"/>
+    <row r="799" ht="12.65" customHeight="1"/>
+    <row r="800" ht="12.65" customHeight="1"/>
+    <row r="801" ht="12.65" customHeight="1"/>
+    <row r="802" ht="12.65" customHeight="1"/>
+    <row r="803" ht="12.65" customHeight="1"/>
+    <row r="804" ht="12.65" customHeight="1"/>
+    <row r="805" ht="12.65" customHeight="1"/>
+    <row r="806" ht="12.65" customHeight="1"/>
+    <row r="807" ht="12.65" customHeight="1"/>
+    <row r="808" ht="12.65" customHeight="1"/>
+    <row r="809" ht="12.65" customHeight="1"/>
+    <row r="810" ht="12.65" customHeight="1"/>
+    <row r="811" ht="12.65" customHeight="1"/>
+    <row r="812" ht="12.65" customHeight="1"/>
+    <row r="813" ht="12.65" customHeight="1"/>
+    <row r="814" ht="12.65" customHeight="1"/>
+    <row r="815" ht="12.65" customHeight="1"/>
+    <row r="816" ht="12.65" customHeight="1"/>
+    <row r="817" ht="12.65" customHeight="1"/>
+    <row r="818" ht="12.65" customHeight="1"/>
+    <row r="819" ht="12.65" customHeight="1"/>
+    <row r="820" ht="12.65" customHeight="1"/>
+    <row r="821" ht="12.65" customHeight="1"/>
+    <row r="822" ht="12.65" customHeight="1"/>
+    <row r="823" ht="12.65" customHeight="1"/>
+    <row r="824" ht="12.65" customHeight="1"/>
+    <row r="825" ht="12.65" customHeight="1"/>
+    <row r="826" ht="12.65" customHeight="1"/>
+    <row r="827" ht="12.65" customHeight="1"/>
+    <row r="828" ht="12.65" customHeight="1"/>
+    <row r="829" ht="12.65" customHeight="1"/>
+    <row r="830" ht="12.65" customHeight="1"/>
+    <row r="831" ht="12.65" customHeight="1"/>
+    <row r="832" ht="12.65" customHeight="1"/>
+    <row r="833" ht="12.65" customHeight="1"/>
+    <row r="834" ht="12.65" customHeight="1"/>
+    <row r="835" ht="12.65" customHeight="1"/>
+    <row r="836" ht="12.65" customHeight="1"/>
+    <row r="837" ht="12.65" customHeight="1"/>
+    <row r="838" ht="12.65" customHeight="1"/>
+    <row r="839" ht="12.65" customHeight="1"/>
+    <row r="840" ht="12.65" customHeight="1"/>
+    <row r="841" ht="12.65" customHeight="1"/>
+    <row r="842" ht="12.65" customHeight="1"/>
+    <row r="843" ht="12.65" customHeight="1"/>
+    <row r="844" ht="12.65" customHeight="1"/>
+    <row r="845" ht="12.65" customHeight="1"/>
+    <row r="846" ht="12.65" customHeight="1"/>
+    <row r="847" ht="12.65" customHeight="1"/>
+    <row r="848" ht="12.65" customHeight="1"/>
+    <row r="849" ht="12.65" customHeight="1"/>
+    <row r="850" ht="12.65" customHeight="1"/>
+    <row r="851" ht="12.65" customHeight="1"/>
+    <row r="852" ht="12.65" customHeight="1"/>
+    <row r="853" ht="12.65" customHeight="1"/>
+    <row r="854" ht="12.65" customHeight="1"/>
+    <row r="855" ht="12.65" customHeight="1"/>
+    <row r="856" ht="12.65" customHeight="1"/>
+    <row r="857" ht="12.65" customHeight="1"/>
+    <row r="858" ht="12.65" customHeight="1"/>
+    <row r="859" ht="12.65" customHeight="1"/>
+    <row r="860" ht="12.65" customHeight="1"/>
+    <row r="861" ht="12.65" customHeight="1"/>
+    <row r="862" ht="12.65" customHeight="1"/>
+    <row r="863" ht="12.65" customHeight="1"/>
+    <row r="864" ht="12.65" customHeight="1"/>
+    <row r="865" ht="12.65" customHeight="1"/>
+    <row r="866" ht="12.65" customHeight="1"/>
+    <row r="867" ht="12.65" customHeight="1"/>
+    <row r="868" ht="12.65" customHeight="1"/>
+    <row r="869" ht="12.65" customHeight="1"/>
+    <row r="870" ht="12.65" customHeight="1"/>
+    <row r="871" ht="12.65" customHeight="1"/>
+    <row r="872" ht="12.65" customHeight="1"/>
+    <row r="873" ht="12.65" customHeight="1"/>
+    <row r="874" ht="12.65" customHeight="1"/>
+    <row r="875" ht="12.65" customHeight="1"/>
+    <row r="876" ht="12.65" customHeight="1"/>
+    <row r="877" ht="12.65" customHeight="1"/>
+    <row r="878" ht="12.65" customHeight="1"/>
+    <row r="879" ht="12.65" customHeight="1"/>
+    <row r="880" ht="12.65" customHeight="1"/>
+    <row r="881" ht="12.65" customHeight="1"/>
+    <row r="882" ht="12.65" customHeight="1"/>
+    <row r="883" ht="12.65" customHeight="1"/>
+    <row r="884" ht="12.65" customHeight="1"/>
+    <row r="885" ht="12.65" customHeight="1"/>
+    <row r="886" ht="12.65" customHeight="1"/>
+    <row r="887" ht="12.65" customHeight="1"/>
+    <row r="888" ht="12.65" customHeight="1"/>
+    <row r="889" ht="12.65" customHeight="1"/>
+    <row r="890" ht="12.65" customHeight="1"/>
+    <row r="891" ht="12.65" customHeight="1"/>
+    <row r="892" ht="12.65" customHeight="1"/>
+    <row r="893" ht="12.65" customHeight="1"/>
+    <row r="894" ht="12.65" customHeight="1"/>
+    <row r="895" ht="12.65" customHeight="1"/>
+    <row r="896" ht="12.65" customHeight="1"/>
+    <row r="897" ht="12.65" customHeight="1"/>
+    <row r="898" ht="12.65" customHeight="1"/>
+    <row r="899" ht="12.65" customHeight="1"/>
+    <row r="900" ht="12.65" customHeight="1"/>
+    <row r="901" ht="12.65" customHeight="1"/>
+    <row r="902" ht="12.65" customHeight="1"/>
+    <row r="903" ht="12.65" customHeight="1"/>
+    <row r="904" ht="12.65" customHeight="1"/>
+    <row r="905" ht="12.65" customHeight="1"/>
+    <row r="906" ht="12.65" customHeight="1"/>
+    <row r="907" ht="12.65" customHeight="1"/>
+    <row r="908" ht="12.65" customHeight="1"/>
+    <row r="909" ht="12.65" customHeight="1"/>
+    <row r="910" ht="12.65" customHeight="1"/>
+    <row r="911" ht="12.65" customHeight="1"/>
+    <row r="912" ht="12.65" customHeight="1"/>
+    <row r="913" ht="12.65" customHeight="1"/>
+    <row r="914" ht="12.65" customHeight="1"/>
+    <row r="915" ht="12.65" customHeight="1"/>
+    <row r="916" ht="12.65" customHeight="1"/>
+    <row r="917" ht="12.65" customHeight="1"/>
+    <row r="918" ht="12.65" customHeight="1"/>
+    <row r="919" ht="12.65" customHeight="1"/>
+    <row r="920" ht="12.65" customHeight="1"/>
+    <row r="921" ht="12.65" customHeight="1"/>
+    <row r="922" ht="12.65" customHeight="1"/>
+    <row r="923" ht="12.65" customHeight="1"/>
+    <row r="924" ht="12.65" customHeight="1"/>
+    <row r="925" ht="12.65" customHeight="1"/>
+    <row r="926" ht="12.65" customHeight="1"/>
+    <row r="927" ht="12.65" customHeight="1"/>
+    <row r="928" ht="12.65" customHeight="1"/>
+    <row r="929" ht="12.65" customHeight="1"/>
+    <row r="930" ht="12.65" customHeight="1"/>
+    <row r="931" ht="12.65" customHeight="1"/>
+    <row r="932" ht="12.65" customHeight="1"/>
+    <row r="933" ht="12.65" customHeight="1"/>
+    <row r="934" ht="12.65" customHeight="1"/>
+    <row r="935" ht="12.65" customHeight="1"/>
+    <row r="936" ht="12.65" customHeight="1"/>
+    <row r="937" ht="12.65" customHeight="1"/>
+    <row r="938" ht="12.65" customHeight="1"/>
+    <row r="939" ht="12.65" customHeight="1"/>
+    <row r="940" ht="12.65" customHeight="1"/>
+    <row r="941" ht="12.65" customHeight="1"/>
+    <row r="942" ht="12.65" customHeight="1"/>
+    <row r="943" ht="12.65" customHeight="1"/>
+    <row r="944" ht="12.65" customHeight="1"/>
+    <row r="945" ht="12.65" customHeight="1"/>
+    <row r="946" ht="12.65" customHeight="1"/>
+    <row r="947" ht="12.65" customHeight="1"/>
+    <row r="948" ht="12.65" customHeight="1"/>
+    <row r="949" ht="12.65" customHeight="1"/>
+    <row r="950" ht="12.65" customHeight="1"/>
+    <row r="951" ht="12.65" customHeight="1"/>
+    <row r="952" ht="12.65" customHeight="1"/>
+    <row r="953" ht="12.65" customHeight="1"/>
+    <row r="954" ht="12.65" customHeight="1"/>
+    <row r="955" ht="12.65" customHeight="1"/>
+    <row r="956" ht="12.65" customHeight="1"/>
+    <row r="957" ht="12.65" customHeight="1"/>
+    <row r="958" ht="12.65" customHeight="1"/>
+    <row r="959" ht="12.65" customHeight="1"/>
+    <row r="960" ht="12.65" customHeight="1"/>
+    <row r="961" ht="12.65" customHeight="1"/>
+    <row r="962" ht="12.65" customHeight="1"/>
+    <row r="963" ht="12.65" customHeight="1"/>
+    <row r="964" ht="12.65" customHeight="1"/>
+    <row r="965" ht="12.65" customHeight="1"/>
+    <row r="966" ht="12.65" customHeight="1"/>
+    <row r="967" ht="12.65" customHeight="1"/>
+    <row r="968" ht="12.65" customHeight="1"/>
+    <row r="969" ht="12.65" customHeight="1"/>
+    <row r="970" ht="12.65" customHeight="1"/>
+    <row r="971" ht="12.65" customHeight="1"/>
+    <row r="972" ht="12.65" customHeight="1"/>
+    <row r="973" ht="12.65" customHeight="1"/>
+    <row r="974" ht="12.65" customHeight="1"/>
+    <row r="975" ht="12.65" customHeight="1"/>
+    <row r="976" ht="12.65" customHeight="1"/>
+    <row r="977" ht="12.65" customHeight="1"/>
+    <row r="978" ht="12.65" customHeight="1"/>
+    <row r="979" ht="12.65" customHeight="1"/>
+    <row r="980" ht="12.65" customHeight="1"/>
+    <row r="981" ht="12.65" customHeight="1"/>
+    <row r="982" ht="12.65" customHeight="1"/>
+    <row r="983" ht="12.65" customHeight="1"/>
+    <row r="984" ht="12.65" customHeight="1"/>
+    <row r="985" ht="12.65" customHeight="1"/>
+    <row r="986" ht="12.65" customHeight="1"/>
+    <row r="987" ht="12.65" customHeight="1"/>
+    <row r="988" ht="12.65" customHeight="1"/>
+    <row r="989" ht="12.65" customHeight="1"/>
+    <row r="990" ht="12.65" customHeight="1"/>
+    <row r="991" ht="12.65" customHeight="1"/>
+    <row r="992" ht="12.65" customHeight="1"/>
+    <row r="993" ht="12.65" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0"/>
@@ -71626,7 +71626,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0"/>

--- a/j-busqueda clientes/j-clientes-gle.xlsx
+++ b/j-busqueda clientes/j-clientes-gle.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rocio\OneDrive\documentos\TRABAJOS AUTONOMOS\JURADA\j-busqueda clientes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D66FC53-5F99-49AF-A956-30573925332B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC2A7A41-F0CC-436A-BECA-FEBB3DDE851D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="-120" windowWidth="27660" windowHeight="14925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1260" yWindow="-120" windowWidth="27660" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="clientes" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5269" uniqueCount="3071">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5270" uniqueCount="3072">
   <si>
     <t>fechaEmail</t>
   </si>
@@ -8849,9 +8849,6 @@
     <t>dd-mm-aa/4-1gu</t>
   </si>
   <si>
-    <t>una fecha másgu significa que he escrito a un Unico después del Genérico, los números quieren decir que he escrito 4 veces al primer contacto y una al segundo. En fechaEmail pongo fecha del genérico y en 2ndpass pongo fecha del único (lo pongo como 2nd pass por si la persona ha llegado a leer el email que envié al genérico)</t>
-  </si>
-  <si>
     <t>dd-mm-aa/v</t>
   </si>
   <si>
@@ -9300,6 +9297,12 @@
   </si>
   <si>
     <t>29-4-26/v</t>
+  </si>
+  <si>
+    <t>una fecha más gu significa que he escrito a un Unico después del Genérico, los números quieren decir que he escrito 4 veces al primer contacto y una al segundo. En fechaEmail pongo fecha del genérico y en 2ndpass pongo fecha del único (lo pongo como 2nd pass por si la persona ha llegado a leer el email que envié al genérico)</t>
+  </si>
+  <si>
+    <t>v / 0,9/pal (rebajo desde 11 céntimos)</t>
   </si>
 </sst>
 </file>
@@ -9937,7 +9940,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="466">
+  <cellXfs count="467">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -11002,9 +11005,6 @@
     <xf numFmtId="49" fontId="21" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -11276,6 +11276,12 @@
     <xf numFmtId="167" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -11496,9 +11502,9 @@
   <dimension ref="A1:AG534"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="11.45" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.140625" style="411" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" style="350" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" style="390" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" style="410" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="350" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" style="389" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" style="75" customWidth="1"/>
     <col min="5" max="5" width="4.42578125" style="75" customWidth="1"/>
     <col min="6" max="6" width="4.140625" style="75" customWidth="1"/>
@@ -11512,7 +11518,7 @@
     <col min="14" max="14" width="3.7109375" style="75" customWidth="1"/>
     <col min="15" max="15" width="4.5703125" style="75" customWidth="1"/>
     <col min="16" max="16" width="7.85546875" style="75" customWidth="1"/>
-    <col min="17" max="17" width="17.5703125" style="435" customWidth="1"/>
+    <col min="17" max="17" width="17.5703125" style="434" customWidth="1"/>
     <col min="18" max="18" width="14.42578125" style="75" customWidth="1"/>
     <col min="19" max="23" width="7.28515625" style="75" customWidth="1"/>
     <col min="24" max="25" width="7.28515625" style="75" hidden="1" customWidth="1"/>
@@ -11522,7 +11528,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="26.25" customHeight="1">
-      <c r="A1" s="409" t="s">
+      <c r="A1" s="408" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="202" t="s">
@@ -11534,7 +11540,7 @@
       <c r="D1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="415" t="s">
+      <c r="E1" s="414" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="26" t="s">
@@ -11570,7 +11576,7 @@
       <c r="P1" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="415" t="s">
+      <c r="Q1" s="414" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="26" t="s">
@@ -11603,8 +11609,8 @@
       <c r="AA1" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="415" t="s">
-        <v>3067</v>
+      <c r="AB1" s="414" t="s">
+        <v>3066</v>
       </c>
       <c r="AC1" s="26"/>
       <c r="AD1" s="26"/>
@@ -11647,7 +11653,7 @@
       </c>
       <c r="O2" s="102"/>
       <c r="P2" s="102"/>
-      <c r="Q2" s="405"/>
+      <c r="Q2" s="404"/>
       <c r="R2" s="102"/>
       <c r="S2" s="102"/>
       <c r="T2" s="102"/>
@@ -11704,7 +11710,7 @@
       </c>
       <c r="O3" s="104"/>
       <c r="P3" s="104"/>
-      <c r="Q3" s="407"/>
+      <c r="Q3" s="406"/>
       <c r="R3" s="104"/>
       <c r="S3" s="104"/>
       <c r="T3" s="104"/>
@@ -11759,7 +11765,7 @@
       </c>
       <c r="O4" s="106"/>
       <c r="P4" s="106"/>
-      <c r="Q4" s="402"/>
+      <c r="Q4" s="401"/>
       <c r="R4" s="106"/>
       <c r="S4" s="106"/>
       <c r="T4" s="106"/>
@@ -11818,7 +11824,7 @@
       </c>
       <c r="O5" s="263"/>
       <c r="P5" s="263"/>
-      <c r="Q5" s="422"/>
+      <c r="Q5" s="421"/>
       <c r="R5" s="263"/>
       <c r="S5" s="263"/>
       <c r="T5" s="263"/>
@@ -11873,7 +11879,7 @@
       </c>
       <c r="O6" s="272"/>
       <c r="P6" s="272"/>
-      <c r="Q6" s="423"/>
+      <c r="Q6" s="422"/>
       <c r="R6" s="272"/>
       <c r="S6" s="272"/>
       <c r="T6" s="272"/>
@@ -11924,7 +11930,7 @@
       </c>
       <c r="O7" s="274"/>
       <c r="P7" s="274"/>
-      <c r="Q7" s="424"/>
+      <c r="Q7" s="423"/>
       <c r="R7" s="274"/>
       <c r="S7" s="274"/>
       <c r="T7" s="274"/>
@@ -11969,7 +11975,7 @@
       </c>
       <c r="O8" s="277"/>
       <c r="P8" s="277"/>
-      <c r="Q8" s="425"/>
+      <c r="Q8" s="424"/>
       <c r="R8" s="277"/>
       <c r="S8" s="277"/>
       <c r="T8" s="277"/>
@@ -12012,7 +12018,7 @@
       </c>
       <c r="O9" s="248"/>
       <c r="P9" s="248"/>
-      <c r="Q9" s="426"/>
+      <c r="Q9" s="425"/>
       <c r="R9" s="248"/>
       <c r="S9" s="248"/>
       <c r="T9" s="248"/>
@@ -12053,7 +12059,7 @@
       <c r="N10" s="282"/>
       <c r="O10" s="282"/>
       <c r="P10" s="282"/>
-      <c r="Q10" s="427"/>
+      <c r="Q10" s="426"/>
       <c r="R10" s="282"/>
       <c r="S10" s="282"/>
       <c r="T10" s="282"/>
@@ -12075,11 +12081,15 @@
       <c r="A11" s="283">
         <v>45756</v>
       </c>
-      <c r="B11" s="283">
+      <c r="B11" s="466">
         <v>46058</v>
       </c>
-      <c r="C11" s="374"/>
-      <c r="D11" s="284"/>
+      <c r="C11" s="465" t="s">
+        <v>3071</v>
+      </c>
+      <c r="D11" s="284">
+        <v>46141</v>
+      </c>
       <c r="E11" s="285"/>
       <c r="F11" s="285" t="s">
         <v>27</v>
@@ -12110,7 +12120,7 @@
       <c r="P11" s="285" t="s">
         <v>78</v>
       </c>
-      <c r="Q11" s="428"/>
+      <c r="Q11" s="427"/>
       <c r="R11" s="285"/>
       <c r="S11" s="285"/>
       <c r="T11" s="285"/>
@@ -12139,9 +12149,9 @@
         <v>46059</v>
       </c>
       <c r="B12" s="287" t="s">
-        <v>3070</v>
-      </c>
-      <c r="C12" s="375"/>
+        <v>3069</v>
+      </c>
+      <c r="C12" s="374"/>
       <c r="D12" s="283">
         <v>46062</v>
       </c>
@@ -12169,7 +12179,7 @@
       </c>
       <c r="O12" s="285"/>
       <c r="P12" s="285"/>
-      <c r="Q12" s="428"/>
+      <c r="Q12" s="427"/>
       <c r="R12" s="285"/>
       <c r="S12" s="285"/>
       <c r="T12" s="285"/>
@@ -12192,7 +12202,7 @@
         <v>46001</v>
       </c>
       <c r="B13" s="289"/>
-      <c r="C13" s="376"/>
+      <c r="C13" s="375"/>
       <c r="D13" s="290"/>
       <c r="E13" s="291" t="s">
         <v>27</v>
@@ -12218,7 +12228,7 @@
       </c>
       <c r="O13" s="291"/>
       <c r="P13" s="291"/>
-      <c r="Q13" s="429"/>
+      <c r="Q13" s="428"/>
       <c r="R13" s="291"/>
       <c r="S13" s="291"/>
       <c r="T13" s="291"/>
@@ -12245,7 +12255,7 @@
       <c r="B14" s="289" t="s">
         <v>89</v>
       </c>
-      <c r="C14" s="376"/>
+      <c r="C14" s="375"/>
       <c r="D14" s="290"/>
       <c r="E14" s="291"/>
       <c r="F14" s="291"/>
@@ -12269,7 +12279,7 @@
       <c r="P14" s="291" t="s">
         <v>93</v>
       </c>
-      <c r="Q14" s="429"/>
+      <c r="Q14" s="428"/>
       <c r="R14" s="291"/>
       <c r="S14" s="291"/>
       <c r="T14" s="291"/>
@@ -12292,7 +12302,7 @@
         <v>46000</v>
       </c>
       <c r="B15" s="203"/>
-      <c r="C15" s="377"/>
+      <c r="C15" s="376"/>
       <c r="D15" s="80"/>
       <c r="E15" s="56"/>
       <c r="F15" s="56"/>
@@ -12313,7 +12323,7 @@
       </c>
       <c r="O15" s="56"/>
       <c r="P15" s="56"/>
-      <c r="Q15" s="404"/>
+      <c r="Q15" s="403"/>
       <c r="R15" s="56"/>
       <c r="S15" s="56"/>
       <c r="T15" s="56"/>
@@ -12338,7 +12348,7 @@
       <c r="B16" s="214">
         <v>46062</v>
       </c>
-      <c r="C16" s="378"/>
+      <c r="C16" s="377"/>
       <c r="E16" s="81"/>
       <c r="F16" s="81"/>
       <c r="G16" s="217" t="s">
@@ -12393,7 +12403,7 @@
       <c r="F17" s="102" t="s">
         <v>27</v>
       </c>
-      <c r="G17" s="408" t="s">
+      <c r="G17" s="407" t="s">
         <v>100</v>
       </c>
       <c r="H17" s="119" t="s">
@@ -12417,7 +12427,7 @@
       </c>
       <c r="O17" s="102"/>
       <c r="P17" s="102"/>
-      <c r="Q17" s="405"/>
+      <c r="Q17" s="404"/>
       <c r="R17" s="102"/>
       <c r="S17" s="102"/>
       <c r="T17" s="102"/>
@@ -12473,7 +12483,7 @@
       </c>
       <c r="O18" s="104"/>
       <c r="P18" s="292"/>
-      <c r="Q18" s="407"/>
+      <c r="Q18" s="406"/>
       <c r="R18" s="104"/>
       <c r="S18" s="104"/>
       <c r="T18" s="104"/>
@@ -12530,7 +12540,7 @@
       </c>
       <c r="O19" s="106"/>
       <c r="P19" s="106"/>
-      <c r="Q19" s="402"/>
+      <c r="Q19" s="401"/>
       <c r="R19" s="106"/>
       <c r="S19" s="106"/>
       <c r="T19" s="106"/>
@@ -12559,7 +12569,7 @@
       <c r="B20" s="203" t="s">
         <v>117</v>
       </c>
-      <c r="C20" s="379"/>
+      <c r="C20" s="378"/>
       <c r="D20" s="293"/>
       <c r="E20" s="56" t="s">
         <v>27</v>
@@ -12591,7 +12601,7 @@
       </c>
       <c r="O20" s="56"/>
       <c r="P20" s="56"/>
-      <c r="Q20" s="404" t="s">
+      <c r="Q20" s="403" t="s">
         <v>124</v>
       </c>
       <c r="R20" s="56"/>
@@ -12654,7 +12664,7 @@
       </c>
       <c r="O21" s="78"/>
       <c r="P21" s="78"/>
-      <c r="Q21" s="406"/>
+      <c r="Q21" s="405"/>
       <c r="R21" s="78"/>
       <c r="S21" s="78" t="s">
         <v>132</v>
@@ -12684,10 +12694,10 @@
       <c r="A22" s="204">
         <v>45924</v>
       </c>
-      <c r="B22" s="465" t="s">
-        <v>3070</v>
-      </c>
-      <c r="C22" s="380"/>
+      <c r="B22" s="464" t="s">
+        <v>3069</v>
+      </c>
+      <c r="C22" s="379"/>
       <c r="D22" s="86">
         <v>45924</v>
       </c>
@@ -12718,7 +12728,7 @@
       </c>
       <c r="O22" s="77"/>
       <c r="P22" s="88"/>
-      <c r="Q22" s="430" t="s">
+      <c r="Q22" s="429" t="s">
         <v>138</v>
       </c>
       <c r="R22" s="297" t="s">
@@ -12747,7 +12757,7 @@
         <v>45770</v>
       </c>
       <c r="B23" s="298"/>
-      <c r="C23" s="381"/>
+      <c r="C23" s="380"/>
       <c r="D23" s="299">
         <v>45770</v>
       </c>
@@ -12779,7 +12789,7 @@
       </c>
       <c r="O23" s="300"/>
       <c r="P23" s="300"/>
-      <c r="Q23" s="431"/>
+      <c r="Q23" s="430"/>
       <c r="R23" s="300"/>
       <c r="S23" s="300"/>
       <c r="T23" s="300"/>
@@ -12810,7 +12820,7 @@
       <c r="B24" s="214">
         <v>46076.958333333343</v>
       </c>
-      <c r="C24" s="378"/>
+      <c r="C24" s="377"/>
       <c r="D24" s="108">
         <v>45940</v>
       </c>
@@ -12909,7 +12919,7 @@
       </c>
       <c r="O25" s="102"/>
       <c r="P25" s="102"/>
-      <c r="Q25" s="405" t="s">
+      <c r="Q25" s="404" t="s">
         <v>159</v>
       </c>
       <c r="R25" s="102"/>
@@ -12970,7 +12980,7 @@
       </c>
       <c r="O26" s="303"/>
       <c r="P26" s="104"/>
-      <c r="Q26" s="430" t="s">
+      <c r="Q26" s="429" t="s">
         <v>164</v>
       </c>
       <c r="R26" s="104"/>
@@ -13017,7 +13027,7 @@
       <c r="N27" s="106"/>
       <c r="O27" s="106"/>
       <c r="P27" s="106"/>
-      <c r="Q27" s="402" t="s">
+      <c r="Q27" s="401" t="s">
         <v>168</v>
       </c>
       <c r="R27" s="106"/>
@@ -13044,7 +13054,7 @@
       <c r="B28" s="206" t="s">
         <v>169</v>
       </c>
-      <c r="C28" s="382"/>
+      <c r="C28" s="381"/>
       <c r="D28" s="296"/>
       <c r="E28" s="78"/>
       <c r="F28" s="78" t="s">
@@ -13076,7 +13086,7 @@
       <c r="P28" s="78" t="s">
         <v>176</v>
       </c>
-      <c r="Q28" s="406" t="s">
+      <c r="Q28" s="405" t="s">
         <v>177</v>
       </c>
       <c r="R28" s="78"/>
@@ -13109,7 +13119,7 @@
       <c r="B29" s="204">
         <v>45924</v>
       </c>
-      <c r="C29" s="380"/>
+      <c r="C29" s="379"/>
       <c r="D29" s="86"/>
       <c r="E29" s="88"/>
       <c r="F29" s="88" t="s">
@@ -13139,7 +13149,7 @@
       </c>
       <c r="O29" s="88"/>
       <c r="P29" s="88"/>
-      <c r="Q29" s="403" t="s">
+      <c r="Q29" s="402" t="s">
         <v>184</v>
       </c>
       <c r="R29" s="88" t="s">
@@ -13178,7 +13188,7 @@
       <c r="B30" s="203">
         <v>45924</v>
       </c>
-      <c r="C30" s="377"/>
+      <c r="C30" s="376"/>
       <c r="D30" s="80">
         <v>45909</v>
       </c>
@@ -13212,7 +13222,7 @@
       </c>
       <c r="O30" s="56"/>
       <c r="P30" s="56"/>
-      <c r="Q30" s="404" t="s">
+      <c r="Q30" s="403" t="s">
         <v>195</v>
       </c>
       <c r="R30" s="56"/>
@@ -13251,7 +13261,7 @@
         <v>45924</v>
       </c>
       <c r="B31" s="214"/>
-      <c r="C31" s="378"/>
+      <c r="C31" s="377"/>
       <c r="D31" s="108"/>
       <c r="E31" s="81" t="s">
         <v>135</v>
@@ -13338,7 +13348,7 @@
       <c r="N32" s="102"/>
       <c r="O32" s="102"/>
       <c r="P32" s="102"/>
-      <c r="Q32" s="405" t="s">
+      <c r="Q32" s="404" t="s">
         <v>210</v>
       </c>
       <c r="R32" s="102"/>
@@ -13386,7 +13396,7 @@
       <c r="N33" s="104"/>
       <c r="O33" s="104"/>
       <c r="P33" s="104"/>
-      <c r="Q33" s="407" t="s">
+      <c r="Q33" s="406" t="s">
         <v>212</v>
       </c>
       <c r="R33" s="104"/>
@@ -13443,7 +13453,7 @@
       </c>
       <c r="O34" s="106"/>
       <c r="P34" s="106"/>
-      <c r="Q34" s="402" t="s">
+      <c r="Q34" s="401" t="s">
         <v>218</v>
       </c>
       <c r="R34" s="106"/>
@@ -13474,7 +13484,7 @@
       <c r="B35" s="206">
         <v>46001</v>
       </c>
-      <c r="C35" s="382"/>
+      <c r="C35" s="381"/>
       <c r="D35" s="296">
         <v>46002</v>
       </c>
@@ -13508,7 +13518,7 @@
       <c r="N35" s="78"/>
       <c r="O35" s="78"/>
       <c r="P35" s="78"/>
-      <c r="Q35" s="406" t="s">
+      <c r="Q35" s="405" t="s">
         <v>223</v>
       </c>
       <c r="R35" s="78"/>
@@ -13535,7 +13545,7 @@
     <row r="36" spans="1:33" ht="11.45" customHeight="1">
       <c r="A36" s="203"/>
       <c r="B36" s="203"/>
-      <c r="C36" s="377"/>
+      <c r="C36" s="376"/>
       <c r="D36" s="80">
         <v>45799</v>
       </c>
@@ -13561,7 +13571,7 @@
       <c r="N36" s="56"/>
       <c r="O36" s="56"/>
       <c r="P36" s="56"/>
-      <c r="Q36" s="404"/>
+      <c r="Q36" s="403"/>
       <c r="R36" s="56"/>
       <c r="S36" s="56"/>
       <c r="T36" s="56"/>
@@ -13586,7 +13596,7 @@
       <c r="B37" s="214">
         <v>46000</v>
       </c>
-      <c r="C37" s="378"/>
+      <c r="C37" s="377"/>
       <c r="D37" s="108"/>
       <c r="E37" s="81" t="s">
         <v>58</v>
@@ -13677,7 +13687,7 @@
       </c>
       <c r="O38" s="102"/>
       <c r="P38" s="102"/>
-      <c r="Q38" s="405"/>
+      <c r="Q38" s="404"/>
       <c r="R38" s="102"/>
       <c r="S38" s="102"/>
       <c r="T38" s="102"/>
@@ -13734,7 +13744,7 @@
       </c>
       <c r="O39" s="104"/>
       <c r="P39" s="104"/>
-      <c r="Q39" s="407"/>
+      <c r="Q39" s="406"/>
       <c r="R39" s="104"/>
       <c r="S39" s="104"/>
       <c r="T39" s="104"/>
@@ -13778,7 +13788,7 @@
       <c r="N40" s="106"/>
       <c r="O40" s="106"/>
       <c r="P40" s="106"/>
-      <c r="Q40" s="402"/>
+      <c r="Q40" s="401"/>
       <c r="R40" s="106"/>
       <c r="S40" s="106"/>
       <c r="T40" s="106"/>
@@ -13799,7 +13809,7 @@
     <row r="41" spans="1:33" ht="11.45" customHeight="1">
       <c r="A41" s="206"/>
       <c r="B41" s="206"/>
-      <c r="C41" s="382"/>
+      <c r="C41" s="381"/>
       <c r="D41" s="296"/>
       <c r="E41" s="78"/>
       <c r="F41" s="78" t="s">
@@ -13825,7 +13835,7 @@
       <c r="N41" s="78"/>
       <c r="O41" s="78"/>
       <c r="P41" s="78"/>
-      <c r="Q41" s="406"/>
+      <c r="Q41" s="405"/>
       <c r="R41" s="78"/>
       <c r="S41" s="78"/>
       <c r="T41" s="78"/>
@@ -13850,7 +13860,7 @@
       <c r="B42" s="304" t="s">
         <v>117</v>
       </c>
-      <c r="C42" s="383"/>
+      <c r="C42" s="382"/>
       <c r="D42" s="305">
         <v>45839</v>
       </c>
@@ -13915,7 +13925,7 @@
       <c r="B43" s="203" t="s">
         <v>117</v>
       </c>
-      <c r="C43" s="377"/>
+      <c r="C43" s="376"/>
       <c r="D43" s="80">
         <v>45812</v>
       </c>
@@ -13949,7 +13959,7 @@
       </c>
       <c r="O43" s="56"/>
       <c r="P43" s="56"/>
-      <c r="Q43" s="404" t="s">
+      <c r="Q43" s="403" t="s">
         <v>272</v>
       </c>
       <c r="R43" s="56"/>
@@ -13978,7 +13988,7 @@
     <row r="44" spans="1:33" ht="11.45" customHeight="1">
       <c r="A44" s="214"/>
       <c r="B44" s="214"/>
-      <c r="C44" s="378"/>
+      <c r="C44" s="377"/>
       <c r="D44" s="81" t="s">
         <v>274</v>
       </c>
@@ -14059,7 +14069,7 @@
       </c>
       <c r="O45" s="102"/>
       <c r="P45" s="102"/>
-      <c r="Q45" s="405" t="s">
+      <c r="Q45" s="404" t="s">
         <v>284</v>
       </c>
       <c r="R45" s="102"/>
@@ -14124,7 +14134,7 @@
       </c>
       <c r="O46" s="104"/>
       <c r="P46" s="104"/>
-      <c r="Q46" s="407" t="s">
+      <c r="Q46" s="406" t="s">
         <v>291</v>
       </c>
       <c r="R46" s="104"/>
@@ -14183,7 +14193,7 @@
       </c>
       <c r="O47" s="106"/>
       <c r="P47" s="106"/>
-      <c r="Q47" s="402"/>
+      <c r="Q47" s="401"/>
       <c r="R47" s="106"/>
       <c r="S47" s="106"/>
       <c r="T47" s="106"/>
@@ -14212,7 +14222,7 @@
       <c r="B48" s="206">
         <v>45924</v>
       </c>
-      <c r="C48" s="382"/>
+      <c r="C48" s="381"/>
       <c r="D48" s="296"/>
       <c r="E48" s="78"/>
       <c r="F48" s="78" t="s">
@@ -14238,7 +14248,7 @@
       </c>
       <c r="O48" s="78"/>
       <c r="P48" s="78"/>
-      <c r="Q48" s="406" t="s">
+      <c r="Q48" s="405" t="s">
         <v>302</v>
       </c>
       <c r="R48" s="78"/>
@@ -14269,7 +14279,7 @@
       <c r="B49" s="204">
         <v>45924</v>
       </c>
-      <c r="C49" s="380"/>
+      <c r="C49" s="379"/>
       <c r="D49" s="86"/>
       <c r="E49" s="88"/>
       <c r="F49" s="88" t="s">
@@ -14299,7 +14309,7 @@
       </c>
       <c r="O49" s="88"/>
       <c r="P49" s="88"/>
-      <c r="Q49" s="403"/>
+      <c r="Q49" s="402"/>
       <c r="R49" s="88"/>
       <c r="S49" s="88" t="s">
         <v>309</v>
@@ -14332,7 +14342,7 @@
       <c r="B50" s="203" t="s">
         <v>311</v>
       </c>
-      <c r="C50" s="377"/>
+      <c r="C50" s="376"/>
       <c r="D50" s="80"/>
       <c r="E50" s="56" t="s">
         <v>58</v>
@@ -14360,7 +14370,7 @@
       </c>
       <c r="O50" s="56"/>
       <c r="P50" s="309"/>
-      <c r="Q50" s="404" t="s">
+      <c r="Q50" s="403" t="s">
         <v>315</v>
       </c>
       <c r="R50" s="56"/>
@@ -14387,7 +14397,7 @@
     <row r="51" spans="1:33" ht="11.45" customHeight="1" thickBot="1">
       <c r="A51" s="214"/>
       <c r="B51" s="214"/>
-      <c r="C51" s="378"/>
+      <c r="C51" s="377"/>
       <c r="D51" s="108"/>
       <c r="E51" s="81"/>
       <c r="F51" s="81"/>
@@ -14468,7 +14478,7 @@
       </c>
       <c r="O52" s="102"/>
       <c r="P52" s="102"/>
-      <c r="Q52" s="405" t="s">
+      <c r="Q52" s="404" t="s">
         <v>325</v>
       </c>
       <c r="R52" s="102"/>
@@ -14527,7 +14537,7 @@
       </c>
       <c r="O53" s="104"/>
       <c r="P53" s="104"/>
-      <c r="Q53" s="407"/>
+      <c r="Q53" s="406"/>
       <c r="R53" s="104"/>
       <c r="S53" s="104"/>
       <c r="T53" s="104"/>
@@ -14573,7 +14583,7 @@
       <c r="N54" s="106"/>
       <c r="O54" s="106"/>
       <c r="P54" s="106"/>
-      <c r="Q54" s="402"/>
+      <c r="Q54" s="401"/>
       <c r="R54" s="106"/>
       <c r="S54" s="106"/>
       <c r="T54" s="106"/>
@@ -14598,7 +14608,7 @@
       <c r="B55" s="206">
         <v>45924</v>
       </c>
-      <c r="C55" s="382"/>
+      <c r="C55" s="381"/>
       <c r="D55" s="296"/>
       <c r="E55" s="310"/>
       <c r="F55" s="78" t="s">
@@ -14628,7 +14638,7 @@
       </c>
       <c r="O55" s="312"/>
       <c r="P55" s="310"/>
-      <c r="Q55" s="406"/>
+      <c r="Q55" s="405"/>
       <c r="R55" s="310"/>
       <c r="S55" s="78"/>
       <c r="T55" s="78"/>
@@ -14655,7 +14665,7 @@
     <row r="56" spans="1:33" ht="11.45" customHeight="1">
       <c r="A56" s="204"/>
       <c r="B56" s="204"/>
-      <c r="C56" s="380"/>
+      <c r="C56" s="379"/>
       <c r="D56" s="86"/>
       <c r="E56" s="88"/>
       <c r="F56" s="88" t="s">
@@ -14681,7 +14691,7 @@
       <c r="N56" s="88"/>
       <c r="O56" s="88"/>
       <c r="P56" s="314"/>
-      <c r="Q56" s="403"/>
+      <c r="Q56" s="402"/>
       <c r="R56" s="88"/>
       <c r="S56" s="315"/>
       <c r="T56" s="315"/>
@@ -14708,7 +14718,7 @@
       <c r="B57" s="203">
         <v>45924</v>
       </c>
-      <c r="C57" s="377"/>
+      <c r="C57" s="376"/>
       <c r="D57" s="80"/>
       <c r="E57" s="56" t="s">
         <v>135</v>
@@ -14740,7 +14750,7 @@
       </c>
       <c r="O57" s="56"/>
       <c r="P57" s="56"/>
-      <c r="Q57" s="404" t="s">
+      <c r="Q57" s="403" t="s">
         <v>350</v>
       </c>
       <c r="R57" s="56"/>
@@ -14771,7 +14781,7 @@
         <v>45959</v>
       </c>
       <c r="B58" s="214"/>
-      <c r="C58" s="378"/>
+      <c r="C58" s="377"/>
       <c r="D58" s="108"/>
       <c r="E58" s="81" t="s">
         <v>27</v>
@@ -14803,7 +14813,7 @@
       </c>
       <c r="O58" s="318"/>
       <c r="P58" s="81"/>
-      <c r="Q58" s="432"/>
+      <c r="Q58" s="431"/>
       <c r="R58" s="81"/>
       <c r="S58" s="81"/>
       <c r="T58" s="81"/>
@@ -14862,7 +14872,7 @@
       </c>
       <c r="O59" s="102"/>
       <c r="P59" s="102"/>
-      <c r="Q59" s="405" t="s">
+      <c r="Q59" s="404" t="s">
         <v>365</v>
       </c>
       <c r="R59" s="102"/>
@@ -14929,7 +14939,7 @@
       </c>
       <c r="O60" s="104"/>
       <c r="P60" s="104"/>
-      <c r="Q60" s="407"/>
+      <c r="Q60" s="406"/>
       <c r="R60" s="104"/>
       <c r="S60" s="104" t="s">
         <v>373</v>
@@ -14988,7 +14998,7 @@
       <c r="N61" s="263"/>
       <c r="O61" s="263"/>
       <c r="P61" s="320"/>
-      <c r="Q61" s="422" t="s">
+      <c r="Q61" s="421" t="s">
         <v>378</v>
       </c>
       <c r="R61" s="263"/>
@@ -15045,7 +15055,7 @@
       </c>
       <c r="O62" s="272"/>
       <c r="P62" s="321"/>
-      <c r="Q62" s="423" t="s">
+      <c r="Q62" s="422" t="s">
         <v>378</v>
       </c>
       <c r="R62" s="272"/>
@@ -15072,7 +15082,7 @@
         <v>45909</v>
       </c>
       <c r="B63" s="322"/>
-      <c r="C63" s="384"/>
+      <c r="C63" s="383"/>
       <c r="D63" s="80">
         <v>45915</v>
       </c>
@@ -15106,7 +15116,7 @@
       </c>
       <c r="O63" s="56"/>
       <c r="P63" s="56"/>
-      <c r="Q63" s="404" t="s">
+      <c r="Q63" s="403" t="s">
         <v>387</v>
       </c>
       <c r="R63" s="56"/>
@@ -15145,7 +15155,7 @@
       <c r="B64" s="214">
         <v>45924</v>
       </c>
-      <c r="C64" s="378"/>
+      <c r="C64" s="377"/>
       <c r="D64" s="108"/>
       <c r="E64" s="81" t="s">
         <v>58</v>
@@ -15227,7 +15237,7 @@
       <c r="N65" s="102"/>
       <c r="O65" s="102"/>
       <c r="P65" s="102"/>
-      <c r="Q65" s="405"/>
+      <c r="Q65" s="404"/>
       <c r="R65" s="102"/>
       <c r="S65" s="102"/>
       <c r="T65" s="102"/>
@@ -15288,7 +15298,7 @@
       </c>
       <c r="O66" s="323"/>
       <c r="P66" s="104"/>
-      <c r="Q66" s="433">
+      <c r="Q66" s="432">
         <v>45909</v>
       </c>
       <c r="R66" s="104"/>
@@ -15361,7 +15371,7 @@
       </c>
       <c r="O67" s="106"/>
       <c r="P67" s="106"/>
-      <c r="Q67" s="402" t="s">
+      <c r="Q67" s="401" t="s">
         <v>417</v>
       </c>
       <c r="R67" s="324"/>
@@ -15394,7 +15404,7 @@
       <c r="B68" s="206">
         <v>45924</v>
       </c>
-      <c r="C68" s="382"/>
+      <c r="C68" s="381"/>
       <c r="D68" s="296"/>
       <c r="E68" s="78" t="s">
         <v>27</v>
@@ -15426,7 +15436,7 @@
       </c>
       <c r="O68" s="82"/>
       <c r="P68" s="78"/>
-      <c r="Q68" s="434"/>
+      <c r="Q68" s="433"/>
       <c r="R68" s="78"/>
       <c r="S68" s="78" t="s">
         <v>427</v>
@@ -15463,7 +15473,7 @@
       <c r="B69" s="204">
         <v>45924</v>
       </c>
-      <c r="C69" s="380"/>
+      <c r="C69" s="379"/>
       <c r="D69" s="86"/>
       <c r="E69" s="88" t="s">
         <v>58</v>
@@ -15495,7 +15505,7 @@
       </c>
       <c r="O69" s="88"/>
       <c r="P69" s="88"/>
-      <c r="Q69" s="403" t="s">
+      <c r="Q69" s="402" t="s">
         <v>437</v>
       </c>
       <c r="R69" s="88"/>
@@ -15534,7 +15544,7 @@
       <c r="B70" s="203">
         <v>45924</v>
       </c>
-      <c r="C70" s="377"/>
+      <c r="C70" s="376"/>
       <c r="D70" s="80"/>
       <c r="E70" s="56" t="s">
         <v>27</v>
@@ -15564,7 +15574,7 @@
       </c>
       <c r="O70" s="56"/>
       <c r="P70" s="56"/>
-      <c r="Q70" s="404"/>
+      <c r="Q70" s="403"/>
       <c r="R70" s="56"/>
       <c r="S70" s="56" t="s">
         <v>447</v>
@@ -15597,7 +15607,7 @@
       <c r="B71" s="214">
         <v>45924</v>
       </c>
-      <c r="C71" s="378"/>
+      <c r="C71" s="377"/>
       <c r="D71" s="108"/>
       <c r="E71" s="81" t="s">
         <v>27</v>
@@ -15686,7 +15696,7 @@
       </c>
       <c r="O72" s="102"/>
       <c r="P72" s="102"/>
-      <c r="Q72" s="405"/>
+      <c r="Q72" s="404"/>
       <c r="R72" s="102"/>
       <c r="S72" s="102"/>
       <c r="T72" s="102"/>
@@ -15749,7 +15759,7 @@
       </c>
       <c r="O73" s="104"/>
       <c r="P73" s="104"/>
-      <c r="Q73" s="407"/>
+      <c r="Q73" s="406"/>
       <c r="R73" s="104"/>
       <c r="S73" s="104" t="s">
         <v>467</v>
@@ -15840,7 +15850,7 @@
       <c r="B75" s="206">
         <v>46079</v>
       </c>
-      <c r="C75" s="451" t="s">
+      <c r="C75" s="450" t="s">
         <v>125</v>
       </c>
       <c r="D75" s="296">
@@ -15852,7 +15862,7 @@
       <c r="F75" s="78" t="s">
         <v>58</v>
       </c>
-      <c r="G75" s="453" t="s">
+      <c r="G75" s="452" t="s">
         <v>96</v>
       </c>
       <c r="H75" s="118" t="s">
@@ -15876,7 +15886,7 @@
       </c>
       <c r="O75" s="78"/>
       <c r="P75" s="78"/>
-      <c r="Q75" s="403" t="s">
+      <c r="Q75" s="402" t="s">
         <v>482</v>
       </c>
       <c r="R75" s="78"/>
@@ -15911,7 +15921,7 @@
       <c r="B76" s="204">
         <v>45952</v>
       </c>
-      <c r="C76" s="380"/>
+      <c r="C76" s="379"/>
       <c r="D76" s="88" t="s">
         <v>486</v>
       </c>
@@ -15943,7 +15953,7 @@
       </c>
       <c r="O76" s="88"/>
       <c r="P76" s="88"/>
-      <c r="Q76" s="403"/>
+      <c r="Q76" s="402"/>
       <c r="R76" s="88"/>
       <c r="S76" s="88"/>
       <c r="T76" s="88"/>
@@ -15970,7 +15980,7 @@
     <row r="77" spans="1:33" ht="11.45" customHeight="1">
       <c r="A77" s="203"/>
       <c r="B77" s="203"/>
-      <c r="C77" s="377"/>
+      <c r="C77" s="376"/>
       <c r="D77" s="80"/>
       <c r="E77" s="294" t="s">
         <v>27</v>
@@ -15994,7 +16004,7 @@
       <c r="N77" s="56"/>
       <c r="O77" s="56"/>
       <c r="P77" s="56"/>
-      <c r="Q77" s="404"/>
+      <c r="Q77" s="403"/>
       <c r="R77" s="56"/>
       <c r="S77" s="56"/>
       <c r="T77" s="56"/>
@@ -16017,7 +16027,7 @@
         <v>45924</v>
       </c>
       <c r="B78" s="214"/>
-      <c r="C78" s="378"/>
+      <c r="C78" s="377"/>
       <c r="D78" s="108"/>
       <c r="E78" s="81" t="s">
         <v>58</v>
@@ -16086,7 +16096,7 @@
       <c r="B79" s="208" t="s">
         <v>502</v>
       </c>
-      <c r="C79" s="385"/>
+      <c r="C79" s="384"/>
       <c r="D79" s="164">
         <v>45966</v>
       </c>
@@ -16195,7 +16205,7 @@
       </c>
       <c r="O80" s="106"/>
       <c r="P80" s="106"/>
-      <c r="Q80" s="402"/>
+      <c r="Q80" s="401"/>
       <c r="R80" s="106"/>
       <c r="S80" s="106"/>
       <c r="T80" s="106"/>
@@ -16224,7 +16234,7 @@
       <c r="B81" s="206">
         <v>45959</v>
       </c>
-      <c r="C81" s="382"/>
+      <c r="C81" s="381"/>
       <c r="D81" s="296">
         <v>45959</v>
       </c>
@@ -16258,7 +16268,7 @@
       <c r="N81" s="78"/>
       <c r="O81" s="78"/>
       <c r="P81" s="78"/>
-      <c r="Q81" s="406" t="s">
+      <c r="Q81" s="405" t="s">
         <v>523</v>
       </c>
       <c r="R81" s="78"/>
@@ -16288,76 +16298,76 @@
       <c r="AF81" s="78"/>
       <c r="AG81" s="78"/>
     </row>
-    <row r="82" spans="1:33" s="464" customFormat="1" ht="11.45" customHeight="1">
-      <c r="A82" s="458">
+    <row r="82" spans="1:33" s="463" customFormat="1" ht="11.45" customHeight="1">
+      <c r="A82" s="457">
         <v>45924</v>
       </c>
-      <c r="B82" s="458">
+      <c r="B82" s="457">
         <v>45963</v>
       </c>
-      <c r="C82" s="459"/>
-      <c r="D82" s="460" t="s">
+      <c r="C82" s="458"/>
+      <c r="D82" s="459" t="s">
         <v>528</v>
       </c>
-      <c r="E82" s="460"/>
-      <c r="F82" s="460" t="s">
+      <c r="E82" s="459"/>
+      <c r="F82" s="459" t="s">
         <v>58</v>
       </c>
-      <c r="G82" s="460"/>
-      <c r="H82" s="461" t="s">
+      <c r="G82" s="459"/>
+      <c r="H82" s="460" t="s">
         <v>529</v>
       </c>
-      <c r="I82" s="462" t="s">
+      <c r="I82" s="461" t="s">
         <v>530</v>
       </c>
-      <c r="J82" s="461" t="s">
+      <c r="J82" s="460" t="s">
         <v>531</v>
       </c>
-      <c r="K82" s="462" t="s">
+      <c r="K82" s="461" t="s">
         <v>532</v>
       </c>
-      <c r="L82" s="461" t="s">
+      <c r="L82" s="460" t="s">
         <v>533</v>
       </c>
-      <c r="M82" s="463" t="s">
+      <c r="M82" s="462" t="s">
         <v>534</v>
       </c>
-      <c r="N82" s="460" t="s">
+      <c r="N82" s="459" t="s">
         <v>32</v>
       </c>
-      <c r="O82" s="460"/>
-      <c r="P82" s="460"/>
-      <c r="Q82" s="460" t="s">
+      <c r="O82" s="459"/>
+      <c r="P82" s="459"/>
+      <c r="Q82" s="459" t="s">
         <v>535</v>
       </c>
-      <c r="R82" s="460"/>
-      <c r="S82" s="460" t="s">
+      <c r="R82" s="459"/>
+      <c r="S82" s="459" t="s">
         <v>536</v>
       </c>
-      <c r="T82" s="460" t="s">
+      <c r="T82" s="459" t="s">
         <v>179</v>
       </c>
-      <c r="U82" s="460" t="s">
+      <c r="U82" s="459" t="s">
         <v>537</v>
       </c>
-      <c r="V82" s="460"/>
-      <c r="W82" s="460" t="s">
+      <c r="V82" s="459"/>
+      <c r="W82" s="459" t="s">
         <v>538</v>
       </c>
-      <c r="X82" s="460"/>
-      <c r="Y82" s="460"/>
-      <c r="Z82" s="460" t="s">
+      <c r="X82" s="459"/>
+      <c r="Y82" s="459"/>
+      <c r="Z82" s="459" t="s">
         <v>165</v>
       </c>
-      <c r="AA82" s="460" t="s">
+      <c r="AA82" s="459" t="s">
         <v>34</v>
       </c>
-      <c r="AB82" s="460"/>
-      <c r="AC82" s="460"/>
-      <c r="AD82" s="460"/>
-      <c r="AE82" s="460"/>
-      <c r="AF82" s="460"/>
-      <c r="AG82" s="460"/>
+      <c r="AB82" s="459"/>
+      <c r="AC82" s="459"/>
+      <c r="AD82" s="459"/>
+      <c r="AE82" s="459"/>
+      <c r="AF82" s="459"/>
+      <c r="AG82" s="459"/>
     </row>
     <row r="83" spans="1:33" ht="11.45" customHeight="1">
       <c r="A83" s="203">
@@ -16366,7 +16376,7 @@
       <c r="B83" s="203">
         <v>45959</v>
       </c>
-      <c r="C83" s="377"/>
+      <c r="C83" s="376"/>
       <c r="D83" s="80">
         <v>45959</v>
       </c>
@@ -16400,7 +16410,7 @@
       </c>
       <c r="O83" s="56"/>
       <c r="P83" s="56"/>
-      <c r="Q83" s="404"/>
+      <c r="Q83" s="403"/>
       <c r="R83" s="56"/>
       <c r="S83" s="56" t="s">
         <v>543</v>
@@ -16435,7 +16445,7 @@
       <c r="B84" s="214">
         <v>45959</v>
       </c>
-      <c r="C84" s="378"/>
+      <c r="C84" s="377"/>
       <c r="D84" s="108">
         <v>45959</v>
       </c>
@@ -16540,7 +16550,7 @@
       </c>
       <c r="O85" s="102"/>
       <c r="P85" s="102"/>
-      <c r="Q85" s="405"/>
+      <c r="Q85" s="404"/>
       <c r="R85" s="102"/>
       <c r="S85" s="102" t="s">
         <v>562</v>
@@ -16567,7 +16577,7 @@
       <c r="AG85" s="102"/>
     </row>
     <row r="86" spans="1:33" ht="11.45" customHeight="1">
-      <c r="A86" s="410">
+      <c r="A86" s="409">
         <v>45930</v>
       </c>
       <c r="B86" s="205">
@@ -16600,7 +16610,7 @@
       <c r="N86" s="104"/>
       <c r="O86" s="104"/>
       <c r="P86" s="104"/>
-      <c r="Q86" s="407" t="s">
+      <c r="Q86" s="406" t="s">
         <v>569</v>
       </c>
       <c r="R86" s="104"/>
@@ -16657,7 +16667,7 @@
       </c>
       <c r="O87" s="106"/>
       <c r="P87" s="106"/>
-      <c r="Q87" s="402"/>
+      <c r="Q87" s="401"/>
       <c r="R87" s="106"/>
       <c r="S87" s="106"/>
       <c r="T87" s="106"/>
@@ -16686,7 +16696,7 @@
       <c r="B88" s="206">
         <v>45959</v>
       </c>
-      <c r="C88" s="382"/>
+      <c r="C88" s="381"/>
       <c r="D88" s="296">
         <v>45960</v>
       </c>
@@ -16716,7 +16726,7 @@
       </c>
       <c r="O88" s="78"/>
       <c r="P88" s="78"/>
-      <c r="Q88" s="406" t="s">
+      <c r="Q88" s="405" t="s">
         <v>576</v>
       </c>
       <c r="R88" s="78"/>
@@ -16747,7 +16757,7 @@
       <c r="B89" s="204" t="s">
         <v>577</v>
       </c>
-      <c r="C89" s="380"/>
+      <c r="C89" s="379"/>
       <c r="D89" s="86">
         <v>45930</v>
       </c>
@@ -16781,7 +16791,7 @@
       </c>
       <c r="O89" s="88"/>
       <c r="P89" s="88"/>
-      <c r="Q89" s="403" t="s">
+      <c r="Q89" s="402" t="s">
         <v>581</v>
       </c>
       <c r="R89" s="88"/>
@@ -16812,7 +16822,7 @@
         <v>45930</v>
       </c>
       <c r="B90" s="203"/>
-      <c r="C90" s="377"/>
+      <c r="C90" s="376"/>
       <c r="D90" s="80"/>
       <c r="E90" s="56" t="s">
         <v>27</v>
@@ -16844,7 +16854,7 @@
       </c>
       <c r="O90" s="56"/>
       <c r="P90" s="56"/>
-      <c r="Q90" s="404"/>
+      <c r="Q90" s="403"/>
       <c r="R90" s="56"/>
       <c r="S90" s="56" t="s">
         <v>590</v>
@@ -16877,7 +16887,7 @@
       <c r="B91" s="214" t="s">
         <v>591</v>
       </c>
-      <c r="C91" s="401" t="s">
+      <c r="C91" s="400" t="s">
         <v>592</v>
       </c>
       <c r="D91" s="108">
@@ -16946,7 +16956,7 @@
       <c r="B92" s="214">
         <v>46077.958333333343</v>
       </c>
-      <c r="C92" s="378"/>
+      <c r="C92" s="377"/>
       <c r="D92" s="108">
         <v>45958.958333333343</v>
       </c>
@@ -17030,7 +17040,7 @@
       </c>
       <c r="O93" s="102"/>
       <c r="P93" s="102"/>
-      <c r="Q93" s="405"/>
+      <c r="Q93" s="404"/>
       <c r="R93" s="102"/>
       <c r="S93" s="102" t="s">
         <v>524</v>
@@ -17093,7 +17103,7 @@
       </c>
       <c r="O94" s="104"/>
       <c r="P94" s="104"/>
-      <c r="Q94" s="407"/>
+      <c r="Q94" s="406"/>
       <c r="R94" s="104"/>
       <c r="S94" s="104" t="s">
         <v>614</v>
@@ -17156,7 +17166,7 @@
       </c>
       <c r="O95" s="106"/>
       <c r="P95" s="106"/>
-      <c r="Q95" s="402" t="s">
+      <c r="Q95" s="401" t="s">
         <v>620</v>
       </c>
       <c r="R95" s="106"/>
@@ -17185,7 +17195,7 @@
         <v>45930</v>
       </c>
       <c r="B96" s="206"/>
-      <c r="C96" s="382"/>
+      <c r="C96" s="381"/>
       <c r="D96" s="296"/>
       <c r="E96" s="78" t="s">
         <v>564</v>
@@ -17217,7 +17227,7 @@
       </c>
       <c r="O96" s="78"/>
       <c r="P96" s="78"/>
-      <c r="Q96" s="406" t="s">
+      <c r="Q96" s="405" t="s">
         <v>626</v>
       </c>
       <c r="R96" s="78"/>
@@ -17248,7 +17258,7 @@
       <c r="B97" s="204" t="s">
         <v>627</v>
       </c>
-      <c r="C97" s="380"/>
+      <c r="C97" s="379"/>
       <c r="D97" s="86">
         <v>45938</v>
       </c>
@@ -17278,7 +17288,7 @@
       </c>
       <c r="O97" s="88"/>
       <c r="P97" s="88"/>
-      <c r="Q97" s="403"/>
+      <c r="Q97" s="402"/>
       <c r="R97" s="88"/>
       <c r="S97" s="88"/>
       <c r="T97" s="88"/>
@@ -17307,7 +17317,7 @@
       <c r="B98" s="203">
         <v>46076.958333333343</v>
       </c>
-      <c r="C98" s="377"/>
+      <c r="C98" s="376"/>
       <c r="D98" s="80">
         <v>45966</v>
       </c>
@@ -17343,7 +17353,7 @@
       </c>
       <c r="O98" s="56"/>
       <c r="P98" s="56"/>
-      <c r="Q98" s="404" t="s">
+      <c r="Q98" s="403" t="s">
         <v>635</v>
       </c>
       <c r="R98" s="56"/>
@@ -17378,7 +17388,7 @@
       <c r="B99" s="214">
         <v>46078</v>
       </c>
-      <c r="C99" s="401" t="s">
+      <c r="C99" s="400" t="s">
         <v>639</v>
       </c>
       <c r="D99" s="108">
@@ -17470,7 +17480,7 @@
       <c r="N100" s="102"/>
       <c r="O100" s="102"/>
       <c r="P100" s="102"/>
-      <c r="Q100" s="405" t="s">
+      <c r="Q100" s="404" t="s">
         <v>649</v>
       </c>
       <c r="R100" s="102"/>
@@ -17529,7 +17539,7 @@
       </c>
       <c r="O101" s="104"/>
       <c r="P101" s="104"/>
-      <c r="Q101" s="407" t="s">
+      <c r="Q101" s="406" t="s">
         <v>649</v>
       </c>
       <c r="R101" s="104"/>
@@ -17590,7 +17600,7 @@
       </c>
       <c r="O102" s="106"/>
       <c r="P102" s="106"/>
-      <c r="Q102" s="402"/>
+      <c r="Q102" s="401"/>
       <c r="R102" s="106"/>
       <c r="S102" s="106" t="s">
         <v>658</v>
@@ -17623,7 +17633,7 @@
       <c r="B103" s="206">
         <v>45986</v>
       </c>
-      <c r="C103" s="382"/>
+      <c r="C103" s="381"/>
       <c r="D103" s="296"/>
       <c r="E103" s="78" t="s">
         <v>27</v>
@@ -17653,7 +17663,7 @@
       </c>
       <c r="O103" s="78"/>
       <c r="P103" s="78"/>
-      <c r="Q103" s="406"/>
+      <c r="Q103" s="405"/>
       <c r="R103" s="78"/>
       <c r="S103" s="78" t="s">
         <v>664</v>
@@ -17686,7 +17696,7 @@
       <c r="B104" s="204">
         <v>45986</v>
       </c>
-      <c r="C104" s="380"/>
+      <c r="C104" s="379"/>
       <c r="D104" s="86">
         <v>45986</v>
       </c>
@@ -17715,7 +17725,7 @@
       </c>
       <c r="O104" s="88"/>
       <c r="P104" s="88"/>
-      <c r="Q104" s="403"/>
+      <c r="Q104" s="402"/>
       <c r="R104" s="88"/>
       <c r="S104" s="88"/>
       <c r="T104" s="88"/>
@@ -17744,7 +17754,7 @@
       <c r="B105" s="203">
         <v>45986</v>
       </c>
-      <c r="C105" s="377"/>
+      <c r="C105" s="376"/>
       <c r="D105" s="80"/>
       <c r="E105" s="56" t="s">
         <v>27</v>
@@ -17776,7 +17786,7 @@
       </c>
       <c r="O105" s="56"/>
       <c r="P105" s="56"/>
-      <c r="Q105" s="404" t="s">
+      <c r="Q105" s="403" t="s">
         <v>673</v>
       </c>
       <c r="R105" s="56"/>
@@ -17813,7 +17823,7 @@
         <v>45979</v>
       </c>
       <c r="B106" s="330"/>
-      <c r="C106" s="386"/>
+      <c r="C106" s="385"/>
       <c r="D106" s="108">
         <v>45979</v>
       </c>
@@ -17946,10 +17956,10 @@
       <c r="A108" s="250">
         <v>45980</v>
       </c>
-      <c r="B108" s="457" t="s">
-        <v>3069</v>
-      </c>
-      <c r="C108" s="387"/>
+      <c r="B108" s="456" t="s">
+        <v>3068</v>
+      </c>
+      <c r="C108" s="386"/>
       <c r="D108" s="332">
         <v>46063</v>
       </c>
@@ -17981,7 +17991,7 @@
       </c>
       <c r="O108" s="255"/>
       <c r="P108" s="255"/>
-      <c r="Q108" s="436"/>
+      <c r="Q108" s="435"/>
       <c r="R108" s="333"/>
       <c r="S108" s="333"/>
       <c r="T108" s="333"/>
@@ -18010,7 +18020,7 @@
       <c r="B109" s="222" t="s">
         <v>696</v>
       </c>
-      <c r="C109" s="388"/>
+      <c r="C109" s="387"/>
       <c r="E109" s="335" t="s">
         <v>58</v>
       </c>
@@ -18039,7 +18049,7 @@
       </c>
       <c r="O109" s="335"/>
       <c r="P109" s="335"/>
-      <c r="Q109" s="437"/>
+      <c r="Q109" s="436"/>
       <c r="R109" s="335"/>
       <c r="S109" s="335"/>
       <c r="T109" s="335"/>
@@ -18066,7 +18076,7 @@
       <c r="B110" s="206">
         <v>46077</v>
       </c>
-      <c r="C110" s="382"/>
+      <c r="C110" s="381"/>
       <c r="D110" s="296">
         <v>45982</v>
       </c>
@@ -18100,7 +18110,7 @@
       </c>
       <c r="O110" s="89"/>
       <c r="P110" s="90"/>
-      <c r="Q110" s="438"/>
+      <c r="Q110" s="437"/>
       <c r="R110" s="78"/>
       <c r="S110" s="78"/>
       <c r="T110" s="78"/>
@@ -18129,7 +18139,7 @@
       <c r="B111" s="203">
         <v>46063</v>
       </c>
-      <c r="C111" s="377"/>
+      <c r="C111" s="376"/>
       <c r="D111" s="80"/>
       <c r="E111" s="56" t="s">
         <v>27</v>
@@ -18161,7 +18171,7 @@
       </c>
       <c r="O111" s="56"/>
       <c r="P111" s="56"/>
-      <c r="Q111" s="404"/>
+      <c r="Q111" s="403"/>
       <c r="R111" s="56"/>
       <c r="S111" s="56"/>
       <c r="T111" s="56"/>
@@ -18190,7 +18200,7 @@
       <c r="B112" s="204">
         <v>45987</v>
       </c>
-      <c r="C112" s="380"/>
+      <c r="C112" s="379"/>
       <c r="D112" s="86"/>
       <c r="E112" s="88" t="s">
         <v>27</v>
@@ -18216,7 +18226,7 @@
       </c>
       <c r="O112" s="91"/>
       <c r="P112" s="92"/>
-      <c r="Q112" s="430" t="s">
+      <c r="Q112" s="429" t="s">
         <v>690</v>
       </c>
       <c r="R112" s="88"/>
@@ -18247,7 +18257,7 @@
       <c r="B113" s="203">
         <v>46076.958333333343</v>
       </c>
-      <c r="C113" s="377"/>
+      <c r="C113" s="376"/>
       <c r="D113" s="80">
         <v>45987</v>
       </c>
@@ -18277,7 +18287,7 @@
       </c>
       <c r="O113" s="93"/>
       <c r="P113" s="94"/>
-      <c r="Q113" s="439"/>
+      <c r="Q113" s="438"/>
       <c r="R113" s="56"/>
       <c r="S113" s="56"/>
       <c r="T113" s="56"/>
@@ -18306,7 +18316,7 @@
       <c r="B114" s="214">
         <v>45988</v>
       </c>
-      <c r="C114" s="378"/>
+      <c r="C114" s="377"/>
       <c r="D114" s="108"/>
       <c r="E114" s="81" t="s">
         <v>27</v>
@@ -18401,7 +18411,7 @@
       </c>
       <c r="O115" s="102"/>
       <c r="P115" s="102"/>
-      <c r="Q115" s="405"/>
+      <c r="Q115" s="404"/>
       <c r="R115" s="102"/>
       <c r="S115" s="102"/>
       <c r="T115" s="102"/>
@@ -18464,7 +18474,7 @@
       </c>
       <c r="O116" s="104"/>
       <c r="P116" s="104"/>
-      <c r="Q116" s="407"/>
+      <c r="Q116" s="406"/>
       <c r="R116" s="104"/>
       <c r="S116" s="104"/>
       <c r="T116" s="104"/>
@@ -18523,7 +18533,7 @@
       </c>
       <c r="O117" s="106"/>
       <c r="P117" s="106"/>
-      <c r="Q117" s="402"/>
+      <c r="Q117" s="401"/>
       <c r="R117" s="106"/>
       <c r="S117" s="106"/>
       <c r="T117" s="106"/>
@@ -18550,7 +18560,7 @@
         <v>45986</v>
       </c>
       <c r="B118" s="206"/>
-      <c r="C118" s="382"/>
+      <c r="C118" s="381"/>
       <c r="D118" s="296">
         <v>45987</v>
       </c>
@@ -18586,7 +18596,7 @@
       </c>
       <c r="O118" s="78"/>
       <c r="P118" s="78"/>
-      <c r="Q118" s="406"/>
+      <c r="Q118" s="405"/>
       <c r="R118" s="78"/>
       <c r="S118" s="78"/>
       <c r="T118" s="78"/>
@@ -18615,7 +18625,7 @@
       <c r="B119" s="204">
         <v>46056</v>
       </c>
-      <c r="C119" s="389"/>
+      <c r="C119" s="388"/>
       <c r="D119" s="337"/>
       <c r="E119" s="88" t="s">
         <v>27</v>
@@ -18647,7 +18657,7 @@
       </c>
       <c r="O119" s="88"/>
       <c r="P119" s="88"/>
-      <c r="Q119" s="403"/>
+      <c r="Q119" s="402"/>
       <c r="R119" s="88"/>
       <c r="S119" s="88"/>
       <c r="T119" s="88"/>
@@ -18674,7 +18684,7 @@
         <v>45986</v>
       </c>
       <c r="B120" s="214"/>
-      <c r="C120" s="378"/>
+      <c r="C120" s="377"/>
       <c r="D120" s="108"/>
       <c r="E120" s="81" t="s">
         <v>27</v>
@@ -18763,7 +18773,7 @@
       </c>
       <c r="O121" s="102"/>
       <c r="P121" s="102"/>
-      <c r="Q121" s="405"/>
+      <c r="Q121" s="404"/>
       <c r="R121" s="102"/>
       <c r="S121" s="102"/>
       <c r="T121" s="102"/>
@@ -18824,7 +18834,7 @@
       </c>
       <c r="O122" s="282"/>
       <c r="P122" s="282"/>
-      <c r="Q122" s="427"/>
+      <c r="Q122" s="426"/>
       <c r="R122" s="282"/>
       <c r="S122" s="282"/>
       <c r="T122" s="282"/>
@@ -18853,7 +18863,7 @@
       <c r="B123" s="222" t="s">
         <v>768</v>
       </c>
-      <c r="C123" s="388"/>
+      <c r="C123" s="387"/>
       <c r="D123" s="343"/>
       <c r="E123" s="335" t="s">
         <v>58</v>
@@ -18885,7 +18895,7 @@
       </c>
       <c r="O123" s="335"/>
       <c r="P123" s="335"/>
-      <c r="Q123" s="437"/>
+      <c r="Q123" s="436"/>
       <c r="R123" s="335"/>
       <c r="S123" s="335"/>
       <c r="T123" s="335"/>
@@ -18912,7 +18922,7 @@
       <c r="B124" s="222" t="s">
         <v>768</v>
       </c>
-      <c r="C124" s="388"/>
+      <c r="C124" s="387"/>
       <c r="D124" s="268">
         <v>46072</v>
       </c>
@@ -18942,7 +18952,7 @@
       </c>
       <c r="O124" s="263"/>
       <c r="P124" s="263"/>
-      <c r="Q124" s="422"/>
+      <c r="Q124" s="421"/>
       <c r="R124" s="263"/>
       <c r="S124" s="263"/>
       <c r="T124" s="263"/>
@@ -18967,7 +18977,7 @@
       <c r="B125" s="204">
         <v>46079.958333333343</v>
       </c>
-      <c r="C125" s="380" t="s">
+      <c r="C125" s="379" t="s">
         <v>774</v>
       </c>
       <c r="D125" s="86"/>
@@ -19001,7 +19011,7 @@
       </c>
       <c r="O125" s="88"/>
       <c r="P125" s="88"/>
-      <c r="Q125" s="403"/>
+      <c r="Q125" s="402"/>
       <c r="R125" s="88"/>
       <c r="S125" s="88"/>
       <c r="T125" s="88"/>
@@ -19026,7 +19036,7 @@
     <row r="126" spans="1:33" ht="11.45" customHeight="1">
       <c r="A126" s="203"/>
       <c r="B126" s="203"/>
-      <c r="C126" s="377"/>
+      <c r="C126" s="376"/>
       <c r="D126" s="80"/>
       <c r="E126" s="56"/>
       <c r="F126" s="56"/>
@@ -19051,7 +19061,7 @@
       </c>
       <c r="O126" s="56"/>
       <c r="P126" s="56"/>
-      <c r="Q126" s="404"/>
+      <c r="Q126" s="403"/>
       <c r="R126" s="56"/>
       <c r="S126" s="56"/>
       <c r="T126" s="56"/>
@@ -19074,7 +19084,7 @@
         <v>45986</v>
       </c>
       <c r="B127" s="214"/>
-      <c r="C127" s="378"/>
+      <c r="C127" s="377"/>
       <c r="D127" s="108"/>
       <c r="E127" s="81" t="s">
         <v>27</v>
@@ -19156,7 +19166,7 @@
       <c r="N128" s="344"/>
       <c r="O128" s="102"/>
       <c r="P128" s="102"/>
-      <c r="Q128" s="440" t="s">
+      <c r="Q128" s="439" t="s">
         <v>797</v>
       </c>
       <c r="R128" s="102"/>
@@ -19213,7 +19223,7 @@
       </c>
       <c r="O129" s="104"/>
       <c r="P129" s="104"/>
-      <c r="Q129" s="407"/>
+      <c r="Q129" s="406"/>
       <c r="R129" s="104"/>
       <c r="S129" s="104"/>
       <c r="T129" s="104"/>
@@ -19264,7 +19274,7 @@
       </c>
       <c r="O130" s="106"/>
       <c r="P130" s="106"/>
-      <c r="Q130" s="402"/>
+      <c r="Q130" s="401"/>
       <c r="R130" s="106"/>
       <c r="S130" s="106"/>
       <c r="T130" s="106"/>
@@ -19291,7 +19301,7 @@
       <c r="B131" s="206">
         <v>46058</v>
       </c>
-      <c r="C131" s="382"/>
+      <c r="C131" s="381"/>
       <c r="D131" s="296"/>
       <c r="E131" s="78" t="s">
         <v>27</v>
@@ -19321,7 +19331,7 @@
       </c>
       <c r="O131" s="78"/>
       <c r="P131" s="78"/>
-      <c r="Q131" s="406"/>
+      <c r="Q131" s="405"/>
       <c r="R131" s="78"/>
       <c r="S131" s="78"/>
       <c r="T131" s="78"/>
@@ -19346,7 +19356,7 @@
     <row r="132" spans="1:33" ht="11.45" customHeight="1">
       <c r="A132" s="204"/>
       <c r="B132" s="204"/>
-      <c r="C132" s="380"/>
+      <c r="C132" s="379"/>
       <c r="D132" s="86"/>
       <c r="E132" s="88"/>
       <c r="F132" s="88"/>
@@ -19361,7 +19371,7 @@
       <c r="N132" s="337"/>
       <c r="O132" s="88"/>
       <c r="P132" s="88"/>
-      <c r="Q132" s="403"/>
+      <c r="Q132" s="402"/>
       <c r="R132" s="88"/>
       <c r="S132" s="88"/>
       <c r="T132" s="88"/>
@@ -19384,7 +19394,7 @@
       <c r="B133" s="203">
         <v>46058</v>
       </c>
-      <c r="C133" s="377"/>
+      <c r="C133" s="376"/>
       <c r="D133" s="80"/>
       <c r="E133" s="56"/>
       <c r="F133" s="56"/>
@@ -19401,7 +19411,7 @@
       <c r="N133" s="293"/>
       <c r="O133" s="56"/>
       <c r="P133" s="56"/>
-      <c r="Q133" s="404"/>
+      <c r="Q133" s="403"/>
       <c r="R133" s="56"/>
       <c r="S133" s="56"/>
       <c r="T133" s="56"/>
@@ -19426,7 +19436,7 @@
       <c r="B134" s="214">
         <v>46079.958333333343</v>
       </c>
-      <c r="C134" s="378">
+      <c r="C134" s="377">
         <v>3</v>
       </c>
       <c r="D134" s="108"/>
@@ -19523,7 +19533,7 @@
       </c>
       <c r="O135" s="102"/>
       <c r="P135" s="102"/>
-      <c r="Q135" s="405"/>
+      <c r="Q135" s="404"/>
       <c r="R135" s="102"/>
       <c r="S135" s="102"/>
       <c r="T135" s="102"/>
@@ -19573,7 +19583,7 @@
       </c>
       <c r="O136" s="104"/>
       <c r="P136" s="104"/>
-      <c r="Q136" s="407"/>
+      <c r="Q136" s="406"/>
       <c r="R136" s="104"/>
       <c r="S136" s="104"/>
       <c r="T136" s="104"/>
@@ -19596,7 +19606,7 @@
         <v>46035</v>
       </c>
       <c r="B137" s="206"/>
-      <c r="C137" s="382"/>
+      <c r="C137" s="381"/>
       <c r="D137" s="296"/>
       <c r="E137" s="78" t="s">
         <v>27</v>
@@ -19628,7 +19638,7 @@
       </c>
       <c r="O137" s="78"/>
       <c r="P137" s="78"/>
-      <c r="Q137" s="406"/>
+      <c r="Q137" s="405"/>
       <c r="R137" s="78"/>
       <c r="S137" s="78"/>
       <c r="T137" s="78"/>
@@ -19691,7 +19701,7 @@
       </c>
       <c r="O138" s="56"/>
       <c r="P138" s="56"/>
-      <c r="Q138" s="404"/>
+      <c r="Q138" s="403"/>
       <c r="R138" s="56"/>
       <c r="S138" s="56"/>
       <c r="T138" s="56"/>
@@ -19860,7 +19870,7 @@
       </c>
       <c r="O141" s="102"/>
       <c r="P141" s="102"/>
-      <c r="Q141" s="405"/>
+      <c r="Q141" s="404"/>
       <c r="R141" s="102"/>
       <c r="S141" s="102"/>
       <c r="T141" s="102"/>
@@ -19919,7 +19929,7 @@
       </c>
       <c r="O142" s="104"/>
       <c r="P142" s="104"/>
-      <c r="Q142" s="407"/>
+      <c r="Q142" s="406"/>
       <c r="R142" s="104"/>
       <c r="S142" s="104"/>
       <c r="T142" s="104"/>
@@ -19976,7 +19986,7 @@
       </c>
       <c r="O143" s="106"/>
       <c r="P143" s="106"/>
-      <c r="Q143" s="402"/>
+      <c r="Q143" s="401"/>
       <c r="R143" s="106"/>
       <c r="S143" s="106"/>
       <c r="T143" s="106"/>
@@ -20003,7 +20013,7 @@
       <c r="B144" s="206">
         <v>46058</v>
       </c>
-      <c r="C144" s="382"/>
+      <c r="C144" s="381"/>
       <c r="D144" s="296"/>
       <c r="E144" s="78" t="s">
         <v>27</v>
@@ -20035,7 +20045,7 @@
       </c>
       <c r="O144" s="78"/>
       <c r="P144" s="78"/>
-      <c r="Q144" s="406"/>
+      <c r="Q144" s="405"/>
       <c r="R144" s="78"/>
       <c r="S144" s="78"/>
       <c r="T144" s="78"/>
@@ -20060,7 +20070,7 @@
         <v>46035</v>
       </c>
       <c r="B145" s="204"/>
-      <c r="C145" s="380"/>
+      <c r="C145" s="379"/>
       <c r="D145" s="86">
         <v>46035</v>
       </c>
@@ -20096,7 +20106,7 @@
       </c>
       <c r="O145" s="88"/>
       <c r="P145" s="88"/>
-      <c r="Q145" s="403"/>
+      <c r="Q145" s="402"/>
       <c r="R145" s="88"/>
       <c r="S145" s="88"/>
       <c r="T145" s="88"/>
@@ -20123,7 +20133,7 @@
       <c r="B146" s="203">
         <v>46058</v>
       </c>
-      <c r="C146" s="377"/>
+      <c r="C146" s="376"/>
       <c r="D146" s="80"/>
       <c r="E146" s="56" t="s">
         <v>27</v>
@@ -20155,7 +20165,7 @@
       </c>
       <c r="O146" s="56"/>
       <c r="P146" s="56"/>
-      <c r="Q146" s="404"/>
+      <c r="Q146" s="403"/>
       <c r="R146" s="56"/>
       <c r="S146" s="56"/>
       <c r="T146" s="56"/>
@@ -20182,7 +20192,7 @@
       <c r="B147" s="214">
         <v>46058</v>
       </c>
-      <c r="C147" s="378"/>
+      <c r="C147" s="377"/>
       <c r="D147" s="108"/>
       <c r="E147" s="81" t="s">
         <v>27</v>
@@ -20273,7 +20283,7 @@
       </c>
       <c r="O148" s="102"/>
       <c r="P148" s="102"/>
-      <c r="Q148" s="405"/>
+      <c r="Q148" s="404"/>
       <c r="R148" s="102"/>
       <c r="S148" s="102"/>
       <c r="T148" s="102"/>
@@ -20308,7 +20318,7 @@
       <c r="F149" s="104" t="s">
         <v>58</v>
       </c>
-      <c r="G149" s="455" t="s">
+      <c r="G149" s="454" t="s">
         <v>96</v>
       </c>
       <c r="H149" s="143" t="s">
@@ -20334,7 +20344,7 @@
       </c>
       <c r="O149" s="104"/>
       <c r="P149" s="104"/>
-      <c r="Q149" s="407"/>
+      <c r="Q149" s="406"/>
       <c r="R149" s="104"/>
       <c r="S149" s="104"/>
       <c r="T149" s="104"/>
@@ -20394,7 +20404,7 @@
       </c>
       <c r="O150" s="106"/>
       <c r="P150" s="106"/>
-      <c r="Q150" s="402"/>
+      <c r="Q150" s="401"/>
       <c r="R150" s="106"/>
       <c r="S150" s="106"/>
       <c r="T150" s="106"/>
@@ -20417,7 +20427,7 @@
     <row r="151" spans="1:33" ht="11.45" customHeight="1">
       <c r="A151" s="204"/>
       <c r="B151" s="204"/>
-      <c r="C151" s="380"/>
+      <c r="C151" s="379"/>
       <c r="D151" s="86"/>
       <c r="E151" s="88"/>
       <c r="F151" s="88"/>
@@ -20443,7 +20453,7 @@
       </c>
       <c r="O151" s="88"/>
       <c r="P151" s="88"/>
-      <c r="Q151" s="403"/>
+      <c r="Q151" s="402"/>
       <c r="R151" s="88"/>
       <c r="S151" s="88"/>
       <c r="T151" s="88"/>
@@ -20464,7 +20474,7 @@
     <row r="152" spans="1:33" ht="11.45" customHeight="1">
       <c r="A152" s="203"/>
       <c r="B152" s="203"/>
-      <c r="C152" s="377"/>
+      <c r="C152" s="376"/>
       <c r="D152" s="80"/>
       <c r="E152" s="56"/>
       <c r="F152" s="56"/>
@@ -20484,7 +20494,7 @@
       <c r="N152" s="295"/>
       <c r="O152" s="56"/>
       <c r="P152" s="56"/>
-      <c r="Q152" s="404"/>
+      <c r="Q152" s="403"/>
       <c r="R152" s="56"/>
       <c r="S152" s="56"/>
       <c r="T152" s="56"/>
@@ -20521,7 +20531,7 @@
       <c r="F153" s="81" t="s">
         <v>58</v>
       </c>
-      <c r="G153" s="416" t="s">
+      <c r="G153" s="415" t="s">
         <v>96</v>
       </c>
       <c r="H153" s="142" t="s">
@@ -20608,7 +20618,7 @@
       </c>
       <c r="O154" s="102"/>
       <c r="P154" s="102"/>
-      <c r="Q154" s="405"/>
+      <c r="Q154" s="404"/>
       <c r="R154" s="102"/>
       <c r="S154" s="102"/>
       <c r="T154" s="102"/>
@@ -20635,7 +20645,7 @@
       <c r="B155" s="205">
         <v>46079.458333333343</v>
       </c>
-      <c r="C155" s="452" t="s">
+      <c r="C155" s="451" t="s">
         <v>125</v>
       </c>
       <c r="D155" s="110">
@@ -20647,7 +20657,7 @@
       <c r="F155" s="104" t="s">
         <v>58</v>
       </c>
-      <c r="G155" s="407" t="s">
+      <c r="G155" s="406" t="s">
         <v>155</v>
       </c>
       <c r="H155" s="143" t="s">
@@ -20673,7 +20683,7 @@
       <c r="P155" s="104" t="s">
         <v>176</v>
       </c>
-      <c r="Q155" s="407" t="s">
+      <c r="Q155" s="406" t="s">
         <v>926</v>
       </c>
       <c r="R155" s="104"/>
@@ -20732,7 +20742,7 @@
       </c>
       <c r="O156" s="106"/>
       <c r="P156" s="106"/>
-      <c r="Q156" s="402" t="s">
+      <c r="Q156" s="401" t="s">
         <v>932</v>
       </c>
       <c r="R156" s="106"/>
@@ -20755,7 +20765,7 @@
     <row r="157" spans="1:33" ht="11.45" customHeight="1">
       <c r="A157" s="206"/>
       <c r="B157" s="206"/>
-      <c r="C157" s="382"/>
+      <c r="C157" s="381"/>
       <c r="D157" s="296"/>
       <c r="E157" s="78"/>
       <c r="F157" s="78"/>
@@ -20777,7 +20787,7 @@
       <c r="N157" s="349"/>
       <c r="O157" s="78"/>
       <c r="P157" s="78"/>
-      <c r="Q157" s="406"/>
+      <c r="Q157" s="405"/>
       <c r="R157" s="78"/>
       <c r="S157" s="78"/>
       <c r="T157" s="78"/>
@@ -20802,7 +20812,7 @@
       <c r="B158" s="204">
         <v>46057</v>
       </c>
-      <c r="C158" s="380"/>
+      <c r="C158" s="379"/>
       <c r="D158" s="86"/>
       <c r="E158" s="88" t="s">
         <v>27</v>
@@ -20836,7 +20846,7 @@
       </c>
       <c r="O158" s="88"/>
       <c r="P158" s="88"/>
-      <c r="Q158" s="403"/>
+      <c r="Q158" s="402"/>
       <c r="R158" s="88"/>
       <c r="S158" s="88"/>
       <c r="T158" s="88"/>
@@ -20863,7 +20873,7 @@
         <v>46035</v>
       </c>
       <c r="B159" s="203"/>
-      <c r="C159" s="377"/>
+      <c r="C159" s="376"/>
       <c r="D159" s="80"/>
       <c r="E159" s="56" t="s">
         <v>58</v>
@@ -20895,7 +20905,7 @@
       </c>
       <c r="O159" s="56"/>
       <c r="P159" s="56"/>
-      <c r="Q159" s="404"/>
+      <c r="Q159" s="403"/>
       <c r="R159" s="56"/>
       <c r="S159" s="56"/>
       <c r="T159" s="56"/>
@@ -20922,7 +20932,7 @@
       <c r="B160" s="214">
         <v>46079.458333333343</v>
       </c>
-      <c r="C160" s="378" t="s">
+      <c r="C160" s="377" t="s">
         <v>949</v>
       </c>
       <c r="D160" s="108"/>
@@ -21023,7 +21033,7 @@
       </c>
       <c r="O161" s="102"/>
       <c r="P161" s="102"/>
-      <c r="Q161" s="405"/>
+      <c r="Q161" s="404"/>
       <c r="R161" s="102"/>
       <c r="S161" s="102"/>
       <c r="T161" s="102"/>
@@ -21063,7 +21073,7 @@
       <c r="N162" s="104"/>
       <c r="O162" s="104"/>
       <c r="P162" s="104"/>
-      <c r="Q162" s="407"/>
+      <c r="Q162" s="406"/>
       <c r="R162" s="104"/>
       <c r="S162" s="104"/>
       <c r="T162" s="104"/>
@@ -21086,7 +21096,7 @@
         <v>46035</v>
       </c>
       <c r="B163" s="204"/>
-      <c r="C163" s="380"/>
+      <c r="C163" s="379"/>
       <c r="D163" s="86"/>
       <c r="E163" s="88" t="s">
         <v>27</v>
@@ -21118,7 +21128,7 @@
       </c>
       <c r="O163" s="88"/>
       <c r="P163" s="88"/>
-      <c r="Q163" s="403"/>
+      <c r="Q163" s="402"/>
       <c r="R163" s="88"/>
       <c r="S163" s="88"/>
       <c r="T163" s="88"/>
@@ -21145,8 +21155,8 @@
       <c r="B164" s="206">
         <v>46098</v>
       </c>
-      <c r="C164" s="451" t="s">
-        <v>3066</v>
+      <c r="C164" s="450" t="s">
+        <v>3065</v>
       </c>
       <c r="D164" s="296"/>
       <c r="E164" s="78" t="s">
@@ -21163,10 +21173,10 @@
         <v>968</v>
       </c>
       <c r="J164" s="152" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="K164" s="120" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="L164" s="121" t="s">
         <v>969</v>
@@ -21179,7 +21189,7 @@
       </c>
       <c r="O164" s="78"/>
       <c r="P164" s="78"/>
-      <c r="Q164" s="406"/>
+      <c r="Q164" s="405"/>
       <c r="R164" s="78"/>
       <c r="S164" s="78"/>
       <c r="T164" s="78"/>
@@ -21202,7 +21212,7 @@
     <row r="165" spans="1:33" ht="11.45" customHeight="1">
       <c r="A165" s="204"/>
       <c r="B165" s="204"/>
-      <c r="C165" s="380"/>
+      <c r="C165" s="379"/>
       <c r="D165" s="86"/>
       <c r="E165" s="88"/>
       <c r="F165" s="88"/>
@@ -21217,7 +21227,7 @@
       <c r="N165" s="88"/>
       <c r="O165" s="88"/>
       <c r="P165" s="88"/>
-      <c r="Q165" s="403"/>
+      <c r="Q165" s="402"/>
       <c r="R165" s="88"/>
       <c r="S165" s="88"/>
       <c r="T165" s="88"/>
@@ -21240,7 +21250,7 @@
         <v>46052</v>
       </c>
       <c r="B166" s="203"/>
-      <c r="C166" s="377"/>
+      <c r="C166" s="376"/>
       <c r="D166" s="80"/>
       <c r="E166" s="56" t="s">
         <v>58</v>
@@ -21274,7 +21284,7 @@
       </c>
       <c r="O166" s="56"/>
       <c r="P166" s="56"/>
-      <c r="Q166" s="404"/>
+      <c r="Q166" s="403"/>
       <c r="R166" s="56"/>
       <c r="S166" s="56"/>
       <c r="T166" s="56"/>
@@ -21301,7 +21311,7 @@
       <c r="B167" s="214">
         <v>46057</v>
       </c>
-      <c r="C167" s="378"/>
+      <c r="C167" s="377"/>
       <c r="D167" s="108"/>
       <c r="E167" s="81" t="s">
         <v>27</v>
@@ -21392,7 +21402,7 @@
       </c>
       <c r="O168" s="102"/>
       <c r="P168" s="102"/>
-      <c r="Q168" s="405"/>
+      <c r="Q168" s="404"/>
       <c r="R168" s="102"/>
       <c r="S168" s="102"/>
       <c r="T168" s="102"/>
@@ -21455,7 +21465,7 @@
       <c r="P169" s="104" t="s">
         <v>176</v>
       </c>
-      <c r="Q169" s="407"/>
+      <c r="Q169" s="406"/>
       <c r="R169" s="104"/>
       <c r="S169" s="104"/>
       <c r="T169" s="104"/>
@@ -21476,7 +21486,7 @@
       <c r="AG169" s="104"/>
     </row>
     <row r="170" spans="1:33" ht="11.45" customHeight="1">
-      <c r="A170" s="412">
+      <c r="A170" s="411">
         <v>46035</v>
       </c>
       <c r="B170" s="207"/>
@@ -21506,7 +21516,7 @@
       <c r="P170" s="106" t="s">
         <v>996</v>
       </c>
-      <c r="Q170" s="402"/>
+      <c r="Q170" s="401"/>
       <c r="R170" s="106"/>
       <c r="S170" s="106"/>
       <c r="T170" s="106"/>
@@ -21531,7 +21541,7 @@
       <c r="B171" s="206">
         <v>46035</v>
       </c>
-      <c r="C171" s="382"/>
+      <c r="C171" s="381"/>
       <c r="D171" s="78" t="s">
         <v>997</v>
       </c>
@@ -21567,7 +21577,7 @@
       <c r="P171" s="78" t="s">
         <v>1004</v>
       </c>
-      <c r="Q171" s="406"/>
+      <c r="Q171" s="405"/>
       <c r="R171" s="78"/>
       <c r="S171" s="78"/>
       <c r="T171" s="78"/>
@@ -21590,7 +21600,7 @@
     <row r="172" spans="1:33" ht="11.45" customHeight="1">
       <c r="A172" s="204"/>
       <c r="B172" s="204"/>
-      <c r="C172" s="380"/>
+      <c r="C172" s="379"/>
       <c r="D172" s="86"/>
       <c r="E172" s="88"/>
       <c r="F172" s="88"/>
@@ -21609,7 +21619,7 @@
       <c r="N172" s="88"/>
       <c r="O172" s="88"/>
       <c r="P172" s="88"/>
-      <c r="Q172" s="403"/>
+      <c r="Q172" s="402"/>
       <c r="R172" s="88"/>
       <c r="S172" s="88"/>
       <c r="T172" s="88"/>
@@ -21634,7 +21644,7 @@
       <c r="B173" s="203">
         <v>46058</v>
       </c>
-      <c r="C173" s="377"/>
+      <c r="C173" s="376"/>
       <c r="D173" s="80"/>
       <c r="E173" s="56" t="s">
         <v>27</v>
@@ -21666,7 +21676,7 @@
       </c>
       <c r="O173" s="56"/>
       <c r="P173" s="56"/>
-      <c r="Q173" s="404"/>
+      <c r="Q173" s="403"/>
       <c r="R173" s="56"/>
       <c r="S173" s="56"/>
       <c r="T173" s="56"/>
@@ -21691,7 +21701,7 @@
       <c r="B174" s="214">
         <v>46056</v>
       </c>
-      <c r="C174" s="378"/>
+      <c r="C174" s="377"/>
       <c r="D174" s="108"/>
       <c r="E174" s="327" t="s">
         <v>58</v>
@@ -21784,7 +21794,7 @@
       <c r="P175" s="102" t="s">
         <v>176</v>
       </c>
-      <c r="Q175" s="405"/>
+      <c r="Q175" s="404"/>
       <c r="R175" s="102"/>
       <c r="S175" s="102"/>
       <c r="T175" s="102"/>
@@ -21845,7 +21855,7 @@
       </c>
       <c r="O176" s="104"/>
       <c r="P176" s="104"/>
-      <c r="Q176" s="407"/>
+      <c r="Q176" s="406"/>
       <c r="R176" s="104"/>
       <c r="S176" s="104"/>
       <c r="T176" s="104"/>
@@ -21904,7 +21914,7 @@
       </c>
       <c r="O177" s="106"/>
       <c r="P177" s="106"/>
-      <c r="Q177" s="402"/>
+      <c r="Q177" s="401"/>
       <c r="R177" s="106"/>
       <c r="S177" s="106"/>
       <c r="T177" s="106"/>
@@ -21931,7 +21941,7 @@
       <c r="B178" s="222">
         <v>46063</v>
       </c>
-      <c r="C178" s="388"/>
+      <c r="C178" s="387"/>
       <c r="D178" s="268">
         <v>46063</v>
       </c>
@@ -21967,7 +21977,7 @@
       </c>
       <c r="O178" s="263"/>
       <c r="P178" s="263"/>
-      <c r="Q178" s="422"/>
+      <c r="Q178" s="421"/>
       <c r="R178" s="263"/>
       <c r="S178" s="263"/>
       <c r="T178" s="263"/>
@@ -21990,7 +22000,7 @@
     <row r="179" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
       <c r="A179" s="267"/>
       <c r="B179" s="222"/>
-      <c r="C179" s="388"/>
+      <c r="C179" s="387"/>
       <c r="D179" s="268"/>
       <c r="E179" s="263"/>
       <c r="F179" s="263"/>
@@ -22010,7 +22020,7 @@
       <c r="N179" s="263"/>
       <c r="O179" s="263"/>
       <c r="P179" s="263"/>
-      <c r="Q179" s="422"/>
+      <c r="Q179" s="421"/>
       <c r="R179" s="263"/>
       <c r="S179" s="263"/>
       <c r="T179" s="263"/>
@@ -22035,7 +22045,7 @@
       <c r="B180" s="204">
         <v>46056</v>
       </c>
-      <c r="C180" s="380"/>
+      <c r="C180" s="379"/>
       <c r="D180" s="86"/>
       <c r="E180" s="88" t="s">
         <v>27</v>
@@ -22067,7 +22077,7 @@
       </c>
       <c r="O180" s="88"/>
       <c r="P180" s="88"/>
-      <c r="Q180" s="403"/>
+      <c r="Q180" s="402"/>
       <c r="R180" s="88"/>
       <c r="S180" s="88"/>
       <c r="T180" s="88"/>
@@ -22094,7 +22104,7 @@
       <c r="B181" s="203">
         <v>46058</v>
       </c>
-      <c r="C181" s="377"/>
+      <c r="C181" s="376"/>
       <c r="D181" s="80"/>
       <c r="E181" s="56" t="s">
         <v>58</v>
@@ -22126,7 +22136,7 @@
       </c>
       <c r="O181" s="56"/>
       <c r="P181" s="56"/>
-      <c r="Q181" s="404"/>
+      <c r="Q181" s="403"/>
       <c r="R181" s="56"/>
       <c r="S181" s="56"/>
       <c r="T181" s="56"/>
@@ -22151,7 +22161,7 @@
         <v>46035</v>
       </c>
       <c r="B182" s="214"/>
-      <c r="C182" s="378"/>
+      <c r="C182" s="377"/>
       <c r="D182" s="108">
         <v>46035</v>
       </c>
@@ -22246,7 +22256,7 @@
       <c r="P183" s="102" t="s">
         <v>176</v>
       </c>
-      <c r="Q183" s="405"/>
+      <c r="Q183" s="404"/>
       <c r="R183" s="102"/>
       <c r="S183" s="102"/>
       <c r="T183" s="102"/>
@@ -22305,7 +22315,7 @@
       </c>
       <c r="O184" s="104"/>
       <c r="P184" s="104"/>
-      <c r="Q184" s="407"/>
+      <c r="Q184" s="406"/>
       <c r="R184" s="104"/>
       <c r="S184" s="104"/>
       <c r="T184" s="104"/>
@@ -22364,7 +22374,7 @@
       </c>
       <c r="O185" s="106"/>
       <c r="P185" s="106"/>
-      <c r="Q185" s="402"/>
+      <c r="Q185" s="401"/>
       <c r="R185" s="106"/>
       <c r="S185" s="106"/>
       <c r="T185" s="106"/>
@@ -22391,7 +22401,7 @@
       <c r="B186" s="206">
         <v>46058</v>
       </c>
-      <c r="C186" s="382"/>
+      <c r="C186" s="381"/>
       <c r="D186" s="296"/>
       <c r="E186" s="78" t="s">
         <v>27</v>
@@ -22423,7 +22433,7 @@
       </c>
       <c r="O186" s="78"/>
       <c r="P186" s="78"/>
-      <c r="Q186" s="406"/>
+      <c r="Q186" s="405"/>
       <c r="R186" s="78"/>
       <c r="S186" s="78"/>
       <c r="T186" s="78"/>
@@ -22448,7 +22458,7 @@
         <v>46035</v>
       </c>
       <c r="B187" s="204"/>
-      <c r="C187" s="380"/>
+      <c r="C187" s="379"/>
       <c r="D187" s="86"/>
       <c r="E187" s="88" t="s">
         <v>27</v>
@@ -22484,7 +22494,7 @@
       <c r="P187" s="88" t="s">
         <v>176</v>
       </c>
-      <c r="Q187" s="403"/>
+      <c r="Q187" s="402"/>
       <c r="R187" s="88"/>
       <c r="S187" s="88"/>
       <c r="T187" s="88"/>
@@ -22507,7 +22517,7 @@
     <row r="188" spans="1:33" ht="11.45" customHeight="1">
       <c r="A188" s="203"/>
       <c r="B188" s="203"/>
-      <c r="C188" s="377"/>
+      <c r="C188" s="376"/>
       <c r="D188" s="80"/>
       <c r="E188" s="56"/>
       <c r="F188" s="56"/>
@@ -22535,7 +22545,7 @@
       </c>
       <c r="O188" s="56"/>
       <c r="P188" s="56"/>
-      <c r="Q188" s="404"/>
+      <c r="Q188" s="403"/>
       <c r="R188" s="56"/>
       <c r="S188" s="56"/>
       <c r="T188" s="56"/>
@@ -22590,7 +22600,7 @@
       </c>
       <c r="O189" s="102"/>
       <c r="P189" s="102"/>
-      <c r="Q189" s="405"/>
+      <c r="Q189" s="404"/>
       <c r="R189" s="102"/>
       <c r="S189" s="102"/>
       <c r="T189" s="102"/>
@@ -22617,7 +22627,7 @@
       <c r="B190" s="203" t="s">
         <v>1099</v>
       </c>
-      <c r="C190" s="377"/>
+      <c r="C190" s="376"/>
       <c r="D190" s="80">
         <v>46063</v>
       </c>
@@ -22653,7 +22663,7 @@
       </c>
       <c r="O190" s="56"/>
       <c r="P190" s="56"/>
-      <c r="Q190" s="404"/>
+      <c r="Q190" s="403"/>
       <c r="R190" s="56"/>
       <c r="S190" s="56"/>
       <c r="T190" s="56"/>
@@ -22682,7 +22692,7 @@
       <c r="B191" s="214">
         <v>46058</v>
       </c>
-      <c r="C191" s="378"/>
+      <c r="C191" s="377"/>
       <c r="D191" s="108"/>
       <c r="E191" s="81" t="s">
         <v>58</v>
@@ -22741,7 +22751,7 @@
       <c r="B192" s="209">
         <v>46076.958333333343</v>
       </c>
-      <c r="C192" s="400" t="s">
+      <c r="C192" s="399" t="s">
         <v>1112</v>
       </c>
       <c r="D192" s="109">
@@ -22779,7 +22789,7 @@
       </c>
       <c r="O192" s="102"/>
       <c r="P192" s="102"/>
-      <c r="Q192" s="405"/>
+      <c r="Q192" s="404"/>
       <c r="R192" s="102"/>
       <c r="S192" s="102"/>
       <c r="T192" s="102"/>
@@ -22828,7 +22838,7 @@
         <v>1119</v>
       </c>
       <c r="J193" s="126" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="K193" s="120" t="s">
         <v>1120</v>
@@ -22844,7 +22854,7 @@
       </c>
       <c r="O193" s="104"/>
       <c r="P193" s="104"/>
-      <c r="Q193" s="407"/>
+      <c r="Q193" s="406"/>
       <c r="R193" s="104"/>
       <c r="S193" s="104"/>
       <c r="T193" s="104"/>
@@ -22890,7 +22900,7 @@
       <c r="N194" s="104"/>
       <c r="O194" s="104"/>
       <c r="P194" s="104"/>
-      <c r="Q194" s="407"/>
+      <c r="Q194" s="406"/>
       <c r="R194" s="104"/>
       <c r="S194" s="104"/>
       <c r="T194" s="104"/>
@@ -22945,7 +22955,7 @@
       </c>
       <c r="O195" s="106"/>
       <c r="P195" s="106"/>
-      <c r="Q195" s="402"/>
+      <c r="Q195" s="401"/>
       <c r="R195" s="106"/>
       <c r="S195" s="106"/>
       <c r="T195" s="106"/>
@@ -22972,7 +22982,7 @@
       <c r="B196" s="206">
         <v>46058</v>
       </c>
-      <c r="C196" s="382"/>
+      <c r="C196" s="381"/>
       <c r="D196" s="296"/>
       <c r="E196" s="78" t="s">
         <v>27</v>
@@ -23004,7 +23014,7 @@
       </c>
       <c r="O196" s="78"/>
       <c r="P196" s="78"/>
-      <c r="Q196" s="406"/>
+      <c r="Q196" s="405"/>
       <c r="R196" s="78"/>
       <c r="S196" s="78"/>
       <c r="T196" s="78"/>
@@ -23031,7 +23041,7 @@
       <c r="B197" s="204">
         <v>46072</v>
       </c>
-      <c r="C197" s="380"/>
+      <c r="C197" s="379"/>
       <c r="D197" s="86"/>
       <c r="E197" s="88" t="s">
         <v>27</v>
@@ -23063,7 +23073,7 @@
       </c>
       <c r="O197" s="88"/>
       <c r="P197" s="88"/>
-      <c r="Q197" s="403"/>
+      <c r="Q197" s="402"/>
       <c r="R197" s="88"/>
       <c r="S197" s="88"/>
       <c r="T197" s="88"/>
@@ -23090,7 +23100,7 @@
       <c r="B198" s="203" t="s">
         <v>1138</v>
       </c>
-      <c r="C198" s="377"/>
+      <c r="C198" s="376"/>
       <c r="D198" s="80"/>
       <c r="E198" s="56" t="s">
         <v>58</v>
@@ -23122,7 +23132,7 @@
       </c>
       <c r="O198" s="56"/>
       <c r="P198" s="56"/>
-      <c r="Q198" s="404"/>
+      <c r="Q198" s="403"/>
       <c r="R198" s="56"/>
       <c r="S198" s="56"/>
       <c r="T198" s="56"/>
@@ -23149,7 +23159,7 @@
       <c r="B199" s="214">
         <v>46058</v>
       </c>
-      <c r="C199" s="378"/>
+      <c r="C199" s="377"/>
       <c r="D199" s="108">
         <v>45790</v>
       </c>
@@ -23204,7 +23214,7 @@
         <v>46058</v>
       </c>
       <c r="B200" s="214"/>
-      <c r="C200" s="391"/>
+      <c r="C200" s="390"/>
       <c r="D200" s="353"/>
       <c r="E200" s="81"/>
       <c r="F200" s="81"/>
@@ -23257,7 +23267,7 @@
         <v>46051</v>
       </c>
       <c r="B201" s="209"/>
-      <c r="C201" s="392"/>
+      <c r="C201" s="391"/>
       <c r="D201" s="354"/>
       <c r="E201" s="102" t="s">
         <v>27</v>
@@ -23289,7 +23299,7 @@
       </c>
       <c r="O201" s="102"/>
       <c r="P201" s="102"/>
-      <c r="Q201" s="405"/>
+      <c r="Q201" s="404"/>
       <c r="R201" s="102"/>
       <c r="S201" s="102"/>
       <c r="T201" s="102"/>
@@ -23348,7 +23358,7 @@
       </c>
       <c r="O202" s="104"/>
       <c r="P202" s="104"/>
-      <c r="Q202" s="407"/>
+      <c r="Q202" s="406"/>
       <c r="R202" s="104"/>
       <c r="S202" s="104"/>
       <c r="T202" s="104"/>
@@ -23409,7 +23419,7 @@
       </c>
       <c r="O203" s="106"/>
       <c r="P203" s="106"/>
-      <c r="Q203" s="402" t="s">
+      <c r="Q203" s="401" t="s">
         <v>1170</v>
       </c>
       <c r="R203" s="106"/>
@@ -23436,7 +23446,7 @@
         <v>46051</v>
       </c>
       <c r="B204" s="206"/>
-      <c r="C204" s="382"/>
+      <c r="C204" s="381"/>
       <c r="D204" s="296"/>
       <c r="E204" s="78" t="s">
         <v>27</v>
@@ -23468,7 +23478,7 @@
       </c>
       <c r="O204" s="78"/>
       <c r="P204" s="78"/>
-      <c r="Q204" s="406"/>
+      <c r="Q204" s="405"/>
       <c r="R204" s="78"/>
       <c r="S204" s="78"/>
       <c r="T204" s="78"/>
@@ -23495,7 +23505,7 @@
       <c r="B205" s="203">
         <v>46058</v>
       </c>
-      <c r="C205" s="377"/>
+      <c r="C205" s="376"/>
       <c r="D205" s="99"/>
       <c r="E205" s="56" t="s">
         <v>27</v>
@@ -23527,7 +23537,7 @@
       </c>
       <c r="O205" s="56"/>
       <c r="P205" s="56"/>
-      <c r="Q205" s="404"/>
+      <c r="Q205" s="403"/>
       <c r="R205" s="56"/>
       <c r="S205" s="56"/>
       <c r="T205" s="56"/>
@@ -23554,7 +23564,7 @@
       <c r="B206" s="210">
         <v>46058</v>
       </c>
-      <c r="C206" s="393"/>
+      <c r="C206" s="392"/>
       <c r="D206" s="100"/>
       <c r="E206" s="81" t="s">
         <v>27</v>
@@ -23586,7 +23596,7 @@
       </c>
       <c r="O206" s="318"/>
       <c r="P206" s="318"/>
-      <c r="Q206" s="432"/>
+      <c r="Q206" s="431"/>
       <c r="R206" s="318"/>
       <c r="S206" s="81"/>
       <c r="T206" s="81"/>
@@ -23611,7 +23621,7 @@
         <v>46051</v>
       </c>
       <c r="B207" s="211"/>
-      <c r="C207" s="394"/>
+      <c r="C207" s="393"/>
       <c r="D207" s="101" t="s">
         <v>274</v>
       </c>
@@ -23643,7 +23653,7 @@
       </c>
       <c r="O207" s="354"/>
       <c r="P207" s="354"/>
-      <c r="Q207" s="441"/>
+      <c r="Q207" s="440"/>
       <c r="R207" s="354"/>
       <c r="S207" s="102"/>
       <c r="T207" s="102"/>
@@ -23668,7 +23678,7 @@
         <v>46051</v>
       </c>
       <c r="B208" s="212"/>
-      <c r="C208" s="395"/>
+      <c r="C208" s="394"/>
       <c r="D208" s="103"/>
       <c r="E208" s="104" t="s">
         <v>58</v>
@@ -23700,7 +23710,7 @@
       </c>
       <c r="O208" s="355"/>
       <c r="P208" s="355"/>
-      <c r="Q208" s="442"/>
+      <c r="Q208" s="441"/>
       <c r="R208" s="355"/>
       <c r="S208" s="104"/>
       <c r="T208" s="104"/>
@@ -23725,7 +23735,7 @@
         <v>46051</v>
       </c>
       <c r="B209" s="213"/>
-      <c r="C209" s="396"/>
+      <c r="C209" s="395"/>
       <c r="D209" s="105"/>
       <c r="E209" s="106" t="s">
         <v>27</v>
@@ -23752,7 +23762,7 @@
       </c>
       <c r="O209" s="326"/>
       <c r="P209" s="326"/>
-      <c r="Q209" s="443"/>
+      <c r="Q209" s="442"/>
       <c r="R209" s="326"/>
       <c r="S209" s="106"/>
       <c r="T209" s="106"/>
@@ -23777,7 +23787,7 @@
       <c r="B210" s="204">
         <v>46058</v>
       </c>
-      <c r="C210" s="380"/>
+      <c r="C210" s="379"/>
       <c r="D210" s="107"/>
       <c r="E210" s="78" t="s">
         <v>27</v>
@@ -23807,7 +23817,7 @@
       </c>
       <c r="O210" s="349"/>
       <c r="P210" s="349"/>
-      <c r="Q210" s="444"/>
+      <c r="Q210" s="443"/>
       <c r="R210" s="349"/>
       <c r="S210" s="78"/>
       <c r="T210" s="78"/>
@@ -23834,7 +23844,7 @@
       <c r="B211" s="204">
         <v>46058</v>
       </c>
-      <c r="C211" s="380"/>
+      <c r="C211" s="379"/>
       <c r="D211" s="86"/>
       <c r="E211" s="88" t="s">
         <v>27</v>
@@ -23861,7 +23871,7 @@
       </c>
       <c r="O211" s="337"/>
       <c r="P211" s="337"/>
-      <c r="Q211" s="445"/>
+      <c r="Q211" s="444"/>
       <c r="R211" s="337"/>
       <c r="S211" s="88"/>
       <c r="T211" s="88"/>
@@ -23888,7 +23898,7 @@
       <c r="B212" s="203">
         <v>46058</v>
       </c>
-      <c r="C212" s="377"/>
+      <c r="C212" s="376"/>
       <c r="D212" s="80"/>
       <c r="E212" s="56" t="s">
         <v>27</v>
@@ -23918,7 +23928,7 @@
       </c>
       <c r="O212" s="293"/>
       <c r="P212" s="293"/>
-      <c r="Q212" s="446"/>
+      <c r="Q212" s="445"/>
       <c r="R212" s="293"/>
       <c r="S212" s="56"/>
       <c r="T212" s="56"/>
@@ -23945,7 +23955,7 @@
       <c r="B213" s="214">
         <v>46058</v>
       </c>
-      <c r="C213" s="378"/>
+      <c r="C213" s="377"/>
       <c r="D213" s="108"/>
       <c r="E213" s="81" t="s">
         <v>27</v>
@@ -23977,7 +23987,7 @@
       </c>
       <c r="O213" s="318"/>
       <c r="P213" s="318"/>
-      <c r="Q213" s="432"/>
+      <c r="Q213" s="431"/>
       <c r="R213" s="318"/>
       <c r="S213" s="81"/>
       <c r="T213" s="81"/>
@@ -24034,7 +24044,7 @@
       </c>
       <c r="O214" s="102"/>
       <c r="P214" s="102"/>
-      <c r="Q214" s="405"/>
+      <c r="Q214" s="404"/>
       <c r="R214" s="102"/>
       <c r="S214" s="102"/>
       <c r="T214" s="102"/>
@@ -24093,7 +24103,7 @@
       </c>
       <c r="O215" s="104"/>
       <c r="P215" s="104"/>
-      <c r="Q215" s="407"/>
+      <c r="Q215" s="406"/>
       <c r="R215" s="104"/>
       <c r="S215" s="104"/>
       <c r="T215" s="104"/>
@@ -24150,7 +24160,7 @@
       </c>
       <c r="O216" s="106"/>
       <c r="P216" s="106"/>
-      <c r="Q216" s="402"/>
+      <c r="Q216" s="401"/>
       <c r="R216" s="106"/>
       <c r="S216" s="106"/>
       <c r="T216" s="106"/>
@@ -24213,7 +24223,7 @@
       </c>
       <c r="O217" s="78"/>
       <c r="P217" s="78"/>
-      <c r="Q217" s="406"/>
+      <c r="Q217" s="405"/>
       <c r="R217" s="78"/>
       <c r="S217" s="78"/>
       <c r="T217" s="78"/>
@@ -24272,7 +24282,7 @@
       </c>
       <c r="O218" s="88"/>
       <c r="P218" s="88"/>
-      <c r="Q218" s="403"/>
+      <c r="Q218" s="402"/>
       <c r="R218" s="88"/>
       <c r="S218" s="88"/>
       <c r="T218" s="88"/>
@@ -24297,7 +24307,7 @@
         <v>46051</v>
       </c>
       <c r="B219" s="203"/>
-      <c r="C219" s="377"/>
+      <c r="C219" s="376"/>
       <c r="D219" s="80">
         <v>46051</v>
       </c>
@@ -24331,7 +24341,7 @@
       </c>
       <c r="O219" s="56"/>
       <c r="P219" s="56"/>
-      <c r="Q219" s="404"/>
+      <c r="Q219" s="403"/>
       <c r="R219" s="56"/>
       <c r="S219" s="56"/>
       <c r="T219" s="56"/>
@@ -24356,7 +24366,7 @@
         <v>46051</v>
       </c>
       <c r="B220" s="214"/>
-      <c r="C220" s="378"/>
+      <c r="C220" s="377"/>
       <c r="D220" s="108"/>
       <c r="E220" s="81" t="s">
         <v>58</v>
@@ -24449,7 +24459,7 @@
       </c>
       <c r="O221" s="102"/>
       <c r="P221" s="102"/>
-      <c r="Q221" s="405"/>
+      <c r="Q221" s="404"/>
       <c r="R221" s="102"/>
       <c r="S221" s="102"/>
       <c r="T221" s="102"/>
@@ -24512,7 +24522,7 @@
       </c>
       <c r="O222" s="104"/>
       <c r="P222" s="104"/>
-      <c r="Q222" s="407"/>
+      <c r="Q222" s="406"/>
       <c r="R222" s="104"/>
       <c r="S222" s="104"/>
       <c r="T222" s="104"/>
@@ -24571,7 +24581,7 @@
       </c>
       <c r="O223" s="106"/>
       <c r="P223" s="106"/>
-      <c r="Q223" s="402"/>
+      <c r="Q223" s="401"/>
       <c r="R223" s="106"/>
       <c r="S223" s="106"/>
       <c r="T223" s="106"/>
@@ -24596,7 +24606,7 @@
         <v>46051</v>
       </c>
       <c r="B224" s="206"/>
-      <c r="C224" s="382"/>
+      <c r="C224" s="381"/>
       <c r="D224" s="296">
         <v>46055</v>
       </c>
@@ -24630,7 +24640,7 @@
       </c>
       <c r="O224" s="78"/>
       <c r="P224" s="78"/>
-      <c r="Q224" s="406"/>
+      <c r="Q224" s="405"/>
       <c r="R224" s="78"/>
       <c r="S224" s="78"/>
       <c r="T224" s="78"/>
@@ -24655,7 +24665,7 @@
         <v>46051</v>
       </c>
       <c r="B225" s="204"/>
-      <c r="C225" s="380"/>
+      <c r="C225" s="379"/>
       <c r="D225" s="86"/>
       <c r="E225" s="88" t="s">
         <v>58</v>
@@ -24687,7 +24697,7 @@
       </c>
       <c r="O225" s="88"/>
       <c r="P225" s="88"/>
-      <c r="Q225" s="403"/>
+      <c r="Q225" s="402"/>
       <c r="R225" s="88"/>
       <c r="S225" s="88"/>
       <c r="T225" s="88"/>
@@ -24712,7 +24722,7 @@
         <v>46051</v>
       </c>
       <c r="B226" s="203"/>
-      <c r="C226" s="377"/>
+      <c r="C226" s="376"/>
       <c r="D226" s="80"/>
       <c r="E226" s="56" t="s">
         <v>58</v>
@@ -24742,7 +24752,7 @@
       <c r="N226" s="56"/>
       <c r="O226" s="56"/>
       <c r="P226" s="56"/>
-      <c r="Q226" s="404"/>
+      <c r="Q226" s="403"/>
       <c r="R226" s="56"/>
       <c r="S226" s="56"/>
       <c r="T226" s="56"/>
@@ -24767,7 +24777,7 @@
       <c r="B227" s="214">
         <v>46058</v>
       </c>
-      <c r="C227" s="378"/>
+      <c r="C227" s="377"/>
       <c r="D227" s="108">
         <v>46063</v>
       </c>
@@ -24866,7 +24876,7 @@
       </c>
       <c r="O228" s="102"/>
       <c r="P228" s="102"/>
-      <c r="Q228" s="405"/>
+      <c r="Q228" s="404"/>
       <c r="R228" s="102"/>
       <c r="S228" s="102"/>
       <c r="T228" s="102"/>
@@ -24925,7 +24935,7 @@
       <c r="P229" s="104" t="s">
         <v>1305</v>
       </c>
-      <c r="Q229" s="407"/>
+      <c r="Q229" s="406"/>
       <c r="R229" s="104"/>
       <c r="S229" s="104"/>
       <c r="T229" s="104"/>
@@ -24980,7 +24990,7 @@
       <c r="N230" s="106"/>
       <c r="O230" s="106"/>
       <c r="P230" s="106"/>
-      <c r="Q230" s="402"/>
+      <c r="Q230" s="401"/>
       <c r="R230" s="106"/>
       <c r="S230" s="106"/>
       <c r="T230" s="106"/>
@@ -25005,7 +25015,7 @@
         <v>46051</v>
       </c>
       <c r="B231" s="206"/>
-      <c r="C231" s="382"/>
+      <c r="C231" s="381"/>
       <c r="D231" s="296">
         <v>46051</v>
       </c>
@@ -25039,7 +25049,7 @@
       </c>
       <c r="O231" s="78"/>
       <c r="P231" s="78"/>
-      <c r="Q231" s="406"/>
+      <c r="Q231" s="405"/>
       <c r="R231" s="78"/>
       <c r="S231" s="78"/>
       <c r="T231" s="78"/>
@@ -25106,7 +25116,7 @@
         <v>46056</v>
       </c>
       <c r="B233" s="204"/>
-      <c r="C233" s="380"/>
+      <c r="C233" s="379"/>
       <c r="D233" s="86"/>
       <c r="E233" s="88" t="s">
         <v>58</v>
@@ -25138,7 +25148,7 @@
       </c>
       <c r="O233" s="88"/>
       <c r="P233" s="88"/>
-      <c r="Q233" s="403"/>
+      <c r="Q233" s="402"/>
       <c r="R233" s="88"/>
       <c r="S233" s="88"/>
       <c r="T233" s="88"/>
@@ -25163,7 +25173,7 @@
         <v>46056</v>
       </c>
       <c r="B234" s="203"/>
-      <c r="C234" s="377"/>
+      <c r="C234" s="376"/>
       <c r="D234" s="80"/>
       <c r="E234" s="56" t="s">
         <v>27</v>
@@ -25195,7 +25205,7 @@
       <c r="P234" s="56" t="s">
         <v>1004</v>
       </c>
-      <c r="Q234" s="404"/>
+      <c r="Q234" s="403"/>
       <c r="R234" s="56"/>
       <c r="S234" s="56"/>
       <c r="T234" s="56"/>
@@ -25220,7 +25230,7 @@
         <v>46051</v>
       </c>
       <c r="B235" s="214"/>
-      <c r="C235" s="378"/>
+      <c r="C235" s="377"/>
       <c r="D235" s="108"/>
       <c r="E235" s="81" t="s">
         <v>58</v>
@@ -25323,7 +25333,7 @@
       <c r="P236" s="102" t="s">
         <v>176</v>
       </c>
-      <c r="Q236" s="405"/>
+      <c r="Q236" s="404"/>
       <c r="R236" s="102"/>
       <c r="S236" s="102"/>
       <c r="T236" s="102"/>
@@ -25386,7 +25396,7 @@
       </c>
       <c r="O237" s="104"/>
       <c r="P237" s="104"/>
-      <c r="Q237" s="407"/>
+      <c r="Q237" s="406"/>
       <c r="R237" s="104"/>
       <c r="S237" s="104"/>
       <c r="T237" s="104"/>
@@ -25447,7 +25457,7 @@
       <c r="P238" s="106" t="s">
         <v>176</v>
       </c>
-      <c r="Q238" s="402" t="s">
+      <c r="Q238" s="401" t="s">
         <v>1351</v>
       </c>
       <c r="R238" s="106"/>
@@ -25476,7 +25486,7 @@
       <c r="B239" s="204">
         <v>46072</v>
       </c>
-      <c r="C239" s="380"/>
+      <c r="C239" s="379"/>
       <c r="D239" s="296"/>
       <c r="E239" s="78" t="s">
         <v>58</v>
@@ -25510,7 +25520,7 @@
       <c r="P239" s="78" t="s">
         <v>1004</v>
       </c>
-      <c r="Q239" s="406"/>
+      <c r="Q239" s="405"/>
       <c r="R239" s="78"/>
       <c r="S239" s="78"/>
       <c r="T239" s="78"/>
@@ -25537,7 +25547,7 @@
       <c r="B240" s="204">
         <v>46072</v>
       </c>
-      <c r="C240" s="380"/>
+      <c r="C240" s="379"/>
       <c r="D240" s="86"/>
       <c r="E240" s="88" t="s">
         <v>58</v>
@@ -25569,7 +25579,7 @@
       </c>
       <c r="O240" s="88"/>
       <c r="P240" s="88"/>
-      <c r="Q240" s="403"/>
+      <c r="Q240" s="402"/>
       <c r="R240" s="88"/>
       <c r="S240" s="88"/>
       <c r="T240" s="88"/>
@@ -25594,7 +25604,7 @@
         <v>46056</v>
       </c>
       <c r="B241" s="203"/>
-      <c r="C241" s="377"/>
+      <c r="C241" s="376"/>
       <c r="D241" s="80"/>
       <c r="E241" s="56" t="s">
         <v>27</v>
@@ -25624,7 +25634,7 @@
       <c r="N241" s="56"/>
       <c r="O241" s="56"/>
       <c r="P241" s="56"/>
-      <c r="Q241" s="404"/>
+      <c r="Q241" s="403"/>
       <c r="R241" s="56"/>
       <c r="S241" s="56"/>
       <c r="T241" s="56"/>
@@ -25651,7 +25661,7 @@
       <c r="B242" s="214">
         <v>46058</v>
       </c>
-      <c r="C242" s="378"/>
+      <c r="C242" s="377"/>
       <c r="D242" s="108"/>
       <c r="E242" s="81" t="s">
         <v>27</v>
@@ -25704,7 +25714,7 @@
       <c r="AG242" s="81"/>
     </row>
     <row r="243" spans="1:33" ht="11.45" customHeight="1">
-      <c r="A243" s="413" t="s">
+      <c r="A243" s="412" t="s">
         <v>1373</v>
       </c>
       <c r="B243" s="209"/>
@@ -25732,7 +25742,7 @@
       </c>
       <c r="O243" s="102"/>
       <c r="P243" s="102"/>
-      <c r="Q243" s="405"/>
+      <c r="Q243" s="404"/>
       <c r="R243" s="102"/>
       <c r="S243" s="102"/>
       <c r="T243" s="102"/>
@@ -25789,7 +25799,7 @@
       </c>
       <c r="O244" s="104"/>
       <c r="P244" s="104"/>
-      <c r="Q244" s="407"/>
+      <c r="Q244" s="406"/>
       <c r="R244" s="104"/>
       <c r="S244" s="104"/>
       <c r="T244" s="104"/>
@@ -25850,7 +25860,7 @@
       </c>
       <c r="O245" s="106"/>
       <c r="P245" s="106"/>
-      <c r="Q245" s="402"/>
+      <c r="Q245" s="401"/>
       <c r="R245" s="106"/>
       <c r="S245" s="106"/>
       <c r="T245" s="106"/>
@@ -25877,7 +25887,7 @@
       <c r="B246" s="206">
         <v>46070</v>
       </c>
-      <c r="C246" s="382"/>
+      <c r="C246" s="381"/>
       <c r="D246" s="296"/>
       <c r="E246" s="78" t="s">
         <v>58</v>
@@ -25911,7 +25921,7 @@
       <c r="P246" s="78" t="s">
         <v>1004</v>
       </c>
-      <c r="Q246" s="406" t="s">
+      <c r="Q246" s="405" t="s">
         <v>1392</v>
       </c>
       <c r="R246" s="78"/>
@@ -25940,7 +25950,7 @@
       <c r="B247" s="204">
         <v>46072</v>
       </c>
-      <c r="C247" s="380"/>
+      <c r="C247" s="379"/>
       <c r="D247" s="86"/>
       <c r="E247" s="88" t="s">
         <v>27</v>
@@ -25970,7 +25980,7 @@
       </c>
       <c r="O247" s="88"/>
       <c r="P247" s="88"/>
-      <c r="Q247" s="403"/>
+      <c r="Q247" s="402"/>
       <c r="R247" s="88"/>
       <c r="S247" s="88"/>
       <c r="T247" s="88"/>
@@ -25995,7 +26005,7 @@
         <v>46051</v>
       </c>
       <c r="B248" s="203"/>
-      <c r="C248" s="377"/>
+      <c r="C248" s="376"/>
       <c r="D248" s="80">
         <v>46052</v>
       </c>
@@ -26031,7 +26041,7 @@
       </c>
       <c r="O248" s="56"/>
       <c r="P248" s="56"/>
-      <c r="Q248" s="404"/>
+      <c r="Q248" s="403"/>
       <c r="R248" s="56"/>
       <c r="S248" s="56"/>
       <c r="T248" s="56"/>
@@ -26060,7 +26070,7 @@
       <c r="B249" s="214" t="s">
         <v>1405</v>
       </c>
-      <c r="C249" s="378"/>
+      <c r="C249" s="377"/>
       <c r="D249" s="108"/>
       <c r="E249" s="81" t="s">
         <v>27</v>
@@ -26149,7 +26159,7 @@
       </c>
       <c r="O250" s="102"/>
       <c r="P250" s="102"/>
-      <c r="Q250" s="405"/>
+      <c r="Q250" s="404"/>
       <c r="R250" s="102"/>
       <c r="S250" s="102"/>
       <c r="T250" s="102"/>
@@ -26210,7 +26220,7 @@
       </c>
       <c r="O251" s="104"/>
       <c r="P251" s="104"/>
-      <c r="Q251" s="407"/>
+      <c r="Q251" s="406"/>
       <c r="R251" s="104"/>
       <c r="S251" s="104"/>
       <c r="T251" s="104"/>
@@ -26267,7 +26277,7 @@
       </c>
       <c r="O252" s="106"/>
       <c r="P252" s="106"/>
-      <c r="Q252" s="402"/>
+      <c r="Q252" s="401"/>
       <c r="R252" s="106"/>
       <c r="S252" s="106"/>
       <c r="T252" s="106"/>
@@ -26292,7 +26302,7 @@
         <v>46056</v>
       </c>
       <c r="B253" s="206"/>
-      <c r="C253" s="382"/>
+      <c r="C253" s="381"/>
       <c r="D253" s="296"/>
       <c r="E253" s="78" t="s">
         <v>27</v>
@@ -26322,7 +26332,7 @@
       </c>
       <c r="O253" s="78"/>
       <c r="P253" s="78"/>
-      <c r="Q253" s="406"/>
+      <c r="Q253" s="405"/>
       <c r="R253" s="78"/>
       <c r="S253" s="78"/>
       <c r="T253" s="78"/>
@@ -26349,7 +26359,7 @@
       <c r="B254" s="204">
         <v>46058</v>
       </c>
-      <c r="C254" s="380"/>
+      <c r="C254" s="379"/>
       <c r="D254" s="86"/>
       <c r="E254" s="88" t="s">
         <v>1432</v>
@@ -26379,7 +26389,7 @@
       </c>
       <c r="O254" s="88"/>
       <c r="P254" s="88"/>
-      <c r="Q254" s="403"/>
+      <c r="Q254" s="402"/>
       <c r="R254" s="88"/>
       <c r="S254" s="88"/>
       <c r="T254" s="88"/>
@@ -26402,7 +26412,7 @@
         <v>46058</v>
       </c>
       <c r="B255" s="204"/>
-      <c r="C255" s="380"/>
+      <c r="C255" s="379"/>
       <c r="D255" s="86"/>
       <c r="E255" s="88" t="s">
         <v>1433</v>
@@ -26427,7 +26437,7 @@
       </c>
       <c r="O255" s="88"/>
       <c r="P255" s="88"/>
-      <c r="Q255" s="403"/>
+      <c r="Q255" s="402"/>
       <c r="R255" s="88"/>
       <c r="S255" s="88"/>
       <c r="T255" s="88"/>
@@ -26452,7 +26462,7 @@
       <c r="B256" s="203">
         <v>46058</v>
       </c>
-      <c r="C256" s="377"/>
+      <c r="C256" s="376"/>
       <c r="D256" s="80">
         <v>46061</v>
       </c>
@@ -26488,7 +26498,7 @@
       </c>
       <c r="O256" s="56"/>
       <c r="P256" s="56"/>
-      <c r="Q256" s="404" t="s">
+      <c r="Q256" s="403" t="s">
         <v>1445</v>
       </c>
       <c r="R256" s="56"/>
@@ -26517,7 +26527,7 @@
       <c r="B257" s="214">
         <v>46072</v>
       </c>
-      <c r="C257" s="378"/>
+      <c r="C257" s="377"/>
       <c r="D257" s="108"/>
       <c r="E257" s="81" t="s">
         <v>1433</v>
@@ -26608,7 +26618,7 @@
       </c>
       <c r="O258" s="102"/>
       <c r="P258" s="102"/>
-      <c r="Q258" s="405"/>
+      <c r="Q258" s="404"/>
       <c r="R258" s="102"/>
       <c r="S258" s="102"/>
       <c r="T258" s="102"/>
@@ -26669,7 +26679,7 @@
       </c>
       <c r="O259" s="104"/>
       <c r="P259" s="104"/>
-      <c r="Q259" s="407"/>
+      <c r="Q259" s="406"/>
       <c r="R259" s="104"/>
       <c r="S259" s="104"/>
       <c r="T259" s="104"/>
@@ -26724,7 +26734,7 @@
       </c>
       <c r="O260" s="106"/>
       <c r="P260" s="106"/>
-      <c r="Q260" s="402" t="s">
+      <c r="Q260" s="401" t="s">
         <v>1471</v>
       </c>
       <c r="R260" s="106"/>
@@ -26753,7 +26763,7 @@
       <c r="B261" s="204">
         <v>46072</v>
       </c>
-      <c r="C261" s="380"/>
+      <c r="C261" s="379"/>
       <c r="D261" s="86"/>
       <c r="E261" s="88" t="s">
         <v>1432</v>
@@ -26785,7 +26795,7 @@
       </c>
       <c r="O261" s="88"/>
       <c r="P261" s="88"/>
-      <c r="Q261" s="403" t="s">
+      <c r="Q261" s="402" t="s">
         <v>1477</v>
       </c>
       <c r="R261" s="88"/>
@@ -26812,7 +26822,7 @@
       <c r="B262" s="203">
         <v>46072</v>
       </c>
-      <c r="C262" s="377"/>
+      <c r="C262" s="376"/>
       <c r="D262" s="80"/>
       <c r="E262" s="56" t="s">
         <v>1432</v>
@@ -26844,7 +26854,7 @@
       </c>
       <c r="O262" s="56"/>
       <c r="P262" s="56"/>
-      <c r="Q262" s="404" t="s">
+      <c r="Q262" s="403" t="s">
         <v>1484</v>
       </c>
       <c r="R262" s="56"/>
@@ -26869,7 +26879,7 @@
         <v>46051</v>
       </c>
       <c r="B263" s="214"/>
-      <c r="C263" s="378"/>
+      <c r="C263" s="377"/>
       <c r="D263" s="108"/>
       <c r="E263" s="356" t="s">
         <v>1433</v>
@@ -26958,7 +26968,7 @@
       </c>
       <c r="O264" s="102"/>
       <c r="P264" s="102"/>
-      <c r="Q264" s="405" t="s">
+      <c r="Q264" s="404" t="s">
         <v>1496</v>
       </c>
       <c r="R264" s="102"/>
@@ -27015,7 +27025,7 @@
       </c>
       <c r="O265" s="104"/>
       <c r="P265" s="104"/>
-      <c r="Q265" s="407" t="s">
+      <c r="Q265" s="406" t="s">
         <v>1503</v>
       </c>
       <c r="R265" s="104"/>
@@ -27072,7 +27082,7 @@
       </c>
       <c r="O266" s="106"/>
       <c r="P266" s="106"/>
-      <c r="Q266" s="402" t="s">
+      <c r="Q266" s="401" t="s">
         <v>1509</v>
       </c>
       <c r="R266" s="106"/>
@@ -27099,7 +27109,7 @@
       <c r="B267" s="204">
         <v>46072</v>
       </c>
-      <c r="C267" s="380"/>
+      <c r="C267" s="379"/>
       <c r="D267" s="86"/>
       <c r="E267" s="88" t="s">
         <v>1432</v>
@@ -27133,7 +27143,7 @@
         <v>1516</v>
       </c>
       <c r="P267" s="337"/>
-      <c r="Q267" s="445" t="s">
+      <c r="Q267" s="444" t="s">
         <v>1517</v>
       </c>
       <c r="R267" s="88"/>
@@ -27160,7 +27170,7 @@
       <c r="B268" s="203">
         <v>46072</v>
       </c>
-      <c r="C268" s="377"/>
+      <c r="C268" s="376"/>
       <c r="D268" s="80"/>
       <c r="E268" s="56" t="s">
         <v>1432</v>
@@ -27194,7 +27204,7 @@
         <v>1524</v>
       </c>
       <c r="P268" s="56"/>
-      <c r="Q268" s="446" t="s">
+      <c r="Q268" s="445" t="s">
         <v>1525</v>
       </c>
       <c r="R268" s="56"/>
@@ -27255,7 +27265,7 @@
         <v>1532</v>
       </c>
       <c r="P269" s="102"/>
-      <c r="Q269" s="441" t="s">
+      <c r="Q269" s="440" t="s">
         <v>1533</v>
       </c>
       <c r="R269" s="102"/>
@@ -27280,7 +27290,7 @@
         <v>46057</v>
       </c>
       <c r="B270" s="358"/>
-      <c r="C270" s="397"/>
+      <c r="C270" s="396"/>
       <c r="D270" s="359"/>
       <c r="E270" s="360" t="s">
         <v>1432</v>
@@ -27316,7 +27326,7 @@
         <v>1540</v>
       </c>
       <c r="P270" s="360"/>
-      <c r="Q270" s="447"/>
+      <c r="Q270" s="446"/>
       <c r="R270" s="360"/>
       <c r="S270" s="360"/>
       <c r="T270" s="360"/>
@@ -27329,8 +27339,8 @@
       <c r="AA270" s="360" t="s">
         <v>34</v>
       </c>
-      <c r="AB270" s="456" t="s">
-        <v>3068</v>
+      <c r="AB270" s="455" t="s">
+        <v>3067</v>
       </c>
       <c r="AC270" s="360"/>
       <c r="AD270" s="360"/>
@@ -27375,7 +27385,7 @@
         <v>1545</v>
       </c>
       <c r="P271" s="102"/>
-      <c r="Q271" s="441" t="s">
+      <c r="Q271" s="440" t="s">
         <v>1546</v>
       </c>
       <c r="R271" s="102"/>
@@ -27432,7 +27442,7 @@
         <v>1551</v>
       </c>
       <c r="P272" s="104"/>
-      <c r="Q272" s="442"/>
+      <c r="Q272" s="441"/>
       <c r="R272" s="104"/>
       <c r="S272" s="104"/>
       <c r="T272" s="104"/>
@@ -27457,7 +27467,7 @@
       <c r="B273" s="204">
         <v>46072</v>
       </c>
-      <c r="C273" s="380"/>
+      <c r="C273" s="379"/>
       <c r="D273" s="86"/>
       <c r="E273" s="88" t="s">
         <v>1433</v>
@@ -27489,7 +27499,7 @@
       </c>
       <c r="O273" s="88"/>
       <c r="P273" s="88"/>
-      <c r="Q273" s="403"/>
+      <c r="Q273" s="402"/>
       <c r="R273" s="88"/>
       <c r="S273" s="88"/>
       <c r="T273" s="88"/>
@@ -27542,7 +27552,7 @@
       </c>
       <c r="O274" s="81"/>
       <c r="P274" s="81"/>
-      <c r="Q274" s="405" t="s">
+      <c r="Q274" s="404" t="s">
         <v>1563</v>
       </c>
       <c r="R274" s="81"/>
@@ -27601,7 +27611,7 @@
       </c>
       <c r="O275" s="104"/>
       <c r="P275" s="104"/>
-      <c r="Q275" s="407"/>
+      <c r="Q275" s="406"/>
       <c r="R275" s="104"/>
       <c r="S275" s="104"/>
       <c r="T275" s="104"/>
@@ -27655,7 +27665,7 @@
       </c>
       <c r="O276" s="106"/>
       <c r="P276" s="106"/>
-      <c r="Q276" s="402" t="s">
+      <c r="Q276" s="401" t="s">
         <v>1573</v>
       </c>
       <c r="R276" s="106"/>
@@ -27714,7 +27724,7 @@
         <v>1578</v>
       </c>
       <c r="P277" s="102"/>
-      <c r="Q277" s="405" t="s">
+      <c r="Q277" s="404" t="s">
         <v>1579</v>
       </c>
       <c r="R277" s="102"/>
@@ -27773,7 +27783,7 @@
         <v>1586</v>
       </c>
       <c r="P278" s="106"/>
-      <c r="Q278" s="402" t="s">
+      <c r="Q278" s="401" t="s">
         <v>1580</v>
       </c>
       <c r="R278" s="106"/>
@@ -27832,7 +27842,7 @@
         <v>1586</v>
       </c>
       <c r="P279" s="78"/>
-      <c r="Q279" s="406" t="s">
+      <c r="Q279" s="405" t="s">
         <v>1589</v>
       </c>
       <c r="R279" s="78"/>
@@ -27891,7 +27901,7 @@
         <v>1596</v>
       </c>
       <c r="P280" s="274"/>
-      <c r="Q280" s="424" t="s">
+      <c r="Q280" s="423" t="s">
         <v>1597</v>
       </c>
       <c r="R280" s="274"/>
@@ -27936,7 +27946,7 @@
       <c r="N281" s="274"/>
       <c r="O281" s="274"/>
       <c r="P281" s="274"/>
-      <c r="Q281" s="424"/>
+      <c r="Q281" s="423"/>
       <c r="R281" s="274"/>
       <c r="S281" s="274"/>
       <c r="T281" s="274"/>
@@ -27991,7 +28001,7 @@
       </c>
       <c r="O282" s="104"/>
       <c r="P282" s="104"/>
-      <c r="Q282" s="407"/>
+      <c r="Q282" s="406"/>
       <c r="R282" s="104"/>
       <c r="S282" s="104"/>
       <c r="T282" s="104"/>
@@ -28018,7 +28028,7 @@
       <c r="B283" s="362">
         <v>46072</v>
       </c>
-      <c r="C283" s="398"/>
+      <c r="C283" s="397"/>
       <c r="D283" s="109"/>
       <c r="E283" s="102" t="s">
         <v>1433</v>
@@ -28050,7 +28060,7 @@
         <v>1610</v>
       </c>
       <c r="P283" s="56"/>
-      <c r="Q283" s="404"/>
+      <c r="Q283" s="403"/>
       <c r="R283" s="56"/>
       <c r="S283" s="56"/>
       <c r="T283" s="56"/>
@@ -28103,7 +28113,7 @@
       </c>
       <c r="O284" s="102"/>
       <c r="P284" s="102"/>
-      <c r="Q284" s="405" t="s">
+      <c r="Q284" s="404" t="s">
         <v>1616</v>
       </c>
       <c r="R284" s="102"/>
@@ -28130,7 +28140,7 @@
       <c r="B285" s="206">
         <v>46072</v>
       </c>
-      <c r="C285" s="382"/>
+      <c r="C285" s="381"/>
       <c r="D285" s="296"/>
       <c r="E285" s="78" t="s">
         <v>1433</v>
@@ -28164,7 +28174,7 @@
         <v>1622</v>
       </c>
       <c r="P285" s="78"/>
-      <c r="Q285" s="406"/>
+      <c r="Q285" s="405"/>
       <c r="R285" s="78"/>
       <c r="S285" s="78"/>
       <c r="T285" s="78"/>
@@ -28223,7 +28233,7 @@
         <v>1629</v>
       </c>
       <c r="P286" s="106"/>
-      <c r="Q286" s="402" t="s">
+      <c r="Q286" s="401" t="s">
         <v>1630</v>
       </c>
       <c r="R286" s="106"/>
@@ -28250,7 +28260,7 @@
       <c r="B287" s="206">
         <v>46072</v>
       </c>
-      <c r="C287" s="382"/>
+      <c r="C287" s="381"/>
       <c r="D287" s="296"/>
       <c r="E287" s="78" t="s">
         <v>1433</v>
@@ -28284,7 +28294,7 @@
         <v>1637</v>
       </c>
       <c r="P287" s="78"/>
-      <c r="Q287" s="406"/>
+      <c r="Q287" s="405"/>
       <c r="R287" s="78"/>
       <c r="S287" s="78"/>
       <c r="T287" s="78"/>
@@ -28309,7 +28319,7 @@
       <c r="B288" s="204">
         <v>46072</v>
       </c>
-      <c r="C288" s="380"/>
+      <c r="C288" s="379"/>
       <c r="D288" s="86"/>
       <c r="E288" s="88" t="s">
         <v>1433</v>
@@ -28343,7 +28353,7 @@
         <v>1637</v>
       </c>
       <c r="P288" s="56"/>
-      <c r="Q288" s="404"/>
+      <c r="Q288" s="403"/>
       <c r="R288" s="56"/>
       <c r="S288" s="56"/>
       <c r="T288" s="56"/>
@@ -28368,7 +28378,7 @@
       <c r="B289" s="214">
         <v>46072</v>
       </c>
-      <c r="C289" s="378"/>
+      <c r="C289" s="377"/>
       <c r="D289" s="108"/>
       <c r="E289" s="81" t="s">
         <v>1433</v>
@@ -28427,7 +28437,7 @@
       <c r="B290" s="204">
         <v>46072</v>
       </c>
-      <c r="C290" s="380"/>
+      <c r="C290" s="379"/>
       <c r="D290" s="86"/>
       <c r="E290" s="88" t="s">
         <v>1432</v>
@@ -28461,7 +28471,7 @@
         <v>1655</v>
       </c>
       <c r="P290" s="88"/>
-      <c r="Q290" s="403" t="s">
+      <c r="Q290" s="402" t="s">
         <v>1656</v>
       </c>
       <c r="R290" s="88"/>
@@ -28488,7 +28498,7 @@
       <c r="B291" s="203">
         <v>46072</v>
       </c>
-      <c r="C291" s="377"/>
+      <c r="C291" s="376"/>
       <c r="D291" s="80">
         <v>46072</v>
       </c>
@@ -28526,7 +28536,7 @@
         <v>1663</v>
       </c>
       <c r="P291" s="56"/>
-      <c r="Q291" s="404"/>
+      <c r="Q291" s="403"/>
       <c r="R291" s="56"/>
       <c r="S291" s="56"/>
       <c r="T291" s="56"/>
@@ -28585,7 +28595,7 @@
         <v>1670</v>
       </c>
       <c r="P292" s="102"/>
-      <c r="Q292" s="405" t="s">
+      <c r="Q292" s="404" t="s">
         <v>1671</v>
       </c>
       <c r="R292" s="102"/>
@@ -28646,7 +28656,7 @@
         <v>1677</v>
       </c>
       <c r="P293" s="104"/>
-      <c r="Q293" s="407" t="s">
+      <c r="Q293" s="406" t="s">
         <v>1678</v>
       </c>
       <c r="R293" s="104"/>
@@ -28703,7 +28713,7 @@
       </c>
       <c r="O294" s="104"/>
       <c r="P294" s="104"/>
-      <c r="Q294" s="407" t="s">
+      <c r="Q294" s="406" t="s">
         <v>1685</v>
       </c>
       <c r="R294" s="104"/>
@@ -28762,7 +28772,7 @@
       </c>
       <c r="O295" s="106"/>
       <c r="P295" s="106"/>
-      <c r="Q295" s="402" t="s">
+      <c r="Q295" s="401" t="s">
         <v>1691</v>
       </c>
       <c r="R295" s="106"/>
@@ -28789,7 +28799,7 @@
       <c r="B296" s="206" t="s">
         <v>1099</v>
       </c>
-      <c r="C296" s="382"/>
+      <c r="C296" s="381"/>
       <c r="D296" s="296"/>
       <c r="E296" s="78" t="s">
         <v>1432</v>
@@ -28823,7 +28833,7 @@
       </c>
       <c r="O296" s="78"/>
       <c r="P296" s="78"/>
-      <c r="Q296" s="406" t="s">
+      <c r="Q296" s="405" t="s">
         <v>1697</v>
       </c>
       <c r="R296" s="78"/>
@@ -28852,7 +28862,7 @@
       <c r="B297" s="204">
         <v>46057</v>
       </c>
-      <c r="C297" s="380"/>
+      <c r="C297" s="379"/>
       <c r="D297" s="86"/>
       <c r="E297" s="88" t="s">
         <v>1432</v>
@@ -28886,7 +28896,7 @@
       </c>
       <c r="O297" s="88"/>
       <c r="P297" s="88"/>
-      <c r="Q297" s="403" t="s">
+      <c r="Q297" s="402" t="s">
         <v>1704</v>
       </c>
       <c r="R297" s="88"/>
@@ -28947,7 +28957,7 @@
         <v>1711</v>
       </c>
       <c r="P298" s="104"/>
-      <c r="Q298" s="407"/>
+      <c r="Q298" s="406"/>
       <c r="R298" s="104"/>
       <c r="S298" s="104"/>
       <c r="T298" s="104"/>
@@ -29004,7 +29014,7 @@
         <v>1711</v>
       </c>
       <c r="P299" s="106"/>
-      <c r="Q299" s="402"/>
+      <c r="Q299" s="401"/>
       <c r="R299" s="106"/>
       <c r="S299" s="106"/>
       <c r="T299" s="106"/>
@@ -29029,7 +29039,7 @@
       <c r="B300" s="206">
         <v>46072</v>
       </c>
-      <c r="C300" s="382"/>
+      <c r="C300" s="381"/>
       <c r="D300" s="296"/>
       <c r="E300" s="78" t="s">
         <v>1432</v>
@@ -29063,7 +29073,7 @@
         <v>1711</v>
       </c>
       <c r="P300" s="78"/>
-      <c r="Q300" s="406"/>
+      <c r="Q300" s="405"/>
       <c r="R300" s="78"/>
       <c r="S300" s="78"/>
       <c r="T300" s="78"/>
@@ -29088,7 +29098,7 @@
       <c r="B301" s="204">
         <v>46072</v>
       </c>
-      <c r="C301" s="380"/>
+      <c r="C301" s="379"/>
       <c r="D301" s="86"/>
       <c r="E301" s="88" t="s">
         <v>1432</v>
@@ -29122,7 +29132,7 @@
         <v>1711</v>
       </c>
       <c r="P301" s="88"/>
-      <c r="Q301" s="403"/>
+      <c r="Q301" s="402"/>
       <c r="R301" s="88"/>
       <c r="S301" s="88"/>
       <c r="T301" s="88"/>
@@ -29147,7 +29157,7 @@
       <c r="B302" s="203">
         <v>46072</v>
       </c>
-      <c r="C302" s="377"/>
+      <c r="C302" s="376"/>
       <c r="D302" s="80"/>
       <c r="E302" s="56" t="s">
         <v>1433</v>
@@ -29183,7 +29193,7 @@
         <v>1711</v>
       </c>
       <c r="P302" s="56"/>
-      <c r="Q302" s="404"/>
+      <c r="Q302" s="403"/>
       <c r="R302" s="56"/>
       <c r="S302" s="56"/>
       <c r="T302" s="56"/>
@@ -29204,7 +29214,7 @@
     <row r="303" spans="1:33" ht="11.45" customHeight="1">
       <c r="A303" s="214"/>
       <c r="B303" s="214"/>
-      <c r="C303" s="378"/>
+      <c r="C303" s="377"/>
       <c r="D303" s="108"/>
       <c r="E303" s="81"/>
       <c r="F303" s="81"/>
@@ -29281,7 +29291,7 @@
         <v>1711</v>
       </c>
       <c r="P304" s="102"/>
-      <c r="Q304" s="405"/>
+      <c r="Q304" s="404"/>
       <c r="R304" s="102"/>
       <c r="S304" s="102"/>
       <c r="T304" s="102"/>
@@ -29340,7 +29350,7 @@
         <v>1711</v>
       </c>
       <c r="P305" s="104"/>
-      <c r="Q305" s="407"/>
+      <c r="Q305" s="406"/>
       <c r="R305" s="104"/>
       <c r="S305" s="104"/>
       <c r="T305" s="104"/>
@@ -29359,10 +29369,10 @@
       <c r="AG305" s="104"/>
     </row>
     <row r="306" spans="1:33" s="121" customFormat="1" ht="11.45" customHeight="1">
-      <c r="A306" s="414">
+      <c r="A306" s="413">
         <v>46066</v>
       </c>
-      <c r="C306" s="399"/>
+      <c r="C306" s="398"/>
       <c r="G306" s="219" t="s">
         <v>997</v>
       </c>
@@ -29390,17 +29400,17 @@
       <c r="O306" s="121" t="s">
         <v>1637</v>
       </c>
-      <c r="Q306" s="448"/>
+      <c r="Q306" s="447"/>
       <c r="AA306" s="121" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="307" spans="1:33" ht="11.45" customHeight="1">
-      <c r="A307" s="414">
+      <c r="A307" s="413">
         <v>46077</v>
       </c>
       <c r="B307" s="214"/>
-      <c r="C307" s="378"/>
+      <c r="C307" s="377"/>
       <c r="D307" s="108"/>
       <c r="E307" s="81" t="s">
         <v>27</v>
@@ -29446,13 +29456,13 @@
       <c r="AG307" s="81"/>
     </row>
     <row r="308" spans="1:33" ht="11.45" customHeight="1">
-      <c r="A308" s="414">
+      <c r="A308" s="413">
         <v>46077</v>
       </c>
       <c r="B308" s="203">
         <v>46077</v>
       </c>
-      <c r="C308" s="377"/>
+      <c r="C308" s="376"/>
       <c r="D308" s="80"/>
       <c r="E308" s="56" t="s">
         <v>58</v>
@@ -29484,7 +29494,7 @@
         <v>1759</v>
       </c>
       <c r="P308" s="56"/>
-      <c r="Q308" s="404"/>
+      <c r="Q308" s="403"/>
       <c r="R308" s="56"/>
       <c r="S308" s="56"/>
       <c r="T308" s="56"/>
@@ -29529,7 +29539,7 @@
         <v>1711</v>
       </c>
       <c r="P309" s="102"/>
-      <c r="Q309" s="405"/>
+      <c r="Q309" s="404"/>
       <c r="R309" s="102"/>
       <c r="S309" s="102"/>
       <c r="T309" s="102"/>
@@ -29581,7 +29591,7 @@
         <v>1622</v>
       </c>
       <c r="P310" s="104"/>
-      <c r="Q310" s="407"/>
+      <c r="Q310" s="406"/>
       <c r="R310" s="104"/>
       <c r="S310" s="104"/>
       <c r="T310" s="104"/>
@@ -29633,7 +29643,7 @@
         <v>1773</v>
       </c>
       <c r="P311" s="106"/>
-      <c r="Q311" s="402"/>
+      <c r="Q311" s="401"/>
       <c r="R311" s="106"/>
       <c r="S311" s="106"/>
       <c r="T311" s="106"/>
@@ -29656,7 +29666,7 @@
         <v>46077</v>
       </c>
       <c r="B312" s="206"/>
-      <c r="C312" s="382"/>
+      <c r="C312" s="381"/>
       <c r="D312" s="296"/>
       <c r="E312" s="78" t="s">
         <v>1432</v>
@@ -29688,7 +29698,7 @@
         <v>1622</v>
       </c>
       <c r="P312" s="78"/>
-      <c r="Q312" s="406"/>
+      <c r="Q312" s="405"/>
       <c r="R312" s="78"/>
       <c r="S312" s="78"/>
       <c r="T312" s="78"/>
@@ -29711,7 +29721,7 @@
         <v>46077</v>
       </c>
       <c r="B313" s="204"/>
-      <c r="C313" s="380"/>
+      <c r="C313" s="379"/>
       <c r="D313" s="86"/>
       <c r="E313" s="88" t="s">
         <v>1432</v>
@@ -29743,7 +29753,7 @@
         <v>1622</v>
       </c>
       <c r="P313" s="88"/>
-      <c r="Q313" s="403"/>
+      <c r="Q313" s="402"/>
       <c r="R313" s="88"/>
       <c r="S313" s="88"/>
       <c r="T313" s="88"/>
@@ -29766,7 +29776,7 @@
         <v>46077</v>
       </c>
       <c r="B314" s="203"/>
-      <c r="C314" s="377"/>
+      <c r="C314" s="376"/>
       <c r="D314" s="80"/>
       <c r="E314" s="56" t="s">
         <v>27</v>
@@ -29800,7 +29810,7 @@
         <v>1773</v>
       </c>
       <c r="P314" s="56"/>
-      <c r="Q314" s="404" t="s">
+      <c r="Q314" s="403" t="s">
         <v>1789</v>
       </c>
       <c r="R314" s="56"/>
@@ -29851,7 +29861,7 @@
       <c r="F315" s="102" t="s">
         <v>58</v>
       </c>
-      <c r="G315" s="405" t="s">
+      <c r="G315" s="404" t="s">
         <v>997</v>
       </c>
       <c r="H315" s="119" t="s">
@@ -29872,7 +29882,7 @@
         <v>1637</v>
       </c>
       <c r="P315" s="102"/>
-      <c r="Q315" s="405"/>
+      <c r="Q315" s="404"/>
       <c r="R315" s="102"/>
       <c r="S315" s="102"/>
       <c r="T315" s="102"/>
@@ -29929,7 +29939,7 @@
         <v>1637</v>
       </c>
       <c r="P316" s="106"/>
-      <c r="Q316" s="402" t="s">
+      <c r="Q316" s="401" t="s">
         <v>1805</v>
       </c>
       <c r="R316" s="106" t="s">
@@ -29974,12 +29984,12 @@
         <v>46077</v>
       </c>
       <c r="B317" s="206"/>
-      <c r="C317" s="382"/>
+      <c r="C317" s="381"/>
       <c r="D317" s="296"/>
-      <c r="E317" s="406" t="s">
+      <c r="E317" s="405" t="s">
         <v>58</v>
       </c>
-      <c r="F317" s="406" t="s">
+      <c r="F317" s="405" t="s">
         <v>27</v>
       </c>
       <c r="G317" s="78"/>
@@ -30002,7 +30012,7 @@
         <v>1711</v>
       </c>
       <c r="P317" s="78"/>
-      <c r="Q317" s="406"/>
+      <c r="Q317" s="405"/>
       <c r="R317" s="78"/>
       <c r="S317" s="78"/>
       <c r="T317" s="78"/>
@@ -30025,7 +30035,7 @@
         <v>46079</v>
       </c>
       <c r="B318" s="204"/>
-      <c r="C318" s="380"/>
+      <c r="C318" s="379"/>
       <c r="D318" s="86"/>
       <c r="E318" s="88" t="s">
         <v>1432</v>
@@ -30055,7 +30065,7 @@
         <v>1622</v>
       </c>
       <c r="P318" s="88"/>
-      <c r="Q318" s="403"/>
+      <c r="Q318" s="402"/>
       <c r="R318" s="88"/>
       <c r="S318" s="88"/>
       <c r="T318" s="88"/>
@@ -30078,7 +30088,7 @@
         <v>46079</v>
       </c>
       <c r="B319" s="203"/>
-      <c r="C319" s="377"/>
+      <c r="C319" s="376"/>
       <c r="D319" s="80"/>
       <c r="E319" s="56" t="s">
         <v>1432</v>
@@ -30110,7 +30120,7 @@
         <v>1622</v>
       </c>
       <c r="P319" s="56"/>
-      <c r="Q319" s="404"/>
+      <c r="Q319" s="403"/>
       <c r="R319" s="56"/>
       <c r="S319" s="56"/>
       <c r="T319" s="56"/>
@@ -30133,7 +30143,7 @@
         <v>46079</v>
       </c>
       <c r="B320" s="214"/>
-      <c r="C320" s="378"/>
+      <c r="C320" s="377"/>
       <c r="D320" s="108">
         <v>46079</v>
       </c>
@@ -30143,7 +30153,7 @@
       <c r="F320" s="81" t="s">
         <v>1432</v>
       </c>
-      <c r="G320" s="416" t="s">
+      <c r="G320" s="415" t="s">
         <v>135</v>
       </c>
       <c r="H320" s="123" t="s">
@@ -30224,7 +30234,7 @@
         <v>1622</v>
       </c>
       <c r="P321" s="102"/>
-      <c r="Q321" s="405"/>
+      <c r="Q321" s="404"/>
       <c r="R321" s="102"/>
       <c r="S321" s="102"/>
       <c r="T321" s="102"/>
@@ -30277,7 +30287,7 @@
         <v>1622</v>
       </c>
       <c r="P322" s="104"/>
-      <c r="Q322" s="407"/>
+      <c r="Q322" s="406"/>
       <c r="R322" s="104"/>
       <c r="S322" s="104"/>
       <c r="T322" s="104"/>
@@ -30300,7 +30310,7 @@
         <v>46079</v>
       </c>
       <c r="B323" s="214"/>
-      <c r="C323" s="378"/>
+      <c r="C323" s="377"/>
       <c r="D323" s="108"/>
       <c r="E323" s="81" t="s">
         <v>27</v>
@@ -30377,7 +30387,7 @@
         <v>46079</v>
       </c>
       <c r="B324" s="214"/>
-      <c r="C324" s="378"/>
+      <c r="C324" s="377"/>
       <c r="D324" s="108"/>
       <c r="E324" s="76" t="s">
         <v>27</v>
@@ -30456,7 +30466,7 @@
         <v>46079</v>
       </c>
       <c r="B325" s="204"/>
-      <c r="C325" s="380"/>
+      <c r="C325" s="379"/>
       <c r="D325" s="86"/>
       <c r="E325" s="88" t="s">
         <v>27</v>
@@ -30490,7 +30500,7 @@
         <v>1773</v>
       </c>
       <c r="P325" s="88"/>
-      <c r="Q325" s="403" t="s">
+      <c r="Q325" s="402" t="s">
         <v>1872</v>
       </c>
       <c r="R325" s="88" t="s">
@@ -30533,7 +30543,7 @@
         <v>46079</v>
       </c>
       <c r="B326" s="206"/>
-      <c r="C326" s="382"/>
+      <c r="C326" s="381"/>
       <c r="D326" s="296">
         <v>46079</v>
       </c>
@@ -30543,7 +30553,7 @@
       <c r="F326" s="78" t="s">
         <v>58</v>
       </c>
-      <c r="G326" s="453" t="s">
+      <c r="G326" s="452" t="s">
         <v>1880</v>
       </c>
       <c r="H326" s="118" t="s">
@@ -30571,7 +30581,7 @@
         <v>1773</v>
       </c>
       <c r="P326" s="78"/>
-      <c r="Q326" s="406" t="s">
+      <c r="Q326" s="405" t="s">
         <v>1887</v>
       </c>
       <c r="R326" s="78"/>
@@ -30614,7 +30624,7 @@
         <v>46079</v>
       </c>
       <c r="B327" s="204"/>
-      <c r="C327" s="380"/>
+      <c r="C327" s="379"/>
       <c r="D327" s="86"/>
       <c r="E327" s="88" t="s">
         <v>58</v>
@@ -30648,7 +30658,7 @@
         <v>1773</v>
       </c>
       <c r="P327" s="88"/>
-      <c r="Q327" s="403" t="s">
+      <c r="Q327" s="402" t="s">
         <v>1901</v>
       </c>
       <c r="R327" s="88" t="s">
@@ -30723,7 +30733,7 @@
         <v>1773</v>
       </c>
       <c r="P328" s="102"/>
-      <c r="Q328" s="405" t="s">
+      <c r="Q328" s="404" t="s">
         <v>1914</v>
       </c>
       <c r="R328" s="102" t="s">
@@ -30768,7 +30778,7 @@
         <v>46079</v>
       </c>
       <c r="B329" s="204"/>
-      <c r="C329" s="380"/>
+      <c r="C329" s="379"/>
       <c r="D329" s="86"/>
       <c r="E329" s="88" t="s">
         <v>27</v>
@@ -30802,7 +30812,7 @@
         <v>1773</v>
       </c>
       <c r="P329" s="88"/>
-      <c r="Q329" s="403" t="s">
+      <c r="Q329" s="402" t="s">
         <v>1929</v>
       </c>
       <c r="R329" s="88" t="s">
@@ -30881,7 +30891,7 @@
         <v>1773</v>
       </c>
       <c r="P330" s="102"/>
-      <c r="Q330" s="405" t="s">
+      <c r="Q330" s="404" t="s">
         <v>1943</v>
       </c>
       <c r="R330" s="102"/>
@@ -30934,7 +30944,7 @@
       <c r="F331" s="106" t="s">
         <v>58</v>
       </c>
-      <c r="G331" s="402" t="s">
+      <c r="G331" s="401" t="s">
         <v>631</v>
       </c>
       <c r="H331" s="121" t="s">
@@ -30962,7 +30972,7 @@
         <v>1773</v>
       </c>
       <c r="P331" s="106"/>
-      <c r="Q331" s="402" t="s">
+      <c r="Q331" s="401" t="s">
         <v>1955</v>
       </c>
       <c r="R331" s="106"/>
@@ -31005,9 +31015,9 @@
         <v>1963</v>
       </c>
       <c r="B332" s="204"/>
-      <c r="C332" s="380"/>
+      <c r="C332" s="379"/>
       <c r="D332" s="86"/>
-      <c r="E332" s="403" t="s">
+      <c r="E332" s="402" t="s">
         <v>27</v>
       </c>
       <c r="F332" s="88" t="s">
@@ -31039,7 +31049,7 @@
         <v>1773</v>
       </c>
       <c r="P332" s="88"/>
-      <c r="Q332" s="403" t="s">
+      <c r="Q332" s="402" t="s">
         <v>1969</v>
       </c>
       <c r="R332" s="88" t="s">
@@ -31112,7 +31122,7 @@
       </c>
       <c r="O333" s="104"/>
       <c r="P333" s="104"/>
-      <c r="Q333" s="407" t="s">
+      <c r="Q333" s="406" t="s">
         <v>1981</v>
       </c>
       <c r="R333" s="104"/>
@@ -31155,7 +31165,7 @@
       <c r="B334" s="207"/>
       <c r="C334" s="367"/>
       <c r="D334" s="83"/>
-      <c r="E334" s="402" t="s">
+      <c r="E334" s="401" t="s">
         <v>58</v>
       </c>
       <c r="F334" s="106" t="s">
@@ -31187,7 +31197,7 @@
         <v>1773</v>
       </c>
       <c r="P334" s="106"/>
-      <c r="Q334" s="402" t="s">
+      <c r="Q334" s="401" t="s">
         <v>1992</v>
       </c>
       <c r="R334" s="106"/>
@@ -31230,7 +31240,7 @@
         <v>46079</v>
       </c>
       <c r="B335" s="203"/>
-      <c r="C335" s="377"/>
+      <c r="C335" s="376"/>
       <c r="D335" s="80"/>
       <c r="E335" s="56" t="s">
         <v>58</v>
@@ -31264,7 +31274,7 @@
         <v>1773</v>
       </c>
       <c r="P335" s="56"/>
-      <c r="Q335" s="404" t="s">
+      <c r="Q335" s="403" t="s">
         <v>2005</v>
       </c>
       <c r="R335" s="56"/>
@@ -31309,7 +31319,7 @@
       <c r="B336" s="214">
         <v>46079</v>
       </c>
-      <c r="C336" s="378"/>
+      <c r="C336" s="377"/>
       <c r="D336" s="108"/>
       <c r="E336" s="81" t="s">
         <v>58</v>
@@ -31317,7 +31327,7 @@
       <c r="F336" s="81" t="s">
         <v>58</v>
       </c>
-      <c r="G336" s="416" t="s">
+      <c r="G336" s="415" t="s">
         <v>45</v>
       </c>
       <c r="H336" s="123" t="s">
@@ -31388,12 +31398,12 @@
         <v>46079</v>
       </c>
       <c r="B337" s="203"/>
-      <c r="C337" s="377"/>
+      <c r="C337" s="376"/>
       <c r="D337" s="80"/>
-      <c r="E337" s="404" t="s">
+      <c r="E337" s="403" t="s">
         <v>27</v>
       </c>
-      <c r="F337" s="404" t="s">
+      <c r="F337" s="403" t="s">
         <v>2026</v>
       </c>
       <c r="G337" s="56"/>
@@ -31416,11 +31426,11 @@
         <v>1427</v>
       </c>
       <c r="N337" s="56"/>
-      <c r="O337" s="404" t="s">
+      <c r="O337" s="403" t="s">
         <v>2032</v>
       </c>
       <c r="P337" s="56"/>
-      <c r="Q337" s="404"/>
+      <c r="Q337" s="403"/>
       <c r="R337" s="56"/>
       <c r="S337" s="56"/>
       <c r="T337" s="56"/>
@@ -31445,7 +31455,7 @@
         <v>46079</v>
       </c>
       <c r="B338" s="204"/>
-      <c r="C338" s="380"/>
+      <c r="C338" s="379"/>
       <c r="D338" s="86"/>
       <c r="E338" s="88" t="s">
         <v>27</v>
@@ -31479,7 +31489,7 @@
         <v>1773</v>
       </c>
       <c r="P338" s="88"/>
-      <c r="Q338" s="403" t="s">
+      <c r="Q338" s="402" t="s">
         <v>2039</v>
       </c>
       <c r="R338" s="88" t="s">
@@ -31524,7 +31534,7 @@
         <v>46079</v>
       </c>
       <c r="B339" s="214"/>
-      <c r="C339" s="378"/>
+      <c r="C339" s="377"/>
       <c r="D339" s="108"/>
       <c r="E339" s="81" t="s">
         <v>58</v>
@@ -31633,7 +31643,7 @@
         <v>1637</v>
       </c>
       <c r="P340" s="102"/>
-      <c r="Q340" s="405" t="s">
+      <c r="Q340" s="404" t="s">
         <v>2067</v>
       </c>
       <c r="R340" s="102"/>
@@ -31678,7 +31688,7 @@
       <c r="B341" s="205"/>
       <c r="C341" s="366"/>
       <c r="D341" s="110"/>
-      <c r="E341" s="407" t="s">
+      <c r="E341" s="406" t="s">
         <v>27</v>
       </c>
       <c r="F341" s="104" t="s">
@@ -31710,7 +31720,7 @@
         <v>1637</v>
       </c>
       <c r="P341" s="104"/>
-      <c r="Q341" s="407" t="s">
+      <c r="Q341" s="406" t="s">
         <v>2081</v>
       </c>
       <c r="R341" s="104" t="s">
@@ -31753,7 +31763,7 @@
         <v>1963</v>
       </c>
       <c r="B342" s="204"/>
-      <c r="C342" s="380"/>
+      <c r="C342" s="379"/>
       <c r="D342" s="86">
         <v>46080</v>
       </c>
@@ -31763,7 +31773,7 @@
       <c r="F342" s="88" t="s">
         <v>58</v>
       </c>
-      <c r="G342" s="403" t="s">
+      <c r="G342" s="402" t="s">
         <v>27</v>
       </c>
       <c r="H342" s="122" t="s">
@@ -31791,7 +31801,7 @@
         <v>1637</v>
       </c>
       <c r="P342" s="88"/>
-      <c r="Q342" s="403" t="s">
+      <c r="Q342" s="402" t="s">
         <v>2094</v>
       </c>
       <c r="R342" s="88" t="s">
@@ -31834,7 +31844,7 @@
         <v>1963</v>
       </c>
       <c r="B343" s="214"/>
-      <c r="C343" s="378"/>
+      <c r="C343" s="377"/>
       <c r="D343" s="108"/>
       <c r="E343" s="81" t="s">
         <v>58</v>
@@ -31907,7 +31917,7 @@
       <c r="AG343" s="81"/>
     </row>
     <row r="344" spans="1:33" ht="11.45" customHeight="1">
-      <c r="A344" s="411" t="s">
+      <c r="A344" s="410" t="s">
         <v>1963</v>
       </c>
       <c r="E344" s="75" t="s">
@@ -32002,7 +32012,7 @@
       <c r="O345" s="122" t="s">
         <v>1773</v>
       </c>
-      <c r="Q345" s="449" t="s">
+      <c r="Q345" s="448" t="s">
         <v>2133</v>
       </c>
       <c r="R345" s="122" t="s">
@@ -32075,7 +32085,7 @@
         <v>1773</v>
       </c>
       <c r="P346" s="104"/>
-      <c r="Q346" s="407" t="s">
+      <c r="Q346" s="406" t="s">
         <v>2148</v>
       </c>
       <c r="R346" s="104" t="s">
@@ -32154,7 +32164,7 @@
         <v>1637</v>
       </c>
       <c r="P347" s="106"/>
-      <c r="Q347" s="402" t="s">
+      <c r="Q347" s="401" t="s">
         <v>2162</v>
       </c>
       <c r="R347" s="106" t="s">
@@ -32199,7 +32209,7 @@
         <v>1963</v>
       </c>
       <c r="B348" s="204"/>
-      <c r="C348" s="380"/>
+      <c r="C348" s="379"/>
       <c r="D348" s="86"/>
       <c r="E348" s="88" t="s">
         <v>27</v>
@@ -32233,7 +32243,7 @@
         <v>1773</v>
       </c>
       <c r="P348" s="88"/>
-      <c r="Q348" s="403" t="s">
+      <c r="Q348" s="402" t="s">
         <v>2176</v>
       </c>
       <c r="R348" s="88"/>
@@ -32272,7 +32282,7 @@
       <c r="B349" s="209"/>
       <c r="C349" s="365"/>
       <c r="D349" s="109"/>
-      <c r="E349" s="405" t="s">
+      <c r="E349" s="404" t="s">
         <v>27</v>
       </c>
       <c r="F349" s="102" t="s">
@@ -32304,7 +32314,7 @@
         <v>1773</v>
       </c>
       <c r="P349" s="102"/>
-      <c r="Q349" s="405" t="s">
+      <c r="Q349" s="404" t="s">
         <v>2185</v>
       </c>
       <c r="R349" s="102"/>
@@ -32345,7 +32355,7 @@
         <v>1963</v>
       </c>
       <c r="B350" s="206"/>
-      <c r="C350" s="382"/>
+      <c r="C350" s="381"/>
       <c r="D350" s="296"/>
       <c r="E350" s="78" t="s">
         <v>27</v>
@@ -32379,7 +32389,7 @@
         <v>1773</v>
       </c>
       <c r="P350" s="78"/>
-      <c r="Q350" s="406" t="s">
+      <c r="Q350" s="405" t="s">
         <v>2197</v>
       </c>
       <c r="R350" s="78"/>
@@ -32420,7 +32430,7 @@
         <v>1963</v>
       </c>
       <c r="B351" s="204"/>
-      <c r="C351" s="380"/>
+      <c r="C351" s="379"/>
       <c r="D351" s="86"/>
       <c r="E351" s="88" t="s">
         <v>27</v>
@@ -32454,7 +32464,7 @@
         <v>1773</v>
       </c>
       <c r="P351" s="88"/>
-      <c r="Q351" s="403" t="s">
+      <c r="Q351" s="402" t="s">
         <v>2209</v>
       </c>
       <c r="R351" s="88"/>
@@ -32492,20 +32502,20 @@
       <c r="AF351" s="88"/>
       <c r="AG351" s="88"/>
     </row>
-    <row r="352" spans="1:33" s="421" customFormat="1" ht="11.45" customHeight="1">
-      <c r="A352" s="417">
+    <row r="352" spans="1:33" s="420" customFormat="1" ht="11.45" customHeight="1">
+      <c r="A352" s="416">
         <v>46084</v>
       </c>
-      <c r="B352" s="417"/>
-      <c r="C352" s="418"/>
-      <c r="D352" s="419"/>
-      <c r="E352" s="420" t="s">
+      <c r="B352" s="416"/>
+      <c r="C352" s="417"/>
+      <c r="D352" s="418"/>
+      <c r="E352" s="419" t="s">
         <v>58</v>
       </c>
-      <c r="F352" s="420" t="s">
+      <c r="F352" s="419" t="s">
         <v>58</v>
       </c>
-      <c r="G352" s="420"/>
+      <c r="G352" s="419"/>
       <c r="H352" s="121" t="s">
         <v>2217</v>
       </c>
@@ -32524,48 +32534,48 @@
       <c r="M352" s="171" t="s">
         <v>2196</v>
       </c>
-      <c r="N352" s="402" t="s">
+      <c r="N352" s="401" t="s">
         <v>32</v>
       </c>
-      <c r="O352" s="402" t="s">
+      <c r="O352" s="401" t="s">
         <v>1773</v>
       </c>
-      <c r="P352" s="420"/>
-      <c r="Q352" s="402" t="s">
+      <c r="P352" s="419"/>
+      <c r="Q352" s="401" t="s">
         <v>2221</v>
       </c>
-      <c r="R352" s="420"/>
-      <c r="S352" s="420" t="s">
+      <c r="R352" s="419"/>
+      <c r="S352" s="419" t="s">
         <v>2222</v>
       </c>
-      <c r="T352" s="420" t="s">
+      <c r="T352" s="419" t="s">
         <v>2223</v>
       </c>
-      <c r="U352" s="420" t="s">
+      <c r="U352" s="419" t="s">
         <v>2224</v>
       </c>
-      <c r="V352" s="420"/>
-      <c r="W352" s="420" t="s">
+      <c r="V352" s="419"/>
+      <c r="W352" s="419" t="s">
         <v>2225</v>
       </c>
-      <c r="X352" s="420" t="s">
+      <c r="X352" s="419" t="s">
         <v>2226</v>
       </c>
-      <c r="Y352" s="420" t="s">
+      <c r="Y352" s="419" t="s">
         <v>2227</v>
       </c>
-      <c r="Z352" s="420" t="s">
+      <c r="Z352" s="419" t="s">
         <v>180</v>
       </c>
-      <c r="AA352" s="420" t="s">
+      <c r="AA352" s="419" t="s">
         <v>34</v>
       </c>
-      <c r="AB352" s="420"/>
-      <c r="AC352" s="420"/>
-      <c r="AD352" s="420"/>
-      <c r="AE352" s="420"/>
-      <c r="AF352" s="420"/>
-      <c r="AG352" s="420"/>
+      <c r="AB352" s="419"/>
+      <c r="AC352" s="419"/>
+      <c r="AD352" s="419"/>
+      <c r="AE352" s="419"/>
+      <c r="AF352" s="419"/>
+      <c r="AG352" s="419"/>
     </row>
     <row r="353" spans="1:33" ht="11.45" customHeight="1">
       <c r="A353" s="205">
@@ -32606,7 +32616,7 @@
         <v>1637</v>
       </c>
       <c r="P353" s="104"/>
-      <c r="Q353" s="407"/>
+      <c r="Q353" s="406"/>
       <c r="R353" s="104"/>
       <c r="S353" s="104" t="s">
         <v>2234</v>
@@ -32647,9 +32657,9 @@
         <v>46084</v>
       </c>
       <c r="B354" s="204"/>
-      <c r="C354" s="380"/>
+      <c r="C354" s="379"/>
       <c r="D354" s="86"/>
-      <c r="E354" s="403" t="s">
+      <c r="E354" s="402" t="s">
         <v>27</v>
       </c>
       <c r="F354" s="88" t="s">
@@ -32681,7 +32691,7 @@
         <v>1773</v>
       </c>
       <c r="P354" s="88"/>
-      <c r="Q354" s="403" t="s">
+      <c r="Q354" s="402" t="s">
         <v>2247</v>
       </c>
       <c r="R354" s="88"/>
@@ -32736,7 +32746,7 @@
         <v>2260</v>
       </c>
       <c r="L355" s="120" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="M355" s="170" t="s">
         <v>1357</v>
@@ -32746,7 +32756,7 @@
         <v>1773</v>
       </c>
       <c r="P355" s="104"/>
-      <c r="Q355" s="407"/>
+      <c r="Q355" s="406"/>
       <c r="R355" s="104"/>
       <c r="S355" s="104"/>
       <c r="T355" s="104"/>
@@ -32789,11 +32799,11 @@
       <c r="J356" s="119" t="s">
         <v>2293</v>
       </c>
-      <c r="K356" s="454" t="s">
+      <c r="K356" s="453" t="s">
         <v>2294</v>
       </c>
       <c r="L356" s="119" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="M356" s="169" t="s">
         <v>1427</v>
@@ -32803,7 +32813,7 @@
         <v>1637</v>
       </c>
       <c r="P356" s="102"/>
-      <c r="Q356" s="405"/>
+      <c r="Q356" s="404"/>
       <c r="R356" s="102"/>
       <c r="S356" s="102"/>
       <c r="T356" s="102"/>
@@ -32830,7 +32840,7 @@
     <row r="357" spans="1:33" ht="11.45" customHeight="1">
       <c r="A357" s="206"/>
       <c r="B357" s="206"/>
-      <c r="C357" s="382"/>
+      <c r="C357" s="381"/>
       <c r="D357" s="296"/>
       <c r="E357" s="78"/>
       <c r="F357" s="78"/>
@@ -32848,7 +32858,7 @@
         <v>2313</v>
       </c>
       <c r="L357" s="118" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="M357" s="172" t="s">
         <v>1427</v>
@@ -32858,7 +32868,7 @@
         <v>1773</v>
       </c>
       <c r="P357" s="78"/>
-      <c r="Q357" s="406"/>
+      <c r="Q357" s="405"/>
       <c r="R357" s="78"/>
       <c r="S357" s="78"/>
       <c r="T357" s="78"/>
@@ -32885,7 +32895,7 @@
     <row r="358" spans="1:33" ht="11.45" customHeight="1">
       <c r="A358" s="204"/>
       <c r="B358" s="204"/>
-      <c r="C358" s="380"/>
+      <c r="C358" s="379"/>
       <c r="D358" s="86"/>
       <c r="E358" s="88"/>
       <c r="F358" s="88"/>
@@ -32913,7 +32923,7 @@
         <v>1773</v>
       </c>
       <c r="P358" s="88"/>
-      <c r="Q358" s="403"/>
+      <c r="Q358" s="402"/>
       <c r="R358" s="88"/>
       <c r="S358" s="88"/>
       <c r="T358" s="88"/>
@@ -32940,7 +32950,7 @@
     <row r="359" spans="1:33" ht="11.45" customHeight="1">
       <c r="A359" s="203"/>
       <c r="B359" s="203"/>
-      <c r="C359" s="377"/>
+      <c r="C359" s="376"/>
       <c r="D359" s="80"/>
       <c r="E359" s="56"/>
       <c r="F359" s="56"/>
@@ -32952,7 +32962,7 @@
       <c r="N359" s="56"/>
       <c r="O359" s="56"/>
       <c r="P359" s="56"/>
-      <c r="Q359" s="404"/>
+      <c r="Q359" s="403"/>
       <c r="R359" s="56"/>
       <c r="S359" s="56"/>
       <c r="T359" s="56"/>
@@ -32973,7 +32983,7 @@
     <row r="360" spans="1:33" ht="11.45" customHeight="1">
       <c r="A360" s="214"/>
       <c r="B360" s="214"/>
-      <c r="C360" s="378"/>
+      <c r="C360" s="377"/>
       <c r="D360" s="108"/>
       <c r="E360" s="81"/>
       <c r="F360" s="81"/>
@@ -33018,7 +33028,7 @@
       <c r="N361" s="102"/>
       <c r="O361" s="102"/>
       <c r="P361" s="102"/>
-      <c r="Q361" s="405"/>
+      <c r="Q361" s="404"/>
       <c r="R361" s="102"/>
       <c r="S361" s="102"/>
       <c r="T361" s="102"/>
@@ -33051,7 +33061,7 @@
       <c r="N362" s="104"/>
       <c r="O362" s="104"/>
       <c r="P362" s="104"/>
-      <c r="Q362" s="407"/>
+      <c r="Q362" s="406"/>
       <c r="R362" s="104"/>
       <c r="S362" s="104"/>
       <c r="T362" s="104"/>
@@ -33084,7 +33094,7 @@
       <c r="N363" s="106"/>
       <c r="O363" s="106"/>
       <c r="P363" s="106"/>
-      <c r="Q363" s="402"/>
+      <c r="Q363" s="401"/>
       <c r="R363" s="106"/>
       <c r="S363" s="106"/>
       <c r="T363" s="106"/>
@@ -33105,7 +33115,7 @@
     <row r="364" spans="1:33" ht="11.45" customHeight="1">
       <c r="A364" s="206"/>
       <c r="B364" s="206"/>
-      <c r="C364" s="382"/>
+      <c r="C364" s="381"/>
       <c r="D364" s="296"/>
       <c r="E364" s="78"/>
       <c r="F364" s="78"/>
@@ -33117,7 +33127,7 @@
       <c r="N364" s="78"/>
       <c r="O364" s="78"/>
       <c r="P364" s="78"/>
-      <c r="Q364" s="406"/>
+      <c r="Q364" s="405"/>
       <c r="R364" s="78"/>
       <c r="S364" s="78"/>
       <c r="T364" s="78"/>
@@ -33138,7 +33148,7 @@
     <row r="365" spans="1:33" ht="11.45" customHeight="1">
       <c r="A365" s="204"/>
       <c r="B365" s="204"/>
-      <c r="C365" s="380"/>
+      <c r="C365" s="379"/>
       <c r="D365" s="86"/>
       <c r="E365" s="88"/>
       <c r="F365" s="88"/>
@@ -33150,7 +33160,7 @@
       <c r="N365" s="88"/>
       <c r="O365" s="88"/>
       <c r="P365" s="88"/>
-      <c r="Q365" s="403"/>
+      <c r="Q365" s="402"/>
       <c r="R365" s="88"/>
       <c r="S365" s="88"/>
       <c r="T365" s="88"/>
@@ -33171,7 +33181,7 @@
     <row r="366" spans="1:33" ht="11.45" customHeight="1">
       <c r="A366" s="203"/>
       <c r="B366" s="203"/>
-      <c r="C366" s="377"/>
+      <c r="C366" s="376"/>
       <c r="D366" s="80"/>
       <c r="E366" s="56"/>
       <c r="F366" s="56"/>
@@ -33183,7 +33193,7 @@
       <c r="N366" s="56"/>
       <c r="O366" s="56"/>
       <c r="P366" s="56"/>
-      <c r="Q366" s="404"/>
+      <c r="Q366" s="403"/>
       <c r="R366" s="56"/>
       <c r="S366" s="56"/>
       <c r="T366" s="56"/>
@@ -33204,7 +33214,7 @@
     <row r="367" spans="1:33" ht="11.45" customHeight="1">
       <c r="A367" s="214"/>
       <c r="B367" s="214"/>
-      <c r="C367" s="378"/>
+      <c r="C367" s="377"/>
       <c r="D367" s="108"/>
       <c r="E367" s="81"/>
       <c r="F367" s="81"/>
@@ -33249,7 +33259,7 @@
       <c r="N368" s="102"/>
       <c r="O368" s="102"/>
       <c r="P368" s="102"/>
-      <c r="Q368" s="405"/>
+      <c r="Q368" s="404"/>
       <c r="R368" s="102"/>
       <c r="S368" s="102"/>
       <c r="T368" s="102"/>
@@ -33282,7 +33292,7 @@
       <c r="N369" s="104"/>
       <c r="O369" s="104"/>
       <c r="P369" s="104"/>
-      <c r="Q369" s="407"/>
+      <c r="Q369" s="406"/>
       <c r="R369" s="104"/>
       <c r="S369" s="104"/>
       <c r="T369" s="104"/>
@@ -33315,7 +33325,7 @@
       <c r="N370" s="106"/>
       <c r="O370" s="106"/>
       <c r="P370" s="106"/>
-      <c r="Q370" s="402"/>
+      <c r="Q370" s="401"/>
       <c r="R370" s="106"/>
       <c r="S370" s="106"/>
       <c r="T370" s="106"/>
@@ -33336,7 +33346,7 @@
     <row r="371" spans="1:33" ht="11.45" customHeight="1">
       <c r="A371" s="206"/>
       <c r="B371" s="206"/>
-      <c r="C371" s="382"/>
+      <c r="C371" s="381"/>
       <c r="D371" s="296"/>
       <c r="E371" s="78"/>
       <c r="F371" s="78"/>
@@ -33348,7 +33358,7 @@
       <c r="N371" s="78"/>
       <c r="O371" s="78"/>
       <c r="P371" s="78"/>
-      <c r="Q371" s="406"/>
+      <c r="Q371" s="405"/>
       <c r="R371" s="78"/>
       <c r="S371" s="78"/>
       <c r="T371" s="78"/>
@@ -33369,7 +33379,7 @@
     <row r="372" spans="1:33" ht="11.45" customHeight="1">
       <c r="A372" s="204"/>
       <c r="B372" s="204"/>
-      <c r="C372" s="380"/>
+      <c r="C372" s="379"/>
       <c r="D372" s="86"/>
       <c r="E372" s="88"/>
       <c r="F372" s="88"/>
@@ -33381,7 +33391,7 @@
       <c r="N372" s="88"/>
       <c r="O372" s="88"/>
       <c r="P372" s="88"/>
-      <c r="Q372" s="403"/>
+      <c r="Q372" s="402"/>
       <c r="R372" s="88"/>
       <c r="S372" s="88"/>
       <c r="T372" s="88"/>
@@ -33402,7 +33412,7 @@
     <row r="373" spans="1:33" ht="11.45" customHeight="1">
       <c r="A373" s="203"/>
       <c r="B373" s="203"/>
-      <c r="C373" s="377"/>
+      <c r="C373" s="376"/>
       <c r="D373" s="80"/>
       <c r="E373" s="56"/>
       <c r="F373" s="56"/>
@@ -33414,7 +33424,7 @@
       <c r="N373" s="56"/>
       <c r="O373" s="56"/>
       <c r="P373" s="56"/>
-      <c r="Q373" s="404"/>
+      <c r="Q373" s="403"/>
       <c r="R373" s="56"/>
       <c r="S373" s="56"/>
       <c r="T373" s="56"/>
@@ -33435,7 +33445,7 @@
     <row r="374" spans="1:33" ht="11.45" customHeight="1">
       <c r="A374" s="214"/>
       <c r="B374" s="214"/>
-      <c r="C374" s="378"/>
+      <c r="C374" s="377"/>
       <c r="D374" s="108"/>
       <c r="E374" s="81"/>
       <c r="F374" s="81"/>
@@ -33480,7 +33490,7 @@
       <c r="N375" s="102"/>
       <c r="O375" s="102"/>
       <c r="P375" s="102"/>
-      <c r="Q375" s="405"/>
+      <c r="Q375" s="404"/>
       <c r="R375" s="102"/>
       <c r="S375" s="102"/>
       <c r="T375" s="102"/>
@@ -33513,7 +33523,7 @@
       <c r="N376" s="104"/>
       <c r="O376" s="104"/>
       <c r="P376" s="104"/>
-      <c r="Q376" s="407"/>
+      <c r="Q376" s="406"/>
       <c r="R376" s="104"/>
       <c r="S376" s="104"/>
       <c r="T376" s="104"/>
@@ -33546,7 +33556,7 @@
       <c r="N377" s="106"/>
       <c r="O377" s="106"/>
       <c r="P377" s="106"/>
-      <c r="Q377" s="402"/>
+      <c r="Q377" s="401"/>
       <c r="R377" s="106"/>
       <c r="S377" s="106"/>
       <c r="T377" s="106"/>
@@ -33567,7 +33577,7 @@
     <row r="378" spans="1:33" ht="11.45" customHeight="1">
       <c r="A378" s="206"/>
       <c r="B378" s="206"/>
-      <c r="C378" s="382"/>
+      <c r="C378" s="381"/>
       <c r="D378" s="296"/>
       <c r="E378" s="78"/>
       <c r="F378" s="78"/>
@@ -33579,7 +33589,7 @@
       <c r="N378" s="78"/>
       <c r="O378" s="78"/>
       <c r="P378" s="78"/>
-      <c r="Q378" s="406"/>
+      <c r="Q378" s="405"/>
       <c r="R378" s="78"/>
       <c r="S378" s="78"/>
       <c r="T378" s="78"/>
@@ -33600,7 +33610,7 @@
     <row r="379" spans="1:33" ht="11.45" customHeight="1">
       <c r="A379" s="204"/>
       <c r="B379" s="204"/>
-      <c r="C379" s="380"/>
+      <c r="C379" s="379"/>
       <c r="D379" s="86"/>
       <c r="E379" s="88"/>
       <c r="F379" s="88"/>
@@ -33612,7 +33622,7 @@
       <c r="N379" s="88"/>
       <c r="O379" s="88"/>
       <c r="P379" s="88"/>
-      <c r="Q379" s="403"/>
+      <c r="Q379" s="402"/>
       <c r="R379" s="88"/>
       <c r="S379" s="88"/>
       <c r="T379" s="88"/>
@@ -33633,7 +33643,7 @@
     <row r="380" spans="1:33" ht="11.45" customHeight="1">
       <c r="A380" s="203"/>
       <c r="B380" s="203"/>
-      <c r="C380" s="377"/>
+      <c r="C380" s="376"/>
       <c r="D380" s="80"/>
       <c r="E380" s="56"/>
       <c r="F380" s="56"/>
@@ -33645,7 +33655,7 @@
       <c r="N380" s="56"/>
       <c r="O380" s="56"/>
       <c r="P380" s="56"/>
-      <c r="Q380" s="404"/>
+      <c r="Q380" s="403"/>
       <c r="R380" s="56"/>
       <c r="S380" s="56"/>
       <c r="T380" s="56"/>
@@ -33666,7 +33676,7 @@
     <row r="381" spans="1:33" ht="11.45" customHeight="1">
       <c r="A381" s="214"/>
       <c r="B381" s="214"/>
-      <c r="C381" s="378"/>
+      <c r="C381" s="377"/>
       <c r="D381" s="108"/>
       <c r="E381" s="81"/>
       <c r="F381" s="81"/>
@@ -33711,7 +33721,7 @@
       <c r="N382" s="102"/>
       <c r="O382" s="102"/>
       <c r="P382" s="102"/>
-      <c r="Q382" s="405"/>
+      <c r="Q382" s="404"/>
       <c r="R382" s="102"/>
       <c r="S382" s="102"/>
       <c r="T382" s="102"/>
@@ -33744,7 +33754,7 @@
       <c r="N383" s="104"/>
       <c r="O383" s="104"/>
       <c r="P383" s="104"/>
-      <c r="Q383" s="407"/>
+      <c r="Q383" s="406"/>
       <c r="R383" s="104"/>
       <c r="S383" s="104"/>
       <c r="T383" s="104"/>
@@ -33777,7 +33787,7 @@
       <c r="N384" s="106"/>
       <c r="O384" s="106"/>
       <c r="P384" s="106"/>
-      <c r="Q384" s="402"/>
+      <c r="Q384" s="401"/>
       <c r="R384" s="106"/>
       <c r="S384" s="106"/>
       <c r="T384" s="106"/>
@@ -33798,7 +33808,7 @@
     <row r="385" spans="1:33" ht="11.45" customHeight="1">
       <c r="A385" s="206"/>
       <c r="B385" s="206"/>
-      <c r="C385" s="382"/>
+      <c r="C385" s="381"/>
       <c r="D385" s="296"/>
       <c r="E385" s="78"/>
       <c r="F385" s="78"/>
@@ -33810,7 +33820,7 @@
       <c r="N385" s="78"/>
       <c r="O385" s="78"/>
       <c r="P385" s="78"/>
-      <c r="Q385" s="406"/>
+      <c r="Q385" s="405"/>
       <c r="R385" s="78"/>
       <c r="S385" s="78"/>
       <c r="T385" s="78"/>
@@ -33831,7 +33841,7 @@
     <row r="386" spans="1:33" ht="11.45" customHeight="1">
       <c r="A386" s="204"/>
       <c r="B386" s="204"/>
-      <c r="C386" s="380"/>
+      <c r="C386" s="379"/>
       <c r="D386" s="86"/>
       <c r="E386" s="88"/>
       <c r="F386" s="88"/>
@@ -33843,7 +33853,7 @@
       <c r="N386" s="88"/>
       <c r="O386" s="88"/>
       <c r="P386" s="88"/>
-      <c r="Q386" s="403"/>
+      <c r="Q386" s="402"/>
       <c r="R386" s="88"/>
       <c r="S386" s="88"/>
       <c r="T386" s="88"/>
@@ -33864,7 +33874,7 @@
     <row r="387" spans="1:33" ht="11.45" customHeight="1">
       <c r="A387" s="203"/>
       <c r="B387" s="203"/>
-      <c r="C387" s="377"/>
+      <c r="C387" s="376"/>
       <c r="D387" s="80"/>
       <c r="E387" s="56"/>
       <c r="F387" s="56"/>
@@ -33876,7 +33886,7 @@
       <c r="N387" s="56"/>
       <c r="O387" s="56"/>
       <c r="P387" s="56"/>
-      <c r="Q387" s="404"/>
+      <c r="Q387" s="403"/>
       <c r="R387" s="56"/>
       <c r="S387" s="56"/>
       <c r="T387" s="56"/>
@@ -33897,7 +33907,7 @@
     <row r="388" spans="1:33" ht="11.45" customHeight="1">
       <c r="A388" s="214"/>
       <c r="B388" s="214"/>
-      <c r="C388" s="378"/>
+      <c r="C388" s="377"/>
       <c r="D388" s="108"/>
       <c r="E388" s="81"/>
       <c r="F388" s="81"/>
@@ -33942,7 +33952,7 @@
       <c r="N389" s="102"/>
       <c r="O389" s="102"/>
       <c r="P389" s="102"/>
-      <c r="Q389" s="405"/>
+      <c r="Q389" s="404"/>
       <c r="R389" s="102"/>
       <c r="S389" s="102"/>
       <c r="T389" s="102"/>
@@ -33975,7 +33985,7 @@
       <c r="N390" s="104"/>
       <c r="O390" s="104"/>
       <c r="P390" s="104"/>
-      <c r="Q390" s="407"/>
+      <c r="Q390" s="406"/>
       <c r="R390" s="104"/>
       <c r="S390" s="104"/>
       <c r="T390" s="104"/>
@@ -34008,7 +34018,7 @@
       <c r="N391" s="106"/>
       <c r="O391" s="106"/>
       <c r="P391" s="106"/>
-      <c r="Q391" s="402"/>
+      <c r="Q391" s="401"/>
       <c r="R391" s="106"/>
       <c r="S391" s="106"/>
       <c r="T391" s="106"/>
@@ -34029,7 +34039,7 @@
     <row r="392" spans="1:33" ht="11.45" customHeight="1">
       <c r="A392" s="206"/>
       <c r="B392" s="206"/>
-      <c r="C392" s="382"/>
+      <c r="C392" s="381"/>
       <c r="D392" s="296"/>
       <c r="E392" s="78"/>
       <c r="F392" s="78"/>
@@ -34041,7 +34051,7 @@
       <c r="N392" s="78"/>
       <c r="O392" s="78"/>
       <c r="P392" s="78"/>
-      <c r="Q392" s="406"/>
+      <c r="Q392" s="405"/>
       <c r="R392" s="78"/>
       <c r="S392" s="78"/>
       <c r="T392" s="78"/>
@@ -34062,7 +34072,7 @@
     <row r="393" spans="1:33" ht="11.45" customHeight="1">
       <c r="A393" s="204"/>
       <c r="B393" s="204"/>
-      <c r="C393" s="380"/>
+      <c r="C393" s="379"/>
       <c r="D393" s="86"/>
       <c r="E393" s="88"/>
       <c r="F393" s="88"/>
@@ -34074,7 +34084,7 @@
       <c r="N393" s="88"/>
       <c r="O393" s="88"/>
       <c r="P393" s="88"/>
-      <c r="Q393" s="403"/>
+      <c r="Q393" s="402"/>
       <c r="R393" s="88"/>
       <c r="S393" s="88"/>
       <c r="T393" s="88"/>
@@ -34095,7 +34105,7 @@
     <row r="394" spans="1:33" ht="11.45" customHeight="1">
       <c r="A394" s="203"/>
       <c r="B394" s="203"/>
-      <c r="C394" s="377"/>
+      <c r="C394" s="376"/>
       <c r="D394" s="80"/>
       <c r="E394" s="56"/>
       <c r="F394" s="56"/>
@@ -34107,7 +34117,7 @@
       <c r="N394" s="56"/>
       <c r="O394" s="56"/>
       <c r="P394" s="56"/>
-      <c r="Q394" s="404"/>
+      <c r="Q394" s="403"/>
       <c r="R394" s="56"/>
       <c r="S394" s="56"/>
       <c r="T394" s="56"/>
@@ -34128,7 +34138,7 @@
     <row r="395" spans="1:33" ht="11.45" customHeight="1">
       <c r="A395" s="214"/>
       <c r="B395" s="214"/>
-      <c r="C395" s="378"/>
+      <c r="C395" s="377"/>
       <c r="D395" s="108"/>
       <c r="E395" s="81"/>
       <c r="F395" s="81"/>
@@ -34173,7 +34183,7 @@
       <c r="N396" s="102"/>
       <c r="O396" s="102"/>
       <c r="P396" s="102"/>
-      <c r="Q396" s="405"/>
+      <c r="Q396" s="404"/>
       <c r="R396" s="102"/>
       <c r="S396" s="102"/>
       <c r="T396" s="102"/>
@@ -34206,7 +34216,7 @@
       <c r="N397" s="104"/>
       <c r="O397" s="104"/>
       <c r="P397" s="104"/>
-      <c r="Q397" s="407"/>
+      <c r="Q397" s="406"/>
       <c r="R397" s="104"/>
       <c r="S397" s="104"/>
       <c r="T397" s="104"/>
@@ -34239,7 +34249,7 @@
       <c r="N398" s="106"/>
       <c r="O398" s="106"/>
       <c r="P398" s="106"/>
-      <c r="Q398" s="402"/>
+      <c r="Q398" s="401"/>
       <c r="R398" s="106"/>
       <c r="S398" s="106"/>
       <c r="T398" s="106"/>
@@ -34260,7 +34270,7 @@
     <row r="399" spans="1:33" ht="11.45" customHeight="1">
       <c r="A399" s="206"/>
       <c r="B399" s="206"/>
-      <c r="C399" s="382"/>
+      <c r="C399" s="381"/>
       <c r="D399" s="296"/>
       <c r="E399" s="78"/>
       <c r="F399" s="78"/>
@@ -34272,7 +34282,7 @@
       <c r="N399" s="78"/>
       <c r="O399" s="78"/>
       <c r="P399" s="78"/>
-      <c r="Q399" s="406"/>
+      <c r="Q399" s="405"/>
       <c r="R399" s="78"/>
       <c r="S399" s="78"/>
       <c r="T399" s="78"/>
@@ -34293,7 +34303,7 @@
     <row r="400" spans="1:33" ht="11.45" customHeight="1">
       <c r="A400" s="204"/>
       <c r="B400" s="204"/>
-      <c r="C400" s="380"/>
+      <c r="C400" s="379"/>
       <c r="D400" s="86"/>
       <c r="E400" s="88"/>
       <c r="F400" s="88"/>
@@ -34305,7 +34315,7 @@
       <c r="N400" s="88"/>
       <c r="O400" s="88"/>
       <c r="P400" s="88"/>
-      <c r="Q400" s="403"/>
+      <c r="Q400" s="402"/>
       <c r="R400" s="88"/>
       <c r="S400" s="88"/>
       <c r="T400" s="88"/>
@@ -34326,7 +34336,7 @@
     <row r="401" spans="1:33" ht="11.45" customHeight="1">
       <c r="A401" s="203"/>
       <c r="B401" s="203"/>
-      <c r="C401" s="377"/>
+      <c r="C401" s="376"/>
       <c r="D401" s="80"/>
       <c r="E401" s="56"/>
       <c r="F401" s="56"/>
@@ -34338,7 +34348,7 @@
       <c r="N401" s="56"/>
       <c r="O401" s="56"/>
       <c r="P401" s="56"/>
-      <c r="Q401" s="404"/>
+      <c r="Q401" s="403"/>
       <c r="R401" s="56"/>
       <c r="S401" s="56"/>
       <c r="T401" s="56"/>
@@ -34359,7 +34369,7 @@
     <row r="402" spans="1:33" ht="11.45" customHeight="1">
       <c r="A402" s="214"/>
       <c r="B402" s="214"/>
-      <c r="C402" s="378"/>
+      <c r="C402" s="377"/>
       <c r="D402" s="108"/>
       <c r="E402" s="81"/>
       <c r="F402" s="81"/>
@@ -34404,7 +34414,7 @@
       <c r="N403" s="102"/>
       <c r="O403" s="102"/>
       <c r="P403" s="102"/>
-      <c r="Q403" s="405"/>
+      <c r="Q403" s="404"/>
       <c r="R403" s="102"/>
       <c r="S403" s="102"/>
       <c r="T403" s="102"/>
@@ -34437,7 +34447,7 @@
       <c r="N404" s="104"/>
       <c r="O404" s="104"/>
       <c r="P404" s="104"/>
-      <c r="Q404" s="407"/>
+      <c r="Q404" s="406"/>
       <c r="R404" s="104"/>
       <c r="S404" s="104"/>
       <c r="T404" s="104"/>
@@ -34470,7 +34480,7 @@
       <c r="N405" s="106"/>
       <c r="O405" s="106"/>
       <c r="P405" s="106"/>
-      <c r="Q405" s="402"/>
+      <c r="Q405" s="401"/>
       <c r="R405" s="106"/>
       <c r="S405" s="106"/>
       <c r="T405" s="106"/>
@@ -34491,7 +34501,7 @@
     <row r="406" spans="1:33" ht="11.45" customHeight="1">
       <c r="A406" s="206"/>
       <c r="B406" s="206"/>
-      <c r="C406" s="382"/>
+      <c r="C406" s="381"/>
       <c r="D406" s="296"/>
       <c r="E406" s="78"/>
       <c r="F406" s="78"/>
@@ -34503,7 +34513,7 @@
       <c r="N406" s="78"/>
       <c r="O406" s="78"/>
       <c r="P406" s="78"/>
-      <c r="Q406" s="406"/>
+      <c r="Q406" s="405"/>
       <c r="R406" s="78"/>
       <c r="S406" s="78"/>
       <c r="T406" s="78"/>
@@ -34524,7 +34534,7 @@
     <row r="407" spans="1:33" ht="11.45" customHeight="1">
       <c r="A407" s="204"/>
       <c r="B407" s="204"/>
-      <c r="C407" s="380"/>
+      <c r="C407" s="379"/>
       <c r="D407" s="86"/>
       <c r="E407" s="88"/>
       <c r="F407" s="88"/>
@@ -34536,7 +34546,7 @@
       <c r="N407" s="88"/>
       <c r="O407" s="88"/>
       <c r="P407" s="88"/>
-      <c r="Q407" s="403"/>
+      <c r="Q407" s="402"/>
       <c r="R407" s="88"/>
       <c r="S407" s="88"/>
       <c r="T407" s="88"/>
@@ -34557,7 +34567,7 @@
     <row r="408" spans="1:33" ht="11.45" customHeight="1">
       <c r="A408" s="203"/>
       <c r="B408" s="203"/>
-      <c r="C408" s="377"/>
+      <c r="C408" s="376"/>
       <c r="D408" s="80"/>
       <c r="E408" s="56"/>
       <c r="F408" s="56"/>
@@ -34569,7 +34579,7 @@
       <c r="N408" s="56"/>
       <c r="O408" s="56"/>
       <c r="P408" s="56"/>
-      <c r="Q408" s="404"/>
+      <c r="Q408" s="403"/>
       <c r="R408" s="56"/>
       <c r="S408" s="56"/>
       <c r="T408" s="56"/>
@@ -34590,7 +34600,7 @@
     <row r="409" spans="1:33" ht="11.45" customHeight="1">
       <c r="A409" s="214"/>
       <c r="B409" s="214"/>
-      <c r="C409" s="378"/>
+      <c r="C409" s="377"/>
       <c r="D409" s="108"/>
       <c r="E409" s="81"/>
       <c r="F409" s="81"/>
@@ -34635,7 +34645,7 @@
       <c r="N410" s="102"/>
       <c r="O410" s="102"/>
       <c r="P410" s="102"/>
-      <c r="Q410" s="405"/>
+      <c r="Q410" s="404"/>
       <c r="R410" s="102"/>
       <c r="S410" s="102"/>
       <c r="T410" s="102"/>
@@ -34668,7 +34678,7 @@
       <c r="N411" s="104"/>
       <c r="O411" s="104"/>
       <c r="P411" s="104"/>
-      <c r="Q411" s="407"/>
+      <c r="Q411" s="406"/>
       <c r="R411" s="104"/>
       <c r="S411" s="104"/>
       <c r="T411" s="104"/>
@@ -34701,7 +34711,7 @@
       <c r="N412" s="106"/>
       <c r="O412" s="106"/>
       <c r="P412" s="106"/>
-      <c r="Q412" s="402"/>
+      <c r="Q412" s="401"/>
       <c r="R412" s="106"/>
       <c r="S412" s="106"/>
       <c r="T412" s="106"/>
@@ -34722,7 +34732,7 @@
     <row r="413" spans="1:33" ht="11.45" customHeight="1">
       <c r="A413" s="206"/>
       <c r="B413" s="206"/>
-      <c r="C413" s="382"/>
+      <c r="C413" s="381"/>
       <c r="D413" s="296"/>
       <c r="E413" s="78"/>
       <c r="F413" s="78"/>
@@ -34734,7 +34744,7 @@
       <c r="N413" s="78"/>
       <c r="O413" s="78"/>
       <c r="P413" s="78"/>
-      <c r="Q413" s="406"/>
+      <c r="Q413" s="405"/>
       <c r="R413" s="78"/>
       <c r="S413" s="78"/>
       <c r="T413" s="78"/>
@@ -34755,7 +34765,7 @@
     <row r="414" spans="1:33" ht="11.45" customHeight="1">
       <c r="A414" s="204"/>
       <c r="B414" s="204"/>
-      <c r="C414" s="380"/>
+      <c r="C414" s="379"/>
       <c r="D414" s="86"/>
       <c r="E414" s="88"/>
       <c r="F414" s="88"/>
@@ -34767,7 +34777,7 @@
       <c r="N414" s="88"/>
       <c r="O414" s="88"/>
       <c r="P414" s="88"/>
-      <c r="Q414" s="403"/>
+      <c r="Q414" s="402"/>
       <c r="R414" s="88"/>
       <c r="S414" s="88"/>
       <c r="T414" s="88"/>
@@ -34788,7 +34798,7 @@
     <row r="415" spans="1:33" ht="11.45" customHeight="1">
       <c r="A415" s="203"/>
       <c r="B415" s="203"/>
-      <c r="C415" s="377"/>
+      <c r="C415" s="376"/>
       <c r="D415" s="80"/>
       <c r="E415" s="56"/>
       <c r="F415" s="56"/>
@@ -34800,7 +34810,7 @@
       <c r="N415" s="56"/>
       <c r="O415" s="56"/>
       <c r="P415" s="56"/>
-      <c r="Q415" s="404"/>
+      <c r="Q415" s="403"/>
       <c r="R415" s="56"/>
       <c r="S415" s="56"/>
       <c r="T415" s="56"/>
@@ -34821,7 +34831,7 @@
     <row r="416" spans="1:33" ht="11.45" customHeight="1">
       <c r="A416" s="214"/>
       <c r="B416" s="214"/>
-      <c r="C416" s="378"/>
+      <c r="C416" s="377"/>
       <c r="D416" s="108"/>
       <c r="E416" s="81"/>
       <c r="F416" s="81"/>
@@ -34866,7 +34876,7 @@
       <c r="N417" s="102"/>
       <c r="O417" s="102"/>
       <c r="P417" s="102"/>
-      <c r="Q417" s="405"/>
+      <c r="Q417" s="404"/>
       <c r="R417" s="102"/>
       <c r="S417" s="102"/>
       <c r="T417" s="102"/>
@@ -34899,7 +34909,7 @@
       <c r="N418" s="104"/>
       <c r="O418" s="104"/>
       <c r="P418" s="104"/>
-      <c r="Q418" s="407"/>
+      <c r="Q418" s="406"/>
       <c r="R418" s="104"/>
       <c r="S418" s="104"/>
       <c r="T418" s="104"/>
@@ -34932,7 +34942,7 @@
       <c r="N419" s="106"/>
       <c r="O419" s="106"/>
       <c r="P419" s="106"/>
-      <c r="Q419" s="402"/>
+      <c r="Q419" s="401"/>
       <c r="R419" s="106"/>
       <c r="S419" s="106"/>
       <c r="T419" s="106"/>
@@ -34953,7 +34963,7 @@
     <row r="420" spans="1:33" ht="11.45" customHeight="1">
       <c r="A420" s="206"/>
       <c r="B420" s="206"/>
-      <c r="C420" s="382"/>
+      <c r="C420" s="381"/>
       <c r="D420" s="296"/>
       <c r="E420" s="78"/>
       <c r="F420" s="78"/>
@@ -34965,7 +34975,7 @@
       <c r="N420" s="78"/>
       <c r="O420" s="78"/>
       <c r="P420" s="78"/>
-      <c r="Q420" s="406"/>
+      <c r="Q420" s="405"/>
       <c r="R420" s="78"/>
       <c r="S420" s="78"/>
       <c r="T420" s="78"/>
@@ -34986,7 +34996,7 @@
     <row r="421" spans="1:33" ht="11.45" customHeight="1">
       <c r="A421" s="204"/>
       <c r="B421" s="204"/>
-      <c r="C421" s="380"/>
+      <c r="C421" s="379"/>
       <c r="D421" s="86"/>
       <c r="E421" s="88"/>
       <c r="F421" s="88"/>
@@ -34998,7 +35008,7 @@
       <c r="N421" s="88"/>
       <c r="O421" s="88"/>
       <c r="P421" s="88"/>
-      <c r="Q421" s="403"/>
+      <c r="Q421" s="402"/>
       <c r="R421" s="88"/>
       <c r="S421" s="88"/>
       <c r="T421" s="88"/>
@@ -35019,7 +35029,7 @@
     <row r="422" spans="1:33" ht="11.45" customHeight="1">
       <c r="A422" s="203"/>
       <c r="B422" s="203"/>
-      <c r="C422" s="377"/>
+      <c r="C422" s="376"/>
       <c r="D422" s="80"/>
       <c r="E422" s="56"/>
       <c r="F422" s="56"/>
@@ -35031,7 +35041,7 @@
       <c r="N422" s="56"/>
       <c r="O422" s="56"/>
       <c r="P422" s="56"/>
-      <c r="Q422" s="404"/>
+      <c r="Q422" s="403"/>
       <c r="R422" s="56"/>
       <c r="S422" s="56"/>
       <c r="T422" s="56"/>
@@ -35052,7 +35062,7 @@
     <row r="423" spans="1:33" ht="11.45" customHeight="1">
       <c r="A423" s="214"/>
       <c r="B423" s="214"/>
-      <c r="C423" s="378"/>
+      <c r="C423" s="377"/>
       <c r="D423" s="108"/>
       <c r="E423" s="81"/>
       <c r="F423" s="81"/>
@@ -35097,7 +35107,7 @@
       <c r="N424" s="102"/>
       <c r="O424" s="102"/>
       <c r="P424" s="102"/>
-      <c r="Q424" s="405"/>
+      <c r="Q424" s="404"/>
       <c r="R424" s="102"/>
       <c r="S424" s="102"/>
       <c r="T424" s="102"/>
@@ -35130,7 +35140,7 @@
       <c r="N425" s="104"/>
       <c r="O425" s="104"/>
       <c r="P425" s="104"/>
-      <c r="Q425" s="407"/>
+      <c r="Q425" s="406"/>
       <c r="R425" s="104"/>
       <c r="S425" s="104"/>
       <c r="T425" s="104"/>
@@ -35163,7 +35173,7 @@
       <c r="N426" s="106"/>
       <c r="O426" s="106"/>
       <c r="P426" s="106"/>
-      <c r="Q426" s="402"/>
+      <c r="Q426" s="401"/>
       <c r="R426" s="106"/>
       <c r="S426" s="106"/>
       <c r="T426" s="106"/>
@@ -35184,7 +35194,7 @@
     <row r="427" spans="1:33" ht="11.45" customHeight="1">
       <c r="A427" s="206"/>
       <c r="B427" s="206"/>
-      <c r="C427" s="382"/>
+      <c r="C427" s="381"/>
       <c r="D427" s="296"/>
       <c r="E427" s="78"/>
       <c r="F427" s="78"/>
@@ -35196,7 +35206,7 @@
       <c r="N427" s="78"/>
       <c r="O427" s="78"/>
       <c r="P427" s="78"/>
-      <c r="Q427" s="406"/>
+      <c r="Q427" s="405"/>
       <c r="R427" s="78"/>
       <c r="S427" s="78"/>
       <c r="T427" s="78"/>
@@ -35217,7 +35227,7 @@
     <row r="428" spans="1:33" ht="11.45" customHeight="1">
       <c r="A428" s="204"/>
       <c r="B428" s="204"/>
-      <c r="C428" s="380"/>
+      <c r="C428" s="379"/>
       <c r="D428" s="86"/>
       <c r="E428" s="88"/>
       <c r="F428" s="88"/>
@@ -35229,7 +35239,7 @@
       <c r="N428" s="88"/>
       <c r="O428" s="88"/>
       <c r="P428" s="88"/>
-      <c r="Q428" s="403"/>
+      <c r="Q428" s="402"/>
       <c r="R428" s="88"/>
       <c r="S428" s="88"/>
       <c r="T428" s="88"/>
@@ -35250,7 +35260,7 @@
     <row r="429" spans="1:33" ht="11.45" customHeight="1">
       <c r="A429" s="203"/>
       <c r="B429" s="203"/>
-      <c r="C429" s="377"/>
+      <c r="C429" s="376"/>
       <c r="D429" s="80"/>
       <c r="E429" s="56"/>
       <c r="F429" s="56"/>
@@ -35262,7 +35272,7 @@
       <c r="N429" s="56"/>
       <c r="O429" s="56"/>
       <c r="P429" s="56"/>
-      <c r="Q429" s="404"/>
+      <c r="Q429" s="403"/>
       <c r="R429" s="56"/>
       <c r="S429" s="56"/>
       <c r="T429" s="56"/>
@@ -35283,7 +35293,7 @@
     <row r="430" spans="1:33" ht="11.45" customHeight="1">
       <c r="A430" s="214"/>
       <c r="B430" s="214"/>
-      <c r="C430" s="378"/>
+      <c r="C430" s="377"/>
       <c r="D430" s="108"/>
       <c r="E430" s="81"/>
       <c r="F430" s="81"/>
@@ -35328,7 +35338,7 @@
       <c r="N431" s="102"/>
       <c r="O431" s="102"/>
       <c r="P431" s="102"/>
-      <c r="Q431" s="405"/>
+      <c r="Q431" s="404"/>
       <c r="R431" s="102"/>
       <c r="S431" s="102"/>
       <c r="T431" s="102"/>
@@ -35361,7 +35371,7 @@
       <c r="N432" s="104"/>
       <c r="O432" s="104"/>
       <c r="P432" s="104"/>
-      <c r="Q432" s="407"/>
+      <c r="Q432" s="406"/>
       <c r="R432" s="104"/>
       <c r="S432" s="104"/>
       <c r="T432" s="104"/>
@@ -35394,7 +35404,7 @@
       <c r="N433" s="106"/>
       <c r="O433" s="106"/>
       <c r="P433" s="106"/>
-      <c r="Q433" s="402"/>
+      <c r="Q433" s="401"/>
       <c r="R433" s="106"/>
       <c r="S433" s="106"/>
       <c r="T433" s="106"/>
@@ -35415,7 +35425,7 @@
     <row r="434" spans="1:33" ht="11.45" customHeight="1">
       <c r="A434" s="206"/>
       <c r="B434" s="206"/>
-      <c r="C434" s="382"/>
+      <c r="C434" s="381"/>
       <c r="D434" s="296"/>
       <c r="E434" s="78"/>
       <c r="F434" s="78"/>
@@ -35427,7 +35437,7 @@
       <c r="N434" s="78"/>
       <c r="O434" s="78"/>
       <c r="P434" s="78"/>
-      <c r="Q434" s="406"/>
+      <c r="Q434" s="405"/>
       <c r="R434" s="78"/>
       <c r="S434" s="78"/>
       <c r="T434" s="78"/>
@@ -35448,7 +35458,7 @@
     <row r="435" spans="1:33" ht="11.45" customHeight="1">
       <c r="A435" s="204"/>
       <c r="B435" s="204"/>
-      <c r="C435" s="380"/>
+      <c r="C435" s="379"/>
       <c r="D435" s="86"/>
       <c r="E435" s="88"/>
       <c r="F435" s="88"/>
@@ -35460,7 +35470,7 @@
       <c r="N435" s="88"/>
       <c r="O435" s="88"/>
       <c r="P435" s="88"/>
-      <c r="Q435" s="403"/>
+      <c r="Q435" s="402"/>
       <c r="R435" s="88"/>
       <c r="S435" s="88"/>
       <c r="T435" s="88"/>
@@ -35481,7 +35491,7 @@
     <row r="436" spans="1:33" ht="11.45" customHeight="1">
       <c r="A436" s="203"/>
       <c r="B436" s="203"/>
-      <c r="C436" s="377"/>
+      <c r="C436" s="376"/>
       <c r="D436" s="80"/>
       <c r="E436" s="56"/>
       <c r="F436" s="56"/>
@@ -35493,7 +35503,7 @@
       <c r="N436" s="56"/>
       <c r="O436" s="56"/>
       <c r="P436" s="56"/>
-      <c r="Q436" s="404"/>
+      <c r="Q436" s="403"/>
       <c r="R436" s="56"/>
       <c r="S436" s="56"/>
       <c r="T436" s="56"/>
@@ -35514,7 +35524,7 @@
     <row r="437" spans="1:33" ht="11.45" customHeight="1">
       <c r="A437" s="214"/>
       <c r="B437" s="214"/>
-      <c r="C437" s="378"/>
+      <c r="C437" s="377"/>
       <c r="D437" s="108"/>
       <c r="E437" s="81"/>
       <c r="F437" s="81"/>
@@ -35559,7 +35569,7 @@
       <c r="N438" s="102"/>
       <c r="O438" s="102"/>
       <c r="P438" s="102"/>
-      <c r="Q438" s="405"/>
+      <c r="Q438" s="404"/>
       <c r="R438" s="102"/>
       <c r="S438" s="102"/>
       <c r="T438" s="102"/>
@@ -35592,7 +35602,7 @@
       <c r="N439" s="104"/>
       <c r="O439" s="104"/>
       <c r="P439" s="104"/>
-      <c r="Q439" s="407"/>
+      <c r="Q439" s="406"/>
       <c r="R439" s="104"/>
       <c r="S439" s="104"/>
       <c r="T439" s="104"/>
@@ -35625,7 +35635,7 @@
       <c r="N440" s="106"/>
       <c r="O440" s="106"/>
       <c r="P440" s="106"/>
-      <c r="Q440" s="402"/>
+      <c r="Q440" s="401"/>
       <c r="R440" s="106"/>
       <c r="S440" s="106"/>
       <c r="T440" s="106"/>
@@ -35646,7 +35656,7 @@
     <row r="441" spans="1:33" ht="11.45" customHeight="1">
       <c r="A441" s="206"/>
       <c r="B441" s="206"/>
-      <c r="C441" s="382"/>
+      <c r="C441" s="381"/>
       <c r="D441" s="296"/>
       <c r="E441" s="78"/>
       <c r="F441" s="78"/>
@@ -35658,7 +35668,7 @@
       <c r="N441" s="78"/>
       <c r="O441" s="78"/>
       <c r="P441" s="78"/>
-      <c r="Q441" s="406"/>
+      <c r="Q441" s="405"/>
       <c r="R441" s="78"/>
       <c r="S441" s="78"/>
       <c r="T441" s="78"/>
@@ -35679,7 +35689,7 @@
     <row r="442" spans="1:33" ht="11.45" customHeight="1">
       <c r="A442" s="204"/>
       <c r="B442" s="204"/>
-      <c r="C442" s="380"/>
+      <c r="C442" s="379"/>
       <c r="D442" s="86"/>
       <c r="E442" s="88"/>
       <c r="F442" s="88"/>
@@ -35691,7 +35701,7 @@
       <c r="N442" s="88"/>
       <c r="O442" s="88"/>
       <c r="P442" s="88"/>
-      <c r="Q442" s="403"/>
+      <c r="Q442" s="402"/>
       <c r="R442" s="88"/>
       <c r="S442" s="88"/>
       <c r="T442" s="88"/>
@@ -35712,7 +35722,7 @@
     <row r="443" spans="1:33" ht="11.45" customHeight="1">
       <c r="A443" s="203"/>
       <c r="B443" s="203"/>
-      <c r="C443" s="377"/>
+      <c r="C443" s="376"/>
       <c r="D443" s="80"/>
       <c r="E443" s="56"/>
       <c r="F443" s="56"/>
@@ -35724,7 +35734,7 @@
       <c r="N443" s="56"/>
       <c r="O443" s="56"/>
       <c r="P443" s="56"/>
-      <c r="Q443" s="404"/>
+      <c r="Q443" s="403"/>
       <c r="R443" s="56"/>
       <c r="S443" s="56"/>
       <c r="T443" s="56"/>
@@ -35745,7 +35755,7 @@
     <row r="444" spans="1:33" ht="11.45" customHeight="1">
       <c r="A444" s="214"/>
       <c r="B444" s="214"/>
-      <c r="C444" s="378"/>
+      <c r="C444" s="377"/>
       <c r="D444" s="108"/>
       <c r="E444" s="81"/>
       <c r="F444" s="81"/>
@@ -35790,7 +35800,7 @@
       <c r="N445" s="102"/>
       <c r="O445" s="102"/>
       <c r="P445" s="102"/>
-      <c r="Q445" s="405"/>
+      <c r="Q445" s="404"/>
       <c r="R445" s="102"/>
       <c r="S445" s="102"/>
       <c r="T445" s="102"/>
@@ -35823,7 +35833,7 @@
       <c r="N446" s="104"/>
       <c r="O446" s="104"/>
       <c r="P446" s="104"/>
-      <c r="Q446" s="407"/>
+      <c r="Q446" s="406"/>
       <c r="R446" s="104"/>
       <c r="S446" s="104"/>
       <c r="T446" s="104"/>
@@ -35856,7 +35866,7 @@
       <c r="N447" s="106"/>
       <c r="O447" s="106"/>
       <c r="P447" s="106"/>
-      <c r="Q447" s="402"/>
+      <c r="Q447" s="401"/>
       <c r="R447" s="106"/>
       <c r="S447" s="106"/>
       <c r="T447" s="106"/>
@@ -35877,7 +35887,7 @@
     <row r="448" spans="1:33" ht="11.45" customHeight="1">
       <c r="A448" s="206"/>
       <c r="B448" s="206"/>
-      <c r="C448" s="382"/>
+      <c r="C448" s="381"/>
       <c r="D448" s="296"/>
       <c r="E448" s="78"/>
       <c r="F448" s="78"/>
@@ -35889,7 +35899,7 @@
       <c r="N448" s="78"/>
       <c r="O448" s="78"/>
       <c r="P448" s="78"/>
-      <c r="Q448" s="406"/>
+      <c r="Q448" s="405"/>
       <c r="R448" s="78"/>
       <c r="S448" s="78"/>
       <c r="T448" s="78"/>
@@ -35910,7 +35920,7 @@
     <row r="449" spans="1:33" ht="11.45" customHeight="1">
       <c r="A449" s="204"/>
       <c r="B449" s="204"/>
-      <c r="C449" s="380"/>
+      <c r="C449" s="379"/>
       <c r="D449" s="86"/>
       <c r="E449" s="88"/>
       <c r="F449" s="88"/>
@@ -35922,7 +35932,7 @@
       <c r="N449" s="88"/>
       <c r="O449" s="88"/>
       <c r="P449" s="88"/>
-      <c r="Q449" s="403"/>
+      <c r="Q449" s="402"/>
       <c r="R449" s="88"/>
       <c r="S449" s="88"/>
       <c r="T449" s="88"/>
@@ -35943,7 +35953,7 @@
     <row r="450" spans="1:33" ht="11.45" customHeight="1">
       <c r="A450" s="203"/>
       <c r="B450" s="203"/>
-      <c r="C450" s="377"/>
+      <c r="C450" s="376"/>
       <c r="D450" s="80"/>
       <c r="E450" s="56"/>
       <c r="F450" s="56"/>
@@ -35955,7 +35965,7 @@
       <c r="N450" s="56"/>
       <c r="O450" s="56"/>
       <c r="P450" s="56"/>
-      <c r="Q450" s="404"/>
+      <c r="Q450" s="403"/>
       <c r="R450" s="56"/>
       <c r="S450" s="56"/>
       <c r="T450" s="56"/>
@@ -35976,7 +35986,7 @@
     <row r="451" spans="1:33" ht="11.45" customHeight="1">
       <c r="A451" s="214"/>
       <c r="B451" s="214"/>
-      <c r="C451" s="378"/>
+      <c r="C451" s="377"/>
       <c r="D451" s="108"/>
       <c r="E451" s="81"/>
       <c r="F451" s="81"/>
@@ -36021,7 +36031,7 @@
       <c r="N452" s="102"/>
       <c r="O452" s="102"/>
       <c r="P452" s="102"/>
-      <c r="Q452" s="405"/>
+      <c r="Q452" s="404"/>
       <c r="R452" s="102"/>
       <c r="S452" s="102"/>
       <c r="T452" s="102"/>
@@ -36054,7 +36064,7 @@
       <c r="N453" s="104"/>
       <c r="O453" s="104"/>
       <c r="P453" s="104"/>
-      <c r="Q453" s="407"/>
+      <c r="Q453" s="406"/>
       <c r="R453" s="104"/>
       <c r="S453" s="104"/>
       <c r="T453" s="104"/>
@@ -36087,7 +36097,7 @@
       <c r="N454" s="106"/>
       <c r="O454" s="106"/>
       <c r="P454" s="106"/>
-      <c r="Q454" s="402"/>
+      <c r="Q454" s="401"/>
       <c r="R454" s="106"/>
       <c r="S454" s="106"/>
       <c r="T454" s="106"/>
@@ -36108,7 +36118,7 @@
     <row r="455" spans="1:33" ht="11.45" customHeight="1">
       <c r="A455" s="206"/>
       <c r="B455" s="206"/>
-      <c r="C455" s="382"/>
+      <c r="C455" s="381"/>
       <c r="D455" s="296"/>
       <c r="E455" s="78"/>
       <c r="F455" s="78"/>
@@ -36120,7 +36130,7 @@
       <c r="N455" s="78"/>
       <c r="O455" s="78"/>
       <c r="P455" s="78"/>
-      <c r="Q455" s="406"/>
+      <c r="Q455" s="405"/>
       <c r="R455" s="78"/>
       <c r="S455" s="78"/>
       <c r="T455" s="78"/>
@@ -36141,7 +36151,7 @@
     <row r="456" spans="1:33" ht="11.45" customHeight="1">
       <c r="A456" s="204"/>
       <c r="B456" s="204"/>
-      <c r="C456" s="380"/>
+      <c r="C456" s="379"/>
       <c r="D456" s="86"/>
       <c r="E456" s="88"/>
       <c r="F456" s="88"/>
@@ -36153,7 +36163,7 @@
       <c r="N456" s="88"/>
       <c r="O456" s="88"/>
       <c r="P456" s="88"/>
-      <c r="Q456" s="403"/>
+      <c r="Q456" s="402"/>
       <c r="R456" s="88"/>
       <c r="S456" s="88"/>
       <c r="T456" s="88"/>
@@ -36174,7 +36184,7 @@
     <row r="457" spans="1:33" ht="11.45" customHeight="1">
       <c r="A457" s="203"/>
       <c r="B457" s="203"/>
-      <c r="C457" s="377"/>
+      <c r="C457" s="376"/>
       <c r="D457" s="80"/>
       <c r="E457" s="56"/>
       <c r="F457" s="56"/>
@@ -36186,7 +36196,7 @@
       <c r="N457" s="56"/>
       <c r="O457" s="56"/>
       <c r="P457" s="56"/>
-      <c r="Q457" s="404"/>
+      <c r="Q457" s="403"/>
       <c r="R457" s="56"/>
       <c r="S457" s="56"/>
       <c r="T457" s="56"/>
@@ -36207,7 +36217,7 @@
     <row r="458" spans="1:33" ht="11.45" customHeight="1">
       <c r="A458" s="214"/>
       <c r="B458" s="214"/>
-      <c r="C458" s="378"/>
+      <c r="C458" s="377"/>
       <c r="D458" s="108"/>
       <c r="E458" s="81"/>
       <c r="F458" s="81"/>
@@ -36252,7 +36262,7 @@
       <c r="N459" s="102"/>
       <c r="O459" s="102"/>
       <c r="P459" s="102"/>
-      <c r="Q459" s="405"/>
+      <c r="Q459" s="404"/>
       <c r="R459" s="102"/>
       <c r="S459" s="102"/>
       <c r="T459" s="102"/>
@@ -36285,7 +36295,7 @@
       <c r="N460" s="104"/>
       <c r="O460" s="104"/>
       <c r="P460" s="104"/>
-      <c r="Q460" s="407"/>
+      <c r="Q460" s="406"/>
       <c r="R460" s="104"/>
       <c r="S460" s="104"/>
       <c r="T460" s="104"/>
@@ -36318,7 +36328,7 @@
       <c r="N461" s="106"/>
       <c r="O461" s="106"/>
       <c r="P461" s="106"/>
-      <c r="Q461" s="402"/>
+      <c r="Q461" s="401"/>
       <c r="R461" s="106"/>
       <c r="S461" s="106"/>
       <c r="T461" s="106"/>
@@ -36339,7 +36349,7 @@
     <row r="462" spans="1:33" ht="11.45" customHeight="1">
       <c r="A462" s="206"/>
       <c r="B462" s="206"/>
-      <c r="C462" s="382"/>
+      <c r="C462" s="381"/>
       <c r="D462" s="296"/>
       <c r="E462" s="78"/>
       <c r="F462" s="78"/>
@@ -36351,7 +36361,7 @@
       <c r="N462" s="78"/>
       <c r="O462" s="78"/>
       <c r="P462" s="78"/>
-      <c r="Q462" s="406"/>
+      <c r="Q462" s="405"/>
       <c r="R462" s="78"/>
       <c r="S462" s="78"/>
       <c r="T462" s="78"/>
@@ -36372,7 +36382,7 @@
     <row r="463" spans="1:33" ht="11.45" customHeight="1">
       <c r="A463" s="204"/>
       <c r="B463" s="204"/>
-      <c r="C463" s="380"/>
+      <c r="C463" s="379"/>
       <c r="D463" s="86"/>
       <c r="E463" s="88"/>
       <c r="F463" s="88"/>
@@ -36384,7 +36394,7 @@
       <c r="N463" s="88"/>
       <c r="O463" s="88"/>
       <c r="P463" s="88"/>
-      <c r="Q463" s="403"/>
+      <c r="Q463" s="402"/>
       <c r="R463" s="88"/>
       <c r="S463" s="88"/>
       <c r="T463" s="88"/>
@@ -36405,7 +36415,7 @@
     <row r="464" spans="1:33" ht="11.45" customHeight="1">
       <c r="A464" s="203"/>
       <c r="B464" s="203"/>
-      <c r="C464" s="377"/>
+      <c r="C464" s="376"/>
       <c r="D464" s="80"/>
       <c r="E464" s="56"/>
       <c r="F464" s="56"/>
@@ -36417,7 +36427,7 @@
       <c r="N464" s="56"/>
       <c r="O464" s="56"/>
       <c r="P464" s="56"/>
-      <c r="Q464" s="404"/>
+      <c r="Q464" s="403"/>
       <c r="R464" s="56"/>
       <c r="S464" s="56"/>
       <c r="T464" s="56"/>
@@ -36438,7 +36448,7 @@
     <row r="465" spans="1:33" ht="11.45" customHeight="1">
       <c r="A465" s="214"/>
       <c r="B465" s="214"/>
-      <c r="C465" s="378"/>
+      <c r="C465" s="377"/>
       <c r="D465" s="108"/>
       <c r="E465" s="81"/>
       <c r="F465" s="81"/>
@@ -36483,7 +36493,7 @@
       <c r="N466" s="102"/>
       <c r="O466" s="102"/>
       <c r="P466" s="102"/>
-      <c r="Q466" s="405"/>
+      <c r="Q466" s="404"/>
       <c r="R466" s="102"/>
       <c r="S466" s="102"/>
       <c r="T466" s="102"/>
@@ -36516,7 +36526,7 @@
       <c r="N467" s="104"/>
       <c r="O467" s="104"/>
       <c r="P467" s="104"/>
-      <c r="Q467" s="407"/>
+      <c r="Q467" s="406"/>
       <c r="R467" s="104"/>
       <c r="S467" s="104"/>
       <c r="T467" s="104"/>
@@ -36549,7 +36559,7 @@
       <c r="N468" s="106"/>
       <c r="O468" s="106"/>
       <c r="P468" s="106"/>
-      <c r="Q468" s="402"/>
+      <c r="Q468" s="401"/>
       <c r="R468" s="106"/>
       <c r="S468" s="106"/>
       <c r="T468" s="106"/>
@@ -36570,7 +36580,7 @@
     <row r="469" spans="1:33" ht="11.45" customHeight="1">
       <c r="A469" s="206"/>
       <c r="B469" s="206"/>
-      <c r="C469" s="382"/>
+      <c r="C469" s="381"/>
       <c r="D469" s="296"/>
       <c r="E469" s="78"/>
       <c r="F469" s="78"/>
@@ -36582,7 +36592,7 @@
       <c r="N469" s="78"/>
       <c r="O469" s="78"/>
       <c r="P469" s="78"/>
-      <c r="Q469" s="406"/>
+      <c r="Q469" s="405"/>
       <c r="R469" s="78"/>
       <c r="S469" s="78"/>
       <c r="T469" s="78"/>
@@ -36603,7 +36613,7 @@
     <row r="470" spans="1:33" ht="11.45" customHeight="1">
       <c r="A470" s="204"/>
       <c r="B470" s="204"/>
-      <c r="C470" s="380"/>
+      <c r="C470" s="379"/>
       <c r="D470" s="86"/>
       <c r="E470" s="88"/>
       <c r="F470" s="88"/>
@@ -36615,7 +36625,7 @@
       <c r="N470" s="88"/>
       <c r="O470" s="88"/>
       <c r="P470" s="88"/>
-      <c r="Q470" s="403"/>
+      <c r="Q470" s="402"/>
       <c r="R470" s="88"/>
       <c r="S470" s="88"/>
       <c r="T470" s="88"/>
@@ -36636,7 +36646,7 @@
     <row r="471" spans="1:33" ht="11.45" customHeight="1">
       <c r="A471" s="203"/>
       <c r="B471" s="203"/>
-      <c r="C471" s="377"/>
+      <c r="C471" s="376"/>
       <c r="D471" s="80"/>
       <c r="E471" s="56"/>
       <c r="F471" s="56"/>
@@ -36648,7 +36658,7 @@
       <c r="N471" s="56"/>
       <c r="O471" s="56"/>
       <c r="P471" s="56"/>
-      <c r="Q471" s="404"/>
+      <c r="Q471" s="403"/>
       <c r="R471" s="56"/>
       <c r="S471" s="56"/>
       <c r="T471" s="56"/>
@@ -36669,7 +36679,7 @@
     <row r="472" spans="1:33" ht="11.45" customHeight="1">
       <c r="A472" s="214"/>
       <c r="B472" s="214"/>
-      <c r="C472" s="378"/>
+      <c r="C472" s="377"/>
       <c r="D472" s="108"/>
       <c r="E472" s="81"/>
       <c r="F472" s="81"/>
@@ -36714,7 +36724,7 @@
       <c r="N473" s="102"/>
       <c r="O473" s="102"/>
       <c r="P473" s="102"/>
-      <c r="Q473" s="405"/>
+      <c r="Q473" s="404"/>
       <c r="R473" s="102"/>
       <c r="S473" s="102"/>
       <c r="T473" s="102"/>
@@ -36747,7 +36757,7 @@
       <c r="N474" s="104"/>
       <c r="O474" s="104"/>
       <c r="P474" s="104"/>
-      <c r="Q474" s="407"/>
+      <c r="Q474" s="406"/>
       <c r="R474" s="104"/>
       <c r="S474" s="104"/>
       <c r="T474" s="104"/>
@@ -36780,7 +36790,7 @@
       <c r="N475" s="106"/>
       <c r="O475" s="106"/>
       <c r="P475" s="106"/>
-      <c r="Q475" s="402"/>
+      <c r="Q475" s="401"/>
       <c r="R475" s="106"/>
       <c r="S475" s="106"/>
       <c r="T475" s="106"/>
@@ -36801,7 +36811,7 @@
     <row r="476" spans="1:33" ht="11.45" customHeight="1">
       <c r="A476" s="206"/>
       <c r="B476" s="206"/>
-      <c r="C476" s="382"/>
+      <c r="C476" s="381"/>
       <c r="D476" s="296"/>
       <c r="E476" s="78"/>
       <c r="F476" s="78"/>
@@ -36813,7 +36823,7 @@
       <c r="N476" s="78"/>
       <c r="O476" s="78"/>
       <c r="P476" s="78"/>
-      <c r="Q476" s="406"/>
+      <c r="Q476" s="405"/>
       <c r="R476" s="78"/>
       <c r="S476" s="78"/>
       <c r="T476" s="78"/>
@@ -36834,7 +36844,7 @@
     <row r="477" spans="1:33" ht="11.45" customHeight="1">
       <c r="A477" s="204"/>
       <c r="B477" s="204"/>
-      <c r="C477" s="380"/>
+      <c r="C477" s="379"/>
       <c r="D477" s="86"/>
       <c r="E477" s="88"/>
       <c r="F477" s="88"/>
@@ -36846,7 +36856,7 @@
       <c r="N477" s="88"/>
       <c r="O477" s="88"/>
       <c r="P477" s="88"/>
-      <c r="Q477" s="403"/>
+      <c r="Q477" s="402"/>
       <c r="R477" s="88"/>
       <c r="S477" s="88"/>
       <c r="T477" s="88"/>
@@ -36867,7 +36877,7 @@
     <row r="478" spans="1:33" ht="11.45" customHeight="1">
       <c r="A478" s="203"/>
       <c r="B478" s="203"/>
-      <c r="C478" s="377"/>
+      <c r="C478" s="376"/>
       <c r="D478" s="80"/>
       <c r="E478" s="56"/>
       <c r="F478" s="56"/>
@@ -36879,7 +36889,7 @@
       <c r="N478" s="56"/>
       <c r="O478" s="56"/>
       <c r="P478" s="56"/>
-      <c r="Q478" s="404"/>
+      <c r="Q478" s="403"/>
       <c r="R478" s="56"/>
       <c r="S478" s="56"/>
       <c r="T478" s="56"/>
@@ -36900,7 +36910,7 @@
     <row r="479" spans="1:33" ht="11.45" customHeight="1">
       <c r="A479" s="214"/>
       <c r="B479" s="214"/>
-      <c r="C479" s="378"/>
+      <c r="C479" s="377"/>
       <c r="D479" s="108"/>
       <c r="E479" s="81"/>
       <c r="F479" s="81"/>
@@ -36945,7 +36955,7 @@
       <c r="N480" s="102"/>
       <c r="O480" s="102"/>
       <c r="P480" s="102"/>
-      <c r="Q480" s="405"/>
+      <c r="Q480" s="404"/>
       <c r="R480" s="102"/>
       <c r="S480" s="102"/>
       <c r="T480" s="102"/>
@@ -36978,7 +36988,7 @@
       <c r="N481" s="104"/>
       <c r="O481" s="104"/>
       <c r="P481" s="104"/>
-      <c r="Q481" s="407"/>
+      <c r="Q481" s="406"/>
       <c r="R481" s="104"/>
       <c r="S481" s="104"/>
       <c r="T481" s="104"/>
@@ -37011,7 +37021,7 @@
       <c r="N482" s="106"/>
       <c r="O482" s="106"/>
       <c r="P482" s="106"/>
-      <c r="Q482" s="402"/>
+      <c r="Q482" s="401"/>
       <c r="R482" s="106"/>
       <c r="S482" s="106"/>
       <c r="T482" s="106"/>
@@ -37032,7 +37042,7 @@
     <row r="483" spans="1:33" ht="11.45" customHeight="1">
       <c r="A483" s="206"/>
       <c r="B483" s="206"/>
-      <c r="C483" s="382"/>
+      <c r="C483" s="381"/>
       <c r="D483" s="296"/>
       <c r="E483" s="78"/>
       <c r="F483" s="78"/>
@@ -37044,7 +37054,7 @@
       <c r="N483" s="78"/>
       <c r="O483" s="78"/>
       <c r="P483" s="78"/>
-      <c r="Q483" s="406"/>
+      <c r="Q483" s="405"/>
       <c r="R483" s="78"/>
       <c r="S483" s="78"/>
       <c r="T483" s="78"/>
@@ -37065,7 +37075,7 @@
     <row r="484" spans="1:33" ht="11.45" customHeight="1">
       <c r="A484" s="204"/>
       <c r="B484" s="204"/>
-      <c r="C484" s="380"/>
+      <c r="C484" s="379"/>
       <c r="D484" s="86"/>
       <c r="E484" s="88"/>
       <c r="F484" s="88"/>
@@ -37077,7 +37087,7 @@
       <c r="N484" s="88"/>
       <c r="O484" s="88"/>
       <c r="P484" s="88"/>
-      <c r="Q484" s="403"/>
+      <c r="Q484" s="402"/>
       <c r="R484" s="88"/>
       <c r="S484" s="88"/>
       <c r="T484" s="88"/>
@@ -37098,7 +37108,7 @@
     <row r="485" spans="1:33" ht="11.45" customHeight="1">
       <c r="A485" s="203"/>
       <c r="B485" s="203"/>
-      <c r="C485" s="377"/>
+      <c r="C485" s="376"/>
       <c r="D485" s="80"/>
       <c r="E485" s="56"/>
       <c r="F485" s="56"/>
@@ -37110,7 +37120,7 @@
       <c r="N485" s="56"/>
       <c r="O485" s="56"/>
       <c r="P485" s="56"/>
-      <c r="Q485" s="404"/>
+      <c r="Q485" s="403"/>
       <c r="R485" s="56"/>
       <c r="S485" s="56"/>
       <c r="T485" s="56"/>
@@ -37131,7 +37141,7 @@
     <row r="486" spans="1:33" ht="11.45" customHeight="1">
       <c r="A486" s="214"/>
       <c r="B486" s="214"/>
-      <c r="C486" s="378"/>
+      <c r="C486" s="377"/>
       <c r="D486" s="108"/>
       <c r="E486" s="81"/>
       <c r="F486" s="81"/>
@@ -37176,7 +37186,7 @@
       <c r="N487" s="102"/>
       <c r="O487" s="102"/>
       <c r="P487" s="102"/>
-      <c r="Q487" s="405"/>
+      <c r="Q487" s="404"/>
       <c r="R487" s="102"/>
       <c r="S487" s="102"/>
       <c r="T487" s="102"/>
@@ -37209,7 +37219,7 @@
       <c r="N488" s="104"/>
       <c r="O488" s="104"/>
       <c r="P488" s="104"/>
-      <c r="Q488" s="407"/>
+      <c r="Q488" s="406"/>
       <c r="R488" s="104"/>
       <c r="S488" s="104"/>
       <c r="T488" s="104"/>
@@ -37242,7 +37252,7 @@
       <c r="N489" s="106"/>
       <c r="O489" s="106"/>
       <c r="P489" s="106"/>
-      <c r="Q489" s="402"/>
+      <c r="Q489" s="401"/>
       <c r="R489" s="106"/>
       <c r="S489" s="106"/>
       <c r="T489" s="106"/>
@@ -37263,7 +37273,7 @@
     <row r="490" spans="1:33" ht="11.45" customHeight="1">
       <c r="A490" s="206"/>
       <c r="B490" s="206"/>
-      <c r="C490" s="382"/>
+      <c r="C490" s="381"/>
       <c r="D490" s="296"/>
       <c r="E490" s="78"/>
       <c r="F490" s="78"/>
@@ -37275,7 +37285,7 @@
       <c r="N490" s="78"/>
       <c r="O490" s="78"/>
       <c r="P490" s="78"/>
-      <c r="Q490" s="406"/>
+      <c r="Q490" s="405"/>
       <c r="R490" s="78"/>
       <c r="S490" s="78"/>
       <c r="T490" s="78"/>
@@ -37296,7 +37306,7 @@
     <row r="491" spans="1:33" ht="11.45" customHeight="1">
       <c r="A491" s="204"/>
       <c r="B491" s="204"/>
-      <c r="C491" s="380"/>
+      <c r="C491" s="379"/>
       <c r="D491" s="86"/>
       <c r="E491" s="88"/>
       <c r="F491" s="88"/>
@@ -37308,7 +37318,7 @@
       <c r="N491" s="88"/>
       <c r="O491" s="88"/>
       <c r="P491" s="88"/>
-      <c r="Q491" s="403"/>
+      <c r="Q491" s="402"/>
       <c r="R491" s="88"/>
       <c r="S491" s="88"/>
       <c r="T491" s="88"/>
@@ -37329,7 +37339,7 @@
     <row r="492" spans="1:33" ht="11.45" customHeight="1">
       <c r="A492" s="203"/>
       <c r="B492" s="203"/>
-      <c r="C492" s="377"/>
+      <c r="C492" s="376"/>
       <c r="D492" s="80"/>
       <c r="E492" s="56"/>
       <c r="F492" s="56"/>
@@ -37341,7 +37351,7 @@
       <c r="N492" s="56"/>
       <c r="O492" s="56"/>
       <c r="P492" s="56"/>
-      <c r="Q492" s="404"/>
+      <c r="Q492" s="403"/>
       <c r="R492" s="56"/>
       <c r="S492" s="56"/>
       <c r="T492" s="56"/>
@@ -37362,7 +37372,7 @@
     <row r="493" spans="1:33" ht="11.45" customHeight="1">
       <c r="A493" s="214"/>
       <c r="B493" s="214"/>
-      <c r="C493" s="378"/>
+      <c r="C493" s="377"/>
       <c r="D493" s="108"/>
       <c r="E493" s="81"/>
       <c r="F493" s="81"/>
@@ -37407,7 +37417,7 @@
       <c r="N494" s="102"/>
       <c r="O494" s="102"/>
       <c r="P494" s="102"/>
-      <c r="Q494" s="405"/>
+      <c r="Q494" s="404"/>
       <c r="R494" s="102"/>
       <c r="S494" s="102"/>
       <c r="T494" s="102"/>
@@ -37440,7 +37450,7 @@
       <c r="N495" s="104"/>
       <c r="O495" s="104"/>
       <c r="P495" s="104"/>
-      <c r="Q495" s="407"/>
+      <c r="Q495" s="406"/>
       <c r="R495" s="104"/>
       <c r="S495" s="104"/>
       <c r="T495" s="104"/>
@@ -37473,7 +37483,7 @@
       <c r="N496" s="106"/>
       <c r="O496" s="106"/>
       <c r="P496" s="106"/>
-      <c r="Q496" s="402"/>
+      <c r="Q496" s="401"/>
       <c r="R496" s="106"/>
       <c r="S496" s="106"/>
       <c r="T496" s="106"/>
@@ -37494,7 +37504,7 @@
     <row r="497" spans="1:33" ht="11.45" customHeight="1">
       <c r="A497" s="206"/>
       <c r="B497" s="206"/>
-      <c r="C497" s="382"/>
+      <c r="C497" s="381"/>
       <c r="D497" s="296"/>
       <c r="E497" s="78"/>
       <c r="F497" s="78"/>
@@ -37506,7 +37516,7 @@
       <c r="N497" s="78"/>
       <c r="O497" s="78"/>
       <c r="P497" s="78"/>
-      <c r="Q497" s="406"/>
+      <c r="Q497" s="405"/>
       <c r="R497" s="78"/>
       <c r="S497" s="78"/>
       <c r="T497" s="78"/>
@@ -37527,7 +37537,7 @@
     <row r="498" spans="1:33" ht="11.45" customHeight="1">
       <c r="A498" s="204"/>
       <c r="B498" s="204"/>
-      <c r="C498" s="380"/>
+      <c r="C498" s="379"/>
       <c r="D498" s="86"/>
       <c r="E498" s="88"/>
       <c r="F498" s="88"/>
@@ -37539,7 +37549,7 @@
       <c r="N498" s="88"/>
       <c r="O498" s="88"/>
       <c r="P498" s="88"/>
-      <c r="Q498" s="403"/>
+      <c r="Q498" s="402"/>
       <c r="R498" s="88"/>
       <c r="S498" s="88"/>
       <c r="T498" s="88"/>
@@ -37560,7 +37570,7 @@
     <row r="499" spans="1:33" ht="11.45" customHeight="1">
       <c r="A499" s="203"/>
       <c r="B499" s="203"/>
-      <c r="C499" s="377"/>
+      <c r="C499" s="376"/>
       <c r="D499" s="80"/>
       <c r="E499" s="56"/>
       <c r="F499" s="56"/>
@@ -37572,7 +37582,7 @@
       <c r="N499" s="56"/>
       <c r="O499" s="56"/>
       <c r="P499" s="56"/>
-      <c r="Q499" s="404"/>
+      <c r="Q499" s="403"/>
       <c r="R499" s="56"/>
       <c r="S499" s="56"/>
       <c r="T499" s="56"/>
@@ -37593,7 +37603,7 @@
     <row r="500" spans="1:33" ht="11.45" customHeight="1">
       <c r="A500" s="214"/>
       <c r="B500" s="214"/>
-      <c r="C500" s="378"/>
+      <c r="C500" s="377"/>
       <c r="D500" s="108"/>
       <c r="E500" s="81"/>
       <c r="F500" s="81"/>
@@ -37638,7 +37648,7 @@
       <c r="N501" s="102"/>
       <c r="O501" s="102"/>
       <c r="P501" s="102"/>
-      <c r="Q501" s="405"/>
+      <c r="Q501" s="404"/>
       <c r="R501" s="102"/>
       <c r="S501" s="102"/>
       <c r="T501" s="102"/>
@@ -37671,7 +37681,7 @@
       <c r="N502" s="104"/>
       <c r="O502" s="104"/>
       <c r="P502" s="104"/>
-      <c r="Q502" s="407"/>
+      <c r="Q502" s="406"/>
       <c r="R502" s="104"/>
       <c r="S502" s="104"/>
       <c r="T502" s="104"/>
@@ -37704,7 +37714,7 @@
       <c r="N503" s="106"/>
       <c r="O503" s="106"/>
       <c r="P503" s="106"/>
-      <c r="Q503" s="402"/>
+      <c r="Q503" s="401"/>
       <c r="R503" s="106"/>
       <c r="S503" s="106"/>
       <c r="T503" s="106"/>
@@ -37725,7 +37735,7 @@
     <row r="504" spans="1:33" ht="11.45" customHeight="1">
       <c r="A504" s="206"/>
       <c r="B504" s="206"/>
-      <c r="C504" s="382"/>
+      <c r="C504" s="381"/>
       <c r="D504" s="296"/>
       <c r="E504" s="78"/>
       <c r="F504" s="78"/>
@@ -37737,7 +37747,7 @@
       <c r="N504" s="78"/>
       <c r="O504" s="78"/>
       <c r="P504" s="78"/>
-      <c r="Q504" s="406"/>
+      <c r="Q504" s="405"/>
       <c r="R504" s="78"/>
       <c r="S504" s="78"/>
       <c r="T504" s="78"/>
@@ -37758,7 +37768,7 @@
     <row r="505" spans="1:33" ht="11.45" customHeight="1">
       <c r="A505" s="204"/>
       <c r="B505" s="204"/>
-      <c r="C505" s="380"/>
+      <c r="C505" s="379"/>
       <c r="D505" s="86"/>
       <c r="E505" s="88"/>
       <c r="F505" s="88"/>
@@ -37770,7 +37780,7 @@
       <c r="N505" s="88"/>
       <c r="O505" s="88"/>
       <c r="P505" s="88"/>
-      <c r="Q505" s="403"/>
+      <c r="Q505" s="402"/>
       <c r="R505" s="88"/>
       <c r="S505" s="88"/>
       <c r="T505" s="88"/>
@@ -37791,7 +37801,7 @@
     <row r="506" spans="1:33" ht="11.45" customHeight="1">
       <c r="A506" s="203"/>
       <c r="B506" s="203"/>
-      <c r="C506" s="377"/>
+      <c r="C506" s="376"/>
       <c r="D506" s="80"/>
       <c r="E506" s="56"/>
       <c r="F506" s="56"/>
@@ -37803,7 +37813,7 @@
       <c r="N506" s="56"/>
       <c r="O506" s="56"/>
       <c r="P506" s="56"/>
-      <c r="Q506" s="404"/>
+      <c r="Q506" s="403"/>
       <c r="R506" s="56"/>
       <c r="S506" s="56"/>
       <c r="T506" s="56"/>
@@ -37824,7 +37834,7 @@
     <row r="507" spans="1:33" ht="11.45" customHeight="1">
       <c r="A507" s="214"/>
       <c r="B507" s="214"/>
-      <c r="C507" s="378"/>
+      <c r="C507" s="377"/>
       <c r="D507" s="108"/>
       <c r="E507" s="81"/>
       <c r="F507" s="81"/>
@@ -37869,7 +37879,7 @@
       <c r="N508" s="102"/>
       <c r="O508" s="102"/>
       <c r="P508" s="102"/>
-      <c r="Q508" s="405"/>
+      <c r="Q508" s="404"/>
       <c r="R508" s="102"/>
       <c r="S508" s="102"/>
       <c r="T508" s="102"/>
@@ -37902,7 +37912,7 @@
       <c r="N509" s="104"/>
       <c r="O509" s="104"/>
       <c r="P509" s="104"/>
-      <c r="Q509" s="407"/>
+      <c r="Q509" s="406"/>
       <c r="R509" s="104"/>
       <c r="S509" s="104"/>
       <c r="T509" s="104"/>
@@ -37935,7 +37945,7 @@
       <c r="N510" s="106"/>
       <c r="O510" s="106"/>
       <c r="P510" s="106"/>
-      <c r="Q510" s="402"/>
+      <c r="Q510" s="401"/>
       <c r="R510" s="106"/>
       <c r="S510" s="106"/>
       <c r="T510" s="106"/>
@@ -37956,7 +37966,7 @@
     <row r="511" spans="1:33" ht="11.45" customHeight="1">
       <c r="A511" s="206"/>
       <c r="B511" s="206"/>
-      <c r="C511" s="382"/>
+      <c r="C511" s="381"/>
       <c r="D511" s="296"/>
       <c r="E511" s="78"/>
       <c r="F511" s="78"/>
@@ -37968,7 +37978,7 @@
       <c r="N511" s="78"/>
       <c r="O511" s="78"/>
       <c r="P511" s="78"/>
-      <c r="Q511" s="406"/>
+      <c r="Q511" s="405"/>
       <c r="R511" s="78"/>
       <c r="S511" s="78"/>
       <c r="T511" s="78"/>
@@ -37989,7 +37999,7 @@
     <row r="512" spans="1:33" ht="11.45" customHeight="1">
       <c r="A512" s="204"/>
       <c r="B512" s="204"/>
-      <c r="C512" s="380"/>
+      <c r="C512" s="379"/>
       <c r="D512" s="86"/>
       <c r="E512" s="88"/>
       <c r="F512" s="88"/>
@@ -38001,7 +38011,7 @@
       <c r="N512" s="88"/>
       <c r="O512" s="88"/>
       <c r="P512" s="88"/>
-      <c r="Q512" s="403"/>
+      <c r="Q512" s="402"/>
       <c r="R512" s="88"/>
       <c r="S512" s="88"/>
       <c r="T512" s="88"/>
@@ -38022,7 +38032,7 @@
     <row r="513" spans="1:33" ht="11.45" customHeight="1">
       <c r="A513" s="203"/>
       <c r="B513" s="203"/>
-      <c r="C513" s="377"/>
+      <c r="C513" s="376"/>
       <c r="D513" s="80"/>
       <c r="E513" s="56"/>
       <c r="F513" s="56"/>
@@ -38034,7 +38044,7 @@
       <c r="N513" s="56"/>
       <c r="O513" s="56"/>
       <c r="P513" s="56"/>
-      <c r="Q513" s="404"/>
+      <c r="Q513" s="403"/>
       <c r="R513" s="56"/>
       <c r="S513" s="56"/>
       <c r="T513" s="56"/>
@@ -38055,7 +38065,7 @@
     <row r="514" spans="1:33" ht="11.45" customHeight="1">
       <c r="A514" s="214"/>
       <c r="B514" s="214"/>
-      <c r="C514" s="378"/>
+      <c r="C514" s="377"/>
       <c r="D514" s="108"/>
       <c r="E514" s="81"/>
       <c r="F514" s="81"/>
@@ -38100,7 +38110,7 @@
       <c r="N515" s="102"/>
       <c r="O515" s="102"/>
       <c r="P515" s="102"/>
-      <c r="Q515" s="405"/>
+      <c r="Q515" s="404"/>
       <c r="R515" s="102"/>
       <c r="S515" s="102"/>
       <c r="T515" s="102"/>
@@ -38133,7 +38143,7 @@
       <c r="N516" s="104"/>
       <c r="O516" s="104"/>
       <c r="P516" s="104"/>
-      <c r="Q516" s="407"/>
+      <c r="Q516" s="406"/>
       <c r="R516" s="104"/>
       <c r="S516" s="104"/>
       <c r="T516" s="104"/>
@@ -38166,7 +38176,7 @@
       <c r="N517" s="106"/>
       <c r="O517" s="106"/>
       <c r="P517" s="106"/>
-      <c r="Q517" s="402"/>
+      <c r="Q517" s="401"/>
       <c r="R517" s="106"/>
       <c r="S517" s="106"/>
       <c r="T517" s="106"/>
@@ -38187,7 +38197,7 @@
     <row r="518" spans="1:33" ht="11.45" customHeight="1">
       <c r="A518" s="206"/>
       <c r="B518" s="206"/>
-      <c r="C518" s="382"/>
+      <c r="C518" s="381"/>
       <c r="D518" s="296"/>
       <c r="E518" s="78"/>
       <c r="F518" s="78"/>
@@ -38199,7 +38209,7 @@
       <c r="N518" s="78"/>
       <c r="O518" s="78"/>
       <c r="P518" s="78"/>
-      <c r="Q518" s="406"/>
+      <c r="Q518" s="405"/>
       <c r="R518" s="78"/>
       <c r="S518" s="78"/>
       <c r="T518" s="78"/>
@@ -38220,7 +38230,7 @@
     <row r="519" spans="1:33" ht="11.45" customHeight="1">
       <c r="A519" s="204"/>
       <c r="B519" s="204"/>
-      <c r="C519" s="380"/>
+      <c r="C519" s="379"/>
       <c r="D519" s="86"/>
       <c r="E519" s="88"/>
       <c r="F519" s="88"/>
@@ -38232,7 +38242,7 @@
       <c r="N519" s="88"/>
       <c r="O519" s="88"/>
       <c r="P519" s="88"/>
-      <c r="Q519" s="403"/>
+      <c r="Q519" s="402"/>
       <c r="R519" s="88"/>
       <c r="S519" s="88"/>
       <c r="T519" s="88"/>
@@ -38253,7 +38263,7 @@
     <row r="520" spans="1:33" ht="11.45" customHeight="1">
       <c r="A520" s="203"/>
       <c r="B520" s="203"/>
-      <c r="C520" s="377"/>
+      <c r="C520" s="376"/>
       <c r="D520" s="80"/>
       <c r="E520" s="56"/>
       <c r="F520" s="56"/>
@@ -38265,7 +38275,7 @@
       <c r="N520" s="56"/>
       <c r="O520" s="56"/>
       <c r="P520" s="56"/>
-      <c r="Q520" s="404"/>
+      <c r="Q520" s="403"/>
       <c r="R520" s="56"/>
       <c r="S520" s="56"/>
       <c r="T520" s="56"/>
@@ -38286,7 +38296,7 @@
     <row r="521" spans="1:33" ht="11.45" customHeight="1">
       <c r="A521" s="214"/>
       <c r="B521" s="214"/>
-      <c r="C521" s="378"/>
+      <c r="C521" s="377"/>
       <c r="D521" s="108"/>
       <c r="E521" s="81"/>
       <c r="F521" s="81"/>
@@ -38331,7 +38341,7 @@
       <c r="N522" s="102"/>
       <c r="O522" s="102"/>
       <c r="P522" s="102"/>
-      <c r="Q522" s="405"/>
+      <c r="Q522" s="404"/>
       <c r="R522" s="102"/>
       <c r="S522" s="102"/>
       <c r="T522" s="102"/>
@@ -38364,7 +38374,7 @@
       <c r="N523" s="104"/>
       <c r="O523" s="104"/>
       <c r="P523" s="104"/>
-      <c r="Q523" s="407"/>
+      <c r="Q523" s="406"/>
       <c r="R523" s="104"/>
       <c r="S523" s="104"/>
       <c r="T523" s="104"/>
@@ -38397,7 +38407,7 @@
       <c r="N524" s="106"/>
       <c r="O524" s="106"/>
       <c r="P524" s="106"/>
-      <c r="Q524" s="402"/>
+      <c r="Q524" s="401"/>
       <c r="R524" s="106"/>
       <c r="S524" s="106"/>
       <c r="T524" s="106"/>
@@ -38418,7 +38428,7 @@
     <row r="525" spans="1:33" ht="11.45" customHeight="1">
       <c r="A525" s="206"/>
       <c r="B525" s="206"/>
-      <c r="C525" s="382"/>
+      <c r="C525" s="381"/>
       <c r="D525" s="296"/>
       <c r="E525" s="78"/>
       <c r="F525" s="78"/>
@@ -38430,7 +38440,7 @@
       <c r="N525" s="78"/>
       <c r="O525" s="78"/>
       <c r="P525" s="78"/>
-      <c r="Q525" s="406"/>
+      <c r="Q525" s="405"/>
       <c r="R525" s="78"/>
       <c r="S525" s="78"/>
       <c r="T525" s="78"/>
@@ -38451,7 +38461,7 @@
     <row r="526" spans="1:33" ht="11.45" customHeight="1">
       <c r="A526" s="204"/>
       <c r="B526" s="204"/>
-      <c r="C526" s="380"/>
+      <c r="C526" s="379"/>
       <c r="D526" s="86"/>
       <c r="E526" s="88"/>
       <c r="F526" s="88"/>
@@ -38463,7 +38473,7 @@
       <c r="N526" s="88"/>
       <c r="O526" s="88"/>
       <c r="P526" s="88"/>
-      <c r="Q526" s="403"/>
+      <c r="Q526" s="402"/>
       <c r="R526" s="88"/>
       <c r="S526" s="88"/>
       <c r="T526" s="88"/>
@@ -38484,7 +38494,7 @@
     <row r="527" spans="1:33" ht="11.45" customHeight="1">
       <c r="A527" s="203"/>
       <c r="B527" s="203"/>
-      <c r="C527" s="377"/>
+      <c r="C527" s="376"/>
       <c r="D527" s="80"/>
       <c r="E527" s="56"/>
       <c r="F527" s="56"/>
@@ -38496,7 +38506,7 @@
       <c r="N527" s="56"/>
       <c r="O527" s="56"/>
       <c r="P527" s="56"/>
-      <c r="Q527" s="404"/>
+      <c r="Q527" s="403"/>
       <c r="R527" s="56"/>
       <c r="S527" s="56"/>
       <c r="T527" s="56"/>
@@ -38517,7 +38527,7 @@
     <row r="528" spans="1:33" ht="11.45" customHeight="1">
       <c r="A528" s="214"/>
       <c r="B528" s="214"/>
-      <c r="C528" s="378"/>
+      <c r="C528" s="377"/>
       <c r="D528" s="108"/>
       <c r="E528" s="81"/>
       <c r="F528" s="81"/>
@@ -38562,7 +38572,7 @@
       <c r="N529" s="102"/>
       <c r="O529" s="102"/>
       <c r="P529" s="102"/>
-      <c r="Q529" s="405"/>
+      <c r="Q529" s="404"/>
       <c r="R529" s="102"/>
       <c r="S529" s="102"/>
       <c r="T529" s="102"/>
@@ -38595,7 +38605,7 @@
       <c r="N530" s="104"/>
       <c r="O530" s="104"/>
       <c r="P530" s="104"/>
-      <c r="Q530" s="407"/>
+      <c r="Q530" s="406"/>
       <c r="R530" s="104"/>
       <c r="S530" s="104"/>
       <c r="T530" s="104"/>
@@ -38628,7 +38638,7 @@
       <c r="N531" s="106"/>
       <c r="O531" s="106"/>
       <c r="P531" s="106"/>
-      <c r="Q531" s="402"/>
+      <c r="Q531" s="401"/>
       <c r="R531" s="106"/>
       <c r="S531" s="106"/>
       <c r="T531" s="106"/>
@@ -38649,7 +38659,7 @@
     <row r="532" spans="1:33" ht="11.45" customHeight="1">
       <c r="A532" s="206"/>
       <c r="B532" s="206"/>
-      <c r="C532" s="382"/>
+      <c r="C532" s="381"/>
       <c r="D532" s="296"/>
       <c r="E532" s="78"/>
       <c r="F532" s="78"/>
@@ -38661,7 +38671,7 @@
       <c r="N532" s="78"/>
       <c r="O532" s="78"/>
       <c r="P532" s="78"/>
-      <c r="Q532" s="406"/>
+      <c r="Q532" s="405"/>
       <c r="R532" s="78"/>
       <c r="S532" s="78"/>
       <c r="T532" s="78"/>
@@ -38682,7 +38692,7 @@
     <row r="533" spans="1:33" ht="11.45" customHeight="1">
       <c r="A533" s="204"/>
       <c r="B533" s="204"/>
-      <c r="C533" s="380"/>
+      <c r="C533" s="379"/>
       <c r="D533" s="86"/>
       <c r="E533" s="88"/>
       <c r="F533" s="88"/>
@@ -38694,7 +38704,7 @@
       <c r="N533" s="88"/>
       <c r="O533" s="88"/>
       <c r="P533" s="88"/>
-      <c r="Q533" s="403"/>
+      <c r="Q533" s="402"/>
       <c r="R533" s="88"/>
       <c r="S533" s="88"/>
       <c r="T533" s="88"/>
@@ -40144,7 +40154,7 @@
     <row r="42" spans="1:47" s="75" customFormat="1" ht="11.45" customHeight="1">
       <c r="A42" s="265"/>
       <c r="B42" s="206"/>
-      <c r="C42" s="382"/>
+      <c r="C42" s="381"/>
       <c r="D42" s="296"/>
       <c r="E42" s="78"/>
       <c r="F42" s="78"/>
@@ -42125,7 +42135,7 @@
         <v>46079</v>
       </c>
       <c r="B133" s="214"/>
-      <c r="C133" s="378"/>
+      <c r="C133" s="377"/>
       <c r="D133" s="108"/>
       <c r="E133" s="81" t="s">
         <v>27</v>
@@ -42163,7 +42173,7 @@
       <c r="P133" s="81" t="s">
         <v>176</v>
       </c>
-      <c r="Q133" s="450" t="s">
+      <c r="Q133" s="449" t="s">
         <v>2844</v>
       </c>
       <c r="R133" s="81"/>
@@ -42758,30 +42768,30 @@
       <c r="A35" s="69" t="s">
         <v>2919</v>
       </c>
-      <c r="B35" s="73" t="s">
-        <v>2920</v>
+      <c r="B35" s="67" t="s">
+        <v>3070</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="25.5" customHeight="1">
       <c r="A36" s="68" t="s">
+        <v>2920</v>
+      </c>
+      <c r="B36" s="70" t="s">
         <v>2921</v>
-      </c>
-      <c r="B36" s="70" t="s">
-        <v>2922</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="25.5" customHeight="1">
       <c r="A38" s="68"/>
       <c r="B38" s="70" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="25.5" customHeight="1">
       <c r="A39" s="68" t="s">
+        <v>2923</v>
+      </c>
+      <c r="B39" s="70" t="s">
         <v>2924</v>
-      </c>
-      <c r="B39" s="70" t="s">
-        <v>2925</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="25.5" customHeight="1">
@@ -42789,31 +42799,31 @@
         <v>27</v>
       </c>
       <c r="B40" s="70" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="25.5" customHeight="1">
       <c r="A41" s="68" t="s">
+        <v>2926</v>
+      </c>
+      <c r="B41" s="70" t="s">
         <v>2927</v>
-      </c>
-      <c r="B41" s="70" t="s">
-        <v>2928</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="25.5" customHeight="1">
       <c r="A42" s="68" t="s">
+        <v>2928</v>
+      </c>
+      <c r="B42" s="70" t="s">
         <v>2929</v>
-      </c>
-      <c r="B42" s="70" t="s">
-        <v>2930</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="25.5" customHeight="1">
       <c r="A43" s="68" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B43" s="70" t="s">
         <v>2931</v>
-      </c>
-      <c r="B43" s="70" t="s">
-        <v>2932</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="25.5" customHeight="1">
@@ -42821,33 +42831,33 @@
         <v>1112</v>
       </c>
       <c r="B44" s="70" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="42.95" customHeight="1">
       <c r="A46" s="216" t="s">
+        <v>2933</v>
+      </c>
+      <c r="B46" s="70" t="s">
         <v>2934</v>
-      </c>
-      <c r="B46" s="70" t="s">
-        <v>2935</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="12.95" customHeight="1">
       <c r="A49" s="71" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="25.5" customHeight="1">
       <c r="A50" s="70" t="s">
+        <v>2936</v>
+      </c>
+      <c r="B50" s="70" t="s">
         <v>2937</v>
-      </c>
-      <c r="B50" s="70" t="s">
-        <v>2938</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -42855,7 +42865,7 @@
         <v>62</v>
       </c>
       <c r="B53" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -42863,7 +42873,7 @@
         <v>394</v>
       </c>
       <c r="B54" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -42871,7 +42881,7 @@
         <v>1042</v>
       </c>
       <c r="B55" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -42879,7 +42889,7 @@
         <v>165</v>
       </c>
       <c r="B56" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -42887,7 +42897,7 @@
         <v>243</v>
       </c>
       <c r="B57" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -42895,7 +42905,7 @@
         <v>141</v>
       </c>
       <c r="B58" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -42903,7 +42913,7 @@
         <v>180</v>
       </c>
       <c r="B59" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -42911,12 +42921,12 @@
         <v>33</v>
       </c>
       <c r="B60" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -42924,7 +42934,7 @@
         <v>34</v>
       </c>
       <c r="B63" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -42932,7 +42942,7 @@
         <v>44</v>
       </c>
       <c r="B64" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -42940,7 +42950,7 @@
         <v>116</v>
       </c>
       <c r="B65" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -42948,7 +42958,7 @@
         <v>52</v>
       </c>
       <c r="B66" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="106" spans="2:2">
@@ -42981,7 +42991,7 @@
   <sheetData>
     <row r="1" spans="1:24" ht="29.25" customHeight="1">
       <c r="A1" s="10" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="11"/>
@@ -43012,7 +43022,7 @@
         <v>46079</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -68557,7 +68567,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="5" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -68570,60 +68580,60 @@
         <v>894</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
+        <v>2956</v>
+      </c>
+      <c r="F6" s="19" t="s">
         <v>2957</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>2958</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -68652,103 +68662,103 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15" customHeight="1">
       <c r="A1" s="262" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1">
       <c r="A2" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="12.6" customHeight="1">
       <c r="A3" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="12.6" customHeight="1"/>
     <row r="5" spans="1:2" ht="12.6" customHeight="1">
       <c r="A5" s="262" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" customHeight="1">
       <c r="A6" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="12.6" customHeight="1">
       <c r="A7" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="12.6" customHeight="1">
       <c r="A8" s="262" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="12.6" customHeight="1"/>
     <row r="10" spans="1:2" ht="12.6" customHeight="1">
       <c r="A10" s="262" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="12.6" customHeight="1">
       <c r="A11" t="s">
+        <v>2975</v>
+      </c>
+      <c r="B11" t="s">
         <v>2976</v>
-      </c>
-      <c r="B11" t="s">
-        <v>2977</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="12.6" customHeight="1">
       <c r="A12" t="s">
+        <v>2977</v>
+      </c>
+      <c r="B12" t="s">
         <v>2978</v>
-      </c>
-      <c r="B12" t="s">
-        <v>2979</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="51.95" customHeight="1">
       <c r="A13" t="s">
+        <v>2979</v>
+      </c>
+      <c r="B13" t="s">
         <v>2980</v>
-      </c>
-      <c r="B13" t="s">
-        <v>2981</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="12.6" customHeight="1">
       <c r="A14" t="s">
+        <v>2981</v>
+      </c>
+      <c r="B14" t="s">
         <v>2982</v>
-      </c>
-      <c r="B14" t="s">
-        <v>2983</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="12.6" customHeight="1">
       <c r="A15" t="s">
+        <v>2983</v>
+      </c>
+      <c r="B15" t="s">
         <v>2984</v>
-      </c>
-      <c r="B15" t="s">
-        <v>2985</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="12.6" customHeight="1"/>
     <row r="17" spans="1:3" ht="12.6" customHeight="1">
       <c r="A17" s="262" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="12.6" customHeight="1">
       <c r="B18" t="s">
+        <v>2986</v>
+      </c>
+      <c r="C18" t="s">
         <v>2987</v>
-      </c>
-      <c r="C18" t="s">
-        <v>2988</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="24.95" customHeight="1">
       <c r="A19" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="B19">
         <v>277</v>
@@ -68756,7 +68766,7 @@
     </row>
     <row r="20" spans="1:3" ht="12.6" customHeight="1">
       <c r="A20" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
       <c r="B20">
         <v>83</v>
@@ -68767,7 +68777,7 @@
     </row>
     <row r="21" spans="1:3" ht="24.95" customHeight="1">
       <c r="A21" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="B21">
         <v>11</v>
@@ -68778,7 +68788,7 @@
     </row>
     <row r="22" spans="1:3" ht="12.6" customHeight="1">
       <c r="A22" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="B22">
         <v>52</v>
@@ -68789,7 +68799,7 @@
     </row>
     <row r="23" spans="1:3" ht="24.95" customHeight="1">
       <c r="A23" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="B23">
         <v>15</v>
@@ -68800,7 +68810,7 @@
     </row>
     <row r="24" spans="1:3" ht="12.6" customHeight="1">
       <c r="A24" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="B24">
         <v>5</v>
@@ -68811,7 +68821,7 @@
     </row>
     <row r="25" spans="1:3" ht="12.6" customHeight="1">
       <c r="A25" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="B25">
         <v>194</v>
@@ -68823,15 +68833,15 @@
     <row r="26" spans="1:3" ht="12.6" customHeight="1"/>
     <row r="27" spans="1:3" ht="12.6" customHeight="1">
       <c r="A27" s="262" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="12.6" customHeight="1">
       <c r="A28" t="s">
+        <v>2996</v>
+      </c>
+      <c r="B28" t="s">
         <v>2997</v>
-      </c>
-      <c r="B28" t="s">
-        <v>2998</v>
       </c>
       <c r="C28" s="260">
         <v>0.94199999999999995</v>
@@ -68839,10 +68849,10 @@
     </row>
     <row r="29" spans="1:3" ht="12.6" customHeight="1">
       <c r="A29" t="s">
+        <v>2998</v>
+      </c>
+      <c r="B29" t="s">
         <v>2999</v>
-      </c>
-      <c r="B29" t="s">
-        <v>3000</v>
       </c>
       <c r="C29" s="260">
         <v>0.73299999999999998</v>
@@ -68850,10 +68860,10 @@
     </row>
     <row r="30" spans="1:3" ht="12.6" customHeight="1">
       <c r="A30" t="s">
+        <v>3000</v>
+      </c>
+      <c r="B30" t="s">
         <v>3001</v>
-      </c>
-      <c r="B30" t="s">
-        <v>3002</v>
       </c>
       <c r="C30" s="260">
         <v>0.39</v>
@@ -68861,10 +68871,10 @@
     </row>
     <row r="31" spans="1:3" ht="12.6" customHeight="1">
       <c r="A31" t="s">
+        <v>3002</v>
+      </c>
+      <c r="B31" t="s">
         <v>3003</v>
-      </c>
-      <c r="B31" t="s">
-        <v>3004</v>
       </c>
       <c r="C31" s="260">
         <v>0.108</v>
@@ -68873,47 +68883,47 @@
     <row r="32" spans="1:3" ht="12.6" customHeight="1"/>
     <row r="33" spans="1:9" ht="12.6" customHeight="1">
       <c r="A33" s="262" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="12.6" customHeight="1">
       <c r="A34" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="12.6" customHeight="1"/>
     <row r="36" spans="1:9" ht="12.6" customHeight="1">
       <c r="A36" s="262" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="12.6" customHeight="1">
       <c r="A37" t="s">
+        <v>3007</v>
+      </c>
+      <c r="B37" t="s">
         <v>3008</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>3009</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>3010</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>3011</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>3012</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>3013</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>3014</v>
       </c>
-      <c r="H37" t="s">
+      <c r="I37" t="s">
         <v>3015</v>
-      </c>
-      <c r="I37" t="s">
-        <v>3016</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="12.6" customHeight="1">
@@ -68921,10 +68931,10 @@
         <v>143</v>
       </c>
       <c r="B38" t="s">
+        <v>3016</v>
+      </c>
+      <c r="D38" t="s">
         <v>3017</v>
-      </c>
-      <c r="D38" t="s">
-        <v>3018</v>
       </c>
       <c r="E38" t="s">
         <v>32</v>
@@ -68944,7 +68954,7 @@
         <v>149</v>
       </c>
       <c r="B39" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="D39" t="s">
         <v>1432</v>
@@ -68967,13 +68977,13 @@
     </row>
     <row r="40" spans="1:9" ht="12.6" customHeight="1">
       <c r="B40" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="C40" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="D40" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="E40" t="s">
         <v>32</v>
@@ -68993,7 +69003,7 @@
         <v>166</v>
       </c>
       <c r="B41" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="E41" t="s">
         <v>51</v>
@@ -69013,7 +69023,7 @@
         <v>1432</v>
       </c>
       <c r="D42" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="E42" t="s">
         <v>32</v>
@@ -69036,7 +69046,7 @@
         <v>692</v>
       </c>
       <c r="B43" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="C43" t="s">
         <v>1432</v>
@@ -69062,13 +69072,13 @@
         <v>938</v>
       </c>
       <c r="B44" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="C44" t="s">
         <v>1432</v>
       </c>
       <c r="D44" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="E44" t="s">
         <v>32</v>
@@ -69091,19 +69101,19 @@
         <v>1113</v>
       </c>
       <c r="B45" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="C45" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="D45" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="E45" t="s">
         <v>51</v>
       </c>
       <c r="F45" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="G45" t="s">
         <v>243</v>
@@ -69120,19 +69130,19 @@
         <v>1118</v>
       </c>
       <c r="B46" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="C46" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="D46" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="E46" t="s">
         <v>51</v>
       </c>
       <c r="F46" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="G46" t="s">
         <v>141</v>
@@ -69155,7 +69165,7 @@
         <v>1432</v>
       </c>
       <c r="D47" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="E47" t="s">
         <v>32</v>
@@ -69181,7 +69191,7 @@
         <v>1432</v>
       </c>
       <c r="D48" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="E48" t="s">
         <v>32</v>
@@ -69199,33 +69209,33 @@
     <row r="49" spans="1:9" ht="12.6" customHeight="1"/>
     <row r="50" spans="1:9" ht="12.6" customHeight="1">
       <c r="A50" s="262" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="12.6" customHeight="1">
       <c r="B51" t="s">
+        <v>3023</v>
+      </c>
+      <c r="C51" t="s">
         <v>3024</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>3025</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>3026</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>3027</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>3028</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
         <v>3029</v>
       </c>
-      <c r="H51" t="s">
+      <c r="I51" t="s">
         <v>3030</v>
-      </c>
-      <c r="I51" t="s">
-        <v>3031</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="12.6" customHeight="1">
@@ -69259,7 +69269,7 @@
     </row>
     <row r="53" spans="1:9" ht="12.6" customHeight="1">
       <c r="A53" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="B53">
         <v>3</v>
@@ -69288,7 +69298,7 @@
     </row>
     <row r="54" spans="1:9" ht="12.6" customHeight="1">
       <c r="A54" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="B54">
         <v>8</v>
@@ -69318,33 +69328,33 @@
     <row r="55" spans="1:9" ht="12.6" customHeight="1"/>
     <row r="56" spans="1:9" ht="12.6" customHeight="1">
       <c r="A56" s="262" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="12.6" customHeight="1">
       <c r="B57" t="s">
+        <v>3023</v>
+      </c>
+      <c r="C57" t="s">
         <v>3024</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>3025</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>3026</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>3027</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>3028</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
         <v>3029</v>
       </c>
-      <c r="H57" t="s">
+      <c r="I57" t="s">
         <v>3030</v>
-      </c>
-      <c r="I57" t="s">
-        <v>3031</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="12.6" customHeight="1">
@@ -69378,7 +69388,7 @@
     </row>
     <row r="59" spans="1:9" ht="12.6" customHeight="1">
       <c r="A59" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="B59">
         <v>8</v>
@@ -69407,7 +69417,7 @@
     </row>
     <row r="60" spans="1:9" ht="12.6" customHeight="1">
       <c r="A60" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="B60">
         <v>10</v>
@@ -69437,33 +69447,33 @@
     <row r="61" spans="1:9" ht="12.6" customHeight="1"/>
     <row r="62" spans="1:9" ht="12.6" customHeight="1">
       <c r="A62" s="262" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="12.6" customHeight="1">
       <c r="B63" t="s">
+        <v>3023</v>
+      </c>
+      <c r="C63" t="s">
         <v>3024</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
         <v>3025</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>3026</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>3027</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>3028</v>
       </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
         <v>3029</v>
       </c>
-      <c r="H63" t="s">
+      <c r="I63" t="s">
         <v>3030</v>
-      </c>
-      <c r="I63" t="s">
-        <v>3031</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="12.6" customHeight="1">
@@ -69526,7 +69536,7 @@
     </row>
     <row r="66" spans="1:9" ht="12.6" customHeight="1">
       <c r="A66" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="B66">
         <v>11</v>
@@ -69556,33 +69566,33 @@
     <row r="67" spans="1:9" ht="12.6" customHeight="1"/>
     <row r="68" spans="1:9" ht="12.6" customHeight="1">
       <c r="A68" s="262" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="12.6" customHeight="1">
       <c r="B69" t="s">
+        <v>3023</v>
+      </c>
+      <c r="C69" t="s">
         <v>3024</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
         <v>3025</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>3026</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>3027</v>
       </c>
-      <c r="F69" t="s">
+      <c r="G69" t="s">
         <v>3028</v>
       </c>
-      <c r="G69" t="s">
+      <c r="H69" t="s">
         <v>3029</v>
       </c>
-      <c r="H69" t="s">
+      <c r="I69" t="s">
         <v>3030</v>
-      </c>
-      <c r="I69" t="s">
-        <v>3031</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="12.6" customHeight="1">
@@ -69674,7 +69684,7 @@
     </row>
     <row r="73" spans="1:9" ht="12.6" customHeight="1">
       <c r="A73" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -69704,33 +69714,33 @@
     <row r="74" spans="1:9" ht="12.6" customHeight="1"/>
     <row r="75" spans="1:9" ht="12.6" customHeight="1">
       <c r="A75" s="262" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="12.6" customHeight="1">
       <c r="B76" t="s">
+        <v>3023</v>
+      </c>
+      <c r="C76" t="s">
         <v>3024</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>3025</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>3026</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>3027</v>
       </c>
-      <c r="F76" t="s">
+      <c r="G76" t="s">
         <v>3028</v>
       </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
         <v>3029</v>
       </c>
-      <c r="H76" t="s">
+      <c r="I76" t="s">
         <v>3030</v>
-      </c>
-      <c r="I76" t="s">
-        <v>3031</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="12.6" customHeight="1">
@@ -69793,7 +69803,7 @@
     </row>
     <row r="79" spans="1:9" ht="12.6" customHeight="1">
       <c r="A79" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -69851,7 +69861,7 @@
     </row>
     <row r="81" spans="1:9" ht="12.6" customHeight="1">
       <c r="A81" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="B81">
         <v>7</v>
@@ -69881,38 +69891,38 @@
     <row r="82" spans="1:9" ht="12.6" customHeight="1"/>
     <row r="83" spans="1:9" ht="12.6" customHeight="1">
       <c r="A83" s="262" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="12.6" customHeight="1">
       <c r="B84" t="s">
+        <v>3023</v>
+      </c>
+      <c r="C84" t="s">
         <v>3024</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
         <v>3025</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>3026</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>3027</v>
       </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>3028</v>
       </c>
-      <c r="G84" t="s">
+      <c r="H84" t="s">
         <v>3029</v>
       </c>
-      <c r="H84" t="s">
+      <c r="I84" t="s">
         <v>3030</v>
-      </c>
-      <c r="I84" t="s">
-        <v>3031</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="12.6" customHeight="1">
       <c r="A85" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="B85">
         <v>6</v>
@@ -69941,7 +69951,7 @@
     </row>
     <row r="86" spans="1:9" ht="12.6" customHeight="1">
       <c r="A86" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -69970,7 +69980,7 @@
     </row>
     <row r="87" spans="1:9" ht="12.6" customHeight="1">
       <c r="A87" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="B87">
         <v>3</v>
@@ -69999,7 +70009,7 @@
     </row>
     <row r="88" spans="1:9" ht="12.6" customHeight="1">
       <c r="A88" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="B88">
         <v>11</v>
@@ -70029,33 +70039,33 @@
     <row r="89" spans="1:9" ht="12.6" customHeight="1"/>
     <row r="90" spans="1:9" ht="12.6" customHeight="1">
       <c r="A90" s="262" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="12.6" customHeight="1">
       <c r="B91" t="s">
+        <v>3023</v>
+      </c>
+      <c r="C91" t="s">
         <v>3024</v>
       </c>
-      <c r="C91" t="s">
+      <c r="D91" t="s">
         <v>3025</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
         <v>3026</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
         <v>3027</v>
       </c>
-      <c r="F91" t="s">
+      <c r="G91" t="s">
         <v>3028</v>
       </c>
-      <c r="G91" t="s">
+      <c r="H91" t="s">
         <v>3029</v>
       </c>
-      <c r="H91" t="s">
+      <c r="I91" t="s">
         <v>3030</v>
-      </c>
-      <c r="I91" t="s">
-        <v>3031</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="12.6" customHeight="1">
@@ -70118,7 +70128,7 @@
     </row>
     <row r="94" spans="1:9" ht="12.6" customHeight="1">
       <c r="A94" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="B94">
         <v>11</v>
@@ -70148,33 +70158,33 @@
     <row r="95" spans="1:9" ht="12.6" customHeight="1"/>
     <row r="96" spans="1:9" ht="12.6" customHeight="1">
       <c r="A96" s="262" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="12.6" customHeight="1">
       <c r="B97" t="s">
+        <v>3023</v>
+      </c>
+      <c r="C97" t="s">
         <v>3024</v>
       </c>
-      <c r="C97" t="s">
+      <c r="D97" t="s">
         <v>3025</v>
       </c>
-      <c r="D97" t="s">
+      <c r="E97" t="s">
         <v>3026</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
         <v>3027</v>
       </c>
-      <c r="F97" t="s">
+      <c r="G97" t="s">
         <v>3028</v>
       </c>
-      <c r="G97" t="s">
+      <c r="H97" t="s">
         <v>3029</v>
       </c>
-      <c r="H97" t="s">
+      <c r="I97" t="s">
         <v>3030</v>
-      </c>
-      <c r="I97" t="s">
-        <v>3031</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="12.6" customHeight="1">
@@ -70411,7 +70421,7 @@
     </row>
     <row r="106" spans="1:9" ht="12.6" customHeight="1">
       <c r="A106" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="B106">
         <v>8</v>
@@ -70441,33 +70451,33 @@
     <row r="107" spans="1:9" ht="12.6" customHeight="1"/>
     <row r="108" spans="1:9" ht="12.6" customHeight="1">
       <c r="A108" s="262" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="12.6" customHeight="1">
       <c r="B109" t="s">
+        <v>3023</v>
+      </c>
+      <c r="C109" t="s">
         <v>3024</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
         <v>3025</v>
       </c>
-      <c r="D109" t="s">
+      <c r="E109" t="s">
         <v>3026</v>
       </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
         <v>3027</v>
       </c>
-      <c r="F109" t="s">
+      <c r="G109" t="s">
         <v>3028</v>
       </c>
-      <c r="G109" t="s">
+      <c r="H109" t="s">
         <v>3029</v>
       </c>
-      <c r="H109" t="s">
+      <c r="I109" t="s">
         <v>3030</v>
-      </c>
-      <c r="I109" t="s">
-        <v>3031</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="12.6" customHeight="1">
@@ -70588,7 +70598,7 @@
     </row>
     <row r="114" spans="1:9" ht="12.6" customHeight="1">
       <c r="A114" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="B114">
         <v>10</v>
@@ -70618,38 +70628,38 @@
     <row r="115" spans="1:9" ht="12.6" customHeight="1"/>
     <row r="116" spans="1:9" ht="12.6" customHeight="1">
       <c r="A116" s="262" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="12.6" customHeight="1">
       <c r="B117" t="s">
+        <v>3023</v>
+      </c>
+      <c r="C117" t="s">
         <v>3024</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
         <v>3025</v>
       </c>
-      <c r="D117" t="s">
+      <c r="E117" t="s">
         <v>3026</v>
       </c>
-      <c r="E117" t="s">
+      <c r="F117" t="s">
         <v>3027</v>
       </c>
-      <c r="F117" t="s">
+      <c r="G117" t="s">
         <v>3028</v>
       </c>
-      <c r="G117" t="s">
+      <c r="H117" t="s">
         <v>3029</v>
       </c>
-      <c r="H117" t="s">
+      <c r="I117" t="s">
         <v>3030</v>
-      </c>
-      <c r="I117" t="s">
-        <v>3031</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="12.6" customHeight="1">
       <c r="A118" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="B118">
         <v>2</v>
@@ -70678,7 +70688,7 @@
     </row>
     <row r="119" spans="1:9" ht="12.6" customHeight="1">
       <c r="A119" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="B119">
         <v>6</v>
@@ -70707,7 +70717,7 @@
     </row>
     <row r="120" spans="1:9" ht="12.6" customHeight="1">
       <c r="A120" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="B120">
         <v>8</v>
@@ -70737,75 +70747,75 @@
     <row r="121" spans="1:9" ht="12.6" customHeight="1"/>
     <row r="122" spans="1:9" ht="12.6" customHeight="1">
       <c r="A122" s="262" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="12.6" customHeight="1"/>
     <row r="124" spans="1:9" ht="12.6" customHeight="1">
       <c r="A124" s="262" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="12.6" customHeight="1">
       <c r="A125" s="262" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="12.6" customHeight="1"/>
     <row r="127" spans="1:9" ht="12.6" customHeight="1">
       <c r="A127" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="12.6" customHeight="1">
       <c r="A128" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
     </row>
     <row r="129" spans="1:1" ht="12.6" customHeight="1">
       <c r="A129" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="130" spans="1:1" ht="12.6" customHeight="1">
       <c r="A130" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
     </row>
     <row r="131" spans="1:1" ht="12.6" customHeight="1">
       <c r="A131" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="132" spans="1:1" ht="12.6" customHeight="1">
       <c r="A132" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
     </row>
     <row r="133" spans="1:1" ht="12.6" customHeight="1">
       <c r="A133" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="134" spans="1:1" ht="12.6" customHeight="1">
       <c r="A134" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="135" spans="1:1" ht="12.6" customHeight="1">
       <c r="A135" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
     </row>
     <row r="136" spans="1:1" ht="12.6" customHeight="1">
       <c r="A136" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="137" spans="1:1" ht="12.6" customHeight="1"/>
     <row r="138" spans="1:1" ht="12.6" customHeight="1">
       <c r="A138" s="262" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="139" spans="1:1" ht="12.6" customHeight="1"/>

--- a/j-busqueda clientes/j-clientes-gle.xlsx
+++ b/j-busqueda clientes/j-clientes-gle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rocio\OneDrive\documentos\TRABAJOS AUTONOMOS\JURADA\j-busqueda clientes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC2A7A41-F0CC-436A-BECA-FEBB3DDE851D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA96B70-6F6B-4B2F-8DBC-688FBCA75807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1260" yWindow="-120" windowWidth="27660" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5270" uniqueCount="3072">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5270" uniqueCount="3073">
   <si>
     <t>fechaEmail</t>
   </si>
@@ -9303,6 +9303,9 @@
   </si>
   <si>
     <t>v / 0,9/pal (rebajo desde 11 céntimos)</t>
+  </si>
+  <si>
+    <t>v / 0,11/pal /30-40 doc</t>
   </si>
 </sst>
 </file>
@@ -22752,7 +22755,7 @@
         <v>46076.958333333343</v>
       </c>
       <c r="C192" s="399" t="s">
-        <v>1112</v>
+        <v>3072</v>
       </c>
       <c r="D192" s="109">
         <v>46036</v>

--- a/j-busqueda clientes/j-clientes-gle.xlsx
+++ b/j-busqueda clientes/j-clientes-gle.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rocio\OneDrive\documentos\TRABAJOS AUTONOMOS\JURADA\j-busqueda clientes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88153b17ae7a9f01/documentos/TRABAJOS AUTONOMOS/JURADA/j-busqueda clientes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC0EFC44-3F1E-411F-B361-DCAF094CE636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{BC0EFC44-3F1E-411F-B361-DCAF094CE636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7613A66-034C-4EA6-A99B-358128BC6273}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="-120" windowWidth="27660" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="810" yWindow="-110" windowWidth="24900" windowHeight="14500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="clientes" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5589" uniqueCount="3317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5590" uniqueCount="3317">
   <si>
     <t>fechaEmail</t>
   </si>
@@ -12274,31 +12274,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:AG533"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="11.45" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="11.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.140625" style="410" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="350" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" style="389" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" style="75" customWidth="1"/>
-    <col min="5" max="5" width="4.42578125" style="75" customWidth="1"/>
-    <col min="6" max="6" width="4.140625" style="75" customWidth="1"/>
-    <col min="7" max="7" width="5.140625" style="75" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" style="125" customWidth="1"/>
+    <col min="1" max="1" width="10.1796875" style="410" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" style="350" customWidth="1"/>
+    <col min="3" max="3" width="9.54296875" style="389" customWidth="1"/>
+    <col min="4" max="4" width="13.26953125" style="75" customWidth="1"/>
+    <col min="5" max="5" width="4.453125" style="75" customWidth="1"/>
+    <col min="6" max="6" width="4.1796875" style="75" customWidth="1"/>
+    <col min="7" max="7" width="5.1796875" style="75" customWidth="1"/>
+    <col min="8" max="8" width="16.54296875" style="125" customWidth="1"/>
     <col min="9" max="9" width="18" style="120" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" style="125" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" style="120" customWidth="1"/>
-    <col min="12" max="12" width="13.85546875" style="125" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" style="198" customWidth="1"/>
-    <col min="14" max="14" width="3.7109375" style="75" customWidth="1"/>
-    <col min="15" max="15" width="4.5703125" style="75" customWidth="1"/>
-    <col min="16" max="16" width="7.85546875" style="75" customWidth="1"/>
-    <col min="17" max="17" width="17.5703125" style="434" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="75" customWidth="1"/>
-    <col min="19" max="23" width="7.28515625" style="75" customWidth="1"/>
-    <col min="24" max="25" width="7.28515625" style="75" hidden="1" customWidth="1"/>
-    <col min="26" max="33" width="7.28515625" style="75" customWidth="1"/>
-    <col min="34" max="46" width="14.42578125" style="75" customWidth="1"/>
-    <col min="47" max="16384" width="14.42578125" style="75"/>
+    <col min="10" max="10" width="9.54296875" style="125" customWidth="1"/>
+    <col min="11" max="11" width="15.81640625" style="120" customWidth="1"/>
+    <col min="12" max="12" width="13.81640625" style="125" customWidth="1"/>
+    <col min="13" max="13" width="6.81640625" style="198" customWidth="1"/>
+    <col min="14" max="14" width="3.7265625" style="75" customWidth="1"/>
+    <col min="15" max="15" width="4.54296875" style="75" customWidth="1"/>
+    <col min="16" max="16" width="7.81640625" style="75" customWidth="1"/>
+    <col min="17" max="17" width="17.54296875" style="434" customWidth="1"/>
+    <col min="18" max="18" width="14.453125" style="75" customWidth="1"/>
+    <col min="19" max="23" width="7.26953125" style="75" customWidth="1"/>
+    <col min="24" max="25" width="7.26953125" style="75" hidden="1" customWidth="1"/>
+    <col min="26" max="33" width="7.26953125" style="75" customWidth="1"/>
+    <col min="34" max="46" width="14.453125" style="75" customWidth="1"/>
+    <col min="47" max="16384" width="14.453125" style="75"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="26.25" customHeight="1">
@@ -12392,7 +12392,7 @@
       <c r="AF1" s="26"/>
       <c r="AG1" s="26"/>
     </row>
-    <row r="2" spans="1:33" ht="11.45" customHeight="1">
+    <row r="2" spans="1:33" ht="11.5" customHeight="1">
       <c r="A2" s="209">
         <v>45770</v>
       </c>
@@ -12449,7 +12449,7 @@
       <c r="AF2" s="102"/>
       <c r="AG2" s="102"/>
     </row>
-    <row r="3" spans="1:33" ht="11.45" customHeight="1">
+    <row r="3" spans="1:33" ht="11.5" customHeight="1">
       <c r="A3" s="205">
         <v>46000</v>
       </c>
@@ -12504,7 +12504,7 @@
       <c r="AF3" s="104"/>
       <c r="AG3" s="104"/>
     </row>
-    <row r="4" spans="1:33" ht="11.45" customHeight="1">
+    <row r="4" spans="1:33" ht="11.5" customHeight="1">
       <c r="A4" s="207">
         <v>45776</v>
       </c>
@@ -12561,7 +12561,7 @@
       <c r="AF4" s="106"/>
       <c r="AG4" s="106"/>
     </row>
-    <row r="5" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="5" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A5" s="267">
         <v>45756</v>
       </c>
@@ -12620,7 +12620,7 @@
       <c r="AF5" s="263"/>
       <c r="AG5" s="263"/>
     </row>
-    <row r="6" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="6" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A6" s="270">
         <v>46000</v>
       </c>
@@ -12671,7 +12671,7 @@
       <c r="AF6" s="272"/>
       <c r="AG6" s="272"/>
     </row>
-    <row r="7" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="7" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A7" s="230">
         <v>46000</v>
       </c>
@@ -12724,7 +12724,7 @@
       <c r="AF7" s="274"/>
       <c r="AG7" s="274"/>
     </row>
-    <row r="8" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="8" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A8" s="275"/>
       <c r="B8" s="275"/>
       <c r="C8" s="371"/>
@@ -12767,7 +12767,7 @@
       <c r="AF8" s="277"/>
       <c r="AG8" s="277"/>
     </row>
-    <row r="9" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="9" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A9" s="278"/>
       <c r="B9" s="278"/>
       <c r="C9" s="372"/>
@@ -12810,7 +12810,7 @@
       <c r="AF9" s="248"/>
       <c r="AG9" s="248"/>
     </row>
-    <row r="10" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="10" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A10" s="280"/>
       <c r="B10" s="280"/>
       <c r="C10" s="373"/>
@@ -12851,7 +12851,7 @@
       <c r="AF10" s="282"/>
       <c r="AG10" s="282"/>
     </row>
-    <row r="11" spans="1:33" s="286" customFormat="1" ht="11.45" customHeight="1">
+    <row r="11" spans="1:33" s="286" customFormat="1" ht="11.5" customHeight="1">
       <c r="A11" s="283">
         <v>45756</v>
       </c>
@@ -12918,7 +12918,7 @@
       <c r="AF11" s="285"/>
       <c r="AG11" s="285"/>
     </row>
-    <row r="12" spans="1:33" s="286" customFormat="1" ht="11.45" customHeight="1">
+    <row r="12" spans="1:33" s="286" customFormat="1" ht="11.5" customHeight="1">
       <c r="A12" s="283">
         <v>46059</v>
       </c>
@@ -12971,7 +12971,7 @@
       <c r="AF12" s="285"/>
       <c r="AG12" s="285"/>
     </row>
-    <row r="13" spans="1:33" s="286" customFormat="1" ht="11.45" customHeight="1">
+    <row r="13" spans="1:33" s="286" customFormat="1" ht="11.5" customHeight="1">
       <c r="A13" s="289">
         <v>46001</v>
       </c>
@@ -13022,7 +13022,7 @@
       <c r="AF13" s="291"/>
       <c r="AG13" s="291"/>
     </row>
-    <row r="14" spans="1:33" s="286" customFormat="1" ht="11.45" customHeight="1">
+    <row r="14" spans="1:33" s="286" customFormat="1" ht="11.5" customHeight="1">
       <c r="A14" s="289" t="s">
         <v>91</v>
       </c>
@@ -13071,7 +13071,7 @@
       <c r="AF14" s="291"/>
       <c r="AG14" s="291"/>
     </row>
-    <row r="15" spans="1:33" ht="11.45" customHeight="1">
+    <row r="15" spans="1:33" ht="11.5" customHeight="1">
       <c r="A15" s="203">
         <v>46000</v>
       </c>
@@ -13115,7 +13115,7 @@
       <c r="AF15" s="56"/>
       <c r="AG15" s="56"/>
     </row>
-    <row r="16" spans="1:33" ht="11.45" customHeight="1">
+    <row r="16" spans="1:33" ht="11.5" customHeight="1">
       <c r="A16" s="214">
         <v>46056</v>
       </c>
@@ -13162,7 +13162,7 @@
       <c r="AF16" s="81"/>
       <c r="AG16" s="81"/>
     </row>
-    <row r="17" spans="1:33" ht="11.45" customHeight="1">
+    <row r="17" spans="1:33" ht="11.5" customHeight="1">
       <c r="A17" s="209">
         <v>45757</v>
       </c>
@@ -13223,7 +13223,7 @@
       <c r="AF17" s="102"/>
       <c r="AG17" s="102"/>
     </row>
-    <row r="18" spans="1:33" ht="11.45" customHeight="1">
+    <row r="18" spans="1:33" ht="11.5" customHeight="1">
       <c r="A18" s="205">
         <v>45770</v>
       </c>
@@ -13279,7 +13279,7 @@
       <c r="AF18" s="104"/>
       <c r="AG18" s="104"/>
     </row>
-    <row r="19" spans="1:33" ht="11.45" customHeight="1">
+    <row r="19" spans="1:33" ht="11.5" customHeight="1">
       <c r="A19" s="207">
         <v>45770</v>
       </c>
@@ -13336,7 +13336,7 @@
       <c r="AF19" s="106"/>
       <c r="AG19" s="106"/>
     </row>
-    <row r="20" spans="1:33" ht="11.45" customHeight="1">
+    <row r="20" spans="1:33" ht="11.5" customHeight="1">
       <c r="A20" s="203">
         <v>46351</v>
       </c>
@@ -13399,7 +13399,7 @@
       <c r="AF20" s="56"/>
       <c r="AG20" s="56"/>
     </row>
-    <row r="21" spans="1:33" ht="11.45" customHeight="1">
+    <row r="21" spans="1:33" ht="11.5" customHeight="1">
       <c r="A21" s="206">
         <v>45770</v>
       </c>
@@ -13464,7 +13464,7 @@
       <c r="AF21" s="78"/>
       <c r="AG21" s="78"/>
     </row>
-    <row r="22" spans="1:33" ht="11.45" customHeight="1">
+    <row r="22" spans="1:33" ht="11.5" customHeight="1">
       <c r="A22" s="204">
         <v>45924</v>
       </c>
@@ -13526,7 +13526,7 @@
       <c r="AF22" s="88"/>
       <c r="AG22" s="88"/>
     </row>
-    <row r="23" spans="1:33" s="302" customFormat="1" ht="11.45" customHeight="1">
+    <row r="23" spans="1:33" s="302" customFormat="1" ht="11.5" customHeight="1">
       <c r="A23" s="298">
         <v>45770</v>
       </c>
@@ -13587,7 +13587,7 @@
       <c r="AF23" s="300"/>
       <c r="AG23" s="300"/>
     </row>
-    <row r="24" spans="1:33" ht="11.45" customHeight="1">
+    <row r="24" spans="1:33" ht="11.5" customHeight="1">
       <c r="A24" s="214">
         <v>45770</v>
       </c>
@@ -13654,7 +13654,7 @@
       <c r="AF24" s="81"/>
       <c r="AG24" s="81"/>
     </row>
-    <row r="25" spans="1:33" ht="11.45" customHeight="1">
+    <row r="25" spans="1:33" ht="11.5" customHeight="1">
       <c r="A25" s="209">
         <v>45770</v>
       </c>
@@ -13719,7 +13719,7 @@
       <c r="AF25" s="102"/>
       <c r="AG25" s="102"/>
     </row>
-    <row r="26" spans="1:33" ht="11.45" customHeight="1">
+    <row r="26" spans="1:33" ht="11.5" customHeight="1">
       <c r="A26" s="205">
         <v>45930</v>
       </c>
@@ -13780,7 +13780,7 @@
       <c r="AF26" s="104"/>
       <c r="AG26" s="104"/>
     </row>
-    <row r="27" spans="1:33" ht="11.45" customHeight="1">
+    <row r="27" spans="1:33" ht="11.5" customHeight="1">
       <c r="A27" s="207"/>
       <c r="B27" s="207"/>
       <c r="C27" s="367"/>
@@ -13823,7 +13823,7 @@
       <c r="AF27" s="106"/>
       <c r="AG27" s="106"/>
     </row>
-    <row r="28" spans="1:33" ht="11.45" customHeight="1">
+    <row r="28" spans="1:33" ht="11.5" customHeight="1">
       <c r="A28" s="206">
         <v>45790</v>
       </c>
@@ -13888,7 +13888,7 @@
       <c r="AF28" s="78"/>
       <c r="AG28" s="78"/>
     </row>
-    <row r="29" spans="1:33" ht="11.45" customHeight="1">
+    <row r="29" spans="1:33" ht="11.5" customHeight="1">
       <c r="A29" s="204">
         <v>45778</v>
       </c>
@@ -13959,7 +13959,7 @@
       <c r="AF29" s="88"/>
       <c r="AG29" s="88"/>
     </row>
-    <row r="30" spans="1:33" ht="11.45" customHeight="1">
+    <row r="30" spans="1:33" ht="11.5" customHeight="1">
       <c r="A30" s="203">
         <v>45814</v>
       </c>
@@ -14034,7 +14034,7 @@
       <c r="AF30" s="56"/>
       <c r="AG30" s="56"/>
     </row>
-    <row r="31" spans="1:33" ht="11.45" customHeight="1">
+    <row r="31" spans="1:33" ht="11.5" customHeight="1">
       <c r="A31" s="214">
         <v>45924</v>
       </c>
@@ -14095,7 +14095,7 @@
       <c r="AF31" s="81"/>
       <c r="AG31" s="81"/>
     </row>
-    <row r="32" spans="1:33" ht="11.45" customHeight="1">
+    <row r="32" spans="1:33" ht="11.5" customHeight="1">
       <c r="A32" s="209">
         <v>45924</v>
       </c>
@@ -14150,7 +14150,7 @@
       <c r="AF32" s="102"/>
       <c r="AG32" s="102"/>
     </row>
-    <row r="33" spans="1:33" ht="11.45" customHeight="1">
+    <row r="33" spans="1:33" ht="11.5" customHeight="1">
       <c r="A33" s="205"/>
       <c r="B33" s="205"/>
       <c r="C33" s="366"/>
@@ -14194,7 +14194,7 @@
       <c r="AF33" s="104"/>
       <c r="AG33" s="104"/>
     </row>
-    <row r="34" spans="1:33" ht="11.45" customHeight="1">
+    <row r="34" spans="1:33" ht="11.5" customHeight="1">
       <c r="A34" s="207">
         <v>45805</v>
       </c>
@@ -14257,7 +14257,7 @@
       <c r="AF34" s="106"/>
       <c r="AG34" s="106"/>
     </row>
-    <row r="35" spans="1:33" ht="11.45" customHeight="1">
+    <row r="35" spans="1:33" ht="11.5" customHeight="1">
       <c r="A35" s="206"/>
       <c r="B35" s="206">
         <v>46167</v>
@@ -14322,7 +14322,7 @@
       <c r="AF35" s="78"/>
       <c r="AG35" s="78"/>
     </row>
-    <row r="36" spans="1:33" ht="11.45" customHeight="1">
+    <row r="36" spans="1:33" ht="11.5" customHeight="1">
       <c r="A36" s="203"/>
       <c r="B36" s="203"/>
       <c r="C36" s="376"/>
@@ -14369,7 +14369,7 @@
       <c r="AF36" s="56"/>
       <c r="AG36" s="56"/>
     </row>
-    <row r="37" spans="1:33" ht="11.45" customHeight="1">
+    <row r="37" spans="1:33" ht="11.5" customHeight="1">
       <c r="A37" s="214">
         <v>45924</v>
       </c>
@@ -14434,7 +14434,7 @@
       <c r="AF37" s="81"/>
       <c r="AG37" s="81"/>
     </row>
-    <row r="38" spans="1:33" ht="11.45" customHeight="1">
+    <row r="38" spans="1:33" ht="11.5" customHeight="1">
       <c r="A38" s="209">
         <v>45810</v>
       </c>
@@ -14487,7 +14487,7 @@
       <c r="AF38" s="102"/>
       <c r="AG38" s="102"/>
     </row>
-    <row r="39" spans="1:33" ht="11.45" customHeight="1">
+    <row r="39" spans="1:33" ht="11.5" customHeight="1">
       <c r="A39" s="205">
         <v>45909</v>
       </c>
@@ -14546,7 +14546,7 @@
       <c r="AF39" s="104"/>
       <c r="AG39" s="104"/>
     </row>
-    <row r="40" spans="1:33" ht="11.45" customHeight="1">
+    <row r="40" spans="1:33" ht="11.5" customHeight="1">
       <c r="A40" s="207"/>
       <c r="B40" s="207">
         <v>45924</v>
@@ -14586,7 +14586,7 @@
       <c r="AF40" s="106"/>
       <c r="AG40" s="106"/>
     </row>
-    <row r="41" spans="1:33" ht="11.45" customHeight="1">
+    <row r="41" spans="1:33" ht="11.5" customHeight="1">
       <c r="A41" s="206"/>
       <c r="B41" s="206"/>
       <c r="C41" s="381"/>
@@ -14633,7 +14633,7 @@
       <c r="AF41" s="78"/>
       <c r="AG41" s="78"/>
     </row>
-    <row r="42" spans="1:33" ht="11.45" customHeight="1">
+    <row r="42" spans="1:33" ht="11.5" customHeight="1">
       <c r="A42" s="304">
         <v>45833</v>
       </c>
@@ -14698,7 +14698,7 @@
       <c r="AF42" s="306"/>
       <c r="AG42" s="306"/>
     </row>
-    <row r="43" spans="1:33" ht="11.45" customHeight="1">
+    <row r="43" spans="1:33" ht="11.5" customHeight="1">
       <c r="A43" s="203">
         <v>45812</v>
       </c>
@@ -14765,7 +14765,7 @@
       <c r="AF43" s="56"/>
       <c r="AG43" s="56"/>
     </row>
-    <row r="44" spans="1:33" ht="11.45" customHeight="1">
+    <row r="44" spans="1:33" ht="11.5" customHeight="1">
       <c r="A44" s="214"/>
       <c r="B44" s="214"/>
       <c r="C44" s="377"/>
@@ -14812,7 +14812,7 @@
       <c r="AF44" s="81"/>
       <c r="AG44" s="81"/>
     </row>
-    <row r="45" spans="1:33" ht="11.45" customHeight="1">
+    <row r="45" spans="1:33" ht="11.5" customHeight="1">
       <c r="A45" s="209">
         <v>45826</v>
       </c>
@@ -14875,7 +14875,7 @@
       <c r="AF45" s="102"/>
       <c r="AG45" s="102"/>
     </row>
-    <row r="46" spans="1:33" ht="11.45" customHeight="1">
+    <row r="46" spans="1:33" ht="11.5" customHeight="1">
       <c r="A46" s="205">
         <v>45840</v>
       </c>
@@ -14938,7 +14938,7 @@
       <c r="AF46" s="104"/>
       <c r="AG46" s="104"/>
     </row>
-    <row r="47" spans="1:33" ht="11.45" customHeight="1">
+    <row r="47" spans="1:33" ht="11.5" customHeight="1">
       <c r="A47" s="207">
         <v>45840</v>
       </c>
@@ -14995,7 +14995,7 @@
       <c r="AF47" s="106"/>
       <c r="AG47" s="106"/>
     </row>
-    <row r="48" spans="1:33" ht="11.45" customHeight="1">
+    <row r="48" spans="1:33" ht="11.5" customHeight="1">
       <c r="A48" s="206">
         <v>45840</v>
       </c>
@@ -15052,7 +15052,7 @@
       <c r="AF48" s="78"/>
       <c r="AG48" s="78"/>
     </row>
-    <row r="49" spans="1:33" ht="11.45" customHeight="1">
+    <row r="49" spans="1:33" ht="11.5" customHeight="1">
       <c r="A49" s="204">
         <v>45840</v>
       </c>
@@ -15115,7 +15115,7 @@
       <c r="AF49" s="88"/>
       <c r="AG49" s="88"/>
     </row>
-    <row r="50" spans="1:33" ht="11.45" customHeight="1" thickBot="1">
+    <row r="50" spans="1:33" ht="11.5" customHeight="1" thickBot="1">
       <c r="A50" s="203">
         <v>45846</v>
       </c>
@@ -15174,7 +15174,7 @@
       <c r="AF50" s="56"/>
       <c r="AG50" s="56"/>
     </row>
-    <row r="51" spans="1:33" ht="11.45" customHeight="1" thickBot="1">
+    <row r="51" spans="1:33" ht="11.5" customHeight="1" thickBot="1">
       <c r="A51" s="214"/>
       <c r="B51" s="214"/>
       <c r="C51" s="377"/>
@@ -15221,7 +15221,7 @@
       <c r="AF51" s="81"/>
       <c r="AG51" s="81"/>
     </row>
-    <row r="52" spans="1:33" ht="11.45" customHeight="1">
+    <row r="52" spans="1:33" ht="11.5" customHeight="1">
       <c r="A52" s="209">
         <v>45846</v>
       </c>
@@ -15282,7 +15282,7 @@
       <c r="AF52" s="102"/>
       <c r="AG52" s="102"/>
     </row>
-    <row r="53" spans="1:33" ht="11.45" customHeight="1">
+    <row r="53" spans="1:33" ht="11.5" customHeight="1">
       <c r="A53" s="205">
         <v>45909</v>
       </c>
@@ -15339,7 +15339,7 @@
       <c r="AF53" s="104"/>
       <c r="AG53" s="104"/>
     </row>
-    <row r="54" spans="1:33" ht="11.45" customHeight="1">
+    <row r="54" spans="1:33" ht="11.5" customHeight="1">
       <c r="A54" s="207"/>
       <c r="B54" s="207"/>
       <c r="C54" s="367"/>
@@ -15381,7 +15381,7 @@
       <c r="AF54" s="106"/>
       <c r="AG54" s="106"/>
     </row>
-    <row r="55" spans="1:33" ht="11.45" customHeight="1">
+    <row r="55" spans="1:33" ht="11.5" customHeight="1">
       <c r="A55" s="206">
         <v>45909</v>
       </c>
@@ -15442,7 +15442,7 @@
       <c r="AF55" s="78"/>
       <c r="AG55" s="78"/>
     </row>
-    <row r="56" spans="1:33" ht="11.45" customHeight="1">
+    <row r="56" spans="1:33" ht="11.5" customHeight="1">
       <c r="A56" s="204"/>
       <c r="B56" s="204"/>
       <c r="C56" s="379"/>
@@ -15491,7 +15491,7 @@
       <c r="AF56" s="88"/>
       <c r="AG56" s="88"/>
     </row>
-    <row r="57" spans="1:33" ht="11.45" customHeight="1">
+    <row r="57" spans="1:33" ht="11.5" customHeight="1">
       <c r="A57" s="203">
         <v>45909</v>
       </c>
@@ -15556,7 +15556,7 @@
       <c r="AF57" s="56"/>
       <c r="AG57" s="56"/>
     </row>
-    <row r="58" spans="1:33" ht="11.45" customHeight="1">
+    <row r="58" spans="1:33" ht="11.5" customHeight="1">
       <c r="A58" s="214">
         <v>45959</v>
       </c>
@@ -15617,7 +15617,7 @@
       <c r="AF58" s="81"/>
       <c r="AG58" s="81"/>
     </row>
-    <row r="59" spans="1:33" ht="11.45" customHeight="1">
+    <row r="59" spans="1:33" ht="11.5" customHeight="1">
       <c r="A59" s="209">
         <v>45909</v>
       </c>
@@ -15684,7 +15684,7 @@
       <c r="AF59" s="102"/>
       <c r="AG59" s="102"/>
     </row>
-    <row r="60" spans="1:33" ht="11.45" customHeight="1">
+    <row r="60" spans="1:33" ht="11.5" customHeight="1">
       <c r="A60" s="205">
         <v>45819</v>
       </c>
@@ -15749,7 +15749,7 @@
       <c r="AF60" s="104"/>
       <c r="AG60" s="104"/>
     </row>
-    <row r="61" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="61" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A61" s="267">
         <v>45909</v>
       </c>
@@ -15806,7 +15806,7 @@
       <c r="AF61" s="263"/>
       <c r="AG61" s="263"/>
     </row>
-    <row r="62" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="62" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A62" s="270">
         <v>45909</v>
       </c>
@@ -15861,7 +15861,7 @@
       <c r="AF62" s="272"/>
       <c r="AG62" s="272"/>
     </row>
-    <row r="63" spans="1:33" ht="11.45" customHeight="1">
+    <row r="63" spans="1:33" ht="11.5" customHeight="1">
       <c r="A63" s="203">
         <v>45909</v>
       </c>
@@ -15934,7 +15934,7 @@
       <c r="AF63" s="56"/>
       <c r="AG63" s="56"/>
     </row>
-    <row r="64" spans="1:33" ht="11.45" customHeight="1">
+    <row r="64" spans="1:33" ht="11.5" customHeight="1">
       <c r="A64" s="214">
         <v>45909</v>
       </c>
@@ -16003,7 +16003,7 @@
       <c r="AF64" s="81"/>
       <c r="AG64" s="81"/>
     </row>
-    <row r="65" spans="1:33" ht="11.45" customHeight="1">
+    <row r="65" spans="1:33" ht="11.5" customHeight="1">
       <c r="A65" s="209"/>
       <c r="B65" s="209"/>
       <c r="C65" s="365"/>
@@ -16043,7 +16043,7 @@
       <c r="AF65" s="102"/>
       <c r="AG65" s="102"/>
     </row>
-    <row r="66" spans="1:33" ht="11.45" customHeight="1">
+    <row r="66" spans="1:33" ht="11.5" customHeight="1">
       <c r="A66" s="205">
         <v>45909</v>
       </c>
@@ -16118,7 +16118,7 @@
       <c r="AF66" s="104"/>
       <c r="AG66" s="104"/>
     </row>
-    <row r="67" spans="1:33" ht="11.45" customHeight="1">
+    <row r="67" spans="1:33" ht="11.5" customHeight="1">
       <c r="A67" s="207">
         <v>45874</v>
       </c>
@@ -16189,7 +16189,7 @@
       <c r="AF67" s="106"/>
       <c r="AG67" s="106"/>
     </row>
-    <row r="68" spans="1:33" ht="11.45" customHeight="1">
+    <row r="68" spans="1:33" ht="11.5" customHeight="1">
       <c r="A68" s="206">
         <v>45909</v>
       </c>
@@ -16258,7 +16258,7 @@
       <c r="AF68" s="78"/>
       <c r="AG68" s="78"/>
     </row>
-    <row r="69" spans="1:33" ht="11.45" customHeight="1">
+    <row r="69" spans="1:33" ht="11.5" customHeight="1">
       <c r="A69" s="204">
         <v>45909</v>
       </c>
@@ -16329,7 +16329,7 @@
       <c r="AF69" s="88"/>
       <c r="AG69" s="88"/>
     </row>
-    <row r="70" spans="1:33" ht="11.45" customHeight="1">
+    <row r="70" spans="1:33" ht="11.5" customHeight="1">
       <c r="A70" s="203">
         <v>45909</v>
       </c>
@@ -16392,7 +16392,7 @@
       <c r="AF70" s="56"/>
       <c r="AG70" s="56"/>
     </row>
-    <row r="71" spans="1:33" ht="11.45" customHeight="1">
+    <row r="71" spans="1:33" ht="11.5" customHeight="1">
       <c r="A71" s="214">
         <v>45909</v>
       </c>
@@ -16453,7 +16453,7 @@
       <c r="AF71" s="81"/>
       <c r="AG71" s="81"/>
     </row>
-    <row r="72" spans="1:33" ht="11.45" customHeight="1">
+    <row r="72" spans="1:33" ht="11.5" customHeight="1">
       <c r="A72" s="209">
         <v>45909</v>
       </c>
@@ -16512,7 +16512,7 @@
       <c r="AF72" s="102"/>
       <c r="AG72" s="102"/>
     </row>
-    <row r="73" spans="1:33" ht="11.45" customHeight="1">
+    <row r="73" spans="1:33" ht="11.5" customHeight="1">
       <c r="A73" s="205">
         <v>45909</v>
       </c>
@@ -16581,7 +16581,7 @@
       <c r="AF73" s="104"/>
       <c r="AG73" s="104"/>
     </row>
-    <row r="74" spans="1:33" ht="11.45" customHeight="1">
+    <row r="74" spans="1:33" ht="11.5" customHeight="1">
       <c r="A74" s="207">
         <v>45909</v>
       </c>
@@ -16637,7 +16637,7 @@
       <c r="AF74" s="106"/>
       <c r="AG74" s="106"/>
     </row>
-    <row r="75" spans="1:33" ht="11.45" customHeight="1">
+    <row r="75" spans="1:33" ht="11.5" customHeight="1">
       <c r="A75" s="206">
         <v>45909</v>
       </c>
@@ -16708,7 +16708,7 @@
       <c r="AF75" s="78"/>
       <c r="AG75" s="78"/>
     </row>
-    <row r="76" spans="1:33" ht="11.45" customHeight="1">
+    <row r="76" spans="1:33" ht="11.5" customHeight="1">
       <c r="A76" s="204">
         <v>45921</v>
       </c>
@@ -16771,7 +16771,7 @@
       <c r="AF76" s="88"/>
       <c r="AG76" s="88"/>
     </row>
-    <row r="77" spans="1:33" ht="11.45" customHeight="1">
+    <row r="77" spans="1:33" ht="11.5" customHeight="1">
       <c r="A77" s="203"/>
       <c r="B77" s="203"/>
       <c r="C77" s="376"/>
@@ -16816,7 +16816,7 @@
       <c r="AF77" s="56"/>
       <c r="AG77" s="56"/>
     </row>
-    <row r="78" spans="1:33" ht="11.45" customHeight="1">
+    <row r="78" spans="1:33" ht="11.5" customHeight="1">
       <c r="A78" s="214">
         <v>45924</v>
       </c>
@@ -16883,7 +16883,7 @@
       <c r="AF78" s="81"/>
       <c r="AG78" s="81"/>
     </row>
-    <row r="79" spans="1:33" s="166" customFormat="1" ht="11.45" customHeight="1">
+    <row r="79" spans="1:33" s="166" customFormat="1" ht="11.5" customHeight="1">
       <c r="A79" s="208">
         <v>45924</v>
       </c>
@@ -16960,7 +16960,7 @@
       <c r="AF79" s="85"/>
       <c r="AG79" s="85"/>
     </row>
-    <row r="80" spans="1:33" ht="11.45" customHeight="1">
+    <row r="80" spans="1:33" ht="11.5" customHeight="1">
       <c r="A80" s="207">
         <v>45924</v>
       </c>
@@ -17021,7 +17021,7 @@
       <c r="AF80" s="106"/>
       <c r="AG80" s="106"/>
     </row>
-    <row r="81" spans="1:33" ht="11.45" customHeight="1">
+    <row r="81" spans="1:33" ht="11.5" customHeight="1">
       <c r="A81" s="206">
         <v>45924</v>
       </c>
@@ -17092,7 +17092,7 @@
       <c r="AF81" s="78"/>
       <c r="AG81" s="78"/>
     </row>
-    <row r="82" spans="1:33" s="463" customFormat="1" ht="11.45" customHeight="1">
+    <row r="82" spans="1:33" s="463" customFormat="1" ht="11.5" customHeight="1">
       <c r="A82" s="457">
         <v>45924</v>
       </c>
@@ -17165,7 +17165,7 @@
       <c r="AF82" s="459"/>
       <c r="AG82" s="459"/>
     </row>
-    <row r="83" spans="1:33" ht="11.45" customHeight="1">
+    <row r="83" spans="1:33" ht="11.5" customHeight="1">
       <c r="A83" s="203">
         <v>45924</v>
       </c>
@@ -17234,7 +17234,7 @@
       <c r="AF83" s="56"/>
       <c r="AG83" s="56"/>
     </row>
-    <row r="84" spans="1:33" ht="11.45" customHeight="1">
+    <row r="84" spans="1:33" ht="11.5" customHeight="1">
       <c r="A84" s="214">
         <v>45924</v>
       </c>
@@ -17307,7 +17307,7 @@
       <c r="AF84" s="81"/>
       <c r="AG84" s="81"/>
     </row>
-    <row r="85" spans="1:33" ht="11.45" customHeight="1">
+    <row r="85" spans="1:33" ht="11.5" customHeight="1">
       <c r="A85" s="209">
         <v>45930</v>
       </c>
@@ -17372,7 +17372,7 @@
       <c r="AF85" s="102"/>
       <c r="AG85" s="102"/>
     </row>
-    <row r="86" spans="1:33" ht="11.45" customHeight="1">
+    <row r="86" spans="1:33" ht="11.5" customHeight="1">
       <c r="A86" s="409">
         <v>45930</v>
       </c>
@@ -17432,7 +17432,7 @@
       <c r="AF86" s="104"/>
       <c r="AG86" s="104"/>
     </row>
-    <row r="87" spans="1:33" ht="11.45" customHeight="1">
+    <row r="87" spans="1:33" ht="11.5" customHeight="1">
       <c r="A87" s="207">
         <v>45924</v>
       </c>
@@ -17485,7 +17485,7 @@
       <c r="AF87" s="106"/>
       <c r="AG87" s="106"/>
     </row>
-    <row r="88" spans="1:33" ht="11.45" customHeight="1">
+    <row r="88" spans="1:33" ht="11.5" customHeight="1">
       <c r="A88" s="206">
         <v>45930</v>
       </c>
@@ -17546,7 +17546,7 @@
       <c r="AF88" s="78"/>
       <c r="AG88" s="78"/>
     </row>
-    <row r="89" spans="1:33" ht="11.45" customHeight="1">
+    <row r="89" spans="1:33" ht="11.5" customHeight="1">
       <c r="A89" s="204">
         <v>45930</v>
       </c>
@@ -17613,7 +17613,7 @@
       <c r="AF89" s="88"/>
       <c r="AG89" s="88"/>
     </row>
-    <row r="90" spans="1:33" ht="11.45" customHeight="1">
+    <row r="90" spans="1:33" ht="11.5" customHeight="1">
       <c r="A90" s="203">
         <v>45930</v>
       </c>
@@ -17676,7 +17676,7 @@
       <c r="AF90" s="56"/>
       <c r="AG90" s="56"/>
     </row>
-    <row r="91" spans="1:33" ht="11.45" customHeight="1">
+    <row r="91" spans="1:33" ht="11.5" customHeight="1">
       <c r="A91" s="214">
         <v>45930</v>
       </c>
@@ -17745,7 +17745,7 @@
       <c r="AF91" s="81"/>
       <c r="AG91" s="81"/>
     </row>
-    <row r="92" spans="1:33" ht="11.45" customHeight="1">
+    <row r="92" spans="1:33" ht="11.5" customHeight="1">
       <c r="A92" s="214">
         <v>45930</v>
       </c>
@@ -17797,7 +17797,7 @@
       <c r="AF92" s="81"/>
       <c r="AG92" s="81"/>
     </row>
-    <row r="93" spans="1:33" ht="11.45" customHeight="1">
+    <row r="93" spans="1:33" ht="11.5" customHeight="1">
       <c r="A93" s="209">
         <v>45930</v>
       </c>
@@ -17864,7 +17864,7 @@
       <c r="AF93" s="102"/>
       <c r="AG93" s="102"/>
     </row>
-    <row r="94" spans="1:33" ht="11.45" customHeight="1">
+    <row r="94" spans="1:33" ht="11.5" customHeight="1">
       <c r="A94" s="205">
         <v>45930</v>
       </c>
@@ -17929,7 +17929,7 @@
       <c r="AF94" s="104"/>
       <c r="AG94" s="104"/>
     </row>
-    <row r="95" spans="1:33" ht="11.45" customHeight="1">
+    <row r="95" spans="1:33" ht="11.5" customHeight="1">
       <c r="A95" s="207">
         <v>45930</v>
       </c>
@@ -17990,7 +17990,7 @@
       <c r="AF95" s="106"/>
       <c r="AG95" s="106"/>
     </row>
-    <row r="96" spans="1:33" ht="11.45" customHeight="1">
+    <row r="96" spans="1:33" ht="11.5" customHeight="1">
       <c r="A96" s="206">
         <v>45930</v>
       </c>
@@ -18051,7 +18051,7 @@
       <c r="AF96" s="78"/>
       <c r="AG96" s="78"/>
     </row>
-    <row r="97" spans="1:33" ht="11.45" customHeight="1">
+    <row r="97" spans="1:33" ht="11.5" customHeight="1">
       <c r="A97" s="204">
         <v>45938</v>
       </c>
@@ -18110,7 +18110,7 @@
       <c r="AF97" s="88"/>
       <c r="AG97" s="88"/>
     </row>
-    <row r="98" spans="1:33" ht="11.45" customHeight="1">
+    <row r="98" spans="1:33" ht="11.5" customHeight="1">
       <c r="A98" s="203">
         <v>45966</v>
       </c>
@@ -18183,7 +18183,7 @@
       <c r="AF98" s="56"/>
       <c r="AG98" s="56"/>
     </row>
-    <row r="99" spans="1:33" ht="11.45" customHeight="1">
+    <row r="99" spans="1:33" ht="11.5" customHeight="1">
       <c r="A99" s="214">
         <v>45966</v>
       </c>
@@ -18252,7 +18252,7 @@
       <c r="AF99" s="81"/>
       <c r="AG99" s="81"/>
     </row>
-    <row r="100" spans="1:33" ht="11.45" customHeight="1">
+    <row r="100" spans="1:33" ht="11.5" customHeight="1">
       <c r="A100" s="209">
         <v>45966</v>
       </c>
@@ -18306,7 +18306,7 @@
       <c r="AF100" s="102"/>
       <c r="AG100" s="102"/>
     </row>
-    <row r="101" spans="1:33" ht="11.45" customHeight="1">
+    <row r="101" spans="1:33" ht="11.5" customHeight="1">
       <c r="A101" s="205">
         <v>45966</v>
       </c>
@@ -18365,7 +18365,7 @@
       <c r="AF101" s="104"/>
       <c r="AG101" s="104"/>
     </row>
-    <row r="102" spans="1:33" ht="11.45" customHeight="1">
+    <row r="102" spans="1:33" ht="11.5" customHeight="1">
       <c r="A102" s="207">
         <v>45972</v>
       </c>
@@ -18430,7 +18430,7 @@
       <c r="AF102" s="106"/>
       <c r="AG102" s="106"/>
     </row>
-    <row r="103" spans="1:33" ht="11.45" customHeight="1">
+    <row r="103" spans="1:33" ht="11.5" customHeight="1">
       <c r="A103" s="206">
         <v>45972</v>
       </c>
@@ -18493,7 +18493,7 @@
       <c r="AF103" s="78"/>
       <c r="AG103" s="78"/>
     </row>
-    <row r="104" spans="1:33" ht="11.45" customHeight="1">
+    <row r="104" spans="1:33" ht="11.5" customHeight="1">
       <c r="A104" s="204">
         <v>45972</v>
       </c>
@@ -18551,7 +18551,7 @@
       <c r="AF104" s="88"/>
       <c r="AG104" s="88"/>
     </row>
-    <row r="105" spans="1:33" ht="11.45" customHeight="1">
+    <row r="105" spans="1:33" ht="11.5" customHeight="1">
       <c r="A105" s="203">
         <v>45979</v>
       </c>
@@ -18624,7 +18624,7 @@
       <c r="AF105" s="56"/>
       <c r="AG105" s="56"/>
     </row>
-    <row r="106" spans="1:33" ht="11.45" customHeight="1">
+    <row r="106" spans="1:33" ht="11.5" customHeight="1">
       <c r="A106" s="214">
         <v>45979</v>
       </c>
@@ -18693,7 +18693,7 @@
       <c r="AF106" s="81"/>
       <c r="AG106" s="81"/>
     </row>
-    <row r="107" spans="1:33" ht="11.45" customHeight="1">
+    <row r="107" spans="1:33" ht="11.5" customHeight="1">
       <c r="A107" s="205">
         <v>45980</v>
       </c>
@@ -18758,7 +18758,7 @@
       <c r="AF107" s="104"/>
       <c r="AG107" s="104"/>
     </row>
-    <row r="108" spans="1:33" s="302" customFormat="1" ht="11.45" customHeight="1">
+    <row r="108" spans="1:33" s="302" customFormat="1" ht="11.5" customHeight="1">
       <c r="A108" s="250">
         <v>45980</v>
       </c>
@@ -18819,7 +18819,7 @@
       <c r="AF108" s="333"/>
       <c r="AG108" s="333"/>
     </row>
-    <row r="109" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="109" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A109" s="222">
         <v>46035</v>
       </c>
@@ -18875,7 +18875,7 @@
       <c r="AF109" s="335"/>
       <c r="AG109" s="335"/>
     </row>
-    <row r="110" spans="1:33" ht="11.45" customHeight="1">
+    <row r="110" spans="1:33" ht="11.5" customHeight="1">
       <c r="A110" s="206">
         <v>45981</v>
       </c>
@@ -18938,7 +18938,7 @@
       <c r="AF110" s="78"/>
       <c r="AG110" s="78"/>
     </row>
-    <row r="111" spans="1:33" ht="11.45" customHeight="1">
+    <row r="111" spans="1:33" ht="11.5" customHeight="1">
       <c r="A111" s="203">
         <v>46035</v>
       </c>
@@ -18999,7 +18999,7 @@
       <c r="AF111" s="56"/>
       <c r="AG111" s="56"/>
     </row>
-    <row r="112" spans="1:33" ht="11.45" customHeight="1">
+    <row r="112" spans="1:33" ht="11.5" customHeight="1">
       <c r="A112" s="204">
         <v>45981</v>
       </c>
@@ -19056,7 +19056,7 @@
       <c r="AF112" s="88"/>
       <c r="AG112" s="88"/>
     </row>
-    <row r="113" spans="1:33" ht="11.45" customHeight="1">
+    <row r="113" spans="1:33" ht="11.5" customHeight="1">
       <c r="A113" s="203">
         <v>45981</v>
       </c>
@@ -19115,7 +19115,7 @@
       <c r="AF113" s="56"/>
       <c r="AG113" s="56"/>
     </row>
-    <row r="114" spans="1:33" ht="11.45" customHeight="1">
+    <row r="114" spans="1:33" ht="11.5" customHeight="1">
       <c r="A114" s="214">
         <v>45981</v>
       </c>
@@ -19176,7 +19176,7 @@
       <c r="AF114" s="81"/>
       <c r="AG114" s="81"/>
     </row>
-    <row r="115" spans="1:33" ht="11.45" customHeight="1">
+    <row r="115" spans="1:33" ht="11.5" customHeight="1">
       <c r="A115" s="209">
         <v>45981</v>
       </c>
@@ -19239,7 +19239,7 @@
       <c r="AF115" s="102"/>
       <c r="AG115" s="102"/>
     </row>
-    <row r="116" spans="1:33" ht="11.45" customHeight="1">
+    <row r="116" spans="1:33" ht="11.5" customHeight="1">
       <c r="A116" s="205">
         <v>45981</v>
       </c>
@@ -19304,7 +19304,7 @@
       <c r="AF116" s="104"/>
       <c r="AG116" s="104"/>
     </row>
-    <row r="117" spans="1:33" ht="11.45" customHeight="1">
+    <row r="117" spans="1:33" ht="11.5" customHeight="1">
       <c r="A117" s="207">
         <v>45986</v>
       </c>
@@ -19363,7 +19363,7 @@
       <c r="AF117" s="106"/>
       <c r="AG117" s="106"/>
     </row>
-    <row r="118" spans="1:33" ht="11.45" customHeight="1">
+    <row r="118" spans="1:33" ht="11.5" customHeight="1">
       <c r="A118" s="206">
         <v>45986</v>
       </c>
@@ -19426,7 +19426,7 @@
       <c r="AF118" s="78"/>
       <c r="AG118" s="78"/>
     </row>
-    <row r="119" spans="1:33" ht="11.45" customHeight="1">
+    <row r="119" spans="1:33" ht="11.5" customHeight="1">
       <c r="A119" s="204">
         <v>45986</v>
       </c>
@@ -19487,7 +19487,7 @@
       <c r="AF119" s="88"/>
       <c r="AG119" s="88"/>
     </row>
-    <row r="120" spans="1:33" ht="11.45" customHeight="1">
+    <row r="120" spans="1:33" ht="11.5" customHeight="1">
       <c r="A120" s="214">
         <v>45986</v>
       </c>
@@ -19603,7 +19603,7 @@
       <c r="AF121" s="102"/>
       <c r="AG121" s="102"/>
     </row>
-    <row r="122" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="122" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A122" s="280">
         <v>45986</v>
       </c>
@@ -19666,7 +19666,7 @@
       <c r="AF122" s="282"/>
       <c r="AG122" s="282"/>
     </row>
-    <row r="123" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="123" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A123" s="222">
         <v>45986</v>
       </c>
@@ -19725,7 +19725,7 @@
       <c r="AF123" s="335"/>
       <c r="AG123" s="335"/>
     </row>
-    <row r="124" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="124" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A124" s="267">
         <v>46072</v>
       </c>
@@ -19780,7 +19780,7 @@
       <c r="AF124" s="263"/>
       <c r="AG124" s="263"/>
     </row>
-    <row r="125" spans="1:33" ht="11.45" customHeight="1">
+    <row r="125" spans="1:33" ht="11.5" customHeight="1">
       <c r="A125" s="204">
         <v>45986</v>
       </c>
@@ -19843,7 +19843,7 @@
       <c r="AF125" s="88"/>
       <c r="AG125" s="88"/>
     </row>
-    <row r="126" spans="1:33" ht="11.45" customHeight="1">
+    <row r="126" spans="1:33" ht="11.5" customHeight="1">
       <c r="A126" s="203"/>
       <c r="B126" s="203"/>
       <c r="C126" s="376"/>
@@ -19889,7 +19889,7 @@
       <c r="AF126" s="56"/>
       <c r="AG126" s="56"/>
     </row>
-    <row r="127" spans="1:33" ht="11.45" customHeight="1">
+    <row r="127" spans="1:33" ht="11.5" customHeight="1">
       <c r="A127" s="214">
         <v>45986</v>
       </c>
@@ -19944,7 +19944,7 @@
       <c r="AF127" s="81"/>
       <c r="AG127" s="81"/>
     </row>
-    <row r="128" spans="1:33" ht="11.45" customHeight="1">
+    <row r="128" spans="1:33" ht="11.5" customHeight="1">
       <c r="A128" s="209">
         <v>46051</v>
       </c>
@@ -19998,7 +19998,7 @@
       <c r="AF128" s="102"/>
       <c r="AG128" s="102"/>
     </row>
-    <row r="129" spans="1:33" ht="11.45" customHeight="1">
+    <row r="129" spans="1:33" ht="11.5" customHeight="1">
       <c r="A129" s="205">
         <v>45987</v>
       </c>
@@ -20053,7 +20053,7 @@
       <c r="AF129" s="104"/>
       <c r="AG129" s="104"/>
     </row>
-    <row r="130" spans="1:33" ht="11.45" customHeight="1">
+    <row r="130" spans="1:33" ht="11.5" customHeight="1">
       <c r="A130" s="207">
         <v>46000</v>
       </c>
@@ -20104,7 +20104,7 @@
       <c r="AF130" s="106"/>
       <c r="AG130" s="106"/>
     </row>
-    <row r="131" spans="1:33" ht="11.45" customHeight="1">
+    <row r="131" spans="1:33" ht="11.5" customHeight="1">
       <c r="A131" s="206">
         <v>46001</v>
       </c>
@@ -20163,7 +20163,7 @@
       <c r="AF131" s="78"/>
       <c r="AG131" s="78"/>
     </row>
-    <row r="132" spans="1:33" ht="11.45" customHeight="1">
+    <row r="132" spans="1:33" ht="11.5" customHeight="1">
       <c r="A132" s="204"/>
       <c r="B132" s="204"/>
       <c r="C132" s="379"/>
@@ -20199,7 +20199,7 @@
       <c r="AF132" s="88"/>
       <c r="AG132" s="88"/>
     </row>
-    <row r="133" spans="1:33" ht="11.45" customHeight="1">
+    <row r="133" spans="1:33" ht="11.5" customHeight="1">
       <c r="A133" s="203"/>
       <c r="B133" s="203">
         <v>46058</v>
@@ -20239,7 +20239,7 @@
       <c r="AF133" s="56"/>
       <c r="AG133" s="56"/>
     </row>
-    <row r="134" spans="1:33" ht="11.45" customHeight="1">
+    <row r="134" spans="1:33" ht="11.5" customHeight="1">
       <c r="A134" s="214">
         <v>46035</v>
       </c>
@@ -20302,7 +20302,7 @@
       <c r="AF134" s="81"/>
       <c r="AG134" s="81"/>
     </row>
-    <row r="135" spans="1:33" ht="11.45" customHeight="1">
+    <row r="135" spans="1:33" ht="11.5" customHeight="1">
       <c r="A135" s="209">
         <v>46035</v>
       </c>
@@ -20365,7 +20365,7 @@
       <c r="AF135" s="102"/>
       <c r="AG135" s="102"/>
     </row>
-    <row r="136" spans="1:33" ht="11.45" customHeight="1">
+    <row r="136" spans="1:33" ht="11.5" customHeight="1">
       <c r="A136" s="205"/>
       <c r="B136" s="205"/>
       <c r="C136" s="366"/>
@@ -20411,7 +20411,7 @@
       <c r="AF136" s="104"/>
       <c r="AG136" s="104"/>
     </row>
-    <row r="137" spans="1:33" ht="11.45" customHeight="1">
+    <row r="137" spans="1:33" ht="11.5" customHeight="1">
       <c r="A137" s="206">
         <v>46035</v>
       </c>
@@ -20468,7 +20468,7 @@
       <c r="AF137" s="78"/>
       <c r="AG137" s="78"/>
     </row>
-    <row r="138" spans="1:33" ht="11.45" customHeight="1">
+    <row r="138" spans="1:33" ht="11.5" customHeight="1">
       <c r="A138" s="203">
         <v>46029</v>
       </c>
@@ -20533,7 +20533,7 @@
       <c r="AF138" s="56"/>
       <c r="AG138" s="56"/>
     </row>
-    <row r="139" spans="1:33" ht="11.45" customHeight="1">
+    <row r="139" spans="1:33" ht="11.5" customHeight="1">
       <c r="A139" s="214">
         <v>46029</v>
       </c>
@@ -20592,7 +20592,7 @@
       <c r="AF139" s="81"/>
       <c r="AG139" s="81"/>
     </row>
-    <row r="140" spans="1:33" ht="11.45" customHeight="1">
+    <row r="140" spans="1:33" ht="11.5" customHeight="1">
       <c r="A140" s="214">
         <v>46035</v>
       </c>
@@ -20641,7 +20641,7 @@
       <c r="AF140" s="81"/>
       <c r="AG140" s="81"/>
     </row>
-    <row r="141" spans="1:33" ht="11.45" customHeight="1">
+    <row r="141" spans="1:33" ht="11.5" customHeight="1">
       <c r="A141" s="209">
         <v>46029</v>
       </c>
@@ -20700,7 +20700,7 @@
       <c r="AF141" s="102"/>
       <c r="AG141" s="102"/>
     </row>
-    <row r="142" spans="1:33" ht="11.45" customHeight="1">
+    <row r="142" spans="1:33" ht="11.5" customHeight="1">
       <c r="A142" s="205">
         <v>46035</v>
       </c>
@@ -20759,7 +20759,7 @@
       <c r="AF142" s="104"/>
       <c r="AG142" s="104"/>
     </row>
-    <row r="143" spans="1:33" ht="11.45" customHeight="1">
+    <row r="143" spans="1:33" ht="11.5" customHeight="1">
       <c r="A143" s="207">
         <v>46035</v>
       </c>
@@ -20816,7 +20816,7 @@
       <c r="AF143" s="106"/>
       <c r="AG143" s="106"/>
     </row>
-    <row r="144" spans="1:33" ht="11.45" customHeight="1">
+    <row r="144" spans="1:33" ht="11.5" customHeight="1">
       <c r="A144" s="206">
         <v>46035</v>
       </c>
@@ -20875,7 +20875,7 @@
       <c r="AF144" s="78"/>
       <c r="AG144" s="78"/>
     </row>
-    <row r="145" spans="1:33" ht="11.45" customHeight="1">
+    <row r="145" spans="1:33" ht="11.5" customHeight="1">
       <c r="A145" s="204">
         <v>46035</v>
       </c>
@@ -20936,7 +20936,7 @@
       <c r="AF145" s="88"/>
       <c r="AG145" s="88"/>
     </row>
-    <row r="146" spans="1:33" ht="11.45" customHeight="1">
+    <row r="146" spans="1:33" ht="11.5" customHeight="1">
       <c r="A146" s="203">
         <v>46030</v>
       </c>
@@ -20995,7 +20995,7 @@
       <c r="AF146" s="56"/>
       <c r="AG146" s="56"/>
     </row>
-    <row r="147" spans="1:33" ht="11.45" customHeight="1">
+    <row r="147" spans="1:33" ht="11.5" customHeight="1">
       <c r="A147" s="214">
         <v>46035</v>
       </c>
@@ -21054,7 +21054,7 @@
       <c r="AF147" s="81"/>
       <c r="AG147" s="81"/>
     </row>
-    <row r="148" spans="1:33" ht="11.45" customHeight="1">
+    <row r="148" spans="1:33" ht="11.5" customHeight="1">
       <c r="A148" s="209">
         <v>46029</v>
       </c>
@@ -21113,7 +21113,7 @@
       <c r="AF148" s="102"/>
       <c r="AG148" s="102"/>
     </row>
-    <row r="149" spans="1:33" ht="11.45" customHeight="1">
+    <row r="149" spans="1:33" ht="11.5" customHeight="1">
       <c r="A149" s="205">
         <v>46029</v>
       </c>
@@ -21176,7 +21176,7 @@
       <c r="AF149" s="104"/>
       <c r="AG149" s="104"/>
     </row>
-    <row r="150" spans="1:33" ht="11.45" customHeight="1">
+    <row r="150" spans="1:33" ht="11.5" customHeight="1">
       <c r="A150" s="207">
         <v>46029</v>
       </c>
@@ -21236,7 +21236,7 @@
       <c r="AF150" s="326"/>
       <c r="AG150" s="326"/>
     </row>
-    <row r="151" spans="1:33" ht="11.45" customHeight="1">
+    <row r="151" spans="1:33" ht="11.5" customHeight="1">
       <c r="A151" s="204"/>
       <c r="B151" s="204"/>
       <c r="C151" s="379"/>
@@ -21283,7 +21283,7 @@
       <c r="AF151" s="88"/>
       <c r="AG151" s="88"/>
     </row>
-    <row r="152" spans="1:33" ht="11.45" customHeight="1">
+    <row r="152" spans="1:33" ht="11.5" customHeight="1">
       <c r="A152" s="203"/>
       <c r="B152" s="203"/>
       <c r="C152" s="376"/>
@@ -21324,7 +21324,7 @@
       <c r="AF152" s="56"/>
       <c r="AG152" s="56"/>
     </row>
-    <row r="153" spans="1:33" ht="11.45" customHeight="1">
+    <row r="153" spans="1:33" ht="11.5" customHeight="1">
       <c r="A153" s="214">
         <v>46035</v>
       </c>
@@ -21389,7 +21389,7 @@
       <c r="AF153" s="81"/>
       <c r="AG153" s="81"/>
     </row>
-    <row r="154" spans="1:33" ht="11.45" customHeight="1">
+    <row r="154" spans="1:33" ht="11.5" customHeight="1">
       <c r="A154" s="209">
         <v>46035</v>
       </c>
@@ -21450,7 +21450,7 @@
       <c r="AF154" s="102"/>
       <c r="AG154" s="102"/>
     </row>
-    <row r="155" spans="1:33" ht="11.45" customHeight="1">
+    <row r="155" spans="1:33" ht="11.5" customHeight="1">
       <c r="A155" s="205">
         <v>46035</v>
       </c>
@@ -21517,7 +21517,7 @@
       <c r="AF155" s="104"/>
       <c r="AG155" s="104"/>
     </row>
-    <row r="156" spans="1:33" ht="11.45" customHeight="1">
+    <row r="156" spans="1:33" ht="11.5" customHeight="1">
       <c r="A156" s="207">
         <v>46035</v>
       </c>
@@ -21574,7 +21574,7 @@
       <c r="AF156" s="106"/>
       <c r="AG156" s="106"/>
     </row>
-    <row r="157" spans="1:33" ht="11.45" customHeight="1">
+    <row r="157" spans="1:33" ht="11.5" customHeight="1">
       <c r="A157" s="206"/>
       <c r="B157" s="206"/>
       <c r="C157" s="381"/>
@@ -21617,7 +21617,7 @@
       <c r="AF157" s="78"/>
       <c r="AG157" s="78"/>
     </row>
-    <row r="158" spans="1:33" ht="11.45" customHeight="1">
+    <row r="158" spans="1:33" ht="11.5" customHeight="1">
       <c r="A158" s="204">
         <v>46035</v>
       </c>
@@ -21680,7 +21680,7 @@
       <c r="AF158" s="88"/>
       <c r="AG158" s="88"/>
     </row>
-    <row r="159" spans="1:33" ht="11.45" customHeight="1">
+    <row r="159" spans="1:33" ht="11.5" customHeight="1">
       <c r="A159" s="203">
         <v>46035</v>
       </c>
@@ -21737,7 +21737,7 @@
       <c r="AF159" s="56"/>
       <c r="AG159" s="56"/>
     </row>
-    <row r="160" spans="1:33" ht="11.45" customHeight="1">
+    <row r="160" spans="1:33" ht="11.5" customHeight="1">
       <c r="A160" s="214">
         <v>46035</v>
       </c>
@@ -21804,7 +21804,7 @@
       <c r="AF160" s="81"/>
       <c r="AG160" s="81"/>
     </row>
-    <row r="161" spans="1:33" ht="11.45" customHeight="1">
+    <row r="161" spans="1:33" ht="11.5" customHeight="1">
       <c r="A161" s="209">
         <v>46035</v>
       </c>
@@ -21865,7 +21865,7 @@
       <c r="AF161" s="102"/>
       <c r="AG161" s="102"/>
     </row>
-    <row r="162" spans="1:33" ht="11.45" customHeight="1">
+    <row r="162" spans="1:33" ht="11.5" customHeight="1">
       <c r="A162" s="205"/>
       <c r="B162" s="205"/>
       <c r="C162" s="366"/>
@@ -21903,7 +21903,7 @@
       <c r="AF162" s="104"/>
       <c r="AG162" s="104"/>
     </row>
-    <row r="163" spans="1:33" ht="11.45" customHeight="1">
+    <row r="163" spans="1:33" ht="11.5" customHeight="1">
       <c r="A163" s="204">
         <v>46035</v>
       </c>
@@ -21960,7 +21960,7 @@
       <c r="AF163" s="88"/>
       <c r="AG163" s="88"/>
     </row>
-    <row r="164" spans="1:33" ht="11.45" customHeight="1">
+    <row r="164" spans="1:33" ht="11.5" customHeight="1">
       <c r="A164" s="206">
         <v>46035</v>
       </c>
@@ -22021,7 +22021,7 @@
       <c r="AF164" s="78"/>
       <c r="AG164" s="78"/>
     </row>
-    <row r="165" spans="1:33" ht="11.45" customHeight="1">
+    <row r="165" spans="1:33" ht="11.5" customHeight="1">
       <c r="A165" s="204"/>
       <c r="B165" s="204"/>
       <c r="C165" s="379"/>
@@ -22057,7 +22057,7 @@
       <c r="AF165" s="88"/>
       <c r="AG165" s="88"/>
     </row>
-    <row r="166" spans="1:33" ht="11.45" customHeight="1">
+    <row r="166" spans="1:33" ht="11.5" customHeight="1">
       <c r="A166" s="203">
         <v>46052</v>
       </c>
@@ -22116,7 +22116,7 @@
       <c r="AF166" s="56"/>
       <c r="AG166" s="56"/>
     </row>
-    <row r="167" spans="1:33" ht="11.45" customHeight="1">
+    <row r="167" spans="1:33" ht="11.5" customHeight="1">
       <c r="A167" s="214">
         <v>46029</v>
       </c>
@@ -22175,7 +22175,7 @@
       <c r="AF167" s="81"/>
       <c r="AG167" s="81"/>
     </row>
-    <row r="168" spans="1:33" ht="11.45" customHeight="1">
+    <row r="168" spans="1:33" ht="11.5" customHeight="1">
       <c r="A168" s="209">
         <v>46035</v>
       </c>
@@ -22234,7 +22234,7 @@
       <c r="AF168" s="102"/>
       <c r="AG168" s="102"/>
     </row>
-    <row r="169" spans="1:33" ht="11.45" customHeight="1">
+    <row r="169" spans="1:33" ht="11.5" customHeight="1">
       <c r="A169" s="205">
         <v>46035</v>
       </c>
@@ -22297,7 +22297,7 @@
       <c r="AF169" s="104"/>
       <c r="AG169" s="104"/>
     </row>
-    <row r="170" spans="1:33" ht="11.45" customHeight="1">
+    <row r="170" spans="1:33" ht="11.5" customHeight="1">
       <c r="A170" s="411">
         <v>46035</v>
       </c>
@@ -22346,7 +22346,7 @@
       <c r="AF170" s="106"/>
       <c r="AG170" s="106"/>
     </row>
-    <row r="171" spans="1:33" ht="11.45" customHeight="1">
+    <row r="171" spans="1:33" ht="11.5" customHeight="1">
       <c r="A171" s="206">
         <v>46035</v>
       </c>
@@ -22409,7 +22409,7 @@
       <c r="AF171" s="78"/>
       <c r="AG171" s="78"/>
     </row>
-    <row r="172" spans="1:33" ht="11.45" customHeight="1">
+    <row r="172" spans="1:33" ht="11.5" customHeight="1">
       <c r="A172" s="204"/>
       <c r="B172" s="204"/>
       <c r="C172" s="379"/>
@@ -22449,7 +22449,7 @@
       <c r="AF172" s="88"/>
       <c r="AG172" s="88"/>
     </row>
-    <row r="173" spans="1:33" ht="11.45" customHeight="1">
+    <row r="173" spans="1:33" ht="11.5" customHeight="1">
       <c r="A173" s="203">
         <v>46035</v>
       </c>
@@ -22506,7 +22506,7 @@
       <c r="AF173" s="56"/>
       <c r="AG173" s="56"/>
     </row>
-    <row r="174" spans="1:33" ht="11.45" customHeight="1">
+    <row r="174" spans="1:33" ht="11.5" customHeight="1">
       <c r="A174" s="214">
         <v>46035</v>
       </c>
@@ -22565,7 +22565,7 @@
       <c r="AF174" s="81"/>
       <c r="AG174" s="81"/>
     </row>
-    <row r="175" spans="1:33" ht="11.45" customHeight="1">
+    <row r="175" spans="1:33" ht="11.5" customHeight="1">
       <c r="A175" s="209">
         <v>46035</v>
       </c>
@@ -22626,7 +22626,7 @@
       <c r="AF175" s="102"/>
       <c r="AG175" s="102"/>
     </row>
-    <row r="176" spans="1:33" ht="11.45" customHeight="1">
+    <row r="176" spans="1:33" ht="11.5" customHeight="1">
       <c r="A176" s="205">
         <v>46035</v>
       </c>
@@ -22687,7 +22687,7 @@
       <c r="AF176" s="104"/>
       <c r="AG176" s="104"/>
     </row>
-    <row r="177" spans="1:33" ht="11.45" customHeight="1">
+    <row r="177" spans="1:33" ht="11.5" customHeight="1">
       <c r="A177" s="207">
         <v>46035</v>
       </c>
@@ -22746,7 +22746,7 @@
       <c r="AF177" s="106"/>
       <c r="AG177" s="106"/>
     </row>
-    <row r="178" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="178" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A178" s="267">
         <v>46035</v>
       </c>
@@ -22809,7 +22809,7 @@
       <c r="AF178" s="263"/>
       <c r="AG178" s="263"/>
     </row>
-    <row r="179" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="179" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A179" s="267"/>
       <c r="B179" s="222"/>
       <c r="C179" s="387"/>
@@ -22850,7 +22850,7 @@
       <c r="AF179" s="263"/>
       <c r="AG179" s="263"/>
     </row>
-    <row r="180" spans="1:33" ht="11.45" customHeight="1">
+    <row r="180" spans="1:33" ht="11.5" customHeight="1">
       <c r="A180" s="204">
         <v>46035</v>
       </c>
@@ -22909,7 +22909,7 @@
       <c r="AF180" s="88"/>
       <c r="AG180" s="88"/>
     </row>
-    <row r="181" spans="1:33" ht="11.45" customHeight="1">
+    <row r="181" spans="1:33" ht="11.5" customHeight="1">
       <c r="A181" s="203">
         <v>46035</v>
       </c>
@@ -22968,7 +22968,7 @@
       <c r="AF181" s="56"/>
       <c r="AG181" s="56"/>
     </row>
-    <row r="182" spans="1:33" ht="11.45" customHeight="1">
+    <row r="182" spans="1:33" ht="11.5" customHeight="1">
       <c r="A182" s="214">
         <v>46035</v>
       </c>
@@ -23027,7 +23027,7 @@
       <c r="AF182" s="81"/>
       <c r="AG182" s="81"/>
     </row>
-    <row r="183" spans="1:33" ht="11.45" customHeight="1">
+    <row r="183" spans="1:33" ht="11.5" customHeight="1">
       <c r="A183" s="209">
         <v>46035</v>
       </c>
@@ -23088,7 +23088,7 @@
       <c r="AF183" s="102"/>
       <c r="AG183" s="102"/>
     </row>
-    <row r="184" spans="1:33" ht="11.45" customHeight="1">
+    <row r="184" spans="1:33" ht="11.5" customHeight="1">
       <c r="A184" s="205">
         <v>46035</v>
       </c>
@@ -23147,7 +23147,7 @@
       <c r="AF184" s="104"/>
       <c r="AG184" s="104"/>
     </row>
-    <row r="185" spans="1:33" ht="11.45" customHeight="1">
+    <row r="185" spans="1:33" ht="11.5" customHeight="1">
       <c r="A185" s="207">
         <v>46035</v>
       </c>
@@ -23206,7 +23206,7 @@
       <c r="AF185" s="106"/>
       <c r="AG185" s="106"/>
     </row>
-    <row r="186" spans="1:33" ht="11.45" customHeight="1">
+    <row r="186" spans="1:33" ht="11.5" customHeight="1">
       <c r="A186" s="206">
         <v>46035</v>
       </c>
@@ -23265,7 +23265,7 @@
       <c r="AF186" s="78"/>
       <c r="AG186" s="78"/>
     </row>
-    <row r="187" spans="1:33" ht="11.45" customHeight="1">
+    <row r="187" spans="1:33" ht="11.5" customHeight="1">
       <c r="A187" s="204">
         <v>46035</v>
       </c>
@@ -23326,7 +23326,7 @@
       <c r="AF187" s="88"/>
       <c r="AG187" s="88"/>
     </row>
-    <row r="188" spans="1:33" ht="11.45" customHeight="1">
+    <row r="188" spans="1:33" ht="11.5" customHeight="1">
       <c r="A188" s="203"/>
       <c r="B188" s="203"/>
       <c r="C188" s="376"/>
@@ -23375,7 +23375,7 @@
       <c r="AF188" s="56"/>
       <c r="AG188" s="56"/>
     </row>
-    <row r="189" spans="1:33" ht="11.45" customHeight="1">
+    <row r="189" spans="1:33" ht="11.5" customHeight="1">
       <c r="A189" s="209">
         <v>46035</v>
       </c>
@@ -23432,7 +23432,7 @@
       <c r="AF189" s="102"/>
       <c r="AG189" s="102"/>
     </row>
-    <row r="190" spans="1:33" ht="11.45" customHeight="1">
+    <row r="190" spans="1:33" ht="11.5" customHeight="1">
       <c r="A190" s="203">
         <v>46035</v>
       </c>
@@ -23497,7 +23497,7 @@
       <c r="AF190" s="56"/>
       <c r="AG190" s="56"/>
     </row>
-    <row r="191" spans="1:33" ht="11.45" customHeight="1">
+    <row r="191" spans="1:33" ht="11.5" customHeight="1">
       <c r="A191" s="214">
         <v>46035</v>
       </c>
@@ -23556,7 +23556,7 @@
       <c r="AF191" s="81"/>
       <c r="AG191" s="81"/>
     </row>
-    <row r="192" spans="1:33" ht="11.45" customHeight="1">
+    <row r="192" spans="1:33" ht="11.5" customHeight="1">
       <c r="A192" s="209">
         <v>46035</v>
       </c>
@@ -23623,7 +23623,7 @@
       <c r="AF192" s="102"/>
       <c r="AG192" s="102"/>
     </row>
-    <row r="193" spans="1:33" ht="11.45" customHeight="1">
+    <row r="193" spans="1:33" ht="11.5" customHeight="1">
       <c r="A193" s="205">
         <v>46035</v>
       </c>
@@ -23688,7 +23688,7 @@
       <c r="AF193" s="104"/>
       <c r="AG193" s="104"/>
     </row>
-    <row r="194" spans="1:33" ht="11.45" customHeight="1">
+    <row r="194" spans="1:33" ht="11.5" customHeight="1">
       <c r="A194" s="205">
         <v>46035</v>
       </c>
@@ -23730,7 +23730,7 @@
       <c r="AF194" s="104"/>
       <c r="AG194" s="104"/>
     </row>
-    <row r="195" spans="1:33" ht="11.45" customHeight="1">
+    <row r="195" spans="1:33" ht="11.5" customHeight="1">
       <c r="A195" s="207">
         <v>46035</v>
       </c>
@@ -23787,7 +23787,7 @@
       <c r="AF195" s="106"/>
       <c r="AG195" s="106"/>
     </row>
-    <row r="196" spans="1:33" ht="11.45" customHeight="1">
+    <row r="196" spans="1:33" ht="11.5" customHeight="1">
       <c r="A196" s="206">
         <v>46035</v>
       </c>
@@ -23846,7 +23846,7 @@
       <c r="AF196" s="78"/>
       <c r="AG196" s="78"/>
     </row>
-    <row r="197" spans="1:33" ht="11.45" customHeight="1">
+    <row r="197" spans="1:33" ht="11.5" customHeight="1">
       <c r="A197" s="204">
         <v>46057</v>
       </c>
@@ -23907,7 +23907,7 @@
       <c r="AF197" s="88"/>
       <c r="AG197" s="88"/>
     </row>
-    <row r="198" spans="1:33" ht="11.45" customHeight="1">
+    <row r="198" spans="1:33" ht="11.5" customHeight="1">
       <c r="A198" s="203">
         <v>46057</v>
       </c>
@@ -23966,7 +23966,7 @@
       <c r="AF198" s="56"/>
       <c r="AG198" s="56"/>
     </row>
-    <row r="199" spans="1:33" ht="11.45" customHeight="1">
+    <row r="199" spans="1:33" ht="11.5" customHeight="1">
       <c r="A199" s="214">
         <v>46035</v>
       </c>
@@ -24023,7 +24023,7 @@
       <c r="AF199" s="81"/>
       <c r="AG199" s="81"/>
     </row>
-    <row r="200" spans="1:33" ht="11.45" customHeight="1">
+    <row r="200" spans="1:33" ht="11.5" customHeight="1">
       <c r="A200" s="214">
         <v>46058</v>
       </c>
@@ -24076,7 +24076,7 @@
       <c r="AF200" s="81"/>
       <c r="AG200" s="81"/>
     </row>
-    <row r="201" spans="1:33" ht="11.45" customHeight="1">
+    <row r="201" spans="1:33" ht="11.5" customHeight="1">
       <c r="A201" s="209">
         <v>46051</v>
       </c>
@@ -24133,7 +24133,7 @@
       <c r="AF201" s="102"/>
       <c r="AG201" s="102"/>
     </row>
-    <row r="202" spans="1:33" ht="11.45" customHeight="1">
+    <row r="202" spans="1:33" ht="11.5" customHeight="1">
       <c r="A202" s="205">
         <v>46051</v>
       </c>
@@ -24192,7 +24192,7 @@
       <c r="AF202" s="104"/>
       <c r="AG202" s="104"/>
     </row>
-    <row r="203" spans="1:33" ht="11.45" customHeight="1">
+    <row r="203" spans="1:33" ht="11.5" customHeight="1">
       <c r="A203" s="207">
         <v>46051</v>
       </c>
@@ -24255,7 +24255,7 @@
       <c r="AF203" s="106"/>
       <c r="AG203" s="106"/>
     </row>
-    <row r="204" spans="1:33" ht="11.45" customHeight="1">
+    <row r="204" spans="1:33" ht="11.5" customHeight="1">
       <c r="A204" s="206">
         <v>46051</v>
       </c>
@@ -24312,7 +24312,7 @@
       <c r="AF204" s="78"/>
       <c r="AG204" s="78"/>
     </row>
-    <row r="205" spans="1:33" ht="11.45" customHeight="1">
+    <row r="205" spans="1:33" ht="11.5" customHeight="1">
       <c r="A205" s="203">
         <v>46051</v>
       </c>
@@ -24371,7 +24371,7 @@
       <c r="AF205" s="56"/>
       <c r="AG205" s="56"/>
     </row>
-    <row r="206" spans="1:33" ht="11.45" customHeight="1">
+    <row r="206" spans="1:33" ht="11.5" customHeight="1">
       <c r="A206" s="214">
         <v>46051</v>
       </c>
@@ -24432,7 +24432,7 @@
       <c r="AF206" s="81"/>
       <c r="AG206" s="81"/>
     </row>
-    <row r="207" spans="1:33" ht="11.45" customHeight="1">
+    <row r="207" spans="1:33" ht="11.5" customHeight="1">
       <c r="A207" s="209">
         <v>46051</v>
       </c>
@@ -24491,7 +24491,7 @@
       <c r="AF207" s="102"/>
       <c r="AG207" s="102"/>
     </row>
-    <row r="208" spans="1:33" ht="11.45" customHeight="1">
+    <row r="208" spans="1:33" ht="11.5" customHeight="1">
       <c r="A208" s="205">
         <v>46051</v>
       </c>
@@ -24548,7 +24548,7 @@
       <c r="AF208" s="104"/>
       <c r="AG208" s="104"/>
     </row>
-    <row r="209" spans="1:33" ht="11.45" customHeight="1">
+    <row r="209" spans="1:33" ht="11.5" customHeight="1">
       <c r="A209" s="207">
         <v>46051</v>
       </c>
@@ -24598,7 +24598,7 @@
       <c r="AF209" s="106"/>
       <c r="AG209" s="106"/>
     </row>
-    <row r="210" spans="1:33" ht="11.45" customHeight="1">
+    <row r="210" spans="1:33" ht="11.5" customHeight="1">
       <c r="A210" s="206">
         <v>46051</v>
       </c>
@@ -24657,7 +24657,7 @@
       <c r="AF210" s="78"/>
       <c r="AG210" s="78"/>
     </row>
-    <row r="211" spans="1:33" ht="11.45" customHeight="1">
+    <row r="211" spans="1:33" ht="11.5" customHeight="1">
       <c r="A211" s="204">
         <v>46051</v>
       </c>
@@ -24711,7 +24711,7 @@
       <c r="AF211" s="88"/>
       <c r="AG211" s="88"/>
     </row>
-    <row r="212" spans="1:33" ht="11.45" customHeight="1">
+    <row r="212" spans="1:33" ht="11.5" customHeight="1">
       <c r="A212" s="203">
         <v>46051</v>
       </c>
@@ -24770,7 +24770,7 @@
       <c r="AF212" s="56"/>
       <c r="AG212" s="56"/>
     </row>
-    <row r="213" spans="1:33" ht="11.45" customHeight="1">
+    <row r="213" spans="1:33" ht="11.5" customHeight="1">
       <c r="A213" s="214">
         <v>46051</v>
       </c>
@@ -24831,7 +24831,7 @@
       <c r="AF213" s="81"/>
       <c r="AG213" s="81"/>
     </row>
-    <row r="214" spans="1:33" ht="11.45" customHeight="1">
+    <row r="214" spans="1:33" ht="11.5" customHeight="1">
       <c r="A214" s="209">
         <v>46051</v>
       </c>
@@ -24888,7 +24888,7 @@
       <c r="AF214" s="102"/>
       <c r="AG214" s="102"/>
     </row>
-    <row r="215" spans="1:33" ht="11.45" customHeight="1">
+    <row r="215" spans="1:33" ht="11.5" customHeight="1">
       <c r="A215" s="205">
         <v>46051</v>
       </c>
@@ -24947,7 +24947,7 @@
       <c r="AF215" s="104"/>
       <c r="AG215" s="104"/>
     </row>
-    <row r="216" spans="1:33" ht="11.45" customHeight="1">
+    <row r="216" spans="1:33" ht="11.5" customHeight="1">
       <c r="A216" s="207">
         <v>46051</v>
       </c>
@@ -25004,7 +25004,7 @@
       <c r="AF216" s="106"/>
       <c r="AG216" s="106"/>
     </row>
-    <row r="217" spans="1:33" ht="11.45" customHeight="1">
+    <row r="217" spans="1:33" ht="11.5" customHeight="1">
       <c r="A217" s="206">
         <v>46051</v>
       </c>
@@ -25069,7 +25069,7 @@
       <c r="AF217" s="78"/>
       <c r="AG217" s="78"/>
     </row>
-    <row r="218" spans="1:33" ht="11.45" customHeight="1">
+    <row r="218" spans="1:33" ht="11.5" customHeight="1">
       <c r="A218" s="204">
         <v>46051</v>
       </c>
@@ -25128,7 +25128,7 @@
       <c r="AF218" s="88"/>
       <c r="AG218" s="88"/>
     </row>
-    <row r="219" spans="1:33" ht="11.45" customHeight="1">
+    <row r="219" spans="1:33" ht="11.5" customHeight="1">
       <c r="A219" s="203">
         <v>46051</v>
       </c>
@@ -25187,7 +25187,7 @@
       <c r="AF219" s="56"/>
       <c r="AG219" s="56"/>
     </row>
-    <row r="220" spans="1:33" ht="11.45" customHeight="1">
+    <row r="220" spans="1:33" ht="11.5" customHeight="1">
       <c r="A220" s="214">
         <v>46051</v>
       </c>
@@ -25244,7 +25244,7 @@
       <c r="AF220" s="81"/>
       <c r="AG220" s="81"/>
     </row>
-    <row r="221" spans="1:33" ht="11.45" customHeight="1">
+    <row r="221" spans="1:33" ht="11.5" customHeight="1">
       <c r="A221" s="209">
         <v>46051</v>
       </c>
@@ -25307,7 +25307,7 @@
       <c r="AF221" s="102"/>
       <c r="AG221" s="102"/>
     </row>
-    <row r="222" spans="1:33" ht="11.45" customHeight="1">
+    <row r="222" spans="1:33" ht="11.5" customHeight="1">
       <c r="A222" s="205">
         <v>46051</v>
       </c>
@@ -25370,7 +25370,7 @@
       <c r="AF222" s="104"/>
       <c r="AG222" s="104"/>
     </row>
-    <row r="223" spans="1:33" ht="11.45" customHeight="1">
+    <row r="223" spans="1:33" ht="11.5" customHeight="1">
       <c r="A223" s="207">
         <v>46051</v>
       </c>
@@ -25427,7 +25427,7 @@
       <c r="AF223" s="106"/>
       <c r="AG223" s="106"/>
     </row>
-    <row r="224" spans="1:33" ht="11.45" customHeight="1">
+    <row r="224" spans="1:33" ht="11.5" customHeight="1">
       <c r="A224" s="206">
         <v>46051</v>
       </c>
@@ -25486,7 +25486,7 @@
       <c r="AF224" s="78"/>
       <c r="AG224" s="78"/>
     </row>
-    <row r="225" spans="1:33" ht="11.45" customHeight="1">
+    <row r="225" spans="1:33" ht="11.5" customHeight="1">
       <c r="A225" s="204">
         <v>46051</v>
       </c>
@@ -25543,7 +25543,7 @@
       <c r="AF225" s="88"/>
       <c r="AG225" s="88"/>
     </row>
-    <row r="226" spans="1:33" ht="11.45" customHeight="1">
+    <row r="226" spans="1:33" ht="11.5" customHeight="1">
       <c r="A226" s="203">
         <v>46051</v>
       </c>
@@ -25596,7 +25596,7 @@
       <c r="AF226" s="56"/>
       <c r="AG226" s="56"/>
     </row>
-    <row r="227" spans="1:33" ht="11.45" customHeight="1">
+    <row r="227" spans="1:33" ht="11.5" customHeight="1">
       <c r="A227" s="214">
         <v>46051</v>
       </c>
@@ -25663,7 +25663,7 @@
       <c r="AF227" s="81"/>
       <c r="AG227" s="81"/>
     </row>
-    <row r="228" spans="1:33" ht="11.45" customHeight="1">
+    <row r="228" spans="1:33" ht="11.5" customHeight="1">
       <c r="A228" s="209">
         <v>46056</v>
       </c>
@@ -25726,7 +25726,7 @@
       <c r="AF228" s="102"/>
       <c r="AG228" s="102"/>
     </row>
-    <row r="229" spans="1:33" ht="11.45" customHeight="1">
+    <row r="229" spans="1:33" ht="11.5" customHeight="1">
       <c r="A229" s="205">
         <v>46056</v>
       </c>
@@ -25783,7 +25783,7 @@
       <c r="AF229" s="104"/>
       <c r="AG229" s="104"/>
     </row>
-    <row r="230" spans="1:33" ht="11.45" customHeight="1">
+    <row r="230" spans="1:33" ht="11.5" customHeight="1">
       <c r="A230" s="207">
         <v>46056</v>
       </c>
@@ -25838,7 +25838,7 @@
       <c r="AF230" s="106"/>
       <c r="AG230" s="106"/>
     </row>
-    <row r="231" spans="1:33" ht="11.45" customHeight="1">
+    <row r="231" spans="1:33" ht="11.5" customHeight="1">
       <c r="A231" s="206">
         <v>46051</v>
       </c>
@@ -25899,7 +25899,7 @@
       <c r="AF231" s="78"/>
       <c r="AG231" s="78"/>
     </row>
-    <row r="232" spans="1:33" ht="11.45" customHeight="1">
+    <row r="232" spans="1:33" ht="11.5" customHeight="1">
       <c r="G232" s="102"/>
       <c r="H232" s="119" t="s">
         <v>170</v>
@@ -25939,7 +25939,7 @@
       <c r="AF232" s="102"/>
       <c r="AG232" s="102"/>
     </row>
-    <row r="233" spans="1:33" ht="11.45" customHeight="1">
+    <row r="233" spans="1:33" ht="11.5" customHeight="1">
       <c r="A233" s="204">
         <v>46056</v>
       </c>
@@ -25996,7 +25996,7 @@
       <c r="AF233" s="88"/>
       <c r="AG233" s="88"/>
     </row>
-    <row r="234" spans="1:33" ht="11.45" customHeight="1">
+    <row r="234" spans="1:33" ht="11.5" customHeight="1">
       <c r="A234" s="203">
         <v>46056</v>
       </c>
@@ -26053,7 +26053,7 @@
       <c r="AF234" s="56"/>
       <c r="AG234" s="56"/>
     </row>
-    <row r="235" spans="1:33" ht="11.45" customHeight="1">
+    <row r="235" spans="1:33" ht="11.5" customHeight="1">
       <c r="A235" s="214">
         <v>46051</v>
       </c>
@@ -26118,7 +26118,7 @@
       <c r="AF235" s="81"/>
       <c r="AG235" s="81"/>
     </row>
-    <row r="236" spans="1:33" ht="11.45" customHeight="1">
+    <row r="236" spans="1:33" ht="11.5" customHeight="1">
       <c r="A236" s="209">
         <v>46051</v>
       </c>
@@ -26183,7 +26183,7 @@
       <c r="AF236" s="102"/>
       <c r="AG236" s="102"/>
     </row>
-    <row r="237" spans="1:33" ht="11.45" customHeight="1">
+    <row r="237" spans="1:33" ht="11.5" customHeight="1">
       <c r="A237" s="205">
         <v>46056</v>
       </c>
@@ -26244,7 +26244,7 @@
       <c r="AF237" s="104"/>
       <c r="AG237" s="104"/>
     </row>
-    <row r="238" spans="1:33" ht="11.45" customHeight="1">
+    <row r="238" spans="1:33" ht="11.5" customHeight="1">
       <c r="A238" s="207">
         <v>46056</v>
       </c>
@@ -26307,7 +26307,7 @@
       <c r="AF238" s="106"/>
       <c r="AG238" s="106"/>
     </row>
-    <row r="239" spans="1:33" ht="11.45" customHeight="1">
+    <row r="239" spans="1:33" ht="11.5" customHeight="1">
       <c r="A239" s="206">
         <v>46056</v>
       </c>
@@ -26368,7 +26368,7 @@
       <c r="AF239" s="78"/>
       <c r="AG239" s="78"/>
     </row>
-    <row r="240" spans="1:33" ht="11.45" customHeight="1">
+    <row r="240" spans="1:33" ht="11.5" customHeight="1">
       <c r="A240" s="204">
         <v>46056</v>
       </c>
@@ -26427,7 +26427,7 @@
       <c r="AF240" s="88"/>
       <c r="AG240" s="88"/>
     </row>
-    <row r="241" spans="1:33" ht="11.45" customHeight="1">
+    <row r="241" spans="1:33" ht="11.5" customHeight="1">
       <c r="A241" s="203">
         <v>46056</v>
       </c>
@@ -26482,7 +26482,7 @@
       <c r="AF241" s="56"/>
       <c r="AG241" s="56"/>
     </row>
-    <row r="242" spans="1:33" ht="11.45" customHeight="1">
+    <row r="242" spans="1:33" ht="11.5" customHeight="1">
       <c r="A242" s="214">
         <v>46051</v>
       </c>
@@ -26541,7 +26541,7 @@
       <c r="AF242" s="81"/>
       <c r="AG242" s="81"/>
     </row>
-    <row r="243" spans="1:33" ht="11.45" customHeight="1">
+    <row r="243" spans="1:33" ht="11.5" customHeight="1">
       <c r="A243" s="412" t="s">
         <v>1383</v>
       </c>
@@ -26588,7 +26588,7 @@
       <c r="AF243" s="102"/>
       <c r="AG243" s="102"/>
     </row>
-    <row r="244" spans="1:33" ht="11.45" customHeight="1">
+    <row r="244" spans="1:33" ht="11.5" customHeight="1">
       <c r="A244" s="205">
         <v>46056</v>
       </c>
@@ -26647,7 +26647,7 @@
       <c r="AF244" s="104"/>
       <c r="AG244" s="104"/>
     </row>
-    <row r="245" spans="1:33" ht="11.45" customHeight="1">
+    <row r="245" spans="1:33" ht="11.5" customHeight="1">
       <c r="A245" s="207">
         <v>46056</v>
       </c>
@@ -26710,7 +26710,7 @@
       <c r="AF245" s="106"/>
       <c r="AG245" s="106"/>
     </row>
-    <row r="246" spans="1:33" ht="11.45" customHeight="1" thickBot="1">
+    <row r="246" spans="1:33" ht="11.5" customHeight="1" thickBot="1">
       <c r="A246" s="206">
         <v>46056</v>
       </c>
@@ -26773,7 +26773,7 @@
       <c r="AF246" s="78"/>
       <c r="AG246" s="78"/>
     </row>
-    <row r="247" spans="1:33" ht="11.45" customHeight="1" thickBot="1">
+    <row r="247" spans="1:33" ht="11.5" customHeight="1" thickBot="1">
       <c r="A247" s="204">
         <v>46056</v>
       </c>
@@ -26830,7 +26830,7 @@
       <c r="AF247" s="88"/>
       <c r="AG247" s="88"/>
     </row>
-    <row r="248" spans="1:33" ht="11.45" customHeight="1" thickBot="1">
+    <row r="248" spans="1:33" ht="11.5" customHeight="1" thickBot="1">
       <c r="A248" s="203">
         <v>46051</v>
       </c>
@@ -26893,7 +26893,7 @@
       <c r="AF248" s="56"/>
       <c r="AG248" s="56"/>
     </row>
-    <row r="249" spans="1:33" ht="11.45" customHeight="1" thickBot="1">
+    <row r="249" spans="1:33" ht="11.5" customHeight="1" thickBot="1">
       <c r="A249" s="214">
         <v>46056</v>
       </c>
@@ -26952,7 +26952,7 @@
       <c r="AF249" s="81"/>
       <c r="AG249" s="81"/>
     </row>
-    <row r="250" spans="1:33" ht="11.45" customHeight="1">
+    <row r="250" spans="1:33" ht="11.5" customHeight="1">
       <c r="A250" s="209">
         <v>46056</v>
       </c>
@@ -27009,7 +27009,7 @@
       <c r="AF250" s="102"/>
       <c r="AG250" s="102"/>
     </row>
-    <row r="251" spans="1:33" ht="11.45" customHeight="1">
+    <row r="251" spans="1:33" ht="11.5" customHeight="1">
       <c r="A251" s="205">
         <v>46051</v>
       </c>
@@ -27070,7 +27070,7 @@
       <c r="AF251" s="104"/>
       <c r="AG251" s="104"/>
     </row>
-    <row r="252" spans="1:33" ht="11.45" customHeight="1">
+    <row r="252" spans="1:33" ht="11.5" customHeight="1">
       <c r="A252" s="207">
         <v>46056</v>
       </c>
@@ -27127,7 +27127,7 @@
       <c r="AF252" s="106"/>
       <c r="AG252" s="106"/>
     </row>
-    <row r="253" spans="1:33" ht="11.45" customHeight="1">
+    <row r="253" spans="1:33" ht="11.5" customHeight="1">
       <c r="A253" s="206">
         <v>46056</v>
       </c>
@@ -27182,7 +27182,7 @@
       <c r="AF253" s="78"/>
       <c r="AG253" s="78"/>
     </row>
-    <row r="254" spans="1:33" ht="11.45" customHeight="1">
+    <row r="254" spans="1:33" ht="11.5" customHeight="1">
       <c r="A254" s="204">
         <v>46056</v>
       </c>
@@ -27237,7 +27237,7 @@
       <c r="AF254" s="88"/>
       <c r="AG254" s="88"/>
     </row>
-    <row r="255" spans="1:33" ht="11.45" customHeight="1">
+    <row r="255" spans="1:33" ht="11.5" customHeight="1">
       <c r="A255" s="204">
         <v>46058</v>
       </c>
@@ -27285,7 +27285,7 @@
       <c r="AF255" s="88"/>
       <c r="AG255" s="88"/>
     </row>
-    <row r="256" spans="1:33" ht="11.45" customHeight="1">
+    <row r="256" spans="1:33" ht="11.5" customHeight="1">
       <c r="A256" s="203">
         <v>46056</v>
       </c>
@@ -27350,7 +27350,7 @@
       <c r="AF256" s="56"/>
       <c r="AG256" s="56"/>
     </row>
-    <row r="257" spans="1:33" ht="11.45" customHeight="1">
+    <row r="257" spans="1:33" ht="11.5" customHeight="1">
       <c r="A257" s="214">
         <v>46057</v>
       </c>
@@ -27407,7 +27407,7 @@
       <c r="AF257" s="81"/>
       <c r="AG257" s="81"/>
     </row>
-    <row r="258" spans="1:33" ht="11.45" customHeight="1">
+    <row r="258" spans="1:33" ht="11.5" customHeight="1">
       <c r="A258" s="209">
         <v>46051</v>
       </c>
@@ -27466,7 +27466,7 @@
       <c r="AF258" s="102"/>
       <c r="AG258" s="102"/>
     </row>
-    <row r="259" spans="1:33" ht="11.45" customHeight="1">
+    <row r="259" spans="1:33" ht="11.5" customHeight="1">
       <c r="A259" s="205">
         <v>46057</v>
       </c>
@@ -27527,7 +27527,7 @@
       <c r="AF259" s="104"/>
       <c r="AG259" s="104"/>
     </row>
-    <row r="260" spans="1:33" ht="11.45" customHeight="1">
+    <row r="260" spans="1:33" ht="11.5" customHeight="1">
       <c r="A260" s="207">
         <v>46057</v>
       </c>
@@ -27586,7 +27586,7 @@
       <c r="AF260" s="106"/>
       <c r="AG260" s="106"/>
     </row>
-    <row r="261" spans="1:33" ht="11.45" customHeight="1">
+    <row r="261" spans="1:33" ht="11.5" customHeight="1">
       <c r="A261" s="204">
         <v>46057</v>
       </c>
@@ -27645,7 +27645,7 @@
       <c r="AF261" s="88"/>
       <c r="AG261" s="88"/>
     </row>
-    <row r="262" spans="1:33" ht="11.45" customHeight="1">
+    <row r="262" spans="1:33" ht="11.5" customHeight="1">
       <c r="A262" s="203">
         <v>46057</v>
       </c>
@@ -27704,7 +27704,7 @@
       <c r="AF262" s="56"/>
       <c r="AG262" s="56"/>
     </row>
-    <row r="263" spans="1:33" ht="11.45" customHeight="1">
+    <row r="263" spans="1:33" ht="11.5" customHeight="1">
       <c r="A263" s="214">
         <v>46051</v>
       </c>
@@ -27761,7 +27761,7 @@
       <c r="AF263" s="81"/>
       <c r="AG263" s="81"/>
     </row>
-    <row r="264" spans="1:33" ht="11.45" customHeight="1">
+    <row r="264" spans="1:33" ht="11.5" customHeight="1">
       <c r="A264" s="209">
         <v>46051</v>
       </c>
@@ -27818,7 +27818,7 @@
       <c r="AF264" s="102"/>
       <c r="AG264" s="102"/>
     </row>
-    <row r="265" spans="1:33" ht="11.45" customHeight="1">
+    <row r="265" spans="1:33" ht="11.5" customHeight="1">
       <c r="A265" s="205">
         <v>46051</v>
       </c>
@@ -27875,7 +27875,7 @@
       <c r="AF265" s="104"/>
       <c r="AG265" s="104"/>
     </row>
-    <row r="266" spans="1:33" ht="11.45" customHeight="1">
+    <row r="266" spans="1:33" ht="11.5" customHeight="1">
       <c r="A266" s="207">
         <v>46051</v>
       </c>
@@ -27932,7 +27932,7 @@
       <c r="AF266" s="106"/>
       <c r="AG266" s="106"/>
     </row>
-    <row r="267" spans="1:33" ht="11.45" customHeight="1">
+    <row r="267" spans="1:33" ht="11.5" customHeight="1">
       <c r="A267" s="204">
         <v>46057</v>
       </c>
@@ -27993,7 +27993,7 @@
       <c r="AF267" s="88"/>
       <c r="AG267" s="88"/>
     </row>
-    <row r="268" spans="1:33" ht="11.45" customHeight="1">
+    <row r="268" spans="1:33" ht="11.5" customHeight="1">
       <c r="A268" s="203">
         <v>46057</v>
       </c>
@@ -28054,7 +28054,7 @@
       <c r="AF268" s="56"/>
       <c r="AG268" s="56"/>
     </row>
-    <row r="269" spans="1:33" ht="11.45" customHeight="1">
+    <row r="269" spans="1:33" ht="11.5" customHeight="1">
       <c r="A269" s="209">
         <v>46057</v>
       </c>
@@ -28115,7 +28115,7 @@
       <c r="AF269" s="102"/>
       <c r="AG269" s="102"/>
     </row>
-    <row r="270" spans="1:33" s="302" customFormat="1" ht="11.45" customHeight="1">
+    <row r="270" spans="1:33" s="302" customFormat="1" ht="11.5" customHeight="1">
       <c r="A270" s="358">
         <v>46057</v>
       </c>
@@ -28178,7 +28178,7 @@
       <c r="AF270" s="360"/>
       <c r="AG270" s="360"/>
     </row>
-    <row r="271" spans="1:33" ht="11.45" customHeight="1">
+    <row r="271" spans="1:33" ht="11.5" customHeight="1">
       <c r="A271" s="209">
         <v>46057</v>
       </c>
@@ -28235,7 +28235,7 @@
       <c r="AF271" s="102"/>
       <c r="AG271" s="102"/>
     </row>
-    <row r="272" spans="1:33" ht="11.45" customHeight="1">
+    <row r="272" spans="1:33" ht="11.5" customHeight="1">
       <c r="A272" s="205">
         <v>46057</v>
       </c>
@@ -28290,7 +28290,7 @@
       <c r="AF272" s="104"/>
       <c r="AG272" s="104"/>
     </row>
-    <row r="273" spans="1:33" ht="11.45" customHeight="1">
+    <row r="273" spans="1:33" ht="11.5" customHeight="1">
       <c r="A273" s="204">
         <v>46057</v>
       </c>
@@ -28347,7 +28347,7 @@
       <c r="AF273" s="88"/>
       <c r="AG273" s="88"/>
     </row>
-    <row r="274" spans="1:33" ht="11.45" customHeight="1">
+    <row r="274" spans="1:33" ht="11.5" customHeight="1">
       <c r="A274" s="209">
         <v>46057</v>
       </c>
@@ -28402,7 +28402,7 @@
       <c r="AF274" s="81"/>
       <c r="AG274" s="81"/>
     </row>
-    <row r="275" spans="1:33" ht="11.45" customHeight="1">
+    <row r="275" spans="1:33" ht="11.5" customHeight="1">
       <c r="A275" s="205">
         <v>46057</v>
       </c>
@@ -28459,7 +28459,7 @@
       <c r="AF275" s="104"/>
       <c r="AG275" s="104"/>
     </row>
-    <row r="276" spans="1:33" ht="11.45" customHeight="1">
+    <row r="276" spans="1:33" ht="11.5" customHeight="1">
       <c r="A276" s="207">
         <v>46057</v>
       </c>
@@ -28515,7 +28515,7 @@
       <c r="AF276" s="106"/>
       <c r="AG276" s="106"/>
     </row>
-    <row r="277" spans="1:33" ht="11.45" customHeight="1">
+    <row r="277" spans="1:33" ht="11.5" customHeight="1">
       <c r="A277" s="209">
         <v>46057</v>
       </c>
@@ -28576,7 +28576,7 @@
       <c r="AF277" s="102"/>
       <c r="AG277" s="102"/>
     </row>
-    <row r="278" spans="1:33" ht="11.45" customHeight="1">
+    <row r="278" spans="1:33" ht="11.5" customHeight="1">
       <c r="A278" s="209">
         <v>46057</v>
       </c>
@@ -28633,7 +28633,7 @@
       <c r="AF278" s="106"/>
       <c r="AG278" s="106"/>
     </row>
-    <row r="279" spans="1:33" ht="11.45" customHeight="1">
+    <row r="279" spans="1:33" ht="11.5" customHeight="1">
       <c r="A279" s="209"/>
       <c r="B279" s="209"/>
       <c r="C279" s="365"/>
@@ -28692,7 +28692,7 @@
       <c r="AF279" s="78"/>
       <c r="AG279" s="78"/>
     </row>
-    <row r="280" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="280" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A280" s="278">
         <v>46057</v>
       </c>
@@ -28751,7 +28751,7 @@
       <c r="AF280" s="274"/>
       <c r="AG280" s="274"/>
     </row>
-    <row r="281" spans="1:33" s="269" customFormat="1" ht="11.45" customHeight="1">
+    <row r="281" spans="1:33" s="269" customFormat="1" ht="11.5" customHeight="1">
       <c r="A281" s="278"/>
       <c r="B281" s="278">
         <v>46072</v>
@@ -28794,7 +28794,7 @@
       <c r="AF281" s="274"/>
       <c r="AG281" s="274"/>
     </row>
-    <row r="282" spans="1:33" ht="11.45" customHeight="1">
+    <row r="282" spans="1:33" ht="11.5" customHeight="1">
       <c r="A282" s="205">
         <v>46035</v>
       </c>
@@ -28851,7 +28851,7 @@
       <c r="AF282" s="104"/>
       <c r="AG282" s="104"/>
     </row>
-    <row r="283" spans="1:33" ht="11.45" customHeight="1">
+    <row r="283" spans="1:33" ht="11.5" customHeight="1">
       <c r="A283" s="203">
         <v>46057</v>
       </c>
@@ -28908,7 +28908,7 @@
       <c r="AF283" s="56"/>
       <c r="AG283" s="56"/>
     </row>
-    <row r="284" spans="1:33" ht="11.45" customHeight="1">
+    <row r="284" spans="1:33" ht="11.5" customHeight="1">
       <c r="A284" s="209">
         <v>46057</v>
       </c>
@@ -28963,7 +28963,7 @@
       <c r="AF284" s="102"/>
       <c r="AG284" s="102"/>
     </row>
-    <row r="285" spans="1:33" ht="11.45" customHeight="1">
+    <row r="285" spans="1:33" ht="11.5" customHeight="1">
       <c r="A285" s="206">
         <v>46057</v>
       </c>
@@ -29022,7 +29022,7 @@
       <c r="AF285" s="78"/>
       <c r="AG285" s="78"/>
     </row>
-    <row r="286" spans="1:33" ht="11.45" customHeight="1">
+    <row r="286" spans="1:33" ht="11.5" customHeight="1">
       <c r="A286" s="207">
         <v>46057</v>
       </c>
@@ -29083,7 +29083,7 @@
       <c r="AF286" s="106"/>
       <c r="AG286" s="106"/>
     </row>
-    <row r="287" spans="1:33" ht="11.45" customHeight="1">
+    <row r="287" spans="1:33" ht="11.5" customHeight="1">
       <c r="A287" s="206">
         <v>46057</v>
       </c>
@@ -29142,7 +29142,7 @@
       <c r="AF287" s="78"/>
       <c r="AG287" s="78"/>
     </row>
-    <row r="288" spans="1:33" ht="11.45" customHeight="1">
+    <row r="288" spans="1:33" ht="11.5" customHeight="1">
       <c r="A288" s="204">
         <v>46056</v>
       </c>
@@ -29201,7 +29201,7 @@
       <c r="AF288" s="56"/>
       <c r="AG288" s="56"/>
     </row>
-    <row r="289" spans="1:33" ht="11.45" customHeight="1">
+    <row r="289" spans="1:33" ht="11.5" customHeight="1">
       <c r="A289" s="214">
         <v>46057</v>
       </c>
@@ -29260,7 +29260,7 @@
       <c r="AF289" s="81"/>
       <c r="AG289" s="81"/>
     </row>
-    <row r="290" spans="1:33" ht="11.45" customHeight="1">
+    <row r="290" spans="1:33" ht="11.5" customHeight="1">
       <c r="A290" s="204">
         <v>46057</v>
       </c>
@@ -29321,7 +29321,7 @@
       <c r="AF290" s="88"/>
       <c r="AG290" s="88"/>
     </row>
-    <row r="291" spans="1:33" ht="11.45" customHeight="1">
+    <row r="291" spans="1:33" ht="11.5" customHeight="1">
       <c r="A291" s="203">
         <v>46057</v>
       </c>
@@ -29384,7 +29384,7 @@
       <c r="AF291" s="56"/>
       <c r="AG291" s="56"/>
     </row>
-    <row r="292" spans="1:33" ht="11.45" customHeight="1">
+    <row r="292" spans="1:33" ht="11.5" customHeight="1">
       <c r="A292" s="209">
         <v>46057</v>
       </c>
@@ -29445,7 +29445,7 @@
       <c r="AF292" s="102"/>
       <c r="AG292" s="102"/>
     </row>
-    <row r="293" spans="1:33" ht="11.45" customHeight="1">
+    <row r="293" spans="1:33" ht="11.5" customHeight="1">
       <c r="A293" s="205">
         <v>46057</v>
       </c>
@@ -29506,7 +29506,7 @@
       <c r="AF293" s="104"/>
       <c r="AG293" s="104"/>
     </row>
-    <row r="294" spans="1:33" ht="11.45" customHeight="1">
+    <row r="294" spans="1:33" ht="11.5" customHeight="1">
       <c r="A294" s="205">
         <v>46057</v>
       </c>
@@ -29563,7 +29563,7 @@
       <c r="AF294" s="104"/>
       <c r="AG294" s="104"/>
     </row>
-    <row r="295" spans="1:33" ht="11.45" customHeight="1">
+    <row r="295" spans="1:33" ht="11.5" customHeight="1">
       <c r="A295" s="207">
         <v>46051</v>
       </c>
@@ -29622,7 +29622,7 @@
       <c r="AF295" s="106"/>
       <c r="AG295" s="106"/>
     </row>
-    <row r="296" spans="1:33" ht="11.45" customHeight="1">
+    <row r="296" spans="1:33" ht="11.5" customHeight="1">
       <c r="A296" s="206">
         <v>46058</v>
       </c>
@@ -29685,7 +29685,7 @@
       <c r="AF296" s="78"/>
       <c r="AG296" s="78"/>
     </row>
-    <row r="297" spans="1:33" ht="11.45" customHeight="1">
+    <row r="297" spans="1:33" ht="11.5" customHeight="1">
       <c r="A297" s="204">
         <v>46057</v>
       </c>
@@ -29746,7 +29746,7 @@
       <c r="AF297" s="88"/>
       <c r="AG297" s="88"/>
     </row>
-    <row r="298" spans="1:33" ht="11.45" customHeight="1">
+    <row r="298" spans="1:33" ht="11.5" customHeight="1">
       <c r="A298" s="205">
         <v>46063</v>
       </c>
@@ -29805,7 +29805,7 @@
       <c r="AF298" s="104"/>
       <c r="AG298" s="104"/>
     </row>
-    <row r="299" spans="1:33" ht="11.45" customHeight="1">
+    <row r="299" spans="1:33" ht="11.5" customHeight="1">
       <c r="A299" s="207">
         <v>46063</v>
       </c>
@@ -29862,7 +29862,7 @@
       <c r="AF299" s="106"/>
       <c r="AG299" s="106"/>
     </row>
-    <row r="300" spans="1:33" ht="11.45" customHeight="1">
+    <row r="300" spans="1:33" ht="11.5" customHeight="1">
       <c r="A300" s="206">
         <v>46063</v>
       </c>
@@ -29921,7 +29921,7 @@
       <c r="AF300" s="78"/>
       <c r="AG300" s="78"/>
     </row>
-    <row r="301" spans="1:33" ht="11.45" customHeight="1">
+    <row r="301" spans="1:33" ht="11.5" customHeight="1">
       <c r="A301" s="204">
         <v>46063</v>
       </c>
@@ -29980,7 +29980,7 @@
       <c r="AF301" s="88"/>
       <c r="AG301" s="88"/>
     </row>
-    <row r="302" spans="1:33" ht="11.45" customHeight="1">
+    <row r="302" spans="1:33" ht="11.5" customHeight="1">
       <c r="A302" s="203">
         <v>46063</v>
       </c>
@@ -30041,7 +30041,7 @@
       <c r="AF302" s="56"/>
       <c r="AG302" s="56"/>
     </row>
-    <row r="303" spans="1:33" ht="11.45" customHeight="1">
+    <row r="303" spans="1:33" ht="11.5" customHeight="1">
       <c r="A303" s="214"/>
       <c r="B303" s="214"/>
       <c r="C303" s="377"/>
@@ -30090,7 +30090,7 @@
       <c r="AF303" s="81"/>
       <c r="AG303" s="81"/>
     </row>
-    <row r="304" spans="1:33" ht="11.45" customHeight="1">
+    <row r="304" spans="1:33" ht="11.5" customHeight="1">
       <c r="A304" s="209"/>
       <c r="B304" s="209"/>
       <c r="C304" s="365"/>
@@ -30139,7 +30139,7 @@
       <c r="AF304" s="102"/>
       <c r="AG304" s="102"/>
     </row>
-    <row r="305" spans="1:33" ht="11.45" customHeight="1">
+    <row r="305" spans="1:33" ht="11.5" customHeight="1">
       <c r="A305" s="205">
         <v>46058</v>
       </c>
@@ -30198,7 +30198,7 @@
       <c r="AF305" s="104"/>
       <c r="AG305" s="104"/>
     </row>
-    <row r="306" spans="1:33" s="121" customFormat="1" ht="11.45" customHeight="1">
+    <row r="306" spans="1:33" s="121" customFormat="1" ht="11.5" customHeight="1">
       <c r="A306" s="413">
         <v>46066</v>
       </c>
@@ -30235,7 +30235,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="307" spans="1:33" ht="11.45" customHeight="1">
+    <row r="307" spans="1:33" ht="11.5" customHeight="1">
       <c r="A307" s="413">
         <v>46077</v>
       </c>
@@ -30285,7 +30285,7 @@
       <c r="AF307" s="81"/>
       <c r="AG307" s="81"/>
     </row>
-    <row r="308" spans="1:33" ht="11.45" customHeight="1">
+    <row r="308" spans="1:33" ht="11.5" customHeight="1">
       <c r="A308" s="413">
         <v>46077</v>
       </c>
@@ -30342,7 +30342,7 @@
       <c r="AF308" s="56"/>
       <c r="AG308" s="56"/>
     </row>
-    <row r="309" spans="1:33" ht="11.45" customHeight="1">
+    <row r="309" spans="1:33" ht="11.5" customHeight="1">
       <c r="A309" s="209">
         <v>46077</v>
       </c>
@@ -30387,7 +30387,7 @@
       <c r="AF309" s="102"/>
       <c r="AG309" s="102"/>
     </row>
-    <row r="310" spans="1:33" ht="11.45" customHeight="1">
+    <row r="310" spans="1:33" ht="11.5" customHeight="1">
       <c r="A310" s="209">
         <v>46077</v>
       </c>
@@ -30439,7 +30439,7 @@
       <c r="AF310" s="104"/>
       <c r="AG310" s="104"/>
     </row>
-    <row r="311" spans="1:33" ht="11.45" customHeight="1">
+    <row r="311" spans="1:33" ht="11.5" customHeight="1">
       <c r="A311" s="209">
         <v>46077</v>
       </c>
@@ -30491,7 +30491,7 @@
       <c r="AF311" s="106"/>
       <c r="AG311" s="106"/>
     </row>
-    <row r="312" spans="1:33" ht="11.45" customHeight="1">
+    <row r="312" spans="1:33" ht="11.5" customHeight="1">
       <c r="A312" s="205">
         <v>46077</v>
       </c>
@@ -30546,7 +30546,7 @@
       <c r="AF312" s="78"/>
       <c r="AG312" s="78"/>
     </row>
-    <row r="313" spans="1:33" ht="11.45" customHeight="1">
+    <row r="313" spans="1:33" ht="11.5" customHeight="1">
       <c r="A313" s="204">
         <v>46077</v>
       </c>
@@ -30601,7 +30601,7 @@
       <c r="AF313" s="88"/>
       <c r="AG313" s="88"/>
     </row>
-    <row r="314" spans="1:33" ht="11.45" customHeight="1">
+    <row r="314" spans="1:33" ht="11.5" customHeight="1">
       <c r="A314" s="203">
         <v>46077</v>
       </c>
@@ -30676,7 +30676,7 @@
       <c r="AF314" s="56"/>
       <c r="AG314" s="56"/>
     </row>
-    <row r="315" spans="1:33" ht="11.45" customHeight="1">
+    <row r="315" spans="1:33" ht="11.5" customHeight="1">
       <c r="A315" s="209">
         <v>46077</v>
       </c>
@@ -30730,7 +30730,7 @@
       <c r="AF315" s="102"/>
       <c r="AG315" s="102"/>
     </row>
-    <row r="316" spans="1:33" ht="11.45" customHeight="1">
+    <row r="316" spans="1:33" ht="11.5" customHeight="1">
       <c r="A316" s="207">
         <v>46077</v>
       </c>
@@ -30809,7 +30809,7 @@
       <c r="AF316" s="106"/>
       <c r="AG316" s="106"/>
     </row>
-    <row r="317" spans="1:33" ht="11.45" customHeight="1">
+    <row r="317" spans="1:33" ht="11.5" customHeight="1">
       <c r="A317" s="209">
         <v>46077</v>
       </c>
@@ -30860,7 +30860,7 @@
       <c r="AF317" s="78"/>
       <c r="AG317" s="78"/>
     </row>
-    <row r="318" spans="1:33" ht="11.45" customHeight="1">
+    <row r="318" spans="1:33" ht="11.5" customHeight="1">
       <c r="A318" s="204">
         <v>46079</v>
       </c>
@@ -30913,7 +30913,7 @@
       <c r="AF318" s="88"/>
       <c r="AG318" s="88"/>
     </row>
-    <row r="319" spans="1:33" ht="11.45" customHeight="1">
+    <row r="319" spans="1:33" ht="11.5" customHeight="1">
       <c r="A319" s="204">
         <v>46079</v>
       </c>
@@ -30968,7 +30968,7 @@
       <c r="AF319" s="56"/>
       <c r="AG319" s="56"/>
     </row>
-    <row r="320" spans="1:33" ht="11.45" customHeight="1">
+    <row r="320" spans="1:33" ht="11.5" customHeight="1">
       <c r="A320" s="204">
         <v>46079</v>
       </c>
@@ -31027,7 +31027,7 @@
       <c r="AF320" s="81"/>
       <c r="AG320" s="81"/>
     </row>
-    <row r="321" spans="1:33" ht="11.45" customHeight="1">
+    <row r="321" spans="1:33" ht="11.5" customHeight="1">
       <c r="A321" s="204">
         <v>46079</v>
       </c>
@@ -31082,7 +31082,7 @@
       <c r="AF321" s="102"/>
       <c r="AG321" s="102"/>
     </row>
-    <row r="322" spans="1:33" ht="11.45" customHeight="1">
+    <row r="322" spans="1:33" ht="11.5" customHeight="1">
       <c r="A322" s="204">
         <v>46079</v>
       </c>
@@ -31135,7 +31135,7 @@
       <c r="AF322" s="104"/>
       <c r="AG322" s="104"/>
     </row>
-    <row r="323" spans="1:33" ht="11.45" customHeight="1">
+    <row r="323" spans="1:33" ht="11.5" customHeight="1">
       <c r="A323" s="214">
         <v>46079</v>
       </c>
@@ -31212,7 +31212,7 @@
       <c r="AF323" s="81"/>
       <c r="AG323" s="81"/>
     </row>
-    <row r="324" spans="1:33" ht="11.45" customHeight="1">
+    <row r="324" spans="1:33" ht="11.5" customHeight="1">
       <c r="A324" s="214">
         <v>46079</v>
       </c>
@@ -31291,7 +31291,7 @@
       <c r="AF324" s="81"/>
       <c r="AG324" s="81"/>
     </row>
-    <row r="325" spans="1:33" ht="11.45" customHeight="1">
+    <row r="325" spans="1:33" ht="11.5" customHeight="1">
       <c r="A325" s="204">
         <v>46079</v>
       </c>
@@ -31368,7 +31368,7 @@
       <c r="AF325" s="88"/>
       <c r="AG325" s="88"/>
     </row>
-    <row r="326" spans="1:33" ht="11.45" customHeight="1">
+    <row r="326" spans="1:33" ht="11.5" customHeight="1">
       <c r="A326" s="206">
         <v>46079</v>
       </c>
@@ -31449,7 +31449,7 @@
       <c r="AF326" s="78"/>
       <c r="AG326" s="78"/>
     </row>
-    <row r="327" spans="1:33" ht="11.45" customHeight="1">
+    <row r="327" spans="1:33" ht="11.5" customHeight="1">
       <c r="A327" s="204">
         <v>46079</v>
       </c>
@@ -31524,7 +31524,7 @@
       <c r="AF327" s="88"/>
       <c r="AG327" s="88"/>
     </row>
-    <row r="328" spans="1:33" ht="11.45" customHeight="1">
+    <row r="328" spans="1:33" ht="11.5" customHeight="1">
       <c r="A328" s="209">
         <v>46079</v>
       </c>
@@ -31603,7 +31603,7 @@
       <c r="AF328" s="102"/>
       <c r="AG328" s="102"/>
     </row>
-    <row r="329" spans="1:33" ht="11.45" customHeight="1">
+    <row r="329" spans="1:33" ht="11.5" customHeight="1">
       <c r="A329" s="204">
         <v>46079</v>
       </c>
@@ -31682,7 +31682,7 @@
       <c r="AF329" s="88"/>
       <c r="AG329" s="88"/>
     </row>
-    <row r="330" spans="1:33" ht="11.45" customHeight="1">
+    <row r="330" spans="1:33" ht="11.5" customHeight="1">
       <c r="A330" s="209">
         <v>46079</v>
       </c>
@@ -31759,7 +31759,7 @@
       <c r="AF330" s="102"/>
       <c r="AG330" s="102"/>
     </row>
-    <row r="331" spans="1:33" ht="11.45" customHeight="1">
+    <row r="331" spans="1:33" ht="11.5" customHeight="1">
       <c r="A331" s="207">
         <v>46079</v>
       </c>
@@ -31840,7 +31840,7 @@
       <c r="AF331" s="106"/>
       <c r="AG331" s="106"/>
     </row>
-    <row r="332" spans="1:33" ht="11.45" customHeight="1">
+    <row r="332" spans="1:33" ht="11.5" customHeight="1">
       <c r="A332" s="204" t="s">
         <v>1978</v>
       </c>
@@ -31915,7 +31915,7 @@
       <c r="AF332" s="88"/>
       <c r="AG332" s="88"/>
     </row>
-    <row r="333" spans="1:33" ht="11.45" customHeight="1">
+    <row r="333" spans="1:33" ht="11.5" customHeight="1">
       <c r="A333" s="205">
         <v>46079</v>
       </c>
@@ -31988,7 +31988,7 @@
       <c r="AF333" s="104"/>
       <c r="AG333" s="104"/>
     </row>
-    <row r="334" spans="1:33" ht="11.45" customHeight="1">
+    <row r="334" spans="1:33" ht="11.5" customHeight="1">
       <c r="A334" s="207">
         <v>46079</v>
       </c>
@@ -32065,7 +32065,7 @@
       <c r="AF334" s="106"/>
       <c r="AG334" s="106"/>
     </row>
-    <row r="335" spans="1:33" ht="11.45" customHeight="1">
+    <row r="335" spans="1:33" ht="11.5" customHeight="1">
       <c r="A335" s="203">
         <v>46079</v>
       </c>
@@ -32142,7 +32142,7 @@
       <c r="AF335" s="56"/>
       <c r="AG335" s="56"/>
     </row>
-    <row r="336" spans="1:33" ht="11.45" customHeight="1">
+    <row r="336" spans="1:33" ht="11.5" customHeight="1">
       <c r="A336" s="214">
         <v>46079</v>
       </c>
@@ -32223,7 +32223,7 @@
       <c r="AF336" s="81"/>
       <c r="AG336" s="81"/>
     </row>
-    <row r="337" spans="1:33" ht="11.45" customHeight="1">
+    <row r="337" spans="1:33" ht="11.5" customHeight="1">
       <c r="A337" s="214">
         <v>46079</v>
       </c>
@@ -32280,7 +32280,7 @@
       <c r="AF337" s="56"/>
       <c r="AG337" s="56"/>
     </row>
-    <row r="338" spans="1:33" ht="11.45" customHeight="1">
+    <row r="338" spans="1:33" ht="11.5" customHeight="1">
       <c r="A338" s="204">
         <v>46079</v>
       </c>
@@ -32359,7 +32359,7 @@
       <c r="AF338" s="88"/>
       <c r="AG338" s="88"/>
     </row>
-    <row r="339" spans="1:33" ht="11.45" customHeight="1">
+    <row r="339" spans="1:33" ht="11.5" customHeight="1">
       <c r="A339" s="214">
         <v>46079</v>
       </c>
@@ -32434,7 +32434,7 @@
       <c r="AF339" s="81"/>
       <c r="AG339" s="81"/>
     </row>
-    <row r="340" spans="1:33" ht="11.45" customHeight="1">
+    <row r="340" spans="1:33" ht="11.5" customHeight="1">
       <c r="A340" s="209">
         <v>46079</v>
       </c>
@@ -32511,7 +32511,7 @@
       <c r="AF340" s="102"/>
       <c r="AG340" s="102"/>
     </row>
-    <row r="341" spans="1:33" ht="11.45" customHeight="1">
+    <row r="341" spans="1:33" ht="11.5" customHeight="1">
       <c r="A341" s="205" t="s">
         <v>1978</v>
       </c>
@@ -32588,7 +32588,7 @@
       <c r="AF341" s="104"/>
       <c r="AG341" s="104"/>
     </row>
-    <row r="342" spans="1:33" ht="11.45" customHeight="1">
+    <row r="342" spans="1:33" ht="11.5" customHeight="1">
       <c r="A342" s="204" t="s">
         <v>1978</v>
       </c>
@@ -32669,7 +32669,7 @@
       <c r="AF342" s="88"/>
       <c r="AG342" s="88"/>
     </row>
-    <row r="343" spans="1:33" ht="11.45" customHeight="1">
+    <row r="343" spans="1:33" ht="11.5" customHeight="1">
       <c r="A343" s="214" t="s">
         <v>1978</v>
       </c>
@@ -32746,7 +32746,7 @@
       <c r="AF343" s="81"/>
       <c r="AG343" s="81"/>
     </row>
-    <row r="344" spans="1:33" ht="11.45" customHeight="1">
+    <row r="344" spans="1:33" ht="11.5" customHeight="1">
       <c r="A344" s="410" t="s">
         <v>1978</v>
       </c>
@@ -32808,7 +32808,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="345" spans="1:33" s="122" customFormat="1" ht="12.6" customHeight="1">
+    <row r="345" spans="1:33" s="122" customFormat="1" ht="12.65" customHeight="1">
       <c r="A345" s="122" t="s">
         <v>1978</v>
       </c>
@@ -32876,7 +32876,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="346" spans="1:33" ht="11.45" customHeight="1">
+    <row r="346" spans="1:33" ht="11.5" customHeight="1">
       <c r="A346" s="205" t="s">
         <v>1978</v>
       </c>
@@ -32955,7 +32955,7 @@
       <c r="AF346" s="104"/>
       <c r="AG346" s="104"/>
     </row>
-    <row r="347" spans="1:33" ht="11.45" customHeight="1">
+    <row r="347" spans="1:33" ht="11.5" customHeight="1">
       <c r="A347" s="207" t="s">
         <v>1978</v>
       </c>
@@ -33034,7 +33034,7 @@
       <c r="AF347" s="106"/>
       <c r="AG347" s="106"/>
     </row>
-    <row r="348" spans="1:33" ht="11.45" customHeight="1">
+    <row r="348" spans="1:33" ht="11.5" customHeight="1">
       <c r="A348" s="204" t="s">
         <v>1978</v>
       </c>
@@ -33105,7 +33105,7 @@
       <c r="AF348" s="88"/>
       <c r="AG348" s="88"/>
     </row>
-    <row r="349" spans="1:33" ht="11.45" customHeight="1">
+    <row r="349" spans="1:33" ht="11.5" customHeight="1">
       <c r="A349" s="209" t="s">
         <v>1978</v>
       </c>
@@ -33180,7 +33180,7 @@
       <c r="AF349" s="102"/>
       <c r="AG349" s="102"/>
     </row>
-    <row r="350" spans="1:33" ht="11.45" customHeight="1">
+    <row r="350" spans="1:33" ht="11.5" customHeight="1">
       <c r="A350" s="206" t="s">
         <v>1978</v>
       </c>
@@ -33255,7 +33255,7 @@
       <c r="AF350" s="78"/>
       <c r="AG350" s="78"/>
     </row>
-    <row r="351" spans="1:33" ht="11.45" customHeight="1">
+    <row r="351" spans="1:33" ht="11.5" customHeight="1">
       <c r="A351" s="204" t="s">
         <v>1978</v>
       </c>
@@ -33332,7 +33332,7 @@
       <c r="AF351" s="88"/>
       <c r="AG351" s="88"/>
     </row>
-    <row r="352" spans="1:33" s="420" customFormat="1" ht="11.45" customHeight="1">
+    <row r="352" spans="1:33" s="420" customFormat="1" ht="11.5" customHeight="1">
       <c r="A352" s="416">
         <v>46084</v>
       </c>
@@ -33407,7 +33407,7 @@
       <c r="AF352" s="419"/>
       <c r="AG352" s="419"/>
     </row>
-    <row r="353" spans="1:33" ht="11.45" customHeight="1">
+    <row r="353" spans="1:33" ht="11.5" customHeight="1">
       <c r="A353" s="205">
         <v>46084.458333333343</v>
       </c>
@@ -33482,7 +33482,7 @@
       <c r="AF353" s="104"/>
       <c r="AG353" s="104"/>
     </row>
-    <row r="354" spans="1:33" ht="11.45" customHeight="1">
+    <row r="354" spans="1:33" ht="11.5" customHeight="1">
       <c r="A354" s="204">
         <v>46084</v>
       </c>
@@ -33555,7 +33555,7 @@
       <c r="AF354" s="88"/>
       <c r="AG354" s="88"/>
     </row>
-    <row r="355" spans="1:33" ht="11.45" customHeight="1">
+    <row r="355" spans="1:33" ht="11.5" customHeight="1">
       <c r="A355" s="205"/>
       <c r="B355" s="205"/>
       <c r="C355" s="366"/>
@@ -33612,7 +33612,7 @@
       <c r="AF355" s="104"/>
       <c r="AG355" s="104"/>
     </row>
-    <row r="356" spans="1:33" ht="11.45" customHeight="1">
+    <row r="356" spans="1:33" ht="11.5" customHeight="1">
       <c r="A356" s="209"/>
       <c r="B356" s="209"/>
       <c r="C356" s="365"/>
@@ -33667,7 +33667,7 @@
       <c r="AF356" s="102"/>
       <c r="AG356" s="102"/>
     </row>
-    <row r="357" spans="1:33" ht="11.45" customHeight="1">
+    <row r="357" spans="1:33" ht="11.5" customHeight="1">
       <c r="A357" s="206"/>
       <c r="B357" s="206"/>
       <c r="C357" s="381"/>
@@ -33722,7 +33722,7 @@
       <c r="AF357" s="78"/>
       <c r="AG357" s="78"/>
     </row>
-    <row r="358" spans="1:33" ht="11.45" customHeight="1">
+    <row r="358" spans="1:33" ht="11.5" customHeight="1">
       <c r="A358" s="204"/>
       <c r="B358" s="204"/>
       <c r="C358" s="379"/>
@@ -33777,7 +33777,7 @@
       <c r="AF358" s="88"/>
       <c r="AG358" s="88"/>
     </row>
-    <row r="359" spans="1:33" ht="11.45" customHeight="1">
+    <row r="359" spans="1:33" ht="11.5" customHeight="1">
       <c r="A359" s="203"/>
       <c r="B359" s="203"/>
       <c r="C359" s="376"/>
@@ -33834,7 +33834,7 @@
       <c r="AF359" s="56"/>
       <c r="AG359" s="56"/>
     </row>
-    <row r="360" spans="1:33" ht="11.45" customHeight="1">
+    <row r="360" spans="1:33" ht="11.5" customHeight="1">
       <c r="A360" s="214">
         <v>46168</v>
       </c>
@@ -33885,16 +33885,20 @@
       <c r="AF360" s="81"/>
       <c r="AG360" s="81"/>
     </row>
-    <row r="361" spans="1:33" ht="11.45" customHeight="1">
+    <row r="361" spans="1:33" ht="11.5" customHeight="1">
       <c r="A361" s="214">
         <v>46168</v>
       </c>
       <c r="B361" s="209"/>
       <c r="C361" s="365"/>
-      <c r="D361" s="109"/>
+      <c r="D361" s="109">
+        <v>46168</v>
+      </c>
       <c r="E361" s="102"/>
       <c r="F361" s="102"/>
-      <c r="G361" s="102"/>
+      <c r="G361" s="407" t="s">
+        <v>46</v>
+      </c>
       <c r="H361" s="119" t="s">
         <v>2306</v>
       </c>
@@ -33936,7 +33940,7 @@
       <c r="AF361" s="102"/>
       <c r="AG361" s="102"/>
     </row>
-    <row r="362" spans="1:33" ht="11.45" customHeight="1">
+    <row r="362" spans="1:33" ht="11.5" customHeight="1">
       <c r="A362" s="205">
         <v>46168</v>
       </c>
@@ -34009,7 +34013,7 @@
       <c r="AF362" s="104"/>
       <c r="AG362" s="104"/>
     </row>
-    <row r="363" spans="1:33" ht="11.45" customHeight="1">
+    <row r="363" spans="1:33" ht="11.5" customHeight="1">
       <c r="A363" s="207"/>
       <c r="B363" s="207"/>
       <c r="C363" s="367"/>
@@ -34054,7 +34058,7 @@
       <c r="AF363" s="106"/>
       <c r="AG363" s="106"/>
     </row>
-    <row r="364" spans="1:33" ht="11.45" customHeight="1">
+    <row r="364" spans="1:33" ht="11.5" customHeight="1">
       <c r="A364" s="206">
         <v>46168</v>
       </c>
@@ -34127,7 +34131,7 @@
       <c r="AF364" s="78"/>
       <c r="AG364" s="78"/>
     </row>
-    <row r="365" spans="1:33" ht="11.45" customHeight="1">
+    <row r="365" spans="1:33" ht="11.5" customHeight="1">
       <c r="A365" s="204">
         <v>46168</v>
       </c>
@@ -34200,7 +34204,7 @@
       <c r="AF365" s="88"/>
       <c r="AG365" s="88"/>
     </row>
-    <row r="366" spans="1:33" ht="11.45" customHeight="1">
+    <row r="366" spans="1:33" ht="11.5" customHeight="1">
       <c r="A366" s="203"/>
       <c r="B366" s="203"/>
       <c r="C366" s="376"/>
@@ -34245,7 +34249,7 @@
       <c r="AF366" s="56"/>
       <c r="AG366" s="56"/>
     </row>
-    <row r="367" spans="1:33" ht="11.45" customHeight="1">
+    <row r="367" spans="1:33" ht="11.5" customHeight="1">
       <c r="A367" s="214"/>
       <c r="B367" s="214"/>
       <c r="C367" s="377"/>
@@ -34289,7 +34293,7 @@
       <c r="AF367" s="81"/>
       <c r="AG367" s="81"/>
     </row>
-    <row r="368" spans="1:33" ht="11.45" customHeight="1">
+    <row r="368" spans="1:33" ht="11.5" customHeight="1">
       <c r="A368" s="209"/>
       <c r="B368" s="209"/>
       <c r="C368" s="365"/>
@@ -34334,7 +34338,7 @@
       <c r="AF368" s="102"/>
       <c r="AG368" s="102"/>
     </row>
-    <row r="369" spans="1:33" ht="11.45" customHeight="1">
+    <row r="369" spans="1:33" ht="11.5" customHeight="1">
       <c r="A369" s="205"/>
       <c r="B369" s="205"/>
       <c r="C369" s="366"/>
@@ -34376,7 +34380,7 @@
       <c r="AF369" s="104"/>
       <c r="AG369" s="104"/>
     </row>
-    <row r="370" spans="1:33" ht="11.45" customHeight="1">
+    <row r="370" spans="1:33" ht="11.5" customHeight="1">
       <c r="A370" s="207"/>
       <c r="B370" s="207"/>
       <c r="C370" s="367"/>
@@ -34422,7 +34426,7 @@
       <c r="AF370" s="106"/>
       <c r="AG370" s="106"/>
     </row>
-    <row r="371" spans="1:33" ht="11.45" customHeight="1">
+    <row r="371" spans="1:33" ht="11.5" customHeight="1">
       <c r="A371" s="206"/>
       <c r="B371" s="206"/>
       <c r="C371" s="381"/>
@@ -34466,7 +34470,7 @@
       <c r="AF371" s="78"/>
       <c r="AG371" s="78"/>
     </row>
-    <row r="372" spans="1:33" ht="11.45" customHeight="1">
+    <row r="372" spans="1:33" ht="11.5" customHeight="1">
       <c r="A372" s="204"/>
       <c r="B372" s="204"/>
       <c r="C372" s="379"/>
@@ -34508,7 +34512,7 @@
       <c r="AF372" s="88"/>
       <c r="AG372" s="88"/>
     </row>
-    <row r="373" spans="1:33" ht="11.45" customHeight="1">
+    <row r="373" spans="1:33" ht="11.5" customHeight="1">
       <c r="A373" s="203"/>
       <c r="B373" s="203"/>
       <c r="C373" s="376"/>
@@ -34553,7 +34557,7 @@
       <c r="AF373" s="56"/>
       <c r="AG373" s="56"/>
     </row>
-    <row r="374" spans="1:33" ht="11.45" customHeight="1">
+    <row r="374" spans="1:33" ht="11.5" customHeight="1">
       <c r="A374" s="214"/>
       <c r="B374" s="214"/>
       <c r="C374" s="377"/>
@@ -34598,7 +34602,7 @@
       <c r="AF374" s="81"/>
       <c r="AG374" s="81"/>
     </row>
-    <row r="375" spans="1:33" ht="11.45" customHeight="1">
+    <row r="375" spans="1:33" ht="11.5" customHeight="1">
       <c r="A375" s="209"/>
       <c r="B375" s="209"/>
       <c r="C375" s="365"/>
@@ -34647,7 +34651,7 @@
       <c r="AF375" s="102"/>
       <c r="AG375" s="102"/>
     </row>
-    <row r="376" spans="1:33" ht="11.45" customHeight="1">
+    <row r="376" spans="1:33" ht="11.5" customHeight="1">
       <c r="A376" s="205"/>
       <c r="B376" s="205"/>
       <c r="C376" s="366"/>
@@ -34689,7 +34693,7 @@
       <c r="AF376" s="104"/>
       <c r="AG376" s="104"/>
     </row>
-    <row r="377" spans="1:33" ht="11.45" customHeight="1">
+    <row r="377" spans="1:33" ht="11.5" customHeight="1">
       <c r="A377" s="207"/>
       <c r="B377" s="207"/>
       <c r="C377" s="367"/>
@@ -34733,7 +34737,7 @@
       <c r="AF377" s="106"/>
       <c r="AG377" s="106"/>
     </row>
-    <row r="378" spans="1:33" ht="11.45" customHeight="1">
+    <row r="378" spans="1:33" ht="11.5" customHeight="1">
       <c r="A378" s="206"/>
       <c r="B378" s="206"/>
       <c r="C378" s="381"/>
@@ -34782,7 +34786,7 @@
       <c r="AF378" s="78"/>
       <c r="AG378" s="78"/>
     </row>
-    <row r="379" spans="1:33" ht="11.45" customHeight="1">
+    <row r="379" spans="1:33" ht="11.5" customHeight="1">
       <c r="A379" s="204"/>
       <c r="B379" s="204"/>
       <c r="C379" s="379"/>
@@ -34828,7 +34832,7 @@
       <c r="AF379" s="88"/>
       <c r="AG379" s="88"/>
     </row>
-    <row r="380" spans="1:33" ht="11.45" customHeight="1">
+    <row r="380" spans="1:33" ht="11.5" customHeight="1">
       <c r="A380" s="203"/>
       <c r="B380" s="203"/>
       <c r="C380" s="376"/>
@@ -34870,7 +34874,7 @@
       <c r="AF380" s="56"/>
       <c r="AG380" s="56"/>
     </row>
-    <row r="381" spans="1:33" ht="11.45" customHeight="1">
+    <row r="381" spans="1:33" ht="11.5" customHeight="1">
       <c r="A381" s="214"/>
       <c r="B381" s="214"/>
       <c r="C381" s="377"/>
@@ -34914,7 +34918,7 @@
       <c r="AF381" s="81"/>
       <c r="AG381" s="81"/>
     </row>
-    <row r="382" spans="1:33" ht="11.45" customHeight="1">
+    <row r="382" spans="1:33" ht="11.5" customHeight="1">
       <c r="A382" s="209"/>
       <c r="B382" s="209"/>
       <c r="C382" s="365"/>
@@ -34947,7 +34951,7 @@
       <c r="AF382" s="102"/>
       <c r="AG382" s="102"/>
     </row>
-    <row r="383" spans="1:33" ht="11.45" customHeight="1">
+    <row r="383" spans="1:33" ht="11.5" customHeight="1">
       <c r="A383" s="205"/>
       <c r="B383" s="205"/>
       <c r="C383" s="366"/>
@@ -34980,7 +34984,7 @@
       <c r="AF383" s="104"/>
       <c r="AG383" s="104"/>
     </row>
-    <row r="384" spans="1:33" ht="11.45" customHeight="1">
+    <row r="384" spans="1:33" ht="11.5" customHeight="1">
       <c r="A384" s="207"/>
       <c r="B384" s="207"/>
       <c r="C384" s="367"/>
@@ -35013,7 +35017,7 @@
       <c r="AF384" s="106"/>
       <c r="AG384" s="106"/>
     </row>
-    <row r="385" spans="1:33" ht="11.45" customHeight="1">
+    <row r="385" spans="1:33" ht="11.5" customHeight="1">
       <c r="A385" s="206"/>
       <c r="B385" s="206"/>
       <c r="C385" s="381"/>
@@ -35046,7 +35050,7 @@
       <c r="AF385" s="78"/>
       <c r="AG385" s="78"/>
     </row>
-    <row r="386" spans="1:33" ht="11.45" customHeight="1">
+    <row r="386" spans="1:33" ht="11.5" customHeight="1">
       <c r="A386" s="204"/>
       <c r="B386" s="204"/>
       <c r="C386" s="379"/>
@@ -35079,7 +35083,7 @@
       <c r="AF386" s="88"/>
       <c r="AG386" s="88"/>
     </row>
-    <row r="387" spans="1:33" ht="11.45" customHeight="1">
+    <row r="387" spans="1:33" ht="11.5" customHeight="1">
       <c r="A387" s="203"/>
       <c r="B387" s="203"/>
       <c r="C387" s="376"/>
@@ -35112,7 +35116,7 @@
       <c r="AF387" s="56"/>
       <c r="AG387" s="56"/>
     </row>
-    <row r="388" spans="1:33" ht="11.45" customHeight="1">
+    <row r="388" spans="1:33" ht="11.5" customHeight="1">
       <c r="A388" s="214"/>
       <c r="B388" s="214"/>
       <c r="C388" s="377"/>
@@ -35145,7 +35149,7 @@
       <c r="AF388" s="81"/>
       <c r="AG388" s="81"/>
     </row>
-    <row r="389" spans="1:33" ht="11.45" customHeight="1">
+    <row r="389" spans="1:33" ht="11.5" customHeight="1">
       <c r="A389" s="209"/>
       <c r="B389" s="209"/>
       <c r="C389" s="365"/>
@@ -35178,7 +35182,7 @@
       <c r="AF389" s="102"/>
       <c r="AG389" s="102"/>
     </row>
-    <row r="390" spans="1:33" ht="11.45" customHeight="1">
+    <row r="390" spans="1:33" ht="11.5" customHeight="1">
       <c r="A390" s="205"/>
       <c r="B390" s="205"/>
       <c r="C390" s="366"/>
@@ -35211,7 +35215,7 @@
       <c r="AF390" s="104"/>
       <c r="AG390" s="104"/>
     </row>
-    <row r="391" spans="1:33" ht="11.45" customHeight="1">
+    <row r="391" spans="1:33" ht="11.5" customHeight="1">
       <c r="A391" s="207"/>
       <c r="B391" s="207"/>
       <c r="C391" s="367"/>
@@ -35244,7 +35248,7 @@
       <c r="AF391" s="106"/>
       <c r="AG391" s="106"/>
     </row>
-    <row r="392" spans="1:33" ht="11.45" customHeight="1">
+    <row r="392" spans="1:33" ht="11.5" customHeight="1">
       <c r="A392" s="206"/>
       <c r="B392" s="206"/>
       <c r="C392" s="381"/>
@@ -35277,7 +35281,7 @@
       <c r="AF392" s="78"/>
       <c r="AG392" s="78"/>
     </row>
-    <row r="393" spans="1:33" ht="11.45" customHeight="1">
+    <row r="393" spans="1:33" ht="11.5" customHeight="1">
       <c r="A393" s="204"/>
       <c r="B393" s="204"/>
       <c r="C393" s="379"/>
@@ -35310,7 +35314,7 @@
       <c r="AF393" s="88"/>
       <c r="AG393" s="88"/>
     </row>
-    <row r="394" spans="1:33" ht="11.45" customHeight="1">
+    <row r="394" spans="1:33" ht="11.5" customHeight="1">
       <c r="A394" s="203"/>
       <c r="B394" s="203"/>
       <c r="C394" s="376"/>
@@ -35343,7 +35347,7 @@
       <c r="AF394" s="56"/>
       <c r="AG394" s="56"/>
     </row>
-    <row r="395" spans="1:33" ht="11.45" customHeight="1">
+    <row r="395" spans="1:33" ht="11.5" customHeight="1">
       <c r="A395" s="214"/>
       <c r="B395" s="214"/>
       <c r="C395" s="377"/>
@@ -35376,7 +35380,7 @@
       <c r="AF395" s="81"/>
       <c r="AG395" s="81"/>
     </row>
-    <row r="396" spans="1:33" ht="11.45" customHeight="1">
+    <row r="396" spans="1:33" ht="11.5" customHeight="1">
       <c r="A396" s="209"/>
       <c r="B396" s="209"/>
       <c r="C396" s="365"/>
@@ -35409,7 +35413,7 @@
       <c r="AF396" s="102"/>
       <c r="AG396" s="102"/>
     </row>
-    <row r="397" spans="1:33" ht="11.45" customHeight="1">
+    <row r="397" spans="1:33" ht="11.5" customHeight="1">
       <c r="A397" s="205"/>
       <c r="B397" s="205"/>
       <c r="C397" s="366"/>
@@ -35442,7 +35446,7 @@
       <c r="AF397" s="104"/>
       <c r="AG397" s="104"/>
     </row>
-    <row r="398" spans="1:33" ht="11.45" customHeight="1">
+    <row r="398" spans="1:33" ht="11.5" customHeight="1">
       <c r="A398" s="207"/>
       <c r="B398" s="207"/>
       <c r="C398" s="367"/>
@@ -35475,7 +35479,7 @@
       <c r="AF398" s="106"/>
       <c r="AG398" s="106"/>
     </row>
-    <row r="399" spans="1:33" ht="11.45" customHeight="1">
+    <row r="399" spans="1:33" ht="11.5" customHeight="1">
       <c r="A399" s="206"/>
       <c r="B399" s="206"/>
       <c r="C399" s="381"/>
@@ -35508,7 +35512,7 @@
       <c r="AF399" s="78"/>
       <c r="AG399" s="78"/>
     </row>
-    <row r="400" spans="1:33" ht="11.45" customHeight="1">
+    <row r="400" spans="1:33" ht="11.5" customHeight="1">
       <c r="A400" s="204"/>
       <c r="B400" s="204"/>
       <c r="C400" s="379"/>
@@ -35541,7 +35545,7 @@
       <c r="AF400" s="88"/>
       <c r="AG400" s="88"/>
     </row>
-    <row r="401" spans="1:33" ht="11.45" customHeight="1">
+    <row r="401" spans="1:33" ht="11.5" customHeight="1">
       <c r="A401" s="203"/>
       <c r="B401" s="203"/>
       <c r="C401" s="376"/>
@@ -35574,7 +35578,7 @@
       <c r="AF401" s="56"/>
       <c r="AG401" s="56"/>
     </row>
-    <row r="402" spans="1:33" ht="11.45" customHeight="1">
+    <row r="402" spans="1:33" ht="11.5" customHeight="1">
       <c r="A402" s="214"/>
       <c r="B402" s="214"/>
       <c r="C402" s="377"/>
@@ -35607,7 +35611,7 @@
       <c r="AF402" s="81"/>
       <c r="AG402" s="81"/>
     </row>
-    <row r="403" spans="1:33" ht="11.45" customHeight="1">
+    <row r="403" spans="1:33" ht="11.5" customHeight="1">
       <c r="A403" s="209"/>
       <c r="B403" s="209"/>
       <c r="C403" s="365"/>
@@ -35640,7 +35644,7 @@
       <c r="AF403" s="102"/>
       <c r="AG403" s="102"/>
     </row>
-    <row r="404" spans="1:33" ht="11.45" customHeight="1">
+    <row r="404" spans="1:33" ht="11.5" customHeight="1">
       <c r="A404" s="205"/>
       <c r="B404" s="205"/>
       <c r="C404" s="366"/>
@@ -35673,7 +35677,7 @@
       <c r="AF404" s="104"/>
       <c r="AG404" s="104"/>
     </row>
-    <row r="405" spans="1:33" ht="11.45" customHeight="1">
+    <row r="405" spans="1:33" ht="11.5" customHeight="1">
       <c r="A405" s="207"/>
       <c r="B405" s="207"/>
       <c r="C405" s="367"/>
@@ -35706,7 +35710,7 @@
       <c r="AF405" s="106"/>
       <c r="AG405" s="106"/>
     </row>
-    <row r="406" spans="1:33" ht="11.45" customHeight="1">
+    <row r="406" spans="1:33" ht="11.5" customHeight="1">
       <c r="A406" s="206"/>
       <c r="B406" s="206"/>
       <c r="C406" s="381"/>
@@ -35739,7 +35743,7 @@
       <c r="AF406" s="78"/>
       <c r="AG406" s="78"/>
     </row>
-    <row r="407" spans="1:33" ht="11.45" customHeight="1">
+    <row r="407" spans="1:33" ht="11.5" customHeight="1">
       <c r="A407" s="204"/>
       <c r="B407" s="204"/>
       <c r="C407" s="379"/>
@@ -35772,7 +35776,7 @@
       <c r="AF407" s="88"/>
       <c r="AG407" s="88"/>
     </row>
-    <row r="408" spans="1:33" ht="11.45" customHeight="1">
+    <row r="408" spans="1:33" ht="11.5" customHeight="1">
       <c r="A408" s="203"/>
       <c r="B408" s="203"/>
       <c r="C408" s="376"/>
@@ -35805,7 +35809,7 @@
       <c r="AF408" s="56"/>
       <c r="AG408" s="56"/>
     </row>
-    <row r="409" spans="1:33" ht="11.45" customHeight="1">
+    <row r="409" spans="1:33" ht="11.5" customHeight="1">
       <c r="A409" s="214"/>
       <c r="B409" s="214"/>
       <c r="C409" s="377"/>
@@ -35838,7 +35842,7 @@
       <c r="AF409" s="81"/>
       <c r="AG409" s="81"/>
     </row>
-    <row r="410" spans="1:33" ht="11.45" customHeight="1">
+    <row r="410" spans="1:33" ht="11.5" customHeight="1">
       <c r="A410" s="209"/>
       <c r="B410" s="209"/>
       <c r="C410" s="365"/>
@@ -35871,7 +35875,7 @@
       <c r="AF410" s="102"/>
       <c r="AG410" s="102"/>
     </row>
-    <row r="411" spans="1:33" ht="11.45" customHeight="1">
+    <row r="411" spans="1:33" ht="11.5" customHeight="1">
       <c r="A411" s="205"/>
       <c r="B411" s="205"/>
       <c r="C411" s="366"/>
@@ -35904,7 +35908,7 @@
       <c r="AF411" s="104"/>
       <c r="AG411" s="104"/>
     </row>
-    <row r="412" spans="1:33" ht="11.45" customHeight="1">
+    <row r="412" spans="1:33" ht="11.5" customHeight="1">
       <c r="A412" s="207"/>
       <c r="B412" s="207"/>
       <c r="C412" s="367"/>
@@ -35937,7 +35941,7 @@
       <c r="AF412" s="106"/>
       <c r="AG412" s="106"/>
     </row>
-    <row r="413" spans="1:33" ht="11.45" customHeight="1">
+    <row r="413" spans="1:33" ht="11.5" customHeight="1">
       <c r="A413" s="206"/>
       <c r="B413" s="206"/>
       <c r="C413" s="381"/>
@@ -35970,7 +35974,7 @@
       <c r="AF413" s="78"/>
       <c r="AG413" s="78"/>
     </row>
-    <row r="414" spans="1:33" ht="11.45" customHeight="1">
+    <row r="414" spans="1:33" ht="11.5" customHeight="1">
       <c r="A414" s="204"/>
       <c r="B414" s="204"/>
       <c r="C414" s="379"/>
@@ -36003,7 +36007,7 @@
       <c r="AF414" s="88"/>
       <c r="AG414" s="88"/>
     </row>
-    <row r="415" spans="1:33" ht="11.45" customHeight="1">
+    <row r="415" spans="1:33" ht="11.5" customHeight="1">
       <c r="A415" s="203"/>
       <c r="B415" s="203"/>
       <c r="C415" s="376"/>
@@ -36036,7 +36040,7 @@
       <c r="AF415" s="56"/>
       <c r="AG415" s="56"/>
     </row>
-    <row r="416" spans="1:33" ht="11.45" customHeight="1">
+    <row r="416" spans="1:33" ht="11.5" customHeight="1">
       <c r="A416" s="214"/>
       <c r="B416" s="214"/>
       <c r="C416" s="377"/>
@@ -36069,7 +36073,7 @@
       <c r="AF416" s="81"/>
       <c r="AG416" s="81"/>
     </row>
-    <row r="417" spans="1:33" ht="11.45" customHeight="1">
+    <row r="417" spans="1:33" ht="11.5" customHeight="1">
       <c r="A417" s="209"/>
       <c r="B417" s="209"/>
       <c r="C417" s="365"/>
@@ -36102,7 +36106,7 @@
       <c r="AF417" s="102"/>
       <c r="AG417" s="102"/>
     </row>
-    <row r="418" spans="1:33" ht="11.45" customHeight="1">
+    <row r="418" spans="1:33" ht="11.5" customHeight="1">
       <c r="A418" s="205"/>
       <c r="B418" s="205"/>
       <c r="C418" s="366"/>
@@ -36135,7 +36139,7 @@
       <c r="AF418" s="104"/>
       <c r="AG418" s="104"/>
     </row>
-    <row r="419" spans="1:33" ht="11.45" customHeight="1">
+    <row r="419" spans="1:33" ht="11.5" customHeight="1">
       <c r="A419" s="207"/>
       <c r="B419" s="207"/>
       <c r="C419" s="367"/>
@@ -36168,7 +36172,7 @@
       <c r="AF419" s="106"/>
       <c r="AG419" s="106"/>
     </row>
-    <row r="420" spans="1:33" ht="11.45" customHeight="1">
+    <row r="420" spans="1:33" ht="11.5" customHeight="1">
       <c r="A420" s="206"/>
       <c r="B420" s="206"/>
       <c r="C420" s="381"/>
@@ -36201,7 +36205,7 @@
       <c r="AF420" s="78"/>
       <c r="AG420" s="78"/>
     </row>
-    <row r="421" spans="1:33" ht="11.45" customHeight="1">
+    <row r="421" spans="1:33" ht="11.5" customHeight="1">
       <c r="A421" s="204"/>
       <c r="B421" s="204"/>
       <c r="C421" s="379"/>
@@ -36234,7 +36238,7 @@
       <c r="AF421" s="88"/>
       <c r="AG421" s="88"/>
     </row>
-    <row r="422" spans="1:33" ht="11.45" customHeight="1">
+    <row r="422" spans="1:33" ht="11.5" customHeight="1">
       <c r="A422" s="203"/>
       <c r="B422" s="203"/>
       <c r="C422" s="376"/>
@@ -36267,7 +36271,7 @@
       <c r="AF422" s="56"/>
       <c r="AG422" s="56"/>
     </row>
-    <row r="423" spans="1:33" ht="11.45" customHeight="1">
+    <row r="423" spans="1:33" ht="11.5" customHeight="1">
       <c r="A423" s="214"/>
       <c r="B423" s="214"/>
       <c r="C423" s="377"/>
@@ -36300,7 +36304,7 @@
       <c r="AF423" s="81"/>
       <c r="AG423" s="81"/>
     </row>
-    <row r="424" spans="1:33" ht="11.45" customHeight="1">
+    <row r="424" spans="1:33" ht="11.5" customHeight="1">
       <c r="A424" s="209"/>
       <c r="B424" s="209"/>
       <c r="C424" s="365"/>
@@ -36333,7 +36337,7 @@
       <c r="AF424" s="102"/>
       <c r="AG424" s="102"/>
     </row>
-    <row r="425" spans="1:33" ht="11.45" customHeight="1">
+    <row r="425" spans="1:33" ht="11.5" customHeight="1">
       <c r="A425" s="205"/>
       <c r="B425" s="205"/>
       <c r="C425" s="366"/>
@@ -36366,7 +36370,7 @@
       <c r="AF425" s="104"/>
       <c r="AG425" s="104"/>
     </row>
-    <row r="426" spans="1:33" ht="11.45" customHeight="1">
+    <row r="426" spans="1:33" ht="11.5" customHeight="1">
       <c r="A426" s="207"/>
       <c r="B426" s="207"/>
       <c r="C426" s="367"/>
@@ -36399,7 +36403,7 @@
       <c r="AF426" s="106"/>
       <c r="AG426" s="106"/>
     </row>
-    <row r="427" spans="1:33" ht="11.45" customHeight="1">
+    <row r="427" spans="1:33" ht="11.5" customHeight="1">
       <c r="A427" s="206"/>
       <c r="B427" s="206"/>
       <c r="C427" s="381"/>
@@ -36432,7 +36436,7 @@
       <c r="AF427" s="78"/>
       <c r="AG427" s="78"/>
     </row>
-    <row r="428" spans="1:33" ht="11.45" customHeight="1">
+    <row r="428" spans="1:33" ht="11.5" customHeight="1">
       <c r="A428" s="204"/>
       <c r="B428" s="204"/>
       <c r="C428" s="379"/>
@@ -36465,7 +36469,7 @@
       <c r="AF428" s="88"/>
       <c r="AG428" s="88"/>
     </row>
-    <row r="429" spans="1:33" ht="11.45" customHeight="1">
+    <row r="429" spans="1:33" ht="11.5" customHeight="1">
       <c r="A429" s="203"/>
       <c r="B429" s="203"/>
       <c r="C429" s="376"/>
@@ -36498,7 +36502,7 @@
       <c r="AF429" s="56"/>
       <c r="AG429" s="56"/>
     </row>
-    <row r="430" spans="1:33" ht="11.45" customHeight="1">
+    <row r="430" spans="1:33" ht="11.5" customHeight="1">
       <c r="A430" s="214"/>
       <c r="B430" s="214"/>
       <c r="C430" s="377"/>
@@ -36531,7 +36535,7 @@
       <c r="AF430" s="81"/>
       <c r="AG430" s="81"/>
     </row>
-    <row r="431" spans="1:33" ht="11.45" customHeight="1">
+    <row r="431" spans="1:33" ht="11.5" customHeight="1">
       <c r="A431" s="209"/>
       <c r="B431" s="209"/>
       <c r="C431" s="365"/>
@@ -36564,7 +36568,7 @@
       <c r="AF431" s="102"/>
       <c r="AG431" s="102"/>
     </row>
-    <row r="432" spans="1:33" ht="11.45" customHeight="1">
+    <row r="432" spans="1:33" ht="11.5" customHeight="1">
       <c r="A432" s="205"/>
       <c r="B432" s="205"/>
       <c r="C432" s="366"/>
@@ -36597,7 +36601,7 @@
       <c r="AF432" s="104"/>
       <c r="AG432" s="104"/>
     </row>
-    <row r="433" spans="1:33" ht="11.45" customHeight="1">
+    <row r="433" spans="1:33" ht="11.5" customHeight="1">
       <c r="A433" s="207"/>
       <c r="B433" s="207"/>
       <c r="C433" s="367"/>
@@ -36630,7 +36634,7 @@
       <c r="AF433" s="106"/>
       <c r="AG433" s="106"/>
     </row>
-    <row r="434" spans="1:33" ht="11.45" customHeight="1">
+    <row r="434" spans="1:33" ht="11.5" customHeight="1">
       <c r="A434" s="206"/>
       <c r="B434" s="206"/>
       <c r="C434" s="381"/>
@@ -36663,7 +36667,7 @@
       <c r="AF434" s="78"/>
       <c r="AG434" s="78"/>
     </row>
-    <row r="435" spans="1:33" ht="11.45" customHeight="1">
+    <row r="435" spans="1:33" ht="11.5" customHeight="1">
       <c r="A435" s="204"/>
       <c r="B435" s="204"/>
       <c r="C435" s="379"/>
@@ -36696,7 +36700,7 @@
       <c r="AF435" s="88"/>
       <c r="AG435" s="88"/>
     </row>
-    <row r="436" spans="1:33" ht="11.45" customHeight="1">
+    <row r="436" spans="1:33" ht="11.5" customHeight="1">
       <c r="A436" s="203"/>
       <c r="B436" s="203"/>
       <c r="C436" s="376"/>
@@ -36729,7 +36733,7 @@
       <c r="AF436" s="56"/>
       <c r="AG436" s="56"/>
     </row>
-    <row r="437" spans="1:33" ht="11.45" customHeight="1">
+    <row r="437" spans="1:33" ht="11.5" customHeight="1">
       <c r="A437" s="214"/>
       <c r="B437" s="214"/>
       <c r="C437" s="377"/>
@@ -36762,7 +36766,7 @@
       <c r="AF437" s="81"/>
       <c r="AG437" s="81"/>
     </row>
-    <row r="438" spans="1:33" ht="11.45" customHeight="1">
+    <row r="438" spans="1:33" ht="11.5" customHeight="1">
       <c r="A438" s="209"/>
       <c r="B438" s="209"/>
       <c r="C438" s="365"/>
@@ -36795,7 +36799,7 @@
       <c r="AF438" s="102"/>
       <c r="AG438" s="102"/>
     </row>
-    <row r="439" spans="1:33" ht="11.45" customHeight="1">
+    <row r="439" spans="1:33" ht="11.5" customHeight="1">
       <c r="A439" s="205"/>
       <c r="B439" s="205"/>
       <c r="C439" s="366"/>
@@ -36828,7 +36832,7 @@
       <c r="AF439" s="104"/>
       <c r="AG439" s="104"/>
     </row>
-    <row r="440" spans="1:33" ht="11.45" customHeight="1">
+    <row r="440" spans="1:33" ht="11.5" customHeight="1">
       <c r="A440" s="207"/>
       <c r="B440" s="207"/>
       <c r="C440" s="367"/>
@@ -36861,7 +36865,7 @@
       <c r="AF440" s="106"/>
       <c r="AG440" s="106"/>
     </row>
-    <row r="441" spans="1:33" ht="11.45" customHeight="1">
+    <row r="441" spans="1:33" ht="11.5" customHeight="1">
       <c r="A441" s="206"/>
       <c r="B441" s="206"/>
       <c r="C441" s="381"/>
@@ -36894,7 +36898,7 @@
       <c r="AF441" s="78"/>
       <c r="AG441" s="78"/>
     </row>
-    <row r="442" spans="1:33" ht="11.45" customHeight="1">
+    <row r="442" spans="1:33" ht="11.5" customHeight="1">
       <c r="A442" s="204"/>
       <c r="B442" s="204"/>
       <c r="C442" s="379"/>
@@ -36927,7 +36931,7 @@
       <c r="AF442" s="88"/>
       <c r="AG442" s="88"/>
     </row>
-    <row r="443" spans="1:33" ht="11.45" customHeight="1">
+    <row r="443" spans="1:33" ht="11.5" customHeight="1">
       <c r="A443" s="203"/>
       <c r="B443" s="203"/>
       <c r="C443" s="376"/>
@@ -36960,7 +36964,7 @@
       <c r="AF443" s="56"/>
       <c r="AG443" s="56"/>
     </row>
-    <row r="444" spans="1:33" ht="11.45" customHeight="1">
+    <row r="444" spans="1:33" ht="11.5" customHeight="1">
       <c r="A444" s="214"/>
       <c r="B444" s="214"/>
       <c r="C444" s="377"/>
@@ -36993,7 +36997,7 @@
       <c r="AF444" s="81"/>
       <c r="AG444" s="81"/>
     </row>
-    <row r="445" spans="1:33" ht="11.45" customHeight="1">
+    <row r="445" spans="1:33" ht="11.5" customHeight="1">
       <c r="A445" s="209"/>
       <c r="B445" s="209"/>
       <c r="C445" s="365"/>
@@ -37026,7 +37030,7 @@
       <c r="AF445" s="102"/>
       <c r="AG445" s="102"/>
     </row>
-    <row r="446" spans="1:33" ht="11.45" customHeight="1">
+    <row r="446" spans="1:33" ht="11.5" customHeight="1">
       <c r="A446" s="205"/>
       <c r="B446" s="205"/>
       <c r="C446" s="366"/>
@@ -37059,7 +37063,7 @@
       <c r="AF446" s="104"/>
       <c r="AG446" s="104"/>
     </row>
-    <row r="447" spans="1:33" ht="11.45" customHeight="1">
+    <row r="447" spans="1:33" ht="11.5" customHeight="1">
       <c r="A447" s="207"/>
       <c r="B447" s="207"/>
       <c r="C447" s="367"/>
@@ -37092,7 +37096,7 @@
       <c r="AF447" s="106"/>
       <c r="AG447" s="106"/>
     </row>
-    <row r="448" spans="1:33" ht="11.45" customHeight="1">
+    <row r="448" spans="1:33" ht="11.5" customHeight="1">
       <c r="A448" s="206"/>
       <c r="B448" s="206"/>
       <c r="C448" s="381"/>
@@ -37125,7 +37129,7 @@
       <c r="AF448" s="78"/>
       <c r="AG448" s="78"/>
     </row>
-    <row r="449" spans="1:33" ht="11.45" customHeight="1">
+    <row r="449" spans="1:33" ht="11.5" customHeight="1">
       <c r="A449" s="204"/>
       <c r="B449" s="204"/>
       <c r="C449" s="379"/>
@@ -37158,7 +37162,7 @@
       <c r="AF449" s="88"/>
       <c r="AG449" s="88"/>
     </row>
-    <row r="450" spans="1:33" ht="11.45" customHeight="1">
+    <row r="450" spans="1:33" ht="11.5" customHeight="1">
       <c r="A450" s="203"/>
       <c r="B450" s="203"/>
       <c r="C450" s="376"/>
@@ -37191,7 +37195,7 @@
       <c r="AF450" s="56"/>
       <c r="AG450" s="56"/>
     </row>
-    <row r="451" spans="1:33" ht="11.45" customHeight="1">
+    <row r="451" spans="1:33" ht="11.5" customHeight="1">
       <c r="A451" s="214"/>
       <c r="B451" s="214"/>
       <c r="C451" s="377"/>
@@ -37224,7 +37228,7 @@
       <c r="AF451" s="81"/>
       <c r="AG451" s="81"/>
     </row>
-    <row r="452" spans="1:33" ht="11.45" customHeight="1">
+    <row r="452" spans="1:33" ht="11.5" customHeight="1">
       <c r="A452" s="209"/>
       <c r="B452" s="209"/>
       <c r="C452" s="365"/>
@@ -37257,7 +37261,7 @@
       <c r="AF452" s="102"/>
       <c r="AG452" s="102"/>
     </row>
-    <row r="453" spans="1:33" ht="11.45" customHeight="1">
+    <row r="453" spans="1:33" ht="11.5" customHeight="1">
       <c r="A453" s="205"/>
       <c r="B453" s="205"/>
       <c r="C453" s="366"/>
@@ -37290,7 +37294,7 @@
       <c r="AF453" s="104"/>
       <c r="AG453" s="104"/>
     </row>
-    <row r="454" spans="1:33" ht="11.45" customHeight="1">
+    <row r="454" spans="1:33" ht="11.5" customHeight="1">
       <c r="A454" s="207"/>
       <c r="B454" s="207"/>
       <c r="C454" s="367"/>
@@ -37323,7 +37327,7 @@
       <c r="AF454" s="106"/>
       <c r="AG454" s="106"/>
     </row>
-    <row r="455" spans="1:33" ht="11.45" customHeight="1">
+    <row r="455" spans="1:33" ht="11.5" customHeight="1">
       <c r="A455" s="206"/>
       <c r="B455" s="206"/>
       <c r="C455" s="381"/>
@@ -37356,7 +37360,7 @@
       <c r="AF455" s="78"/>
       <c r="AG455" s="78"/>
     </row>
-    <row r="456" spans="1:33" ht="11.45" customHeight="1">
+    <row r="456" spans="1:33" ht="11.5" customHeight="1">
       <c r="A456" s="204"/>
       <c r="B456" s="204"/>
       <c r="C456" s="379"/>
@@ -37389,7 +37393,7 @@
       <c r="AF456" s="88"/>
       <c r="AG456" s="88"/>
     </row>
-    <row r="457" spans="1:33" ht="11.45" customHeight="1">
+    <row r="457" spans="1:33" ht="11.5" customHeight="1">
       <c r="A457" s="203"/>
       <c r="B457" s="203"/>
       <c r="C457" s="376"/>
@@ -37422,7 +37426,7 @@
       <c r="AF457" s="56"/>
       <c r="AG457" s="56"/>
     </row>
-    <row r="458" spans="1:33" ht="11.45" customHeight="1">
+    <row r="458" spans="1:33" ht="11.5" customHeight="1">
       <c r="A458" s="214"/>
       <c r="B458" s="214"/>
       <c r="C458" s="377"/>
@@ -37455,7 +37459,7 @@
       <c r="AF458" s="81"/>
       <c r="AG458" s="81"/>
     </row>
-    <row r="459" spans="1:33" ht="11.45" customHeight="1">
+    <row r="459" spans="1:33" ht="11.5" customHeight="1">
       <c r="A459" s="209"/>
       <c r="B459" s="209"/>
       <c r="C459" s="365"/>
@@ -37488,7 +37492,7 @@
       <c r="AF459" s="102"/>
       <c r="AG459" s="102"/>
     </row>
-    <row r="460" spans="1:33" ht="11.45" customHeight="1">
+    <row r="460" spans="1:33" ht="11.5" customHeight="1">
       <c r="A460" s="205"/>
       <c r="B460" s="205"/>
       <c r="C460" s="366"/>
@@ -37521,7 +37525,7 @@
       <c r="AF460" s="104"/>
       <c r="AG460" s="104"/>
     </row>
-    <row r="461" spans="1:33" ht="11.45" customHeight="1">
+    <row r="461" spans="1:33" ht="11.5" customHeight="1">
       <c r="A461" s="207"/>
       <c r="B461" s="207"/>
       <c r="C461" s="367"/>
@@ -37554,7 +37558,7 @@
       <c r="AF461" s="106"/>
       <c r="AG461" s="106"/>
     </row>
-    <row r="462" spans="1:33" ht="11.45" customHeight="1">
+    <row r="462" spans="1:33" ht="11.5" customHeight="1">
       <c r="A462" s="206"/>
       <c r="B462" s="206"/>
       <c r="C462" s="381"/>
@@ -37587,7 +37591,7 @@
       <c r="AF462" s="78"/>
       <c r="AG462" s="78"/>
     </row>
-    <row r="463" spans="1:33" ht="11.45" customHeight="1">
+    <row r="463" spans="1:33" ht="11.5" customHeight="1">
       <c r="A463" s="204"/>
       <c r="B463" s="204"/>
       <c r="C463" s="379"/>
@@ -37620,7 +37624,7 @@
       <c r="AF463" s="88"/>
       <c r="AG463" s="88"/>
     </row>
-    <row r="464" spans="1:33" ht="11.45" customHeight="1">
+    <row r="464" spans="1:33" ht="11.5" customHeight="1">
       <c r="A464" s="203"/>
       <c r="B464" s="203"/>
       <c r="C464" s="376"/>
@@ -37653,7 +37657,7 @@
       <c r="AF464" s="56"/>
       <c r="AG464" s="56"/>
     </row>
-    <row r="465" spans="1:33" ht="11.45" customHeight="1">
+    <row r="465" spans="1:33" ht="11.5" customHeight="1">
       <c r="A465" s="214"/>
       <c r="B465" s="214"/>
       <c r="C465" s="377"/>
@@ -37686,7 +37690,7 @@
       <c r="AF465" s="81"/>
       <c r="AG465" s="81"/>
     </row>
-    <row r="466" spans="1:33" ht="11.45" customHeight="1">
+    <row r="466" spans="1:33" ht="11.5" customHeight="1">
       <c r="A466" s="209"/>
       <c r="B466" s="209"/>
       <c r="C466" s="365"/>
@@ -37719,7 +37723,7 @@
       <c r="AF466" s="102"/>
       <c r="AG466" s="102"/>
     </row>
-    <row r="467" spans="1:33" ht="11.45" customHeight="1">
+    <row r="467" spans="1:33" ht="11.5" customHeight="1">
       <c r="A467" s="205"/>
       <c r="B467" s="205"/>
       <c r="C467" s="366"/>
@@ -37752,7 +37756,7 @@
       <c r="AF467" s="104"/>
       <c r="AG467" s="104"/>
     </row>
-    <row r="468" spans="1:33" ht="11.45" customHeight="1">
+    <row r="468" spans="1:33" ht="11.5" customHeight="1">
       <c r="A468" s="207"/>
       <c r="B468" s="207"/>
       <c r="C468" s="367"/>
@@ -37785,7 +37789,7 @@
       <c r="AF468" s="106"/>
       <c r="AG468" s="106"/>
     </row>
-    <row r="469" spans="1:33" ht="11.45" customHeight="1">
+    <row r="469" spans="1:33" ht="11.5" customHeight="1">
       <c r="A469" s="206"/>
       <c r="B469" s="206"/>
       <c r="C469" s="381"/>
@@ -37818,7 +37822,7 @@
       <c r="AF469" s="78"/>
       <c r="AG469" s="78"/>
     </row>
-    <row r="470" spans="1:33" ht="11.45" customHeight="1">
+    <row r="470" spans="1:33" ht="11.5" customHeight="1">
       <c r="A470" s="204"/>
       <c r="B470" s="204"/>
       <c r="C470" s="379"/>
@@ -37851,7 +37855,7 @@
       <c r="AF470" s="88"/>
       <c r="AG470" s="88"/>
     </row>
-    <row r="471" spans="1:33" ht="11.45" customHeight="1">
+    <row r="471" spans="1:33" ht="11.5" customHeight="1">
       <c r="A471" s="203"/>
       <c r="B471" s="203"/>
       <c r="C471" s="376"/>
@@ -37884,7 +37888,7 @@
       <c r="AF471" s="56"/>
       <c r="AG471" s="56"/>
     </row>
-    <row r="472" spans="1:33" ht="11.45" customHeight="1">
+    <row r="472" spans="1:33" ht="11.5" customHeight="1">
       <c r="A472" s="214"/>
       <c r="B472" s="214"/>
       <c r="C472" s="377"/>
@@ -37917,7 +37921,7 @@
       <c r="AF472" s="81"/>
       <c r="AG472" s="81"/>
     </row>
-    <row r="473" spans="1:33" ht="11.45" customHeight="1">
+    <row r="473" spans="1:33" ht="11.5" customHeight="1">
       <c r="A473" s="209"/>
       <c r="B473" s="209"/>
       <c r="C473" s="365"/>
@@ -37950,7 +37954,7 @@
       <c r="AF473" s="102"/>
       <c r="AG473" s="102"/>
     </row>
-    <row r="474" spans="1:33" ht="11.45" customHeight="1">
+    <row r="474" spans="1:33" ht="11.5" customHeight="1">
       <c r="A474" s="205"/>
       <c r="B474" s="205"/>
       <c r="C474" s="366"/>
@@ -37983,7 +37987,7 @@
       <c r="AF474" s="104"/>
       <c r="AG474" s="104"/>
     </row>
-    <row r="475" spans="1:33" ht="11.45" customHeight="1">
+    <row r="475" spans="1:33" ht="11.5" customHeight="1">
       <c r="A475" s="207"/>
       <c r="B475" s="207"/>
       <c r="C475" s="367"/>
@@ -38016,7 +38020,7 @@
       <c r="AF475" s="106"/>
       <c r="AG475" s="106"/>
     </row>
-    <row r="476" spans="1:33" ht="11.45" customHeight="1">
+    <row r="476" spans="1:33" ht="11.5" customHeight="1">
       <c r="A476" s="206"/>
       <c r="B476" s="206"/>
       <c r="C476" s="381"/>
@@ -38049,7 +38053,7 @@
       <c r="AF476" s="78"/>
       <c r="AG476" s="78"/>
     </row>
-    <row r="477" spans="1:33" ht="11.45" customHeight="1">
+    <row r="477" spans="1:33" ht="11.5" customHeight="1">
       <c r="A477" s="204"/>
       <c r="B477" s="204"/>
       <c r="C477" s="379"/>
@@ -38082,7 +38086,7 @@
       <c r="AF477" s="88"/>
       <c r="AG477" s="88"/>
     </row>
-    <row r="478" spans="1:33" ht="11.45" customHeight="1">
+    <row r="478" spans="1:33" ht="11.5" customHeight="1">
       <c r="A478" s="203"/>
       <c r="B478" s="203"/>
       <c r="C478" s="376"/>
@@ -38115,7 +38119,7 @@
       <c r="AF478" s="56"/>
       <c r="AG478" s="56"/>
     </row>
-    <row r="479" spans="1:33" ht="11.45" customHeight="1">
+    <row r="479" spans="1:33" ht="11.5" customHeight="1">
       <c r="A479" s="214"/>
       <c r="B479" s="214"/>
       <c r="C479" s="377"/>
@@ -38148,7 +38152,7 @@
       <c r="AF479" s="81"/>
       <c r="AG479" s="81"/>
     </row>
-    <row r="480" spans="1:33" ht="11.45" customHeight="1">
+    <row r="480" spans="1:33" ht="11.5" customHeight="1">
       <c r="A480" s="209"/>
       <c r="B480" s="209"/>
       <c r="C480" s="365"/>
@@ -38181,7 +38185,7 @@
       <c r="AF480" s="102"/>
       <c r="AG480" s="102"/>
     </row>
-    <row r="481" spans="1:33" ht="11.45" customHeight="1">
+    <row r="481" spans="1:33" ht="11.5" customHeight="1">
       <c r="A481" s="205"/>
       <c r="B481" s="205"/>
       <c r="C481" s="366"/>
@@ -38214,7 +38218,7 @@
       <c r="AF481" s="104"/>
       <c r="AG481" s="104"/>
     </row>
-    <row r="482" spans="1:33" ht="11.45" customHeight="1">
+    <row r="482" spans="1:33" ht="11.5" customHeight="1">
       <c r="A482" s="207"/>
       <c r="B482" s="207"/>
       <c r="C482" s="367"/>
@@ -38247,7 +38251,7 @@
       <c r="AF482" s="106"/>
       <c r="AG482" s="106"/>
     </row>
-    <row r="483" spans="1:33" ht="11.45" customHeight="1">
+    <row r="483" spans="1:33" ht="11.5" customHeight="1">
       <c r="A483" s="206"/>
       <c r="B483" s="206"/>
       <c r="C483" s="381"/>
@@ -38280,7 +38284,7 @@
       <c r="AF483" s="78"/>
       <c r="AG483" s="78"/>
     </row>
-    <row r="484" spans="1:33" ht="11.45" customHeight="1">
+    <row r="484" spans="1:33" ht="11.5" customHeight="1">
       <c r="A484" s="204"/>
       <c r="B484" s="204"/>
       <c r="C484" s="379"/>
@@ -38313,7 +38317,7 @@
       <c r="AF484" s="88"/>
       <c r="AG484" s="88"/>
     </row>
-    <row r="485" spans="1:33" ht="11.45" customHeight="1">
+    <row r="485" spans="1:33" ht="11.5" customHeight="1">
       <c r="A485" s="203"/>
       <c r="B485" s="203"/>
       <c r="C485" s="376"/>
@@ -38346,7 +38350,7 @@
       <c r="AF485" s="56"/>
       <c r="AG485" s="56"/>
     </row>
-    <row r="486" spans="1:33" ht="11.45" customHeight="1">
+    <row r="486" spans="1:33" ht="11.5" customHeight="1">
       <c r="A486" s="214"/>
       <c r="B486" s="214"/>
       <c r="C486" s="377"/>
@@ -38379,7 +38383,7 @@
       <c r="AF486" s="81"/>
       <c r="AG486" s="81"/>
     </row>
-    <row r="487" spans="1:33" ht="11.45" customHeight="1">
+    <row r="487" spans="1:33" ht="11.5" customHeight="1">
       <c r="A487" s="209"/>
       <c r="B487" s="209"/>
       <c r="C487" s="365"/>
@@ -38412,7 +38416,7 @@
       <c r="AF487" s="102"/>
       <c r="AG487" s="102"/>
     </row>
-    <row r="488" spans="1:33" ht="11.45" customHeight="1">
+    <row r="488" spans="1:33" ht="11.5" customHeight="1">
       <c r="A488" s="205"/>
       <c r="B488" s="205"/>
       <c r="C488" s="366"/>
@@ -38445,7 +38449,7 @@
       <c r="AF488" s="104"/>
       <c r="AG488" s="104"/>
     </row>
-    <row r="489" spans="1:33" ht="11.45" customHeight="1">
+    <row r="489" spans="1:33" ht="11.5" customHeight="1">
       <c r="A489" s="207"/>
       <c r="B489" s="207"/>
       <c r="C489" s="367"/>
@@ -38478,7 +38482,7 @@
       <c r="AF489" s="106"/>
       <c r="AG489" s="106"/>
     </row>
-    <row r="490" spans="1:33" ht="11.45" customHeight="1">
+    <row r="490" spans="1:33" ht="11.5" customHeight="1">
       <c r="A490" s="206"/>
       <c r="B490" s="206"/>
       <c r="C490" s="381"/>
@@ -38511,7 +38515,7 @@
       <c r="AF490" s="78"/>
       <c r="AG490" s="78"/>
     </row>
-    <row r="491" spans="1:33" ht="11.45" customHeight="1">
+    <row r="491" spans="1:33" ht="11.5" customHeight="1">
       <c r="A491" s="204"/>
       <c r="B491" s="204"/>
       <c r="C491" s="379"/>
@@ -38544,7 +38548,7 @@
       <c r="AF491" s="88"/>
       <c r="AG491" s="88"/>
     </row>
-    <row r="492" spans="1:33" ht="11.45" customHeight="1">
+    <row r="492" spans="1:33" ht="11.5" customHeight="1">
       <c r="A492" s="203"/>
       <c r="B492" s="203"/>
       <c r="C492" s="376"/>
@@ -38577,7 +38581,7 @@
       <c r="AF492" s="56"/>
       <c r="AG492" s="56"/>
     </row>
-    <row r="493" spans="1:33" ht="11.45" customHeight="1">
+    <row r="493" spans="1:33" ht="11.5" customHeight="1">
       <c r="A493" s="214"/>
       <c r="B493" s="214"/>
       <c r="C493" s="377"/>
@@ -38610,7 +38614,7 @@
       <c r="AF493" s="81"/>
       <c r="AG493" s="81"/>
     </row>
-    <row r="494" spans="1:33" ht="11.45" customHeight="1">
+    <row r="494" spans="1:33" ht="11.5" customHeight="1">
       <c r="A494" s="209"/>
       <c r="B494" s="209"/>
       <c r="C494" s="365"/>
@@ -38643,7 +38647,7 @@
       <c r="AF494" s="102"/>
       <c r="AG494" s="102"/>
     </row>
-    <row r="495" spans="1:33" ht="11.45" customHeight="1">
+    <row r="495" spans="1:33" ht="11.5" customHeight="1">
       <c r="A495" s="205"/>
       <c r="B495" s="205"/>
       <c r="C495" s="366"/>
@@ -38676,7 +38680,7 @@
       <c r="AF495" s="104"/>
       <c r="AG495" s="104"/>
     </row>
-    <row r="496" spans="1:33" ht="11.45" customHeight="1">
+    <row r="496" spans="1:33" ht="11.5" customHeight="1">
       <c r="A496" s="207"/>
       <c r="B496" s="207"/>
       <c r="C496" s="367"/>
@@ -38709,7 +38713,7 @@
       <c r="AF496" s="106"/>
       <c r="AG496" s="106"/>
     </row>
-    <row r="497" spans="1:33" ht="11.45" customHeight="1">
+    <row r="497" spans="1:33" ht="11.5" customHeight="1">
       <c r="A497" s="206"/>
       <c r="B497" s="206"/>
       <c r="C497" s="381"/>
@@ -38742,7 +38746,7 @@
       <c r="AF497" s="78"/>
       <c r="AG497" s="78"/>
     </row>
-    <row r="498" spans="1:33" ht="11.45" customHeight="1">
+    <row r="498" spans="1:33" ht="11.5" customHeight="1">
       <c r="A498" s="204"/>
       <c r="B498" s="204"/>
       <c r="C498" s="379"/>
@@ -38775,7 +38779,7 @@
       <c r="AF498" s="88"/>
       <c r="AG498" s="88"/>
     </row>
-    <row r="499" spans="1:33" ht="11.45" customHeight="1">
+    <row r="499" spans="1:33" ht="11.5" customHeight="1">
       <c r="A499" s="203"/>
       <c r="B499" s="203"/>
       <c r="C499" s="376"/>
@@ -38808,7 +38812,7 @@
       <c r="AF499" s="56"/>
       <c r="AG499" s="56"/>
     </row>
-    <row r="500" spans="1:33" ht="11.45" customHeight="1">
+    <row r="500" spans="1:33" ht="11.5" customHeight="1">
       <c r="A500" s="214"/>
       <c r="B500" s="214"/>
       <c r="C500" s="377"/>
@@ -38841,7 +38845,7 @@
       <c r="AF500" s="81"/>
       <c r="AG500" s="81"/>
     </row>
-    <row r="501" spans="1:33" ht="11.45" customHeight="1">
+    <row r="501" spans="1:33" ht="11.5" customHeight="1">
       <c r="A501" s="209"/>
       <c r="B501" s="209"/>
       <c r="C501" s="365"/>
@@ -38874,7 +38878,7 @@
       <c r="AF501" s="102"/>
       <c r="AG501" s="102"/>
     </row>
-    <row r="502" spans="1:33" ht="11.45" customHeight="1">
+    <row r="502" spans="1:33" ht="11.5" customHeight="1">
       <c r="A502" s="205"/>
       <c r="B502" s="205"/>
       <c r="C502" s="366"/>
@@ -38907,7 +38911,7 @@
       <c r="AF502" s="104"/>
       <c r="AG502" s="104"/>
     </row>
-    <row r="503" spans="1:33" ht="11.45" customHeight="1">
+    <row r="503" spans="1:33" ht="11.5" customHeight="1">
       <c r="A503" s="207"/>
       <c r="B503" s="207"/>
       <c r="C503" s="367"/>
@@ -38940,7 +38944,7 @@
       <c r="AF503" s="106"/>
       <c r="AG503" s="106"/>
     </row>
-    <row r="504" spans="1:33" ht="11.45" customHeight="1">
+    <row r="504" spans="1:33" ht="11.5" customHeight="1">
       <c r="A504" s="206"/>
       <c r="B504" s="206"/>
       <c r="C504" s="381"/>
@@ -38973,7 +38977,7 @@
       <c r="AF504" s="78"/>
       <c r="AG504" s="78"/>
     </row>
-    <row r="505" spans="1:33" ht="11.45" customHeight="1">
+    <row r="505" spans="1:33" ht="11.5" customHeight="1">
       <c r="A505" s="204"/>
       <c r="B505" s="204"/>
       <c r="C505" s="379"/>
@@ -39006,7 +39010,7 @@
       <c r="AF505" s="88"/>
       <c r="AG505" s="88"/>
     </row>
-    <row r="506" spans="1:33" ht="11.45" customHeight="1">
+    <row r="506" spans="1:33" ht="11.5" customHeight="1">
       <c r="A506" s="203"/>
       <c r="B506" s="203"/>
       <c r="C506" s="376"/>
@@ -39039,7 +39043,7 @@
       <c r="AF506" s="56"/>
       <c r="AG506" s="56"/>
     </row>
-    <row r="507" spans="1:33" ht="11.45" customHeight="1">
+    <row r="507" spans="1:33" ht="11.5" customHeight="1">
       <c r="A507" s="214"/>
       <c r="B507" s="214"/>
       <c r="C507" s="377"/>
@@ -39072,7 +39076,7 @@
       <c r="AF507" s="81"/>
       <c r="AG507" s="81"/>
     </row>
-    <row r="508" spans="1:33" ht="11.45" customHeight="1">
+    <row r="508" spans="1:33" ht="11.5" customHeight="1">
       <c r="A508" s="209"/>
       <c r="B508" s="209"/>
       <c r="C508" s="365"/>
@@ -39105,7 +39109,7 @@
       <c r="AF508" s="102"/>
       <c r="AG508" s="102"/>
     </row>
-    <row r="509" spans="1:33" ht="11.45" customHeight="1">
+    <row r="509" spans="1:33" ht="11.5" customHeight="1">
       <c r="A509" s="205"/>
       <c r="B509" s="205"/>
       <c r="C509" s="366"/>
@@ -39138,7 +39142,7 @@
       <c r="AF509" s="104"/>
       <c r="AG509" s="104"/>
     </row>
-    <row r="510" spans="1:33" ht="11.45" customHeight="1">
+    <row r="510" spans="1:33" ht="11.5" customHeight="1">
       <c r="A510" s="207"/>
       <c r="B510" s="207"/>
       <c r="C510" s="367"/>
@@ -39171,7 +39175,7 @@
       <c r="AF510" s="106"/>
       <c r="AG510" s="106"/>
     </row>
-    <row r="511" spans="1:33" ht="11.45" customHeight="1">
+    <row r="511" spans="1:33" ht="11.5" customHeight="1">
       <c r="A511" s="206"/>
       <c r="B511" s="206"/>
       <c r="C511" s="381"/>
@@ -39204,7 +39208,7 @@
       <c r="AF511" s="78"/>
       <c r="AG511" s="78"/>
     </row>
-    <row r="512" spans="1:33" ht="11.45" customHeight="1">
+    <row r="512" spans="1:33" ht="11.5" customHeight="1">
       <c r="A512" s="204"/>
       <c r="B512" s="204"/>
       <c r="C512" s="379"/>
@@ -39237,7 +39241,7 @@
       <c r="AF512" s="88"/>
       <c r="AG512" s="88"/>
     </row>
-    <row r="513" spans="1:33" ht="11.45" customHeight="1">
+    <row r="513" spans="1:33" ht="11.5" customHeight="1">
       <c r="A513" s="203"/>
       <c r="B513" s="203"/>
       <c r="C513" s="376"/>
@@ -39270,7 +39274,7 @@
       <c r="AF513" s="56"/>
       <c r="AG513" s="56"/>
     </row>
-    <row r="514" spans="1:33" ht="11.45" customHeight="1">
+    <row r="514" spans="1:33" ht="11.5" customHeight="1">
       <c r="A514" s="214"/>
       <c r="B514" s="214"/>
       <c r="C514" s="377"/>
@@ -39303,7 +39307,7 @@
       <c r="AF514" s="81"/>
       <c r="AG514" s="81"/>
     </row>
-    <row r="515" spans="1:33" ht="11.45" customHeight="1">
+    <row r="515" spans="1:33" ht="11.5" customHeight="1">
       <c r="A515" s="209"/>
       <c r="B515" s="209"/>
       <c r="C515" s="365"/>
@@ -39336,7 +39340,7 @@
       <c r="AF515" s="102"/>
       <c r="AG515" s="102"/>
     </row>
-    <row r="516" spans="1:33" ht="11.45" customHeight="1">
+    <row r="516" spans="1:33" ht="11.5" customHeight="1">
       <c r="A516" s="205"/>
       <c r="B516" s="205"/>
       <c r="C516" s="366"/>
@@ -39369,7 +39373,7 @@
       <c r="AF516" s="104"/>
       <c r="AG516" s="104"/>
     </row>
-    <row r="517" spans="1:33" ht="11.45" customHeight="1">
+    <row r="517" spans="1:33" ht="11.5" customHeight="1">
       <c r="A517" s="207"/>
       <c r="B517" s="207"/>
       <c r="C517" s="367"/>
@@ -39402,7 +39406,7 @@
       <c r="AF517" s="106"/>
       <c r="AG517" s="106"/>
     </row>
-    <row r="518" spans="1:33" ht="11.45" customHeight="1">
+    <row r="518" spans="1:33" ht="11.5" customHeight="1">
       <c r="A518" s="206"/>
       <c r="B518" s="206"/>
       <c r="C518" s="381"/>
@@ -39435,7 +39439,7 @@
       <c r="AF518" s="78"/>
       <c r="AG518" s="78"/>
     </row>
-    <row r="519" spans="1:33" ht="11.45" customHeight="1">
+    <row r="519" spans="1:33" ht="11.5" customHeight="1">
       <c r="A519" s="204"/>
       <c r="B519" s="204"/>
       <c r="C519" s="379"/>
@@ -39468,7 +39472,7 @@
       <c r="AF519" s="88"/>
       <c r="AG519" s="88"/>
     </row>
-    <row r="520" spans="1:33" ht="11.45" customHeight="1">
+    <row r="520" spans="1:33" ht="11.5" customHeight="1">
       <c r="A520" s="203"/>
       <c r="B520" s="203"/>
       <c r="C520" s="376"/>
@@ -39501,7 +39505,7 @@
       <c r="AF520" s="56"/>
       <c r="AG520" s="56"/>
     </row>
-    <row r="521" spans="1:33" ht="11.45" customHeight="1">
+    <row r="521" spans="1:33" ht="11.5" customHeight="1">
       <c r="A521" s="214"/>
       <c r="B521" s="214"/>
       <c r="C521" s="377"/>
@@ -39534,7 +39538,7 @@
       <c r="AF521" s="81"/>
       <c r="AG521" s="81"/>
     </row>
-    <row r="522" spans="1:33" ht="11.45" customHeight="1">
+    <row r="522" spans="1:33" ht="11.5" customHeight="1">
       <c r="A522" s="209"/>
       <c r="B522" s="209"/>
       <c r="C522" s="365"/>
@@ -39567,7 +39571,7 @@
       <c r="AF522" s="102"/>
       <c r="AG522" s="102"/>
     </row>
-    <row r="523" spans="1:33" ht="11.45" customHeight="1">
+    <row r="523" spans="1:33" ht="11.5" customHeight="1">
       <c r="A523" s="205"/>
       <c r="B523" s="205"/>
       <c r="C523" s="366"/>
@@ -39600,7 +39604,7 @@
       <c r="AF523" s="104"/>
       <c r="AG523" s="104"/>
     </row>
-    <row r="524" spans="1:33" ht="11.45" customHeight="1">
+    <row r="524" spans="1:33" ht="11.5" customHeight="1">
       <c r="A524" s="207"/>
       <c r="B524" s="207"/>
       <c r="C524" s="367"/>
@@ -39633,7 +39637,7 @@
       <c r="AF524" s="106"/>
       <c r="AG524" s="106"/>
     </row>
-    <row r="525" spans="1:33" ht="11.45" customHeight="1">
+    <row r="525" spans="1:33" ht="11.5" customHeight="1">
       <c r="A525" s="206"/>
       <c r="B525" s="206"/>
       <c r="C525" s="381"/>
@@ -39666,7 +39670,7 @@
       <c r="AF525" s="78"/>
       <c r="AG525" s="78"/>
     </row>
-    <row r="526" spans="1:33" ht="11.45" customHeight="1">
+    <row r="526" spans="1:33" ht="11.5" customHeight="1">
       <c r="A526" s="204"/>
       <c r="B526" s="204"/>
       <c r="C526" s="379"/>
@@ -39699,7 +39703,7 @@
       <c r="AF526" s="88"/>
       <c r="AG526" s="88"/>
     </row>
-    <row r="527" spans="1:33" ht="11.45" customHeight="1">
+    <row r="527" spans="1:33" ht="11.5" customHeight="1">
       <c r="A527" s="203"/>
       <c r="B527" s="203"/>
       <c r="C527" s="376"/>
@@ -39732,7 +39736,7 @@
       <c r="AF527" s="56"/>
       <c r="AG527" s="56"/>
     </row>
-    <row r="528" spans="1:33" ht="11.45" customHeight="1">
+    <row r="528" spans="1:33" ht="11.5" customHeight="1">
       <c r="A528" s="214"/>
       <c r="B528" s="214"/>
       <c r="C528" s="377"/>
@@ -39765,7 +39769,7 @@
       <c r="AF528" s="81"/>
       <c r="AG528" s="81"/>
     </row>
-    <row r="529" spans="1:33" ht="11.45" customHeight="1">
+    <row r="529" spans="1:33" ht="11.5" customHeight="1">
       <c r="A529" s="209"/>
       <c r="B529" s="209"/>
       <c r="C529" s="365"/>
@@ -39798,7 +39802,7 @@
       <c r="AF529" s="102"/>
       <c r="AG529" s="102"/>
     </row>
-    <row r="530" spans="1:33" ht="11.45" customHeight="1">
+    <row r="530" spans="1:33" ht="11.5" customHeight="1">
       <c r="A530" s="205"/>
       <c r="B530" s="205"/>
       <c r="C530" s="366"/>
@@ -39831,7 +39835,7 @@
       <c r="AF530" s="104"/>
       <c r="AG530" s="104"/>
     </row>
-    <row r="531" spans="1:33" ht="11.45" customHeight="1">
+    <row r="531" spans="1:33" ht="11.5" customHeight="1">
       <c r="A531" s="207"/>
       <c r="B531" s="207"/>
       <c r="C531" s="367"/>
@@ -39864,7 +39868,7 @@
       <c r="AF531" s="106"/>
       <c r="AG531" s="106"/>
     </row>
-    <row r="532" spans="1:33" ht="11.45" customHeight="1">
+    <row r="532" spans="1:33" ht="11.5" customHeight="1">
       <c r="A532" s="206"/>
       <c r="B532" s="206"/>
       <c r="C532" s="381"/>
@@ -39897,7 +39901,7 @@
       <c r="AF532" s="78"/>
       <c r="AG532" s="78"/>
     </row>
-    <row r="533" spans="1:33" ht="11.45" customHeight="1">
+    <row r="533" spans="1:33" ht="11.5" customHeight="1">
       <c r="A533" s="204"/>
       <c r="B533" s="204"/>
       <c r="C533" s="379"/>
@@ -39954,37 +39958,37 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AU142"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="5.140625" customWidth="1"/>
-    <col min="3" max="4" width="4.5703125" customWidth="1"/>
-    <col min="5" max="5" width="4.140625" customWidth="1"/>
-    <col min="6" max="6" width="2.42578125" customWidth="1"/>
-    <col min="7" max="7" width="4.42578125" customWidth="1"/>
-    <col min="8" max="8" width="51.7109375" customWidth="1"/>
+    <col min="1" max="2" width="5.1796875" customWidth="1"/>
+    <col min="3" max="4" width="4.54296875" customWidth="1"/>
+    <col min="5" max="5" width="4.1796875" customWidth="1"/>
+    <col min="6" max="6" width="2.453125" customWidth="1"/>
+    <col min="7" max="7" width="4.453125" customWidth="1"/>
+    <col min="8" max="8" width="51.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="8:15" ht="12.6" customHeight="1">
+    <row r="1" spans="8:15" ht="12.65" customHeight="1">
       <c r="H1" s="5" t="s">
         <v>2391</v>
       </c>
     </row>
-    <row r="2" spans="8:15" ht="12.6" customHeight="1">
+    <row r="2" spans="8:15" ht="12.65" customHeight="1">
       <c r="H2" s="20" t="s">
         <v>2392</v>
       </c>
     </row>
-    <row r="3" spans="8:15" ht="12.6" customHeight="1">
+    <row r="3" spans="8:15" ht="12.65" customHeight="1">
       <c r="H3" s="20" t="s">
         <v>2393</v>
       </c>
     </row>
-    <row r="4" spans="8:15" ht="12.6" customHeight="1">
+    <row r="4" spans="8:15" ht="12.65" customHeight="1">
       <c r="H4" s="21" t="s">
         <v>2394</v>
       </c>
     </row>
-    <row r="5" spans="8:15" ht="12.6" customHeight="1">
+    <row r="5" spans="8:15" ht="12.65" customHeight="1">
       <c r="H5" s="6" t="s">
         <v>2395</v>
       </c>
@@ -40008,7 +40012,7 @@
         <v>2399</v>
       </c>
     </row>
-    <row r="6" spans="8:15" ht="12.6" customHeight="1">
+    <row r="6" spans="8:15" ht="12.65" customHeight="1">
       <c r="H6" s="6" t="s">
         <v>2400</v>
       </c>
@@ -40100,7 +40104,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="8:15" ht="12.6" customHeight="1">
+    <row r="10" spans="8:15" ht="12.65" customHeight="1">
       <c r="H10" s="5" t="s">
         <v>2412</v>
       </c>
@@ -41325,7 +41329,7 @@
       <c r="AT41" s="39"/>
       <c r="AU41" s="39"/>
     </row>
-    <row r="42" spans="1:47" s="75" customFormat="1" ht="11.45" customHeight="1">
+    <row r="42" spans="1:47" s="75" customFormat="1" ht="11.5" customHeight="1">
       <c r="A42" s="265"/>
       <c r="B42" s="206"/>
       <c r="C42" s="381"/>
@@ -41654,7 +41658,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="70" spans="8:27" ht="11.45" customHeight="1">
+    <row r="70" spans="8:27" ht="11.5" customHeight="1">
       <c r="H70" t="s">
         <v>2623</v>
       </c>
@@ -42455,7 +42459,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="8:27" ht="11.45" customHeight="1">
+    <row r="100" spans="8:27" ht="11.5" customHeight="1">
       <c r="H100" t="s">
         <v>2767</v>
       </c>
@@ -42487,7 +42491,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="101" spans="8:27" ht="11.45" customHeight="1">
+    <row r="101" spans="8:27" ht="11.5" customHeight="1">
       <c r="H101" t="s">
         <v>2774</v>
       </c>
@@ -42510,7 +42514,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="102" spans="8:27" ht="11.45" customHeight="1">
+    <row r="102" spans="8:27" ht="11.5" customHeight="1">
       <c r="H102" t="s">
         <v>2779</v>
       </c>
@@ -42530,7 +42534,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="103" spans="8:27" ht="11.45" customHeight="1">
+    <row r="103" spans="8:27" ht="11.5" customHeight="1">
       <c r="H103" t="s">
         <v>2783</v>
       </c>
@@ -42553,7 +42557,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="104" spans="8:27" ht="11.45" customHeight="1">
+    <row r="104" spans="8:27" ht="11.5" customHeight="1">
       <c r="H104" t="s">
         <v>2482</v>
       </c>
@@ -42809,7 +42813,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="115" spans="8:27" ht="11.45" customHeight="1">
+    <row r="115" spans="8:27" ht="11.5" customHeight="1">
       <c r="H115" t="s">
         <v>2830</v>
       </c>
@@ -42832,7 +42836,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="116" spans="8:27" ht="11.45" customHeight="1">
+    <row r="116" spans="8:27" ht="11.5" customHeight="1">
       <c r="H116" t="s">
         <v>2834</v>
       </c>
@@ -42855,7 +42859,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="117" spans="8:27" ht="11.45" customHeight="1">
+    <row r="117" spans="8:27" ht="11.5" customHeight="1">
       <c r="H117" t="s">
         <v>2838</v>
       </c>
@@ -42887,7 +42891,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="118" spans="8:27" ht="11.45" customHeight="1">
+    <row r="118" spans="8:27" ht="11.5" customHeight="1">
       <c r="H118" t="s">
         <v>2846</v>
       </c>
@@ -42919,7 +42923,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="119" spans="8:27" ht="11.45" customHeight="1">
+    <row r="119" spans="8:27" ht="11.5" customHeight="1">
       <c r="H119" t="s">
         <v>2854</v>
       </c>
@@ -42951,7 +42955,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="120" spans="8:27" ht="11.45" customHeight="1">
+    <row r="120" spans="8:27" ht="11.5" customHeight="1">
       <c r="H120" t="s">
         <v>2862</v>
       </c>
@@ -42980,7 +42984,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="121" spans="8:27" ht="11.45" customHeight="1">
+    <row r="121" spans="8:27" ht="11.5" customHeight="1">
       <c r="H121" t="s">
         <v>2868</v>
       </c>
@@ -43006,7 +43010,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="122" spans="8:27" ht="11.45" customHeight="1">
+    <row r="122" spans="8:27" ht="11.5" customHeight="1">
       <c r="H122" t="s">
         <v>2873</v>
       </c>
@@ -43304,7 +43308,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="133" spans="1:33" s="75" customFormat="1" ht="11.45" customHeight="1">
+    <row r="133" spans="1:33" s="75" customFormat="1" ht="11.5" customHeight="1">
       <c r="A133" s="214">
         <v>46079</v>
       </c>
@@ -43699,23 +43703,23 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:C224"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="30" style="69" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="142.5703125" style="70" customWidth="1"/>
-    <col min="3" max="3" width="41.42578125" style="28" customWidth="1"/>
-    <col min="4" max="10" width="14.42578125" style="28" customWidth="1"/>
-    <col min="11" max="16384" width="14.42578125" style="28"/>
+    <col min="2" max="2" width="142.54296875" style="70" customWidth="1"/>
+    <col min="3" max="3" width="41.453125" style="28" customWidth="1"/>
+    <col min="4" max="10" width="14.453125" style="28" customWidth="1"/>
+    <col min="11" max="16384" width="14.453125" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="12.95" customHeight="1">
+    <row r="1" spans="1:3" ht="13" customHeight="1">
       <c r="A1" s="27" t="s">
         <v>2982</v>
       </c>
       <c r="B1" s="58"/>
       <c r="C1" s="59"/>
     </row>
-    <row r="2" spans="1:3" s="63" customFormat="1" ht="12.95" customHeight="1">
+    <row r="2" spans="1:3" s="63" customFormat="1" ht="13" customHeight="1">
       <c r="A2" s="60" t="s">
         <v>2983</v>
       </c>
@@ -43724,7 +43728,7 @@
       </c>
       <c r="C2" s="62"/>
     </row>
-    <row r="3" spans="1:3" ht="12.95" customHeight="1">
+    <row r="3" spans="1:3" ht="13" customHeight="1">
       <c r="A3" s="215" t="s">
         <v>144</v>
       </c>
@@ -43733,7 +43737,7 @@
       </c>
       <c r="C3" s="59"/>
     </row>
-    <row r="4" spans="1:3" ht="12.95" customHeight="1">
+    <row r="4" spans="1:3" ht="13" customHeight="1">
       <c r="A4" s="27" t="s">
         <v>2986</v>
       </c>
@@ -43742,7 +43746,7 @@
       </c>
       <c r="C4" s="59"/>
     </row>
-    <row r="5" spans="1:3" ht="12.95" customHeight="1">
+    <row r="5" spans="1:3" ht="13" customHeight="1">
       <c r="A5" s="27" t="s">
         <v>763</v>
       </c>
@@ -43751,7 +43755,7 @@
       </c>
       <c r="C5" s="59"/>
     </row>
-    <row r="6" spans="1:3" ht="12.95" customHeight="1">
+    <row r="6" spans="1:3" ht="13" customHeight="1">
       <c r="A6" s="27" t="s">
         <v>605</v>
       </c>
@@ -43852,7 +43856,7 @@
       <c r="A18" s="65"/>
       <c r="B18" s="66"/>
     </row>
-    <row r="19" spans="1:2" ht="12.95" customHeight="1">
+    <row r="19" spans="1:2" ht="13" customHeight="1">
       <c r="A19" s="216" t="s">
         <v>3006</v>
       </c>
@@ -43892,7 +43896,7 @@
         <v>3010</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="12.95" customHeight="1">
+    <row r="29" spans="1:2" ht="13" customHeight="1">
       <c r="A29" s="71"/>
       <c r="B29" s="70" t="s">
         <v>3011</v>
@@ -44008,7 +44012,7 @@
         <v>3036</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="42.95" customHeight="1">
+    <row r="46" spans="1:2" ht="43" customHeight="1">
       <c r="A46" s="216" t="s">
         <v>3037</v>
       </c>
@@ -44016,7 +44020,7 @@
         <v>3038</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="12.95" customHeight="1">
+    <row r="49" spans="1:2" ht="13" customHeight="1">
       <c r="A49" s="71" t="s">
         <v>3039</v>
       </c>
@@ -44147,7 +44151,7 @@
     <row r="204" spans="1:2">
       <c r="B204" s="266"/>
     </row>
-    <row r="206" spans="1:2">
+    <row r="206" spans="1:2" ht="13">
       <c r="A206" s="468" t="s">
         <v>3056</v>
       </c>
@@ -44168,7 +44172,7 @@
         <v>3058</v>
       </c>
     </row>
-    <row r="210" spans="1:2">
+    <row r="210" spans="1:2" ht="13">
       <c r="A210" s="468" t="s">
         <v>3059</v>
       </c>
@@ -44229,7 +44233,7 @@
         <v>3073</v>
       </c>
     </row>
-    <row r="219" spans="1:2">
+    <row r="219" spans="1:2" ht="13">
       <c r="A219" s="468" t="s">
         <v>3074</v>
       </c>
@@ -44272,11 +44276,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:X983"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="26.5703125" customWidth="1"/>
-    <col min="2" max="2" width="181.28515625" customWidth="1"/>
-    <col min="3" max="24" width="40.5703125" customWidth="1"/>
+    <col min="1" max="1" width="26.54296875" customWidth="1"/>
+    <col min="2" max="2" width="181.26953125" customWidth="1"/>
+    <col min="3" max="24" width="40.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="29.25" customHeight="1">
@@ -69853,7 +69857,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="5" t="s">
@@ -69943,11 +69947,11 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:I993"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="43.42578125" customWidth="1"/>
-    <col min="2" max="2" width="35.42578125" customWidth="1"/>
-    <col min="3" max="3" width="25.28515625" customWidth="1"/>
+    <col min="1" max="1" width="43.453125" customWidth="1"/>
+    <col min="2" max="2" width="35.453125" customWidth="1"/>
+    <col min="3" max="3" width="25.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15" customHeight="1">
@@ -69960,13 +69964,13 @@
         <v>3098</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="12.6" customHeight="1">
+    <row r="3" spans="1:2" ht="12.65" customHeight="1">
       <c r="A3" t="s">
         <v>3099</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="12.6" customHeight="1"/>
-    <row r="5" spans="1:2" ht="12.6" customHeight="1">
+    <row r="4" spans="1:2" ht="12.65" customHeight="1"/>
+    <row r="5" spans="1:2" ht="12.65" customHeight="1">
       <c r="A5" s="262" t="s">
         <v>3100</v>
       </c>
@@ -69976,23 +69980,23 @@
         <v>3101</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="12.6" customHeight="1">
+    <row r="7" spans="1:2" ht="12.65" customHeight="1">
       <c r="A7" t="s">
         <v>3102</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="12.6" customHeight="1">
+    <row r="8" spans="1:2" ht="12.65" customHeight="1">
       <c r="A8" s="262" t="s">
         <v>3103</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="12.6" customHeight="1"/>
-    <row r="10" spans="1:2" ht="12.6" customHeight="1">
+    <row r="9" spans="1:2" ht="12.65" customHeight="1"/>
+    <row r="10" spans="1:2" ht="12.65" customHeight="1">
       <c r="A10" s="262" t="s">
         <v>3104</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="12.6" customHeight="1">
+    <row r="11" spans="1:2" ht="12.65" customHeight="1">
       <c r="A11" t="s">
         <v>3105</v>
       </c>
@@ -70000,7 +70004,7 @@
         <v>3106</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="12.6" customHeight="1">
+    <row r="12" spans="1:2" ht="12.65" customHeight="1">
       <c r="A12" t="s">
         <v>3107</v>
       </c>
@@ -70008,7 +70012,7 @@
         <v>3108</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="51.95" customHeight="1">
+    <row r="13" spans="1:2" ht="52" customHeight="1">
       <c r="A13" t="s">
         <v>3109</v>
       </c>
@@ -70016,7 +70020,7 @@
         <v>3110</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="12.6" customHeight="1">
+    <row r="14" spans="1:2" ht="12.65" customHeight="1">
       <c r="A14" t="s">
         <v>3111</v>
       </c>
@@ -70024,7 +70028,7 @@
         <v>3112</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="12.6" customHeight="1">
+    <row r="15" spans="1:2" ht="12.65" customHeight="1">
       <c r="A15" t="s">
         <v>3113</v>
       </c>
@@ -70032,13 +70036,13 @@
         <v>3114</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="12.6" customHeight="1"/>
-    <row r="17" spans="1:3" ht="12.6" customHeight="1">
+    <row r="16" spans="1:2" ht="12.65" customHeight="1"/>
+    <row r="17" spans="1:3" ht="12.65" customHeight="1">
       <c r="A17" s="262" t="s">
         <v>3115</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="12.6" customHeight="1">
+    <row r="18" spans="1:3" ht="12.65" customHeight="1">
       <c r="B18" t="s">
         <v>3116</v>
       </c>
@@ -70046,7 +70050,7 @@
         <v>3117</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="24.95" customHeight="1">
+    <row r="19" spans="1:3" ht="25" customHeight="1">
       <c r="A19" t="s">
         <v>3118</v>
       </c>
@@ -70054,7 +70058,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="12.6" customHeight="1">
+    <row r="20" spans="1:3" ht="12.65" customHeight="1">
       <c r="A20" t="s">
         <v>3119</v>
       </c>
@@ -70065,7 +70069,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="24.95" customHeight="1">
+    <row r="21" spans="1:3" ht="25" customHeight="1">
       <c r="A21" t="s">
         <v>3120</v>
       </c>
@@ -70076,7 +70080,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="12.6" customHeight="1">
+    <row r="22" spans="1:3" ht="12.65" customHeight="1">
       <c r="A22" t="s">
         <v>3121</v>
       </c>
@@ -70087,7 +70091,7 @@
         <v>0.188</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="24.95" customHeight="1">
+    <row r="23" spans="1:3" ht="25" customHeight="1">
       <c r="A23" t="s">
         <v>3122</v>
       </c>
@@ -70098,7 +70102,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="12.6" customHeight="1">
+    <row r="24" spans="1:3" ht="12.65" customHeight="1">
       <c r="A24" t="s">
         <v>3123</v>
       </c>
@@ -70109,7 +70113,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="12.6" customHeight="1">
+    <row r="25" spans="1:3" ht="12.65" customHeight="1">
       <c r="A25" t="s">
         <v>3124</v>
       </c>
@@ -70120,13 +70124,13 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="12.6" customHeight="1"/>
-    <row r="27" spans="1:3" ht="12.6" customHeight="1">
+    <row r="26" spans="1:3" ht="12.65" customHeight="1"/>
+    <row r="27" spans="1:3" ht="12.65" customHeight="1">
       <c r="A27" s="262" t="s">
         <v>3125</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="12.6" customHeight="1">
+    <row r="28" spans="1:3" ht="12.65" customHeight="1">
       <c r="A28" t="s">
         <v>3126</v>
       </c>
@@ -70137,7 +70141,7 @@
         <v>0.94199999999999995</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="12.6" customHeight="1">
+    <row r="29" spans="1:3" ht="12.65" customHeight="1">
       <c r="A29" t="s">
         <v>3128</v>
       </c>
@@ -70148,7 +70152,7 @@
         <v>0.73299999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="12.6" customHeight="1">
+    <row r="30" spans="1:3" ht="12.65" customHeight="1">
       <c r="A30" t="s">
         <v>3130</v>
       </c>
@@ -70159,7 +70163,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="12.6" customHeight="1">
+    <row r="31" spans="1:3" ht="12.65" customHeight="1">
       <c r="A31" t="s">
         <v>3132</v>
       </c>
@@ -70170,24 +70174,24 @@
         <v>0.108</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="12.6" customHeight="1"/>
-    <row r="33" spans="1:9" ht="12.6" customHeight="1">
+    <row r="32" spans="1:3" ht="12.65" customHeight="1"/>
+    <row r="33" spans="1:9" ht="12.65" customHeight="1">
       <c r="A33" s="262" t="s">
         <v>3134</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="12.6" customHeight="1">
+    <row r="34" spans="1:9" ht="12.65" customHeight="1">
       <c r="A34" t="s">
         <v>3135</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="36" spans="1:9" ht="12.6" customHeight="1">
+    <row r="35" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="36" spans="1:9" ht="12.65" customHeight="1">
       <c r="A36" s="262" t="s">
         <v>3136</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="12.6" customHeight="1">
+    <row r="37" spans="1:9" ht="12.65" customHeight="1">
       <c r="A37" t="s">
         <v>3137</v>
       </c>
@@ -70216,7 +70220,7 @@
         <v>3145</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="12.6" customHeight="1">
+    <row r="38" spans="1:9" ht="12.65" customHeight="1">
       <c r="A38" t="s">
         <v>145</v>
       </c>
@@ -70239,7 +70243,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="12.6" customHeight="1">
+    <row r="39" spans="1:9" ht="12.65" customHeight="1">
       <c r="A39" t="s">
         <v>151</v>
       </c>
@@ -70265,7 +70269,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="12.6" customHeight="1">
+    <row r="40" spans="1:9" ht="12.65" customHeight="1">
       <c r="B40" t="s">
         <v>3148</v>
       </c>
@@ -70288,7 +70292,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="12.6" customHeight="1">
+    <row r="41" spans="1:9" ht="12.65" customHeight="1">
       <c r="A41" t="s">
         <v>170</v>
       </c>
@@ -70302,7 +70306,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="12.6" customHeight="1">
+    <row r="42" spans="1:9" ht="12.65" customHeight="1">
       <c r="A42" t="s">
         <v>646</v>
       </c>
@@ -70331,7 +70335,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="12.6" customHeight="1">
+    <row r="43" spans="1:9" ht="12.65" customHeight="1">
       <c r="A43" t="s">
         <v>698</v>
       </c>
@@ -70357,7 +70361,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="12.6" customHeight="1">
+    <row r="44" spans="1:9" ht="12.65" customHeight="1">
       <c r="A44" t="s">
         <v>944</v>
       </c>
@@ -70386,7 +70390,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="12.6" customHeight="1">
+    <row r="45" spans="1:9" ht="12.65" customHeight="1">
       <c r="A45" t="s">
         <v>1122</v>
       </c>
@@ -70415,7 +70419,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="12.6" customHeight="1">
+    <row r="46" spans="1:9" ht="12.65" customHeight="1">
       <c r="A46" t="s">
         <v>1127</v>
       </c>
@@ -70444,7 +70448,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="12.6" customHeight="1">
+    <row r="47" spans="1:9" ht="12.65" customHeight="1">
       <c r="A47" t="s">
         <v>1544</v>
       </c>
@@ -70470,7 +70474,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="12.6" customHeight="1">
+    <row r="48" spans="1:9" ht="12.65" customHeight="1">
       <c r="A48" t="s">
         <v>1703</v>
       </c>
@@ -70496,13 +70500,13 @@
         <v>730</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="50" spans="1:9" ht="12.6" customHeight="1">
+    <row r="49" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="50" spans="1:9" ht="12.65" customHeight="1">
       <c r="A50" s="262" t="s">
         <v>3152</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="12.6" customHeight="1">
+    <row r="51" spans="1:9" ht="12.65" customHeight="1">
       <c r="B51" t="s">
         <v>3153</v>
       </c>
@@ -70528,7 +70532,7 @@
         <v>3160</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="12.6" customHeight="1">
+    <row r="52" spans="1:9" ht="12.65" customHeight="1">
       <c r="A52" t="s">
         <v>1442</v>
       </c>
@@ -70557,7 +70561,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="12.6" customHeight="1">
+    <row r="53" spans="1:9" ht="12.65" customHeight="1">
       <c r="A53" t="s">
         <v>3147</v>
       </c>
@@ -70586,7 +70590,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="12.6" customHeight="1">
+    <row r="54" spans="1:9" ht="12.65" customHeight="1">
       <c r="A54" t="s">
         <v>3158</v>
       </c>
@@ -70615,13 +70619,13 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="56" spans="1:9" ht="12.6" customHeight="1">
+    <row r="55" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="56" spans="1:9" ht="12.65" customHeight="1">
       <c r="A56" s="262" t="s">
         <v>3161</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="12.6" customHeight="1">
+    <row r="57" spans="1:9" ht="12.65" customHeight="1">
       <c r="B57" t="s">
         <v>3153</v>
       </c>
@@ -70647,7 +70651,7 @@
         <v>3160</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="12.6" customHeight="1">
+    <row r="58" spans="1:9" ht="12.65" customHeight="1">
       <c r="A58" t="s">
         <v>1442</v>
       </c>
@@ -70676,7 +70680,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="12.6" customHeight="1">
+    <row r="59" spans="1:9" ht="12.65" customHeight="1">
       <c r="A59" t="s">
         <v>3147</v>
       </c>
@@ -70705,7 +70709,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="12.6" customHeight="1">
+    <row r="60" spans="1:9" ht="12.65" customHeight="1">
       <c r="A60" t="s">
         <v>3158</v>
       </c>
@@ -70734,13 +70738,13 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="62" spans="1:9" ht="12.6" customHeight="1">
+    <row r="61" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="62" spans="1:9" ht="12.65" customHeight="1">
       <c r="A62" s="262" t="s">
         <v>3162</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="12.6" customHeight="1">
+    <row r="63" spans="1:9" ht="12.65" customHeight="1">
       <c r="B63" t="s">
         <v>3153</v>
       </c>
@@ -70766,7 +70770,7 @@
         <v>3160</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="12.6" customHeight="1">
+    <row r="64" spans="1:9" ht="12.65" customHeight="1">
       <c r="A64" t="s">
         <v>52</v>
       </c>
@@ -70795,7 +70799,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="12.6" customHeight="1">
+    <row r="65" spans="1:9" ht="12.65" customHeight="1">
       <c r="A65" t="s">
         <v>33</v>
       </c>
@@ -70824,7 +70828,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="12.6" customHeight="1">
+    <row r="66" spans="1:9" ht="12.65" customHeight="1">
       <c r="A66" t="s">
         <v>3158</v>
       </c>
@@ -70853,13 +70857,13 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="68" spans="1:9" ht="12.6" customHeight="1">
+    <row r="67" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="68" spans="1:9" ht="12.65" customHeight="1">
       <c r="A68" s="262" t="s">
         <v>3163</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="12.6" customHeight="1">
+    <row r="69" spans="1:9" ht="12.65" customHeight="1">
       <c r="B69" t="s">
         <v>3153</v>
       </c>
@@ -70885,7 +70889,7 @@
         <v>3160</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="12.6" customHeight="1">
+    <row r="70" spans="1:9" ht="12.65" customHeight="1">
       <c r="A70" t="s">
         <v>1802</v>
       </c>
@@ -70914,7 +70918,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="12.6" customHeight="1">
+    <row r="71" spans="1:9" ht="12.65" customHeight="1">
       <c r="A71" t="s">
         <v>1648</v>
       </c>
@@ -70943,7 +70947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="12.6" customHeight="1">
+    <row r="72" spans="1:9" ht="12.65" customHeight="1">
       <c r="A72" t="s">
         <v>1633</v>
       </c>
@@ -70972,7 +70976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="12.6" customHeight="1">
+    <row r="73" spans="1:9" ht="12.65" customHeight="1">
       <c r="A73" t="s">
         <v>3158</v>
       </c>
@@ -71001,13 +71005,13 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="75" spans="1:9" ht="12.6" customHeight="1">
+    <row r="74" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="75" spans="1:9" ht="12.65" customHeight="1">
       <c r="A75" s="262" t="s">
         <v>3164</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="12.6" customHeight="1">
+    <row r="76" spans="1:9" ht="12.65" customHeight="1">
       <c r="B76" t="s">
         <v>3153</v>
       </c>
@@ -71033,7 +71037,7 @@
         <v>3160</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="12.6" customHeight="1">
+    <row r="77" spans="1:9" ht="12.65" customHeight="1">
       <c r="A77" t="s">
         <v>803</v>
       </c>
@@ -71062,7 +71066,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="12.6" customHeight="1">
+    <row r="78" spans="1:9" ht="12.65" customHeight="1">
       <c r="A78" t="s">
         <v>1120</v>
       </c>
@@ -71091,7 +71095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="12.6" customHeight="1">
+    <row r="79" spans="1:9" ht="12.65" customHeight="1">
       <c r="A79" t="s">
         <v>3151</v>
       </c>
@@ -71120,7 +71124,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="12.6" customHeight="1">
+    <row r="80" spans="1:9" ht="12.65" customHeight="1">
       <c r="A80" t="s">
         <v>1474</v>
       </c>
@@ -71149,7 +71153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="12.6" customHeight="1">
+    <row r="81" spans="1:9" ht="12.65" customHeight="1">
       <c r="A81" t="s">
         <v>3158</v>
       </c>
@@ -71178,13 +71182,13 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="83" spans="1:9" ht="12.6" customHeight="1">
+    <row r="82" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="83" spans="1:9" ht="12.65" customHeight="1">
       <c r="A83" s="262" t="s">
         <v>3165</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="12.6" customHeight="1">
+    <row r="84" spans="1:9" ht="12.65" customHeight="1">
       <c r="B84" t="s">
         <v>3153</v>
       </c>
@@ -71210,7 +71214,7 @@
         <v>3160</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="12.6" customHeight="1">
+    <row r="85" spans="1:9" ht="12.65" customHeight="1">
       <c r="A85" t="s">
         <v>3166</v>
       </c>
@@ -71239,7 +71243,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="12.6" customHeight="1">
+    <row r="86" spans="1:9" ht="12.65" customHeight="1">
       <c r="A86" t="s">
         <v>3167</v>
       </c>
@@ -71268,7 +71272,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="12.6" customHeight="1">
+    <row r="87" spans="1:9" ht="12.65" customHeight="1">
       <c r="A87" t="s">
         <v>3168</v>
       </c>
@@ -71297,7 +71301,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="12.6" customHeight="1">
+    <row r="88" spans="1:9" ht="12.65" customHeight="1">
       <c r="A88" t="s">
         <v>3158</v>
       </c>
@@ -71326,13 +71330,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="90" spans="1:9" ht="12.6" customHeight="1">
+    <row r="89" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="90" spans="1:9" ht="12.65" customHeight="1">
       <c r="A90" s="262" t="s">
         <v>3169</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="12.6" customHeight="1">
+    <row r="91" spans="1:9" ht="12.65" customHeight="1">
       <c r="B91" t="s">
         <v>3153</v>
       </c>
@@ -71358,7 +71362,7 @@
         <v>3160</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="12.6" customHeight="1">
+    <row r="92" spans="1:9" ht="12.65" customHeight="1">
       <c r="A92" t="b">
         <v>0</v>
       </c>
@@ -71387,7 +71391,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="12.6" customHeight="1">
+    <row r="93" spans="1:9" ht="12.65" customHeight="1">
       <c r="A93" t="b">
         <v>1</v>
       </c>
@@ -71416,7 +71420,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="12.6" customHeight="1">
+    <row r="94" spans="1:9" ht="12.65" customHeight="1">
       <c r="A94" t="s">
         <v>3158</v>
       </c>
@@ -71445,13 +71449,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="96" spans="1:9" ht="12.6" customHeight="1">
+    <row r="95" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="96" spans="1:9" ht="12.65" customHeight="1">
       <c r="A96" s="262" t="s">
         <v>3170</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="12.6" customHeight="1">
+    <row r="97" spans="1:9" ht="12.65" customHeight="1">
       <c r="B97" t="s">
         <v>3153</v>
       </c>
@@ -71477,7 +71481,7 @@
         <v>3160</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="12.6" customHeight="1">
+    <row r="98" spans="1:9" ht="12.65" customHeight="1">
       <c r="A98" t="s">
         <v>34</v>
       </c>
@@ -71506,7 +71510,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="12.6" customHeight="1">
+    <row r="99" spans="1:9" ht="12.65" customHeight="1">
       <c r="A99" t="s">
         <v>248</v>
       </c>
@@ -71535,7 +71539,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="12.6" customHeight="1">
+    <row r="100" spans="1:9" ht="12.65" customHeight="1">
       <c r="A100" t="s">
         <v>63</v>
       </c>
@@ -71564,7 +71568,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="12.6" customHeight="1">
+    <row r="101" spans="1:9" ht="12.65" customHeight="1">
       <c r="A101" t="s">
         <v>184</v>
       </c>
@@ -71593,7 +71597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="12.6" customHeight="1">
+    <row r="102" spans="1:9" ht="12.65" customHeight="1">
       <c r="A102" t="s">
         <v>143</v>
       </c>
@@ -71622,7 +71626,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="12.6" customHeight="1">
+    <row r="103" spans="1:9" ht="12.65" customHeight="1">
       <c r="A103" t="s">
         <v>1051</v>
       </c>
@@ -71651,7 +71655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="12.6" customHeight="1">
+    <row r="104" spans="1:9" ht="12.65" customHeight="1">
       <c r="A104" t="s">
         <v>169</v>
       </c>
@@ -71680,7 +71684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="12.6" customHeight="1">
+    <row r="105" spans="1:9" ht="12.65" customHeight="1">
       <c r="A105" t="s">
         <v>399</v>
       </c>
@@ -71709,7 +71713,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="12.6" customHeight="1">
+    <row r="106" spans="1:9" ht="12.65" customHeight="1">
       <c r="A106" t="s">
         <v>3158</v>
       </c>
@@ -71738,13 +71742,13 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="108" spans="1:9" ht="12.6" customHeight="1">
+    <row r="107" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="108" spans="1:9" ht="12.65" customHeight="1">
       <c r="A108" s="262" t="s">
         <v>3171</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="12.6" customHeight="1">
+    <row r="109" spans="1:9" ht="12.65" customHeight="1">
       <c r="B109" t="s">
         <v>3153</v>
       </c>
@@ -71770,7 +71774,7 @@
         <v>3160</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="12.6" customHeight="1">
+    <row r="110" spans="1:9" ht="12.65" customHeight="1">
       <c r="A110" t="s">
         <v>35</v>
       </c>
@@ -71799,7 +71803,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="12.6" customHeight="1">
+    <row r="111" spans="1:9" ht="12.65" customHeight="1">
       <c r="A111" t="s">
         <v>53</v>
       </c>
@@ -71828,7 +71832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="12.6" customHeight="1">
+    <row r="112" spans="1:9" ht="12.65" customHeight="1">
       <c r="A112" t="s">
         <v>119</v>
       </c>
@@ -71857,7 +71861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="12.6" customHeight="1">
+    <row r="113" spans="1:9" ht="12.65" customHeight="1">
       <c r="A113" t="s">
         <v>45</v>
       </c>
@@ -71886,7 +71890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="12.6" customHeight="1">
+    <row r="114" spans="1:9" ht="12.65" customHeight="1">
       <c r="A114" t="s">
         <v>3158</v>
       </c>
@@ -71915,13 +71919,13 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="116" spans="1:9" ht="12.6" customHeight="1">
+    <row r="115" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="116" spans="1:9" ht="12.65" customHeight="1">
       <c r="A116" s="262" t="s">
         <v>3172</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="12.6" customHeight="1">
+    <row r="117" spans="1:9" ht="12.65" customHeight="1">
       <c r="B117" t="s">
         <v>3153</v>
       </c>
@@ -71947,7 +71951,7 @@
         <v>3160</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="12.6" customHeight="1">
+    <row r="118" spans="1:9" ht="12.65" customHeight="1">
       <c r="A118" t="s">
         <v>3173</v>
       </c>
@@ -71976,7 +71980,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="12.6" customHeight="1">
+    <row r="119" spans="1:9" ht="12.65" customHeight="1">
       <c r="A119" t="s">
         <v>3174</v>
       </c>
@@ -72005,7 +72009,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="12.6" customHeight="1">
+    <row r="120" spans="1:9" ht="12.65" customHeight="1">
       <c r="A120" t="s">
         <v>3158</v>
       </c>
@@ -72034,99 +72038,99 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="122" spans="1:9" ht="12.6" customHeight="1">
+    <row r="121" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="122" spans="1:9" ht="12.65" customHeight="1">
       <c r="A122" s="262" t="s">
         <v>3175</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="124" spans="1:9" ht="12.6" customHeight="1">
+    <row r="123" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="124" spans="1:9" ht="12.65" customHeight="1">
       <c r="A124" s="262" t="s">
         <v>3176</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="12.6" customHeight="1">
+    <row r="125" spans="1:9" ht="12.65" customHeight="1">
       <c r="A125" s="262" t="s">
         <v>3177</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="12.6" customHeight="1"/>
-    <row r="127" spans="1:9" ht="12.6" customHeight="1">
+    <row r="126" spans="1:9" ht="12.65" customHeight="1"/>
+    <row r="127" spans="1:9" ht="12.65" customHeight="1">
       <c r="A127" t="s">
         <v>3178</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="12.6" customHeight="1">
+    <row r="128" spans="1:9" ht="12.65" customHeight="1">
       <c r="A128" t="s">
         <v>3179</v>
       </c>
     </row>
-    <row r="129" spans="1:1" ht="12.6" customHeight="1">
+    <row r="129" spans="1:1" ht="12.65" customHeight="1">
       <c r="A129" t="s">
         <v>3180</v>
       </c>
     </row>
-    <row r="130" spans="1:1" ht="12.6" customHeight="1">
+    <row r="130" spans="1:1" ht="12.65" customHeight="1">
       <c r="A130" t="s">
         <v>3181</v>
       </c>
     </row>
-    <row r="131" spans="1:1" ht="12.6" customHeight="1">
+    <row r="131" spans="1:1" ht="12.65" customHeight="1">
       <c r="A131" t="s">
         <v>3182</v>
       </c>
     </row>
-    <row r="132" spans="1:1" ht="12.6" customHeight="1">
+    <row r="132" spans="1:1" ht="12.65" customHeight="1">
       <c r="A132" t="s">
         <v>3183</v>
       </c>
     </row>
-    <row r="133" spans="1:1" ht="12.6" customHeight="1">
+    <row r="133" spans="1:1" ht="12.65" customHeight="1">
       <c r="A133" t="s">
         <v>3184</v>
       </c>
     </row>
-    <row r="134" spans="1:1" ht="12.6" customHeight="1">
+    <row r="134" spans="1:1" ht="12.65" customHeight="1">
       <c r="A134" t="s">
         <v>3185</v>
       </c>
     </row>
-    <row r="135" spans="1:1" ht="12.6" customHeight="1">
+    <row r="135" spans="1:1" ht="12.65" customHeight="1">
       <c r="A135" t="s">
         <v>3186</v>
       </c>
     </row>
-    <row r="136" spans="1:1" ht="12.6" customHeight="1">
+    <row r="136" spans="1:1" ht="12.65" customHeight="1">
       <c r="A136" t="s">
         <v>3187</v>
       </c>
     </row>
-    <row r="137" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="138" spans="1:1" ht="12.6" customHeight="1">
+    <row r="137" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="138" spans="1:1" ht="12.65" customHeight="1">
       <c r="A138" s="262" t="s">
         <v>3188</v>
       </c>
     </row>
-    <row r="139" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="140" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="141" spans="1:1" ht="12.6" customHeight="1">
+    <row r="139" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="140" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="141" spans="1:1" ht="12.65" customHeight="1">
       <c r="A141" s="467" t="s">
         <v>3189</v>
       </c>
     </row>
-    <row r="142" spans="1:1" ht="12.6" customHeight="1">
+    <row r="142" spans="1:1" ht="12.65" customHeight="1">
       <c r="A142" t="s">
         <v>3190</v>
       </c>
     </row>
-    <row r="143" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="144" spans="1:1" ht="12.6" customHeight="1">
+    <row r="143" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="144" spans="1:1" ht="12.65" customHeight="1">
       <c r="A144" s="468" t="s">
         <v>3191</v>
       </c>
     </row>
-    <row r="145" spans="1:2" ht="12.6" customHeight="1">
+    <row r="145" spans="1:2" ht="12.65" customHeight="1">
       <c r="A145" t="s">
         <v>3192</v>
       </c>
@@ -72134,7 +72138,7 @@
         <v>3193</v>
       </c>
     </row>
-    <row r="146" spans="1:2" ht="12.6" customHeight="1">
+    <row r="146" spans="1:2" ht="12.65" customHeight="1">
       <c r="A146" t="s">
         <v>3194</v>
       </c>
@@ -72142,7 +72146,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="147" spans="1:2" ht="12.6" customHeight="1">
+    <row r="147" spans="1:2" ht="12.65" customHeight="1">
       <c r="A147" t="s">
         <v>3195</v>
       </c>
@@ -72150,7 +72154,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="148" spans="1:2" ht="12.6" customHeight="1">
+    <row r="148" spans="1:2" ht="12.65" customHeight="1">
       <c r="A148" t="s">
         <v>3196</v>
       </c>
@@ -72158,7 +72162,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="149" spans="1:2" ht="12.6" customHeight="1">
+    <row r="149" spans="1:2" ht="12.65" customHeight="1">
       <c r="A149" t="s">
         <v>3197</v>
       </c>
@@ -72166,7 +72170,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="1:2" ht="12.6" customHeight="1">
+    <row r="150" spans="1:2" ht="12.65" customHeight="1">
       <c r="A150" t="s">
         <v>3198</v>
       </c>
@@ -72174,51 +72178,51 @@
         <v>3199</v>
       </c>
     </row>
-    <row r="151" spans="1:2" ht="12.6" customHeight="1"/>
-    <row r="152" spans="1:2" ht="12.6" customHeight="1"/>
-    <row r="153" spans="1:2" ht="12.6" customHeight="1">
+    <row r="151" spans="1:2" ht="12.65" customHeight="1"/>
+    <row r="152" spans="1:2" ht="12.65" customHeight="1"/>
+    <row r="153" spans="1:2" ht="12.65" customHeight="1">
       <c r="A153" s="469" t="s">
         <v>3200</v>
       </c>
     </row>
-    <row r="154" spans="1:2" ht="12.6" customHeight="1">
+    <row r="154" spans="1:2" ht="12.65" customHeight="1">
       <c r="A154" t="s">
         <v>3201</v>
       </c>
     </row>
-    <row r="155" spans="1:2" ht="12.6" customHeight="1"/>
-    <row r="156" spans="1:2" ht="12.6" customHeight="1">
+    <row r="155" spans="1:2" ht="12.65" customHeight="1"/>
+    <row r="156" spans="1:2" ht="12.65" customHeight="1">
       <c r="A156" s="470" t="s">
         <v>3202</v>
       </c>
     </row>
-    <row r="157" spans="1:2" ht="12.6" customHeight="1">
+    <row r="157" spans="1:2" ht="12.65" customHeight="1">
       <c r="A157" t="s">
         <v>3203</v>
       </c>
     </row>
-    <row r="158" spans="1:2" ht="12.6" customHeight="1">
+    <row r="158" spans="1:2" ht="12.65" customHeight="1">
       <c r="A158" t="s">
         <v>3204</v>
       </c>
     </row>
-    <row r="159" spans="1:2" ht="12.6" customHeight="1">
+    <row r="159" spans="1:2" ht="12.65" customHeight="1">
       <c r="A159" t="s">
         <v>3205</v>
       </c>
     </row>
-    <row r="160" spans="1:2" ht="12.6" customHeight="1"/>
-    <row r="161" spans="1:2" ht="12.6" customHeight="1">
+    <row r="160" spans="1:2" ht="12.65" customHeight="1"/>
+    <row r="161" spans="1:2" ht="12.65" customHeight="1">
       <c r="A161" s="470" t="s">
         <v>3206</v>
       </c>
     </row>
-    <row r="162" spans="1:2" ht="12.6" customHeight="1">
+    <row r="162" spans="1:2" ht="12.65" customHeight="1">
       <c r="A162" t="s">
         <v>3207</v>
       </c>
     </row>
-    <row r="163" spans="1:2" ht="12.6" customHeight="1">
+    <row r="163" spans="1:2" ht="12.65" customHeight="1">
       <c r="A163" t="s">
         <v>3208</v>
       </c>
@@ -72226,7 +72230,7 @@
         <v>3209</v>
       </c>
     </row>
-    <row r="164" spans="1:2" ht="12.6" customHeight="1">
+    <row r="164" spans="1:2" ht="12.65" customHeight="1">
       <c r="A164" t="s">
         <v>3210</v>
       </c>
@@ -72234,7 +72238,7 @@
         <v>3211</v>
       </c>
     </row>
-    <row r="165" spans="1:2" ht="12.6" customHeight="1">
+    <row r="165" spans="1:2" ht="12.65" customHeight="1">
       <c r="A165" t="s">
         <v>3212</v>
       </c>
@@ -72242,7 +72246,7 @@
         <v>3213</v>
       </c>
     </row>
-    <row r="166" spans="1:2" ht="12.6" customHeight="1">
+    <row r="166" spans="1:2" ht="12.65" customHeight="1">
       <c r="A166" t="s">
         <v>3214</v>
       </c>
@@ -72250,7 +72254,7 @@
         <v>3215</v>
       </c>
     </row>
-    <row r="167" spans="1:2" ht="12.6" customHeight="1">
+    <row r="167" spans="1:2" ht="12.65" customHeight="1">
       <c r="A167" t="s">
         <v>3216</v>
       </c>
@@ -72258,301 +72262,301 @@
         <v>3215</v>
       </c>
     </row>
-    <row r="168" spans="1:2" ht="12.6" customHeight="1"/>
-    <row r="169" spans="1:2" ht="12.6" customHeight="1">
+    <row r="168" spans="1:2" ht="12.65" customHeight="1"/>
+    <row r="169" spans="1:2" ht="12.65" customHeight="1">
       <c r="A169" t="s">
         <v>3217</v>
       </c>
     </row>
-    <row r="170" spans="1:2" ht="12.6" customHeight="1">
+    <row r="170" spans="1:2" ht="12.65" customHeight="1">
       <c r="A170" t="s">
         <v>3218</v>
       </c>
     </row>
-    <row r="171" spans="1:2" ht="12.6" customHeight="1">
+    <row r="171" spans="1:2" ht="12.65" customHeight="1">
       <c r="A171" t="s">
         <v>3219</v>
       </c>
     </row>
-    <row r="172" spans="1:2" ht="12.6" customHeight="1"/>
-    <row r="173" spans="1:2" ht="12.6" customHeight="1">
+    <row r="172" spans="1:2" ht="12.65" customHeight="1"/>
+    <row r="173" spans="1:2" ht="12.65" customHeight="1">
       <c r="A173" s="470" t="s">
         <v>3220</v>
       </c>
     </row>
-    <row r="174" spans="1:2" ht="12.6" customHeight="1">
+    <row r="174" spans="1:2" ht="12.65" customHeight="1">
       <c r="A174" t="s">
         <v>3221</v>
       </c>
     </row>
-    <row r="175" spans="1:2" ht="12.6" customHeight="1">
+    <row r="175" spans="1:2" ht="12.65" customHeight="1">
       <c r="A175" t="s">
         <v>3222</v>
       </c>
     </row>
-    <row r="176" spans="1:2" ht="12.6" customHeight="1">
+    <row r="176" spans="1:2" ht="12.65" customHeight="1">
       <c r="A176" t="s">
         <v>3223</v>
       </c>
     </row>
-    <row r="177" spans="1:1" ht="12.6" customHeight="1">
+    <row r="177" spans="1:1" ht="12.65" customHeight="1">
       <c r="A177" t="s">
         <v>3224</v>
       </c>
     </row>
-    <row r="178" spans="1:1" ht="12.6" customHeight="1">
+    <row r="178" spans="1:1" ht="12.65" customHeight="1">
       <c r="A178" t="s">
         <v>3225</v>
       </c>
     </row>
-    <row r="179" spans="1:1" ht="12.6" customHeight="1">
+    <row r="179" spans="1:1" ht="12.65" customHeight="1">
       <c r="A179" t="s">
         <v>3226</v>
       </c>
     </row>
-    <row r="180" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="181" spans="1:1" ht="12.6" customHeight="1">
+    <row r="180" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="181" spans="1:1" ht="12.65" customHeight="1">
       <c r="A181" s="471" t="s">
         <v>3227</v>
       </c>
     </row>
-    <row r="182" spans="1:1" ht="12.6" customHeight="1">
+    <row r="182" spans="1:1" ht="12.65" customHeight="1">
       <c r="A182" t="s">
         <v>3228</v>
       </c>
     </row>
-    <row r="183" spans="1:1" ht="12.6" customHeight="1">
+    <row r="183" spans="1:1" ht="12.65" customHeight="1">
       <c r="A183" t="s">
         <v>3229</v>
       </c>
     </row>
-    <row r="184" spans="1:1" ht="12.6" customHeight="1">
+    <row r="184" spans="1:1" ht="12.65" customHeight="1">
       <c r="A184" t="s">
         <v>3230</v>
       </c>
     </row>
-    <row r="185" spans="1:1" ht="12.6" customHeight="1">
+    <row r="185" spans="1:1" ht="12.65" customHeight="1">
       <c r="A185" t="s">
         <v>3231</v>
       </c>
     </row>
-    <row r="186" spans="1:1" ht="12.6" customHeight="1">
+    <row r="186" spans="1:1" ht="12.65" customHeight="1">
       <c r="A186" t="s">
         <v>3232</v>
       </c>
     </row>
-    <row r="187" spans="1:1" ht="12.6" customHeight="1">
+    <row r="187" spans="1:1" ht="12.65" customHeight="1">
       <c r="A187" t="s">
         <v>3233</v>
       </c>
     </row>
-    <row r="188" spans="1:1" ht="12.6" customHeight="1">
+    <row r="188" spans="1:1" ht="12.65" customHeight="1">
       <c r="A188" t="s">
         <v>3234</v>
       </c>
     </row>
-    <row r="189" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="190" spans="1:1" ht="12.6" customHeight="1">
+    <row r="189" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="190" spans="1:1" ht="12.65" customHeight="1">
       <c r="A190" s="469" t="s">
         <v>3235</v>
       </c>
     </row>
-    <row r="191" spans="1:1" ht="12.6" customHeight="1">
+    <row r="191" spans="1:1" ht="12.65" customHeight="1">
       <c r="A191" t="s">
         <v>3236</v>
       </c>
     </row>
-    <row r="192" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="193" spans="1:1" ht="12.6" customHeight="1">
+    <row r="192" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="193" spans="1:1" ht="12.65" customHeight="1">
       <c r="A193" s="468" t="s">
         <v>3237</v>
       </c>
     </row>
-    <row r="194" spans="1:1" ht="12.6" customHeight="1">
+    <row r="194" spans="1:1" ht="12.65" customHeight="1">
       <c r="A194" t="s">
         <v>3238</v>
       </c>
     </row>
-    <row r="195" spans="1:1" ht="12.6" customHeight="1">
+    <row r="195" spans="1:1" ht="12.65" customHeight="1">
       <c r="A195" t="s">
         <v>3239</v>
       </c>
     </row>
-    <row r="196" spans="1:1" ht="12.6" customHeight="1">
+    <row r="196" spans="1:1" ht="12.65" customHeight="1">
       <c r="A196" t="s">
         <v>3240</v>
       </c>
     </row>
-    <row r="197" spans="1:1" ht="12.6" customHeight="1">
+    <row r="197" spans="1:1" ht="12.65" customHeight="1">
       <c r="A197" t="s">
         <v>3241</v>
       </c>
     </row>
-    <row r="198" spans="1:1" ht="12.6" customHeight="1">
+    <row r="198" spans="1:1" ht="12.65" customHeight="1">
       <c r="A198" t="s">
         <v>3242</v>
       </c>
     </row>
-    <row r="199" spans="1:1" ht="12.6" customHeight="1">
+    <row r="199" spans="1:1" ht="12.65" customHeight="1">
       <c r="A199" t="s">
         <v>3243</v>
       </c>
     </row>
-    <row r="200" spans="1:1" ht="12.6" customHeight="1">
+    <row r="200" spans="1:1" ht="12.65" customHeight="1">
       <c r="A200" t="s">
         <v>3244</v>
       </c>
     </row>
-    <row r="201" spans="1:1" ht="12.6" customHeight="1">
+    <row r="201" spans="1:1" ht="12.65" customHeight="1">
       <c r="A201" t="s">
         <v>3245</v>
       </c>
     </row>
-    <row r="202" spans="1:1" ht="12.6" customHeight="1">
+    <row r="202" spans="1:1" ht="12.65" customHeight="1">
       <c r="A202" t="s">
         <v>3246</v>
       </c>
     </row>
-    <row r="203" spans="1:1" ht="12.6" customHeight="1">
+    <row r="203" spans="1:1" ht="12.65" customHeight="1">
       <c r="A203" t="s">
         <v>3247</v>
       </c>
     </row>
-    <row r="204" spans="1:1" ht="12.6" customHeight="1">
+    <row r="204" spans="1:1" ht="12.65" customHeight="1">
       <c r="A204" t="s">
         <v>3248</v>
       </c>
     </row>
-    <row r="205" spans="1:1" ht="12.6" customHeight="1">
+    <row r="205" spans="1:1" ht="12.65" customHeight="1">
       <c r="A205" t="s">
         <v>3249</v>
       </c>
     </row>
-    <row r="206" spans="1:1" ht="12.6" customHeight="1">
+    <row r="206" spans="1:1" ht="12.65" customHeight="1">
       <c r="A206" t="s">
         <v>3250</v>
       </c>
     </row>
-    <row r="207" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="208" spans="1:1" ht="12.6" customHeight="1">
+    <row r="207" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="208" spans="1:1" ht="12.65" customHeight="1">
       <c r="A208" s="468" t="s">
         <v>3251</v>
       </c>
     </row>
-    <row r="209" spans="1:1" ht="12.6" customHeight="1">
+    <row r="209" spans="1:1" ht="12.65" customHeight="1">
       <c r="A209" t="s">
         <v>3252</v>
       </c>
     </row>
-    <row r="210" spans="1:1" ht="12.6" customHeight="1">
+    <row r="210" spans="1:1" ht="12.65" customHeight="1">
       <c r="A210" t="s">
         <v>3253</v>
       </c>
     </row>
-    <row r="211" spans="1:1" ht="12.6" customHeight="1">
+    <row r="211" spans="1:1" ht="12.65" customHeight="1">
       <c r="A211" t="s">
         <v>3254</v>
       </c>
     </row>
-    <row r="212" spans="1:1" ht="12.6" customHeight="1">
+    <row r="212" spans="1:1" ht="12.65" customHeight="1">
       <c r="A212" t="s">
         <v>3255</v>
       </c>
     </row>
-    <row r="213" spans="1:1" ht="12.6" customHeight="1">
+    <row r="213" spans="1:1" ht="12.65" customHeight="1">
       <c r="A213" t="s">
         <v>3256</v>
       </c>
     </row>
-    <row r="214" spans="1:1" ht="12.6" customHeight="1">
+    <row r="214" spans="1:1" ht="12.65" customHeight="1">
       <c r="A214" t="s">
         <v>3257</v>
       </c>
     </row>
-    <row r="215" spans="1:1" ht="12.6" customHeight="1">
+    <row r="215" spans="1:1" ht="12.65" customHeight="1">
       <c r="A215" t="s">
         <v>3258</v>
       </c>
     </row>
-    <row r="216" spans="1:1" ht="12.6" customHeight="1">
+    <row r="216" spans="1:1" ht="12.65" customHeight="1">
       <c r="A216" t="s">
         <v>3259</v>
       </c>
     </row>
-    <row r="217" spans="1:1" ht="12.6" customHeight="1">
+    <row r="217" spans="1:1" ht="12.65" customHeight="1">
       <c r="A217" t="s">
         <v>3260</v>
       </c>
     </row>
-    <row r="218" spans="1:1" ht="12.6" customHeight="1">
+    <row r="218" spans="1:1" ht="12.65" customHeight="1">
       <c r="A218" t="s">
         <v>3261</v>
       </c>
     </row>
-    <row r="219" spans="1:1" ht="12.6" customHeight="1">
+    <row r="219" spans="1:1" ht="12.65" customHeight="1">
       <c r="A219" t="s">
         <v>3262</v>
       </c>
     </row>
-    <row r="220" spans="1:1" ht="12.6" customHeight="1">
+    <row r="220" spans="1:1" ht="12.65" customHeight="1">
       <c r="A220" t="s">
         <v>3263</v>
       </c>
     </row>
-    <row r="221" spans="1:1" ht="12.6" customHeight="1">
+    <row r="221" spans="1:1" ht="12.65" customHeight="1">
       <c r="A221" t="s">
         <v>3264</v>
       </c>
     </row>
-    <row r="222" spans="1:1" ht="12.6" customHeight="1">
+    <row r="222" spans="1:1" ht="12.65" customHeight="1">
       <c r="A222" t="s">
         <v>3265</v>
       </c>
     </row>
-    <row r="223" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="224" spans="1:1" ht="12.6" customHeight="1">
+    <row r="223" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="224" spans="1:1" ht="12.65" customHeight="1">
       <c r="A224" s="472" t="s">
         <v>3266</v>
       </c>
     </row>
-    <row r="225" spans="1:2" ht="12.6" customHeight="1">
+    <row r="225" spans="1:2" ht="12.65" customHeight="1">
       <c r="A225" t="s">
         <v>3267</v>
       </c>
     </row>
-    <row r="226" spans="1:2" ht="12.6" customHeight="1">
+    <row r="226" spans="1:2" ht="12.65" customHeight="1">
       <c r="A226" t="s">
         <v>3268</v>
       </c>
     </row>
-    <row r="227" spans="1:2" ht="12.6" customHeight="1">
+    <row r="227" spans="1:2" ht="12.65" customHeight="1">
       <c r="A227" t="s">
         <v>3269</v>
       </c>
     </row>
-    <row r="228" spans="1:2" ht="12.6" customHeight="1">
+    <row r="228" spans="1:2" ht="12.65" customHeight="1">
       <c r="A228" t="s">
         <v>3270</v>
       </c>
     </row>
-    <row r="229" spans="1:2" ht="12.6" customHeight="1"/>
-    <row r="230" spans="1:2" ht="12.6" customHeight="1">
+    <row r="229" spans="1:2" ht="12.65" customHeight="1"/>
+    <row r="230" spans="1:2" ht="12.65" customHeight="1">
       <c r="A230" s="469" t="s">
         <v>3271</v>
       </c>
     </row>
-    <row r="231" spans="1:2" ht="12.6" customHeight="1">
+    <row r="231" spans="1:2" ht="12.65" customHeight="1">
       <c r="A231" t="s">
         <v>3272</v>
       </c>
     </row>
-    <row r="232" spans="1:2" ht="12.6" customHeight="1"/>
-    <row r="233" spans="1:2" ht="12.6" customHeight="1">
+    <row r="232" spans="1:2" ht="12.65" customHeight="1"/>
+    <row r="233" spans="1:2" ht="12.65" customHeight="1">
       <c r="A233" s="468" t="s">
         <v>3273</v>
       </c>
     </row>
-    <row r="234" spans="1:2" ht="12.6" customHeight="1">
+    <row r="234" spans="1:2" ht="12.65" customHeight="1">
       <c r="A234" t="s">
         <v>3060</v>
       </c>
@@ -72560,7 +72564,7 @@
         <v>3274</v>
       </c>
     </row>
-    <row r="235" spans="1:2" ht="12.6" customHeight="1">
+    <row r="235" spans="1:2" ht="12.65" customHeight="1">
       <c r="A235" t="s">
         <v>3275</v>
       </c>
@@ -72568,7 +72572,7 @@
         <v>3276</v>
       </c>
     </row>
-    <row r="236" spans="1:2" ht="12.6" customHeight="1">
+    <row r="236" spans="1:2" ht="12.65" customHeight="1">
       <c r="A236" t="s">
         <v>3277</v>
       </c>
@@ -72576,7 +72580,7 @@
         <v>3065</v>
       </c>
     </row>
-    <row r="237" spans="1:2" ht="12.6" customHeight="1">
+    <row r="237" spans="1:2" ht="12.65" customHeight="1">
       <c r="A237" t="s">
         <v>3278</v>
       </c>
@@ -72584,7 +72588,7 @@
         <v>3067</v>
       </c>
     </row>
-    <row r="238" spans="1:2" ht="12.6" customHeight="1">
+    <row r="238" spans="1:2" ht="12.65" customHeight="1">
       <c r="A238" t="s">
         <v>3279</v>
       </c>
@@ -72592,7 +72596,7 @@
         <v>3069</v>
       </c>
     </row>
-    <row r="239" spans="1:2" ht="12.6" customHeight="1">
+    <row r="239" spans="1:2" ht="12.65" customHeight="1">
       <c r="A239" t="s">
         <v>3070</v>
       </c>
@@ -72600,7 +72604,7 @@
         <v>3071</v>
       </c>
     </row>
-    <row r="240" spans="1:2" ht="12.6" customHeight="1">
+    <row r="240" spans="1:2" ht="12.65" customHeight="1">
       <c r="A240" t="s">
         <v>3072</v>
       </c>
@@ -72608,791 +72612,791 @@
         <v>3073</v>
       </c>
     </row>
-    <row r="241" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="242" spans="1:1" ht="12.6" customHeight="1">
+    <row r="241" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="242" spans="1:1" ht="12.65" customHeight="1">
       <c r="A242" s="468" t="s">
         <v>3280</v>
       </c>
     </row>
-    <row r="243" spans="1:1" ht="12.6" customHeight="1">
+    <row r="243" spans="1:1" ht="12.65" customHeight="1">
       <c r="A243" t="s">
         <v>3281</v>
       </c>
     </row>
-    <row r="244" spans="1:1" ht="12.6" customHeight="1">
+    <row r="244" spans="1:1" ht="12.65" customHeight="1">
       <c r="A244" t="s">
         <v>3282</v>
       </c>
     </row>
-    <row r="245" spans="1:1" ht="12.6" customHeight="1">
+    <row r="245" spans="1:1" ht="12.65" customHeight="1">
       <c r="A245" t="s">
         <v>3283</v>
       </c>
     </row>
-    <row r="246" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="247" spans="1:1" ht="12.6" customHeight="1">
+    <row r="246" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="247" spans="1:1" ht="12.65" customHeight="1">
       <c r="A247" s="468" t="s">
         <v>3284</v>
       </c>
     </row>
-    <row r="248" spans="1:1" ht="12.6" customHeight="1">
+    <row r="248" spans="1:1" ht="12.65" customHeight="1">
       <c r="A248" t="s">
         <v>3285</v>
       </c>
     </row>
-    <row r="249" spans="1:1" ht="12.6" customHeight="1">
+    <row r="249" spans="1:1" ht="12.65" customHeight="1">
       <c r="A249" t="s">
         <v>3286</v>
       </c>
     </row>
-    <row r="250" spans="1:1" ht="12.6" customHeight="1">
+    <row r="250" spans="1:1" ht="12.65" customHeight="1">
       <c r="A250" t="s">
         <v>3287</v>
       </c>
     </row>
-    <row r="251" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="252" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="253" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="254" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="255" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="256" spans="1:1" ht="12.6" customHeight="1"/>
-    <row r="257" ht="12.6" customHeight="1"/>
-    <row r="258" ht="12.6" customHeight="1"/>
-    <row r="259" ht="12.6" customHeight="1"/>
-    <row r="260" ht="12.6" customHeight="1"/>
-    <row r="261" ht="12.6" customHeight="1"/>
-    <row r="262" ht="12.6" customHeight="1"/>
-    <row r="263" ht="12.6" customHeight="1"/>
-    <row r="264" ht="12.6" customHeight="1"/>
-    <row r="265" ht="12.6" customHeight="1"/>
-    <row r="266" ht="12.6" customHeight="1"/>
-    <row r="267" ht="12.6" customHeight="1"/>
-    <row r="268" ht="12.6" customHeight="1"/>
-    <row r="269" ht="12.6" customHeight="1"/>
-    <row r="270" ht="12.6" customHeight="1"/>
-    <row r="271" ht="12.6" customHeight="1"/>
-    <row r="272" ht="12.6" customHeight="1"/>
-    <row r="273" ht="12.6" customHeight="1"/>
-    <row r="274" ht="12.6" customHeight="1"/>
-    <row r="275" ht="12.6" customHeight="1"/>
-    <row r="276" ht="12.6" customHeight="1"/>
-    <row r="277" ht="12.6" customHeight="1"/>
-    <row r="278" ht="12.6" customHeight="1"/>
-    <row r="279" ht="12.6" customHeight="1"/>
-    <row r="280" ht="12.6" customHeight="1"/>
-    <row r="281" ht="12.6" customHeight="1"/>
-    <row r="282" ht="12.6" customHeight="1"/>
-    <row r="283" ht="12.6" customHeight="1"/>
-    <row r="284" ht="12.6" customHeight="1"/>
-    <row r="285" ht="12.6" customHeight="1"/>
-    <row r="286" ht="12.6" customHeight="1"/>
-    <row r="287" ht="12.6" customHeight="1"/>
-    <row r="288" ht="12.6" customHeight="1"/>
-    <row r="289" ht="12.6" customHeight="1"/>
-    <row r="290" ht="12.6" customHeight="1"/>
-    <row r="291" ht="12.6" customHeight="1"/>
-    <row r="292" ht="12.6" customHeight="1"/>
-    <row r="293" ht="12.6" customHeight="1"/>
-    <row r="294" ht="12.6" customHeight="1"/>
-    <row r="295" ht="12.6" customHeight="1"/>
-    <row r="296" ht="12.6" customHeight="1"/>
-    <row r="297" ht="12.6" customHeight="1"/>
-    <row r="298" ht="12.6" customHeight="1"/>
-    <row r="299" ht="12.6" customHeight="1"/>
-    <row r="300" ht="12.6" customHeight="1"/>
-    <row r="301" ht="12.6" customHeight="1"/>
-    <row r="302" ht="12.6" customHeight="1"/>
-    <row r="303" ht="12.6" customHeight="1"/>
-    <row r="304" ht="12.6" customHeight="1"/>
-    <row r="305" ht="12.6" customHeight="1"/>
-    <row r="306" ht="12.6" customHeight="1"/>
-    <row r="307" ht="12.6" customHeight="1"/>
-    <row r="308" ht="12.6" customHeight="1"/>
-    <row r="309" ht="12.6" customHeight="1"/>
-    <row r="310" ht="12.6" customHeight="1"/>
-    <row r="311" ht="12.6" customHeight="1"/>
-    <row r="312" ht="12.6" customHeight="1"/>
-    <row r="313" ht="12.6" customHeight="1"/>
-    <row r="314" ht="12.6" customHeight="1"/>
-    <row r="315" ht="12.6" customHeight="1"/>
-    <row r="316" ht="12.6" customHeight="1"/>
-    <row r="317" ht="12.6" customHeight="1"/>
-    <row r="318" ht="12.6" customHeight="1"/>
-    <row r="319" ht="12.6" customHeight="1"/>
-    <row r="320" ht="12.6" customHeight="1"/>
-    <row r="321" ht="12.6" customHeight="1"/>
-    <row r="322" ht="12.6" customHeight="1"/>
-    <row r="323" ht="12.6" customHeight="1"/>
-    <row r="324" ht="12.6" customHeight="1"/>
-    <row r="325" ht="12.6" customHeight="1"/>
-    <row r="326" ht="12.6" customHeight="1"/>
-    <row r="327" ht="12.6" customHeight="1"/>
-    <row r="328" ht="12.6" customHeight="1"/>
-    <row r="329" ht="12.6" customHeight="1"/>
-    <row r="330" ht="12.6" customHeight="1"/>
-    <row r="331" ht="12.6" customHeight="1"/>
-    <row r="332" ht="12.6" customHeight="1"/>
-    <row r="333" ht="12.6" customHeight="1"/>
-    <row r="334" ht="12.6" customHeight="1"/>
-    <row r="335" ht="12.6" customHeight="1"/>
-    <row r="336" ht="12.6" customHeight="1"/>
-    <row r="337" ht="12.6" customHeight="1"/>
-    <row r="338" ht="12.6" customHeight="1"/>
-    <row r="339" ht="12.6" customHeight="1"/>
-    <row r="340" ht="12.6" customHeight="1"/>
-    <row r="341" ht="12.6" customHeight="1"/>
-    <row r="342" ht="12.6" customHeight="1"/>
-    <row r="343" ht="12.6" customHeight="1"/>
-    <row r="344" ht="12.6" customHeight="1"/>
-    <row r="345" ht="12.6" customHeight="1"/>
-    <row r="346" ht="12.6" customHeight="1"/>
-    <row r="347" ht="12.6" customHeight="1"/>
-    <row r="348" ht="12.6" customHeight="1"/>
-    <row r="349" ht="12.6" customHeight="1"/>
-    <row r="350" ht="12.6" customHeight="1"/>
-    <row r="351" ht="12.6" customHeight="1"/>
-    <row r="352" ht="12.6" customHeight="1"/>
-    <row r="353" ht="12.6" customHeight="1"/>
-    <row r="354" ht="12.6" customHeight="1"/>
-    <row r="355" ht="12.6" customHeight="1"/>
-    <row r="356" ht="12.6" customHeight="1"/>
-    <row r="357" ht="12.6" customHeight="1"/>
-    <row r="358" ht="12.6" customHeight="1"/>
-    <row r="359" ht="12.6" customHeight="1"/>
-    <row r="360" ht="12.6" customHeight="1"/>
-    <row r="361" ht="12.6" customHeight="1"/>
-    <row r="362" ht="12.6" customHeight="1"/>
-    <row r="363" ht="12.6" customHeight="1"/>
-    <row r="364" ht="12.6" customHeight="1"/>
-    <row r="365" ht="12.6" customHeight="1"/>
-    <row r="366" ht="12.6" customHeight="1"/>
-    <row r="367" ht="12.6" customHeight="1"/>
-    <row r="368" ht="12.6" customHeight="1"/>
-    <row r="369" ht="12.6" customHeight="1"/>
-    <row r="370" ht="12.6" customHeight="1"/>
-    <row r="371" ht="12.6" customHeight="1"/>
-    <row r="372" ht="12.6" customHeight="1"/>
-    <row r="373" ht="12.6" customHeight="1"/>
-    <row r="374" ht="12.6" customHeight="1"/>
-    <row r="375" ht="12.6" customHeight="1"/>
-    <row r="376" ht="12.6" customHeight="1"/>
-    <row r="377" ht="12.6" customHeight="1"/>
-    <row r="378" ht="12.6" customHeight="1"/>
-    <row r="379" ht="12.6" customHeight="1"/>
-    <row r="380" ht="12.6" customHeight="1"/>
-    <row r="381" ht="12.6" customHeight="1"/>
-    <row r="382" ht="12.6" customHeight="1"/>
-    <row r="383" ht="12.6" customHeight="1"/>
-    <row r="384" ht="12.6" customHeight="1"/>
-    <row r="385" ht="12.6" customHeight="1"/>
-    <row r="386" ht="12.6" customHeight="1"/>
-    <row r="387" ht="12.6" customHeight="1"/>
-    <row r="388" ht="12.6" customHeight="1"/>
-    <row r="389" ht="12.6" customHeight="1"/>
-    <row r="390" ht="12.6" customHeight="1"/>
-    <row r="391" ht="12.6" customHeight="1"/>
-    <row r="392" ht="12.6" customHeight="1"/>
-    <row r="393" ht="12.6" customHeight="1"/>
-    <row r="394" ht="12.6" customHeight="1"/>
-    <row r="395" ht="12.6" customHeight="1"/>
-    <row r="396" ht="12.6" customHeight="1"/>
-    <row r="397" ht="12.6" customHeight="1"/>
-    <row r="398" ht="12.6" customHeight="1"/>
-    <row r="399" ht="12.6" customHeight="1"/>
-    <row r="400" ht="12.6" customHeight="1"/>
-    <row r="401" ht="12.6" customHeight="1"/>
-    <row r="402" ht="12.6" customHeight="1"/>
-    <row r="403" ht="12.6" customHeight="1"/>
-    <row r="404" ht="12.6" customHeight="1"/>
-    <row r="405" ht="12.6" customHeight="1"/>
-    <row r="406" ht="12.6" customHeight="1"/>
-    <row r="407" ht="12.6" customHeight="1"/>
-    <row r="408" ht="12.6" customHeight="1"/>
-    <row r="409" ht="12.6" customHeight="1"/>
-    <row r="410" ht="12.6" customHeight="1"/>
-    <row r="411" ht="12.6" customHeight="1"/>
-    <row r="412" ht="12.6" customHeight="1"/>
-    <row r="413" ht="12.6" customHeight="1"/>
-    <row r="414" ht="12.6" customHeight="1"/>
-    <row r="415" ht="12.6" customHeight="1"/>
-    <row r="416" ht="12.6" customHeight="1"/>
-    <row r="417" ht="12.6" customHeight="1"/>
-    <row r="418" ht="12.6" customHeight="1"/>
-    <row r="419" ht="12.6" customHeight="1"/>
-    <row r="420" ht="12.6" customHeight="1"/>
-    <row r="421" ht="12.6" customHeight="1"/>
-    <row r="422" ht="12.6" customHeight="1"/>
-    <row r="423" ht="12.6" customHeight="1"/>
-    <row r="424" ht="12.6" customHeight="1"/>
-    <row r="425" ht="12.6" customHeight="1"/>
-    <row r="426" ht="12.6" customHeight="1"/>
-    <row r="427" ht="12.6" customHeight="1"/>
-    <row r="428" ht="12.6" customHeight="1"/>
-    <row r="429" ht="12.6" customHeight="1"/>
-    <row r="430" ht="12.6" customHeight="1"/>
-    <row r="431" ht="12.6" customHeight="1"/>
-    <row r="432" ht="12.6" customHeight="1"/>
-    <row r="433" ht="12.6" customHeight="1"/>
-    <row r="434" ht="12.6" customHeight="1"/>
-    <row r="435" ht="12.6" customHeight="1"/>
-    <row r="436" ht="12.6" customHeight="1"/>
-    <row r="437" ht="12.6" customHeight="1"/>
-    <row r="438" ht="12.6" customHeight="1"/>
-    <row r="439" ht="12.6" customHeight="1"/>
-    <row r="440" ht="12.6" customHeight="1"/>
-    <row r="441" ht="12.6" customHeight="1"/>
-    <row r="442" ht="12.6" customHeight="1"/>
-    <row r="443" ht="12.6" customHeight="1"/>
-    <row r="444" ht="12.6" customHeight="1"/>
-    <row r="445" ht="12.6" customHeight="1"/>
-    <row r="446" ht="12.6" customHeight="1"/>
-    <row r="447" ht="12.6" customHeight="1"/>
-    <row r="448" ht="12.6" customHeight="1"/>
-    <row r="449" ht="12.6" customHeight="1"/>
-    <row r="450" ht="12.6" customHeight="1"/>
-    <row r="451" ht="12.6" customHeight="1"/>
-    <row r="452" ht="12.6" customHeight="1"/>
-    <row r="453" ht="12.6" customHeight="1"/>
-    <row r="454" ht="12.6" customHeight="1"/>
-    <row r="455" ht="12.6" customHeight="1"/>
-    <row r="456" ht="12.6" customHeight="1"/>
-    <row r="457" ht="12.6" customHeight="1"/>
-    <row r="458" ht="12.6" customHeight="1"/>
-    <row r="459" ht="12.6" customHeight="1"/>
-    <row r="460" ht="12.6" customHeight="1"/>
-    <row r="461" ht="12.6" customHeight="1"/>
-    <row r="462" ht="12.6" customHeight="1"/>
-    <row r="463" ht="12.6" customHeight="1"/>
-    <row r="464" ht="12.6" customHeight="1"/>
-    <row r="465" ht="12.6" customHeight="1"/>
-    <row r="466" ht="12.6" customHeight="1"/>
-    <row r="467" ht="12.6" customHeight="1"/>
-    <row r="468" ht="12.6" customHeight="1"/>
-    <row r="469" ht="12.6" customHeight="1"/>
-    <row r="470" ht="12.6" customHeight="1"/>
-    <row r="471" ht="12.6" customHeight="1"/>
-    <row r="472" ht="12.6" customHeight="1"/>
-    <row r="473" ht="12.6" customHeight="1"/>
-    <row r="474" ht="12.6" customHeight="1"/>
-    <row r="475" ht="12.6" customHeight="1"/>
-    <row r="476" ht="12.6" customHeight="1"/>
-    <row r="477" ht="12.6" customHeight="1"/>
-    <row r="478" ht="12.6" customHeight="1"/>
-    <row r="479" ht="12.6" customHeight="1"/>
-    <row r="480" ht="12.6" customHeight="1"/>
-    <row r="481" ht="12.6" customHeight="1"/>
-    <row r="482" ht="12.6" customHeight="1"/>
-    <row r="483" ht="12.6" customHeight="1"/>
-    <row r="484" ht="12.6" customHeight="1"/>
-    <row r="485" ht="12.6" customHeight="1"/>
-    <row r="486" ht="12.6" customHeight="1"/>
-    <row r="487" ht="12.6" customHeight="1"/>
-    <row r="488" ht="12.6" customHeight="1"/>
-    <row r="489" ht="12.6" customHeight="1"/>
-    <row r="490" ht="12.6" customHeight="1"/>
-    <row r="491" ht="12.6" customHeight="1"/>
-    <row r="492" ht="12.6" customHeight="1"/>
-    <row r="493" ht="12.6" customHeight="1"/>
-    <row r="494" ht="12.6" customHeight="1"/>
-    <row r="495" ht="12.6" customHeight="1"/>
-    <row r="496" ht="12.6" customHeight="1"/>
-    <row r="497" ht="12.6" customHeight="1"/>
-    <row r="498" ht="12.6" customHeight="1"/>
-    <row r="499" ht="12.6" customHeight="1"/>
-    <row r="500" ht="12.6" customHeight="1"/>
-    <row r="501" ht="12.6" customHeight="1"/>
-    <row r="502" ht="12.6" customHeight="1"/>
-    <row r="503" ht="12.6" customHeight="1"/>
-    <row r="504" ht="12.6" customHeight="1"/>
-    <row r="505" ht="12.6" customHeight="1"/>
-    <row r="506" ht="12.6" customHeight="1"/>
-    <row r="507" ht="12.6" customHeight="1"/>
-    <row r="508" ht="12.6" customHeight="1"/>
-    <row r="509" ht="12.6" customHeight="1"/>
-    <row r="510" ht="12.6" customHeight="1"/>
-    <row r="511" ht="12.6" customHeight="1"/>
-    <row r="512" ht="12.6" customHeight="1"/>
-    <row r="513" ht="12.6" customHeight="1"/>
-    <row r="514" ht="12.6" customHeight="1"/>
-    <row r="515" ht="12.6" customHeight="1"/>
-    <row r="516" ht="12.6" customHeight="1"/>
-    <row r="517" ht="12.6" customHeight="1"/>
-    <row r="518" ht="12.6" customHeight="1"/>
-    <row r="519" ht="12.6" customHeight="1"/>
-    <row r="520" ht="12.6" customHeight="1"/>
-    <row r="521" ht="12.6" customHeight="1"/>
-    <row r="522" ht="12.6" customHeight="1"/>
-    <row r="523" ht="12.6" customHeight="1"/>
-    <row r="524" ht="12.6" customHeight="1"/>
-    <row r="525" ht="12.6" customHeight="1"/>
-    <row r="526" ht="12.6" customHeight="1"/>
-    <row r="527" ht="12.6" customHeight="1"/>
-    <row r="528" ht="12.6" customHeight="1"/>
-    <row r="529" ht="12.6" customHeight="1"/>
-    <row r="530" ht="12.6" customHeight="1"/>
-    <row r="531" ht="12.6" customHeight="1"/>
-    <row r="532" ht="12.6" customHeight="1"/>
-    <row r="533" ht="12.6" customHeight="1"/>
-    <row r="534" ht="12.6" customHeight="1"/>
-    <row r="535" ht="12.6" customHeight="1"/>
-    <row r="536" ht="12.6" customHeight="1"/>
-    <row r="537" ht="12.6" customHeight="1"/>
-    <row r="538" ht="12.6" customHeight="1"/>
-    <row r="539" ht="12.6" customHeight="1"/>
-    <row r="540" ht="12.6" customHeight="1"/>
-    <row r="541" ht="12.6" customHeight="1"/>
-    <row r="542" ht="12.6" customHeight="1"/>
-    <row r="543" ht="12.6" customHeight="1"/>
-    <row r="544" ht="12.6" customHeight="1"/>
-    <row r="545" ht="12.6" customHeight="1"/>
-    <row r="546" ht="12.6" customHeight="1"/>
-    <row r="547" ht="12.6" customHeight="1"/>
-    <row r="548" ht="12.6" customHeight="1"/>
-    <row r="549" ht="12.6" customHeight="1"/>
-    <row r="550" ht="12.6" customHeight="1"/>
-    <row r="551" ht="12.6" customHeight="1"/>
-    <row r="552" ht="12.6" customHeight="1"/>
-    <row r="553" ht="12.6" customHeight="1"/>
-    <row r="554" ht="12.6" customHeight="1"/>
-    <row r="555" ht="12.6" customHeight="1"/>
-    <row r="556" ht="12.6" customHeight="1"/>
-    <row r="557" ht="12.6" customHeight="1"/>
-    <row r="558" ht="12.6" customHeight="1"/>
-    <row r="559" ht="12.6" customHeight="1"/>
-    <row r="560" ht="12.6" customHeight="1"/>
-    <row r="561" ht="12.6" customHeight="1"/>
-    <row r="562" ht="12.6" customHeight="1"/>
-    <row r="563" ht="12.6" customHeight="1"/>
-    <row r="564" ht="12.6" customHeight="1"/>
-    <row r="565" ht="12.6" customHeight="1"/>
-    <row r="566" ht="12.6" customHeight="1"/>
-    <row r="567" ht="12.6" customHeight="1"/>
-    <row r="568" ht="12.6" customHeight="1"/>
-    <row r="569" ht="12.6" customHeight="1"/>
-    <row r="570" ht="12.6" customHeight="1"/>
-    <row r="571" ht="12.6" customHeight="1"/>
-    <row r="572" ht="12.6" customHeight="1"/>
-    <row r="573" ht="12.6" customHeight="1"/>
-    <row r="574" ht="12.6" customHeight="1"/>
-    <row r="575" ht="12.6" customHeight="1"/>
-    <row r="576" ht="12.6" customHeight="1"/>
-    <row r="577" ht="12.6" customHeight="1"/>
-    <row r="578" ht="12.6" customHeight="1"/>
-    <row r="579" ht="12.6" customHeight="1"/>
-    <row r="580" ht="12.6" customHeight="1"/>
-    <row r="581" ht="12.6" customHeight="1"/>
-    <row r="582" ht="12.6" customHeight="1"/>
-    <row r="583" ht="12.6" customHeight="1"/>
-    <row r="584" ht="12.6" customHeight="1"/>
-    <row r="585" ht="12.6" customHeight="1"/>
-    <row r="586" ht="12.6" customHeight="1"/>
-    <row r="587" ht="12.6" customHeight="1"/>
-    <row r="588" ht="12.6" customHeight="1"/>
-    <row r="589" ht="12.6" customHeight="1"/>
-    <row r="590" ht="12.6" customHeight="1"/>
-    <row r="591" ht="12.6" customHeight="1"/>
-    <row r="592" ht="12.6" customHeight="1"/>
-    <row r="593" ht="12.6" customHeight="1"/>
-    <row r="594" ht="12.6" customHeight="1"/>
-    <row r="595" ht="12.6" customHeight="1"/>
-    <row r="596" ht="12.6" customHeight="1"/>
-    <row r="597" ht="12.6" customHeight="1"/>
-    <row r="598" ht="12.6" customHeight="1"/>
-    <row r="599" ht="12.6" customHeight="1"/>
-    <row r="600" ht="12.6" customHeight="1"/>
-    <row r="601" ht="12.6" customHeight="1"/>
-    <row r="602" ht="12.6" customHeight="1"/>
-    <row r="603" ht="12.6" customHeight="1"/>
-    <row r="604" ht="12.6" customHeight="1"/>
-    <row r="605" ht="12.6" customHeight="1"/>
-    <row r="606" ht="12.6" customHeight="1"/>
-    <row r="607" ht="12.6" customHeight="1"/>
-    <row r="608" ht="12.6" customHeight="1"/>
-    <row r="609" ht="12.6" customHeight="1"/>
-    <row r="610" ht="12.6" customHeight="1"/>
-    <row r="611" ht="12.6" customHeight="1"/>
-    <row r="612" ht="12.6" customHeight="1"/>
-    <row r="613" ht="12.6" customHeight="1"/>
-    <row r="614" ht="12.6" customHeight="1"/>
-    <row r="615" ht="12.6" customHeight="1"/>
-    <row r="616" ht="12.6" customHeight="1"/>
-    <row r="617" ht="12.6" customHeight="1"/>
-    <row r="618" ht="12.6" customHeight="1"/>
-    <row r="619" ht="12.6" customHeight="1"/>
-    <row r="620" ht="12.6" customHeight="1"/>
-    <row r="621" ht="12.6" customHeight="1"/>
-    <row r="622" ht="12.6" customHeight="1"/>
-    <row r="623" ht="12.6" customHeight="1"/>
-    <row r="624" ht="12.6" customHeight="1"/>
-    <row r="625" ht="12.6" customHeight="1"/>
-    <row r="626" ht="12.6" customHeight="1"/>
-    <row r="627" ht="12.6" customHeight="1"/>
-    <row r="628" ht="12.6" customHeight="1"/>
-    <row r="629" ht="12.6" customHeight="1"/>
-    <row r="630" ht="12.6" customHeight="1"/>
-    <row r="631" ht="12.6" customHeight="1"/>
-    <row r="632" ht="12.6" customHeight="1"/>
-    <row r="633" ht="12.6" customHeight="1"/>
-    <row r="634" ht="12.6" customHeight="1"/>
-    <row r="635" ht="12.6" customHeight="1"/>
-    <row r="636" ht="12.6" customHeight="1"/>
-    <row r="637" ht="12.6" customHeight="1"/>
-    <row r="638" ht="12.6" customHeight="1"/>
-    <row r="639" ht="12.6" customHeight="1"/>
-    <row r="640" ht="12.6" customHeight="1"/>
-    <row r="641" ht="12.6" customHeight="1"/>
-    <row r="642" ht="12.6" customHeight="1"/>
-    <row r="643" ht="12.6" customHeight="1"/>
-    <row r="644" ht="12.6" customHeight="1"/>
-    <row r="645" ht="12.6" customHeight="1"/>
-    <row r="646" ht="12.6" customHeight="1"/>
-    <row r="647" ht="12.6" customHeight="1"/>
-    <row r="648" ht="12.6" customHeight="1"/>
-    <row r="649" ht="12.6" customHeight="1"/>
-    <row r="650" ht="12.6" customHeight="1"/>
-    <row r="651" ht="12.6" customHeight="1"/>
-    <row r="652" ht="12.6" customHeight="1"/>
-    <row r="653" ht="12.6" customHeight="1"/>
-    <row r="654" ht="12.6" customHeight="1"/>
-    <row r="655" ht="12.6" customHeight="1"/>
-    <row r="656" ht="12.6" customHeight="1"/>
-    <row r="657" ht="12.6" customHeight="1"/>
-    <row r="658" ht="12.6" customHeight="1"/>
-    <row r="659" ht="12.6" customHeight="1"/>
-    <row r="660" ht="12.6" customHeight="1"/>
-    <row r="661" ht="12.6" customHeight="1"/>
-    <row r="662" ht="12.6" customHeight="1"/>
-    <row r="663" ht="12.6" customHeight="1"/>
-    <row r="664" ht="12.6" customHeight="1"/>
-    <row r="665" ht="12.6" customHeight="1"/>
-    <row r="666" ht="12.6" customHeight="1"/>
-    <row r="667" ht="12.6" customHeight="1"/>
-    <row r="668" ht="12.6" customHeight="1"/>
-    <row r="669" ht="12.6" customHeight="1"/>
-    <row r="670" ht="12.6" customHeight="1"/>
-    <row r="671" ht="12.6" customHeight="1"/>
-    <row r="672" ht="12.6" customHeight="1"/>
-    <row r="673" ht="12.6" customHeight="1"/>
-    <row r="674" ht="12.6" customHeight="1"/>
-    <row r="675" ht="12.6" customHeight="1"/>
-    <row r="676" ht="12.6" customHeight="1"/>
-    <row r="677" ht="12.6" customHeight="1"/>
-    <row r="678" ht="12.6" customHeight="1"/>
-    <row r="679" ht="12.6" customHeight="1"/>
-    <row r="680" ht="12.6" customHeight="1"/>
-    <row r="681" ht="12.6" customHeight="1"/>
-    <row r="682" ht="12.6" customHeight="1"/>
-    <row r="683" ht="12.6" customHeight="1"/>
-    <row r="684" ht="12.6" customHeight="1"/>
-    <row r="685" ht="12.6" customHeight="1"/>
-    <row r="686" ht="12.6" customHeight="1"/>
-    <row r="687" ht="12.6" customHeight="1"/>
-    <row r="688" ht="12.6" customHeight="1"/>
-    <row r="689" ht="12.6" customHeight="1"/>
-    <row r="690" ht="12.6" customHeight="1"/>
-    <row r="691" ht="12.6" customHeight="1"/>
-    <row r="692" ht="12.6" customHeight="1"/>
-    <row r="693" ht="12.6" customHeight="1"/>
-    <row r="694" ht="12.6" customHeight="1"/>
-    <row r="695" ht="12.6" customHeight="1"/>
-    <row r="696" ht="12.6" customHeight="1"/>
-    <row r="697" ht="12.6" customHeight="1"/>
-    <row r="698" ht="12.6" customHeight="1"/>
-    <row r="699" ht="12.6" customHeight="1"/>
-    <row r="700" ht="12.6" customHeight="1"/>
-    <row r="701" ht="12.6" customHeight="1"/>
-    <row r="702" ht="12.6" customHeight="1"/>
-    <row r="703" ht="12.6" customHeight="1"/>
-    <row r="704" ht="12.6" customHeight="1"/>
-    <row r="705" ht="12.6" customHeight="1"/>
-    <row r="706" ht="12.6" customHeight="1"/>
-    <row r="707" ht="12.6" customHeight="1"/>
-    <row r="708" ht="12.6" customHeight="1"/>
-    <row r="709" ht="12.6" customHeight="1"/>
-    <row r="710" ht="12.6" customHeight="1"/>
-    <row r="711" ht="12.6" customHeight="1"/>
-    <row r="712" ht="12.6" customHeight="1"/>
-    <row r="713" ht="12.6" customHeight="1"/>
-    <row r="714" ht="12.6" customHeight="1"/>
-    <row r="715" ht="12.6" customHeight="1"/>
-    <row r="716" ht="12.6" customHeight="1"/>
-    <row r="717" ht="12.6" customHeight="1"/>
-    <row r="718" ht="12.6" customHeight="1"/>
-    <row r="719" ht="12.6" customHeight="1"/>
-    <row r="720" ht="12.6" customHeight="1"/>
-    <row r="721" ht="12.6" customHeight="1"/>
-    <row r="722" ht="12.6" customHeight="1"/>
-    <row r="723" ht="12.6" customHeight="1"/>
-    <row r="724" ht="12.6" customHeight="1"/>
-    <row r="725" ht="12.6" customHeight="1"/>
-    <row r="726" ht="12.6" customHeight="1"/>
-    <row r="727" ht="12.6" customHeight="1"/>
-    <row r="728" ht="12.6" customHeight="1"/>
-    <row r="729" ht="12.6" customHeight="1"/>
-    <row r="730" ht="12.6" customHeight="1"/>
-    <row r="731" ht="12.6" customHeight="1"/>
-    <row r="732" ht="12.6" customHeight="1"/>
-    <row r="733" ht="12.6" customHeight="1"/>
-    <row r="734" ht="12.6" customHeight="1"/>
-    <row r="735" ht="12.6" customHeight="1"/>
-    <row r="736" ht="12.6" customHeight="1"/>
-    <row r="737" ht="12.6" customHeight="1"/>
-    <row r="738" ht="12.6" customHeight="1"/>
-    <row r="739" ht="12.6" customHeight="1"/>
-    <row r="740" ht="12.6" customHeight="1"/>
-    <row r="741" ht="12.6" customHeight="1"/>
-    <row r="742" ht="12.6" customHeight="1"/>
-    <row r="743" ht="12.6" customHeight="1"/>
-    <row r="744" ht="12.6" customHeight="1"/>
-    <row r="745" ht="12.6" customHeight="1"/>
-    <row r="746" ht="12.6" customHeight="1"/>
-    <row r="747" ht="12.6" customHeight="1"/>
-    <row r="748" ht="12.6" customHeight="1"/>
-    <row r="749" ht="12.6" customHeight="1"/>
-    <row r="750" ht="12.6" customHeight="1"/>
-    <row r="751" ht="12.6" customHeight="1"/>
-    <row r="752" ht="12.6" customHeight="1"/>
-    <row r="753" ht="12.6" customHeight="1"/>
-    <row r="754" ht="12.6" customHeight="1"/>
-    <row r="755" ht="12.6" customHeight="1"/>
-    <row r="756" ht="12.6" customHeight="1"/>
-    <row r="757" ht="12.6" customHeight="1"/>
-    <row r="758" ht="12.6" customHeight="1"/>
-    <row r="759" ht="12.6" customHeight="1"/>
-    <row r="760" ht="12.6" customHeight="1"/>
-    <row r="761" ht="12.6" customHeight="1"/>
-    <row r="762" ht="12.6" customHeight="1"/>
-    <row r="763" ht="12.6" customHeight="1"/>
-    <row r="764" ht="12.6" customHeight="1"/>
-    <row r="765" ht="12.6" customHeight="1"/>
-    <row r="766" ht="12.6" customHeight="1"/>
-    <row r="767" ht="12.6" customHeight="1"/>
-    <row r="768" ht="12.6" customHeight="1"/>
-    <row r="769" ht="12.6" customHeight="1"/>
-    <row r="770" ht="12.6" customHeight="1"/>
-    <row r="771" ht="12.6" customHeight="1"/>
-    <row r="772" ht="12.6" customHeight="1"/>
-    <row r="773" ht="12.6" customHeight="1"/>
-    <row r="774" ht="12.6" customHeight="1"/>
-    <row r="775" ht="12.6" customHeight="1"/>
-    <row r="776" ht="12.6" customHeight="1"/>
-    <row r="777" ht="12.6" customHeight="1"/>
-    <row r="778" ht="12.6" customHeight="1"/>
-    <row r="779" ht="12.6" customHeight="1"/>
-    <row r="780" ht="12.6" customHeight="1"/>
-    <row r="781" ht="12.6" customHeight="1"/>
-    <row r="782" ht="12.6" customHeight="1"/>
-    <row r="783" ht="12.6" customHeight="1"/>
-    <row r="784" ht="12.6" customHeight="1"/>
-    <row r="785" ht="12.6" customHeight="1"/>
-    <row r="786" ht="12.6" customHeight="1"/>
-    <row r="787" ht="12.6" customHeight="1"/>
-    <row r="788" ht="12.6" customHeight="1"/>
-    <row r="789" ht="12.6" customHeight="1"/>
-    <row r="790" ht="12.6" customHeight="1"/>
-    <row r="791" ht="12.6" customHeight="1"/>
-    <row r="792" ht="12.6" customHeight="1"/>
-    <row r="793" ht="12.6" customHeight="1"/>
-    <row r="794" ht="12.6" customHeight="1"/>
-    <row r="795" ht="12.6" customHeight="1"/>
-    <row r="796" ht="12.6" customHeight="1"/>
-    <row r="797" ht="12.6" customHeight="1"/>
-    <row r="798" ht="12.6" customHeight="1"/>
-    <row r="799" ht="12.6" customHeight="1"/>
-    <row r="800" ht="12.6" customHeight="1"/>
-    <row r="801" ht="12.6" customHeight="1"/>
-    <row r="802" ht="12.6" customHeight="1"/>
-    <row r="803" ht="12.6" customHeight="1"/>
-    <row r="804" ht="12.6" customHeight="1"/>
-    <row r="805" ht="12.6" customHeight="1"/>
-    <row r="806" ht="12.6" customHeight="1"/>
-    <row r="807" ht="12.6" customHeight="1"/>
-    <row r="808" ht="12.6" customHeight="1"/>
-    <row r="809" ht="12.6" customHeight="1"/>
-    <row r="810" ht="12.6" customHeight="1"/>
-    <row r="811" ht="12.6" customHeight="1"/>
-    <row r="812" ht="12.6" customHeight="1"/>
-    <row r="813" ht="12.6" customHeight="1"/>
-    <row r="814" ht="12.6" customHeight="1"/>
-    <row r="815" ht="12.6" customHeight="1"/>
-    <row r="816" ht="12.6" customHeight="1"/>
-    <row r="817" ht="12.6" customHeight="1"/>
-    <row r="818" ht="12.6" customHeight="1"/>
-    <row r="819" ht="12.6" customHeight="1"/>
-    <row r="820" ht="12.6" customHeight="1"/>
-    <row r="821" ht="12.6" customHeight="1"/>
-    <row r="822" ht="12.6" customHeight="1"/>
-    <row r="823" ht="12.6" customHeight="1"/>
-    <row r="824" ht="12.6" customHeight="1"/>
-    <row r="825" ht="12.6" customHeight="1"/>
-    <row r="826" ht="12.6" customHeight="1"/>
-    <row r="827" ht="12.6" customHeight="1"/>
-    <row r="828" ht="12.6" customHeight="1"/>
-    <row r="829" ht="12.6" customHeight="1"/>
-    <row r="830" ht="12.6" customHeight="1"/>
-    <row r="831" ht="12.6" customHeight="1"/>
-    <row r="832" ht="12.6" customHeight="1"/>
-    <row r="833" ht="12.6" customHeight="1"/>
-    <row r="834" ht="12.6" customHeight="1"/>
-    <row r="835" ht="12.6" customHeight="1"/>
-    <row r="836" ht="12.6" customHeight="1"/>
-    <row r="837" ht="12.6" customHeight="1"/>
-    <row r="838" ht="12.6" customHeight="1"/>
-    <row r="839" ht="12.6" customHeight="1"/>
-    <row r="840" ht="12.6" customHeight="1"/>
-    <row r="841" ht="12.6" customHeight="1"/>
-    <row r="842" ht="12.6" customHeight="1"/>
-    <row r="843" ht="12.6" customHeight="1"/>
-    <row r="844" ht="12.6" customHeight="1"/>
-    <row r="845" ht="12.6" customHeight="1"/>
-    <row r="846" ht="12.6" customHeight="1"/>
-    <row r="847" ht="12.6" customHeight="1"/>
-    <row r="848" ht="12.6" customHeight="1"/>
-    <row r="849" ht="12.6" customHeight="1"/>
-    <row r="850" ht="12.6" customHeight="1"/>
-    <row r="851" ht="12.6" customHeight="1"/>
-    <row r="852" ht="12.6" customHeight="1"/>
-    <row r="853" ht="12.6" customHeight="1"/>
-    <row r="854" ht="12.6" customHeight="1"/>
-    <row r="855" ht="12.6" customHeight="1"/>
-    <row r="856" ht="12.6" customHeight="1"/>
-    <row r="857" ht="12.6" customHeight="1"/>
-    <row r="858" ht="12.6" customHeight="1"/>
-    <row r="859" ht="12.6" customHeight="1"/>
-    <row r="860" ht="12.6" customHeight="1"/>
-    <row r="861" ht="12.6" customHeight="1"/>
-    <row r="862" ht="12.6" customHeight="1"/>
-    <row r="863" ht="12.6" customHeight="1"/>
-    <row r="864" ht="12.6" customHeight="1"/>
-    <row r="865" ht="12.6" customHeight="1"/>
-    <row r="866" ht="12.6" customHeight="1"/>
-    <row r="867" ht="12.6" customHeight="1"/>
-    <row r="868" ht="12.6" customHeight="1"/>
-    <row r="869" ht="12.6" customHeight="1"/>
-    <row r="870" ht="12.6" customHeight="1"/>
-    <row r="871" ht="12.6" customHeight="1"/>
-    <row r="872" ht="12.6" customHeight="1"/>
-    <row r="873" ht="12.6" customHeight="1"/>
-    <row r="874" ht="12.6" customHeight="1"/>
-    <row r="875" ht="12.6" customHeight="1"/>
-    <row r="876" ht="12.6" customHeight="1"/>
-    <row r="877" ht="12.6" customHeight="1"/>
-    <row r="878" ht="12.6" customHeight="1"/>
-    <row r="879" ht="12.6" customHeight="1"/>
-    <row r="880" ht="12.6" customHeight="1"/>
-    <row r="881" ht="12.6" customHeight="1"/>
-    <row r="882" ht="12.6" customHeight="1"/>
-    <row r="883" ht="12.6" customHeight="1"/>
-    <row r="884" ht="12.6" customHeight="1"/>
-    <row r="885" ht="12.6" customHeight="1"/>
-    <row r="886" ht="12.6" customHeight="1"/>
-    <row r="887" ht="12.6" customHeight="1"/>
-    <row r="888" ht="12.6" customHeight="1"/>
-    <row r="889" ht="12.6" customHeight="1"/>
-    <row r="890" ht="12.6" customHeight="1"/>
-    <row r="891" ht="12.6" customHeight="1"/>
-    <row r="892" ht="12.6" customHeight="1"/>
-    <row r="893" ht="12.6" customHeight="1"/>
-    <row r="894" ht="12.6" customHeight="1"/>
-    <row r="895" ht="12.6" customHeight="1"/>
-    <row r="896" ht="12.6" customHeight="1"/>
-    <row r="897" ht="12.6" customHeight="1"/>
-    <row r="898" ht="12.6" customHeight="1"/>
-    <row r="899" ht="12.6" customHeight="1"/>
-    <row r="900" ht="12.6" customHeight="1"/>
-    <row r="901" ht="12.6" customHeight="1"/>
-    <row r="902" ht="12.6" customHeight="1"/>
-    <row r="903" ht="12.6" customHeight="1"/>
-    <row r="904" ht="12.6" customHeight="1"/>
-    <row r="905" ht="12.6" customHeight="1"/>
-    <row r="906" ht="12.6" customHeight="1"/>
-    <row r="907" ht="12.6" customHeight="1"/>
-    <row r="908" ht="12.6" customHeight="1"/>
-    <row r="909" ht="12.6" customHeight="1"/>
-    <row r="910" ht="12.6" customHeight="1"/>
-    <row r="911" ht="12.6" customHeight="1"/>
-    <row r="912" ht="12.6" customHeight="1"/>
-    <row r="913" ht="12.6" customHeight="1"/>
-    <row r="914" ht="12.6" customHeight="1"/>
-    <row r="915" ht="12.6" customHeight="1"/>
-    <row r="916" ht="12.6" customHeight="1"/>
-    <row r="917" ht="12.6" customHeight="1"/>
-    <row r="918" ht="12.6" customHeight="1"/>
-    <row r="919" ht="12.6" customHeight="1"/>
-    <row r="920" ht="12.6" customHeight="1"/>
-    <row r="921" ht="12.6" customHeight="1"/>
-    <row r="922" ht="12.6" customHeight="1"/>
-    <row r="923" ht="12.6" customHeight="1"/>
-    <row r="924" ht="12.6" customHeight="1"/>
-    <row r="925" ht="12.6" customHeight="1"/>
-    <row r="926" ht="12.6" customHeight="1"/>
-    <row r="927" ht="12.6" customHeight="1"/>
-    <row r="928" ht="12.6" customHeight="1"/>
-    <row r="929" ht="12.6" customHeight="1"/>
-    <row r="930" ht="12.6" customHeight="1"/>
-    <row r="931" ht="12.6" customHeight="1"/>
-    <row r="932" ht="12.6" customHeight="1"/>
-    <row r="933" ht="12.6" customHeight="1"/>
-    <row r="934" ht="12.6" customHeight="1"/>
-    <row r="935" ht="12.6" customHeight="1"/>
-    <row r="936" ht="12.6" customHeight="1"/>
-    <row r="937" ht="12.6" customHeight="1"/>
-    <row r="938" ht="12.6" customHeight="1"/>
-    <row r="939" ht="12.6" customHeight="1"/>
-    <row r="940" ht="12.6" customHeight="1"/>
-    <row r="941" ht="12.6" customHeight="1"/>
-    <row r="942" ht="12.6" customHeight="1"/>
-    <row r="943" ht="12.6" customHeight="1"/>
-    <row r="944" ht="12.6" customHeight="1"/>
-    <row r="945" ht="12.6" customHeight="1"/>
-    <row r="946" ht="12.6" customHeight="1"/>
-    <row r="947" ht="12.6" customHeight="1"/>
-    <row r="948" ht="12.6" customHeight="1"/>
-    <row r="949" ht="12.6" customHeight="1"/>
-    <row r="950" ht="12.6" customHeight="1"/>
-    <row r="951" ht="12.6" customHeight="1"/>
-    <row r="952" ht="12.6" customHeight="1"/>
-    <row r="953" ht="12.6" customHeight="1"/>
-    <row r="954" ht="12.6" customHeight="1"/>
-    <row r="955" ht="12.6" customHeight="1"/>
-    <row r="956" ht="12.6" customHeight="1"/>
-    <row r="957" ht="12.6" customHeight="1"/>
-    <row r="958" ht="12.6" customHeight="1"/>
-    <row r="959" ht="12.6" customHeight="1"/>
-    <row r="960" ht="12.6" customHeight="1"/>
-    <row r="961" ht="12.6" customHeight="1"/>
-    <row r="962" ht="12.6" customHeight="1"/>
-    <row r="963" ht="12.6" customHeight="1"/>
-    <row r="964" ht="12.6" customHeight="1"/>
-    <row r="965" ht="12.6" customHeight="1"/>
-    <row r="966" ht="12.6" customHeight="1"/>
-    <row r="967" ht="12.6" customHeight="1"/>
-    <row r="968" ht="12.6" customHeight="1"/>
-    <row r="969" ht="12.6" customHeight="1"/>
-    <row r="970" ht="12.6" customHeight="1"/>
-    <row r="971" ht="12.6" customHeight="1"/>
-    <row r="972" ht="12.6" customHeight="1"/>
-    <row r="973" ht="12.6" customHeight="1"/>
-    <row r="974" ht="12.6" customHeight="1"/>
-    <row r="975" ht="12.6" customHeight="1"/>
-    <row r="976" ht="12.6" customHeight="1"/>
-    <row r="977" ht="12.6" customHeight="1"/>
-    <row r="978" ht="12.6" customHeight="1"/>
-    <row r="979" ht="12.6" customHeight="1"/>
-    <row r="980" ht="12.6" customHeight="1"/>
-    <row r="981" ht="12.6" customHeight="1"/>
-    <row r="982" ht="12.6" customHeight="1"/>
-    <row r="983" ht="12.6" customHeight="1"/>
-    <row r="984" ht="12.6" customHeight="1"/>
-    <row r="985" ht="12.6" customHeight="1"/>
-    <row r="986" ht="12.6" customHeight="1"/>
-    <row r="987" ht="12.6" customHeight="1"/>
-    <row r="988" ht="12.6" customHeight="1"/>
-    <row r="989" ht="12.6" customHeight="1"/>
-    <row r="990" ht="12.6" customHeight="1"/>
-    <row r="991" ht="12.6" customHeight="1"/>
-    <row r="992" ht="12.6" customHeight="1"/>
-    <row r="993" ht="12.6" customHeight="1"/>
+    <row r="251" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="252" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="253" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="254" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="255" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="256" spans="1:1" ht="12.65" customHeight="1"/>
+    <row r="257" ht="12.65" customHeight="1"/>
+    <row r="258" ht="12.65" customHeight="1"/>
+    <row r="259" ht="12.65" customHeight="1"/>
+    <row r="260" ht="12.65" customHeight="1"/>
+    <row r="261" ht="12.65" customHeight="1"/>
+    <row r="262" ht="12.65" customHeight="1"/>
+    <row r="263" ht="12.65" customHeight="1"/>
+    <row r="264" ht="12.65" customHeight="1"/>
+    <row r="265" ht="12.65" customHeight="1"/>
+    <row r="266" ht="12.65" customHeight="1"/>
+    <row r="267" ht="12.65" customHeight="1"/>
+    <row r="268" ht="12.65" customHeight="1"/>
+    <row r="269" ht="12.65" customHeight="1"/>
+    <row r="270" ht="12.65" customHeight="1"/>
+    <row r="271" ht="12.65" customHeight="1"/>
+    <row r="272" ht="12.65" customHeight="1"/>
+    <row r="273" ht="12.65" customHeight="1"/>
+    <row r="274" ht="12.65" customHeight="1"/>
+    <row r="275" ht="12.65" customHeight="1"/>
+    <row r="276" ht="12.65" customHeight="1"/>
+    <row r="277" ht="12.65" customHeight="1"/>
+    <row r="278" ht="12.65" customHeight="1"/>
+    <row r="279" ht="12.65" customHeight="1"/>
+    <row r="280" ht="12.65" customHeight="1"/>
+    <row r="281" ht="12.65" customHeight="1"/>
+    <row r="282" ht="12.65" customHeight="1"/>
+    <row r="283" ht="12.65" customHeight="1"/>
+    <row r="284" ht="12.65" customHeight="1"/>
+    <row r="285" ht="12.65" customHeight="1"/>
+    <row r="286" ht="12.65" customHeight="1"/>
+    <row r="287" ht="12.65" customHeight="1"/>
+    <row r="288" ht="12.65" customHeight="1"/>
+    <row r="289" ht="12.65" customHeight="1"/>
+    <row r="290" ht="12.65" customHeight="1"/>
+    <row r="291" ht="12.65" customHeight="1"/>
+    <row r="292" ht="12.65" customHeight="1"/>
+    <row r="293" ht="12.65" customHeight="1"/>
+    <row r="294" ht="12.65" customHeight="1"/>
+    <row r="295" ht="12.65" customHeight="1"/>
+    <row r="296" ht="12.65" customHeight="1"/>
+    <row r="297" ht="12.65" customHeight="1"/>
+    <row r="298" ht="12.65" customHeight="1"/>
+    <row r="299" ht="12.65" customHeight="1"/>
+    <row r="300" ht="12.65" customHeight="1"/>
+    <row r="301" ht="12.65" customHeight="1"/>
+    <row r="302" ht="12.65" customHeight="1"/>
+    <row r="303" ht="12.65" customHeight="1"/>
+    <row r="304" ht="12.65" customHeight="1"/>
+    <row r="305" ht="12.65" customHeight="1"/>
+    <row r="306" ht="12.65" customHeight="1"/>
+    <row r="307" ht="12.65" customHeight="1"/>
+    <row r="308" ht="12.65" customHeight="1"/>
+    <row r="309" ht="12.65" customHeight="1"/>
+    <row r="310" ht="12.65" customHeight="1"/>
+    <row r="311" ht="12.65" customHeight="1"/>
+    <row r="312" ht="12.65" customHeight="1"/>
+    <row r="313" ht="12.65" customHeight="1"/>
+    <row r="314" ht="12.65" customHeight="1"/>
+    <row r="315" ht="12.65" customHeight="1"/>
+    <row r="316" ht="12.65" customHeight="1"/>
+    <row r="317" ht="12.65" customHeight="1"/>
+    <row r="318" ht="12.65" customHeight="1"/>
+    <row r="319" ht="12.65" customHeight="1"/>
+    <row r="320" ht="12.65" customHeight="1"/>
+    <row r="321" ht="12.65" customHeight="1"/>
+    <row r="322" ht="12.65" customHeight="1"/>
+    <row r="323" ht="12.65" customHeight="1"/>
+    <row r="324" ht="12.65" customHeight="1"/>
+    <row r="325" ht="12.65" customHeight="1"/>
+    <row r="326" ht="12.65" customHeight="1"/>
+    <row r="327" ht="12.65" customHeight="1"/>
+    <row r="328" ht="12.65" customHeight="1"/>
+    <row r="329" ht="12.65" customHeight="1"/>
+    <row r="330" ht="12.65" customHeight="1"/>
+    <row r="331" ht="12.65" customHeight="1"/>
+    <row r="332" ht="12.65" customHeight="1"/>
+    <row r="333" ht="12.65" customHeight="1"/>
+    <row r="334" ht="12.65" customHeight="1"/>
+    <row r="335" ht="12.65" customHeight="1"/>
+    <row r="336" ht="12.65" customHeight="1"/>
+    <row r="337" ht="12.65" customHeight="1"/>
+    <row r="338" ht="12.65" customHeight="1"/>
+    <row r="339" ht="12.65" customHeight="1"/>
+    <row r="340" ht="12.65" customHeight="1"/>
+    <row r="341" ht="12.65" customHeight="1"/>
+    <row r="342" ht="12.65" customHeight="1"/>
+    <row r="343" ht="12.65" customHeight="1"/>
+    <row r="344" ht="12.65" customHeight="1"/>
+    <row r="345" ht="12.65" customHeight="1"/>
+    <row r="346" ht="12.65" customHeight="1"/>
+    <row r="347" ht="12.65" customHeight="1"/>
+    <row r="348" ht="12.65" customHeight="1"/>
+    <row r="349" ht="12.65" customHeight="1"/>
+    <row r="350" ht="12.65" customHeight="1"/>
+    <row r="351" ht="12.65" customHeight="1"/>
+    <row r="352" ht="12.65" customHeight="1"/>
+    <row r="353" ht="12.65" customHeight="1"/>
+    <row r="354" ht="12.65" customHeight="1"/>
+    <row r="355" ht="12.65" customHeight="1"/>
+    <row r="356" ht="12.65" customHeight="1"/>
+    <row r="357" ht="12.65" customHeight="1"/>
+    <row r="358" ht="12.65" customHeight="1"/>
+    <row r="359" ht="12.65" customHeight="1"/>
+    <row r="360" ht="12.65" customHeight="1"/>
+    <row r="361" ht="12.65" customHeight="1"/>
+    <row r="362" ht="12.65" customHeight="1"/>
+    <row r="363" ht="12.65" customHeight="1"/>
+    <row r="364" ht="12.65" customHeight="1"/>
+    <row r="365" ht="12.65" customHeight="1"/>
+    <row r="366" ht="12.65" customHeight="1"/>
+    <row r="367" ht="12.65" customHeight="1"/>
+    <row r="368" ht="12.65" customHeight="1"/>
+    <row r="369" ht="12.65" customHeight="1"/>
+    <row r="370" ht="12.65" customHeight="1"/>
+    <row r="371" ht="12.65" customHeight="1"/>
+    <row r="372" ht="12.65" customHeight="1"/>
+    <row r="373" ht="12.65" customHeight="1"/>
+    <row r="374" ht="12.65" customHeight="1"/>
+    <row r="375" ht="12.65" customHeight="1"/>
+    <row r="376" ht="12.65" customHeight="1"/>
+    <row r="377" ht="12.65" customHeight="1"/>
+    <row r="378" ht="12.65" customHeight="1"/>
+    <row r="379" ht="12.65" customHeight="1"/>
+    <row r="380" ht="12.65" customHeight="1"/>
+    <row r="381" ht="12.65" customHeight="1"/>
+    <row r="382" ht="12.65" customHeight="1"/>
+    <row r="383" ht="12.65" customHeight="1"/>
+    <row r="384" ht="12.65" customHeight="1"/>
+    <row r="385" ht="12.65" customHeight="1"/>
+    <row r="386" ht="12.65" customHeight="1"/>
+    <row r="387" ht="12.65" customHeight="1"/>
+    <row r="388" ht="12.65" customHeight="1"/>
+    <row r="389" ht="12.65" customHeight="1"/>
+    <row r="390" ht="12.65" customHeight="1"/>
+    <row r="391" ht="12.65" customHeight="1"/>
+    <row r="392" ht="12.65" customHeight="1"/>
+    <row r="393" ht="12.65" customHeight="1"/>
+    <row r="394" ht="12.65" customHeight="1"/>
+    <row r="395" ht="12.65" customHeight="1"/>
+    <row r="396" ht="12.65" customHeight="1"/>
+    <row r="397" ht="12.65" customHeight="1"/>
+    <row r="398" ht="12.65" customHeight="1"/>
+    <row r="399" ht="12.65" customHeight="1"/>
+    <row r="400" ht="12.65" customHeight="1"/>
+    <row r="401" ht="12.65" customHeight="1"/>
+    <row r="402" ht="12.65" customHeight="1"/>
+    <row r="403" ht="12.65" customHeight="1"/>
+    <row r="404" ht="12.65" customHeight="1"/>
+    <row r="405" ht="12.65" customHeight="1"/>
+    <row r="406" ht="12.65" customHeight="1"/>
+    <row r="407" ht="12.65" customHeight="1"/>
+    <row r="408" ht="12.65" customHeight="1"/>
+    <row r="409" ht="12.65" customHeight="1"/>
+    <row r="410" ht="12.65" customHeight="1"/>
+    <row r="411" ht="12.65" customHeight="1"/>
+    <row r="412" ht="12.65" customHeight="1"/>
+    <row r="413" ht="12.65" customHeight="1"/>
+    <row r="414" ht="12.65" customHeight="1"/>
+    <row r="415" ht="12.65" customHeight="1"/>
+    <row r="416" ht="12.65" customHeight="1"/>
+    <row r="417" ht="12.65" customHeight="1"/>
+    <row r="418" ht="12.65" customHeight="1"/>
+    <row r="419" ht="12.65" customHeight="1"/>
+    <row r="420" ht="12.65" customHeight="1"/>
+    <row r="421" ht="12.65" customHeight="1"/>
+    <row r="422" ht="12.65" customHeight="1"/>
+    <row r="423" ht="12.65" customHeight="1"/>
+    <row r="424" ht="12.65" customHeight="1"/>
+    <row r="425" ht="12.65" customHeight="1"/>
+    <row r="426" ht="12.65" customHeight="1"/>
+    <row r="427" ht="12.65" customHeight="1"/>
+    <row r="428" ht="12.65" customHeight="1"/>
+    <row r="429" ht="12.65" customHeight="1"/>
+    <row r="430" ht="12.65" customHeight="1"/>
+    <row r="431" ht="12.65" customHeight="1"/>
+    <row r="432" ht="12.65" customHeight="1"/>
+    <row r="433" ht="12.65" customHeight="1"/>
+    <row r="434" ht="12.65" customHeight="1"/>
+    <row r="435" ht="12.65" customHeight="1"/>
+    <row r="436" ht="12.65" customHeight="1"/>
+    <row r="437" ht="12.65" customHeight="1"/>
+    <row r="438" ht="12.65" customHeight="1"/>
+    <row r="439" ht="12.65" customHeight="1"/>
+    <row r="440" ht="12.65" customHeight="1"/>
+    <row r="441" ht="12.65" customHeight="1"/>
+    <row r="442" ht="12.65" customHeight="1"/>
+    <row r="443" ht="12.65" customHeight="1"/>
+    <row r="444" ht="12.65" customHeight="1"/>
+    <row r="445" ht="12.65" customHeight="1"/>
+    <row r="446" ht="12.65" customHeight="1"/>
+    <row r="447" ht="12.65" customHeight="1"/>
+    <row r="448" ht="12.65" customHeight="1"/>
+    <row r="449" ht="12.65" customHeight="1"/>
+    <row r="450" ht="12.65" customHeight="1"/>
+    <row r="451" ht="12.65" customHeight="1"/>
+    <row r="452" ht="12.65" customHeight="1"/>
+    <row r="453" ht="12.65" customHeight="1"/>
+    <row r="454" ht="12.65" customHeight="1"/>
+    <row r="455" ht="12.65" customHeight="1"/>
+    <row r="456" ht="12.65" customHeight="1"/>
+    <row r="457" ht="12.65" customHeight="1"/>
+    <row r="458" ht="12.65" customHeight="1"/>
+    <row r="459" ht="12.65" customHeight="1"/>
+    <row r="460" ht="12.65" customHeight="1"/>
+    <row r="461" ht="12.65" customHeight="1"/>
+    <row r="462" ht="12.65" customHeight="1"/>
+    <row r="463" ht="12.65" customHeight="1"/>
+    <row r="464" ht="12.65" customHeight="1"/>
+    <row r="465" ht="12.65" customHeight="1"/>
+    <row r="466" ht="12.65" customHeight="1"/>
+    <row r="467" ht="12.65" customHeight="1"/>
+    <row r="468" ht="12.65" customHeight="1"/>
+    <row r="469" ht="12.65" customHeight="1"/>
+    <row r="470" ht="12.65" customHeight="1"/>
+    <row r="471" ht="12.65" customHeight="1"/>
+    <row r="472" ht="12.65" customHeight="1"/>
+    <row r="473" ht="12.65" customHeight="1"/>
+    <row r="474" ht="12.65" customHeight="1"/>
+    <row r="475" ht="12.65" customHeight="1"/>
+    <row r="476" ht="12.65" customHeight="1"/>
+    <row r="477" ht="12.65" customHeight="1"/>
+    <row r="478" ht="12.65" customHeight="1"/>
+    <row r="479" ht="12.65" customHeight="1"/>
+    <row r="480" ht="12.65" customHeight="1"/>
+    <row r="481" ht="12.65" customHeight="1"/>
+    <row r="482" ht="12.65" customHeight="1"/>
+    <row r="483" ht="12.65" customHeight="1"/>
+    <row r="484" ht="12.65" customHeight="1"/>
+    <row r="485" ht="12.65" customHeight="1"/>
+    <row r="486" ht="12.65" customHeight="1"/>
+    <row r="487" ht="12.65" customHeight="1"/>
+    <row r="488" ht="12.65" customHeight="1"/>
+    <row r="489" ht="12.65" customHeight="1"/>
+    <row r="490" ht="12.65" customHeight="1"/>
+    <row r="491" ht="12.65" customHeight="1"/>
+    <row r="492" ht="12.65" customHeight="1"/>
+    <row r="493" ht="12.65" customHeight="1"/>
+    <row r="494" ht="12.65" customHeight="1"/>
+    <row r="495" ht="12.65" customHeight="1"/>
+    <row r="496" ht="12.65" customHeight="1"/>
+    <row r="497" ht="12.65" customHeight="1"/>
+    <row r="498" ht="12.65" customHeight="1"/>
+    <row r="499" ht="12.65" customHeight="1"/>
+    <row r="500" ht="12.65" customHeight="1"/>
+    <row r="501" ht="12.65" customHeight="1"/>
+    <row r="502" ht="12.65" customHeight="1"/>
+    <row r="503" ht="12.65" customHeight="1"/>
+    <row r="504" ht="12.65" customHeight="1"/>
+    <row r="505" ht="12.65" customHeight="1"/>
+    <row r="506" ht="12.65" customHeight="1"/>
+    <row r="507" ht="12.65" customHeight="1"/>
+    <row r="508" ht="12.65" customHeight="1"/>
+    <row r="509" ht="12.65" customHeight="1"/>
+    <row r="510" ht="12.65" customHeight="1"/>
+    <row r="511" ht="12.65" customHeight="1"/>
+    <row r="512" ht="12.65" customHeight="1"/>
+    <row r="513" ht="12.65" customHeight="1"/>
+    <row r="514" ht="12.65" customHeight="1"/>
+    <row r="515" ht="12.65" customHeight="1"/>
+    <row r="516" ht="12.65" customHeight="1"/>
+    <row r="517" ht="12.65" customHeight="1"/>
+    <row r="518" ht="12.65" customHeight="1"/>
+    <row r="519" ht="12.65" customHeight="1"/>
+    <row r="520" ht="12.65" customHeight="1"/>
+    <row r="521" ht="12.65" customHeight="1"/>
+    <row r="522" ht="12.65" customHeight="1"/>
+    <row r="523" ht="12.65" customHeight="1"/>
+    <row r="524" ht="12.65" customHeight="1"/>
+    <row r="525" ht="12.65" customHeight="1"/>
+    <row r="526" ht="12.65" customHeight="1"/>
+    <row r="527" ht="12.65" customHeight="1"/>
+    <row r="528" ht="12.65" customHeight="1"/>
+    <row r="529" ht="12.65" customHeight="1"/>
+    <row r="530" ht="12.65" customHeight="1"/>
+    <row r="531" ht="12.65" customHeight="1"/>
+    <row r="532" ht="12.65" customHeight="1"/>
+    <row r="533" ht="12.65" customHeight="1"/>
+    <row r="534" ht="12.65" customHeight="1"/>
+    <row r="535" ht="12.65" customHeight="1"/>
+    <row r="536" ht="12.65" customHeight="1"/>
+    <row r="537" ht="12.65" customHeight="1"/>
+    <row r="538" ht="12.65" customHeight="1"/>
+    <row r="539" ht="12.65" customHeight="1"/>
+    <row r="540" ht="12.65" customHeight="1"/>
+    <row r="541" ht="12.65" customHeight="1"/>
+    <row r="542" ht="12.65" customHeight="1"/>
+    <row r="543" ht="12.65" customHeight="1"/>
+    <row r="544" ht="12.65" customHeight="1"/>
+    <row r="545" ht="12.65" customHeight="1"/>
+    <row r="546" ht="12.65" customHeight="1"/>
+    <row r="547" ht="12.65" customHeight="1"/>
+    <row r="548" ht="12.65" customHeight="1"/>
+    <row r="549" ht="12.65" customHeight="1"/>
+    <row r="550" ht="12.65" customHeight="1"/>
+    <row r="551" ht="12.65" customHeight="1"/>
+    <row r="552" ht="12.65" customHeight="1"/>
+    <row r="553" ht="12.65" customHeight="1"/>
+    <row r="554" ht="12.65" customHeight="1"/>
+    <row r="555" ht="12.65" customHeight="1"/>
+    <row r="556" ht="12.65" customHeight="1"/>
+    <row r="557" ht="12.65" customHeight="1"/>
+    <row r="558" ht="12.65" customHeight="1"/>
+    <row r="559" ht="12.65" customHeight="1"/>
+    <row r="560" ht="12.65" customHeight="1"/>
+    <row r="561" ht="12.65" customHeight="1"/>
+    <row r="562" ht="12.65" customHeight="1"/>
+    <row r="563" ht="12.65" customHeight="1"/>
+    <row r="564" ht="12.65" customHeight="1"/>
+    <row r="565" ht="12.65" customHeight="1"/>
+    <row r="566" ht="12.65" customHeight="1"/>
+    <row r="567" ht="12.65" customHeight="1"/>
+    <row r="568" ht="12.65" customHeight="1"/>
+    <row r="569" ht="12.65" customHeight="1"/>
+    <row r="570" ht="12.65" customHeight="1"/>
+    <row r="571" ht="12.65" customHeight="1"/>
+    <row r="572" ht="12.65" customHeight="1"/>
+    <row r="573" ht="12.65" customHeight="1"/>
+    <row r="574" ht="12.65" customHeight="1"/>
+    <row r="575" ht="12.65" customHeight="1"/>
+    <row r="576" ht="12.65" customHeight="1"/>
+    <row r="577" ht="12.65" customHeight="1"/>
+    <row r="578" ht="12.65" customHeight="1"/>
+    <row r="579" ht="12.65" customHeight="1"/>
+    <row r="580" ht="12.65" customHeight="1"/>
+    <row r="581" ht="12.65" customHeight="1"/>
+    <row r="582" ht="12.65" customHeight="1"/>
+    <row r="583" ht="12.65" customHeight="1"/>
+    <row r="584" ht="12.65" customHeight="1"/>
+    <row r="585" ht="12.65" customHeight="1"/>
+    <row r="586" ht="12.65" customHeight="1"/>
+    <row r="587" ht="12.65" customHeight="1"/>
+    <row r="588" ht="12.65" customHeight="1"/>
+    <row r="589" ht="12.65" customHeight="1"/>
+    <row r="590" ht="12.65" customHeight="1"/>
+    <row r="591" ht="12.65" customHeight="1"/>
+    <row r="592" ht="12.65" customHeight="1"/>
+    <row r="593" ht="12.65" customHeight="1"/>
+    <row r="594" ht="12.65" customHeight="1"/>
+    <row r="595" ht="12.65" customHeight="1"/>
+    <row r="596" ht="12.65" customHeight="1"/>
+    <row r="597" ht="12.65" customHeight="1"/>
+    <row r="598" ht="12.65" customHeight="1"/>
+    <row r="599" ht="12.65" customHeight="1"/>
+    <row r="600" ht="12.65" customHeight="1"/>
+    <row r="601" ht="12.65" customHeight="1"/>
+    <row r="602" ht="12.65" customHeight="1"/>
+    <row r="603" ht="12.65" customHeight="1"/>
+    <row r="604" ht="12.65" customHeight="1"/>
+    <row r="605" ht="12.65" customHeight="1"/>
+    <row r="606" ht="12.65" customHeight="1"/>
+    <row r="607" ht="12.65" customHeight="1"/>
+    <row r="608" ht="12.65" customHeight="1"/>
+    <row r="609" ht="12.65" customHeight="1"/>
+    <row r="610" ht="12.65" customHeight="1"/>
+    <row r="611" ht="12.65" customHeight="1"/>
+    <row r="612" ht="12.65" customHeight="1"/>
+    <row r="613" ht="12.65" customHeight="1"/>
+    <row r="614" ht="12.65" customHeight="1"/>
+    <row r="615" ht="12.65" customHeight="1"/>
+    <row r="616" ht="12.65" customHeight="1"/>
+    <row r="617" ht="12.65" customHeight="1"/>
+    <row r="618" ht="12.65" customHeight="1"/>
+    <row r="619" ht="12.65" customHeight="1"/>
+    <row r="620" ht="12.65" customHeight="1"/>
+    <row r="621" ht="12.65" customHeight="1"/>
+    <row r="622" ht="12.65" customHeight="1"/>
+    <row r="623" ht="12.65" customHeight="1"/>
+    <row r="624" ht="12.65" customHeight="1"/>
+    <row r="625" ht="12.65" customHeight="1"/>
+    <row r="626" ht="12.65" customHeight="1"/>
+    <row r="627" ht="12.65" customHeight="1"/>
+    <row r="628" ht="12.65" customHeight="1"/>
+    <row r="629" ht="12.65" customHeight="1"/>
+    <row r="630" ht="12.65" customHeight="1"/>
+    <row r="631" ht="12.65" customHeight="1"/>
+    <row r="632" ht="12.65" customHeight="1"/>
+    <row r="633" ht="12.65" customHeight="1"/>
+    <row r="634" ht="12.65" customHeight="1"/>
+    <row r="635" ht="12.65" customHeight="1"/>
+    <row r="636" ht="12.65" customHeight="1"/>
+    <row r="637" ht="12.65" customHeight="1"/>
+    <row r="638" ht="12.65" customHeight="1"/>
+    <row r="639" ht="12.65" customHeight="1"/>
+    <row r="640" ht="12.65" customHeight="1"/>
+    <row r="641" ht="12.65" customHeight="1"/>
+    <row r="642" ht="12.65" customHeight="1"/>
+    <row r="643" ht="12.65" customHeight="1"/>
+    <row r="644" ht="12.65" customHeight="1"/>
+    <row r="645" ht="12.65" customHeight="1"/>
+    <row r="646" ht="12.65" customHeight="1"/>
+    <row r="647" ht="12.65" customHeight="1"/>
+    <row r="648" ht="12.65" customHeight="1"/>
+    <row r="649" ht="12.65" customHeight="1"/>
+    <row r="650" ht="12.65" customHeight="1"/>
+    <row r="651" ht="12.65" customHeight="1"/>
+    <row r="652" ht="12.65" customHeight="1"/>
+    <row r="653" ht="12.65" customHeight="1"/>
+    <row r="654" ht="12.65" customHeight="1"/>
+    <row r="655" ht="12.65" customHeight="1"/>
+    <row r="656" ht="12.65" customHeight="1"/>
+    <row r="657" ht="12.65" customHeight="1"/>
+    <row r="658" ht="12.65" customHeight="1"/>
+    <row r="659" ht="12.65" customHeight="1"/>
+    <row r="660" ht="12.65" customHeight="1"/>
+    <row r="661" ht="12.65" customHeight="1"/>
+    <row r="662" ht="12.65" customHeight="1"/>
+    <row r="663" ht="12.65" customHeight="1"/>
+    <row r="664" ht="12.65" customHeight="1"/>
+    <row r="665" ht="12.65" customHeight="1"/>
+    <row r="666" ht="12.65" customHeight="1"/>
+    <row r="667" ht="12.65" customHeight="1"/>
+    <row r="668" ht="12.65" customHeight="1"/>
+    <row r="669" ht="12.65" customHeight="1"/>
+    <row r="670" ht="12.65" customHeight="1"/>
+    <row r="671" ht="12.65" customHeight="1"/>
+    <row r="672" ht="12.65" customHeight="1"/>
+    <row r="673" ht="12.65" customHeight="1"/>
+    <row r="674" ht="12.65" customHeight="1"/>
+    <row r="675" ht="12.65" customHeight="1"/>
+    <row r="676" ht="12.65" customHeight="1"/>
+    <row r="677" ht="12.65" customHeight="1"/>
+    <row r="678" ht="12.65" customHeight="1"/>
+    <row r="679" ht="12.65" customHeight="1"/>
+    <row r="680" ht="12.65" customHeight="1"/>
+    <row r="681" ht="12.65" customHeight="1"/>
+    <row r="682" ht="12.65" customHeight="1"/>
+    <row r="683" ht="12.65" customHeight="1"/>
+    <row r="684" ht="12.65" customHeight="1"/>
+    <row r="685" ht="12.65" customHeight="1"/>
+    <row r="686" ht="12.65" customHeight="1"/>
+    <row r="687" ht="12.65" customHeight="1"/>
+    <row r="688" ht="12.65" customHeight="1"/>
+    <row r="689" ht="12.65" customHeight="1"/>
+    <row r="690" ht="12.65" customHeight="1"/>
+    <row r="691" ht="12.65" customHeight="1"/>
+    <row r="692" ht="12.65" customHeight="1"/>
+    <row r="693" ht="12.65" customHeight="1"/>
+    <row r="694" ht="12.65" customHeight="1"/>
+    <row r="695" ht="12.65" customHeight="1"/>
+    <row r="696" ht="12.65" customHeight="1"/>
+    <row r="697" ht="12.65" customHeight="1"/>
+    <row r="698" ht="12.65" customHeight="1"/>
+    <row r="699" ht="12.65" customHeight="1"/>
+    <row r="700" ht="12.65" customHeight="1"/>
+    <row r="701" ht="12.65" customHeight="1"/>
+    <row r="702" ht="12.65" customHeight="1"/>
+    <row r="703" ht="12.65" customHeight="1"/>
+    <row r="704" ht="12.65" customHeight="1"/>
+    <row r="705" ht="12.65" customHeight="1"/>
+    <row r="706" ht="12.65" customHeight="1"/>
+    <row r="707" ht="12.65" customHeight="1"/>
+    <row r="708" ht="12.65" customHeight="1"/>
+    <row r="709" ht="12.65" customHeight="1"/>
+    <row r="710" ht="12.65" customHeight="1"/>
+    <row r="711" ht="12.65" customHeight="1"/>
+    <row r="712" ht="12.65" customHeight="1"/>
+    <row r="713" ht="12.65" customHeight="1"/>
+    <row r="714" ht="12.65" customHeight="1"/>
+    <row r="715" ht="12.65" customHeight="1"/>
+    <row r="716" ht="12.65" customHeight="1"/>
+    <row r="717" ht="12.65" customHeight="1"/>
+    <row r="718" ht="12.65" customHeight="1"/>
+    <row r="719" ht="12.65" customHeight="1"/>
+    <row r="720" ht="12.65" customHeight="1"/>
+    <row r="721" ht="12.65" customHeight="1"/>
+    <row r="722" ht="12.65" customHeight="1"/>
+    <row r="723" ht="12.65" customHeight="1"/>
+    <row r="724" ht="12.65" customHeight="1"/>
+    <row r="725" ht="12.65" customHeight="1"/>
+    <row r="726" ht="12.65" customHeight="1"/>
+    <row r="727" ht="12.65" customHeight="1"/>
+    <row r="728" ht="12.65" customHeight="1"/>
+    <row r="729" ht="12.65" customHeight="1"/>
+    <row r="730" ht="12.65" customHeight="1"/>
+    <row r="731" ht="12.65" customHeight="1"/>
+    <row r="732" ht="12.65" customHeight="1"/>
+    <row r="733" ht="12.65" customHeight="1"/>
+    <row r="734" ht="12.65" customHeight="1"/>
+    <row r="735" ht="12.65" customHeight="1"/>
+    <row r="736" ht="12.65" customHeight="1"/>
+    <row r="737" ht="12.65" customHeight="1"/>
+    <row r="738" ht="12.65" customHeight="1"/>
+    <row r="739" ht="12.65" customHeight="1"/>
+    <row r="740" ht="12.65" customHeight="1"/>
+    <row r="741" ht="12.65" customHeight="1"/>
+    <row r="742" ht="12.65" customHeight="1"/>
+    <row r="743" ht="12.65" customHeight="1"/>
+    <row r="744" ht="12.65" customHeight="1"/>
+    <row r="745" ht="12.65" customHeight="1"/>
+    <row r="746" ht="12.65" customHeight="1"/>
+    <row r="747" ht="12.65" customHeight="1"/>
+    <row r="748" ht="12.65" customHeight="1"/>
+    <row r="749" ht="12.65" customHeight="1"/>
+    <row r="750" ht="12.65" customHeight="1"/>
+    <row r="751" ht="12.65" customHeight="1"/>
+    <row r="752" ht="12.65" customHeight="1"/>
+    <row r="753" ht="12.65" customHeight="1"/>
+    <row r="754" ht="12.65" customHeight="1"/>
+    <row r="755" ht="12.65" customHeight="1"/>
+    <row r="756" ht="12.65" customHeight="1"/>
+    <row r="757" ht="12.65" customHeight="1"/>
+    <row r="758" ht="12.65" customHeight="1"/>
+    <row r="759" ht="12.65" customHeight="1"/>
+    <row r="760" ht="12.65" customHeight="1"/>
+    <row r="761" ht="12.65" customHeight="1"/>
+    <row r="762" ht="12.65" customHeight="1"/>
+    <row r="763" ht="12.65" customHeight="1"/>
+    <row r="764" ht="12.65" customHeight="1"/>
+    <row r="765" ht="12.65" customHeight="1"/>
+    <row r="766" ht="12.65" customHeight="1"/>
+    <row r="767" ht="12.65" customHeight="1"/>
+    <row r="768" ht="12.65" customHeight="1"/>
+    <row r="769" ht="12.65" customHeight="1"/>
+    <row r="770" ht="12.65" customHeight="1"/>
+    <row r="771" ht="12.65" customHeight="1"/>
+    <row r="772" ht="12.65" customHeight="1"/>
+    <row r="773" ht="12.65" customHeight="1"/>
+    <row r="774" ht="12.65" customHeight="1"/>
+    <row r="775" ht="12.65" customHeight="1"/>
+    <row r="776" ht="12.65" customHeight="1"/>
+    <row r="777" ht="12.65" customHeight="1"/>
+    <row r="778" ht="12.65" customHeight="1"/>
+    <row r="779" ht="12.65" customHeight="1"/>
+    <row r="780" ht="12.65" customHeight="1"/>
+    <row r="781" ht="12.65" customHeight="1"/>
+    <row r="782" ht="12.65" customHeight="1"/>
+    <row r="783" ht="12.65" customHeight="1"/>
+    <row r="784" ht="12.65" customHeight="1"/>
+    <row r="785" ht="12.65" customHeight="1"/>
+    <row r="786" ht="12.65" customHeight="1"/>
+    <row r="787" ht="12.65" customHeight="1"/>
+    <row r="788" ht="12.65" customHeight="1"/>
+    <row r="789" ht="12.65" customHeight="1"/>
+    <row r="790" ht="12.65" customHeight="1"/>
+    <row r="791" ht="12.65" customHeight="1"/>
+    <row r="792" ht="12.65" customHeight="1"/>
+    <row r="793" ht="12.65" customHeight="1"/>
+    <row r="794" ht="12.65" customHeight="1"/>
+    <row r="795" ht="12.65" customHeight="1"/>
+    <row r="796" ht="12.65" customHeight="1"/>
+    <row r="797" ht="12.65" customHeight="1"/>
+    <row r="798" ht="12.65" customHeight="1"/>
+    <row r="799" ht="12.65" customHeight="1"/>
+    <row r="800" ht="12.65" customHeight="1"/>
+    <row r="801" ht="12.65" customHeight="1"/>
+    <row r="802" ht="12.65" customHeight="1"/>
+    <row r="803" ht="12.65" customHeight="1"/>
+    <row r="804" ht="12.65" customHeight="1"/>
+    <row r="805" ht="12.65" customHeight="1"/>
+    <row r="806" ht="12.65" customHeight="1"/>
+    <row r="807" ht="12.65" customHeight="1"/>
+    <row r="808" ht="12.65" customHeight="1"/>
+    <row r="809" ht="12.65" customHeight="1"/>
+    <row r="810" ht="12.65" customHeight="1"/>
+    <row r="811" ht="12.65" customHeight="1"/>
+    <row r="812" ht="12.65" customHeight="1"/>
+    <row r="813" ht="12.65" customHeight="1"/>
+    <row r="814" ht="12.65" customHeight="1"/>
+    <row r="815" ht="12.65" customHeight="1"/>
+    <row r="816" ht="12.65" customHeight="1"/>
+    <row r="817" ht="12.65" customHeight="1"/>
+    <row r="818" ht="12.65" customHeight="1"/>
+    <row r="819" ht="12.65" customHeight="1"/>
+    <row r="820" ht="12.65" customHeight="1"/>
+    <row r="821" ht="12.65" customHeight="1"/>
+    <row r="822" ht="12.65" customHeight="1"/>
+    <row r="823" ht="12.65" customHeight="1"/>
+    <row r="824" ht="12.65" customHeight="1"/>
+    <row r="825" ht="12.65" customHeight="1"/>
+    <row r="826" ht="12.65" customHeight="1"/>
+    <row r="827" ht="12.65" customHeight="1"/>
+    <row r="828" ht="12.65" customHeight="1"/>
+    <row r="829" ht="12.65" customHeight="1"/>
+    <row r="830" ht="12.65" customHeight="1"/>
+    <row r="831" ht="12.65" customHeight="1"/>
+    <row r="832" ht="12.65" customHeight="1"/>
+    <row r="833" ht="12.65" customHeight="1"/>
+    <row r="834" ht="12.65" customHeight="1"/>
+    <row r="835" ht="12.65" customHeight="1"/>
+    <row r="836" ht="12.65" customHeight="1"/>
+    <row r="837" ht="12.65" customHeight="1"/>
+    <row r="838" ht="12.65" customHeight="1"/>
+    <row r="839" ht="12.65" customHeight="1"/>
+    <row r="840" ht="12.65" customHeight="1"/>
+    <row r="841" ht="12.65" customHeight="1"/>
+    <row r="842" ht="12.65" customHeight="1"/>
+    <row r="843" ht="12.65" customHeight="1"/>
+    <row r="844" ht="12.65" customHeight="1"/>
+    <row r="845" ht="12.65" customHeight="1"/>
+    <row r="846" ht="12.65" customHeight="1"/>
+    <row r="847" ht="12.65" customHeight="1"/>
+    <row r="848" ht="12.65" customHeight="1"/>
+    <row r="849" ht="12.65" customHeight="1"/>
+    <row r="850" ht="12.65" customHeight="1"/>
+    <row r="851" ht="12.65" customHeight="1"/>
+    <row r="852" ht="12.65" customHeight="1"/>
+    <row r="853" ht="12.65" customHeight="1"/>
+    <row r="854" ht="12.65" customHeight="1"/>
+    <row r="855" ht="12.65" customHeight="1"/>
+    <row r="856" ht="12.65" customHeight="1"/>
+    <row r="857" ht="12.65" customHeight="1"/>
+    <row r="858" ht="12.65" customHeight="1"/>
+    <row r="859" ht="12.65" customHeight="1"/>
+    <row r="860" ht="12.65" customHeight="1"/>
+    <row r="861" ht="12.65" customHeight="1"/>
+    <row r="862" ht="12.65" customHeight="1"/>
+    <row r="863" ht="12.65" customHeight="1"/>
+    <row r="864" ht="12.65" customHeight="1"/>
+    <row r="865" ht="12.65" customHeight="1"/>
+    <row r="866" ht="12.65" customHeight="1"/>
+    <row r="867" ht="12.65" customHeight="1"/>
+    <row r="868" ht="12.65" customHeight="1"/>
+    <row r="869" ht="12.65" customHeight="1"/>
+    <row r="870" ht="12.65" customHeight="1"/>
+    <row r="871" ht="12.65" customHeight="1"/>
+    <row r="872" ht="12.65" customHeight="1"/>
+    <row r="873" ht="12.65" customHeight="1"/>
+    <row r="874" ht="12.65" customHeight="1"/>
+    <row r="875" ht="12.65" customHeight="1"/>
+    <row r="876" ht="12.65" customHeight="1"/>
+    <row r="877" ht="12.65" customHeight="1"/>
+    <row r="878" ht="12.65" customHeight="1"/>
+    <row r="879" ht="12.65" customHeight="1"/>
+    <row r="880" ht="12.65" customHeight="1"/>
+    <row r="881" ht="12.65" customHeight="1"/>
+    <row r="882" ht="12.65" customHeight="1"/>
+    <row r="883" ht="12.65" customHeight="1"/>
+    <row r="884" ht="12.65" customHeight="1"/>
+    <row r="885" ht="12.65" customHeight="1"/>
+    <row r="886" ht="12.65" customHeight="1"/>
+    <row r="887" ht="12.65" customHeight="1"/>
+    <row r="888" ht="12.65" customHeight="1"/>
+    <row r="889" ht="12.65" customHeight="1"/>
+    <row r="890" ht="12.65" customHeight="1"/>
+    <row r="891" ht="12.65" customHeight="1"/>
+    <row r="892" ht="12.65" customHeight="1"/>
+    <row r="893" ht="12.65" customHeight="1"/>
+    <row r="894" ht="12.65" customHeight="1"/>
+    <row r="895" ht="12.65" customHeight="1"/>
+    <row r="896" ht="12.65" customHeight="1"/>
+    <row r="897" ht="12.65" customHeight="1"/>
+    <row r="898" ht="12.65" customHeight="1"/>
+    <row r="899" ht="12.65" customHeight="1"/>
+    <row r="900" ht="12.65" customHeight="1"/>
+    <row r="901" ht="12.65" customHeight="1"/>
+    <row r="902" ht="12.65" customHeight="1"/>
+    <row r="903" ht="12.65" customHeight="1"/>
+    <row r="904" ht="12.65" customHeight="1"/>
+    <row r="905" ht="12.65" customHeight="1"/>
+    <row r="906" ht="12.65" customHeight="1"/>
+    <row r="907" ht="12.65" customHeight="1"/>
+    <row r="908" ht="12.65" customHeight="1"/>
+    <row r="909" ht="12.65" customHeight="1"/>
+    <row r="910" ht="12.65" customHeight="1"/>
+    <row r="911" ht="12.65" customHeight="1"/>
+    <row r="912" ht="12.65" customHeight="1"/>
+    <row r="913" ht="12.65" customHeight="1"/>
+    <row r="914" ht="12.65" customHeight="1"/>
+    <row r="915" ht="12.65" customHeight="1"/>
+    <row r="916" ht="12.65" customHeight="1"/>
+    <row r="917" ht="12.65" customHeight="1"/>
+    <row r="918" ht="12.65" customHeight="1"/>
+    <row r="919" ht="12.65" customHeight="1"/>
+    <row r="920" ht="12.65" customHeight="1"/>
+    <row r="921" ht="12.65" customHeight="1"/>
+    <row r="922" ht="12.65" customHeight="1"/>
+    <row r="923" ht="12.65" customHeight="1"/>
+    <row r="924" ht="12.65" customHeight="1"/>
+    <row r="925" ht="12.65" customHeight="1"/>
+    <row r="926" ht="12.65" customHeight="1"/>
+    <row r="927" ht="12.65" customHeight="1"/>
+    <row r="928" ht="12.65" customHeight="1"/>
+    <row r="929" ht="12.65" customHeight="1"/>
+    <row r="930" ht="12.65" customHeight="1"/>
+    <row r="931" ht="12.65" customHeight="1"/>
+    <row r="932" ht="12.65" customHeight="1"/>
+    <row r="933" ht="12.65" customHeight="1"/>
+    <row r="934" ht="12.65" customHeight="1"/>
+    <row r="935" ht="12.65" customHeight="1"/>
+    <row r="936" ht="12.65" customHeight="1"/>
+    <row r="937" ht="12.65" customHeight="1"/>
+    <row r="938" ht="12.65" customHeight="1"/>
+    <row r="939" ht="12.65" customHeight="1"/>
+    <row r="940" ht="12.65" customHeight="1"/>
+    <row r="941" ht="12.65" customHeight="1"/>
+    <row r="942" ht="12.65" customHeight="1"/>
+    <row r="943" ht="12.65" customHeight="1"/>
+    <row r="944" ht="12.65" customHeight="1"/>
+    <row r="945" ht="12.65" customHeight="1"/>
+    <row r="946" ht="12.65" customHeight="1"/>
+    <row r="947" ht="12.65" customHeight="1"/>
+    <row r="948" ht="12.65" customHeight="1"/>
+    <row r="949" ht="12.65" customHeight="1"/>
+    <row r="950" ht="12.65" customHeight="1"/>
+    <row r="951" ht="12.65" customHeight="1"/>
+    <row r="952" ht="12.65" customHeight="1"/>
+    <row r="953" ht="12.65" customHeight="1"/>
+    <row r="954" ht="12.65" customHeight="1"/>
+    <row r="955" ht="12.65" customHeight="1"/>
+    <row r="956" ht="12.65" customHeight="1"/>
+    <row r="957" ht="12.65" customHeight="1"/>
+    <row r="958" ht="12.65" customHeight="1"/>
+    <row r="959" ht="12.65" customHeight="1"/>
+    <row r="960" ht="12.65" customHeight="1"/>
+    <row r="961" ht="12.65" customHeight="1"/>
+    <row r="962" ht="12.65" customHeight="1"/>
+    <row r="963" ht="12.65" customHeight="1"/>
+    <row r="964" ht="12.65" customHeight="1"/>
+    <row r="965" ht="12.65" customHeight="1"/>
+    <row r="966" ht="12.65" customHeight="1"/>
+    <row r="967" ht="12.65" customHeight="1"/>
+    <row r="968" ht="12.65" customHeight="1"/>
+    <row r="969" ht="12.65" customHeight="1"/>
+    <row r="970" ht="12.65" customHeight="1"/>
+    <row r="971" ht="12.65" customHeight="1"/>
+    <row r="972" ht="12.65" customHeight="1"/>
+    <row r="973" ht="12.65" customHeight="1"/>
+    <row r="974" ht="12.65" customHeight="1"/>
+    <row r="975" ht="12.65" customHeight="1"/>
+    <row r="976" ht="12.65" customHeight="1"/>
+    <row r="977" ht="12.65" customHeight="1"/>
+    <row r="978" ht="12.65" customHeight="1"/>
+    <row r="979" ht="12.65" customHeight="1"/>
+    <row r="980" ht="12.65" customHeight="1"/>
+    <row r="981" ht="12.65" customHeight="1"/>
+    <row r="982" ht="12.65" customHeight="1"/>
+    <row r="983" ht="12.65" customHeight="1"/>
+    <row r="984" ht="12.65" customHeight="1"/>
+    <row r="985" ht="12.65" customHeight="1"/>
+    <row r="986" ht="12.65" customHeight="1"/>
+    <row r="987" ht="12.65" customHeight="1"/>
+    <row r="988" ht="12.65" customHeight="1"/>
+    <row r="989" ht="12.65" customHeight="1"/>
+    <row r="990" ht="12.65" customHeight="1"/>
+    <row r="991" ht="12.65" customHeight="1"/>
+    <row r="992" ht="12.65" customHeight="1"/>
+    <row r="993" ht="12.65" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0"/>
@@ -73405,7 +73409,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0"/>

--- a/j-busqueda clientes/j-clientes-gle.xlsx
+++ b/j-busqueda clientes/j-clientes-gle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88153b17ae7a9f01/documentos/TRABAJOS AUTONOMOS/JURADA/j-busqueda clientes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{BC0EFC44-3F1E-411F-B361-DCAF094CE636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{327A1177-7A15-4175-99E6-DE5DDB75BDC4}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{BC0EFC44-3F1E-411F-B361-DCAF094CE636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A658D85B-3160-4247-885D-E3D4A8EF1A78}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="-110" windowWidth="24900" windowHeight="14500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34473,7 +34473,9 @@
     </row>
     <row r="369" spans="1:33" ht="11.5" customHeight="1">
       <c r="A369" s="205"/>
-      <c r="B369" s="205"/>
+      <c r="B369" s="207">
+        <v>46176</v>
+      </c>
       <c r="C369" s="366"/>
       <c r="D369" s="110"/>
       <c r="E369" s="104"/>
@@ -34517,7 +34519,9 @@
       <c r="A370" s="207">
         <v>46081.458333333336</v>
       </c>
-      <c r="B370" s="207"/>
+      <c r="B370" s="207">
+        <v>46176</v>
+      </c>
       <c r="C370" s="367"/>
       <c r="D370" s="83"/>
       <c r="E370" s="106"/>
@@ -34768,7 +34772,9 @@
       <c r="A375" s="209">
         <v>46170.416666666664</v>
       </c>
-      <c r="B375" s="209"/>
+      <c r="B375" s="207">
+        <v>46176</v>
+      </c>
       <c r="C375" s="365"/>
       <c r="D375" s="109"/>
       <c r="E375" s="102" t="s">

--- a/j-busqueda clientes/j-clientes-gle.xlsx
+++ b/j-busqueda clientes/j-clientes-gle.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88153b17ae7a9f01/documentos/TRABAJOS AUTONOMOS/JURADA/j-busqueda clientes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_D63F57C2E7E2542D700A1305F6CE983A5695B77D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC466DDA-5CF9-4EB2-8B4B-BDE160056D0D}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_D63F57C2E7E2542D700A1305F6CE983A5695B77D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{195BA87F-D777-4390-AE5B-F85746C539A4}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="-110" windowWidth="24900" windowHeight="14900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="810" yWindow="-110" windowWidth="24900" windowHeight="14500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="clientes" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5635" uniqueCount="3348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5638" uniqueCount="3350">
   <si>
     <t>para día</t>
   </si>
@@ -10131,6 +10131,12 @@
   </si>
   <si>
     <t>le envío email sin tarifas</t>
+  </si>
+  <si>
+    <t>A Zaragoza</t>
+  </si>
+  <si>
+    <t>azarazaga@deloitte.es</t>
   </si>
 </sst>
 </file>
@@ -10801,7 +10807,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="492">
+  <cellXfs count="493">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -12208,6 +12214,9 @@
     <xf numFmtId="169" fontId="21" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="55" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -34617,20 +34626,31 @@
       <c r="AG370" s="77"/>
     </row>
     <row r="371" spans="1:33" ht="11.5" customHeight="1">
-      <c r="A371" s="203"/>
+      <c r="A371" s="203">
+        <v>46224</v>
+      </c>
       <c r="B371" s="203"/>
       <c r="C371" s="378"/>
-      <c r="D371" s="85"/>
+      <c r="D371" s="85">
+        <v>46224</v>
+      </c>
       <c r="E371" s="87"/>
       <c r="F371" s="87"/>
-      <c r="G371" s="87"/>
+      <c r="G371" s="492" t="s">
+        <v>56</v>
+      </c>
       <c r="H371" s="121" t="s">
         <v>2389</v>
       </c>
       <c r="I371" t="s">
         <v>2390</v>
       </c>
-      <c r="J371" s="121"/>
+      <c r="J371" s="121" t="s">
+        <v>3348</v>
+      </c>
+      <c r="K371" s="119" t="s">
+        <v>3349</v>
+      </c>
       <c r="L371" s="121" t="s">
         <v>2391</v>
       </c>

--- a/j-busqueda clientes/j-clientes-gle.xlsx
+++ b/j-busqueda clientes/j-clientes-gle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88153b17ae7a9f01/documentos/TRABAJOS AUTONOMOS/JURADA/j-busqueda clientes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_D63F57C2E7E2542D700A1305F6CE983A5695B77D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{195BA87F-D777-4390-AE5B-F85746C539A4}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_D63F57C2E7E2542D700A1305F6CE983A5695B77D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33FB9B58-734D-4C8F-B6D2-4D421C711F1B}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="-110" windowWidth="24900" windowHeight="14500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5638" uniqueCount="3350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5639" uniqueCount="3350">
   <si>
     <t>para día</t>
   </si>
@@ -21571,7 +21571,9 @@
       <c r="F154" s="101" t="s">
         <v>69</v>
       </c>
-      <c r="G154" s="101"/>
+      <c r="G154" s="406" t="s">
+        <v>154</v>
+      </c>
       <c r="H154" s="146" t="s">
         <v>934</v>
       </c>

--- a/j-busqueda clientes/j-clientes-gle.xlsx
+++ b/j-busqueda clientes/j-clientes-gle.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88153b17ae7a9f01/documentos/TRABAJOS AUTONOMOS/JURADA/j-busqueda clientes/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rocio\OneDrive\documentos\TRABAJOS AUTONOMOS\JURADA\j-busqueda clientes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_D63F57C2E7E2542D700A1305F6CE983A5695B77D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33FB9B58-734D-4C8F-B6D2-4D421C711F1B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0494F7BF-8BF6-4CEA-9291-1163A9074BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="-110" windowWidth="24900" windowHeight="14500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,20 @@
   <definedNames>
     <definedName name="DatosExternos_1" localSheetId="0">clientes!$A$1:$Y$58</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -53,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5639" uniqueCount="3350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5641" uniqueCount="3352">
   <si>
     <t>para día</t>
   </si>
@@ -7271,9 +7284,6 @@
     <t>https://kpmg.com/es/es/servicios/abogados.html</t>
   </si>
   <si>
-    <t>info-es@kpmg.com</t>
-  </si>
-  <si>
     <t>People Services: equipo multidisciplinar para compensación, movilidad internacional, asesoría fiscal-legal. Coordinación centralizada desde España en 145+ países. +1000 abogados en 13 oficinas.</t>
   </si>
   <si>
@@ -10137,6 +10147,15 @@
   </si>
   <si>
     <t>azarazaga@deloitte.es</t>
+  </si>
+  <si>
+    <t>Carmen Marull</t>
+  </si>
+  <si>
+    <t>deducidos 2: carmen.marull@kpmg.es / cmarull@kpmg.com</t>
+  </si>
+  <si>
+    <t>deducidos cmarull@kpmg.es / carmen.marull@kpmg.es / cmarull@kpmg.com</t>
   </si>
 </sst>
 </file>
@@ -34139,7 +34158,7 @@
       <c r="E362" s="105"/>
       <c r="F362" s="105"/>
       <c r="G362" s="400" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
       <c r="H362" s="120" t="s">
         <v>2329</v>
@@ -34148,10 +34167,10 @@
         <v>2330</v>
       </c>
       <c r="J362" s="120" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
       <c r="K362" t="s">
-        <v>3345</v>
+        <v>3344</v>
       </c>
       <c r="L362" s="120" t="s">
         <v>2331</v>
@@ -34648,10 +34667,10 @@
         <v>2390</v>
       </c>
       <c r="J371" s="121" t="s">
+        <v>3347</v>
+      </c>
+      <c r="K371" s="119" t="s">
         <v>3348</v>
-      </c>
-      <c r="K371" s="119" t="s">
-        <v>3349</v>
       </c>
       <c r="L371" s="121" t="s">
         <v>2391</v>
@@ -34681,7 +34700,9 @@
       <c r="AG371" s="87"/>
     </row>
     <row r="372" spans="1:33" ht="11.5" customHeight="1">
-      <c r="A372" s="202"/>
+      <c r="A372" s="202">
+        <v>46234</v>
+      </c>
       <c r="B372" s="202"/>
       <c r="C372" s="375"/>
       <c r="D372" s="79"/>
@@ -34694,12 +34715,14 @@
       <c r="I372" t="s">
         <v>2393</v>
       </c>
-      <c r="J372" s="123"/>
-      <c r="K372" t="s">
+      <c r="J372" s="118" t="s">
+        <v>3349</v>
+      </c>
+      <c r="K372" s="118" t="s">
+        <v>3351</v>
+      </c>
+      <c r="L372" s="123" t="s">
         <v>2394</v>
-      </c>
-      <c r="L372" s="123" t="s">
-        <v>2395</v>
       </c>
       <c r="M372" s="173" t="s">
         <v>1448</v>
@@ -34734,17 +34757,17 @@
       <c r="F373" s="80"/>
       <c r="G373" s="80"/>
       <c r="H373" s="122" t="s">
+        <v>2395</v>
+      </c>
+      <c r="I373" t="s">
         <v>2396</v>
-      </c>
-      <c r="I373" t="s">
-        <v>2397</v>
       </c>
       <c r="J373" s="122"/>
       <c r="K373" t="s">
+        <v>2397</v>
+      </c>
+      <c r="L373" s="122" t="s">
         <v>2398</v>
-      </c>
-      <c r="L373" s="122" t="s">
-        <v>2399</v>
       </c>
       <c r="M373" s="174" t="s">
         <v>1448</v>
@@ -34787,19 +34810,19 @@
       </c>
       <c r="G374" s="101"/>
       <c r="H374" s="118" t="s">
+        <v>2399</v>
+      </c>
+      <c r="I374" t="s">
         <v>2400</v>
       </c>
-      <c r="I374" t="s">
+      <c r="J374" s="118" t="s">
         <v>2401</v>
       </c>
-      <c r="J374" s="118" t="s">
+      <c r="K374" t="s">
         <v>2402</v>
       </c>
-      <c r="K374" t="s">
+      <c r="L374" s="118" t="s">
         <v>2403</v>
-      </c>
-      <c r="L374" s="118" t="s">
-        <v>2404</v>
       </c>
       <c r="M374" s="168" t="s">
         <v>1448</v>
@@ -34812,31 +34835,31 @@
       </c>
       <c r="P374" s="101"/>
       <c r="Q374" s="403" t="s">
+        <v>2404</v>
+      </c>
+      <c r="R374" s="101" t="s">
         <v>2405</v>
       </c>
-      <c r="R374" s="101" t="s">
+      <c r="S374" s="101" t="s">
         <v>2406</v>
-      </c>
-      <c r="S374" s="101" t="s">
-        <v>2407</v>
       </c>
       <c r="T374" s="101" t="s">
         <v>483</v>
       </c>
       <c r="U374" s="101" t="s">
+        <v>2407</v>
+      </c>
+      <c r="V374" s="101" t="s">
         <v>2408</v>
       </c>
-      <c r="V374" s="101" t="s">
+      <c r="W374" s="101" t="s">
         <v>2409</v>
       </c>
-      <c r="W374" s="101" t="s">
+      <c r="X374" s="101" t="s">
         <v>2410</v>
       </c>
-      <c r="X374" s="101" t="s">
+      <c r="Y374" s="101" t="s">
         <v>2411</v>
-      </c>
-      <c r="Y374" s="101" t="s">
-        <v>2412</v>
       </c>
       <c r="Z374" s="101" t="s">
         <v>258</v>
@@ -34860,17 +34883,17 @@
       <c r="F375" s="103"/>
       <c r="G375" s="103"/>
       <c r="H375" s="119" t="s">
+        <v>2412</v>
+      </c>
+      <c r="I375" t="s">
         <v>2413</v>
-      </c>
-      <c r="I375" t="s">
-        <v>2414</v>
       </c>
       <c r="J375" s="119"/>
       <c r="L375" s="119" t="s">
+        <v>2414</v>
+      </c>
+      <c r="M375" s="169" t="s">
         <v>2415</v>
-      </c>
-      <c r="M375" s="169" t="s">
-        <v>2416</v>
       </c>
       <c r="N375" s="103"/>
       <c r="O375" s="103"/>
@@ -34914,22 +34937,22 @@
         <v>774</v>
       </c>
       <c r="H376" s="121" t="s">
+        <v>2416</v>
+      </c>
+      <c r="I376" t="s">
         <v>2417</v>
       </c>
-      <c r="I376" t="s">
+      <c r="J376" s="121" t="s">
         <v>2418</v>
       </c>
-      <c r="J376" s="121" t="s">
+      <c r="K376" s="119" t="s">
         <v>2419</v>
       </c>
-      <c r="K376" s="119" t="s">
+      <c r="L376" s="121" t="s">
         <v>2420</v>
       </c>
-      <c r="L376" s="121" t="s">
+      <c r="M376" s="172" t="s">
         <v>2421</v>
-      </c>
-      <c r="M376" s="172" t="s">
-        <v>2422</v>
       </c>
       <c r="N376" s="87" t="s">
         <v>43</v>
@@ -34939,29 +34962,29 @@
       </c>
       <c r="P376" s="87"/>
       <c r="Q376" s="401" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="R376" s="87"/>
       <c r="S376" s="87" t="s">
+        <v>2423</v>
+      </c>
+      <c r="T376" s="87" t="s">
         <v>2424</v>
       </c>
-      <c r="T376" s="87" t="s">
+      <c r="U376" s="87" t="s">
         <v>2425</v>
       </c>
-      <c r="U376" s="87" t="s">
+      <c r="V376" s="87" t="s">
         <v>2426</v>
       </c>
-      <c r="V376" s="87" t="s">
+      <c r="W376" s="87" t="s">
         <v>2427</v>
-      </c>
-      <c r="W376" s="87" t="s">
-        <v>2428</v>
       </c>
       <c r="X376" s="87" t="s">
         <v>2299</v>
       </c>
       <c r="Y376" s="87" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="Z376" s="87" t="s">
         <v>194</v>
@@ -34985,17 +35008,17 @@
       <c r="F377" s="55"/>
       <c r="G377" s="488"/>
       <c r="H377" s="123" t="s">
+        <v>2429</v>
+      </c>
+      <c r="I377" t="s">
         <v>2430</v>
-      </c>
-      <c r="I377" t="s">
-        <v>2431</v>
       </c>
       <c r="J377" s="123"/>
       <c r="L377" s="123" t="s">
+        <v>2431</v>
+      </c>
+      <c r="M377" s="173" t="s">
         <v>2432</v>
-      </c>
-      <c r="M377" s="173" t="s">
-        <v>2433</v>
       </c>
       <c r="N377" s="55"/>
       <c r="O377" s="55"/>
@@ -35027,9 +35050,9 @@
       <c r="F378" s="101"/>
       <c r="G378" s="101"/>
       <c r="H378" s="118"/>
-      <c r="J378" s="118"/>
-      <c r="L378" s="118"/>
-      <c r="M378" s="168"/>
+      <c r="M378" s="168" t="s">
+        <v>3350</v>
+      </c>
       <c r="N378" s="101"/>
       <c r="O378" s="101"/>
       <c r="P378" s="101"/>
@@ -40070,36 +40093,36 @@
   <sheetData>
     <row r="1" spans="8:15" ht="12.65" customHeight="1">
       <c r="H1" s="5" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="2" spans="8:15" ht="12.65" customHeight="1">
       <c r="H2" s="20" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="3" spans="8:15" ht="12.65" customHeight="1">
       <c r="H3" s="20" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="4" spans="8:15" ht="12.65" customHeight="1">
       <c r="H4" s="21" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="5" spans="8:15" ht="12.65" customHeight="1">
       <c r="H5" s="6" t="s">
+        <v>2437</v>
+      </c>
+      <c r="I5" s="9" t="s">
         <v>2438</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="J5" s="9" t="s">
         <v>2439</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="K5" s="6" t="s">
         <v>2440</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>2441</v>
       </c>
       <c r="L5" s="6"/>
       <c r="M5" s="5" t="s">
@@ -40109,19 +40132,19 @@
         <v>62</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="6" spans="8:15" ht="12.65" customHeight="1">
       <c r="H6" s="6" t="s">
+        <v>2442</v>
+      </c>
+      <c r="I6" s="9" t="s">
         <v>2443</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>2444</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="22" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
@@ -40129,24 +40152,24 @@
         <v>43</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="7" spans="8:15" ht="15" customHeight="1">
       <c r="H7" s="1" t="s">
+        <v>2446</v>
+      </c>
+      <c r="I7" s="23" t="s">
         <v>2447</v>
       </c>
-      <c r="I7" s="23" t="s">
+      <c r="J7" s="1" t="s">
         <v>2448</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>2449</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>2450</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>2451</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>779</v>
@@ -40192,13 +40215,13 @@
         <v>1576</v>
       </c>
       <c r="K9" s="1" t="s">
+        <v>2451</v>
+      </c>
+      <c r="L9" s="1" t="s">
         <v>2452</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="M9" s="1" t="s">
         <v>2453</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>2454</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>62</v>
@@ -40206,19 +40229,19 @@
     </row>
     <row r="10" spans="8:15" ht="12.65" customHeight="1">
       <c r="H10" s="5" t="s">
+        <v>2454</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>2455</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="J10" s="5" t="s">
         <v>2456</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="K10" s="6" t="s">
         <v>2457</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="L10" s="5" t="s">
         <v>2458</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>2459</v>
       </c>
       <c r="M10" s="5" t="s">
         <v>912</v>
@@ -40227,212 +40250,212 @@
         <v>62</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="11" spans="8:15" ht="15" customHeight="1">
       <c r="H11" s="1" t="s">
+        <v>2460</v>
+      </c>
+      <c r="I11" s="8" t="s">
         <v>2461</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>2462</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>1296</v>
       </c>
       <c r="K11" s="1" t="s">
+        <v>2462</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>2463</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="M11" s="1" t="s">
         <v>2464</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>2465</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>62</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="12" spans="8:15" ht="15" customHeight="1">
       <c r="H12" s="1" t="s">
+        <v>2466</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>2467</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>2468</v>
       </c>
       <c r="J12" s="1"/>
       <c r="L12" s="1" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>1772</v>
       </c>
       <c r="O12" s="5" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="13" spans="8:15" ht="15" customHeight="1">
       <c r="H13" s="1" t="s">
+        <v>2470</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>2471</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="1" t="s">
         <v>2472</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="K13" s="1" t="s">
         <v>2473</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>2474</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>2475</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="O13" s="25" t="s">
         <v>2476</v>
-      </c>
-      <c r="O13" s="25" t="s">
-        <v>2477</v>
       </c>
     </row>
     <row r="14" spans="8:15" ht="15" customHeight="1">
       <c r="H14" s="1" t="s">
+        <v>2477</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>2478</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>2479</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>1296</v>
       </c>
       <c r="K14" s="1" t="s">
+        <v>2479</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>2480</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="M14" s="1" t="s">
         <v>2481</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>2482</v>
       </c>
     </row>
     <row r="15" spans="8:15" ht="15" customHeight="1">
       <c r="H15" s="1" t="s">
+        <v>2482</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>2483</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="1" t="s">
         <v>2484</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>2485</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>2486</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>2487</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>814</v>
       </c>
       <c r="O15" s="25" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="16" spans="8:15" ht="15" customHeight="1">
       <c r="H16" s="29" t="s">
+        <v>2488</v>
+      </c>
+      <c r="I16" s="30" t="s">
         <v>2489</v>
       </c>
-      <c r="I16" s="30" t="s">
+      <c r="J16" s="29" t="s">
         <v>2490</v>
       </c>
-      <c r="J16" s="29" t="s">
+      <c r="K16" s="29" t="s">
         <v>2491</v>
       </c>
-      <c r="K16" s="29" t="s">
+      <c r="L16" s="29" t="s">
         <v>2492</v>
-      </c>
-      <c r="L16" s="29" t="s">
-        <v>2493</v>
       </c>
       <c r="M16" s="29" t="s">
         <v>1378</v>
       </c>
       <c r="N16" s="29"/>
       <c r="O16" s="32" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="17" spans="1:47" ht="15" customHeight="1">
       <c r="H17" s="31" t="s">
+        <v>2494</v>
+      </c>
+      <c r="I17" s="31" t="s">
         <v>2495</v>
-      </c>
-      <c r="I17" s="31" t="s">
-        <v>2496</v>
       </c>
       <c r="J17" s="31"/>
       <c r="K17" s="31" t="s">
         <v>1296</v>
       </c>
       <c r="L17" s="31" t="s">
+        <v>2496</v>
+      </c>
+      <c r="M17" s="31" t="s">
         <v>2497</v>
       </c>
-      <c r="M17" s="31" t="s">
+      <c r="O17" s="25" t="s">
         <v>2498</v>
-      </c>
-      <c r="O17" s="25" t="s">
-        <v>2499</v>
       </c>
     </row>
     <row r="18" spans="1:47" ht="15" customHeight="1">
       <c r="H18" s="31" t="s">
+        <v>2499</v>
+      </c>
+      <c r="I18" s="31" t="s">
         <v>2500</v>
-      </c>
-      <c r="I18" s="31" t="s">
-        <v>2501</v>
       </c>
       <c r="J18" s="31"/>
       <c r="K18" s="31" t="s">
         <v>1296</v>
       </c>
       <c r="L18" s="31" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="M18" s="31" t="s">
+        <v>2497</v>
+      </c>
+      <c r="O18" s="25" t="s">
         <v>2498</v>
-      </c>
-      <c r="O18" s="25" t="s">
-        <v>2499</v>
       </c>
     </row>
     <row r="19" spans="1:47" ht="15" customHeight="1">
       <c r="H19" s="31" t="s">
+        <v>2502</v>
+      </c>
+      <c r="I19" s="31" t="s">
         <v>2503</v>
-      </c>
-      <c r="I19" s="31" t="s">
-        <v>2504</v>
       </c>
       <c r="J19" s="31"/>
       <c r="K19" s="31" t="s">
         <v>1296</v>
       </c>
       <c r="L19" s="31" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="M19" s="31" t="s">
         <v>1491</v>
       </c>
       <c r="O19" s="25" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="20" spans="1:47" ht="15" customHeight="1">
       <c r="H20" s="29" t="s">
+        <v>2506</v>
+      </c>
+      <c r="I20" s="30" t="s">
         <v>2507</v>
-      </c>
-      <c r="I20" s="30" t="s">
-        <v>2508</v>
       </c>
       <c r="J20" s="29"/>
       <c r="K20" s="29"/>
@@ -40445,39 +40468,39 @@
     </row>
     <row r="21" spans="1:47" ht="15" customHeight="1">
       <c r="H21" s="45" t="s">
+        <v>2508</v>
+      </c>
+      <c r="I21" s="51" t="s">
         <v>2509</v>
-      </c>
-      <c r="I21" s="51" t="s">
-        <v>2510</v>
       </c>
       <c r="J21" s="45"/>
       <c r="K21" s="45"/>
       <c r="L21" s="45" t="s">
+        <v>2510</v>
+      </c>
+      <c r="M21" s="45" t="s">
         <v>2511</v>
-      </c>
-      <c r="M21" s="45" t="s">
-        <v>2512</v>
       </c>
       <c r="N21" s="45"/>
       <c r="O21" s="45"/>
       <c r="P21" s="46"/>
       <c r="Q21" s="51" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="R21" s="45"/>
       <c r="S21" s="45"/>
     </row>
     <row r="22" spans="1:47" ht="15" customHeight="1">
       <c r="H22" s="35" t="s">
+        <v>2513</v>
+      </c>
+      <c r="I22" s="49" t="s">
         <v>2514</v>
-      </c>
-      <c r="I22" s="49" t="s">
-        <v>2515</v>
       </c>
       <c r="J22" s="35"/>
       <c r="K22" s="35"/>
       <c r="L22" s="35" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="M22" s="35" t="s">
         <v>635</v>
@@ -40486,62 +40509,62 @@
       <c r="O22" s="35"/>
       <c r="P22" s="47"/>
       <c r="Q22" s="49" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="R22" s="35"/>
     </row>
     <row r="23" spans="1:47" ht="15" customHeight="1">
       <c r="H23" s="39" t="s">
+        <v>2517</v>
+      </c>
+      <c r="I23" s="48" t="s">
         <v>2518</v>
-      </c>
-      <c r="I23" s="48" t="s">
-        <v>2519</v>
       </c>
       <c r="J23" s="39"/>
       <c r="O23" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="24" spans="1:47" ht="15" customHeight="1">
       <c r="H24" s="38" t="s">
+        <v>2520</v>
+      </c>
+      <c r="I24" s="54" t="s">
         <v>2521</v>
       </c>
-      <c r="I24" s="54" t="s">
+      <c r="O24" t="s">
         <v>2522</v>
-      </c>
-      <c r="O24" t="s">
-        <v>2523</v>
       </c>
     </row>
     <row r="25" spans="1:47" ht="15" customHeight="1">
       <c r="H25" s="35" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="I25" s="49" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="J25" s="35" t="s">
         <v>1296</v>
       </c>
       <c r="K25" s="35" t="s">
+        <v>2524</v>
+      </c>
+      <c r="L25" s="35" t="s">
         <v>2525</v>
-      </c>
-      <c r="L25" s="35" t="s">
-        <v>2526</v>
       </c>
       <c r="M25" s="35" t="s">
         <v>1378</v>
       </c>
       <c r="O25" s="56" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="26" spans="1:47" ht="15" customHeight="1">
       <c r="H26" s="41" t="s">
+        <v>2527</v>
+      </c>
+      <c r="I26" s="52" t="s">
         <v>2528</v>
-      </c>
-      <c r="I26" s="52" t="s">
-        <v>2529</v>
       </c>
       <c r="J26" s="41" t="s">
         <v>1296</v>
@@ -40550,16 +40573,16 @@
         <v>1296</v>
       </c>
       <c r="L26" s="41" t="s">
+        <v>2529</v>
+      </c>
+      <c r="M26" s="41" t="s">
         <v>2530</v>
-      </c>
-      <c r="M26" s="41" t="s">
-        <v>2531</v>
       </c>
       <c r="N26" s="41"/>
       <c r="O26" s="41"/>
       <c r="P26" s="41"/>
       <c r="Q26" s="41" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="27" spans="1:47" s="28" customFormat="1" ht="12.75" customHeight="1">
@@ -40567,28 +40590,28 @@
       <c r="B27" s="42"/>
       <c r="C27" s="42"/>
       <c r="D27" s="40" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="E27" s="43"/>
       <c r="F27" s="43"/>
       <c r="G27" s="43"/>
       <c r="H27" s="43" t="s">
+        <v>2533</v>
+      </c>
+      <c r="I27" s="50" t="s">
         <v>2534</v>
       </c>
-      <c r="I27" s="50" t="s">
+      <c r="J27" s="43" t="s">
         <v>2535</v>
       </c>
-      <c r="J27" s="43" t="s">
+      <c r="K27" s="43" t="s">
         <v>2536</v>
       </c>
-      <c r="K27" s="43" t="s">
+      <c r="L27" s="43" t="s">
         <v>2537</v>
       </c>
-      <c r="L27" s="43" t="s">
+      <c r="M27" s="43" t="s">
         <v>2538</v>
-      </c>
-      <c r="M27" s="43" t="s">
-        <v>2539</v>
       </c>
       <c r="N27" s="43"/>
       <c r="O27" s="43"/>
@@ -40634,22 +40657,22 @@
       <c r="F28" s="45"/>
       <c r="G28" s="45"/>
       <c r="H28" s="45" t="s">
+        <v>2539</v>
+      </c>
+      <c r="I28" s="51" t="s">
         <v>2540</v>
       </c>
-      <c r="I28" s="51" t="s">
+      <c r="J28" s="45" t="s">
         <v>2541</v>
       </c>
-      <c r="J28" s="45" t="s">
+      <c r="K28" s="45" t="s">
         <v>2542</v>
       </c>
-      <c r="K28" s="45" t="s">
+      <c r="L28" s="45" t="s">
         <v>2543</v>
       </c>
-      <c r="L28" s="45" t="s">
+      <c r="M28" s="45" t="s">
         <v>2544</v>
-      </c>
-      <c r="M28" s="45" t="s">
-        <v>2545</v>
       </c>
       <c r="N28" s="45"/>
       <c r="O28" s="45"/>
@@ -40695,22 +40718,22 @@
       <c r="F29" s="34"/>
       <c r="G29" s="34"/>
       <c r="H29" s="34" t="s">
+        <v>2545</v>
+      </c>
+      <c r="I29" s="53" t="s">
         <v>2546</v>
-      </c>
-      <c r="I29" s="53" t="s">
-        <v>2547</v>
       </c>
       <c r="J29" s="34" t="s">
         <v>1296</v>
       </c>
       <c r="K29" s="34" t="s">
+        <v>2547</v>
+      </c>
+      <c r="L29" s="34" t="s">
         <v>2548</v>
       </c>
-      <c r="L29" s="34" t="s">
+      <c r="M29" s="34" t="s">
         <v>2549</v>
-      </c>
-      <c r="M29" s="34" t="s">
-        <v>2550</v>
       </c>
       <c r="N29" s="34"/>
       <c r="O29" s="34"/>
@@ -40756,10 +40779,10 @@
       <c r="F30" s="35"/>
       <c r="G30" s="35"/>
       <c r="H30" s="35" t="s">
+        <v>2550</v>
+      </c>
+      <c r="I30" s="49" t="s">
         <v>2551</v>
-      </c>
-      <c r="I30" s="49" t="s">
-        <v>2552</v>
       </c>
       <c r="J30" s="35" t="s">
         <v>1296</v>
@@ -40768,10 +40791,10 @@
         <v>1296</v>
       </c>
       <c r="L30" s="35" t="s">
+        <v>2552</v>
+      </c>
+      <c r="M30" s="35" t="s">
         <v>2553</v>
-      </c>
-      <c r="M30" s="35" t="s">
-        <v>2554</v>
       </c>
       <c r="N30" s="35"/>
       <c r="O30" s="35"/>
@@ -40817,22 +40840,22 @@
       <c r="F31" s="38"/>
       <c r="G31" s="38"/>
       <c r="H31" s="38" t="s">
+        <v>2554</v>
+      </c>
+      <c r="I31" s="54" t="s">
         <v>2555</v>
       </c>
-      <c r="I31" s="54" t="s">
+      <c r="J31" s="38" t="s">
         <v>2556</v>
       </c>
-      <c r="J31" s="38" t="s">
+      <c r="K31" s="38" t="s">
         <v>2557</v>
       </c>
-      <c r="K31" s="38" t="s">
+      <c r="L31" s="38" t="s">
         <v>2558</v>
       </c>
-      <c r="L31" s="38" t="s">
+      <c r="M31" s="38" t="s">
         <v>2559</v>
-      </c>
-      <c r="M31" s="38" t="s">
-        <v>2560</v>
       </c>
       <c r="N31" s="38"/>
       <c r="O31" s="38"/>
@@ -40878,19 +40901,19 @@
       <c r="F32" s="41"/>
       <c r="G32" s="41"/>
       <c r="H32" s="41" t="s">
+        <v>2560</v>
+      </c>
+      <c r="I32" s="52" t="s">
         <v>2561</v>
       </c>
-      <c r="I32" s="52" t="s">
+      <c r="J32" s="41" t="s">
         <v>2562</v>
       </c>
-      <c r="J32" s="41" t="s">
+      <c r="K32" s="41" t="s">
         <v>2563</v>
       </c>
-      <c r="K32" s="41" t="s">
+      <c r="L32" s="41" t="s">
         <v>2564</v>
-      </c>
-      <c r="L32" s="41" t="s">
-        <v>2565</v>
       </c>
       <c r="M32" s="41" t="s">
         <v>1378</v>
@@ -40938,22 +40961,22 @@
       <c r="F33" s="43"/>
       <c r="G33" s="43"/>
       <c r="H33" s="43" t="s">
+        <v>2565</v>
+      </c>
+      <c r="I33" s="50" t="s">
         <v>2566</v>
-      </c>
-      <c r="I33" s="50" t="s">
-        <v>2567</v>
       </c>
       <c r="J33" s="43" t="s">
         <v>1296</v>
       </c>
       <c r="K33" s="43" t="s">
+        <v>2567</v>
+      </c>
+      <c r="L33" s="43" t="s">
         <v>2568</v>
       </c>
-      <c r="L33" s="43" t="s">
+      <c r="M33" s="43" t="s">
         <v>2569</v>
-      </c>
-      <c r="M33" s="43" t="s">
-        <v>2570</v>
       </c>
       <c r="N33" s="43"/>
       <c r="O33" s="43"/>
@@ -40999,22 +41022,22 @@
       <c r="F34" s="45"/>
       <c r="G34" s="45"/>
       <c r="H34" s="45" t="s">
+        <v>2570</v>
+      </c>
+      <c r="I34" s="51" t="s">
         <v>2571</v>
       </c>
-      <c r="I34" s="51" t="s">
+      <c r="J34" s="45" t="s">
+        <v>2562</v>
+      </c>
+      <c r="K34" s="45" t="s">
         <v>2572</v>
       </c>
-      <c r="J34" s="45" t="s">
-        <v>2563</v>
-      </c>
-      <c r="K34" s="45" t="s">
+      <c r="L34" s="45" t="s">
         <v>2573</v>
       </c>
-      <c r="L34" s="45" t="s">
-        <v>2574</v>
-      </c>
       <c r="M34" s="45" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
       <c r="N34" s="45"/>
       <c r="O34" s="45"/>
@@ -41060,10 +41083,10 @@
       <c r="F35" s="34"/>
       <c r="G35" s="34"/>
       <c r="H35" s="34" t="s">
+        <v>2574</v>
+      </c>
+      <c r="I35" s="53" t="s">
         <v>2575</v>
-      </c>
-      <c r="I35" s="53" t="s">
-        <v>2576</v>
       </c>
       <c r="J35" s="34" t="s">
         <v>1296</v>
@@ -41072,10 +41095,10 @@
         <v>1296</v>
       </c>
       <c r="L35" s="34" t="s">
+        <v>2576</v>
+      </c>
+      <c r="M35" s="34" t="s">
         <v>2577</v>
-      </c>
-      <c r="M35" s="34" t="s">
-        <v>2578</v>
       </c>
       <c r="N35" s="34"/>
       <c r="O35" s="34"/>
@@ -41121,10 +41144,10 @@
       <c r="F36" s="35"/>
       <c r="G36" s="35"/>
       <c r="H36" s="35" t="s">
+        <v>2578</v>
+      </c>
+      <c r="I36" s="49" t="s">
         <v>2579</v>
-      </c>
-      <c r="I36" s="49" t="s">
-        <v>2580</v>
       </c>
       <c r="J36" s="35" t="s">
         <v>1296</v>
@@ -41133,7 +41156,7 @@
         <v>1296</v>
       </c>
       <c r="L36" s="35" t="s">
-        <v>2581</v>
+        <v>2580</v>
       </c>
       <c r="M36" s="35" t="s">
         <v>1670</v>
@@ -41182,10 +41205,10 @@
       <c r="F37" s="41"/>
       <c r="G37" s="41"/>
       <c r="H37" s="41" t="s">
+        <v>2581</v>
+      </c>
+      <c r="I37" s="52" t="s">
         <v>2582</v>
-      </c>
-      <c r="I37" s="52" t="s">
-        <v>2583</v>
       </c>
       <c r="J37" s="41" t="s">
         <v>1296</v>
@@ -41194,7 +41217,7 @@
         <v>1296</v>
       </c>
       <c r="L37" s="41" t="s">
-        <v>2584</v>
+        <v>2583</v>
       </c>
       <c r="M37" s="41" t="s">
         <v>1431</v>
@@ -41243,19 +41266,19 @@
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
       <c r="H38" s="35" t="s">
+        <v>2584</v>
+      </c>
+      <c r="I38" s="49" t="s">
         <v>2585</v>
       </c>
-      <c r="I38" s="49" t="s">
+      <c r="J38" s="35" t="s">
         <v>2586</v>
       </c>
-      <c r="J38" s="35" t="s">
+      <c r="K38" s="35" t="s">
         <v>2587</v>
       </c>
-      <c r="K38" s="35" t="s">
+      <c r="L38" s="35" t="s">
         <v>2588</v>
-      </c>
-      <c r="L38" s="35" t="s">
-        <v>2589</v>
       </c>
       <c r="M38" s="35" t="s">
         <v>1378</v>
@@ -41304,20 +41327,20 @@
       <c r="F39" s="35"/>
       <c r="G39" s="35"/>
       <c r="H39" s="35" t="s">
+        <v>2589</v>
+      </c>
+      <c r="I39" s="49" t="s">
         <v>2590</v>
-      </c>
-      <c r="I39" s="49" t="s">
-        <v>2591</v>
       </c>
       <c r="J39" s="35"/>
       <c r="K39" s="35" t="s">
+        <v>2591</v>
+      </c>
+      <c r="L39" s="35" t="s">
         <v>2592</v>
       </c>
-      <c r="L39" s="35" t="s">
+      <c r="M39" s="35" t="s">
         <v>2593</v>
-      </c>
-      <c r="M39" s="35" t="s">
-        <v>2594</v>
       </c>
       <c r="N39" s="35"/>
       <c r="O39" s="35"/>
@@ -41363,20 +41386,20 @@
       <c r="F40" s="38"/>
       <c r="G40" s="38"/>
       <c r="H40" s="38" t="s">
+        <v>2594</v>
+      </c>
+      <c r="I40" s="54" t="s">
         <v>2595</v>
-      </c>
-      <c r="I40" s="54" t="s">
-        <v>2596</v>
       </c>
       <c r="J40" s="38"/>
       <c r="K40" s="38" t="s">
+        <v>2596</v>
+      </c>
+      <c r="L40" s="38" t="s">
         <v>2597</v>
       </c>
-      <c r="L40" s="38" t="s">
-        <v>2598</v>
-      </c>
       <c r="M40" s="38" t="s">
-        <v>2594</v>
+        <v>2593</v>
       </c>
       <c r="N40" s="38"/>
       <c r="O40" s="38"/>
@@ -41422,19 +41445,19 @@
       <c r="F41" s="77"/>
       <c r="G41" s="77"/>
       <c r="H41" s="117" t="s">
+        <v>2598</v>
+      </c>
+      <c r="I41" s="119" t="s">
         <v>2599</v>
       </c>
-      <c r="I41" s="119" t="s">
+      <c r="J41" s="117" t="s">
         <v>2600</v>
       </c>
-      <c r="J41" s="117" t="s">
+      <c r="K41" s="119" t="s">
         <v>2601</v>
       </c>
-      <c r="K41" s="119" t="s">
+      <c r="L41" s="117" t="s">
         <v>2602</v>
-      </c>
-      <c r="L41" s="117" t="s">
-        <v>2603</v>
       </c>
       <c r="M41" s="171" t="s">
         <v>1448</v>
@@ -41477,22 +41500,22 @@
         <v>38</v>
       </c>
       <c r="I57" t="s">
+        <v>2603</v>
+      </c>
+      <c r="J57" t="s">
         <v>2604</v>
       </c>
-      <c r="J57" t="s">
+      <c r="K57" t="s">
         <v>2605</v>
       </c>
-      <c r="K57" t="s">
+      <c r="L57" t="s">
         <v>2606</v>
       </c>
-      <c r="L57" t="s">
+      <c r="M57" t="s">
         <v>2607</v>
       </c>
-      <c r="M57" t="s">
+      <c r="N57" t="s">
         <v>2608</v>
-      </c>
-      <c r="N57" t="s">
-        <v>2609</v>
       </c>
       <c r="O57" t="s">
         <v>62</v>
@@ -41506,16 +41529,16 @@
     </row>
     <row r="58" spans="1:28" ht="15" customHeight="1">
       <c r="H58" t="s">
+        <v>2609</v>
+      </c>
+      <c r="I58" t="s">
         <v>2610</v>
       </c>
-      <c r="I58" t="s">
+      <c r="K58" t="s">
         <v>2611</v>
       </c>
-      <c r="K58" t="s">
+      <c r="L58" t="s">
         <v>2612</v>
-      </c>
-      <c r="L58" t="s">
-        <v>2613</v>
       </c>
       <c r="M58" t="s">
         <v>1448</v>
@@ -41526,16 +41549,16 @@
     </row>
     <row r="59" spans="1:28" ht="15" customHeight="1">
       <c r="H59" t="s">
+        <v>2613</v>
+      </c>
+      <c r="I59" t="s">
         <v>2614</v>
       </c>
-      <c r="I59" t="s">
+      <c r="J59" t="s">
         <v>2615</v>
       </c>
-      <c r="J59" t="s">
+      <c r="L59" t="s">
         <v>2616</v>
-      </c>
-      <c r="L59" t="s">
-        <v>2617</v>
       </c>
       <c r="M59" t="s">
         <v>1448</v>
@@ -41546,16 +41569,16 @@
     </row>
     <row r="60" spans="1:28" ht="15" customHeight="1">
       <c r="H60" t="s">
+        <v>2617</v>
+      </c>
+      <c r="I60" t="s">
         <v>2618</v>
       </c>
-      <c r="I60" t="s">
+      <c r="K60" t="s">
         <v>2619</v>
       </c>
-      <c r="K60" t="s">
+      <c r="L60" t="s">
         <v>2620</v>
-      </c>
-      <c r="L60" t="s">
-        <v>2621</v>
       </c>
       <c r="M60" t="s">
         <v>1448</v>
@@ -41566,19 +41589,19 @@
     </row>
     <row r="61" spans="1:28" ht="15" customHeight="1">
       <c r="H61" t="s">
+        <v>2621</v>
+      </c>
+      <c r="I61" t="s">
         <v>2622</v>
       </c>
-      <c r="I61" t="s">
+      <c r="J61" t="s">
         <v>2623</v>
       </c>
-      <c r="J61" t="s">
+      <c r="K61" t="s">
         <v>2624</v>
       </c>
-      <c r="K61" t="s">
+      <c r="L61" t="s">
         <v>2625</v>
-      </c>
-      <c r="L61" t="s">
-        <v>2626</v>
       </c>
       <c r="M61" t="s">
         <v>1448</v>
@@ -41589,19 +41612,19 @@
     </row>
     <row r="62" spans="1:28" ht="15" customHeight="1">
       <c r="H62" t="s">
+        <v>2626</v>
+      </c>
+      <c r="I62" t="s">
         <v>2627</v>
       </c>
-      <c r="I62" t="s">
+      <c r="J62" t="s">
         <v>2628</v>
       </c>
-      <c r="J62" t="s">
+      <c r="K62" t="s">
         <v>2629</v>
       </c>
-      <c r="K62" t="s">
+      <c r="L62" t="s">
         <v>2630</v>
-      </c>
-      <c r="L62" t="s">
-        <v>2631</v>
       </c>
       <c r="M62" t="s">
         <v>1448</v>
@@ -41612,19 +41635,19 @@
     </row>
     <row r="63" spans="1:28" ht="15" customHeight="1">
       <c r="H63" t="s">
+        <v>2631</v>
+      </c>
+      <c r="I63" t="s">
         <v>2632</v>
       </c>
-      <c r="I63" t="s">
+      <c r="J63" t="s">
         <v>2633</v>
       </c>
-      <c r="J63" t="s">
+      <c r="K63" t="s">
         <v>2634</v>
       </c>
-      <c r="K63" t="s">
+      <c r="L63" t="s">
         <v>2635</v>
-      </c>
-      <c r="L63" t="s">
-        <v>2636</v>
       </c>
       <c r="M63" t="s">
         <v>1448</v>
@@ -41635,19 +41658,19 @@
     </row>
     <row r="64" spans="1:28" ht="15" customHeight="1">
       <c r="H64" t="s">
+        <v>2636</v>
+      </c>
+      <c r="I64" t="s">
         <v>2637</v>
       </c>
-      <c r="I64" t="s">
+      <c r="J64" t="s">
         <v>2638</v>
       </c>
-      <c r="J64" t="s">
+      <c r="K64" t="s">
         <v>2639</v>
       </c>
-      <c r="K64" t="s">
+      <c r="L64" t="s">
         <v>2640</v>
-      </c>
-      <c r="L64" t="s">
-        <v>2641</v>
       </c>
       <c r="M64" t="s">
         <v>1437</v>
@@ -41658,19 +41681,19 @@
     </row>
     <row r="65" spans="8:27" ht="15" customHeight="1">
       <c r="H65" t="s">
+        <v>2641</v>
+      </c>
+      <c r="I65" t="s">
         <v>2642</v>
       </c>
-      <c r="I65" t="s">
+      <c r="J65" t="s">
         <v>2643</v>
       </c>
-      <c r="J65" t="s">
+      <c r="K65" t="s">
         <v>2644</v>
       </c>
-      <c r="K65" t="s">
+      <c r="L65" t="s">
         <v>2645</v>
-      </c>
-      <c r="L65" t="s">
-        <v>2646</v>
       </c>
       <c r="M65" t="s">
         <v>1437</v>
@@ -41681,19 +41704,19 @@
     </row>
     <row r="66" spans="8:27" ht="15" customHeight="1">
       <c r="H66" t="s">
+        <v>2646</v>
+      </c>
+      <c r="I66" t="s">
         <v>2647</v>
       </c>
-      <c r="I66" t="s">
+      <c r="J66" t="s">
         <v>2648</v>
       </c>
-      <c r="J66" t="s">
+      <c r="L66" t="s">
         <v>2649</v>
       </c>
-      <c r="L66" t="s">
+      <c r="M66" t="s">
         <v>2650</v>
-      </c>
-      <c r="M66" t="s">
-        <v>2651</v>
       </c>
       <c r="O66" t="s">
         <v>1644</v>
@@ -41701,39 +41724,39 @@
     </row>
     <row r="67" spans="8:27" ht="15" customHeight="1">
       <c r="H67" t="s">
+        <v>2651</v>
+      </c>
+      <c r="I67" t="s">
         <v>2652</v>
       </c>
-      <c r="I67" t="s">
+      <c r="J67" t="s">
         <v>2653</v>
       </c>
-      <c r="J67" t="s">
+      <c r="K67" t="s">
         <v>2654</v>
       </c>
-      <c r="K67" t="s">
+      <c r="L67" t="s">
         <v>2655</v>
-      </c>
-      <c r="L67" t="s">
-        <v>2656</v>
       </c>
       <c r="M67" t="s">
         <v>1912</v>
       </c>
       <c r="O67" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="68" spans="8:27" ht="15" customHeight="1">
       <c r="H68" t="s">
+        <v>2657</v>
+      </c>
+      <c r="I68" t="s">
         <v>2658</v>
       </c>
-      <c r="I68" t="s">
+      <c r="K68" t="s">
         <v>2659</v>
       </c>
-      <c r="K68" t="s">
+      <c r="L68" t="s">
         <v>2660</v>
-      </c>
-      <c r="L68" t="s">
-        <v>2661</v>
       </c>
       <c r="M68" t="s">
         <v>1431</v>
@@ -41744,19 +41767,19 @@
     </row>
     <row r="69" spans="8:27" ht="11.5" customHeight="1">
       <c r="H69" t="s">
+        <v>2661</v>
+      </c>
+      <c r="I69" t="s">
         <v>2662</v>
       </c>
-      <c r="I69" t="s">
+      <c r="J69" t="s">
         <v>2663</v>
       </c>
-      <c r="J69" t="s">
+      <c r="K69" t="s">
+        <v>2659</v>
+      </c>
+      <c r="L69" t="s">
         <v>2664</v>
-      </c>
-      <c r="K69" t="s">
-        <v>2660</v>
-      </c>
-      <c r="L69" t="s">
-        <v>2665</v>
       </c>
       <c r="M69" t="s">
         <v>1431</v>
@@ -41768,7 +41791,7 @@
         <v>2241</v>
       </c>
       <c r="Y69" t="s">
-        <v>2666</v>
+        <v>2665</v>
       </c>
       <c r="AA69" t="s">
         <v>45</v>
@@ -41776,19 +41799,19 @@
     </row>
     <row r="70" spans="8:27" ht="15" customHeight="1">
       <c r="H70" t="s">
+        <v>2666</v>
+      </c>
+      <c r="I70" t="s">
         <v>2667</v>
       </c>
-      <c r="I70" t="s">
+      <c r="K70" t="s">
         <v>2668</v>
       </c>
-      <c r="K70" t="s">
+      <c r="L70" t="s">
         <v>2669</v>
       </c>
-      <c r="L70" t="s">
+      <c r="M70" t="s">
         <v>2670</v>
-      </c>
-      <c r="M70" t="s">
-        <v>2671</v>
       </c>
       <c r="O70" t="s">
         <v>1644</v>
@@ -41796,16 +41819,16 @@
     </row>
     <row r="71" spans="8:27" ht="15" customHeight="1">
       <c r="H71" t="s">
+        <v>2671</v>
+      </c>
+      <c r="I71" t="s">
         <v>2672</v>
       </c>
-      <c r="I71" t="s">
+      <c r="K71" t="s">
         <v>2673</v>
       </c>
-      <c r="K71" t="s">
+      <c r="L71" t="s">
         <v>2674</v>
-      </c>
-      <c r="L71" t="s">
-        <v>2675</v>
       </c>
       <c r="M71" t="s">
         <v>1758</v>
@@ -41816,19 +41839,19 @@
     </row>
     <row r="72" spans="8:27" ht="15" customHeight="1">
       <c r="H72" t="s">
+        <v>2675</v>
+      </c>
+      <c r="I72" t="s">
         <v>2676</v>
       </c>
-      <c r="I72" t="s">
+      <c r="J72" t="s">
         <v>2677</v>
       </c>
-      <c r="J72" t="s">
+      <c r="K72" t="s">
         <v>2678</v>
       </c>
-      <c r="K72" t="s">
+      <c r="L72" t="s">
         <v>2679</v>
-      </c>
-      <c r="L72" t="s">
-        <v>2680</v>
       </c>
       <c r="M72" t="s">
         <v>1758</v>
@@ -41839,82 +41862,82 @@
     </row>
     <row r="73" spans="8:27" ht="15" customHeight="1">
       <c r="H73" t="s">
+        <v>2680</v>
+      </c>
+      <c r="I73" t="s">
         <v>2681</v>
       </c>
-      <c r="I73" t="s">
+      <c r="J73" t="s">
         <v>2682</v>
       </c>
-      <c r="J73" t="s">
+      <c r="K73" t="s">
         <v>2683</v>
       </c>
-      <c r="K73" t="s">
+      <c r="L73" t="s">
         <v>2684</v>
-      </c>
-      <c r="L73" t="s">
-        <v>2685</v>
       </c>
       <c r="M73" t="s">
         <v>1691</v>
       </c>
       <c r="O73" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="74" spans="8:27" ht="15" customHeight="1">
       <c r="H74" t="s">
+        <v>2685</v>
+      </c>
+      <c r="I74" t="s">
         <v>2686</v>
       </c>
-      <c r="I74" t="s">
+      <c r="J74" t="s">
         <v>2687</v>
       </c>
-      <c r="J74" t="s">
+      <c r="L74" t="s">
         <v>2688</v>
       </c>
-      <c r="L74" t="s">
+      <c r="M74" t="s">
         <v>2689</v>
       </c>
-      <c r="M74" t="s">
-        <v>2690</v>
-      </c>
       <c r="O74" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="75" spans="8:27" ht="15" customHeight="1">
       <c r="H75" t="s">
+        <v>2690</v>
+      </c>
+      <c r="I75" t="s">
         <v>2691</v>
       </c>
-      <c r="I75" t="s">
+      <c r="K75" t="s">
         <v>2692</v>
       </c>
-      <c r="K75" t="s">
+      <c r="L75" t="s">
         <v>2693</v>
       </c>
-      <c r="L75" t="s">
+      <c r="M75" t="s">
         <v>2694</v>
       </c>
-      <c r="M75" t="s">
-        <v>2695</v>
-      </c>
       <c r="O75" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="76" spans="8:27" ht="15" customHeight="1">
       <c r="H76" t="s">
+        <v>2695</v>
+      </c>
+      <c r="I76" t="s">
         <v>2696</v>
       </c>
-      <c r="I76" t="s">
+      <c r="K76" t="s">
         <v>2697</v>
       </c>
-      <c r="K76" t="s">
+      <c r="L76" t="s">
         <v>2698</v>
       </c>
-      <c r="L76" t="s">
+      <c r="M76" t="s">
         <v>2699</v>
-      </c>
-      <c r="M76" t="s">
-        <v>2700</v>
       </c>
       <c r="O76" t="s">
         <v>1644</v>
@@ -41922,22 +41945,22 @@
     </row>
     <row r="77" spans="8:27" ht="15" customHeight="1">
       <c r="H77" t="s">
+        <v>2700</v>
+      </c>
+      <c r="I77" t="s">
         <v>2701</v>
       </c>
-      <c r="I77" t="s">
+      <c r="J77" t="s">
         <v>2702</v>
       </c>
-      <c r="J77" t="s">
+      <c r="K77" t="s">
         <v>2703</v>
       </c>
-      <c r="K77" t="s">
+      <c r="L77" t="s">
         <v>2704</v>
       </c>
-      <c r="L77" t="s">
+      <c r="M77" t="s">
         <v>2705</v>
-      </c>
-      <c r="M77" t="s">
-        <v>2706</v>
       </c>
       <c r="O77" t="s">
         <v>1644</v>
@@ -41945,22 +41968,22 @@
     </row>
     <row r="78" spans="8:27" ht="15" customHeight="1">
       <c r="H78" t="s">
+        <v>2706</v>
+      </c>
+      <c r="I78" t="s">
         <v>2707</v>
       </c>
-      <c r="I78" t="s">
+      <c r="J78" t="s">
         <v>2708</v>
       </c>
-      <c r="J78" t="s">
+      <c r="K78" t="s">
         <v>2709</v>
       </c>
-      <c r="K78" t="s">
+      <c r="L78" t="s">
         <v>2710</v>
       </c>
-      <c r="L78" t="s">
-        <v>2711</v>
-      </c>
       <c r="M78" t="s">
-        <v>2690</v>
+        <v>2689</v>
       </c>
       <c r="O78" t="s">
         <v>1644</v>
@@ -41968,19 +41991,19 @@
     </row>
     <row r="79" spans="8:27" ht="15" customHeight="1">
       <c r="H79" t="s">
+        <v>2711</v>
+      </c>
+      <c r="I79" t="s">
         <v>2712</v>
       </c>
-      <c r="I79" t="s">
+      <c r="J79" t="s">
         <v>2713</v>
       </c>
-      <c r="J79" t="s">
+      <c r="K79" t="s">
         <v>2714</v>
       </c>
-      <c r="K79" t="s">
+      <c r="L79" t="s">
         <v>2715</v>
-      </c>
-      <c r="L79" t="s">
-        <v>2716</v>
       </c>
       <c r="M79" t="s">
         <v>2222</v>
@@ -41991,19 +42014,19 @@
     </row>
     <row r="80" spans="8:27" ht="15" customHeight="1">
       <c r="H80" t="s">
+        <v>2716</v>
+      </c>
+      <c r="I80" t="s">
         <v>2717</v>
       </c>
-      <c r="I80" t="s">
+      <c r="K80" t="s">
         <v>2718</v>
       </c>
-      <c r="K80" t="s">
+      <c r="L80" t="s">
         <v>2719</v>
       </c>
-      <c r="L80" t="s">
+      <c r="M80" t="s">
         <v>2720</v>
-      </c>
-      <c r="M80" t="s">
-        <v>2721</v>
       </c>
       <c r="O80" t="s">
         <v>1644</v>
@@ -42023,7 +42046,7 @@
         <v>2297</v>
       </c>
       <c r="L81" t="s">
-        <v>2722</v>
+        <v>2721</v>
       </c>
       <c r="M81" t="s">
         <v>1448</v>
@@ -42043,19 +42066,19 @@
     </row>
     <row r="82" spans="8:27" ht="15" customHeight="1">
       <c r="H82" t="s">
+        <v>2722</v>
+      </c>
+      <c r="I82" t="s">
+        <v>2637</v>
+      </c>
+      <c r="J82" t="s">
         <v>2723</v>
       </c>
-      <c r="I82" t="s">
-        <v>2638</v>
-      </c>
-      <c r="J82" t="s">
+      <c r="K82" t="s">
+        <v>2639</v>
+      </c>
+      <c r="L82" t="s">
         <v>2724</v>
-      </c>
-      <c r="K82" t="s">
-        <v>2640</v>
-      </c>
-      <c r="L82" t="s">
-        <v>2725</v>
       </c>
       <c r="M82" t="s">
         <v>1437</v>
@@ -42064,10 +42087,10 @@
         <v>1644</v>
       </c>
       <c r="X82" t="s">
+        <v>2725</v>
+      </c>
+      <c r="Y82" t="s">
         <v>2726</v>
-      </c>
-      <c r="Y82" t="s">
-        <v>2727</v>
       </c>
       <c r="AA82" t="s">
         <v>45</v>
@@ -42075,19 +42098,19 @@
     </row>
     <row r="83" spans="8:27" ht="15" customHeight="1">
       <c r="H83" t="s">
+        <v>2727</v>
+      </c>
+      <c r="I83" t="s">
         <v>2728</v>
       </c>
-      <c r="I83" t="s">
+      <c r="J83" t="s">
         <v>2729</v>
       </c>
-      <c r="J83" t="s">
+      <c r="K83" t="s">
         <v>2730</v>
       </c>
-      <c r="K83" t="s">
+      <c r="L83" t="s">
         <v>2731</v>
-      </c>
-      <c r="L83" t="s">
-        <v>2732</v>
       </c>
       <c r="M83" t="s">
         <v>1437</v>
@@ -42096,10 +42119,10 @@
         <v>1644</v>
       </c>
       <c r="X83" t="s">
+        <v>2732</v>
+      </c>
+      <c r="Y83" t="s">
         <v>2733</v>
-      </c>
-      <c r="Y83" t="s">
-        <v>2734</v>
       </c>
       <c r="AA83" t="s">
         <v>55</v>
@@ -42107,19 +42130,19 @@
     </row>
     <row r="84" spans="8:27" ht="15" customHeight="1">
       <c r="H84" t="s">
+        <v>2734</v>
+      </c>
+      <c r="I84" t="s">
         <v>2735</v>
       </c>
-      <c r="I84" t="s">
+      <c r="J84" t="s">
         <v>2736</v>
       </c>
-      <c r="J84" t="s">
+      <c r="K84" t="s">
         <v>2737</v>
       </c>
-      <c r="K84" t="s">
+      <c r="L84" t="s">
         <v>2738</v>
-      </c>
-      <c r="L84" t="s">
-        <v>2739</v>
       </c>
       <c r="M84" t="s">
         <v>1437</v>
@@ -42128,10 +42151,10 @@
         <v>1644</v>
       </c>
       <c r="X84" t="s">
+        <v>2739</v>
+      </c>
+      <c r="Y84" t="s">
         <v>2740</v>
-      </c>
-      <c r="Y84" t="s">
-        <v>2741</v>
       </c>
       <c r="AA84" t="s">
         <v>45</v>
@@ -42139,31 +42162,31 @@
     </row>
     <row r="85" spans="8:27" ht="15" customHeight="1">
       <c r="H85" t="s">
+        <v>2741</v>
+      </c>
+      <c r="I85" t="s">
         <v>2742</v>
       </c>
-      <c r="I85" t="s">
+      <c r="J85" t="s">
         <v>2743</v>
       </c>
-      <c r="J85" t="s">
+      <c r="K85" t="s">
         <v>2744</v>
       </c>
-      <c r="K85" t="s">
+      <c r="L85" t="s">
         <v>2745</v>
-      </c>
-      <c r="L85" t="s">
-        <v>2746</v>
       </c>
       <c r="M85" t="s">
         <v>1437</v>
       </c>
       <c r="O85" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="X85" t="s">
+        <v>2746</v>
+      </c>
+      <c r="Y85" t="s">
         <v>2747</v>
-      </c>
-      <c r="Y85" t="s">
-        <v>2748</v>
       </c>
       <c r="AA85" t="s">
         <v>45</v>
@@ -42171,19 +42194,19 @@
     </row>
     <row r="86" spans="8:27" ht="15" customHeight="1">
       <c r="H86" t="s">
+        <v>2748</v>
+      </c>
+      <c r="I86" t="s">
         <v>2749</v>
       </c>
-      <c r="I86" t="s">
+      <c r="J86" t="s">
         <v>2750</v>
       </c>
-      <c r="J86" t="s">
+      <c r="K86" t="s">
         <v>2751</v>
       </c>
-      <c r="K86" t="s">
+      <c r="L86" t="s">
         <v>2752</v>
-      </c>
-      <c r="L86" t="s">
-        <v>2753</v>
       </c>
       <c r="M86" t="s">
         <v>1437</v>
@@ -42192,10 +42215,10 @@
         <v>1644</v>
       </c>
       <c r="X86" t="s">
+        <v>2753</v>
+      </c>
+      <c r="Y86" t="s">
         <v>2754</v>
-      </c>
-      <c r="Y86" t="s">
-        <v>2755</v>
       </c>
       <c r="AA86" t="s">
         <v>55</v>
@@ -42203,19 +42226,19 @@
     </row>
     <row r="87" spans="8:27" ht="15" customHeight="1">
       <c r="H87" t="s">
+        <v>2755</v>
+      </c>
+      <c r="I87" t="s">
         <v>2756</v>
       </c>
-      <c r="I87" t="s">
+      <c r="J87" t="s">
         <v>2757</v>
       </c>
-      <c r="J87" t="s">
+      <c r="K87" t="s">
         <v>2758</v>
       </c>
-      <c r="K87" t="s">
+      <c r="L87" t="s">
         <v>2759</v>
-      </c>
-      <c r="L87" t="s">
-        <v>2760</v>
       </c>
       <c r="M87" t="s">
         <v>1437</v>
@@ -42224,10 +42247,10 @@
         <v>1644</v>
       </c>
       <c r="X87" t="s">
+        <v>2760</v>
+      </c>
+      <c r="Y87" t="s">
         <v>2761</v>
-      </c>
-      <c r="Y87" t="s">
-        <v>2762</v>
       </c>
       <c r="AA87" t="s">
         <v>45</v>
@@ -42235,31 +42258,31 @@
     </row>
     <row r="88" spans="8:27" ht="15" customHeight="1">
       <c r="H88" t="s">
+        <v>2626</v>
+      </c>
+      <c r="I88" t="s">
         <v>2627</v>
       </c>
-      <c r="I88" t="s">
-        <v>2628</v>
-      </c>
       <c r="J88" t="s">
+        <v>2762</v>
+      </c>
+      <c r="K88" t="s">
+        <v>2629</v>
+      </c>
+      <c r="L88" t="s">
         <v>2763</v>
-      </c>
-      <c r="K88" t="s">
-        <v>2630</v>
-      </c>
-      <c r="L88" t="s">
-        <v>2764</v>
       </c>
       <c r="M88" t="s">
         <v>1448</v>
       </c>
       <c r="O88" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="X88" t="s">
+        <v>2764</v>
+      </c>
+      <c r="Y88" t="s">
         <v>2765</v>
-      </c>
-      <c r="Y88" t="s">
-        <v>2766</v>
       </c>
       <c r="AA88" t="s">
         <v>45</v>
@@ -42267,31 +42290,31 @@
     </row>
     <row r="89" spans="8:27" ht="15" customHeight="1">
       <c r="H89" t="s">
+        <v>2766</v>
+      </c>
+      <c r="I89" t="s">
+        <v>2632</v>
+      </c>
+      <c r="J89" t="s">
+        <v>2633</v>
+      </c>
+      <c r="K89" t="s">
+        <v>2634</v>
+      </c>
+      <c r="L89" t="s">
         <v>2767</v>
-      </c>
-      <c r="I89" t="s">
-        <v>2633</v>
-      </c>
-      <c r="J89" t="s">
-        <v>2634</v>
-      </c>
-      <c r="K89" t="s">
-        <v>2635</v>
-      </c>
-      <c r="L89" t="s">
-        <v>2768</v>
       </c>
       <c r="M89" t="s">
         <v>1448</v>
       </c>
       <c r="O89" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="X89" t="s">
+        <v>2768</v>
+      </c>
+      <c r="Y89" t="s">
         <v>2769</v>
-      </c>
-      <c r="Y89" t="s">
-        <v>2770</v>
       </c>
       <c r="AA89" t="s">
         <v>45</v>
@@ -42299,16 +42322,16 @@
     </row>
     <row r="90" spans="8:27" ht="15" customHeight="1">
       <c r="H90" t="s">
-        <v>2696</v>
+        <v>2695</v>
       </c>
       <c r="I90" t="s">
+        <v>2770</v>
+      </c>
+      <c r="K90" t="s">
+        <v>2697</v>
+      </c>
+      <c r="L90" t="s">
         <v>2771</v>
-      </c>
-      <c r="K90" t="s">
-        <v>2698</v>
-      </c>
-      <c r="L90" t="s">
-        <v>2772</v>
       </c>
       <c r="M90" t="s">
         <v>1448</v>
@@ -42322,31 +42345,31 @@
     </row>
     <row r="91" spans="8:27" ht="15" customHeight="1">
       <c r="H91" t="s">
+        <v>2772</v>
+      </c>
+      <c r="I91" t="s">
         <v>2773</v>
       </c>
-      <c r="I91" t="s">
+      <c r="J91" t="s">
         <v>2774</v>
       </c>
-      <c r="J91" t="s">
+      <c r="K91" t="s">
         <v>2775</v>
       </c>
-      <c r="K91" t="s">
+      <c r="L91" t="s">
         <v>2776</v>
-      </c>
-      <c r="L91" t="s">
-        <v>2777</v>
       </c>
       <c r="M91" t="s">
         <v>1448</v>
       </c>
       <c r="O91" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="X91" t="s">
+        <v>2777</v>
+      </c>
+      <c r="Y91" t="s">
         <v>2778</v>
-      </c>
-      <c r="Y91" t="s">
-        <v>2779</v>
       </c>
       <c r="AA91" t="s">
         <v>45</v>
@@ -42354,19 +42377,19 @@
     </row>
     <row r="92" spans="8:27" ht="15" customHeight="1">
       <c r="H92" t="s">
+        <v>2621</v>
+      </c>
+      <c r="I92" t="s">
         <v>2622</v>
       </c>
-      <c r="I92" t="s">
+      <c r="J92" t="s">
         <v>2623</v>
       </c>
-      <c r="J92" t="s">
+      <c r="K92" t="s">
         <v>2624</v>
       </c>
-      <c r="K92" t="s">
-        <v>2625</v>
-      </c>
       <c r="L92" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="M92" t="s">
         <v>1448</v>
@@ -42375,10 +42398,10 @@
         <v>1644</v>
       </c>
       <c r="X92" t="s">
+        <v>2780</v>
+      </c>
+      <c r="Y92" t="s">
         <v>2781</v>
-      </c>
-      <c r="Y92" t="s">
-        <v>2782</v>
       </c>
       <c r="AA92" t="s">
         <v>45</v>
@@ -42386,16 +42409,16 @@
     </row>
     <row r="93" spans="8:27" ht="15" customHeight="1">
       <c r="H93" t="s">
+        <v>2617</v>
+      </c>
+      <c r="I93" t="s">
         <v>2618</v>
       </c>
-      <c r="I93" t="s">
+      <c r="K93" t="s">
         <v>2619</v>
       </c>
-      <c r="K93" t="s">
-        <v>2620</v>
-      </c>
       <c r="L93" t="s">
-        <v>2783</v>
+        <v>2782</v>
       </c>
       <c r="M93" t="s">
         <v>1448</v>
@@ -42409,19 +42432,19 @@
     </row>
     <row r="94" spans="8:27" ht="15" customHeight="1">
       <c r="H94" t="s">
+        <v>2783</v>
+      </c>
+      <c r="I94" t="s">
         <v>2784</v>
       </c>
-      <c r="I94" t="s">
+      <c r="J94" t="s">
+        <v>2783</v>
+      </c>
+      <c r="K94" t="s">
         <v>2785</v>
       </c>
-      <c r="J94" t="s">
-        <v>2784</v>
-      </c>
-      <c r="K94" t="s">
+      <c r="L94" t="s">
         <v>2786</v>
-      </c>
-      <c r="L94" t="s">
-        <v>2787</v>
       </c>
       <c r="M94" t="s">
         <v>1448</v>
@@ -42430,10 +42453,10 @@
         <v>1644</v>
       </c>
       <c r="X94" t="s">
+        <v>2787</v>
+      </c>
+      <c r="Y94" t="s">
         <v>2788</v>
-      </c>
-      <c r="Y94" t="s">
-        <v>2789</v>
       </c>
       <c r="AA94" t="s">
         <v>45</v>
@@ -42441,16 +42464,16 @@
     </row>
     <row r="95" spans="8:27" ht="15" customHeight="1">
       <c r="H95" t="s">
+        <v>2789</v>
+      </c>
+      <c r="I95" t="s">
         <v>2790</v>
       </c>
-      <c r="I95" t="s">
+      <c r="K95" t="s">
         <v>2791</v>
       </c>
-      <c r="K95" t="s">
+      <c r="L95" t="s">
         <v>2792</v>
-      </c>
-      <c r="L95" t="s">
-        <v>2793</v>
       </c>
       <c r="M95" t="s">
         <v>1448</v>
@@ -42464,16 +42487,16 @@
     </row>
     <row r="96" spans="8:27" ht="15" customHeight="1">
       <c r="H96" t="s">
+        <v>2793</v>
+      </c>
+      <c r="I96" t="s">
         <v>2794</v>
       </c>
-      <c r="I96" t="s">
+      <c r="K96" t="s">
         <v>2795</v>
       </c>
-      <c r="K96" t="s">
+      <c r="L96" t="s">
         <v>2796</v>
-      </c>
-      <c r="L96" t="s">
-        <v>2797</v>
       </c>
       <c r="M96" t="s">
         <v>1448</v>
@@ -42487,16 +42510,16 @@
     </row>
     <row r="97" spans="8:27" ht="15" customHeight="1">
       <c r="H97" t="s">
+        <v>2797</v>
+      </c>
+      <c r="I97" t="s">
         <v>2798</v>
       </c>
-      <c r="I97" t="s">
+      <c r="J97" t="s">
         <v>2799</v>
       </c>
-      <c r="J97" t="s">
+      <c r="L97" t="s">
         <v>2800</v>
-      </c>
-      <c r="L97" t="s">
-        <v>2801</v>
       </c>
       <c r="M97" t="s">
         <v>1448</v>
@@ -42505,10 +42528,10 @@
         <v>1644</v>
       </c>
       <c r="X97" t="s">
+        <v>2801</v>
+      </c>
+      <c r="Y97" t="s">
         <v>2802</v>
-      </c>
-      <c r="Y97" t="s">
-        <v>2803</v>
       </c>
       <c r="AA97" t="s">
         <v>45</v>
@@ -42516,16 +42539,16 @@
     </row>
     <row r="98" spans="8:27" ht="15" customHeight="1">
       <c r="H98" t="s">
+        <v>2613</v>
+      </c>
+      <c r="I98" t="s">
         <v>2614</v>
       </c>
-      <c r="I98" t="s">
-        <v>2615</v>
-      </c>
       <c r="J98" t="s">
+        <v>2803</v>
+      </c>
+      <c r="L98" t="s">
         <v>2804</v>
-      </c>
-      <c r="L98" t="s">
-        <v>2805</v>
       </c>
       <c r="M98" t="s">
         <v>1448</v>
@@ -42534,10 +42557,10 @@
         <v>1644</v>
       </c>
       <c r="X98" t="s">
+        <v>2805</v>
+      </c>
+      <c r="Y98" t="s">
         <v>2806</v>
-      </c>
-      <c r="Y98" t="s">
-        <v>2807</v>
       </c>
       <c r="AA98" t="s">
         <v>45</v>
@@ -42545,31 +42568,31 @@
     </row>
     <row r="99" spans="8:27" ht="11.5" customHeight="1">
       <c r="H99" t="s">
+        <v>2807</v>
+      </c>
+      <c r="I99" t="s">
         <v>2808</v>
       </c>
-      <c r="I99" t="s">
+      <c r="J99" t="s">
         <v>2809</v>
       </c>
-      <c r="J99" t="s">
+      <c r="K99" t="s">
         <v>2810</v>
       </c>
-      <c r="K99" t="s">
+      <c r="L99" t="s">
         <v>2811</v>
       </c>
-      <c r="L99" t="s">
+      <c r="M99" t="s">
         <v>2812</v>
-      </c>
-      <c r="M99" t="s">
-        <v>2813</v>
       </c>
       <c r="O99" t="s">
         <v>1644</v>
       </c>
       <c r="X99" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="Y99" t="s">
-        <v>2814</v>
+        <v>2813</v>
       </c>
       <c r="AA99" t="s">
         <v>45</v>
@@ -42577,19 +42600,19 @@
     </row>
     <row r="100" spans="8:27" ht="11.5" customHeight="1">
       <c r="H100" t="s">
+        <v>2814</v>
+      </c>
+      <c r="I100" t="s">
         <v>2815</v>
       </c>
-      <c r="I100" t="s">
+      <c r="K100" t="s">
         <v>2816</v>
       </c>
-      <c r="K100" t="s">
+      <c r="L100" t="s">
         <v>2817</v>
       </c>
-      <c r="L100" t="s">
+      <c r="M100" t="s">
         <v>2818</v>
-      </c>
-      <c r="M100" t="s">
-        <v>2819</v>
       </c>
       <c r="O100" t="s">
         <v>1644</v>
@@ -42600,16 +42623,16 @@
     </row>
     <row r="101" spans="8:27" ht="11.5" customHeight="1">
       <c r="H101" t="s">
+        <v>2819</v>
+      </c>
+      <c r="I101" t="s">
         <v>2820</v>
       </c>
-      <c r="I101" t="s">
+      <c r="L101" t="s">
         <v>2821</v>
       </c>
-      <c r="L101" t="s">
+      <c r="M101" t="s">
         <v>2822</v>
-      </c>
-      <c r="M101" t="s">
-        <v>2823</v>
       </c>
       <c r="O101" t="s">
         <v>1644</v>
@@ -42620,19 +42643,19 @@
     </row>
     <row r="102" spans="8:27" ht="11.5" customHeight="1">
       <c r="H102" t="s">
+        <v>2823</v>
+      </c>
+      <c r="I102" t="s">
         <v>2824</v>
       </c>
-      <c r="I102" t="s">
+      <c r="K102" t="s">
         <v>2825</v>
       </c>
-      <c r="K102" t="s">
+      <c r="L102" t="s">
         <v>2826</v>
       </c>
-      <c r="L102" t="s">
+      <c r="M102" t="s">
         <v>2827</v>
-      </c>
-      <c r="M102" t="s">
-        <v>2828</v>
       </c>
       <c r="O102" t="s">
         <v>1644</v>
@@ -42643,19 +42666,19 @@
     </row>
     <row r="103" spans="8:27" ht="11.5" customHeight="1">
       <c r="H103" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="I103" t="s">
+        <v>2828</v>
+      </c>
+      <c r="K103" t="s">
         <v>2829</v>
       </c>
-      <c r="K103" t="s">
+      <c r="L103" t="s">
         <v>2830</v>
       </c>
-      <c r="L103" t="s">
+      <c r="M103" t="s">
         <v>2831</v>
-      </c>
-      <c r="M103" t="s">
-        <v>2832</v>
       </c>
       <c r="O103" t="s">
         <v>1644</v>
@@ -42666,16 +42689,16 @@
     </row>
     <row r="104" spans="8:27" ht="15" customHeight="1">
       <c r="H104" t="s">
+        <v>2832</v>
+      </c>
+      <c r="I104" t="s">
         <v>2833</v>
       </c>
-      <c r="I104" t="s">
+      <c r="L104" t="s">
         <v>2834</v>
       </c>
-      <c r="L104" t="s">
+      <c r="M104" t="s">
         <v>2835</v>
-      </c>
-      <c r="M104" t="s">
-        <v>2836</v>
       </c>
       <c r="O104" t="s">
         <v>1644</v>
@@ -42686,19 +42709,19 @@
     </row>
     <row r="105" spans="8:27" ht="15" customHeight="1">
       <c r="H105" t="s">
-        <v>2662</v>
+        <v>2661</v>
       </c>
       <c r="I105" t="s">
+        <v>2658</v>
+      </c>
+      <c r="K105" t="s">
         <v>2659</v>
       </c>
-      <c r="K105" t="s">
-        <v>2660</v>
-      </c>
       <c r="L105" t="s">
+        <v>2836</v>
+      </c>
+      <c r="M105" t="s">
         <v>2837</v>
-      </c>
-      <c r="M105" t="s">
-        <v>2838</v>
       </c>
       <c r="O105" t="s">
         <v>1644</v>
@@ -42709,16 +42732,16 @@
     </row>
     <row r="106" spans="8:27" ht="15" customHeight="1">
       <c r="H106" t="s">
+        <v>2838</v>
+      </c>
+      <c r="I106" t="s">
         <v>2839</v>
       </c>
-      <c r="I106" t="s">
+      <c r="L106" t="s">
         <v>2840</v>
       </c>
-      <c r="L106" t="s">
+      <c r="M106" t="s">
         <v>2841</v>
-      </c>
-      <c r="M106" t="s">
-        <v>2842</v>
       </c>
       <c r="O106" t="s">
         <v>1644</v>
@@ -42729,22 +42752,22 @@
     </row>
     <row r="107" spans="8:27" ht="15" customHeight="1">
       <c r="H107" t="s">
+        <v>2842</v>
+      </c>
+      <c r="I107" t="s">
         <v>2843</v>
       </c>
-      <c r="I107" t="s">
+      <c r="J107" t="s">
         <v>2844</v>
       </c>
-      <c r="J107" t="s">
+      <c r="K107" t="s">
         <v>2845</v>
       </c>
-      <c r="K107" t="s">
+      <c r="L107" t="s">
         <v>2846</v>
       </c>
-      <c r="L107" t="s">
-        <v>2847</v>
-      </c>
       <c r="M107" t="s">
-        <v>2690</v>
+        <v>2689</v>
       </c>
       <c r="O107" t="s">
         <v>1644</v>
@@ -42753,7 +42776,7 @@
         <v>1947</v>
       </c>
       <c r="Y107" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
       <c r="AA107" t="s">
         <v>45</v>
@@ -42761,16 +42784,16 @@
     </row>
     <row r="108" spans="8:27" ht="15" customHeight="1">
       <c r="H108" t="s">
+        <v>2848</v>
+      </c>
+      <c r="I108" t="s">
         <v>2849</v>
       </c>
-      <c r="I108" t="s">
+      <c r="L108" t="s">
         <v>2850</v>
       </c>
-      <c r="L108" t="s">
+      <c r="M108" t="s">
         <v>2851</v>
-      </c>
-      <c r="M108" t="s">
-        <v>2852</v>
       </c>
       <c r="O108" t="s">
         <v>1644</v>
@@ -42781,16 +42804,16 @@
     </row>
     <row r="109" spans="8:27" ht="15" customHeight="1">
       <c r="H109" t="s">
+        <v>2852</v>
+      </c>
+      <c r="I109" t="s">
         <v>2853</v>
       </c>
-      <c r="I109" t="s">
+      <c r="L109" t="s">
         <v>2854</v>
       </c>
-      <c r="L109" t="s">
-        <v>2855</v>
-      </c>
       <c r="M109" t="s">
-        <v>2690</v>
+        <v>2689</v>
       </c>
       <c r="O109" t="s">
         <v>1644</v>
@@ -42801,22 +42824,22 @@
     </row>
     <row r="110" spans="8:27" ht="15" customHeight="1">
       <c r="H110" t="s">
+        <v>2855</v>
+      </c>
+      <c r="I110" t="s">
         <v>2856</v>
       </c>
-      <c r="I110" t="s">
+      <c r="K110" t="s">
         <v>2857</v>
       </c>
-      <c r="K110" t="s">
+      <c r="L110" t="s">
         <v>2858</v>
       </c>
-      <c r="L110" t="s">
-        <v>2859</v>
-      </c>
       <c r="M110" t="s">
-        <v>2690</v>
+        <v>2689</v>
       </c>
       <c r="O110" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="AA110" t="s">
         <v>45</v>
@@ -42824,31 +42847,31 @@
     </row>
     <row r="111" spans="8:27" ht="15" customHeight="1">
       <c r="H111" t="s">
+        <v>2651</v>
+      </c>
+      <c r="I111" t="s">
         <v>2652</v>
       </c>
-      <c r="I111" t="s">
+      <c r="J111" t="s">
         <v>2653</v>
       </c>
-      <c r="J111" t="s">
+      <c r="K111" t="s">
         <v>2654</v>
       </c>
-      <c r="K111" t="s">
-        <v>2655</v>
-      </c>
       <c r="L111" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="M111" t="s">
         <v>1912</v>
       </c>
       <c r="O111" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="X111" t="s">
+        <v>2860</v>
+      </c>
+      <c r="Y111" t="s">
         <v>2861</v>
-      </c>
-      <c r="Y111" t="s">
-        <v>2862</v>
       </c>
       <c r="AA111" t="s">
         <v>45</v>
@@ -42856,19 +42879,19 @@
     </row>
     <row r="112" spans="8:27" ht="15" customHeight="1">
       <c r="H112" t="s">
+        <v>2862</v>
+      </c>
+      <c r="I112" t="s">
         <v>2863</v>
       </c>
-      <c r="I112" t="s">
+      <c r="L112" t="s">
         <v>2864</v>
       </c>
-      <c r="L112" t="s">
-        <v>2865</v>
-      </c>
       <c r="M112" t="s">
-        <v>2690</v>
+        <v>2689</v>
       </c>
       <c r="O112" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="AA112" t="s">
         <v>45</v>
@@ -42876,22 +42899,22 @@
     </row>
     <row r="113" spans="8:27" ht="15" customHeight="1">
       <c r="H113" t="s">
+        <v>2865</v>
+      </c>
+      <c r="I113" t="s">
         <v>2866</v>
       </c>
-      <c r="I113" t="s">
+      <c r="K113" t="s">
         <v>2867</v>
       </c>
-      <c r="K113" t="s">
+      <c r="L113" t="s">
         <v>2868</v>
       </c>
-      <c r="L113" t="s">
+      <c r="M113" t="s">
         <v>2869</v>
       </c>
-      <c r="M113" t="s">
-        <v>2870</v>
-      </c>
       <c r="O113" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="AA113" t="s">
         <v>55</v>
@@ -42899,16 +42922,16 @@
     </row>
     <row r="114" spans="8:27" ht="11.5" customHeight="1">
       <c r="H114" t="s">
+        <v>2870</v>
+      </c>
+      <c r="I114" t="s">
         <v>2871</v>
       </c>
-      <c r="I114" t="s">
+      <c r="K114" t="s">
         <v>2872</v>
       </c>
-      <c r="K114" t="s">
+      <c r="L114" t="s">
         <v>2873</v>
-      </c>
-      <c r="L114" t="s">
-        <v>2874</v>
       </c>
       <c r="M114" t="s">
         <v>1912</v>
@@ -42922,16 +42945,16 @@
     </row>
     <row r="115" spans="8:27" ht="11.5" customHeight="1">
       <c r="H115" t="s">
+        <v>2874</v>
+      </c>
+      <c r="I115" t="s">
         <v>2875</v>
       </c>
-      <c r="I115" t="s">
+      <c r="K115" t="s">
         <v>2876</v>
       </c>
-      <c r="K115" t="s">
+      <c r="L115" t="s">
         <v>2877</v>
-      </c>
-      <c r="L115" t="s">
-        <v>2878</v>
       </c>
       <c r="M115" t="s">
         <v>1912</v>
@@ -42945,31 +42968,31 @@
     </row>
     <row r="116" spans="8:27" ht="11.5" customHeight="1">
       <c r="H116" t="s">
+        <v>2878</v>
+      </c>
+      <c r="I116" t="s">
         <v>2879</v>
       </c>
-      <c r="I116" t="s">
+      <c r="J116" t="s">
         <v>2880</v>
       </c>
-      <c r="J116" t="s">
+      <c r="K116" t="s">
         <v>2881</v>
       </c>
-      <c r="K116" t="s">
+      <c r="L116" t="s">
         <v>2882</v>
       </c>
-      <c r="L116" t="s">
+      <c r="M116" t="s">
         <v>2883</v>
-      </c>
-      <c r="M116" t="s">
-        <v>2884</v>
       </c>
       <c r="O116" t="s">
         <v>1644</v>
       </c>
       <c r="X116" t="s">
+        <v>2884</v>
+      </c>
+      <c r="Y116" t="s">
         <v>2885</v>
-      </c>
-      <c r="Y116" t="s">
-        <v>2886</v>
       </c>
       <c r="AA116" t="s">
         <v>45</v>
@@ -42977,31 +43000,31 @@
     </row>
     <row r="117" spans="8:27" ht="11.5" customHeight="1">
       <c r="H117" t="s">
+        <v>2886</v>
+      </c>
+      <c r="I117" t="s">
         <v>2887</v>
       </c>
-      <c r="I117" t="s">
+      <c r="J117" t="s">
         <v>2888</v>
       </c>
-      <c r="J117" t="s">
+      <c r="L117" t="s">
         <v>2889</v>
       </c>
-      <c r="L117" t="s">
+      <c r="M117" t="s">
         <v>2890</v>
-      </c>
-      <c r="M117" t="s">
-        <v>2891</v>
       </c>
       <c r="O117" t="s">
         <v>1644</v>
       </c>
       <c r="W117" t="s">
+        <v>2891</v>
+      </c>
+      <c r="X117" t="s">
         <v>2892</v>
       </c>
-      <c r="X117" t="s">
+      <c r="Y117" t="s">
         <v>2893</v>
-      </c>
-      <c r="Y117" t="s">
-        <v>2894</v>
       </c>
       <c r="AA117" t="s">
         <v>55</v>
@@ -43009,31 +43032,31 @@
     </row>
     <row r="118" spans="8:27" ht="11.5" customHeight="1">
       <c r="H118" t="s">
+        <v>2894</v>
+      </c>
+      <c r="I118" t="s">
         <v>2895</v>
       </c>
-      <c r="I118" t="s">
+      <c r="J118" t="s">
         <v>2896</v>
       </c>
-      <c r="J118" t="s">
+      <c r="K118" t="s">
         <v>2897</v>
       </c>
-      <c r="K118" t="s">
+      <c r="L118" t="s">
         <v>2898</v>
       </c>
-      <c r="L118" t="s">
+      <c r="M118" t="s">
         <v>2899</v>
-      </c>
-      <c r="M118" t="s">
-        <v>2900</v>
       </c>
       <c r="O118" t="s">
         <v>1644</v>
       </c>
       <c r="X118" t="s">
+        <v>2900</v>
+      </c>
+      <c r="Y118" t="s">
         <v>2901</v>
-      </c>
-      <c r="Y118" t="s">
-        <v>2902</v>
       </c>
       <c r="AA118" t="s">
         <v>45</v>
@@ -43041,28 +43064,28 @@
     </row>
     <row r="119" spans="8:27" ht="11.5" customHeight="1">
       <c r="H119" t="s">
+        <v>2902</v>
+      </c>
+      <c r="I119" t="s">
         <v>2903</v>
       </c>
-      <c r="I119" t="s">
+      <c r="J119" t="s">
         <v>2904</v>
       </c>
-      <c r="J119" t="s">
+      <c r="L119" t="s">
         <v>2905</v>
       </c>
-      <c r="L119" t="s">
-        <v>2906</v>
-      </c>
       <c r="M119" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="O119" t="s">
         <v>1644</v>
       </c>
       <c r="X119" t="s">
+        <v>2906</v>
+      </c>
+      <c r="Y119" t="s">
         <v>2907</v>
-      </c>
-      <c r="Y119" t="s">
-        <v>2908</v>
       </c>
       <c r="AA119" t="s">
         <v>45</v>
@@ -43070,25 +43093,25 @@
     </row>
     <row r="120" spans="8:27" ht="11.5" customHeight="1">
       <c r="H120" t="s">
+        <v>2908</v>
+      </c>
+      <c r="J120" t="s">
         <v>2909</v>
       </c>
-      <c r="J120" t="s">
+      <c r="L120" t="s">
         <v>2910</v>
       </c>
-      <c r="L120" t="s">
-        <v>2911</v>
-      </c>
       <c r="M120" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="O120" t="s">
         <v>1644</v>
       </c>
       <c r="X120" t="s">
+        <v>2911</v>
+      </c>
+      <c r="Y120" t="s">
         <v>2912</v>
-      </c>
-      <c r="Y120" t="s">
-        <v>2913</v>
       </c>
       <c r="AA120" t="s">
         <v>45</v>
@@ -43096,19 +43119,19 @@
     </row>
     <row r="121" spans="8:27" ht="11.5" customHeight="1">
       <c r="H121" t="s">
+        <v>2913</v>
+      </c>
+      <c r="I121" t="s">
         <v>2914</v>
       </c>
-      <c r="I121" t="s">
+      <c r="L121" t="s">
         <v>2915</v>
       </c>
-      <c r="L121" t="s">
+      <c r="M121" t="s">
         <v>2916</v>
       </c>
-      <c r="M121" t="s">
-        <v>2917</v>
-      </c>
       <c r="O121" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="AA121" t="s">
         <v>45</v>
@@ -43116,16 +43139,16 @@
     </row>
     <row r="122" spans="8:27" ht="15" customHeight="1">
       <c r="H122" t="s">
-        <v>2696</v>
+        <v>2695</v>
       </c>
       <c r="I122" t="s">
+        <v>2917</v>
+      </c>
+      <c r="K122" t="s">
+        <v>2697</v>
+      </c>
+      <c r="L122" t="s">
         <v>2918</v>
-      </c>
-      <c r="K122" t="s">
-        <v>2698</v>
-      </c>
-      <c r="L122" t="s">
-        <v>2919</v>
       </c>
       <c r="M122" t="s">
         <v>1448</v>
@@ -43139,31 +43162,31 @@
     </row>
     <row r="123" spans="8:27" ht="15" customHeight="1">
       <c r="H123" t="s">
+        <v>2919</v>
+      </c>
+      <c r="I123" t="s">
         <v>2920</v>
       </c>
-      <c r="I123" t="s">
+      <c r="J123" t="s">
         <v>2921</v>
       </c>
-      <c r="J123" t="s">
+      <c r="K123" t="s">
         <v>2922</v>
       </c>
-      <c r="K123" t="s">
+      <c r="L123" t="s">
         <v>2923</v>
-      </c>
-      <c r="L123" t="s">
-        <v>2924</v>
       </c>
       <c r="M123" t="s">
         <v>1448</v>
       </c>
       <c r="O123" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="X123" t="s">
+        <v>2924</v>
+      </c>
+      <c r="Y123" t="s">
         <v>2925</v>
-      </c>
-      <c r="Y123" t="s">
-        <v>2926</v>
       </c>
       <c r="AA123" t="s">
         <v>45</v>
@@ -43171,22 +43194,22 @@
     </row>
     <row r="124" spans="8:27" ht="15" customHeight="1">
       <c r="H124" t="s">
+        <v>2926</v>
+      </c>
+      <c r="I124" t="s">
         <v>2927</v>
       </c>
-      <c r="I124" t="s">
+      <c r="K124" t="s">
+        <v>2611</v>
+      </c>
+      <c r="L124" t="s">
         <v>2928</v>
-      </c>
-      <c r="K124" t="s">
-        <v>2612</v>
-      </c>
-      <c r="L124" t="s">
-        <v>2929</v>
       </c>
       <c r="M124" t="s">
         <v>1448</v>
       </c>
       <c r="O124" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="AA124" t="s">
         <v>45</v>
@@ -43194,19 +43217,19 @@
     </row>
     <row r="125" spans="8:27" ht="15" customHeight="1">
       <c r="H125" t="s">
+        <v>2929</v>
+      </c>
+      <c r="I125" t="s">
         <v>2930</v>
       </c>
-      <c r="I125" t="s">
+      <c r="J125" t="s">
+        <v>2600</v>
+      </c>
+      <c r="K125" t="s">
+        <v>2601</v>
+      </c>
+      <c r="L125" t="s">
         <v>2931</v>
-      </c>
-      <c r="J125" t="s">
-        <v>2601</v>
-      </c>
-      <c r="K125" t="s">
-        <v>2602</v>
-      </c>
-      <c r="L125" t="s">
-        <v>2932</v>
       </c>
       <c r="M125" t="s">
         <v>1448</v>
@@ -43218,7 +43241,7 @@
         <v>2072</v>
       </c>
       <c r="Y125" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
       <c r="AA125" t="s">
         <v>45</v>
@@ -43226,16 +43249,16 @@
     </row>
     <row r="126" spans="8:27" ht="15" customHeight="1">
       <c r="H126" t="s">
-        <v>2790</v>
+        <v>2789</v>
       </c>
       <c r="I126" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="K126" t="s">
-        <v>2792</v>
+        <v>2791</v>
       </c>
       <c r="L126" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="M126" t="s">
         <v>1448</v>
@@ -43249,19 +43272,19 @@
     </row>
     <row r="127" spans="8:27" ht="15" customHeight="1">
       <c r="H127" t="s">
+        <v>2934</v>
+      </c>
+      <c r="I127" t="s">
         <v>2935</v>
       </c>
-      <c r="I127" t="s">
+      <c r="J127" t="s">
         <v>2936</v>
       </c>
-      <c r="J127" t="s">
+      <c r="K127" t="s">
         <v>2937</v>
       </c>
-      <c r="K127" t="s">
+      <c r="L127" t="s">
         <v>2938</v>
-      </c>
-      <c r="L127" t="s">
-        <v>2939</v>
       </c>
       <c r="M127" t="s">
         <v>2201</v>
@@ -43270,10 +43293,10 @@
         <v>1644</v>
       </c>
       <c r="X127" t="s">
+        <v>2939</v>
+      </c>
+      <c r="Y127" t="s">
         <v>2940</v>
-      </c>
-      <c r="Y127" t="s">
-        <v>2941</v>
       </c>
       <c r="AA127" t="s">
         <v>45</v>
@@ -43281,19 +43304,19 @@
     </row>
     <row r="128" spans="8:27" ht="15" customHeight="1">
       <c r="H128" t="s">
+        <v>2941</v>
+      </c>
+      <c r="I128" t="s">
         <v>2942</v>
       </c>
-      <c r="I128" t="s">
+      <c r="J128" t="s">
         <v>2943</v>
       </c>
-      <c r="J128" t="s">
+      <c r="L128" t="s">
         <v>2944</v>
       </c>
-      <c r="L128" t="s">
+      <c r="M128" t="s">
         <v>2945</v>
-      </c>
-      <c r="M128" t="s">
-        <v>2946</v>
       </c>
       <c r="O128" t="s">
         <v>1644</v>
@@ -43302,7 +43325,7 @@
         <v>1819</v>
       </c>
       <c r="Y128" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="AA128" t="s">
         <v>45</v>
@@ -43310,16 +43333,16 @@
     </row>
     <row r="129" spans="1:33" ht="15" customHeight="1">
       <c r="H129" t="s">
-        <v>2672</v>
+        <v>2671</v>
       </c>
       <c r="I129" t="s">
+        <v>2947</v>
+      </c>
+      <c r="K129" t="s">
+        <v>2673</v>
+      </c>
+      <c r="L129" t="s">
         <v>2948</v>
-      </c>
-      <c r="K129" t="s">
-        <v>2674</v>
-      </c>
-      <c r="L129" t="s">
-        <v>2949</v>
       </c>
       <c r="M129" t="s">
         <v>1758</v>
@@ -43333,28 +43356,28 @@
     </row>
     <row r="130" spans="1:33" ht="15" customHeight="1">
       <c r="H130" t="s">
+        <v>2949</v>
+      </c>
+      <c r="I130" t="s">
         <v>2950</v>
       </c>
-      <c r="I130" t="s">
+      <c r="J130" t="s">
+        <v>2949</v>
+      </c>
+      <c r="L130" t="s">
         <v>2951</v>
       </c>
-      <c r="J130" t="s">
-        <v>2950</v>
-      </c>
-      <c r="L130" t="s">
+      <c r="M130" t="s">
         <v>2952</v>
-      </c>
-      <c r="M130" t="s">
-        <v>2953</v>
       </c>
       <c r="O130" t="s">
         <v>1644</v>
       </c>
       <c r="X130" t="s">
+        <v>2953</v>
+      </c>
+      <c r="Y130" t="s">
         <v>2954</v>
-      </c>
-      <c r="Y130" t="s">
-        <v>2955</v>
       </c>
       <c r="AA130" t="s">
         <v>45</v>
@@ -43362,31 +43385,31 @@
     </row>
     <row r="131" spans="1:33" ht="15" customHeight="1">
       <c r="H131" t="s">
-        <v>2707</v>
+        <v>2706</v>
       </c>
       <c r="I131" t="s">
+        <v>2955</v>
+      </c>
+      <c r="J131" t="s">
+        <v>2708</v>
+      </c>
+      <c r="K131" t="s">
+        <v>2709</v>
+      </c>
+      <c r="L131" t="s">
         <v>2956</v>
       </c>
-      <c r="J131" t="s">
-        <v>2709</v>
-      </c>
-      <c r="K131" t="s">
-        <v>2710</v>
-      </c>
-      <c r="L131" t="s">
-        <v>2957</v>
-      </c>
       <c r="M131" t="s">
-        <v>2690</v>
+        <v>2689</v>
       </c>
       <c r="O131" t="s">
         <v>1644</v>
       </c>
       <c r="X131" t="s">
+        <v>2957</v>
+      </c>
+      <c r="Y131" t="s">
         <v>2958</v>
-      </c>
-      <c r="Y131" t="s">
-        <v>2959</v>
       </c>
       <c r="AA131" t="s">
         <v>55</v>
@@ -43409,19 +43432,19 @@
         <v>799</v>
       </c>
       <c r="H132" s="122" t="s">
+        <v>2959</v>
+      </c>
+      <c r="I132" s="24" t="s">
         <v>2960</v>
       </c>
-      <c r="I132" s="24" t="s">
+      <c r="J132" s="122" t="s">
         <v>2961</v>
       </c>
-      <c r="J132" s="122" t="s">
+      <c r="K132" s="119" t="s">
         <v>2962</v>
       </c>
-      <c r="K132" s="119" t="s">
+      <c r="L132" s="122" t="s">
         <v>2963</v>
-      </c>
-      <c r="L132" s="122" t="s">
-        <v>2964</v>
       </c>
       <c r="M132" s="174" t="s">
         <v>1437</v>
@@ -43430,35 +43453,35 @@
         <v>43</v>
       </c>
       <c r="O132" s="75" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="P132" s="80" t="s">
         <v>190</v>
       </c>
       <c r="Q132" s="448" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="R132" s="80"/>
       <c r="S132" s="80" t="s">
+        <v>2966</v>
+      </c>
+      <c r="T132" s="80" t="s">
         <v>2967</v>
       </c>
-      <c r="T132" s="80" t="s">
+      <c r="U132" s="80" t="s">
         <v>2968</v>
       </c>
-      <c r="U132" s="80" t="s">
+      <c r="V132" s="80" t="s">
         <v>2969</v>
       </c>
-      <c r="V132" s="80" t="s">
+      <c r="W132" s="80" t="s">
         <v>2970</v>
       </c>
-      <c r="W132" s="80" t="s">
+      <c r="X132" s="80" t="s">
         <v>2971</v>
       </c>
-      <c r="X132" s="80" t="s">
+      <c r="Y132" s="80" t="s">
         <v>2972</v>
-      </c>
-      <c r="Y132" s="80" t="s">
-        <v>2973</v>
       </c>
       <c r="Z132" s="80" t="s">
         <v>153</v>
@@ -43475,31 +43498,31 @@
     </row>
     <row r="133" spans="1:33" ht="15" customHeight="1">
       <c r="H133" t="s">
+        <v>2973</v>
+      </c>
+      <c r="I133" t="s">
         <v>2974</v>
       </c>
-      <c r="I133" t="s">
+      <c r="J133" t="s">
         <v>2975</v>
       </c>
-      <c r="J133" t="s">
+      <c r="K133" t="s">
         <v>2976</v>
       </c>
-      <c r="K133" t="s">
+      <c r="L133" t="s">
         <v>2977</v>
       </c>
-      <c r="L133" t="s">
+      <c r="M133" t="s">
         <v>2978</v>
-      </c>
-      <c r="M133" t="s">
-        <v>2979</v>
       </c>
       <c r="O133" t="s">
         <v>1644</v>
       </c>
       <c r="X133" t="s">
+        <v>2979</v>
+      </c>
+      <c r="Y133" t="s">
         <v>2980</v>
-      </c>
-      <c r="Y133" t="s">
-        <v>2981</v>
       </c>
       <c r="AA133" t="s">
         <v>45</v>
@@ -43507,28 +43530,28 @@
     </row>
     <row r="134" spans="1:33" ht="15" customHeight="1">
       <c r="H134" t="s">
+        <v>2981</v>
+      </c>
+      <c r="I134" t="s">
         <v>2982</v>
       </c>
-      <c r="I134" t="s">
+      <c r="J134" t="s">
         <v>2983</v>
       </c>
-      <c r="J134" t="s">
+      <c r="L134" t="s">
         <v>2984</v>
       </c>
-      <c r="L134" t="s">
+      <c r="M134" t="s">
         <v>2985</v>
-      </c>
-      <c r="M134" t="s">
-        <v>2986</v>
       </c>
       <c r="O134" t="s">
         <v>1644</v>
       </c>
       <c r="X134" t="s">
+        <v>2986</v>
+      </c>
+      <c r="Y134" t="s">
         <v>2987</v>
-      </c>
-      <c r="Y134" t="s">
-        <v>2988</v>
       </c>
       <c r="AA134" t="s">
         <v>45</v>
@@ -43536,19 +43559,19 @@
     </row>
     <row r="135" spans="1:33" ht="15" customHeight="1">
       <c r="H135" t="s">
+        <v>2988</v>
+      </c>
+      <c r="I135" t="s">
         <v>2989</v>
       </c>
-      <c r="I135" t="s">
+      <c r="J135" t="s">
         <v>2990</v>
       </c>
-      <c r="J135" t="s">
+      <c r="K135" t="s">
         <v>2991</v>
       </c>
-      <c r="K135" t="s">
+      <c r="L135" t="s">
         <v>2992</v>
-      </c>
-      <c r="L135" t="s">
-        <v>2993</v>
       </c>
       <c r="M135" t="s">
         <v>1691</v>
@@ -43560,7 +43583,7 @@
         <v>1891</v>
       </c>
       <c r="Y135" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="AA135" t="s">
         <v>45</v>
@@ -43568,16 +43591,16 @@
     </row>
     <row r="136" spans="1:33" ht="15" customHeight="1">
       <c r="H136" t="s">
+        <v>2994</v>
+      </c>
+      <c r="I136" t="s">
         <v>2995</v>
       </c>
-      <c r="I136" t="s">
+      <c r="J136" t="s">
         <v>2996</v>
       </c>
-      <c r="J136" t="s">
+      <c r="L136" t="s">
         <v>2997</v>
-      </c>
-      <c r="L136" t="s">
-        <v>2998</v>
       </c>
       <c r="M136" t="s">
         <v>1670</v>
@@ -43586,10 +43609,10 @@
         <v>1644</v>
       </c>
       <c r="X136" t="s">
+        <v>2998</v>
+      </c>
+      <c r="Y136" t="s">
         <v>2999</v>
-      </c>
-      <c r="Y136" t="s">
-        <v>3000</v>
       </c>
       <c r="AA136" t="s">
         <v>45</v>
@@ -43597,19 +43620,19 @@
     </row>
     <row r="137" spans="1:33" ht="15" customHeight="1">
       <c r="H137" t="s">
+        <v>2626</v>
+      </c>
+      <c r="I137" t="s">
         <v>2627</v>
       </c>
-      <c r="I137" t="s">
+      <c r="J137" t="s">
         <v>2628</v>
       </c>
-      <c r="J137" t="s">
+      <c r="K137" t="s">
         <v>2629</v>
       </c>
-      <c r="K137" t="s">
-        <v>2630</v>
-      </c>
       <c r="L137" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="M137" t="s">
         <v>1448</v>
@@ -43618,13 +43641,13 @@
         <v>1659</v>
       </c>
       <c r="W137" t="s">
+        <v>3001</v>
+      </c>
+      <c r="X137" t="s">
         <v>3002</v>
       </c>
-      <c r="X137" t="s">
-        <v>3003</v>
-      </c>
       <c r="Y137" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="AA137" t="s">
         <v>45</v>
@@ -43632,19 +43655,19 @@
     </row>
     <row r="138" spans="1:33" ht="15" customHeight="1">
       <c r="H138" t="s">
-        <v>2767</v>
+        <v>2766</v>
       </c>
       <c r="I138" t="s">
+        <v>2632</v>
+      </c>
+      <c r="J138" t="s">
         <v>2633</v>
       </c>
-      <c r="J138" t="s">
+      <c r="K138" t="s">
         <v>2634</v>
       </c>
-      <c r="K138" t="s">
-        <v>2635</v>
-      </c>
       <c r="L138" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="M138" t="s">
         <v>1448</v>
@@ -43653,10 +43676,10 @@
         <v>1659</v>
       </c>
       <c r="X138" t="s">
+        <v>2768</v>
+      </c>
+      <c r="Y138" t="s">
         <v>2769</v>
-      </c>
-      <c r="Y138" t="s">
-        <v>2770</v>
       </c>
       <c r="AA138" t="s">
         <v>45</v>
@@ -43664,16 +43687,16 @@
     </row>
     <row r="139" spans="1:33" ht="15" customHeight="1">
       <c r="H139" t="s">
+        <v>3004</v>
+      </c>
+      <c r="I139" t="s">
         <v>3005</v>
       </c>
-      <c r="I139" t="s">
+      <c r="J139" t="s">
         <v>3006</v>
       </c>
-      <c r="J139" t="s">
+      <c r="L139" t="s">
         <v>3007</v>
-      </c>
-      <c r="L139" t="s">
-        <v>3008</v>
       </c>
       <c r="M139" t="s">
         <v>1448</v>
@@ -43682,10 +43705,10 @@
         <v>1813</v>
       </c>
       <c r="X139" t="s">
+        <v>3008</v>
+      </c>
+      <c r="Y139" t="s">
         <v>3009</v>
-      </c>
-      <c r="Y139" t="s">
-        <v>3010</v>
       </c>
       <c r="AA139" t="s">
         <v>45</v>
@@ -43693,19 +43716,19 @@
     </row>
     <row r="140" spans="1:33" ht="15" customHeight="1">
       <c r="H140" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="I140" t="s">
+        <v>3010</v>
+      </c>
+      <c r="J140" t="s">
         <v>3011</v>
       </c>
-      <c r="J140" t="s">
+      <c r="K140" t="s">
+        <v>2922</v>
+      </c>
+      <c r="L140" t="s">
         <v>3012</v>
-      </c>
-      <c r="K140" t="s">
-        <v>2923</v>
-      </c>
-      <c r="L140" t="s">
-        <v>3013</v>
       </c>
       <c r="M140" t="s">
         <v>1448</v>
@@ -43717,10 +43740,10 @@
         <v>436</v>
       </c>
       <c r="X140" t="s">
+        <v>3013</v>
+      </c>
+      <c r="Y140" t="s">
         <v>3014</v>
-      </c>
-      <c r="Y140" t="s">
-        <v>3015</v>
       </c>
       <c r="AA140" t="s">
         <v>55</v>
@@ -43728,19 +43751,19 @@
     </row>
     <row r="141" spans="1:33" ht="15" customHeight="1">
       <c r="H141" t="s">
+        <v>3015</v>
+      </c>
+      <c r="I141" t="s">
         <v>3016</v>
       </c>
-      <c r="I141" t="s">
+      <c r="J141" t="s">
         <v>3017</v>
       </c>
-      <c r="J141" t="s">
+      <c r="K141" t="s">
         <v>3018</v>
       </c>
-      <c r="K141" t="s">
+      <c r="L141" t="s">
         <v>3019</v>
-      </c>
-      <c r="L141" t="s">
-        <v>3020</v>
       </c>
       <c r="M141" t="s">
         <v>1448</v>
@@ -43749,10 +43772,10 @@
         <v>1659</v>
       </c>
       <c r="X141" t="s">
+        <v>3020</v>
+      </c>
+      <c r="Y141" t="s">
         <v>3021</v>
-      </c>
-      <c r="Y141" t="s">
-        <v>3022</v>
       </c>
       <c r="AA141" t="s">
         <v>45</v>
@@ -43760,23 +43783,23 @@
     </row>
     <row r="142" spans="1:33" ht="15" customHeight="1">
       <c r="H142" t="s">
+        <v>3022</v>
+      </c>
+      <c r="I142" t="s">
         <v>3023</v>
       </c>
-      <c r="I142" t="s">
+      <c r="J142" s="122" t="s">
         <v>3024</v>
-      </c>
-      <c r="J142" s="122" t="s">
-        <v>3025</v>
       </c>
       <c r="K142" s="119"/>
       <c r="L142" s="122" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="M142" s="174" t="s">
         <v>2364</v>
       </c>
       <c r="O142" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="143" spans="1:33" s="74" customFormat="1" ht="11.5" customHeight="1">
@@ -43788,24 +43811,24 @@
       <c r="F143" s="105"/>
       <c r="G143" s="105"/>
       <c r="H143" s="120" t="s">
+        <v>3027</v>
+      </c>
+      <c r="I143" t="s">
         <v>3028</v>
       </c>
-      <c r="I143" t="s">
+      <c r="J143" s="120" t="s">
         <v>3029</v>
-      </c>
-      <c r="J143" s="120" t="s">
-        <v>3030</v>
       </c>
       <c r="K143" s="119"/>
       <c r="L143" s="120" t="s">
+        <v>3030</v>
+      </c>
+      <c r="M143" s="170" t="s">
         <v>3031</v>
-      </c>
-      <c r="M143" s="170" t="s">
-        <v>3032</v>
       </c>
       <c r="N143" s="105"/>
       <c r="O143" s="400" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="P143" s="105"/>
       <c r="Q143" s="400"/>
@@ -43835,19 +43858,19 @@
       <c r="F144" s="77"/>
       <c r="G144" s="77"/>
       <c r="H144" s="117" t="s">
+        <v>3033</v>
+      </c>
+      <c r="I144" s="119" t="s">
         <v>3034</v>
       </c>
-      <c r="I144" s="119" t="s">
+      <c r="J144" s="117" t="s">
         <v>3035</v>
       </c>
-      <c r="J144" s="117" t="s">
+      <c r="K144" s="119" t="s">
         <v>3036</v>
       </c>
-      <c r="K144" s="119" t="s">
+      <c r="L144" s="117" t="s">
         <v>3037</v>
-      </c>
-      <c r="L144" s="117" t="s">
-        <v>3038</v>
       </c>
       <c r="M144" s="171" t="s">
         <v>1448</v>
@@ -43865,10 +43888,10 @@
       <c r="V144" s="77"/>
       <c r="W144" s="77"/>
       <c r="X144" s="77" t="s">
+        <v>3038</v>
+      </c>
+      <c r="Y144" s="77" t="s">
         <v>3039</v>
-      </c>
-      <c r="Y144" s="77" t="s">
-        <v>3040</v>
       </c>
       <c r="Z144" s="77"/>
       <c r="AA144" s="77" t="s">
@@ -43921,17 +43944,17 @@
   <sheetData>
     <row r="1" spans="1:3" ht="13" customHeight="1">
       <c r="A1" s="27" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="58"/>
     </row>
     <row r="2" spans="1:3" s="62" customFormat="1" ht="13" customHeight="1">
       <c r="A2" s="59" t="s">
+        <v>3041</v>
+      </c>
+      <c r="B2" s="60" t="s">
         <v>3042</v>
-      </c>
-      <c r="B2" s="60" t="s">
-        <v>3043</v>
       </c>
       <c r="C2" s="61"/>
     </row>
@@ -43940,16 +43963,16 @@
         <v>154</v>
       </c>
       <c r="B3" s="147" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="C3" s="58"/>
     </row>
     <row r="4" spans="1:3" ht="13" customHeight="1">
       <c r="A4" s="27" t="s">
+        <v>3044</v>
+      </c>
+      <c r="B4" s="147" t="s">
         <v>3045</v>
-      </c>
-      <c r="B4" s="147" t="s">
-        <v>3046</v>
       </c>
       <c r="C4" s="58"/>
     </row>
@@ -43958,7 +43981,7 @@
         <v>774</v>
       </c>
       <c r="B5" s="147" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="C5" s="58"/>
     </row>
@@ -43967,16 +43990,16 @@
         <v>616</v>
       </c>
       <c r="B6" s="63" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="C6" s="58"/>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="64" t="s">
+        <v>3048</v>
+      </c>
+      <c r="B7" s="65" t="s">
         <v>3049</v>
-      </c>
-      <c r="B7" s="65" t="s">
-        <v>3050</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -43984,7 +44007,7 @@
         <v>588</v>
       </c>
       <c r="B8" s="65" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -43992,15 +44015,15 @@
         <v>647</v>
       </c>
       <c r="B9" s="65" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="64" t="s">
+        <v>3052</v>
+      </c>
+      <c r="B10" s="65" t="s">
         <v>3053</v>
-      </c>
-      <c r="B10" s="65" t="s">
-        <v>3054</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="25.5" customHeight="1">
@@ -44008,7 +44031,7 @@
         <v>168</v>
       </c>
       <c r="B11" s="66" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="25.5" customHeight="1">
@@ -44016,7 +44039,7 @@
         <v>1017</v>
       </c>
       <c r="B12" s="66" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="25.5" customHeight="1">
@@ -44024,31 +44047,31 @@
         <v>1275</v>
       </c>
       <c r="B13" s="66" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="71" t="s">
+        <v>3057</v>
+      </c>
+      <c r="B14" s="65" t="s">
         <v>3058</v>
-      </c>
-      <c r="B14" s="65" t="s">
-        <v>3059</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="25.5" customHeight="1">
       <c r="A15" s="71" t="s">
+        <v>3059</v>
+      </c>
+      <c r="B15" s="66" t="s">
         <v>3060</v>
-      </c>
-      <c r="B15" s="66" t="s">
-        <v>3061</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="64" t="s">
+        <v>3061</v>
+      </c>
+      <c r="B16" s="65" t="s">
         <v>3062</v>
-      </c>
-      <c r="B16" s="65" t="s">
-        <v>3063</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="25.5" customHeight="1">
@@ -44056,7 +44079,7 @@
         <v>799</v>
       </c>
       <c r="B17" s="66" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -44065,7 +44088,7 @@
     </row>
     <row r="19" spans="1:2" ht="13" customHeight="1">
       <c r="A19" s="215" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="B19" s="65"/>
     </row>
@@ -44074,7 +44097,7 @@
         <v>69</v>
       </c>
       <c r="B20" s="65" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -44082,7 +44105,7 @@
         <v>38</v>
       </c>
       <c r="B21" s="65" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -44097,86 +44120,86 @@
     </row>
     <row r="28" spans="1:2" ht="33.75" customHeight="1">
       <c r="A28" s="70" t="s">
+        <v>3067</v>
+      </c>
+      <c r="B28" s="69" t="s">
         <v>3068</v>
-      </c>
-      <c r="B28" s="69" t="s">
-        <v>3069</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="13" customHeight="1">
       <c r="A29" s="70"/>
       <c r="B29" s="69" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="25.5" customHeight="1">
       <c r="A30" s="71" t="s">
+        <v>3070</v>
+      </c>
+      <c r="B30" s="72" t="s">
         <v>3071</v>
-      </c>
-      <c r="B30" s="72" t="s">
-        <v>3072</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="71" t="s">
+        <v>3072</v>
+      </c>
+      <c r="B31" s="65" t="s">
         <v>3073</v>
-      </c>
-      <c r="B31" s="65" t="s">
-        <v>3074</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="25.5" customHeight="1">
       <c r="A32" s="71" t="s">
+        <v>3074</v>
+      </c>
+      <c r="B32" s="72" t="s">
         <v>3075</v>
-      </c>
-      <c r="B32" s="72" t="s">
-        <v>3076</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="68" t="s">
+        <v>3076</v>
+      </c>
+      <c r="B33" s="66" t="s">
         <v>3077</v>
-      </c>
-      <c r="B33" s="66" t="s">
-        <v>3078</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="25.5" customHeight="1">
       <c r="A34" s="68" t="s">
+        <v>3078</v>
+      </c>
+      <c r="B34" s="72" t="s">
         <v>3079</v>
-      </c>
-      <c r="B34" s="72" t="s">
-        <v>3080</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="25.5" customHeight="1">
       <c r="A35" s="68" t="s">
+        <v>3080</v>
+      </c>
+      <c r="B35" s="66" t="s">
         <v>3081</v>
-      </c>
-      <c r="B35" s="66" t="s">
-        <v>3082</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="25.5" customHeight="1">
       <c r="A36" s="67" t="s">
+        <v>3082</v>
+      </c>
+      <c r="B36" s="69" t="s">
         <v>3083</v>
-      </c>
-      <c r="B36" s="69" t="s">
-        <v>3084</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="25.5" customHeight="1">
       <c r="A38" s="67"/>
       <c r="B38" s="69" t="s">
-        <v>3085</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="25.5" customHeight="1">
       <c r="A39" s="67" t="s">
+        <v>3085</v>
+      </c>
+      <c r="B39" s="69" t="s">
         <v>3086</v>
-      </c>
-      <c r="B39" s="69" t="s">
-        <v>3087</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="25.5" customHeight="1">
@@ -44184,31 +44207,31 @@
         <v>38</v>
       </c>
       <c r="B40" s="69" t="s">
-        <v>3088</v>
+        <v>3087</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="25.5" customHeight="1">
       <c r="A41" s="67" t="s">
+        <v>3088</v>
+      </c>
+      <c r="B41" s="69" t="s">
         <v>3089</v>
-      </c>
-      <c r="B41" s="69" t="s">
-        <v>3090</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="25.5" customHeight="1">
       <c r="A42" s="67" t="s">
+        <v>3090</v>
+      </c>
+      <c r="B42" s="69" t="s">
         <v>3091</v>
-      </c>
-      <c r="B42" s="69" t="s">
-        <v>3092</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="25.5" customHeight="1">
       <c r="A43" s="67" t="s">
+        <v>3092</v>
+      </c>
+      <c r="B43" s="69" t="s">
         <v>3093</v>
-      </c>
-      <c r="B43" s="69" t="s">
-        <v>3094</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="25.5" customHeight="1">
@@ -44216,33 +44239,33 @@
         <v>234</v>
       </c>
       <c r="B44" s="69" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="43" customHeight="1">
       <c r="A46" s="215" t="s">
+        <v>3095</v>
+      </c>
+      <c r="B46" s="69" t="s">
         <v>3096</v>
-      </c>
-      <c r="B46" s="69" t="s">
-        <v>3097</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="13" customHeight="1">
       <c r="A49" s="70" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="25.5" customHeight="1">
       <c r="A50" s="69" t="s">
+        <v>3098</v>
+      </c>
+      <c r="B50" s="69" t="s">
         <v>3099</v>
-      </c>
-      <c r="B50" s="69" t="s">
-        <v>3100</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -44250,7 +44273,7 @@
         <v>73</v>
       </c>
       <c r="B53" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -44258,7 +44281,7 @@
         <v>409</v>
       </c>
       <c r="B54" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -44266,7 +44289,7 @@
         <v>1062</v>
       </c>
       <c r="B55" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -44274,7 +44297,7 @@
         <v>179</v>
       </c>
       <c r="B56" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -44282,7 +44305,7 @@
         <v>258</v>
       </c>
       <c r="B57" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -44290,7 +44313,7 @@
         <v>153</v>
       </c>
       <c r="B58" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -44298,7 +44321,7 @@
         <v>194</v>
       </c>
       <c r="B59" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -44306,12 +44329,12 @@
         <v>44</v>
       </c>
       <c r="B60" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -44319,7 +44342,7 @@
         <v>45</v>
       </c>
       <c r="B63" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -44327,7 +44350,7 @@
         <v>55</v>
       </c>
       <c r="B64" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -44335,7 +44358,7 @@
         <v>129</v>
       </c>
       <c r="B65" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -44343,12 +44366,12 @@
         <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="13" customHeight="1">
       <c r="A68" s="467" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -44356,7 +44379,7 @@
         <v>166</v>
       </c>
       <c r="B69" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -44364,102 +44387,102 @@
         <v>1797</v>
       </c>
       <c r="B70" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="13" customHeight="1">
       <c r="A72" s="467" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
+        <v>3118</v>
+      </c>
+      <c r="B73" t="s">
         <v>3119</v>
-      </c>
-      <c r="B73" t="s">
-        <v>3120</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
+        <v>3120</v>
+      </c>
+      <c r="B74" t="s">
         <v>3121</v>
-      </c>
-      <c r="B74" t="s">
-        <v>3122</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
+        <v>3122</v>
+      </c>
+      <c r="B75" t="s">
         <v>3123</v>
-      </c>
-      <c r="B75" t="s">
-        <v>3124</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
+        <v>3124</v>
+      </c>
+      <c r="B76" t="s">
         <v>3125</v>
-      </c>
-      <c r="B76" t="s">
-        <v>3126</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
+        <v>3126</v>
+      </c>
+      <c r="B77" t="s">
         <v>3127</v>
-      </c>
-      <c r="B77" t="s">
-        <v>3128</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
+        <v>3128</v>
+      </c>
+      <c r="B78" t="s">
         <v>3129</v>
-      </c>
-      <c r="B78" t="s">
-        <v>3130</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
+        <v>3130</v>
+      </c>
+      <c r="B79" t="s">
         <v>3131</v>
-      </c>
-      <c r="B79" t="s">
-        <v>3132</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="13" customHeight="1">
       <c r="A81" s="467" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
+        <v>3133</v>
+      </c>
+      <c r="B82" t="s">
         <v>3134</v>
-      </c>
-      <c r="B82" t="s">
-        <v>3135</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
+        <v>3135</v>
+      </c>
+      <c r="B83" t="s">
         <v>3136</v>
-      </c>
-      <c r="B83" t="s">
-        <v>3137</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
+        <v>3137</v>
+      </c>
+      <c r="B84" t="s">
         <v>3138</v>
-      </c>
-      <c r="B84" t="s">
-        <v>3139</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
     </row>
   </sheetData>
@@ -70074,12 +70097,12 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="5" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="5" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -70087,60 +70110,60 @@
         <v>912</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
+        <v>3142</v>
+      </c>
+      <c r="F6" s="19" t="s">
         <v>3143</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>3144</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>3149</v>
+        <v>3148</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -70169,103 +70192,103 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15" customHeight="1">
       <c r="A1" s="261" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1">
       <c r="A2" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="12.65" customHeight="1">
       <c r="A3" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="5" spans="1:2" ht="12.65" customHeight="1">
       <c r="A5" s="261" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" customHeight="1">
       <c r="A6" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="12.65" customHeight="1">
       <c r="A7" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="12.65" customHeight="1">
       <c r="A8" s="261" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="10" spans="1:2" ht="12.65" customHeight="1">
       <c r="A10" s="261" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="12.65" customHeight="1">
       <c r="A11" t="s">
+        <v>3161</v>
+      </c>
+      <c r="B11" t="s">
         <v>3162</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3163</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="12.65" customHeight="1">
       <c r="A12" t="s">
+        <v>3163</v>
+      </c>
+      <c r="B12" t="s">
         <v>3164</v>
-      </c>
-      <c r="B12" t="s">
-        <v>3165</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="52" customHeight="1">
       <c r="A13" t="s">
+        <v>3165</v>
+      </c>
+      <c r="B13" t="s">
         <v>3166</v>
-      </c>
-      <c r="B13" t="s">
-        <v>3167</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="12.65" customHeight="1">
       <c r="A14" t="s">
+        <v>3167</v>
+      </c>
+      <c r="B14" t="s">
         <v>3168</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3169</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="12.65" customHeight="1">
       <c r="A15" t="s">
+        <v>3169</v>
+      </c>
+      <c r="B15" t="s">
         <v>3170</v>
-      </c>
-      <c r="B15" t="s">
-        <v>3171</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="17" spans="1:3" ht="12.65" customHeight="1">
       <c r="A17" s="261" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="12.65" customHeight="1">
       <c r="B18" t="s">
+        <v>3172</v>
+      </c>
+      <c r="C18" t="s">
         <v>3173</v>
-      </c>
-      <c r="C18" t="s">
-        <v>3174</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="25" customHeight="1">
       <c r="A19" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="B19">
         <v>277</v>
@@ -70273,7 +70296,7 @@
     </row>
     <row r="20" spans="1:3" ht="12.65" customHeight="1">
       <c r="A20" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="B20">
         <v>83</v>
@@ -70284,7 +70307,7 @@
     </row>
     <row r="21" spans="1:3" ht="25" customHeight="1">
       <c r="A21" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="B21">
         <v>11</v>
@@ -70295,7 +70318,7 @@
     </row>
     <row r="22" spans="1:3" ht="12.65" customHeight="1">
       <c r="A22" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
       <c r="B22">
         <v>52</v>
@@ -70306,7 +70329,7 @@
     </row>
     <row r="23" spans="1:3" ht="25" customHeight="1">
       <c r="A23" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="B23">
         <v>15</v>
@@ -70317,7 +70340,7 @@
     </row>
     <row r="24" spans="1:3" ht="12.65" customHeight="1">
       <c r="A24" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
       <c r="B24">
         <v>5</v>
@@ -70328,7 +70351,7 @@
     </row>
     <row r="25" spans="1:3" ht="12.65" customHeight="1">
       <c r="A25" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="B25">
         <v>194</v>
@@ -70340,15 +70363,15 @@
     <row r="26" spans="1:3" ht="12.65" customHeight="1"/>
     <row r="27" spans="1:3" ht="12.65" customHeight="1">
       <c r="A27" s="261" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="12.65" customHeight="1">
       <c r="A28" t="s">
+        <v>3182</v>
+      </c>
+      <c r="B28" t="s">
         <v>3183</v>
-      </c>
-      <c r="B28" t="s">
-        <v>3184</v>
       </c>
       <c r="C28" s="259">
         <v>0.94199999999999995</v>
@@ -70356,10 +70379,10 @@
     </row>
     <row r="29" spans="1:3" ht="12.65" customHeight="1">
       <c r="A29" t="s">
+        <v>3184</v>
+      </c>
+      <c r="B29" t="s">
         <v>3185</v>
-      </c>
-      <c r="B29" t="s">
-        <v>3186</v>
       </c>
       <c r="C29" s="259">
         <v>0.73299999999999998</v>
@@ -70367,10 +70390,10 @@
     </row>
     <row r="30" spans="1:3" ht="12.65" customHeight="1">
       <c r="A30" t="s">
+        <v>3186</v>
+      </c>
+      <c r="B30" t="s">
         <v>3187</v>
-      </c>
-      <c r="B30" t="s">
-        <v>3188</v>
       </c>
       <c r="C30" s="259">
         <v>0.39</v>
@@ -70378,10 +70401,10 @@
     </row>
     <row r="31" spans="1:3" ht="12.65" customHeight="1">
       <c r="A31" t="s">
+        <v>3188</v>
+      </c>
+      <c r="B31" t="s">
         <v>3189</v>
-      </c>
-      <c r="B31" t="s">
-        <v>3190</v>
       </c>
       <c r="C31" s="259">
         <v>0.108</v>
@@ -70390,47 +70413,47 @@
     <row r="32" spans="1:3" ht="12.65" customHeight="1"/>
     <row r="33" spans="1:9" ht="12.65" customHeight="1">
       <c r="A33" s="261" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="12.65" customHeight="1">
       <c r="A34" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="36" spans="1:9" ht="12.65" customHeight="1">
       <c r="A36" s="261" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="12.65" customHeight="1">
       <c r="A37" t="s">
+        <v>3193</v>
+      </c>
+      <c r="B37" t="s">
         <v>3194</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>3195</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>3196</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>3197</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>3198</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>3199</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>3200</v>
       </c>
-      <c r="H37" t="s">
+      <c r="I37" t="s">
         <v>3201</v>
-      </c>
-      <c r="I37" t="s">
-        <v>3202</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="12.65" customHeight="1">
@@ -70438,10 +70461,10 @@
         <v>155</v>
       </c>
       <c r="B38" t="s">
+        <v>3202</v>
+      </c>
+      <c r="D38" t="s">
         <v>3203</v>
-      </c>
-      <c r="D38" t="s">
-        <v>3204</v>
       </c>
       <c r="E38" t="s">
         <v>43</v>
@@ -70461,7 +70484,7 @@
         <v>161</v>
       </c>
       <c r="B39" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="D39" t="s">
         <v>1453</v>
@@ -70484,13 +70507,13 @@
     </row>
     <row r="40" spans="1:9" ht="12.65" customHeight="1">
       <c r="B40" t="s">
-        <v>3205</v>
+        <v>3204</v>
       </c>
       <c r="C40" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="D40" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="E40" t="s">
         <v>43</v>
@@ -70510,7 +70533,7 @@
         <v>180</v>
       </c>
       <c r="B41" t="s">
-        <v>3205</v>
+        <v>3204</v>
       </c>
       <c r="E41" t="s">
         <v>62</v>
@@ -70530,7 +70553,7 @@
         <v>1453</v>
       </c>
       <c r="D42" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="E42" t="s">
         <v>43</v>
@@ -70553,7 +70576,7 @@
         <v>709</v>
       </c>
       <c r="B43" t="s">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="C43" t="s">
         <v>1453</v>
@@ -70579,13 +70602,13 @@
         <v>955</v>
       </c>
       <c r="B44" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="C44" t="s">
         <v>1453</v>
       </c>
       <c r="D44" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="E44" t="s">
         <v>43</v>
@@ -70608,19 +70631,19 @@
         <v>1133</v>
       </c>
       <c r="B45" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="C45" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="D45" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="E45" t="s">
         <v>62</v>
       </c>
       <c r="F45" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="G45" t="s">
         <v>258</v>
@@ -70637,19 +70660,19 @@
         <v>1138</v>
       </c>
       <c r="B46" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="C46" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="D46" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="E46" t="s">
         <v>62</v>
       </c>
       <c r="F46" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="G46" t="s">
         <v>153</v>
@@ -70672,7 +70695,7 @@
         <v>1453</v>
       </c>
       <c r="D47" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="E47" t="s">
         <v>43</v>
@@ -70698,7 +70721,7 @@
         <v>1453</v>
       </c>
       <c r="D48" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="E48" t="s">
         <v>43</v>
@@ -70716,33 +70739,33 @@
     <row r="49" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="50" spans="1:9" ht="12.65" customHeight="1">
       <c r="A50" s="261" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="12.65" customHeight="1">
       <c r="B51" t="s">
+        <v>3209</v>
+      </c>
+      <c r="C51" t="s">
         <v>3210</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>3211</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>3212</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>3213</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>3214</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
         <v>3215</v>
       </c>
-      <c r="H51" t="s">
+      <c r="I51" t="s">
         <v>3216</v>
-      </c>
-      <c r="I51" t="s">
-        <v>3217</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="12.65" customHeight="1">
@@ -70776,7 +70799,7 @@
     </row>
     <row r="53" spans="1:9" ht="12.65" customHeight="1">
       <c r="A53" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="B53">
         <v>3</v>
@@ -70805,7 +70828,7 @@
     </row>
     <row r="54" spans="1:9" ht="12.65" customHeight="1">
       <c r="A54" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="B54">
         <v>8</v>
@@ -70835,33 +70858,33 @@
     <row r="55" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="56" spans="1:9" ht="12.65" customHeight="1">
       <c r="A56" s="261" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="12.65" customHeight="1">
       <c r="B57" t="s">
+        <v>3209</v>
+      </c>
+      <c r="C57" t="s">
         <v>3210</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>3211</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>3212</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>3213</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>3214</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
         <v>3215</v>
       </c>
-      <c r="H57" t="s">
+      <c r="I57" t="s">
         <v>3216</v>
-      </c>
-      <c r="I57" t="s">
-        <v>3217</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="12.65" customHeight="1">
@@ -70895,7 +70918,7 @@
     </row>
     <row r="59" spans="1:9" ht="12.65" customHeight="1">
       <c r="A59" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="B59">
         <v>8</v>
@@ -70924,7 +70947,7 @@
     </row>
     <row r="60" spans="1:9" ht="12.65" customHeight="1">
       <c r="A60" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="B60">
         <v>10</v>
@@ -70954,33 +70977,33 @@
     <row r="61" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="62" spans="1:9" ht="12.65" customHeight="1">
       <c r="A62" s="261" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="12.65" customHeight="1">
       <c r="B63" t="s">
+        <v>3209</v>
+      </c>
+      <c r="C63" t="s">
         <v>3210</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
         <v>3211</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>3212</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>3213</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>3214</v>
       </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
         <v>3215</v>
       </c>
-      <c r="H63" t="s">
+      <c r="I63" t="s">
         <v>3216</v>
-      </c>
-      <c r="I63" t="s">
-        <v>3217</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="12.65" customHeight="1">
@@ -71043,7 +71066,7 @@
     </row>
     <row r="66" spans="1:9" ht="12.65" customHeight="1">
       <c r="A66" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="B66">
         <v>11</v>
@@ -71073,33 +71096,33 @@
     <row r="67" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="68" spans="1:9" ht="12.65" customHeight="1">
       <c r="A68" s="261" t="s">
-        <v>3220</v>
+        <v>3219</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="12.65" customHeight="1">
       <c r="B69" t="s">
+        <v>3209</v>
+      </c>
+      <c r="C69" t="s">
         <v>3210</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
         <v>3211</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>3212</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>3213</v>
       </c>
-      <c r="F69" t="s">
+      <c r="G69" t="s">
         <v>3214</v>
       </c>
-      <c r="G69" t="s">
+      <c r="H69" t="s">
         <v>3215</v>
       </c>
-      <c r="H69" t="s">
+      <c r="I69" t="s">
         <v>3216</v>
-      </c>
-      <c r="I69" t="s">
-        <v>3217</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="12.65" customHeight="1">
@@ -71191,7 +71214,7 @@
     </row>
     <row r="73" spans="1:9" ht="12.65" customHeight="1">
       <c r="A73" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -71221,33 +71244,33 @@
     <row r="74" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="75" spans="1:9" ht="12.65" customHeight="1">
       <c r="A75" s="261" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="12.65" customHeight="1">
       <c r="B76" t="s">
+        <v>3209</v>
+      </c>
+      <c r="C76" t="s">
         <v>3210</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>3211</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>3212</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>3213</v>
       </c>
-      <c r="F76" t="s">
+      <c r="G76" t="s">
         <v>3214</v>
       </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
         <v>3215</v>
       </c>
-      <c r="H76" t="s">
+      <c r="I76" t="s">
         <v>3216</v>
-      </c>
-      <c r="I76" t="s">
-        <v>3217</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="12.65" customHeight="1">
@@ -71310,7 +71333,7 @@
     </row>
     <row r="79" spans="1:9" ht="12.65" customHeight="1">
       <c r="A79" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -71368,7 +71391,7 @@
     </row>
     <row r="81" spans="1:9" ht="12.65" customHeight="1">
       <c r="A81" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="B81">
         <v>7</v>
@@ -71398,38 +71421,38 @@
     <row r="82" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="83" spans="1:9" ht="12.65" customHeight="1">
       <c r="A83" s="261" t="s">
-        <v>3222</v>
+        <v>3221</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="12.65" customHeight="1">
       <c r="B84" t="s">
+        <v>3209</v>
+      </c>
+      <c r="C84" t="s">
         <v>3210</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
         <v>3211</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>3212</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>3213</v>
       </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>3214</v>
       </c>
-      <c r="G84" t="s">
+      <c r="H84" t="s">
         <v>3215</v>
       </c>
-      <c r="H84" t="s">
+      <c r="I84" t="s">
         <v>3216</v>
-      </c>
-      <c r="I84" t="s">
-        <v>3217</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="12.65" customHeight="1">
       <c r="A85" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="B85">
         <v>6</v>
@@ -71458,7 +71481,7 @@
     </row>
     <row r="86" spans="1:9" ht="12.65" customHeight="1">
       <c r="A86" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -71487,7 +71510,7 @@
     </row>
     <row r="87" spans="1:9" ht="12.65" customHeight="1">
       <c r="A87" t="s">
-        <v>3225</v>
+        <v>3224</v>
       </c>
       <c r="B87">
         <v>3</v>
@@ -71516,7 +71539,7 @@
     </row>
     <row r="88" spans="1:9" ht="12.65" customHeight="1">
       <c r="A88" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="B88">
         <v>11</v>
@@ -71546,33 +71569,33 @@
     <row r="89" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="90" spans="1:9" ht="12.65" customHeight="1">
       <c r="A90" s="261" t="s">
-        <v>3226</v>
+        <v>3225</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="12.65" customHeight="1">
       <c r="B91" t="s">
+        <v>3209</v>
+      </c>
+      <c r="C91" t="s">
         <v>3210</v>
       </c>
-      <c r="C91" t="s">
+      <c r="D91" t="s">
         <v>3211</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
         <v>3212</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
         <v>3213</v>
       </c>
-      <c r="F91" t="s">
+      <c r="G91" t="s">
         <v>3214</v>
       </c>
-      <c r="G91" t="s">
+      <c r="H91" t="s">
         <v>3215</v>
       </c>
-      <c r="H91" t="s">
+      <c r="I91" t="s">
         <v>3216</v>
-      </c>
-      <c r="I91" t="s">
-        <v>3217</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="12.65" customHeight="1">
@@ -71635,7 +71658,7 @@
     </row>
     <row r="94" spans="1:9" ht="12.65" customHeight="1">
       <c r="A94" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="B94">
         <v>11</v>
@@ -71665,33 +71688,33 @@
     <row r="95" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="96" spans="1:9" ht="12.65" customHeight="1">
       <c r="A96" s="261" t="s">
-        <v>3227</v>
+        <v>3226</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="12.65" customHeight="1">
       <c r="B97" t="s">
+        <v>3209</v>
+      </c>
+      <c r="C97" t="s">
         <v>3210</v>
       </c>
-      <c r="C97" t="s">
+      <c r="D97" t="s">
         <v>3211</v>
       </c>
-      <c r="D97" t="s">
+      <c r="E97" t="s">
         <v>3212</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
         <v>3213</v>
       </c>
-      <c r="F97" t="s">
+      <c r="G97" t="s">
         <v>3214</v>
       </c>
-      <c r="G97" t="s">
+      <c r="H97" t="s">
         <v>3215</v>
       </c>
-      <c r="H97" t="s">
+      <c r="I97" t="s">
         <v>3216</v>
-      </c>
-      <c r="I97" t="s">
-        <v>3217</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="12.65" customHeight="1">
@@ -71928,7 +71951,7 @@
     </row>
     <row r="106" spans="1:9" ht="12.65" customHeight="1">
       <c r="A106" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="B106">
         <v>8</v>
@@ -71958,33 +71981,33 @@
     <row r="107" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="108" spans="1:9" ht="12.65" customHeight="1">
       <c r="A108" s="261" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="12.65" customHeight="1">
       <c r="B109" t="s">
+        <v>3209</v>
+      </c>
+      <c r="C109" t="s">
         <v>3210</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
         <v>3211</v>
       </c>
-      <c r="D109" t="s">
+      <c r="E109" t="s">
         <v>3212</v>
       </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
         <v>3213</v>
       </c>
-      <c r="F109" t="s">
+      <c r="G109" t="s">
         <v>3214</v>
       </c>
-      <c r="G109" t="s">
+      <c r="H109" t="s">
         <v>3215</v>
       </c>
-      <c r="H109" t="s">
+      <c r="I109" t="s">
         <v>3216</v>
-      </c>
-      <c r="I109" t="s">
-        <v>3217</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="12.65" customHeight="1">
@@ -72105,7 +72128,7 @@
     </row>
     <row r="114" spans="1:9" ht="12.65" customHeight="1">
       <c r="A114" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="B114">
         <v>10</v>
@@ -72135,38 +72158,38 @@
     <row r="115" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="116" spans="1:9" ht="12.65" customHeight="1">
       <c r="A116" s="261" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="12.65" customHeight="1">
       <c r="B117" t="s">
+        <v>3209</v>
+      </c>
+      <c r="C117" t="s">
         <v>3210</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
         <v>3211</v>
       </c>
-      <c r="D117" t="s">
+      <c r="E117" t="s">
         <v>3212</v>
       </c>
-      <c r="E117" t="s">
+      <c r="F117" t="s">
         <v>3213</v>
       </c>
-      <c r="F117" t="s">
+      <c r="G117" t="s">
         <v>3214</v>
       </c>
-      <c r="G117" t="s">
+      <c r="H117" t="s">
         <v>3215</v>
       </c>
-      <c r="H117" t="s">
+      <c r="I117" t="s">
         <v>3216</v>
-      </c>
-      <c r="I117" t="s">
-        <v>3217</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="12.65" customHeight="1">
       <c r="A118" t="s">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="B118">
         <v>2</v>
@@ -72195,7 +72218,7 @@
     </row>
     <row r="119" spans="1:9" ht="12.65" customHeight="1">
       <c r="A119" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
       <c r="B119">
         <v>6</v>
@@ -72224,7 +72247,7 @@
     </row>
     <row r="120" spans="1:9" ht="12.65" customHeight="1">
       <c r="A120" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="B120">
         <v>8</v>
@@ -72254,106 +72277,106 @@
     <row r="121" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="122" spans="1:9" ht="12.65" customHeight="1">
       <c r="A122" s="261" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="124" spans="1:9" ht="12.65" customHeight="1">
       <c r="A124" s="261" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="12.65" customHeight="1">
       <c r="A125" s="261" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="127" spans="1:9" ht="12.65" customHeight="1">
       <c r="A127" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="12.65" customHeight="1">
       <c r="A128" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="129" spans="1:1" ht="12.65" customHeight="1">
       <c r="A129" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
     </row>
     <row r="130" spans="1:1" ht="12.65" customHeight="1">
       <c r="A130" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
     </row>
     <row r="131" spans="1:1" ht="12.65" customHeight="1">
       <c r="A131" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="132" spans="1:1" ht="12.65" customHeight="1">
       <c r="A132" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
     </row>
     <row r="133" spans="1:1" ht="12.65" customHeight="1">
       <c r="A133" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="134" spans="1:1" ht="12.65" customHeight="1">
       <c r="A134" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
     </row>
     <row r="135" spans="1:1" ht="12.65" customHeight="1">
       <c r="A135" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
     </row>
     <row r="136" spans="1:1" ht="12.65" customHeight="1">
       <c r="A136" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
     </row>
     <row r="137" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="138" spans="1:1" ht="12.65" customHeight="1">
       <c r="A138" s="261" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
     </row>
     <row r="139" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="140" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="141" spans="1:1" ht="12.65" customHeight="1">
       <c r="A141" s="466" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
     </row>
     <row r="142" spans="1:1" ht="12.65" customHeight="1">
       <c r="A142" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="143" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="144" spans="1:1" ht="12.65" customHeight="1">
       <c r="A144" s="467" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
     </row>
     <row r="145" spans="1:2" ht="12.65" customHeight="1">
       <c r="A145" t="s">
+        <v>3248</v>
+      </c>
+      <c r="B145" t="s">
         <v>3249</v>
-      </c>
-      <c r="B145" t="s">
-        <v>3250</v>
       </c>
     </row>
     <row r="146" spans="1:2" ht="12.65" customHeight="1">
       <c r="A146" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="B146">
         <v>12</v>
@@ -72361,7 +72384,7 @@
     </row>
     <row r="147" spans="1:2" ht="12.65" customHeight="1">
       <c r="A147" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="B147">
         <v>28</v>
@@ -72369,7 +72392,7 @@
     </row>
     <row r="148" spans="1:2" ht="12.65" customHeight="1">
       <c r="A148" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="B148">
         <v>23</v>
@@ -72377,7 +72400,7 @@
     </row>
     <row r="149" spans="1:2" ht="12.65" customHeight="1">
       <c r="A149" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="B149">
         <v>17</v>
@@ -72385,486 +72408,486 @@
     </row>
     <row r="150" spans="1:2" ht="12.65" customHeight="1">
       <c r="A150" t="s">
+        <v>3254</v>
+      </c>
+      <c r="B150" t="s">
         <v>3255</v>
-      </c>
-      <c r="B150" t="s">
-        <v>3256</v>
       </c>
     </row>
     <row r="151" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="152" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="153" spans="1:2" ht="12.65" customHeight="1">
       <c r="A153" s="468" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
     </row>
     <row r="154" spans="1:2" ht="12.65" customHeight="1">
       <c r="A154" t="s">
-        <v>3258</v>
+        <v>3257</v>
       </c>
     </row>
     <row r="155" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="156" spans="1:2" ht="12.65" customHeight="1">
       <c r="A156" s="469" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
     </row>
     <row r="157" spans="1:2" ht="12.65" customHeight="1">
       <c r="A157" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="158" spans="1:2" ht="12.65" customHeight="1">
       <c r="A158" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
     </row>
     <row r="159" spans="1:2" ht="12.65" customHeight="1">
       <c r="A159" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="160" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="161" spans="1:2" ht="12.65" customHeight="1">
       <c r="A161" s="469" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="162" spans="1:2" ht="12.65" customHeight="1">
       <c r="A162" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
     </row>
     <row r="163" spans="1:2" ht="12.65" customHeight="1">
       <c r="A163" t="s">
+        <v>3264</v>
+      </c>
+      <c r="B163" t="s">
         <v>3265</v>
-      </c>
-      <c r="B163" t="s">
-        <v>3266</v>
       </c>
     </row>
     <row r="164" spans="1:2" ht="12.65" customHeight="1">
       <c r="A164" t="s">
+        <v>3266</v>
+      </c>
+      <c r="B164" t="s">
         <v>3267</v>
-      </c>
-      <c r="B164" t="s">
-        <v>3268</v>
       </c>
     </row>
     <row r="165" spans="1:2" ht="12.65" customHeight="1">
       <c r="A165" t="s">
+        <v>3268</v>
+      </c>
+      <c r="B165" t="s">
         <v>3269</v>
-      </c>
-      <c r="B165" t="s">
-        <v>3270</v>
       </c>
     </row>
     <row r="166" spans="1:2" ht="12.65" customHeight="1">
       <c r="A166" t="s">
+        <v>3270</v>
+      </c>
+      <c r="B166" t="s">
         <v>3271</v>
-      </c>
-      <c r="B166" t="s">
-        <v>3272</v>
       </c>
     </row>
     <row r="167" spans="1:2" ht="12.65" customHeight="1">
       <c r="A167" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="B167" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
     </row>
     <row r="168" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="169" spans="1:2" ht="12.65" customHeight="1">
       <c r="A169" t="s">
-        <v>3274</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="170" spans="1:2" ht="12.65" customHeight="1">
       <c r="A170" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
     </row>
     <row r="171" spans="1:2" ht="12.65" customHeight="1">
       <c r="A171" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
     </row>
     <row r="172" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="173" spans="1:2" ht="12.65" customHeight="1">
       <c r="A173" s="469" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
     </row>
     <row r="174" spans="1:2" ht="12.65" customHeight="1">
       <c r="A174" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
     </row>
     <row r="175" spans="1:2" ht="12.65" customHeight="1">
       <c r="A175" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
     </row>
     <row r="176" spans="1:2" ht="12.65" customHeight="1">
       <c r="A176" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
     </row>
     <row r="177" spans="1:1" ht="12.65" customHeight="1">
       <c r="A177" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
     </row>
     <row r="178" spans="1:1" ht="12.65" customHeight="1">
       <c r="A178" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
     </row>
     <row r="179" spans="1:1" ht="12.65" customHeight="1">
       <c r="A179" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
     </row>
     <row r="180" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="181" spans="1:1" ht="12.65" customHeight="1">
       <c r="A181" s="470" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
     </row>
     <row r="182" spans="1:1" ht="12.65" customHeight="1">
       <c r="A182" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
     </row>
     <row r="183" spans="1:1" ht="12.65" customHeight="1">
       <c r="A183" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
     </row>
     <row r="184" spans="1:1" ht="12.65" customHeight="1">
       <c r="A184" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
     </row>
     <row r="185" spans="1:1" ht="12.65" customHeight="1">
       <c r="A185" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
     </row>
     <row r="186" spans="1:1" ht="12.65" customHeight="1">
       <c r="A186" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
     </row>
     <row r="187" spans="1:1" ht="12.65" customHeight="1">
       <c r="A187" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
     </row>
     <row r="188" spans="1:1" ht="12.65" customHeight="1">
       <c r="A188" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="189" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="190" spans="1:1" ht="12.65" customHeight="1">
       <c r="A190" s="468" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
     </row>
     <row r="191" spans="1:1" ht="12.65" customHeight="1">
       <c r="A191" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
     </row>
     <row r="192" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="193" spans="1:1" ht="12.65" customHeight="1">
       <c r="A193" s="467" t="s">
-        <v>3294</v>
+        <v>3293</v>
       </c>
     </row>
     <row r="194" spans="1:1" ht="12.65" customHeight="1">
       <c r="A194" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
     </row>
     <row r="195" spans="1:1" ht="12.65" customHeight="1">
       <c r="A195" t="s">
-        <v>3296</v>
+        <v>3295</v>
       </c>
     </row>
     <row r="196" spans="1:1" ht="12.65" customHeight="1">
       <c r="A196" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
     </row>
     <row r="197" spans="1:1" ht="12.65" customHeight="1">
       <c r="A197" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
     </row>
     <row r="198" spans="1:1" ht="12.65" customHeight="1">
       <c r="A198" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
     </row>
     <row r="199" spans="1:1" ht="12.65" customHeight="1">
       <c r="A199" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
     </row>
     <row r="200" spans="1:1" ht="12.65" customHeight="1">
       <c r="A200" t="s">
-        <v>3301</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="201" spans="1:1" ht="12.65" customHeight="1">
       <c r="A201" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
     </row>
     <row r="202" spans="1:1" ht="12.65" customHeight="1">
       <c r="A202" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
     </row>
     <row r="203" spans="1:1" ht="12.65" customHeight="1">
       <c r="A203" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
     </row>
     <row r="204" spans="1:1" ht="12.65" customHeight="1">
       <c r="A204" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
     </row>
     <row r="205" spans="1:1" ht="12.65" customHeight="1">
       <c r="A205" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
     </row>
     <row r="206" spans="1:1" ht="12.65" customHeight="1">
       <c r="A206" t="s">
-        <v>3307</v>
+        <v>3306</v>
       </c>
     </row>
     <row r="207" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="208" spans="1:1" ht="12.65" customHeight="1">
       <c r="A208" s="467" t="s">
-        <v>3308</v>
+        <v>3307</v>
       </c>
     </row>
     <row r="209" spans="1:1" ht="12.65" customHeight="1">
       <c r="A209" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
     </row>
     <row r="210" spans="1:1" ht="12.65" customHeight="1">
       <c r="A210" t="s">
-        <v>3310</v>
+        <v>3309</v>
       </c>
     </row>
     <row r="211" spans="1:1" ht="12.65" customHeight="1">
       <c r="A211" t="s">
-        <v>3311</v>
+        <v>3310</v>
       </c>
     </row>
     <row r="212" spans="1:1" ht="12.65" customHeight="1">
       <c r="A212" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
     </row>
     <row r="213" spans="1:1" ht="12.65" customHeight="1">
       <c r="A213" t="s">
-        <v>3313</v>
+        <v>3312</v>
       </c>
     </row>
     <row r="214" spans="1:1" ht="12.65" customHeight="1">
       <c r="A214" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
     </row>
     <row r="215" spans="1:1" ht="12.65" customHeight="1">
       <c r="A215" t="s">
-        <v>3315</v>
+        <v>3314</v>
       </c>
     </row>
     <row r="216" spans="1:1" ht="12.65" customHeight="1">
       <c r="A216" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
     </row>
     <row r="217" spans="1:1" ht="12.65" customHeight="1">
       <c r="A217" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
     </row>
     <row r="218" spans="1:1" ht="12.65" customHeight="1">
       <c r="A218" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
     </row>
     <row r="219" spans="1:1" ht="12.65" customHeight="1">
       <c r="A219" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="220" spans="1:1" ht="12.65" customHeight="1">
       <c r="A220" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
     </row>
     <row r="221" spans="1:1" ht="12.65" customHeight="1">
       <c r="A221" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
     </row>
     <row r="222" spans="1:1" ht="12.65" customHeight="1">
       <c r="A222" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
     </row>
     <row r="223" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="224" spans="1:1" ht="12.65" customHeight="1">
       <c r="A224" s="471" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="225" spans="1:2" ht="12.65" customHeight="1">
       <c r="A225" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="226" spans="1:2" ht="12.65" customHeight="1">
       <c r="A226" t="s">
-        <v>3325</v>
+        <v>3324</v>
       </c>
     </row>
     <row r="227" spans="1:2" ht="12.65" customHeight="1">
       <c r="A227" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="228" spans="1:2" ht="12.65" customHeight="1">
       <c r="A228" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
     </row>
     <row r="229" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="230" spans="1:2" ht="12.65" customHeight="1">
       <c r="A230" s="468" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
     </row>
     <row r="231" spans="1:2" ht="12.65" customHeight="1">
       <c r="A231" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
     </row>
     <row r="232" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="233" spans="1:2" ht="12.65" customHeight="1">
       <c r="A233" s="467" t="s">
-        <v>3330</v>
+        <v>3329</v>
       </c>
     </row>
     <row r="234" spans="1:2" ht="12.65" customHeight="1">
       <c r="A234" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B234" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="235" spans="1:2" ht="12.65" customHeight="1">
       <c r="A235" t="s">
+        <v>3331</v>
+      </c>
+      <c r="B235" t="s">
         <v>3332</v>
-      </c>
-      <c r="B235" t="s">
-        <v>3333</v>
       </c>
     </row>
     <row r="236" spans="1:2" ht="12.65" customHeight="1">
       <c r="A236" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="B236" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="237" spans="1:2" ht="12.65" customHeight="1">
       <c r="A237" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="B237" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
     </row>
     <row r="238" spans="1:2" ht="12.65" customHeight="1">
       <c r="A238" t="s">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="B238" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
     </row>
     <row r="239" spans="1:2" ht="12.65" customHeight="1">
       <c r="A239" t="s">
+        <v>3128</v>
+      </c>
+      <c r="B239" t="s">
         <v>3129</v>
-      </c>
-      <c r="B239" t="s">
-        <v>3130</v>
       </c>
     </row>
     <row r="240" spans="1:2" ht="12.65" customHeight="1">
       <c r="A240" t="s">
+        <v>3130</v>
+      </c>
+      <c r="B240" t="s">
         <v>3131</v>
-      </c>
-      <c r="B240" t="s">
-        <v>3132</v>
       </c>
     </row>
     <row r="241" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="242" spans="1:1" ht="12.65" customHeight="1">
       <c r="A242" s="467" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
     </row>
     <row r="243" spans="1:1" ht="12.65" customHeight="1">
       <c r="A243" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
     </row>
     <row r="244" spans="1:1" ht="12.65" customHeight="1">
       <c r="A244" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="245" spans="1:1" ht="12.65" customHeight="1">
       <c r="A245" t="s">
-        <v>3340</v>
+        <v>3339</v>
       </c>
     </row>
     <row r="246" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="247" spans="1:1" ht="12.65" customHeight="1">
       <c r="A247" s="467" t="s">
-        <v>3341</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="248" spans="1:1" ht="12.65" customHeight="1">
       <c r="A248" t="s">
-        <v>3342</v>
+        <v>3341</v>
       </c>
     </row>
     <row r="249" spans="1:1" ht="12.65" customHeight="1">
       <c r="A249" t="s">
-        <v>3343</v>
+        <v>3342</v>
       </c>
     </row>
     <row r="250" spans="1:1" ht="12.65" customHeight="1">
       <c r="A250" t="s">
-        <v>3344</v>
+        <v>3343</v>
       </c>
     </row>
     <row r="251" spans="1:1" ht="12.65" customHeight="1"/>

--- a/j-busqueda clientes/j-clientes-gle.xlsx
+++ b/j-busqueda clientes/j-clientes-gle.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88153b17ae7a9f01/documentos/TRABAJOS AUTONOMOS/JURADA/j-busqueda clientes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_8D71D4E3FF54086EB3E5708B7890922AE0578CDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AC1CC79-5B46-4F19-A930-9ED8F7B01944}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_8D71D4E3FF54086EB3E5708B7890922AE0578CDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CB0FE34-902F-45A7-9FF3-4862903B6F36}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="-110" windowWidth="24900" windowHeight="14500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="810" yWindow="-110" windowWidth="24900" windowHeight="14500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="clientes" sheetId="1" r:id="rId1"/>
@@ -10993,7 +10993,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="495">
+  <cellXfs count="497">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -12405,6 +12405,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -12421,6 +12423,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -73742,19 +73748,19 @@
   <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="1" max="1" width="11" style="496" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" customWidth="1"/>
     <col min="6" max="6" width="42" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="70" customWidth="1"/>
+    <col min="9" max="9" width="50.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="13">
-      <c r="A1" s="492" t="s">
+      <c r="A1" s="495" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="492" t="s">
@@ -73783,7 +73789,9 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="37.5">
-      <c r="A2" s="493"/>
+      <c r="A2" s="496">
+        <v>46238</v>
+      </c>
       <c r="B2" t="s">
         <v>3365</v>
       </c>
@@ -73802,7 +73810,6 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="37.5">
-      <c r="A3" s="493"/>
       <c r="B3" t="s">
         <v>3370</v>
       </c>
@@ -73824,7 +73831,6 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="25">
-      <c r="A4" s="493"/>
       <c r="B4" t="s">
         <v>3375</v>
       </c>
@@ -73846,7 +73852,6 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="25">
-      <c r="A5" s="493"/>
       <c r="B5" t="s">
         <v>3380</v>
       </c>
@@ -73865,7 +73870,6 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="25">
-      <c r="A6" s="493"/>
       <c r="B6" t="s">
         <v>3385</v>
       </c>
@@ -73884,7 +73888,6 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="25">
-      <c r="A7" s="493"/>
       <c r="B7" t="s">
         <v>3390</v>
       </c>
@@ -73903,7 +73906,6 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="25">
-      <c r="A8" s="493"/>
       <c r="B8" t="s">
         <v>3394</v>
       </c>
@@ -73922,7 +73924,6 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="25">
-      <c r="A9" s="493"/>
       <c r="B9" t="s">
         <v>3398</v>
       </c>
@@ -73944,7 +73945,6 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="25">
-      <c r="A10" s="493"/>
       <c r="B10" t="s">
         <v>3402</v>
       </c>
@@ -73961,6 +73961,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/j-busqueda clientes/j-clientes-gle.xlsx
+++ b/j-busqueda clientes/j-clientes-gle.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88153b17ae7a9f01/documentos/TRABAJOS AUTONOMOS/JURADA/j-busqueda clientes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_8D71D4E3FF54086EB3E5708B7890922AE0578CDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CB0FE34-902F-45A7-9FF3-4862903B6F36}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_8D71D4E3FF54086EB3E5708B7890922AE0578CDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A87CF92-D83C-4851-9AF3-027F5301E3F1}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="-110" windowWidth="24900" windowHeight="14500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="810" yWindow="-110" windowWidth="24900" windowHeight="14500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="clientes" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5709" uniqueCount="3410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5708" uniqueCount="3409">
   <si>
     <t>para día</t>
   </si>
@@ -7299,15 +7299,9 @@
     <t>Borja Montesino-Espartero Velasco</t>
   </si>
   <si>
-    <t>pwc.comunicacion@pwc.com</t>
-  </si>
-  <si>
     <t>International Assignment Services (IAS): Global Mobility, inmigración, planificación fiscal para asignaciones internacionales. +3200 profesionales en Madrid. Asesoría integrada fiscal-inmigratoria.</t>
   </si>
   <si>
-    <t>deducidos 1: borja.montesino.espartero@pwc.com / borja.montesino@pwc.com; deducidos 2: b.montesino@pwc.com / bmontesino@pwc.com</t>
-  </si>
-  <si>
     <t>Multinacionales con empleados desplazados (Global Mobility / expatriados)</t>
   </si>
   <si>
@@ -10318,6 +10312,9 @@
   </si>
   <si>
     <t>Borrador creado 31-7-2026 pero NO ENVIAR hasta despues del 14-8-2026: cerrada por vacaciones del 24-7 al 14-8</t>
+  </si>
+  <si>
+    <t>borja.montesino@pwc.com (deducido)</t>
   </si>
 </sst>
 </file>
@@ -34936,7 +34933,9 @@
       <c r="A373" s="212">
         <v>46238.416666666657</v>
       </c>
-      <c r="B373" s="212"/>
+      <c r="B373" s="212">
+        <v>46238</v>
+      </c>
       <c r="C373" s="375"/>
       <c r="D373" s="106"/>
       <c r="E373" s="79" t="s">
@@ -34955,11 +34954,11 @@
       <c r="J373" s="121" t="s">
         <v>2402</v>
       </c>
-      <c r="K373" t="s">
+      <c r="K373" s="295" t="s">
+        <v>3408</v>
+      </c>
+      <c r="L373" s="121" t="s">
         <v>2403</v>
-      </c>
-      <c r="L373" s="121" t="s">
-        <v>2404</v>
       </c>
       <c r="M373" s="173" t="s">
         <v>1446</v>
@@ -34971,30 +34970,28 @@
       <c r="P373" s="79" t="s">
         <v>1022</v>
       </c>
-      <c r="Q373" s="74" t="s">
-        <v>2405</v>
-      </c>
+      <c r="Q373" s="74"/>
       <c r="R373" s="79"/>
       <c r="S373" s="79" t="s">
-        <v>2406</v>
+        <v>2404</v>
       </c>
       <c r="T373" s="79" t="s">
         <v>478</v>
       </c>
       <c r="U373" s="79" t="s">
+        <v>2405</v>
+      </c>
+      <c r="V373" s="79" t="s">
+        <v>2406</v>
+      </c>
+      <c r="W373" s="79" t="s">
         <v>2407</v>
       </c>
-      <c r="V373" s="79" t="s">
+      <c r="X373" s="79" t="s">
         <v>2408</v>
       </c>
-      <c r="W373" s="79" t="s">
+      <c r="Y373" s="79" t="s">
         <v>2409</v>
-      </c>
-      <c r="X373" s="79" t="s">
-        <v>2410</v>
-      </c>
-      <c r="Y373" s="79" t="s">
-        <v>2411</v>
       </c>
       <c r="Z373" s="79" t="s">
         <v>1060</v>
@@ -35026,19 +35023,19 @@
       </c>
       <c r="G374" s="100"/>
       <c r="H374" s="117" t="s">
+        <v>2410</v>
+      </c>
+      <c r="I374" t="s">
+        <v>2411</v>
+      </c>
+      <c r="J374" s="117" t="s">
         <v>2412</v>
       </c>
-      <c r="I374" t="s">
+      <c r="K374" t="s">
         <v>2413</v>
       </c>
-      <c r="J374" s="117" t="s">
+      <c r="L374" s="117" t="s">
         <v>2414</v>
-      </c>
-      <c r="K374" t="s">
-        <v>2415</v>
-      </c>
-      <c r="L374" s="117" t="s">
-        <v>2416</v>
       </c>
       <c r="M374" s="167" t="s">
         <v>1446</v>
@@ -35051,31 +35048,31 @@
       </c>
       <c r="P374" s="100"/>
       <c r="Q374" s="402" t="s">
+        <v>2415</v>
+      </c>
+      <c r="R374" s="100" t="s">
+        <v>2416</v>
+      </c>
+      <c r="S374" s="100" t="s">
         <v>2417</v>
-      </c>
-      <c r="R374" s="100" t="s">
-        <v>2418</v>
-      </c>
-      <c r="S374" s="100" t="s">
-        <v>2419</v>
       </c>
       <c r="T374" s="100" t="s">
         <v>478</v>
       </c>
       <c r="U374" s="100" t="s">
+        <v>2418</v>
+      </c>
+      <c r="V374" s="100" t="s">
+        <v>2419</v>
+      </c>
+      <c r="W374" s="100" t="s">
         <v>2420</v>
       </c>
-      <c r="V374" s="100" t="s">
+      <c r="X374" s="100" t="s">
         <v>2421</v>
       </c>
-      <c r="W374" s="100" t="s">
+      <c r="Y374" s="100" t="s">
         <v>2422</v>
-      </c>
-      <c r="X374" s="100" t="s">
-        <v>2423</v>
-      </c>
-      <c r="Y374" s="100" t="s">
-        <v>2424</v>
       </c>
       <c r="Z374" s="100" t="s">
         <v>253</v>
@@ -35099,17 +35096,17 @@
       <c r="F375" s="102"/>
       <c r="G375" s="102"/>
       <c r="H375" s="118" t="s">
-        <v>2425</v>
+        <v>2423</v>
       </c>
       <c r="I375" t="s">
-        <v>2426</v>
+        <v>2424</v>
       </c>
       <c r="J375" s="118"/>
       <c r="L375" s="118" t="s">
-        <v>2427</v>
+        <v>2425</v>
       </c>
       <c r="M375" s="168" t="s">
-        <v>2428</v>
+        <v>2426</v>
       </c>
       <c r="N375" s="102"/>
       <c r="O375" s="102"/>
@@ -35153,22 +35150,22 @@
         <v>772</v>
       </c>
       <c r="H376" s="120" t="s">
+        <v>2427</v>
+      </c>
+      <c r="I376" t="s">
+        <v>2428</v>
+      </c>
+      <c r="J376" s="120" t="s">
         <v>2429</v>
       </c>
-      <c r="I376" t="s">
+      <c r="K376" s="118" t="s">
         <v>2430</v>
       </c>
-      <c r="J376" s="120" t="s">
+      <c r="L376" s="120" t="s">
         <v>2431</v>
       </c>
-      <c r="K376" s="118" t="s">
+      <c r="M376" s="171" t="s">
         <v>2432</v>
-      </c>
-      <c r="L376" s="120" t="s">
-        <v>2433</v>
-      </c>
-      <c r="M376" s="171" t="s">
-        <v>2434</v>
       </c>
       <c r="N376" s="86" t="s">
         <v>38</v>
@@ -35178,29 +35175,29 @@
       </c>
       <c r="P376" s="86"/>
       <c r="Q376" s="400" t="s">
-        <v>2435</v>
+        <v>2433</v>
       </c>
       <c r="R376" s="86"/>
       <c r="S376" s="86" t="s">
+        <v>2434</v>
+      </c>
+      <c r="T376" s="86" t="s">
+        <v>2435</v>
+      </c>
+      <c r="U376" s="86" t="s">
         <v>2436</v>
       </c>
-      <c r="T376" s="86" t="s">
+      <c r="V376" s="86" t="s">
         <v>2437</v>
       </c>
-      <c r="U376" s="86" t="s">
+      <c r="W376" s="86" t="s">
         <v>2438</v>
-      </c>
-      <c r="V376" s="86" t="s">
-        <v>2439</v>
-      </c>
-      <c r="W376" s="86" t="s">
-        <v>2440</v>
       </c>
       <c r="X376" s="86" t="s">
         <v>2297</v>
       </c>
       <c r="Y376" s="86" t="s">
-        <v>2441</v>
+        <v>2439</v>
       </c>
       <c r="Z376" s="86" t="s">
         <v>189</v>
@@ -35224,17 +35221,17 @@
       <c r="F377" s="54"/>
       <c r="G377" s="487"/>
       <c r="H377" s="122" t="s">
-        <v>2442</v>
+        <v>2440</v>
       </c>
       <c r="I377" t="s">
-        <v>2443</v>
+        <v>2441</v>
       </c>
       <c r="J377" s="122"/>
       <c r="L377" s="122" t="s">
-        <v>2444</v>
+        <v>2442</v>
       </c>
       <c r="M377" s="172" t="s">
-        <v>2445</v>
+        <v>2443</v>
       </c>
       <c r="N377" s="54"/>
       <c r="O377" s="54"/>
@@ -35267,7 +35264,7 @@
       <c r="G378" s="100"/>
       <c r="H378" s="117"/>
       <c r="M378" s="167" t="s">
-        <v>2446</v>
+        <v>2444</v>
       </c>
       <c r="N378" s="100"/>
       <c r="O378" s="100"/>
@@ -40309,36 +40306,36 @@
   <sheetData>
     <row r="1" spans="8:15" ht="12.65" customHeight="1">
       <c r="H1" s="5" t="s">
-        <v>2447</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="2" spans="8:15" ht="12.65" customHeight="1">
       <c r="H2" s="19" t="s">
-        <v>2448</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="3" spans="8:15" ht="12.65" customHeight="1">
       <c r="H3" s="19" t="s">
-        <v>2449</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="4" spans="8:15" ht="12.65" customHeight="1">
       <c r="H4" s="20" t="s">
-        <v>2450</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="5" spans="8:15" ht="12.65" customHeight="1">
       <c r="H5" s="6" t="s">
+        <v>2449</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>2450</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>2451</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="K5" s="6" t="s">
         <v>2452</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>2453</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>2454</v>
       </c>
       <c r="L5" s="6"/>
       <c r="M5" s="5" t="s">
@@ -40348,19 +40345,19 @@
         <v>57</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>2455</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="6" spans="8:15" ht="12.65" customHeight="1">
       <c r="H6" s="6" t="s">
-        <v>2456</v>
+        <v>2454</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>2457</v>
+        <v>2455</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="21" t="s">
-        <v>2458</v>
+        <v>2456</v>
       </c>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
@@ -40368,24 +40365,24 @@
         <v>38</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>2459</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="7" spans="8:15" ht="15" customHeight="1">
       <c r="H7" s="1" t="s">
+        <v>2458</v>
+      </c>
+      <c r="I7" s="22" t="s">
+        <v>2459</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>2460</v>
       </c>
-      <c r="I7" s="22" t="s">
+      <c r="K7" s="1" t="s">
         <v>2461</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>2462</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>2463</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>2464</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>777</v>
@@ -40431,13 +40428,13 @@
         <v>1574</v>
       </c>
       <c r="K9" s="1" t="s">
+        <v>2463</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>2464</v>
+      </c>
+      <c r="M9" s="1" t="s">
         <v>2465</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>2466</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>2467</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>57</v>
@@ -40445,19 +40442,19 @@
     </row>
     <row r="10" spans="8:15" ht="12.65" customHeight="1">
       <c r="H10" s="5" t="s">
+        <v>2466</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>2467</v>
+      </c>
+      <c r="J10" s="5" t="s">
         <v>2468</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="K10" s="6" t="s">
         <v>2469</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="L10" s="5" t="s">
         <v>2470</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>2471</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>2472</v>
       </c>
       <c r="M10" s="5" t="s">
         <v>910</v>
@@ -40466,212 +40463,212 @@
         <v>57</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>2473</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="11" spans="8:15" ht="15" customHeight="1">
       <c r="H11" s="1" t="s">
-        <v>2474</v>
+        <v>2472</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>2475</v>
+        <v>2473</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>1294</v>
       </c>
       <c r="K11" s="1" t="s">
+        <v>2474</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>2475</v>
+      </c>
+      <c r="M11" s="1" t="s">
         <v>2476</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>2477</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>2478</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>57</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>2479</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="12" spans="8:15" ht="15" customHeight="1">
       <c r="H12" s="1" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>2481</v>
+        <v>2479</v>
       </c>
       <c r="J12" s="1"/>
       <c r="L12" s="1" t="s">
-        <v>2482</v>
+        <v>2480</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>1770</v>
       </c>
       <c r="O12" s="5" t="s">
-        <v>2483</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="13" spans="8:15" ht="15" customHeight="1">
       <c r="H13" s="1" t="s">
+        <v>2482</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>2483</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>2484</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="K13" s="1" t="s">
         <v>2485</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>2486</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>2487</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="O13" s="24" t="s">
         <v>2488</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>2489</v>
-      </c>
-      <c r="O13" s="24" t="s">
-        <v>2490</v>
       </c>
     </row>
     <row r="14" spans="8:15" ht="15" customHeight="1">
       <c r="H14" s="1" t="s">
-        <v>2491</v>
+        <v>2489</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>2492</v>
+        <v>2490</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>1294</v>
       </c>
       <c r="K14" s="1" t="s">
+        <v>2491</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>2492</v>
+      </c>
+      <c r="M14" s="1" t="s">
         <v>2493</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>2494</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>2495</v>
       </c>
     </row>
     <row r="15" spans="8:15" ht="15" customHeight="1">
       <c r="H15" s="1" t="s">
+        <v>2494</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>2495</v>
+      </c>
+      <c r="J15" s="1" t="s">
         <v>2496</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="K15" s="1" t="s">
         <v>2497</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>2498</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>2499</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>2500</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>812</v>
       </c>
       <c r="O15" s="24" t="s">
-        <v>2501</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="16" spans="8:15" ht="15" customHeight="1">
       <c r="H16" s="28" t="s">
+        <v>2500</v>
+      </c>
+      <c r="I16" s="29" t="s">
+        <v>2501</v>
+      </c>
+      <c r="J16" s="28" t="s">
         <v>2502</v>
       </c>
-      <c r="I16" s="29" t="s">
+      <c r="K16" s="28" t="s">
         <v>2503</v>
       </c>
-      <c r="J16" s="28" t="s">
+      <c r="L16" s="28" t="s">
         <v>2504</v>
-      </c>
-      <c r="K16" s="28" t="s">
-        <v>2505</v>
-      </c>
-      <c r="L16" s="28" t="s">
-        <v>2506</v>
       </c>
       <c r="M16" s="28" t="s">
         <v>1376</v>
       </c>
       <c r="N16" s="28"/>
       <c r="O16" s="31" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="17" spans="1:47" ht="15" customHeight="1">
       <c r="H17" s="30" t="s">
-        <v>2508</v>
+        <v>2506</v>
       </c>
       <c r="I17" s="30" t="s">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="J17" s="30"/>
       <c r="K17" s="30" t="s">
         <v>1294</v>
       </c>
       <c r="L17" s="30" t="s">
+        <v>2508</v>
+      </c>
+      <c r="M17" s="30" t="s">
+        <v>2509</v>
+      </c>
+      <c r="O17" s="24" t="s">
         <v>2510</v>
-      </c>
-      <c r="M17" s="30" t="s">
-        <v>2511</v>
-      </c>
-      <c r="O17" s="24" t="s">
-        <v>2512</v>
       </c>
     </row>
     <row r="18" spans="1:47" ht="15" customHeight="1">
       <c r="H18" s="30" t="s">
-        <v>2513</v>
+        <v>2511</v>
       </c>
       <c r="I18" s="30" t="s">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="J18" s="30"/>
       <c r="K18" s="30" t="s">
         <v>1294</v>
       </c>
       <c r="L18" s="30" t="s">
-        <v>2515</v>
+        <v>2513</v>
       </c>
       <c r="M18" s="30" t="s">
-        <v>2511</v>
+        <v>2509</v>
       </c>
       <c r="O18" s="24" t="s">
-        <v>2512</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="19" spans="1:47" ht="15" customHeight="1">
       <c r="H19" s="30" t="s">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="I19" s="30" t="s">
-        <v>2517</v>
+        <v>2515</v>
       </c>
       <c r="J19" s="30"/>
       <c r="K19" s="30" t="s">
         <v>1294</v>
       </c>
       <c r="L19" s="30" t="s">
-        <v>2518</v>
+        <v>2516</v>
       </c>
       <c r="M19" s="30" t="s">
         <v>1489</v>
       </c>
       <c r="O19" s="24" t="s">
-        <v>2519</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="20" spans="1:47" ht="15" customHeight="1">
       <c r="H20" s="28" t="s">
-        <v>2520</v>
+        <v>2518</v>
       </c>
       <c r="I20" s="29" t="s">
-        <v>2521</v>
+        <v>2519</v>
       </c>
       <c r="J20" s="28"/>
       <c r="K20" s="28"/>
@@ -40684,39 +40681,39 @@
     </row>
     <row r="21" spans="1:47" ht="15" customHeight="1">
       <c r="H21" s="44" t="s">
-        <v>2522</v>
+        <v>2520</v>
       </c>
       <c r="I21" s="50" t="s">
-        <v>2523</v>
+        <v>2521</v>
       </c>
       <c r="J21" s="44"/>
       <c r="K21" s="44"/>
       <c r="L21" s="44" t="s">
-        <v>2524</v>
+        <v>2522</v>
       </c>
       <c r="M21" s="44" t="s">
-        <v>2525</v>
+        <v>2523</v>
       </c>
       <c r="N21" s="44"/>
       <c r="O21" s="44"/>
       <c r="P21" s="45"/>
       <c r="Q21" s="50" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
       <c r="R21" s="44"/>
       <c r="S21" s="44"/>
     </row>
     <row r="22" spans="1:47" ht="15" customHeight="1">
       <c r="H22" s="34" t="s">
-        <v>2527</v>
+        <v>2525</v>
       </c>
       <c r="I22" s="48" t="s">
-        <v>2528</v>
+        <v>2526</v>
       </c>
       <c r="J22" s="34"/>
       <c r="K22" s="34"/>
       <c r="L22" s="34" t="s">
-        <v>2529</v>
+        <v>2527</v>
       </c>
       <c r="M22" s="34" t="s">
         <v>633</v>
@@ -40725,62 +40722,62 @@
       <c r="O22" s="34"/>
       <c r="P22" s="46"/>
       <c r="Q22" s="48" t="s">
-        <v>2530</v>
+        <v>2528</v>
       </c>
       <c r="R22" s="34"/>
     </row>
     <row r="23" spans="1:47" ht="15" customHeight="1">
       <c r="H23" s="38" t="s">
-        <v>2531</v>
+        <v>2529</v>
       </c>
       <c r="I23" s="47" t="s">
-        <v>2532</v>
+        <v>2530</v>
       </c>
       <c r="J23" s="38"/>
       <c r="O23" t="s">
-        <v>2533</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="24" spans="1:47" ht="15" customHeight="1">
       <c r="H24" s="37" t="s">
+        <v>2532</v>
+      </c>
+      <c r="I24" s="53" t="s">
+        <v>2533</v>
+      </c>
+      <c r="O24" t="s">
         <v>2534</v>
-      </c>
-      <c r="I24" s="53" t="s">
-        <v>2535</v>
-      </c>
-      <c r="O24" t="s">
-        <v>2536</v>
       </c>
     </row>
     <row r="25" spans="1:47" ht="15" customHeight="1">
       <c r="H25" s="34" t="s">
-        <v>2508</v>
+        <v>2506</v>
       </c>
       <c r="I25" s="48" t="s">
-        <v>2537</v>
+        <v>2535</v>
       </c>
       <c r="J25" s="34" t="s">
         <v>1294</v>
       </c>
       <c r="K25" s="34" t="s">
-        <v>2538</v>
+        <v>2536</v>
       </c>
       <c r="L25" s="34" t="s">
-        <v>2539</v>
+        <v>2537</v>
       </c>
       <c r="M25" s="34" t="s">
         <v>1376</v>
       </c>
       <c r="O25" s="55" t="s">
-        <v>2540</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="26" spans="1:47" ht="15" customHeight="1">
       <c r="H26" s="40" t="s">
-        <v>2541</v>
+        <v>2539</v>
       </c>
       <c r="I26" s="51" t="s">
-        <v>2542</v>
+        <v>2540</v>
       </c>
       <c r="J26" s="40" t="s">
         <v>1294</v>
@@ -40789,16 +40786,16 @@
         <v>1294</v>
       </c>
       <c r="L26" s="40" t="s">
-        <v>2543</v>
+        <v>2541</v>
       </c>
       <c r="M26" s="40" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
       <c r="N26" s="40"/>
       <c r="O26" s="40"/>
       <c r="P26" s="40"/>
       <c r="Q26" s="40" t="s">
-        <v>2545</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="27" spans="1:47" s="27" customFormat="1" ht="12.75" customHeight="1">
@@ -40806,28 +40803,28 @@
       <c r="B27" s="41"/>
       <c r="C27" s="41"/>
       <c r="D27" s="39" t="s">
-        <v>2546</v>
+        <v>2544</v>
       </c>
       <c r="E27" s="42"/>
       <c r="F27" s="42"/>
       <c r="G27" s="42"/>
       <c r="H27" s="42" t="s">
+        <v>2545</v>
+      </c>
+      <c r="I27" s="49" t="s">
+        <v>2546</v>
+      </c>
+      <c r="J27" s="42" t="s">
         <v>2547</v>
       </c>
-      <c r="I27" s="49" t="s">
+      <c r="K27" s="42" t="s">
         <v>2548</v>
       </c>
-      <c r="J27" s="42" t="s">
+      <c r="L27" s="42" t="s">
         <v>2549</v>
       </c>
-      <c r="K27" s="42" t="s">
+      <c r="M27" s="42" t="s">
         <v>2550</v>
-      </c>
-      <c r="L27" s="42" t="s">
-        <v>2551</v>
-      </c>
-      <c r="M27" s="42" t="s">
-        <v>2552</v>
       </c>
       <c r="N27" s="42"/>
       <c r="O27" s="42"/>
@@ -40873,22 +40870,22 @@
       <c r="F28" s="44"/>
       <c r="G28" s="44"/>
       <c r="H28" s="44" t="s">
+        <v>2551</v>
+      </c>
+      <c r="I28" s="50" t="s">
+        <v>2552</v>
+      </c>
+      <c r="J28" s="44" t="s">
         <v>2553</v>
       </c>
-      <c r="I28" s="50" t="s">
+      <c r="K28" s="44" t="s">
         <v>2554</v>
       </c>
-      <c r="J28" s="44" t="s">
+      <c r="L28" s="44" t="s">
         <v>2555</v>
       </c>
-      <c r="K28" s="44" t="s">
+      <c r="M28" s="44" t="s">
         <v>2556</v>
-      </c>
-      <c r="L28" s="44" t="s">
-        <v>2557</v>
-      </c>
-      <c r="M28" s="44" t="s">
-        <v>2558</v>
       </c>
       <c r="N28" s="44"/>
       <c r="O28" s="44"/>
@@ -40934,22 +40931,22 @@
       <c r="F29" s="33"/>
       <c r="G29" s="33"/>
       <c r="H29" s="33" t="s">
-        <v>2559</v>
+        <v>2557</v>
       </c>
       <c r="I29" s="52" t="s">
-        <v>2560</v>
+        <v>2558</v>
       </c>
       <c r="J29" s="33" t="s">
         <v>1294</v>
       </c>
       <c r="K29" s="33" t="s">
+        <v>2559</v>
+      </c>
+      <c r="L29" s="33" t="s">
+        <v>2560</v>
+      </c>
+      <c r="M29" s="33" t="s">
         <v>2561</v>
-      </c>
-      <c r="L29" s="33" t="s">
-        <v>2562</v>
-      </c>
-      <c r="M29" s="33" t="s">
-        <v>2563</v>
       </c>
       <c r="N29" s="33"/>
       <c r="O29" s="33"/>
@@ -40995,10 +40992,10 @@
       <c r="F30" s="34"/>
       <c r="G30" s="34"/>
       <c r="H30" s="34" t="s">
-        <v>2564</v>
+        <v>2562</v>
       </c>
       <c r="I30" s="48" t="s">
-        <v>2565</v>
+        <v>2563</v>
       </c>
       <c r="J30" s="34" t="s">
         <v>1294</v>
@@ -41007,10 +41004,10 @@
         <v>1294</v>
       </c>
       <c r="L30" s="34" t="s">
-        <v>2566</v>
+        <v>2564</v>
       </c>
       <c r="M30" s="34" t="s">
-        <v>2567</v>
+        <v>2565</v>
       </c>
       <c r="N30" s="34"/>
       <c r="O30" s="34"/>
@@ -41056,22 +41053,22 @@
       <c r="F31" s="37"/>
       <c r="G31" s="37"/>
       <c r="H31" s="37" t="s">
+        <v>2566</v>
+      </c>
+      <c r="I31" s="53" t="s">
+        <v>2567</v>
+      </c>
+      <c r="J31" s="37" t="s">
         <v>2568</v>
       </c>
-      <c r="I31" s="53" t="s">
+      <c r="K31" s="37" t="s">
         <v>2569</v>
       </c>
-      <c r="J31" s="37" t="s">
+      <c r="L31" s="37" t="s">
         <v>2570</v>
       </c>
-      <c r="K31" s="37" t="s">
+      <c r="M31" s="37" t="s">
         <v>2571</v>
-      </c>
-      <c r="L31" s="37" t="s">
-        <v>2572</v>
-      </c>
-      <c r="M31" s="37" t="s">
-        <v>2573</v>
       </c>
       <c r="N31" s="37"/>
       <c r="O31" s="37"/>
@@ -41117,19 +41114,19 @@
       <c r="F32" s="40"/>
       <c r="G32" s="40"/>
       <c r="H32" s="40" t="s">
+        <v>2572</v>
+      </c>
+      <c r="I32" s="51" t="s">
+        <v>2573</v>
+      </c>
+      <c r="J32" s="40" t="s">
         <v>2574</v>
       </c>
-      <c r="I32" s="51" t="s">
+      <c r="K32" s="40" t="s">
         <v>2575</v>
       </c>
-      <c r="J32" s="40" t="s">
+      <c r="L32" s="40" t="s">
         <v>2576</v>
-      </c>
-      <c r="K32" s="40" t="s">
-        <v>2577</v>
-      </c>
-      <c r="L32" s="40" t="s">
-        <v>2578</v>
       </c>
       <c r="M32" s="40" t="s">
         <v>1376</v>
@@ -41177,22 +41174,22 @@
       <c r="F33" s="42"/>
       <c r="G33" s="42"/>
       <c r="H33" s="42" t="s">
-        <v>2579</v>
+        <v>2577</v>
       </c>
       <c r="I33" s="49" t="s">
-        <v>2580</v>
+        <v>2578</v>
       </c>
       <c r="J33" s="42" t="s">
         <v>1294</v>
       </c>
       <c r="K33" s="42" t="s">
+        <v>2579</v>
+      </c>
+      <c r="L33" s="42" t="s">
+        <v>2580</v>
+      </c>
+      <c r="M33" s="42" t="s">
         <v>2581</v>
-      </c>
-      <c r="L33" s="42" t="s">
-        <v>2582</v>
-      </c>
-      <c r="M33" s="42" t="s">
-        <v>2583</v>
       </c>
       <c r="N33" s="42"/>
       <c r="O33" s="42"/>
@@ -41238,22 +41235,22 @@
       <c r="F34" s="44"/>
       <c r="G34" s="44"/>
       <c r="H34" s="44" t="s">
+        <v>2582</v>
+      </c>
+      <c r="I34" s="50" t="s">
+        <v>2583</v>
+      </c>
+      <c r="J34" s="44" t="s">
+        <v>2574</v>
+      </c>
+      <c r="K34" s="44" t="s">
         <v>2584</v>
       </c>
-      <c r="I34" s="50" t="s">
+      <c r="L34" s="44" t="s">
         <v>2585</v>
       </c>
-      <c r="J34" s="44" t="s">
-        <v>2576</v>
-      </c>
-      <c r="K34" s="44" t="s">
-        <v>2586</v>
-      </c>
-      <c r="L34" s="44" t="s">
-        <v>2587</v>
-      </c>
       <c r="M34" s="44" t="s">
-        <v>2573</v>
+        <v>2571</v>
       </c>
       <c r="N34" s="44"/>
       <c r="O34" s="44"/>
@@ -41299,10 +41296,10 @@
       <c r="F35" s="33"/>
       <c r="G35" s="33"/>
       <c r="H35" s="33" t="s">
-        <v>2588</v>
+        <v>2586</v>
       </c>
       <c r="I35" s="52" t="s">
-        <v>2589</v>
+        <v>2587</v>
       </c>
       <c r="J35" s="33" t="s">
         <v>1294</v>
@@ -41311,10 +41308,10 @@
         <v>1294</v>
       </c>
       <c r="L35" s="33" t="s">
-        <v>2590</v>
+        <v>2588</v>
       </c>
       <c r="M35" s="33" t="s">
-        <v>2591</v>
+        <v>2589</v>
       </c>
       <c r="N35" s="33"/>
       <c r="O35" s="33"/>
@@ -41360,10 +41357,10 @@
       <c r="F36" s="34"/>
       <c r="G36" s="34"/>
       <c r="H36" s="34" t="s">
-        <v>2592</v>
+        <v>2590</v>
       </c>
       <c r="I36" s="48" t="s">
-        <v>2593</v>
+        <v>2591</v>
       </c>
       <c r="J36" s="34" t="s">
         <v>1294</v>
@@ -41372,7 +41369,7 @@
         <v>1294</v>
       </c>
       <c r="L36" s="34" t="s">
-        <v>2594</v>
+        <v>2592</v>
       </c>
       <c r="M36" s="34" t="s">
         <v>1668</v>
@@ -41421,10 +41418,10 @@
       <c r="F37" s="40"/>
       <c r="G37" s="40"/>
       <c r="H37" s="40" t="s">
-        <v>2595</v>
+        <v>2593</v>
       </c>
       <c r="I37" s="51" t="s">
-        <v>2596</v>
+        <v>2594</v>
       </c>
       <c r="J37" s="40" t="s">
         <v>1294</v>
@@ -41433,7 +41430,7 @@
         <v>1294</v>
       </c>
       <c r="L37" s="40" t="s">
-        <v>2597</v>
+        <v>2595</v>
       </c>
       <c r="M37" s="40" t="s">
         <v>1429</v>
@@ -41482,19 +41479,19 @@
       <c r="F38" s="34"/>
       <c r="G38" s="34"/>
       <c r="H38" s="34" t="s">
+        <v>2596</v>
+      </c>
+      <c r="I38" s="48" t="s">
+        <v>2597</v>
+      </c>
+      <c r="J38" s="34" t="s">
         <v>2598</v>
       </c>
-      <c r="I38" s="48" t="s">
+      <c r="K38" s="34" t="s">
         <v>2599</v>
       </c>
-      <c r="J38" s="34" t="s">
+      <c r="L38" s="34" t="s">
         <v>2600</v>
-      </c>
-      <c r="K38" s="34" t="s">
-        <v>2601</v>
-      </c>
-      <c r="L38" s="34" t="s">
-        <v>2602</v>
       </c>
       <c r="M38" s="34" t="s">
         <v>1376</v>
@@ -41543,20 +41540,20 @@
       <c r="F39" s="34"/>
       <c r="G39" s="34"/>
       <c r="H39" s="34" t="s">
-        <v>2603</v>
+        <v>2601</v>
       </c>
       <c r="I39" s="48" t="s">
-        <v>2604</v>
+        <v>2602</v>
       </c>
       <c r="J39" s="34"/>
       <c r="K39" s="34" t="s">
+        <v>2603</v>
+      </c>
+      <c r="L39" s="34" t="s">
+        <v>2604</v>
+      </c>
+      <c r="M39" s="34" t="s">
         <v>2605</v>
-      </c>
-      <c r="L39" s="34" t="s">
-        <v>2606</v>
-      </c>
-      <c r="M39" s="34" t="s">
-        <v>2607</v>
       </c>
       <c r="N39" s="34"/>
       <c r="O39" s="34"/>
@@ -41602,20 +41599,20 @@
       <c r="F40" s="37"/>
       <c r="G40" s="37"/>
       <c r="H40" s="37" t="s">
-        <v>2608</v>
+        <v>2606</v>
       </c>
       <c r="I40" s="53" t="s">
-        <v>2609</v>
+        <v>2607</v>
       </c>
       <c r="J40" s="37"/>
       <c r="K40" s="37" t="s">
-        <v>2610</v>
+        <v>2608</v>
       </c>
       <c r="L40" s="37" t="s">
-        <v>2611</v>
+        <v>2609</v>
       </c>
       <c r="M40" s="37" t="s">
-        <v>2607</v>
+        <v>2605</v>
       </c>
       <c r="N40" s="37"/>
       <c r="O40" s="37"/>
@@ -41661,19 +41658,19 @@
       <c r="F41" s="76"/>
       <c r="G41" s="76"/>
       <c r="H41" s="116" t="s">
+        <v>2610</v>
+      </c>
+      <c r="I41" s="118" t="s">
+        <v>2611</v>
+      </c>
+      <c r="J41" s="116" t="s">
         <v>2612</v>
       </c>
-      <c r="I41" s="118" t="s">
+      <c r="K41" s="118" t="s">
         <v>2613</v>
       </c>
-      <c r="J41" s="116" t="s">
+      <c r="L41" s="116" t="s">
         <v>2614</v>
-      </c>
-      <c r="K41" s="118" t="s">
-        <v>2615</v>
-      </c>
-      <c r="L41" s="116" t="s">
-        <v>2616</v>
       </c>
       <c r="M41" s="170" t="s">
         <v>1446</v>
@@ -41716,22 +41713,22 @@
         <v>33</v>
       </c>
       <c r="I57" t="s">
+        <v>2615</v>
+      </c>
+      <c r="J57" t="s">
+        <v>2616</v>
+      </c>
+      <c r="K57" t="s">
         <v>2617</v>
       </c>
-      <c r="J57" t="s">
+      <c r="L57" t="s">
         <v>2618</v>
       </c>
-      <c r="K57" t="s">
+      <c r="M57" t="s">
         <v>2619</v>
       </c>
-      <c r="L57" t="s">
+      <c r="N57" t="s">
         <v>2620</v>
-      </c>
-      <c r="M57" t="s">
-        <v>2621</v>
-      </c>
-      <c r="N57" t="s">
-        <v>2622</v>
       </c>
       <c r="O57" t="s">
         <v>57</v>
@@ -41745,16 +41742,16 @@
     </row>
     <row r="58" spans="1:28" ht="15" customHeight="1">
       <c r="H58" t="s">
+        <v>2621</v>
+      </c>
+      <c r="I58" t="s">
+        <v>2622</v>
+      </c>
+      <c r="K58" t="s">
         <v>2623</v>
       </c>
-      <c r="I58" t="s">
+      <c r="L58" t="s">
         <v>2624</v>
-      </c>
-      <c r="K58" t="s">
-        <v>2625</v>
-      </c>
-      <c r="L58" t="s">
-        <v>2626</v>
       </c>
       <c r="M58" t="s">
         <v>1446</v>
@@ -41765,16 +41762,16 @@
     </row>
     <row r="59" spans="1:28" ht="15" customHeight="1">
       <c r="H59" t="s">
+        <v>2625</v>
+      </c>
+      <c r="I59" t="s">
+        <v>2626</v>
+      </c>
+      <c r="J59" t="s">
         <v>2627</v>
       </c>
-      <c r="I59" t="s">
+      <c r="L59" t="s">
         <v>2628</v>
-      </c>
-      <c r="J59" t="s">
-        <v>2629</v>
-      </c>
-      <c r="L59" t="s">
-        <v>2630</v>
       </c>
       <c r="M59" t="s">
         <v>1446</v>
@@ -41785,16 +41782,16 @@
     </row>
     <row r="60" spans="1:28" ht="15" customHeight="1">
       <c r="H60" t="s">
+        <v>2629</v>
+      </c>
+      <c r="I60" t="s">
+        <v>2630</v>
+      </c>
+      <c r="K60" t="s">
         <v>2631</v>
       </c>
-      <c r="I60" t="s">
+      <c r="L60" t="s">
         <v>2632</v>
-      </c>
-      <c r="K60" t="s">
-        <v>2633</v>
-      </c>
-      <c r="L60" t="s">
-        <v>2634</v>
       </c>
       <c r="M60" t="s">
         <v>1446</v>
@@ -41805,19 +41802,19 @@
     </row>
     <row r="61" spans="1:28" ht="15" customHeight="1">
       <c r="H61" t="s">
+        <v>2633</v>
+      </c>
+      <c r="I61" t="s">
+        <v>2634</v>
+      </c>
+      <c r="J61" t="s">
         <v>2635</v>
       </c>
-      <c r="I61" t="s">
+      <c r="K61" t="s">
         <v>2636</v>
       </c>
-      <c r="J61" t="s">
+      <c r="L61" t="s">
         <v>2637</v>
-      </c>
-      <c r="K61" t="s">
-        <v>2638</v>
-      </c>
-      <c r="L61" t="s">
-        <v>2639</v>
       </c>
       <c r="M61" t="s">
         <v>1446</v>
@@ -41828,19 +41825,19 @@
     </row>
     <row r="62" spans="1:28" ht="15" customHeight="1">
       <c r="H62" t="s">
+        <v>2638</v>
+      </c>
+      <c r="I62" t="s">
+        <v>2639</v>
+      </c>
+      <c r="J62" t="s">
         <v>2640</v>
       </c>
-      <c r="I62" t="s">
+      <c r="K62" t="s">
         <v>2641</v>
       </c>
-      <c r="J62" t="s">
+      <c r="L62" t="s">
         <v>2642</v>
-      </c>
-      <c r="K62" t="s">
-        <v>2643</v>
-      </c>
-      <c r="L62" t="s">
-        <v>2644</v>
       </c>
       <c r="M62" t="s">
         <v>1446</v>
@@ -41851,19 +41848,19 @@
     </row>
     <row r="63" spans="1:28" ht="15" customHeight="1">
       <c r="H63" t="s">
+        <v>2643</v>
+      </c>
+      <c r="I63" t="s">
+        <v>2644</v>
+      </c>
+      <c r="J63" t="s">
         <v>2645</v>
       </c>
-      <c r="I63" t="s">
+      <c r="K63" t="s">
         <v>2646</v>
       </c>
-      <c r="J63" t="s">
+      <c r="L63" t="s">
         <v>2647</v>
-      </c>
-      <c r="K63" t="s">
-        <v>2648</v>
-      </c>
-      <c r="L63" t="s">
-        <v>2649</v>
       </c>
       <c r="M63" t="s">
         <v>1446</v>
@@ -41874,19 +41871,19 @@
     </row>
     <row r="64" spans="1:28" ht="15" customHeight="1">
       <c r="H64" t="s">
+        <v>2648</v>
+      </c>
+      <c r="I64" t="s">
+        <v>2649</v>
+      </c>
+      <c r="J64" t="s">
         <v>2650</v>
       </c>
-      <c r="I64" t="s">
+      <c r="K64" t="s">
         <v>2651</v>
       </c>
-      <c r="J64" t="s">
+      <c r="L64" t="s">
         <v>2652</v>
-      </c>
-      <c r="K64" t="s">
-        <v>2653</v>
-      </c>
-      <c r="L64" t="s">
-        <v>2654</v>
       </c>
       <c r="M64" t="s">
         <v>1435</v>
@@ -41897,19 +41894,19 @@
     </row>
     <row r="65" spans="8:27" ht="15" customHeight="1">
       <c r="H65" t="s">
+        <v>2653</v>
+      </c>
+      <c r="I65" t="s">
+        <v>2654</v>
+      </c>
+      <c r="J65" t="s">
         <v>2655</v>
       </c>
-      <c r="I65" t="s">
+      <c r="K65" t="s">
         <v>2656</v>
       </c>
-      <c r="J65" t="s">
+      <c r="L65" t="s">
         <v>2657</v>
-      </c>
-      <c r="K65" t="s">
-        <v>2658</v>
-      </c>
-      <c r="L65" t="s">
-        <v>2659</v>
       </c>
       <c r="M65" t="s">
         <v>1435</v>
@@ -41920,19 +41917,19 @@
     </row>
     <row r="66" spans="8:27" ht="15" customHeight="1">
       <c r="H66" t="s">
+        <v>2658</v>
+      </c>
+      <c r="I66" t="s">
+        <v>2659</v>
+      </c>
+      <c r="J66" t="s">
         <v>2660</v>
       </c>
-      <c r="I66" t="s">
+      <c r="L66" t="s">
         <v>2661</v>
       </c>
-      <c r="J66" t="s">
+      <c r="M66" t="s">
         <v>2662</v>
-      </c>
-      <c r="L66" t="s">
-        <v>2663</v>
-      </c>
-      <c r="M66" t="s">
-        <v>2664</v>
       </c>
       <c r="O66" t="s">
         <v>1642</v>
@@ -41940,39 +41937,39 @@
     </row>
     <row r="67" spans="8:27" ht="15" customHeight="1">
       <c r="H67" t="s">
+        <v>2663</v>
+      </c>
+      <c r="I67" t="s">
+        <v>2664</v>
+      </c>
+      <c r="J67" t="s">
         <v>2665</v>
       </c>
-      <c r="I67" t="s">
+      <c r="K67" t="s">
         <v>2666</v>
       </c>
-      <c r="J67" t="s">
+      <c r="L67" t="s">
         <v>2667</v>
-      </c>
-      <c r="K67" t="s">
-        <v>2668</v>
-      </c>
-      <c r="L67" t="s">
-        <v>2669</v>
       </c>
       <c r="M67" t="s">
         <v>1910</v>
       </c>
       <c r="O67" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
     </row>
     <row r="68" spans="8:27" ht="15" customHeight="1">
       <c r="H68" t="s">
+        <v>2669</v>
+      </c>
+      <c r="I68" t="s">
+        <v>2670</v>
+      </c>
+      <c r="K68" t="s">
         <v>2671</v>
       </c>
-      <c r="I68" t="s">
+      <c r="L68" t="s">
         <v>2672</v>
-      </c>
-      <c r="K68" t="s">
-        <v>2673</v>
-      </c>
-      <c r="L68" t="s">
-        <v>2674</v>
       </c>
       <c r="M68" t="s">
         <v>1429</v>
@@ -41983,19 +41980,19 @@
     </row>
     <row r="69" spans="8:27" ht="11.5" customHeight="1">
       <c r="H69" t="s">
+        <v>2673</v>
+      </c>
+      <c r="I69" t="s">
+        <v>2674</v>
+      </c>
+      <c r="J69" t="s">
         <v>2675</v>
       </c>
-      <c r="I69" t="s">
+      <c r="K69" t="s">
+        <v>2671</v>
+      </c>
+      <c r="L69" t="s">
         <v>2676</v>
-      </c>
-      <c r="J69" t="s">
-        <v>2677</v>
-      </c>
-      <c r="K69" t="s">
-        <v>2673</v>
-      </c>
-      <c r="L69" t="s">
-        <v>2678</v>
       </c>
       <c r="M69" t="s">
         <v>1429</v>
@@ -42007,7 +42004,7 @@
         <v>2239</v>
       </c>
       <c r="Y69" t="s">
-        <v>2679</v>
+        <v>2677</v>
       </c>
       <c r="AA69" t="s">
         <v>40</v>
@@ -42015,19 +42012,19 @@
     </row>
     <row r="70" spans="8:27" ht="15" customHeight="1">
       <c r="H70" t="s">
+        <v>2678</v>
+      </c>
+      <c r="I70" t="s">
+        <v>2679</v>
+      </c>
+      <c r="K70" t="s">
         <v>2680</v>
       </c>
-      <c r="I70" t="s">
+      <c r="L70" t="s">
         <v>2681</v>
       </c>
-      <c r="K70" t="s">
+      <c r="M70" t="s">
         <v>2682</v>
-      </c>
-      <c r="L70" t="s">
-        <v>2683</v>
-      </c>
-      <c r="M70" t="s">
-        <v>2684</v>
       </c>
       <c r="O70" t="s">
         <v>1642</v>
@@ -42035,16 +42032,16 @@
     </row>
     <row r="71" spans="8:27" ht="15" customHeight="1">
       <c r="H71" t="s">
+        <v>2683</v>
+      </c>
+      <c r="I71" t="s">
+        <v>2684</v>
+      </c>
+      <c r="K71" t="s">
         <v>2685</v>
       </c>
-      <c r="I71" t="s">
+      <c r="L71" t="s">
         <v>2686</v>
-      </c>
-      <c r="K71" t="s">
-        <v>2687</v>
-      </c>
-      <c r="L71" t="s">
-        <v>2688</v>
       </c>
       <c r="M71" t="s">
         <v>1756</v>
@@ -42055,19 +42052,19 @@
     </row>
     <row r="72" spans="8:27" ht="15" customHeight="1">
       <c r="H72" t="s">
+        <v>2687</v>
+      </c>
+      <c r="I72" t="s">
+        <v>2688</v>
+      </c>
+      <c r="J72" t="s">
         <v>2689</v>
       </c>
-      <c r="I72" t="s">
+      <c r="K72" t="s">
         <v>2690</v>
       </c>
-      <c r="J72" t="s">
+      <c r="L72" t="s">
         <v>2691</v>
-      </c>
-      <c r="K72" t="s">
-        <v>2692</v>
-      </c>
-      <c r="L72" t="s">
-        <v>2693</v>
       </c>
       <c r="M72" t="s">
         <v>1756</v>
@@ -42078,82 +42075,82 @@
     </row>
     <row r="73" spans="8:27" ht="15" customHeight="1">
       <c r="H73" t="s">
+        <v>2692</v>
+      </c>
+      <c r="I73" t="s">
+        <v>2693</v>
+      </c>
+      <c r="J73" t="s">
         <v>2694</v>
       </c>
-      <c r="I73" t="s">
+      <c r="K73" t="s">
         <v>2695</v>
       </c>
-      <c r="J73" t="s">
+      <c r="L73" t="s">
         <v>2696</v>
-      </c>
-      <c r="K73" t="s">
-        <v>2697</v>
-      </c>
-      <c r="L73" t="s">
-        <v>2698</v>
       </c>
       <c r="M73" t="s">
         <v>1689</v>
       </c>
       <c r="O73" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
     </row>
     <row r="74" spans="8:27" ht="15" customHeight="1">
       <c r="H74" t="s">
+        <v>2697</v>
+      </c>
+      <c r="I74" t="s">
+        <v>2698</v>
+      </c>
+      <c r="J74" t="s">
         <v>2699</v>
       </c>
-      <c r="I74" t="s">
+      <c r="L74" t="s">
         <v>2700</v>
       </c>
-      <c r="J74" t="s">
+      <c r="M74" t="s">
         <v>2701</v>
       </c>
-      <c r="L74" t="s">
-        <v>2702</v>
-      </c>
-      <c r="M74" t="s">
-        <v>2703</v>
-      </c>
       <c r="O74" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
     </row>
     <row r="75" spans="8:27" ht="15" customHeight="1">
       <c r="H75" t="s">
+        <v>2702</v>
+      </c>
+      <c r="I75" t="s">
+        <v>2703</v>
+      </c>
+      <c r="K75" t="s">
         <v>2704</v>
       </c>
-      <c r="I75" t="s">
+      <c r="L75" t="s">
         <v>2705</v>
       </c>
-      <c r="K75" t="s">
+      <c r="M75" t="s">
         <v>2706</v>
       </c>
-      <c r="L75" t="s">
-        <v>2707</v>
-      </c>
-      <c r="M75" t="s">
-        <v>2708</v>
-      </c>
       <c r="O75" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
     </row>
     <row r="76" spans="8:27" ht="15" customHeight="1">
       <c r="H76" t="s">
+        <v>2707</v>
+      </c>
+      <c r="I76" t="s">
+        <v>2708</v>
+      </c>
+      <c r="K76" t="s">
         <v>2709</v>
       </c>
-      <c r="I76" t="s">
+      <c r="L76" t="s">
         <v>2710</v>
       </c>
-      <c r="K76" t="s">
+      <c r="M76" t="s">
         <v>2711</v>
-      </c>
-      <c r="L76" t="s">
-        <v>2712</v>
-      </c>
-      <c r="M76" t="s">
-        <v>2713</v>
       </c>
       <c r="O76" t="s">
         <v>1642</v>
@@ -42161,22 +42158,22 @@
     </row>
     <row r="77" spans="8:27" ht="15" customHeight="1">
       <c r="H77" t="s">
+        <v>2712</v>
+      </c>
+      <c r="I77" t="s">
+        <v>2713</v>
+      </c>
+      <c r="J77" t="s">
         <v>2714</v>
       </c>
-      <c r="I77" t="s">
+      <c r="K77" t="s">
         <v>2715</v>
       </c>
-      <c r="J77" t="s">
+      <c r="L77" t="s">
         <v>2716</v>
       </c>
-      <c r="K77" t="s">
+      <c r="M77" t="s">
         <v>2717</v>
-      </c>
-      <c r="L77" t="s">
-        <v>2718</v>
-      </c>
-      <c r="M77" t="s">
-        <v>2719</v>
       </c>
       <c r="O77" t="s">
         <v>1642</v>
@@ -42184,22 +42181,22 @@
     </row>
     <row r="78" spans="8:27" ht="15" customHeight="1">
       <c r="H78" t="s">
+        <v>2718</v>
+      </c>
+      <c r="I78" t="s">
+        <v>2719</v>
+      </c>
+      <c r="J78" t="s">
         <v>2720</v>
       </c>
-      <c r="I78" t="s">
+      <c r="K78" t="s">
         <v>2721</v>
       </c>
-      <c r="J78" t="s">
+      <c r="L78" t="s">
         <v>2722</v>
       </c>
-      <c r="K78" t="s">
-        <v>2723</v>
-      </c>
-      <c r="L78" t="s">
-        <v>2724</v>
-      </c>
       <c r="M78" t="s">
-        <v>2703</v>
+        <v>2701</v>
       </c>
       <c r="O78" t="s">
         <v>1642</v>
@@ -42207,19 +42204,19 @@
     </row>
     <row r="79" spans="8:27" ht="15" customHeight="1">
       <c r="H79" t="s">
+        <v>2723</v>
+      </c>
+      <c r="I79" t="s">
+        <v>2724</v>
+      </c>
+      <c r="J79" t="s">
         <v>2725</v>
       </c>
-      <c r="I79" t="s">
+      <c r="K79" t="s">
         <v>2726</v>
       </c>
-      <c r="J79" t="s">
+      <c r="L79" t="s">
         <v>2727</v>
-      </c>
-      <c r="K79" t="s">
-        <v>2728</v>
-      </c>
-      <c r="L79" t="s">
-        <v>2729</v>
       </c>
       <c r="M79" t="s">
         <v>2220</v>
@@ -42230,19 +42227,19 @@
     </row>
     <row r="80" spans="8:27" ht="15" customHeight="1">
       <c r="H80" t="s">
+        <v>2728</v>
+      </c>
+      <c r="I80" t="s">
+        <v>2729</v>
+      </c>
+      <c r="K80" t="s">
         <v>2730</v>
       </c>
-      <c r="I80" t="s">
+      <c r="L80" t="s">
         <v>2731</v>
       </c>
-      <c r="K80" t="s">
+      <c r="M80" t="s">
         <v>2732</v>
-      </c>
-      <c r="L80" t="s">
-        <v>2733</v>
-      </c>
-      <c r="M80" t="s">
-        <v>2734</v>
       </c>
       <c r="O80" t="s">
         <v>1642</v>
@@ -42262,7 +42259,7 @@
         <v>2295</v>
       </c>
       <c r="L81" t="s">
-        <v>2735</v>
+        <v>2733</v>
       </c>
       <c r="M81" t="s">
         <v>1446</v>
@@ -42282,19 +42279,19 @@
     </row>
     <row r="82" spans="8:27" ht="15" customHeight="1">
       <c r="H82" t="s">
+        <v>2734</v>
+      </c>
+      <c r="I82" t="s">
+        <v>2649</v>
+      </c>
+      <c r="J82" t="s">
+        <v>2735</v>
+      </c>
+      <c r="K82" t="s">
+        <v>2651</v>
+      </c>
+      <c r="L82" t="s">
         <v>2736</v>
-      </c>
-      <c r="I82" t="s">
-        <v>2651</v>
-      </c>
-      <c r="J82" t="s">
-        <v>2737</v>
-      </c>
-      <c r="K82" t="s">
-        <v>2653</v>
-      </c>
-      <c r="L82" t="s">
-        <v>2738</v>
       </c>
       <c r="M82" t="s">
         <v>1435</v>
@@ -42303,10 +42300,10 @@
         <v>1642</v>
       </c>
       <c r="X82" t="s">
-        <v>2739</v>
+        <v>2737</v>
       </c>
       <c r="Y82" t="s">
-        <v>2740</v>
+        <v>2738</v>
       </c>
       <c r="AA82" t="s">
         <v>40</v>
@@ -42314,19 +42311,19 @@
     </row>
     <row r="83" spans="8:27" ht="15" customHeight="1">
       <c r="H83" t="s">
+        <v>2739</v>
+      </c>
+      <c r="I83" t="s">
+        <v>2740</v>
+      </c>
+      <c r="J83" t="s">
         <v>2741</v>
       </c>
-      <c r="I83" t="s">
+      <c r="K83" t="s">
         <v>2742</v>
       </c>
-      <c r="J83" t="s">
+      <c r="L83" t="s">
         <v>2743</v>
-      </c>
-      <c r="K83" t="s">
-        <v>2744</v>
-      </c>
-      <c r="L83" t="s">
-        <v>2745</v>
       </c>
       <c r="M83" t="s">
         <v>1435</v>
@@ -42335,10 +42332,10 @@
         <v>1642</v>
       </c>
       <c r="X83" t="s">
-        <v>2746</v>
+        <v>2744</v>
       </c>
       <c r="Y83" t="s">
-        <v>2747</v>
+        <v>2745</v>
       </c>
       <c r="AA83" t="s">
         <v>50</v>
@@ -42346,19 +42343,19 @@
     </row>
     <row r="84" spans="8:27" ht="15" customHeight="1">
       <c r="H84" t="s">
+        <v>2746</v>
+      </c>
+      <c r="I84" t="s">
+        <v>2747</v>
+      </c>
+      <c r="J84" t="s">
         <v>2748</v>
       </c>
-      <c r="I84" t="s">
+      <c r="K84" t="s">
         <v>2749</v>
       </c>
-      <c r="J84" t="s">
+      <c r="L84" t="s">
         <v>2750</v>
-      </c>
-      <c r="K84" t="s">
-        <v>2751</v>
-      </c>
-      <c r="L84" t="s">
-        <v>2752</v>
       </c>
       <c r="M84" t="s">
         <v>1435</v>
@@ -42367,10 +42364,10 @@
         <v>1642</v>
       </c>
       <c r="X84" t="s">
-        <v>2753</v>
+        <v>2751</v>
       </c>
       <c r="Y84" t="s">
-        <v>2754</v>
+        <v>2752</v>
       </c>
       <c r="AA84" t="s">
         <v>40</v>
@@ -42378,31 +42375,31 @@
     </row>
     <row r="85" spans="8:27" ht="15" customHeight="1">
       <c r="H85" t="s">
+        <v>2753</v>
+      </c>
+      <c r="I85" t="s">
+        <v>2754</v>
+      </c>
+      <c r="J85" t="s">
         <v>2755</v>
       </c>
-      <c r="I85" t="s">
+      <c r="K85" t="s">
         <v>2756</v>
       </c>
-      <c r="J85" t="s">
+      <c r="L85" t="s">
         <v>2757</v>
-      </c>
-      <c r="K85" t="s">
-        <v>2758</v>
-      </c>
-      <c r="L85" t="s">
-        <v>2759</v>
       </c>
       <c r="M85" t="s">
         <v>1435</v>
       </c>
       <c r="O85" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="X85" t="s">
-        <v>2760</v>
+        <v>2758</v>
       </c>
       <c r="Y85" t="s">
-        <v>2761</v>
+        <v>2759</v>
       </c>
       <c r="AA85" t="s">
         <v>40</v>
@@ -42410,19 +42407,19 @@
     </row>
     <row r="86" spans="8:27" ht="15" customHeight="1">
       <c r="H86" t="s">
+        <v>2760</v>
+      </c>
+      <c r="I86" t="s">
+        <v>2761</v>
+      </c>
+      <c r="J86" t="s">
         <v>2762</v>
       </c>
-      <c r="I86" t="s">
+      <c r="K86" t="s">
         <v>2763</v>
       </c>
-      <c r="J86" t="s">
+      <c r="L86" t="s">
         <v>2764</v>
-      </c>
-      <c r="K86" t="s">
-        <v>2765</v>
-      </c>
-      <c r="L86" t="s">
-        <v>2766</v>
       </c>
       <c r="M86" t="s">
         <v>1435</v>
@@ -42431,10 +42428,10 @@
         <v>1642</v>
       </c>
       <c r="X86" t="s">
-        <v>2767</v>
+        <v>2765</v>
       </c>
       <c r="Y86" t="s">
-        <v>2768</v>
+        <v>2766</v>
       </c>
       <c r="AA86" t="s">
         <v>50</v>
@@ -42442,19 +42439,19 @@
     </row>
     <row r="87" spans="8:27" ht="15" customHeight="1">
       <c r="H87" t="s">
+        <v>2767</v>
+      </c>
+      <c r="I87" t="s">
+        <v>2768</v>
+      </c>
+      <c r="J87" t="s">
         <v>2769</v>
       </c>
-      <c r="I87" t="s">
+      <c r="K87" t="s">
         <v>2770</v>
       </c>
-      <c r="J87" t="s">
+      <c r="L87" t="s">
         <v>2771</v>
-      </c>
-      <c r="K87" t="s">
-        <v>2772</v>
-      </c>
-      <c r="L87" t="s">
-        <v>2773</v>
       </c>
       <c r="M87" t="s">
         <v>1435</v>
@@ -42463,10 +42460,10 @@
         <v>1642</v>
       </c>
       <c r="X87" t="s">
-        <v>2774</v>
+        <v>2772</v>
       </c>
       <c r="Y87" t="s">
-        <v>2775</v>
+        <v>2773</v>
       </c>
       <c r="AA87" t="s">
         <v>40</v>
@@ -42474,31 +42471,31 @@
     </row>
     <row r="88" spans="8:27" ht="15" customHeight="1">
       <c r="H88" t="s">
-        <v>2640</v>
+        <v>2638</v>
       </c>
       <c r="I88" t="s">
+        <v>2639</v>
+      </c>
+      <c r="J88" t="s">
+        <v>2774</v>
+      </c>
+      <c r="K88" t="s">
         <v>2641</v>
       </c>
-      <c r="J88" t="s">
-        <v>2776</v>
-      </c>
-      <c r="K88" t="s">
-        <v>2643</v>
-      </c>
       <c r="L88" t="s">
-        <v>2777</v>
+        <v>2775</v>
       </c>
       <c r="M88" t="s">
         <v>1446</v>
       </c>
       <c r="O88" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="X88" t="s">
-        <v>2778</v>
+        <v>2776</v>
       </c>
       <c r="Y88" t="s">
-        <v>2779</v>
+        <v>2777</v>
       </c>
       <c r="AA88" t="s">
         <v>40</v>
@@ -42506,31 +42503,31 @@
     </row>
     <row r="89" spans="8:27" ht="15" customHeight="1">
       <c r="H89" t="s">
-        <v>2780</v>
+        <v>2778</v>
       </c>
       <c r="I89" t="s">
+        <v>2644</v>
+      </c>
+      <c r="J89" t="s">
+        <v>2645</v>
+      </c>
+      <c r="K89" t="s">
         <v>2646</v>
       </c>
-      <c r="J89" t="s">
-        <v>2647</v>
-      </c>
-      <c r="K89" t="s">
-        <v>2648</v>
-      </c>
       <c r="L89" t="s">
-        <v>2781</v>
+        <v>2779</v>
       </c>
       <c r="M89" t="s">
         <v>1446</v>
       </c>
       <c r="O89" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="X89" t="s">
-        <v>2782</v>
+        <v>2780</v>
       </c>
       <c r="Y89" t="s">
-        <v>2783</v>
+        <v>2781</v>
       </c>
       <c r="AA89" t="s">
         <v>40</v>
@@ -42538,16 +42535,16 @@
     </row>
     <row r="90" spans="8:27" ht="15" customHeight="1">
       <c r="H90" t="s">
+        <v>2707</v>
+      </c>
+      <c r="I90" t="s">
+        <v>2782</v>
+      </c>
+      <c r="K90" t="s">
         <v>2709</v>
       </c>
-      <c r="I90" t="s">
-        <v>2784</v>
-      </c>
-      <c r="K90" t="s">
-        <v>2711</v>
-      </c>
       <c r="L90" t="s">
-        <v>2785</v>
+        <v>2783</v>
       </c>
       <c r="M90" t="s">
         <v>1446</v>
@@ -42561,31 +42558,31 @@
     </row>
     <row r="91" spans="8:27" ht="15" customHeight="1">
       <c r="H91" t="s">
+        <v>2784</v>
+      </c>
+      <c r="I91" t="s">
+        <v>2785</v>
+      </c>
+      <c r="J91" t="s">
         <v>2786</v>
       </c>
-      <c r="I91" t="s">
+      <c r="K91" t="s">
         <v>2787</v>
       </c>
-      <c r="J91" t="s">
+      <c r="L91" t="s">
         <v>2788</v>
-      </c>
-      <c r="K91" t="s">
-        <v>2789</v>
-      </c>
-      <c r="L91" t="s">
-        <v>2790</v>
       </c>
       <c r="M91" t="s">
         <v>1446</v>
       </c>
       <c r="O91" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="X91" t="s">
-        <v>2791</v>
+        <v>2789</v>
       </c>
       <c r="Y91" t="s">
-        <v>2792</v>
+        <v>2790</v>
       </c>
       <c r="AA91" t="s">
         <v>40</v>
@@ -42593,19 +42590,19 @@
     </row>
     <row r="92" spans="8:27" ht="15" customHeight="1">
       <c r="H92" t="s">
+        <v>2633</v>
+      </c>
+      <c r="I92" t="s">
+        <v>2634</v>
+      </c>
+      <c r="J92" t="s">
         <v>2635</v>
       </c>
-      <c r="I92" t="s">
+      <c r="K92" t="s">
         <v>2636</v>
       </c>
-      <c r="J92" t="s">
-        <v>2637</v>
-      </c>
-      <c r="K92" t="s">
-        <v>2638</v>
-      </c>
       <c r="L92" t="s">
-        <v>2793</v>
+        <v>2791</v>
       </c>
       <c r="M92" t="s">
         <v>1446</v>
@@ -42614,10 +42611,10 @@
         <v>1642</v>
       </c>
       <c r="X92" t="s">
-        <v>2794</v>
+        <v>2792</v>
       </c>
       <c r="Y92" t="s">
-        <v>2795</v>
+        <v>2793</v>
       </c>
       <c r="AA92" t="s">
         <v>40</v>
@@ -42625,16 +42622,16 @@
     </row>
     <row r="93" spans="8:27" ht="15" customHeight="1">
       <c r="H93" t="s">
+        <v>2629</v>
+      </c>
+      <c r="I93" t="s">
+        <v>2630</v>
+      </c>
+      <c r="K93" t="s">
         <v>2631</v>
       </c>
-      <c r="I93" t="s">
-        <v>2632</v>
-      </c>
-      <c r="K93" t="s">
-        <v>2633</v>
-      </c>
       <c r="L93" t="s">
-        <v>2796</v>
+        <v>2794</v>
       </c>
       <c r="M93" t="s">
         <v>1446</v>
@@ -42648,19 +42645,19 @@
     </row>
     <row r="94" spans="8:27" ht="15" customHeight="1">
       <c r="H94" t="s">
+        <v>2795</v>
+      </c>
+      <c r="I94" t="s">
+        <v>2796</v>
+      </c>
+      <c r="J94" t="s">
+        <v>2795</v>
+      </c>
+      <c r="K94" t="s">
         <v>2797</v>
       </c>
-      <c r="I94" t="s">
+      <c r="L94" t="s">
         <v>2798</v>
-      </c>
-      <c r="J94" t="s">
-        <v>2797</v>
-      </c>
-      <c r="K94" t="s">
-        <v>2799</v>
-      </c>
-      <c r="L94" t="s">
-        <v>2800</v>
       </c>
       <c r="M94" t="s">
         <v>1446</v>
@@ -42669,10 +42666,10 @@
         <v>1642</v>
       </c>
       <c r="X94" t="s">
-        <v>2801</v>
+        <v>2799</v>
       </c>
       <c r="Y94" t="s">
-        <v>2802</v>
+        <v>2800</v>
       </c>
       <c r="AA94" t="s">
         <v>40</v>
@@ -42680,16 +42677,16 @@
     </row>
     <row r="95" spans="8:27" ht="15" customHeight="1">
       <c r="H95" t="s">
+        <v>2801</v>
+      </c>
+      <c r="I95" t="s">
+        <v>2802</v>
+      </c>
+      <c r="K95" t="s">
         <v>2803</v>
       </c>
-      <c r="I95" t="s">
+      <c r="L95" t="s">
         <v>2804</v>
-      </c>
-      <c r="K95" t="s">
-        <v>2805</v>
-      </c>
-      <c r="L95" t="s">
-        <v>2806</v>
       </c>
       <c r="M95" t="s">
         <v>1446</v>
@@ -42703,16 +42700,16 @@
     </row>
     <row r="96" spans="8:27" ht="15" customHeight="1">
       <c r="H96" t="s">
+        <v>2805</v>
+      </c>
+      <c r="I96" t="s">
+        <v>2806</v>
+      </c>
+      <c r="K96" t="s">
         <v>2807</v>
       </c>
-      <c r="I96" t="s">
+      <c r="L96" t="s">
         <v>2808</v>
-      </c>
-      <c r="K96" t="s">
-        <v>2809</v>
-      </c>
-      <c r="L96" t="s">
-        <v>2810</v>
       </c>
       <c r="M96" t="s">
         <v>1446</v>
@@ -42726,16 +42723,16 @@
     </row>
     <row r="97" spans="8:27" ht="15" customHeight="1">
       <c r="H97" t="s">
+        <v>2809</v>
+      </c>
+      <c r="I97" t="s">
+        <v>2810</v>
+      </c>
+      <c r="J97" t="s">
         <v>2811</v>
       </c>
-      <c r="I97" t="s">
+      <c r="L97" t="s">
         <v>2812</v>
-      </c>
-      <c r="J97" t="s">
-        <v>2813</v>
-      </c>
-      <c r="L97" t="s">
-        <v>2814</v>
       </c>
       <c r="M97" t="s">
         <v>1446</v>
@@ -42744,10 +42741,10 @@
         <v>1642</v>
       </c>
       <c r="X97" t="s">
-        <v>2815</v>
+        <v>2813</v>
       </c>
       <c r="Y97" t="s">
-        <v>2816</v>
+        <v>2814</v>
       </c>
       <c r="AA97" t="s">
         <v>40</v>
@@ -42755,16 +42752,16 @@
     </row>
     <row r="98" spans="8:27" ht="15" customHeight="1">
       <c r="H98" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="I98" t="s">
-        <v>2628</v>
+        <v>2626</v>
       </c>
       <c r="J98" t="s">
-        <v>2817</v>
+        <v>2815</v>
       </c>
       <c r="L98" t="s">
-        <v>2818</v>
+        <v>2816</v>
       </c>
       <c r="M98" t="s">
         <v>1446</v>
@@ -42773,10 +42770,10 @@
         <v>1642</v>
       </c>
       <c r="X98" t="s">
-        <v>2819</v>
+        <v>2817</v>
       </c>
       <c r="Y98" t="s">
-        <v>2820</v>
+        <v>2818</v>
       </c>
       <c r="AA98" t="s">
         <v>40</v>
@@ -42784,31 +42781,31 @@
     </row>
     <row r="99" spans="8:27" ht="11.5" customHeight="1">
       <c r="H99" t="s">
+        <v>2819</v>
+      </c>
+      <c r="I99" t="s">
+        <v>2820</v>
+      </c>
+      <c r="J99" t="s">
         <v>2821</v>
       </c>
-      <c r="I99" t="s">
+      <c r="K99" t="s">
         <v>2822</v>
       </c>
-      <c r="J99" t="s">
+      <c r="L99" t="s">
         <v>2823</v>
       </c>
-      <c r="K99" t="s">
+      <c r="M99" t="s">
         <v>2824</v>
-      </c>
-      <c r="L99" t="s">
-        <v>2825</v>
-      </c>
-      <c r="M99" t="s">
-        <v>2826</v>
       </c>
       <c r="O99" t="s">
         <v>1642</v>
       </c>
       <c r="X99" t="s">
-        <v>2791</v>
+        <v>2789</v>
       </c>
       <c r="Y99" t="s">
-        <v>2827</v>
+        <v>2825</v>
       </c>
       <c r="AA99" t="s">
         <v>40</v>
@@ -42816,19 +42813,19 @@
     </row>
     <row r="100" spans="8:27" ht="11.5" customHeight="1">
       <c r="H100" t="s">
+        <v>2826</v>
+      </c>
+      <c r="I100" t="s">
+        <v>2827</v>
+      </c>
+      <c r="K100" t="s">
         <v>2828</v>
       </c>
-      <c r="I100" t="s">
+      <c r="L100" t="s">
         <v>2829</v>
       </c>
-      <c r="K100" t="s">
+      <c r="M100" t="s">
         <v>2830</v>
-      </c>
-      <c r="L100" t="s">
-        <v>2831</v>
-      </c>
-      <c r="M100" t="s">
-        <v>2832</v>
       </c>
       <c r="O100" t="s">
         <v>1642</v>
@@ -42839,16 +42836,16 @@
     </row>
     <row r="101" spans="8:27" ht="11.5" customHeight="1">
       <c r="H101" t="s">
+        <v>2831</v>
+      </c>
+      <c r="I101" t="s">
+        <v>2832</v>
+      </c>
+      <c r="L101" t="s">
         <v>2833</v>
       </c>
-      <c r="I101" t="s">
+      <c r="M101" t="s">
         <v>2834</v>
-      </c>
-      <c r="L101" t="s">
-        <v>2835</v>
-      </c>
-      <c r="M101" t="s">
-        <v>2836</v>
       </c>
       <c r="O101" t="s">
         <v>1642</v>
@@ -42859,19 +42856,19 @@
     </row>
     <row r="102" spans="8:27" ht="11.5" customHeight="1">
       <c r="H102" t="s">
+        <v>2835</v>
+      </c>
+      <c r="I102" t="s">
+        <v>2836</v>
+      </c>
+      <c r="K102" t="s">
         <v>2837</v>
       </c>
-      <c r="I102" t="s">
+      <c r="L102" t="s">
         <v>2838</v>
       </c>
-      <c r="K102" t="s">
+      <c r="M102" t="s">
         <v>2839</v>
-      </c>
-      <c r="L102" t="s">
-        <v>2840</v>
-      </c>
-      <c r="M102" t="s">
-        <v>2841</v>
       </c>
       <c r="O102" t="s">
         <v>1642</v>
@@ -42882,19 +42879,19 @@
     </row>
     <row r="103" spans="8:27" ht="11.5" customHeight="1">
       <c r="H103" t="s">
-        <v>2534</v>
+        <v>2532</v>
       </c>
       <c r="I103" t="s">
+        <v>2840</v>
+      </c>
+      <c r="K103" t="s">
+        <v>2841</v>
+      </c>
+      <c r="L103" t="s">
         <v>2842</v>
       </c>
-      <c r="K103" t="s">
+      <c r="M103" t="s">
         <v>2843</v>
-      </c>
-      <c r="L103" t="s">
-        <v>2844</v>
-      </c>
-      <c r="M103" t="s">
-        <v>2845</v>
       </c>
       <c r="O103" t="s">
         <v>1642</v>
@@ -42905,16 +42902,16 @@
     </row>
     <row r="104" spans="8:27" ht="15" customHeight="1">
       <c r="H104" t="s">
+        <v>2844</v>
+      </c>
+      <c r="I104" t="s">
+        <v>2845</v>
+      </c>
+      <c r="L104" t="s">
         <v>2846</v>
       </c>
-      <c r="I104" t="s">
+      <c r="M104" t="s">
         <v>2847</v>
-      </c>
-      <c r="L104" t="s">
-        <v>2848</v>
-      </c>
-      <c r="M104" t="s">
-        <v>2849</v>
       </c>
       <c r="O104" t="s">
         <v>1642</v>
@@ -42925,19 +42922,19 @@
     </row>
     <row r="105" spans="8:27" ht="15" customHeight="1">
       <c r="H105" t="s">
-        <v>2675</v>
+        <v>2673</v>
       </c>
       <c r="I105" t="s">
-        <v>2672</v>
+        <v>2670</v>
       </c>
       <c r="K105" t="s">
-        <v>2673</v>
+        <v>2671</v>
       </c>
       <c r="L105" t="s">
-        <v>2850</v>
+        <v>2848</v>
       </c>
       <c r="M105" t="s">
-        <v>2851</v>
+        <v>2849</v>
       </c>
       <c r="O105" t="s">
         <v>1642</v>
@@ -42948,16 +42945,16 @@
     </row>
     <row r="106" spans="8:27" ht="15" customHeight="1">
       <c r="H106" t="s">
+        <v>2850</v>
+      </c>
+      <c r="I106" t="s">
+        <v>2851</v>
+      </c>
+      <c r="L106" t="s">
         <v>2852</v>
       </c>
-      <c r="I106" t="s">
+      <c r="M106" t="s">
         <v>2853</v>
-      </c>
-      <c r="L106" t="s">
-        <v>2854</v>
-      </c>
-      <c r="M106" t="s">
-        <v>2855</v>
       </c>
       <c r="O106" t="s">
         <v>1642</v>
@@ -42968,22 +42965,22 @@
     </row>
     <row r="107" spans="8:27" ht="15" customHeight="1">
       <c r="H107" t="s">
+        <v>2854</v>
+      </c>
+      <c r="I107" t="s">
+        <v>2855</v>
+      </c>
+      <c r="J107" t="s">
         <v>2856</v>
       </c>
-      <c r="I107" t="s">
+      <c r="K107" t="s">
         <v>2857</v>
       </c>
-      <c r="J107" t="s">
+      <c r="L107" t="s">
         <v>2858</v>
       </c>
-      <c r="K107" t="s">
-        <v>2859</v>
-      </c>
-      <c r="L107" t="s">
-        <v>2860</v>
-      </c>
       <c r="M107" t="s">
-        <v>2703</v>
+        <v>2701</v>
       </c>
       <c r="O107" t="s">
         <v>1642</v>
@@ -42992,7 +42989,7 @@
         <v>1945</v>
       </c>
       <c r="Y107" t="s">
-        <v>2861</v>
+        <v>2859</v>
       </c>
       <c r="AA107" t="s">
         <v>40</v>
@@ -43000,16 +42997,16 @@
     </row>
     <row r="108" spans="8:27" ht="15" customHeight="1">
       <c r="H108" t="s">
+        <v>2860</v>
+      </c>
+      <c r="I108" t="s">
+        <v>2861</v>
+      </c>
+      <c r="L108" t="s">
         <v>2862</v>
       </c>
-      <c r="I108" t="s">
+      <c r="M108" t="s">
         <v>2863</v>
-      </c>
-      <c r="L108" t="s">
-        <v>2864</v>
-      </c>
-      <c r="M108" t="s">
-        <v>2865</v>
       </c>
       <c r="O108" t="s">
         <v>1642</v>
@@ -43020,16 +43017,16 @@
     </row>
     <row r="109" spans="8:27" ht="15" customHeight="1">
       <c r="H109" t="s">
+        <v>2864</v>
+      </c>
+      <c r="I109" t="s">
+        <v>2865</v>
+      </c>
+      <c r="L109" t="s">
         <v>2866</v>
       </c>
-      <c r="I109" t="s">
-        <v>2867</v>
-      </c>
-      <c r="L109" t="s">
-        <v>2868</v>
-      </c>
       <c r="M109" t="s">
-        <v>2703</v>
+        <v>2701</v>
       </c>
       <c r="O109" t="s">
         <v>1642</v>
@@ -43040,22 +43037,22 @@
     </row>
     <row r="110" spans="8:27" ht="15" customHeight="1">
       <c r="H110" t="s">
+        <v>2867</v>
+      </c>
+      <c r="I110" t="s">
+        <v>2868</v>
+      </c>
+      <c r="K110" t="s">
         <v>2869</v>
       </c>
-      <c r="I110" t="s">
+      <c r="L110" t="s">
         <v>2870</v>
       </c>
-      <c r="K110" t="s">
-        <v>2871</v>
-      </c>
-      <c r="L110" t="s">
-        <v>2872</v>
-      </c>
       <c r="M110" t="s">
-        <v>2703</v>
+        <v>2701</v>
       </c>
       <c r="O110" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="AA110" t="s">
         <v>40</v>
@@ -43063,31 +43060,31 @@
     </row>
     <row r="111" spans="8:27" ht="15" customHeight="1">
       <c r="H111" t="s">
+        <v>2663</v>
+      </c>
+      <c r="I111" t="s">
+        <v>2664</v>
+      </c>
+      <c r="J111" t="s">
         <v>2665</v>
       </c>
-      <c r="I111" t="s">
+      <c r="K111" t="s">
         <v>2666</v>
       </c>
-      <c r="J111" t="s">
-        <v>2667</v>
-      </c>
-      <c r="K111" t="s">
-        <v>2668</v>
-      </c>
       <c r="L111" t="s">
-        <v>2873</v>
+        <v>2871</v>
       </c>
       <c r="M111" t="s">
         <v>1910</v>
       </c>
       <c r="O111" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="X111" t="s">
-        <v>2874</v>
+        <v>2872</v>
       </c>
       <c r="Y111" t="s">
-        <v>2875</v>
+        <v>2873</v>
       </c>
       <c r="AA111" t="s">
         <v>40</v>
@@ -43095,19 +43092,19 @@
     </row>
     <row r="112" spans="8:27" ht="15" customHeight="1">
       <c r="H112" t="s">
+        <v>2874</v>
+      </c>
+      <c r="I112" t="s">
+        <v>2875</v>
+      </c>
+      <c r="L112" t="s">
         <v>2876</v>
       </c>
-      <c r="I112" t="s">
-        <v>2877</v>
-      </c>
-      <c r="L112" t="s">
-        <v>2878</v>
-      </c>
       <c r="M112" t="s">
-        <v>2703</v>
+        <v>2701</v>
       </c>
       <c r="O112" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="AA112" t="s">
         <v>40</v>
@@ -43115,22 +43112,22 @@
     </row>
     <row r="113" spans="8:27" ht="15" customHeight="1">
       <c r="H113" t="s">
+        <v>2877</v>
+      </c>
+      <c r="I113" t="s">
+        <v>2878</v>
+      </c>
+      <c r="K113" t="s">
         <v>2879</v>
       </c>
-      <c r="I113" t="s">
+      <c r="L113" t="s">
         <v>2880</v>
       </c>
-      <c r="K113" t="s">
+      <c r="M113" t="s">
         <v>2881</v>
       </c>
-      <c r="L113" t="s">
-        <v>2882</v>
-      </c>
-      <c r="M113" t="s">
-        <v>2883</v>
-      </c>
       <c r="O113" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="AA113" t="s">
         <v>50</v>
@@ -43138,16 +43135,16 @@
     </row>
     <row r="114" spans="8:27" ht="11.5" customHeight="1">
       <c r="H114" t="s">
+        <v>2882</v>
+      </c>
+      <c r="I114" t="s">
+        <v>2883</v>
+      </c>
+      <c r="K114" t="s">
         <v>2884</v>
       </c>
-      <c r="I114" t="s">
+      <c r="L114" t="s">
         <v>2885</v>
-      </c>
-      <c r="K114" t="s">
-        <v>2886</v>
-      </c>
-      <c r="L114" t="s">
-        <v>2887</v>
       </c>
       <c r="M114" t="s">
         <v>1910</v>
@@ -43161,16 +43158,16 @@
     </row>
     <row r="115" spans="8:27" ht="11.5" customHeight="1">
       <c r="H115" t="s">
+        <v>2886</v>
+      </c>
+      <c r="I115" t="s">
+        <v>2887</v>
+      </c>
+      <c r="K115" t="s">
         <v>2888</v>
       </c>
-      <c r="I115" t="s">
+      <c r="L115" t="s">
         <v>2889</v>
-      </c>
-      <c r="K115" t="s">
-        <v>2890</v>
-      </c>
-      <c r="L115" t="s">
-        <v>2891</v>
       </c>
       <c r="M115" t="s">
         <v>1910</v>
@@ -43184,31 +43181,31 @@
     </row>
     <row r="116" spans="8:27" ht="11.5" customHeight="1">
       <c r="H116" t="s">
+        <v>2890</v>
+      </c>
+      <c r="I116" t="s">
+        <v>2891</v>
+      </c>
+      <c r="J116" t="s">
         <v>2892</v>
       </c>
-      <c r="I116" t="s">
+      <c r="K116" t="s">
         <v>2893</v>
       </c>
-      <c r="J116" t="s">
+      <c r="L116" t="s">
         <v>2894</v>
       </c>
-      <c r="K116" t="s">
+      <c r="M116" t="s">
         <v>2895</v>
-      </c>
-      <c r="L116" t="s">
-        <v>2896</v>
-      </c>
-      <c r="M116" t="s">
-        <v>2897</v>
       </c>
       <c r="O116" t="s">
         <v>1642</v>
       </c>
       <c r="X116" t="s">
-        <v>2898</v>
+        <v>2896</v>
       </c>
       <c r="Y116" t="s">
-        <v>2899</v>
+        <v>2897</v>
       </c>
       <c r="AA116" t="s">
         <v>40</v>
@@ -43216,31 +43213,31 @@
     </row>
     <row r="117" spans="8:27" ht="11.5" customHeight="1">
       <c r="H117" t="s">
+        <v>2898</v>
+      </c>
+      <c r="I117" t="s">
+        <v>2899</v>
+      </c>
+      <c r="J117" t="s">
         <v>2900</v>
       </c>
-      <c r="I117" t="s">
+      <c r="L117" t="s">
         <v>2901</v>
       </c>
-      <c r="J117" t="s">
+      <c r="M117" t="s">
         <v>2902</v>
-      </c>
-      <c r="L117" t="s">
-        <v>2903</v>
-      </c>
-      <c r="M117" t="s">
-        <v>2904</v>
       </c>
       <c r="O117" t="s">
         <v>1642</v>
       </c>
       <c r="W117" t="s">
+        <v>2903</v>
+      </c>
+      <c r="X117" t="s">
+        <v>2904</v>
+      </c>
+      <c r="Y117" t="s">
         <v>2905</v>
-      </c>
-      <c r="X117" t="s">
-        <v>2906</v>
-      </c>
-      <c r="Y117" t="s">
-        <v>2907</v>
       </c>
       <c r="AA117" t="s">
         <v>50</v>
@@ -43248,31 +43245,31 @@
     </row>
     <row r="118" spans="8:27" ht="11.5" customHeight="1">
       <c r="H118" t="s">
+        <v>2906</v>
+      </c>
+      <c r="I118" t="s">
+        <v>2907</v>
+      </c>
+      <c r="J118" t="s">
         <v>2908</v>
       </c>
-      <c r="I118" t="s">
+      <c r="K118" t="s">
         <v>2909</v>
       </c>
-      <c r="J118" t="s">
+      <c r="L118" t="s">
         <v>2910</v>
       </c>
-      <c r="K118" t="s">
+      <c r="M118" t="s">
         <v>2911</v>
-      </c>
-      <c r="L118" t="s">
-        <v>2912</v>
-      </c>
-      <c r="M118" t="s">
-        <v>2913</v>
       </c>
       <c r="O118" t="s">
         <v>1642</v>
       </c>
       <c r="X118" t="s">
-        <v>2914</v>
+        <v>2912</v>
       </c>
       <c r="Y118" t="s">
-        <v>2915</v>
+        <v>2913</v>
       </c>
       <c r="AA118" t="s">
         <v>40</v>
@@ -43280,28 +43277,28 @@
     </row>
     <row r="119" spans="8:27" ht="11.5" customHeight="1">
       <c r="H119" t="s">
+        <v>2914</v>
+      </c>
+      <c r="I119" t="s">
+        <v>2915</v>
+      </c>
+      <c r="J119" t="s">
         <v>2916</v>
       </c>
-      <c r="I119" t="s">
+      <c r="L119" t="s">
         <v>2917</v>
       </c>
-      <c r="J119" t="s">
-        <v>2918</v>
-      </c>
-      <c r="L119" t="s">
-        <v>2919</v>
-      </c>
       <c r="M119" t="s">
-        <v>2913</v>
+        <v>2911</v>
       </c>
       <c r="O119" t="s">
         <v>1642</v>
       </c>
       <c r="X119" t="s">
-        <v>2920</v>
+        <v>2918</v>
       </c>
       <c r="Y119" t="s">
-        <v>2921</v>
+        <v>2919</v>
       </c>
       <c r="AA119" t="s">
         <v>40</v>
@@ -43309,25 +43306,25 @@
     </row>
     <row r="120" spans="8:27" ht="11.5" customHeight="1">
       <c r="H120" t="s">
+        <v>2920</v>
+      </c>
+      <c r="J120" t="s">
+        <v>2921</v>
+      </c>
+      <c r="L120" t="s">
         <v>2922</v>
       </c>
-      <c r="J120" t="s">
-        <v>2923</v>
-      </c>
-      <c r="L120" t="s">
-        <v>2924</v>
-      </c>
       <c r="M120" t="s">
-        <v>2913</v>
+        <v>2911</v>
       </c>
       <c r="O120" t="s">
         <v>1642</v>
       </c>
       <c r="X120" t="s">
-        <v>2925</v>
+        <v>2923</v>
       </c>
       <c r="Y120" t="s">
-        <v>2926</v>
+        <v>2924</v>
       </c>
       <c r="AA120" t="s">
         <v>40</v>
@@ -43335,19 +43332,19 @@
     </row>
     <row r="121" spans="8:27" ht="11.5" customHeight="1">
       <c r="H121" t="s">
+        <v>2925</v>
+      </c>
+      <c r="I121" t="s">
+        <v>2926</v>
+      </c>
+      <c r="L121" t="s">
         <v>2927</v>
       </c>
-      <c r="I121" t="s">
+      <c r="M121" t="s">
         <v>2928</v>
       </c>
-      <c r="L121" t="s">
-        <v>2929</v>
-      </c>
-      <c r="M121" t="s">
-        <v>2930</v>
-      </c>
       <c r="O121" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="AA121" t="s">
         <v>40</v>
@@ -43355,16 +43352,16 @@
     </row>
     <row r="122" spans="8:27" ht="15" customHeight="1">
       <c r="H122" t="s">
+        <v>2707</v>
+      </c>
+      <c r="I122" t="s">
+        <v>2929</v>
+      </c>
+      <c r="K122" t="s">
         <v>2709</v>
       </c>
-      <c r="I122" t="s">
-        <v>2931</v>
-      </c>
-      <c r="K122" t="s">
-        <v>2711</v>
-      </c>
       <c r="L122" t="s">
-        <v>2932</v>
+        <v>2930</v>
       </c>
       <c r="M122" t="s">
         <v>1446</v>
@@ -43378,31 +43375,31 @@
     </row>
     <row r="123" spans="8:27" ht="15" customHeight="1">
       <c r="H123" t="s">
+        <v>2931</v>
+      </c>
+      <c r="I123" t="s">
+        <v>2932</v>
+      </c>
+      <c r="J123" t="s">
         <v>2933</v>
       </c>
-      <c r="I123" t="s">
+      <c r="K123" t="s">
         <v>2934</v>
       </c>
-      <c r="J123" t="s">
+      <c r="L123" t="s">
         <v>2935</v>
-      </c>
-      <c r="K123" t="s">
-        <v>2936</v>
-      </c>
-      <c r="L123" t="s">
-        <v>2937</v>
       </c>
       <c r="M123" t="s">
         <v>1446</v>
       </c>
       <c r="O123" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="X123" t="s">
-        <v>2938</v>
+        <v>2936</v>
       </c>
       <c r="Y123" t="s">
-        <v>2939</v>
+        <v>2937</v>
       </c>
       <c r="AA123" t="s">
         <v>40</v>
@@ -43410,22 +43407,22 @@
     </row>
     <row r="124" spans="8:27" ht="15" customHeight="1">
       <c r="H124" t="s">
+        <v>2938</v>
+      </c>
+      <c r="I124" t="s">
+        <v>2939</v>
+      </c>
+      <c r="K124" t="s">
+        <v>2623</v>
+      </c>
+      <c r="L124" t="s">
         <v>2940</v>
-      </c>
-      <c r="I124" t="s">
-        <v>2941</v>
-      </c>
-      <c r="K124" t="s">
-        <v>2625</v>
-      </c>
-      <c r="L124" t="s">
-        <v>2942</v>
       </c>
       <c r="M124" t="s">
         <v>1446</v>
       </c>
       <c r="O124" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="AA124" t="s">
         <v>40</v>
@@ -43433,19 +43430,19 @@
     </row>
     <row r="125" spans="8:27" ht="15" customHeight="1">
       <c r="H125" t="s">
+        <v>2941</v>
+      </c>
+      <c r="I125" t="s">
+        <v>2942</v>
+      </c>
+      <c r="J125" t="s">
+        <v>2612</v>
+      </c>
+      <c r="K125" t="s">
+        <v>2613</v>
+      </c>
+      <c r="L125" t="s">
         <v>2943</v>
-      </c>
-      <c r="I125" t="s">
-        <v>2944</v>
-      </c>
-      <c r="J125" t="s">
-        <v>2614</v>
-      </c>
-      <c r="K125" t="s">
-        <v>2615</v>
-      </c>
-      <c r="L125" t="s">
-        <v>2945</v>
       </c>
       <c r="M125" t="s">
         <v>1446</v>
@@ -43457,7 +43454,7 @@
         <v>2070</v>
       </c>
       <c r="Y125" t="s">
-        <v>2946</v>
+        <v>2944</v>
       </c>
       <c r="AA125" t="s">
         <v>40</v>
@@ -43465,16 +43462,16 @@
     </row>
     <row r="126" spans="8:27" ht="15" customHeight="1">
       <c r="H126" t="s">
+        <v>2801</v>
+      </c>
+      <c r="I126" t="s">
+        <v>2424</v>
+      </c>
+      <c r="K126" t="s">
         <v>2803</v>
       </c>
-      <c r="I126" t="s">
-        <v>2426</v>
-      </c>
-      <c r="K126" t="s">
-        <v>2805</v>
-      </c>
       <c r="L126" t="s">
-        <v>2947</v>
+        <v>2945</v>
       </c>
       <c r="M126" t="s">
         <v>1446</v>
@@ -43488,19 +43485,19 @@
     </row>
     <row r="127" spans="8:27" ht="15" customHeight="1">
       <c r="H127" t="s">
+        <v>2946</v>
+      </c>
+      <c r="I127" t="s">
+        <v>2947</v>
+      </c>
+      <c r="J127" t="s">
         <v>2948</v>
       </c>
-      <c r="I127" t="s">
+      <c r="K127" t="s">
         <v>2949</v>
       </c>
-      <c r="J127" t="s">
+      <c r="L127" t="s">
         <v>2950</v>
-      </c>
-      <c r="K127" t="s">
-        <v>2951</v>
-      </c>
-      <c r="L127" t="s">
-        <v>2952</v>
       </c>
       <c r="M127" t="s">
         <v>2199</v>
@@ -43509,10 +43506,10 @@
         <v>1642</v>
       </c>
       <c r="X127" t="s">
-        <v>2953</v>
+        <v>2951</v>
       </c>
       <c r="Y127" t="s">
-        <v>2954</v>
+        <v>2952</v>
       </c>
       <c r="AA127" t="s">
         <v>40</v>
@@ -43520,19 +43517,19 @@
     </row>
     <row r="128" spans="8:27" ht="15" customHeight="1">
       <c r="H128" t="s">
+        <v>2953</v>
+      </c>
+      <c r="I128" t="s">
+        <v>2954</v>
+      </c>
+      <c r="J128" t="s">
         <v>2955</v>
       </c>
-      <c r="I128" t="s">
+      <c r="L128" t="s">
         <v>2956</v>
       </c>
-      <c r="J128" t="s">
+      <c r="M128" t="s">
         <v>2957</v>
-      </c>
-      <c r="L128" t="s">
-        <v>2958</v>
-      </c>
-      <c r="M128" t="s">
-        <v>2959</v>
       </c>
       <c r="O128" t="s">
         <v>1642</v>
@@ -43541,7 +43538,7 @@
         <v>1817</v>
       </c>
       <c r="Y128" t="s">
-        <v>2960</v>
+        <v>2958</v>
       </c>
       <c r="AA128" t="s">
         <v>40</v>
@@ -43549,16 +43546,16 @@
     </row>
     <row r="129" spans="1:33" ht="15" customHeight="1">
       <c r="H129" t="s">
+        <v>2683</v>
+      </c>
+      <c r="I129" t="s">
+        <v>2959</v>
+      </c>
+      <c r="K129" t="s">
         <v>2685</v>
       </c>
-      <c r="I129" t="s">
-        <v>2961</v>
-      </c>
-      <c r="K129" t="s">
-        <v>2687</v>
-      </c>
       <c r="L129" t="s">
-        <v>2962</v>
+        <v>2960</v>
       </c>
       <c r="M129" t="s">
         <v>1756</v>
@@ -43572,28 +43569,28 @@
     </row>
     <row r="130" spans="1:33" ht="15" customHeight="1">
       <c r="H130" t="s">
+        <v>2961</v>
+      </c>
+      <c r="I130" t="s">
+        <v>2962</v>
+      </c>
+      <c r="J130" t="s">
+        <v>2961</v>
+      </c>
+      <c r="L130" t="s">
         <v>2963</v>
       </c>
-      <c r="I130" t="s">
+      <c r="M130" t="s">
         <v>2964</v>
-      </c>
-      <c r="J130" t="s">
-        <v>2963</v>
-      </c>
-      <c r="L130" t="s">
-        <v>2965</v>
-      </c>
-      <c r="M130" t="s">
-        <v>2966</v>
       </c>
       <c r="O130" t="s">
         <v>1642</v>
       </c>
       <c r="X130" t="s">
-        <v>2967</v>
+        <v>2965</v>
       </c>
       <c r="Y130" t="s">
-        <v>2968</v>
+        <v>2966</v>
       </c>
       <c r="AA130" t="s">
         <v>40</v>
@@ -43601,31 +43598,31 @@
     </row>
     <row r="131" spans="1:33" ht="15" customHeight="1">
       <c r="H131" t="s">
+        <v>2718</v>
+      </c>
+      <c r="I131" t="s">
+        <v>2967</v>
+      </c>
+      <c r="J131" t="s">
         <v>2720</v>
       </c>
-      <c r="I131" t="s">
-        <v>2969</v>
-      </c>
-      <c r="J131" t="s">
-        <v>2722</v>
-      </c>
       <c r="K131" t="s">
-        <v>2723</v>
+        <v>2721</v>
       </c>
       <c r="L131" t="s">
-        <v>2970</v>
+        <v>2968</v>
       </c>
       <c r="M131" t="s">
-        <v>2703</v>
+        <v>2701</v>
       </c>
       <c r="O131" t="s">
         <v>1642</v>
       </c>
       <c r="X131" t="s">
-        <v>2971</v>
+        <v>2969</v>
       </c>
       <c r="Y131" t="s">
-        <v>2972</v>
+        <v>2970</v>
       </c>
       <c r="AA131" t="s">
         <v>50</v>
@@ -43648,19 +43645,19 @@
         <v>797</v>
       </c>
       <c r="H132" s="121" t="s">
+        <v>2971</v>
+      </c>
+      <c r="I132" s="23" t="s">
+        <v>2972</v>
+      </c>
+      <c r="J132" s="121" t="s">
         <v>2973</v>
       </c>
-      <c r="I132" s="23" t="s">
+      <c r="K132" s="118" t="s">
         <v>2974</v>
       </c>
-      <c r="J132" s="121" t="s">
+      <c r="L132" s="121" t="s">
         <v>2975</v>
-      </c>
-      <c r="K132" s="118" t="s">
-        <v>2976</v>
-      </c>
-      <c r="L132" s="121" t="s">
-        <v>2977</v>
       </c>
       <c r="M132" s="173" t="s">
         <v>1435</v>
@@ -43669,35 +43666,35 @@
         <v>38</v>
       </c>
       <c r="O132" s="74" t="s">
-        <v>2978</v>
+        <v>2976</v>
       </c>
       <c r="P132" s="79" t="s">
         <v>185</v>
       </c>
       <c r="Q132" s="447" t="s">
-        <v>2979</v>
+        <v>2977</v>
       </c>
       <c r="R132" s="79"/>
       <c r="S132" s="79" t="s">
+        <v>2978</v>
+      </c>
+      <c r="T132" s="79" t="s">
+        <v>2979</v>
+      </c>
+      <c r="U132" s="79" t="s">
         <v>2980</v>
       </c>
-      <c r="T132" s="79" t="s">
+      <c r="V132" s="79" t="s">
         <v>2981</v>
       </c>
-      <c r="U132" s="79" t="s">
+      <c r="W132" s="79" t="s">
         <v>2982</v>
       </c>
-      <c r="V132" s="79" t="s">
+      <c r="X132" s="79" t="s">
         <v>2983</v>
       </c>
-      <c r="W132" s="79" t="s">
+      <c r="Y132" s="79" t="s">
         <v>2984</v>
-      </c>
-      <c r="X132" s="79" t="s">
-        <v>2985</v>
-      </c>
-      <c r="Y132" s="79" t="s">
-        <v>2986</v>
       </c>
       <c r="Z132" s="79" t="s">
         <v>148</v>
@@ -43714,31 +43711,31 @@
     </row>
     <row r="133" spans="1:33" ht="15" customHeight="1">
       <c r="H133" t="s">
+        <v>2985</v>
+      </c>
+      <c r="I133" t="s">
+        <v>2986</v>
+      </c>
+      <c r="J133" t="s">
         <v>2987</v>
       </c>
-      <c r="I133" t="s">
+      <c r="K133" t="s">
         <v>2988</v>
       </c>
-      <c r="J133" t="s">
+      <c r="L133" t="s">
         <v>2989</v>
       </c>
-      <c r="K133" t="s">
+      <c r="M133" t="s">
         <v>2990</v>
-      </c>
-      <c r="L133" t="s">
-        <v>2991</v>
-      </c>
-      <c r="M133" t="s">
-        <v>2992</v>
       </c>
       <c r="O133" t="s">
         <v>1642</v>
       </c>
       <c r="X133" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
       <c r="Y133" t="s">
-        <v>2994</v>
+        <v>2992</v>
       </c>
       <c r="AA133" t="s">
         <v>40</v>
@@ -43746,28 +43743,28 @@
     </row>
     <row r="134" spans="1:33" ht="15" customHeight="1">
       <c r="H134" t="s">
+        <v>2993</v>
+      </c>
+      <c r="I134" t="s">
+        <v>2994</v>
+      </c>
+      <c r="J134" t="s">
         <v>2995</v>
       </c>
-      <c r="I134" t="s">
+      <c r="L134" t="s">
         <v>2996</v>
       </c>
-      <c r="J134" t="s">
+      <c r="M134" t="s">
         <v>2997</v>
-      </c>
-      <c r="L134" t="s">
-        <v>2998</v>
-      </c>
-      <c r="M134" t="s">
-        <v>2999</v>
       </c>
       <c r="O134" t="s">
         <v>1642</v>
       </c>
       <c r="X134" t="s">
-        <v>3000</v>
+        <v>2998</v>
       </c>
       <c r="Y134" t="s">
-        <v>3001</v>
+        <v>2999</v>
       </c>
       <c r="AA134" t="s">
         <v>40</v>
@@ -43775,19 +43772,19 @@
     </row>
     <row r="135" spans="1:33" ht="15" customHeight="1">
       <c r="H135" t="s">
+        <v>3000</v>
+      </c>
+      <c r="I135" t="s">
+        <v>3001</v>
+      </c>
+      <c r="J135" t="s">
         <v>3002</v>
       </c>
-      <c r="I135" t="s">
+      <c r="K135" t="s">
         <v>3003</v>
       </c>
-      <c r="J135" t="s">
+      <c r="L135" t="s">
         <v>3004</v>
-      </c>
-      <c r="K135" t="s">
-        <v>3005</v>
-      </c>
-      <c r="L135" t="s">
-        <v>3006</v>
       </c>
       <c r="M135" t="s">
         <v>1689</v>
@@ -43799,7 +43796,7 @@
         <v>1889</v>
       </c>
       <c r="Y135" t="s">
-        <v>3007</v>
+        <v>3005</v>
       </c>
       <c r="AA135" t="s">
         <v>40</v>
@@ -43807,16 +43804,16 @@
     </row>
     <row r="136" spans="1:33" ht="15" customHeight="1">
       <c r="H136" t="s">
+        <v>3006</v>
+      </c>
+      <c r="I136" t="s">
+        <v>3007</v>
+      </c>
+      <c r="J136" t="s">
         <v>3008</v>
       </c>
-      <c r="I136" t="s">
+      <c r="L136" t="s">
         <v>3009</v>
-      </c>
-      <c r="J136" t="s">
-        <v>3010</v>
-      </c>
-      <c r="L136" t="s">
-        <v>3011</v>
       </c>
       <c r="M136" t="s">
         <v>1668</v>
@@ -43825,10 +43822,10 @@
         <v>1642</v>
       </c>
       <c r="X136" t="s">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="Y136" t="s">
-        <v>3013</v>
+        <v>3011</v>
       </c>
       <c r="AA136" t="s">
         <v>40</v>
@@ -43836,19 +43833,19 @@
     </row>
     <row r="137" spans="1:33" ht="15" customHeight="1">
       <c r="H137" t="s">
+        <v>2638</v>
+      </c>
+      <c r="I137" t="s">
+        <v>2639</v>
+      </c>
+      <c r="J137" t="s">
         <v>2640</v>
       </c>
-      <c r="I137" t="s">
+      <c r="K137" t="s">
         <v>2641</v>
       </c>
-      <c r="J137" t="s">
-        <v>2642</v>
-      </c>
-      <c r="K137" t="s">
-        <v>2643</v>
-      </c>
       <c r="L137" t="s">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="M137" t="s">
         <v>1446</v>
@@ -43857,13 +43854,13 @@
         <v>1657</v>
       </c>
       <c r="W137" t="s">
-        <v>3015</v>
+        <v>3013</v>
       </c>
       <c r="X137" t="s">
-        <v>3016</v>
+        <v>3014</v>
       </c>
       <c r="Y137" t="s">
-        <v>2779</v>
+        <v>2777</v>
       </c>
       <c r="AA137" t="s">
         <v>40</v>
@@ -43871,19 +43868,19 @@
     </row>
     <row r="138" spans="1:33" ht="15" customHeight="1">
       <c r="H138" t="s">
-        <v>2780</v>
+        <v>2778</v>
       </c>
       <c r="I138" t="s">
+        <v>2644</v>
+      </c>
+      <c r="J138" t="s">
+        <v>2645</v>
+      </c>
+      <c r="K138" t="s">
         <v>2646</v>
       </c>
-      <c r="J138" t="s">
-        <v>2647</v>
-      </c>
-      <c r="K138" t="s">
-        <v>2648</v>
-      </c>
       <c r="L138" t="s">
-        <v>3017</v>
+        <v>3015</v>
       </c>
       <c r="M138" t="s">
         <v>1446</v>
@@ -43892,10 +43889,10 @@
         <v>1657</v>
       </c>
       <c r="X138" t="s">
-        <v>2782</v>
+        <v>2780</v>
       </c>
       <c r="Y138" t="s">
-        <v>2783</v>
+        <v>2781</v>
       </c>
       <c r="AA138" t="s">
         <v>40</v>
@@ -43903,16 +43900,16 @@
     </row>
     <row r="139" spans="1:33" ht="15" customHeight="1">
       <c r="H139" t="s">
+        <v>3016</v>
+      </c>
+      <c r="I139" t="s">
+        <v>3017</v>
+      </c>
+      <c r="J139" t="s">
         <v>3018</v>
       </c>
-      <c r="I139" t="s">
+      <c r="L139" t="s">
         <v>3019</v>
-      </c>
-      <c r="J139" t="s">
-        <v>3020</v>
-      </c>
-      <c r="L139" t="s">
-        <v>3021</v>
       </c>
       <c r="M139" t="s">
         <v>1446</v>
@@ -43921,10 +43918,10 @@
         <v>1811</v>
       </c>
       <c r="X139" t="s">
-        <v>3022</v>
+        <v>3020</v>
       </c>
       <c r="Y139" t="s">
-        <v>3023</v>
+        <v>3021</v>
       </c>
       <c r="AA139" t="s">
         <v>40</v>
@@ -43932,19 +43929,19 @@
     </row>
     <row r="140" spans="1:33" ht="15" customHeight="1">
       <c r="H140" t="s">
-        <v>2933</v>
+        <v>2931</v>
       </c>
       <c r="I140" t="s">
+        <v>3022</v>
+      </c>
+      <c r="J140" t="s">
+        <v>3023</v>
+      </c>
+      <c r="K140" t="s">
+        <v>2934</v>
+      </c>
+      <c r="L140" t="s">
         <v>3024</v>
-      </c>
-      <c r="J140" t="s">
-        <v>3025</v>
-      </c>
-      <c r="K140" t="s">
-        <v>2936</v>
-      </c>
-      <c r="L140" t="s">
-        <v>3026</v>
       </c>
       <c r="M140" t="s">
         <v>1446</v>
@@ -43956,10 +43953,10 @@
         <v>431</v>
       </c>
       <c r="X140" t="s">
-        <v>3027</v>
+        <v>3025</v>
       </c>
       <c r="Y140" t="s">
-        <v>3028</v>
+        <v>3026</v>
       </c>
       <c r="AA140" t="s">
         <v>50</v>
@@ -43967,19 +43964,19 @@
     </row>
     <row r="141" spans="1:33" ht="15" customHeight="1">
       <c r="H141" t="s">
+        <v>3027</v>
+      </c>
+      <c r="I141" t="s">
+        <v>3028</v>
+      </c>
+      <c r="J141" t="s">
         <v>3029</v>
       </c>
-      <c r="I141" t="s">
+      <c r="K141" t="s">
         <v>3030</v>
       </c>
-      <c r="J141" t="s">
+      <c r="L141" t="s">
         <v>3031</v>
-      </c>
-      <c r="K141" t="s">
-        <v>3032</v>
-      </c>
-      <c r="L141" t="s">
-        <v>3033</v>
       </c>
       <c r="M141" t="s">
         <v>1446</v>
@@ -43988,10 +43985,10 @@
         <v>1657</v>
       </c>
       <c r="X141" t="s">
-        <v>3034</v>
+        <v>3032</v>
       </c>
       <c r="Y141" t="s">
-        <v>3035</v>
+        <v>3033</v>
       </c>
       <c r="AA141" t="s">
         <v>40</v>
@@ -43999,23 +43996,23 @@
     </row>
     <row r="142" spans="1:33" ht="15" customHeight="1">
       <c r="H142" t="s">
+        <v>3034</v>
+      </c>
+      <c r="I142" t="s">
+        <v>3035</v>
+      </c>
+      <c r="J142" s="121" t="s">
         <v>3036</v>
-      </c>
-      <c r="I142" t="s">
-        <v>3037</v>
-      </c>
-      <c r="J142" s="121" t="s">
-        <v>3038</v>
       </c>
       <c r="K142" s="118"/>
       <c r="L142" s="121" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="M142" s="173" t="s">
         <v>2365</v>
       </c>
       <c r="O142" t="s">
-        <v>3040</v>
+        <v>3038</v>
       </c>
     </row>
     <row r="143" spans="1:33" s="73" customFormat="1" ht="11.5" customHeight="1">
@@ -44027,24 +44024,24 @@
       <c r="F143" s="104"/>
       <c r="G143" s="104"/>
       <c r="H143" s="119" t="s">
+        <v>3039</v>
+      </c>
+      <c r="I143" t="s">
+        <v>3040</v>
+      </c>
+      <c r="J143" s="119" t="s">
         <v>3041</v>
-      </c>
-      <c r="I143" t="s">
-        <v>3042</v>
-      </c>
-      <c r="J143" s="119" t="s">
-        <v>3043</v>
       </c>
       <c r="K143" s="118"/>
       <c r="L143" s="119" t="s">
-        <v>3044</v>
+        <v>3042</v>
       </c>
       <c r="M143" s="169" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="N143" s="104"/>
       <c r="O143" s="399" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="P143" s="104"/>
       <c r="Q143" s="399"/>
@@ -44074,19 +44071,19 @@
       <c r="F144" s="76"/>
       <c r="G144" s="76"/>
       <c r="H144" s="116" t="s">
+        <v>3045</v>
+      </c>
+      <c r="I144" s="118" t="s">
+        <v>3046</v>
+      </c>
+      <c r="J144" s="116" t="s">
         <v>3047</v>
       </c>
-      <c r="I144" s="118" t="s">
+      <c r="K144" s="118" t="s">
         <v>3048</v>
       </c>
-      <c r="J144" s="116" t="s">
+      <c r="L144" s="116" t="s">
         <v>3049</v>
-      </c>
-      <c r="K144" s="118" t="s">
-        <v>3050</v>
-      </c>
-      <c r="L144" s="116" t="s">
-        <v>3051</v>
       </c>
       <c r="M144" s="170" t="s">
         <v>1446</v>
@@ -44104,10 +44101,10 @@
       <c r="V144" s="76"/>
       <c r="W144" s="76"/>
       <c r="X144" s="76" t="s">
-        <v>3052</v>
+        <v>3050</v>
       </c>
       <c r="Y144" s="76" t="s">
-        <v>3053</v>
+        <v>3051</v>
       </c>
       <c r="Z144" s="76"/>
       <c r="AA144" s="76" t="s">
@@ -44160,17 +44157,17 @@
   <sheetData>
     <row r="1" spans="1:3" ht="13" customHeight="1">
       <c r="A1" s="26" t="s">
-        <v>3054</v>
+        <v>3052</v>
       </c>
       <c r="B1" s="56"/>
       <c r="C1" s="57"/>
     </row>
     <row r="2" spans="1:3" s="61" customFormat="1" ht="13" customHeight="1">
       <c r="A2" s="58" t="s">
-        <v>3055</v>
+        <v>3053</v>
       </c>
       <c r="B2" s="59" t="s">
-        <v>3056</v>
+        <v>3054</v>
       </c>
       <c r="C2" s="60"/>
     </row>
@@ -44179,16 +44176,16 @@
         <v>149</v>
       </c>
       <c r="B3" s="146" t="s">
-        <v>3057</v>
+        <v>3055</v>
       </c>
       <c r="C3" s="57"/>
     </row>
     <row r="4" spans="1:3" ht="13" customHeight="1">
       <c r="A4" s="26" t="s">
-        <v>3058</v>
+        <v>3056</v>
       </c>
       <c r="B4" s="146" t="s">
-        <v>3059</v>
+        <v>3057</v>
       </c>
       <c r="C4" s="57"/>
     </row>
@@ -44197,7 +44194,7 @@
         <v>772</v>
       </c>
       <c r="B5" s="146" t="s">
-        <v>3060</v>
+        <v>3058</v>
       </c>
       <c r="C5" s="57"/>
     </row>
@@ -44206,16 +44203,16 @@
         <v>614</v>
       </c>
       <c r="B6" s="62" t="s">
-        <v>3061</v>
+        <v>3059</v>
       </c>
       <c r="C6" s="57"/>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="63" t="s">
-        <v>3062</v>
+        <v>3060</v>
       </c>
       <c r="B7" s="64" t="s">
-        <v>3063</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -44223,7 +44220,7 @@
         <v>584</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>3064</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -44231,15 +44228,15 @@
         <v>645</v>
       </c>
       <c r="B9" s="64" t="s">
-        <v>3065</v>
+        <v>3063</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="63" t="s">
-        <v>3066</v>
+        <v>3064</v>
       </c>
       <c r="B10" s="64" t="s">
-        <v>3067</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="25.5" customHeight="1">
@@ -44247,7 +44244,7 @@
         <v>163</v>
       </c>
       <c r="B11" s="65" t="s">
-        <v>3068</v>
+        <v>3066</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="25.5" customHeight="1">
@@ -44255,7 +44252,7 @@
         <v>1015</v>
       </c>
       <c r="B12" s="65" t="s">
-        <v>3069</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="25.5" customHeight="1">
@@ -44263,31 +44260,31 @@
         <v>1273</v>
       </c>
       <c r="B13" s="65" t="s">
-        <v>3070</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="70" t="s">
-        <v>3071</v>
+        <v>3069</v>
       </c>
       <c r="B14" s="64" t="s">
-        <v>3072</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="25.5" customHeight="1">
       <c r="A15" s="70" t="s">
-        <v>3073</v>
+        <v>3071</v>
       </c>
       <c r="B15" s="65" t="s">
-        <v>3074</v>
+        <v>3072</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="63" t="s">
-        <v>3075</v>
+        <v>3073</v>
       </c>
       <c r="B16" s="64" t="s">
-        <v>3076</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="25.5" customHeight="1">
@@ -44295,7 +44292,7 @@
         <v>797</v>
       </c>
       <c r="B17" s="65" t="s">
-        <v>3077</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -44304,7 +44301,7 @@
     </row>
     <row r="19" spans="1:2" ht="13" customHeight="1">
       <c r="A19" s="214" t="s">
-        <v>3078</v>
+        <v>3076</v>
       </c>
       <c r="B19" s="64"/>
     </row>
@@ -44313,7 +44310,7 @@
         <v>64</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>3079</v>
+        <v>3077</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -44321,7 +44318,7 @@
         <v>33</v>
       </c>
       <c r="B21" s="64" t="s">
-        <v>3080</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -44336,86 +44333,86 @@
     </row>
     <row r="28" spans="1:2" ht="33.75" customHeight="1">
       <c r="A28" s="69" t="s">
-        <v>3081</v>
+        <v>3079</v>
       </c>
       <c r="B28" s="68" t="s">
-        <v>3082</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="13" customHeight="1">
       <c r="A29" s="69"/>
       <c r="B29" s="68" t="s">
-        <v>3083</v>
+        <v>3081</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="25.5" customHeight="1">
       <c r="A30" s="70" t="s">
-        <v>3084</v>
+        <v>3082</v>
       </c>
       <c r="B30" s="71" t="s">
-        <v>3085</v>
+        <v>3083</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="70" t="s">
-        <v>3086</v>
+        <v>3084</v>
       </c>
       <c r="B31" s="64" t="s">
-        <v>3087</v>
+        <v>3085</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="25.5" customHeight="1">
       <c r="A32" s="70" t="s">
-        <v>3088</v>
+        <v>3086</v>
       </c>
       <c r="B32" s="71" t="s">
-        <v>3089</v>
+        <v>3087</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="67" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="B33" s="65" t="s">
-        <v>3091</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="25.5" customHeight="1">
       <c r="A34" s="67" t="s">
-        <v>3092</v>
+        <v>3090</v>
       </c>
       <c r="B34" s="71" t="s">
-        <v>3093</v>
+        <v>3091</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="25.5" customHeight="1">
       <c r="A35" s="67" t="s">
-        <v>3094</v>
+        <v>3092</v>
       </c>
       <c r="B35" s="65" t="s">
-        <v>3095</v>
+        <v>3093</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="25.5" customHeight="1">
       <c r="A36" s="66" t="s">
-        <v>3096</v>
+        <v>3094</v>
       </c>
       <c r="B36" s="68" t="s">
-        <v>3097</v>
+        <v>3095</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="25.5" customHeight="1">
       <c r="A38" s="66"/>
       <c r="B38" s="68" t="s">
-        <v>3098</v>
+        <v>3096</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="25.5" customHeight="1">
       <c r="A39" s="66" t="s">
-        <v>3099</v>
+        <v>3097</v>
       </c>
       <c r="B39" s="68" t="s">
-        <v>3100</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="25.5" customHeight="1">
@@ -44423,31 +44420,31 @@
         <v>33</v>
       </c>
       <c r="B40" s="68" t="s">
-        <v>3101</v>
+        <v>3099</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="25.5" customHeight="1">
       <c r="A41" s="66" t="s">
-        <v>3102</v>
+        <v>3100</v>
       </c>
       <c r="B41" s="68" t="s">
-        <v>3103</v>
+        <v>3101</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="25.5" customHeight="1">
       <c r="A42" s="66" t="s">
-        <v>3104</v>
+        <v>3102</v>
       </c>
       <c r="B42" s="68" t="s">
-        <v>3105</v>
+        <v>3103</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="25.5" customHeight="1">
       <c r="A43" s="66" t="s">
-        <v>3106</v>
+        <v>3104</v>
       </c>
       <c r="B43" s="68" t="s">
-        <v>3107</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="25.5" customHeight="1">
@@ -44455,33 +44452,33 @@
         <v>229</v>
       </c>
       <c r="B44" s="68" t="s">
-        <v>3108</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="43" customHeight="1">
       <c r="A46" s="214" t="s">
-        <v>3109</v>
+        <v>3107</v>
       </c>
       <c r="B46" s="68" t="s">
-        <v>3110</v>
+        <v>3108</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="13" customHeight="1">
       <c r="A49" s="69" t="s">
-        <v>3111</v>
+        <v>3109</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="25.5" customHeight="1">
       <c r="A50" s="68" t="s">
-        <v>3112</v>
+        <v>3110</v>
       </c>
       <c r="B50" s="68" t="s">
-        <v>3113</v>
+        <v>3111</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>3114</v>
+        <v>3112</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -44489,7 +44486,7 @@
         <v>68</v>
       </c>
       <c r="B53" t="s">
-        <v>3115</v>
+        <v>3113</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -44497,7 +44494,7 @@
         <v>404</v>
       </c>
       <c r="B54" t="s">
-        <v>3116</v>
+        <v>3114</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -44505,7 +44502,7 @@
         <v>1060</v>
       </c>
       <c r="B55" t="s">
-        <v>3117</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -44513,7 +44510,7 @@
         <v>174</v>
       </c>
       <c r="B56" t="s">
-        <v>3118</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -44521,7 +44518,7 @@
         <v>253</v>
       </c>
       <c r="B57" t="s">
-        <v>3119</v>
+        <v>3117</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -44529,7 +44526,7 @@
         <v>148</v>
       </c>
       <c r="B58" t="s">
-        <v>3120</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -44537,7 +44534,7 @@
         <v>189</v>
       </c>
       <c r="B59" t="s">
-        <v>3121</v>
+        <v>3119</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -44545,12 +44542,12 @@
         <v>39</v>
       </c>
       <c r="B60" t="s">
-        <v>3122</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -44558,7 +44555,7 @@
         <v>40</v>
       </c>
       <c r="B63" t="s">
-        <v>3124</v>
+        <v>3122</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -44566,7 +44563,7 @@
         <v>50</v>
       </c>
       <c r="B64" t="s">
-        <v>3125</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -44574,7 +44571,7 @@
         <v>124</v>
       </c>
       <c r="B65" t="s">
-        <v>3126</v>
+        <v>3124</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -44582,12 +44579,12 @@
         <v>58</v>
       </c>
       <c r="B66" t="s">
-        <v>3127</v>
+        <v>3125</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="13" customHeight="1">
       <c r="A68" s="466" t="s">
-        <v>3128</v>
+        <v>3126</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -44595,7 +44592,7 @@
         <v>161</v>
       </c>
       <c r="B69" t="s">
-        <v>3129</v>
+        <v>3127</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -44603,102 +44600,102 @@
         <v>1795</v>
       </c>
       <c r="B70" t="s">
-        <v>3130</v>
+        <v>3128</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="13" customHeight="1">
       <c r="A72" s="466" t="s">
-        <v>3131</v>
+        <v>3129</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>3132</v>
+        <v>3130</v>
       </c>
       <c r="B73" t="s">
-        <v>3133</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>3134</v>
+        <v>3132</v>
       </c>
       <c r="B74" t="s">
-        <v>3135</v>
+        <v>3133</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>3136</v>
+        <v>3134</v>
       </c>
       <c r="B75" t="s">
-        <v>3137</v>
+        <v>3135</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>3138</v>
+        <v>3136</v>
       </c>
       <c r="B76" t="s">
-        <v>3139</v>
+        <v>3137</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>3140</v>
+        <v>3138</v>
       </c>
       <c r="B77" t="s">
-        <v>3141</v>
+        <v>3139</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>3142</v>
+        <v>3140</v>
       </c>
       <c r="B78" t="s">
-        <v>3143</v>
+        <v>3141</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>3144</v>
+        <v>3142</v>
       </c>
       <c r="B79" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="13" customHeight="1">
       <c r="A81" s="466" t="s">
-        <v>3146</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>3147</v>
+        <v>3145</v>
       </c>
       <c r="B82" t="s">
-        <v>3148</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>3149</v>
+        <v>3147</v>
       </c>
       <c r="B83" t="s">
-        <v>3150</v>
+        <v>3148</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>3151</v>
+        <v>3149</v>
       </c>
       <c r="B84" t="s">
-        <v>3152</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>3153</v>
+        <v>3151</v>
       </c>
     </row>
   </sheetData>
@@ -44886,7 +44883,7 @@
     <row r="7" spans="1:24" ht="12.75" customHeight="1">
       <c r="A7" s="15"/>
       <c r="B7" s="15" t="s">
-        <v>3406</v>
+        <v>3404</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
@@ -70201,12 +70198,12 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="5" t="s">
-        <v>3154</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="5" t="s">
-        <v>2495</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -70214,60 +70211,60 @@
         <v>910</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>3155</v>
+        <v>3153</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>3156</v>
+        <v>3154</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>3157</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>3158</v>
+        <v>3156</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>3159</v>
+        <v>3157</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>3160</v>
+        <v>3158</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>3161</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>3162</v>
+        <v>3160</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>3163</v>
+        <v>3161</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>3164</v>
+        <v>3162</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>3165</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>3166</v>
+        <v>3164</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -70296,103 +70293,103 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15" customHeight="1">
       <c r="A1" s="260" t="s">
-        <v>3167</v>
+        <v>3165</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1">
       <c r="A2" t="s">
-        <v>3168</v>
+        <v>3166</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="12.65" customHeight="1">
       <c r="A3" t="s">
-        <v>3169</v>
+        <v>3167</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="5" spans="1:2" ht="12.65" customHeight="1">
       <c r="A5" s="260" t="s">
-        <v>3170</v>
+        <v>3168</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" customHeight="1">
       <c r="A6" t="s">
-        <v>3171</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="12.65" customHeight="1">
       <c r="A7" t="s">
-        <v>3172</v>
+        <v>3170</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="12.65" customHeight="1">
       <c r="A8" s="260" t="s">
-        <v>3173</v>
+        <v>3171</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="10" spans="1:2" ht="12.65" customHeight="1">
       <c r="A10" s="260" t="s">
-        <v>3174</v>
+        <v>3172</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="12.65" customHeight="1">
       <c r="A11" t="s">
-        <v>3175</v>
+        <v>3173</v>
       </c>
       <c r="B11" t="s">
-        <v>3176</v>
+        <v>3174</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="12.65" customHeight="1">
       <c r="A12" t="s">
-        <v>3177</v>
+        <v>3175</v>
       </c>
       <c r="B12" t="s">
-        <v>3178</v>
+        <v>3176</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="52" customHeight="1">
       <c r="A13" t="s">
-        <v>3179</v>
+        <v>3177</v>
       </c>
       <c r="B13" t="s">
-        <v>3180</v>
+        <v>3178</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="12.65" customHeight="1">
       <c r="A14" t="s">
-        <v>3181</v>
+        <v>3179</v>
       </c>
       <c r="B14" t="s">
-        <v>3182</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="12.65" customHeight="1">
       <c r="A15" t="s">
-        <v>3183</v>
+        <v>3181</v>
       </c>
       <c r="B15" t="s">
-        <v>3184</v>
+        <v>3182</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="17" spans="1:3" ht="12.65" customHeight="1">
       <c r="A17" s="260" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="12.65" customHeight="1">
       <c r="B18" t="s">
-        <v>3186</v>
+        <v>3184</v>
       </c>
       <c r="C18" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="25" customHeight="1">
       <c r="A19" t="s">
-        <v>3188</v>
+        <v>3186</v>
       </c>
       <c r="B19">
         <v>277</v>
@@ -70400,7 +70397,7 @@
     </row>
     <row r="20" spans="1:3" ht="12.65" customHeight="1">
       <c r="A20" t="s">
-        <v>3189</v>
+        <v>3187</v>
       </c>
       <c r="B20">
         <v>83</v>
@@ -70411,7 +70408,7 @@
     </row>
     <row r="21" spans="1:3" ht="25" customHeight="1">
       <c r="A21" t="s">
-        <v>3190</v>
+        <v>3188</v>
       </c>
       <c r="B21">
         <v>11</v>
@@ -70422,7 +70419,7 @@
     </row>
     <row r="22" spans="1:3" ht="12.65" customHeight="1">
       <c r="A22" t="s">
-        <v>3191</v>
+        <v>3189</v>
       </c>
       <c r="B22">
         <v>52</v>
@@ -70433,7 +70430,7 @@
     </row>
     <row r="23" spans="1:3" ht="25" customHeight="1">
       <c r="A23" t="s">
-        <v>3192</v>
+        <v>3190</v>
       </c>
       <c r="B23">
         <v>15</v>
@@ -70444,7 +70441,7 @@
     </row>
     <row r="24" spans="1:3" ht="12.65" customHeight="1">
       <c r="A24" t="s">
-        <v>3193</v>
+        <v>3191</v>
       </c>
       <c r="B24">
         <v>5</v>
@@ -70455,7 +70452,7 @@
     </row>
     <row r="25" spans="1:3" ht="12.65" customHeight="1">
       <c r="A25" t="s">
-        <v>3194</v>
+        <v>3192</v>
       </c>
       <c r="B25">
         <v>194</v>
@@ -70467,15 +70464,15 @@
     <row r="26" spans="1:3" ht="12.65" customHeight="1"/>
     <row r="27" spans="1:3" ht="12.65" customHeight="1">
       <c r="A27" s="260" t="s">
-        <v>3195</v>
+        <v>3193</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="12.65" customHeight="1">
       <c r="A28" t="s">
-        <v>3196</v>
+        <v>3194</v>
       </c>
       <c r="B28" t="s">
-        <v>3197</v>
+        <v>3195</v>
       </c>
       <c r="C28" s="258">
         <v>0.94199999999999995</v>
@@ -70483,10 +70480,10 @@
     </row>
     <row r="29" spans="1:3" ht="12.65" customHeight="1">
       <c r="A29" t="s">
-        <v>3198</v>
+        <v>3196</v>
       </c>
       <c r="B29" t="s">
-        <v>3199</v>
+        <v>3197</v>
       </c>
       <c r="C29" s="258">
         <v>0.73299999999999998</v>
@@ -70494,10 +70491,10 @@
     </row>
     <row r="30" spans="1:3" ht="12.65" customHeight="1">
       <c r="A30" t="s">
-        <v>3200</v>
+        <v>3198</v>
       </c>
       <c r="B30" t="s">
-        <v>3201</v>
+        <v>3199</v>
       </c>
       <c r="C30" s="258">
         <v>0.39</v>
@@ -70505,10 +70502,10 @@
     </row>
     <row r="31" spans="1:3" ht="12.65" customHeight="1">
       <c r="A31" t="s">
-        <v>3202</v>
+        <v>3200</v>
       </c>
       <c r="B31" t="s">
-        <v>3203</v>
+        <v>3201</v>
       </c>
       <c r="C31" s="258">
         <v>0.108</v>
@@ -70517,47 +70514,47 @@
     <row r="32" spans="1:3" ht="12.65" customHeight="1"/>
     <row r="33" spans="1:9" ht="12.65" customHeight="1">
       <c r="A33" s="260" t="s">
-        <v>3204</v>
+        <v>3202</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="12.65" customHeight="1">
       <c r="A34" t="s">
-        <v>3205</v>
+        <v>3203</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="36" spans="1:9" ht="12.65" customHeight="1">
       <c r="A36" s="260" t="s">
-        <v>3206</v>
+        <v>3204</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="12.65" customHeight="1">
       <c r="A37" t="s">
+        <v>3205</v>
+      </c>
+      <c r="B37" t="s">
+        <v>3206</v>
+      </c>
+      <c r="C37" t="s">
         <v>3207</v>
       </c>
-      <c r="B37" t="s">
+      <c r="D37" t="s">
         <v>3208</v>
       </c>
-      <c r="C37" t="s">
+      <c r="E37" t="s">
         <v>3209</v>
       </c>
-      <c r="D37" t="s">
+      <c r="F37" t="s">
         <v>3210</v>
       </c>
-      <c r="E37" t="s">
+      <c r="G37" t="s">
         <v>3211</v>
       </c>
-      <c r="F37" t="s">
+      <c r="H37" t="s">
         <v>3212</v>
       </c>
-      <c r="G37" t="s">
+      <c r="I37" t="s">
         <v>3213</v>
-      </c>
-      <c r="H37" t="s">
-        <v>3214</v>
-      </c>
-      <c r="I37" t="s">
-        <v>3215</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="12.65" customHeight="1">
@@ -70565,10 +70562,10 @@
         <v>150</v>
       </c>
       <c r="B38" t="s">
-        <v>3216</v>
+        <v>3214</v>
       </c>
       <c r="D38" t="s">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="E38" t="s">
         <v>38</v>
@@ -70588,7 +70585,7 @@
         <v>156</v>
       </c>
       <c r="B39" t="s">
-        <v>3216</v>
+        <v>3214</v>
       </c>
       <c r="D39" t="s">
         <v>1451</v>
@@ -70611,13 +70608,13 @@
     </row>
     <row r="40" spans="1:9" ht="12.65" customHeight="1">
       <c r="B40" t="s">
-        <v>3218</v>
+        <v>3216</v>
       </c>
       <c r="C40" t="s">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="D40" t="s">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="E40" t="s">
         <v>38</v>
@@ -70637,7 +70634,7 @@
         <v>175</v>
       </c>
       <c r="B41" t="s">
-        <v>3218</v>
+        <v>3216</v>
       </c>
       <c r="E41" t="s">
         <v>57</v>
@@ -70657,7 +70654,7 @@
         <v>1451</v>
       </c>
       <c r="D42" t="s">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="E42" t="s">
         <v>38</v>
@@ -70680,7 +70677,7 @@
         <v>707</v>
       </c>
       <c r="B43" t="s">
-        <v>3219</v>
+        <v>3217</v>
       </c>
       <c r="C43" t="s">
         <v>1451</v>
@@ -70706,13 +70703,13 @@
         <v>953</v>
       </c>
       <c r="B44" t="s">
-        <v>3220</v>
+        <v>3218</v>
       </c>
       <c r="C44" t="s">
         <v>1451</v>
       </c>
       <c r="D44" t="s">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="E44" t="s">
         <v>38</v>
@@ -70735,19 +70732,19 @@
         <v>1131</v>
       </c>
       <c r="B45" t="s">
-        <v>3220</v>
+        <v>3218</v>
       </c>
       <c r="C45" t="s">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="D45" t="s">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="E45" t="s">
         <v>57</v>
       </c>
       <c r="F45" t="s">
-        <v>3221</v>
+        <v>3219</v>
       </c>
       <c r="G45" t="s">
         <v>253</v>
@@ -70764,19 +70761,19 @@
         <v>1136</v>
       </c>
       <c r="B46" t="s">
-        <v>3220</v>
+        <v>3218</v>
       </c>
       <c r="C46" t="s">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="D46" t="s">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="E46" t="s">
         <v>57</v>
       </c>
       <c r="F46" t="s">
-        <v>3221</v>
+        <v>3219</v>
       </c>
       <c r="G46" t="s">
         <v>148</v>
@@ -70799,7 +70796,7 @@
         <v>1451</v>
       </c>
       <c r="D47" t="s">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="E47" t="s">
         <v>38</v>
@@ -70825,7 +70822,7 @@
         <v>1451</v>
       </c>
       <c r="D48" t="s">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="E48" t="s">
         <v>38</v>
@@ -70843,33 +70840,33 @@
     <row r="49" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="50" spans="1:9" ht="12.65" customHeight="1">
       <c r="A50" s="260" t="s">
-        <v>3222</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="12.65" customHeight="1">
       <c r="B51" t="s">
+        <v>3221</v>
+      </c>
+      <c r="C51" t="s">
+        <v>3222</v>
+      </c>
+      <c r="D51" t="s">
         <v>3223</v>
       </c>
-      <c r="C51" t="s">
+      <c r="E51" t="s">
         <v>3224</v>
       </c>
-      <c r="D51" t="s">
+      <c r="F51" t="s">
         <v>3225</v>
       </c>
-      <c r="E51" t="s">
+      <c r="G51" t="s">
         <v>3226</v>
       </c>
-      <c r="F51" t="s">
+      <c r="H51" t="s">
         <v>3227</v>
       </c>
-      <c r="G51" t="s">
+      <c r="I51" t="s">
         <v>3228</v>
-      </c>
-      <c r="H51" t="s">
-        <v>3229</v>
-      </c>
-      <c r="I51" t="s">
-        <v>3230</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="12.65" customHeight="1">
@@ -70903,7 +70900,7 @@
     </row>
     <row r="53" spans="1:9" ht="12.65" customHeight="1">
       <c r="A53" t="s">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="B53">
         <v>3</v>
@@ -70932,7 +70929,7 @@
     </row>
     <row r="54" spans="1:9" ht="12.65" customHeight="1">
       <c r="A54" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B54">
         <v>8</v>
@@ -70962,33 +70959,33 @@
     <row r="55" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="56" spans="1:9" ht="12.65" customHeight="1">
       <c r="A56" s="260" t="s">
-        <v>3231</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="12.65" customHeight="1">
       <c r="B57" t="s">
+        <v>3221</v>
+      </c>
+      <c r="C57" t="s">
+        <v>3222</v>
+      </c>
+      <c r="D57" t="s">
         <v>3223</v>
       </c>
-      <c r="C57" t="s">
+      <c r="E57" t="s">
         <v>3224</v>
       </c>
-      <c r="D57" t="s">
+      <c r="F57" t="s">
         <v>3225</v>
       </c>
-      <c r="E57" t="s">
+      <c r="G57" t="s">
         <v>3226</v>
       </c>
-      <c r="F57" t="s">
+      <c r="H57" t="s">
         <v>3227</v>
       </c>
-      <c r="G57" t="s">
+      <c r="I57" t="s">
         <v>3228</v>
-      </c>
-      <c r="H57" t="s">
-        <v>3229</v>
-      </c>
-      <c r="I57" t="s">
-        <v>3230</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="12.65" customHeight="1">
@@ -71022,7 +71019,7 @@
     </row>
     <row r="59" spans="1:9" ht="12.65" customHeight="1">
       <c r="A59" t="s">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="B59">
         <v>8</v>
@@ -71051,7 +71048,7 @@
     </row>
     <row r="60" spans="1:9" ht="12.65" customHeight="1">
       <c r="A60" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B60">
         <v>10</v>
@@ -71081,33 +71078,33 @@
     <row r="61" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="62" spans="1:9" ht="12.65" customHeight="1">
       <c r="A62" s="260" t="s">
-        <v>3232</v>
+        <v>3230</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="12.65" customHeight="1">
       <c r="B63" t="s">
+        <v>3221</v>
+      </c>
+      <c r="C63" t="s">
+        <v>3222</v>
+      </c>
+      <c r="D63" t="s">
         <v>3223</v>
       </c>
-      <c r="C63" t="s">
+      <c r="E63" t="s">
         <v>3224</v>
       </c>
-      <c r="D63" t="s">
+      <c r="F63" t="s">
         <v>3225</v>
       </c>
-      <c r="E63" t="s">
+      <c r="G63" t="s">
         <v>3226</v>
       </c>
-      <c r="F63" t="s">
+      <c r="H63" t="s">
         <v>3227</v>
       </c>
-      <c r="G63" t="s">
+      <c r="I63" t="s">
         <v>3228</v>
-      </c>
-      <c r="H63" t="s">
-        <v>3229</v>
-      </c>
-      <c r="I63" t="s">
-        <v>3230</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="12.65" customHeight="1">
@@ -71170,7 +71167,7 @@
     </row>
     <row r="66" spans="1:9" ht="12.65" customHeight="1">
       <c r="A66" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B66">
         <v>11</v>
@@ -71200,33 +71197,33 @@
     <row r="67" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="68" spans="1:9" ht="12.65" customHeight="1">
       <c r="A68" s="260" t="s">
-        <v>3233</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="12.65" customHeight="1">
       <c r="B69" t="s">
+        <v>3221</v>
+      </c>
+      <c r="C69" t="s">
+        <v>3222</v>
+      </c>
+      <c r="D69" t="s">
         <v>3223</v>
       </c>
-      <c r="C69" t="s">
+      <c r="E69" t="s">
         <v>3224</v>
       </c>
-      <c r="D69" t="s">
+      <c r="F69" t="s">
         <v>3225</v>
       </c>
-      <c r="E69" t="s">
+      <c r="G69" t="s">
         <v>3226</v>
       </c>
-      <c r="F69" t="s">
+      <c r="H69" t="s">
         <v>3227</v>
       </c>
-      <c r="G69" t="s">
+      <c r="I69" t="s">
         <v>3228</v>
-      </c>
-      <c r="H69" t="s">
-        <v>3229</v>
-      </c>
-      <c r="I69" t="s">
-        <v>3230</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="12.65" customHeight="1">
@@ -71318,7 +71315,7 @@
     </row>
     <row r="73" spans="1:9" ht="12.65" customHeight="1">
       <c r="A73" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -71348,33 +71345,33 @@
     <row r="74" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="75" spans="1:9" ht="12.65" customHeight="1">
       <c r="A75" s="260" t="s">
-        <v>3234</v>
+        <v>3232</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="12.65" customHeight="1">
       <c r="B76" t="s">
+        <v>3221</v>
+      </c>
+      <c r="C76" t="s">
+        <v>3222</v>
+      </c>
+      <c r="D76" t="s">
         <v>3223</v>
       </c>
-      <c r="C76" t="s">
+      <c r="E76" t="s">
         <v>3224</v>
       </c>
-      <c r="D76" t="s">
+      <c r="F76" t="s">
         <v>3225</v>
       </c>
-      <c r="E76" t="s">
+      <c r="G76" t="s">
         <v>3226</v>
       </c>
-      <c r="F76" t="s">
+      <c r="H76" t="s">
         <v>3227</v>
       </c>
-      <c r="G76" t="s">
+      <c r="I76" t="s">
         <v>3228</v>
-      </c>
-      <c r="H76" t="s">
-        <v>3229</v>
-      </c>
-      <c r="I76" t="s">
-        <v>3230</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="12.65" customHeight="1">
@@ -71437,7 +71434,7 @@
     </row>
     <row r="79" spans="1:9" ht="12.65" customHeight="1">
       <c r="A79" t="s">
-        <v>3221</v>
+        <v>3219</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -71495,7 +71492,7 @@
     </row>
     <row r="81" spans="1:9" ht="12.65" customHeight="1">
       <c r="A81" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B81">
         <v>7</v>
@@ -71525,38 +71522,38 @@
     <row r="82" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="83" spans="1:9" ht="12.65" customHeight="1">
       <c r="A83" s="260" t="s">
-        <v>3235</v>
+        <v>3233</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="12.65" customHeight="1">
       <c r="B84" t="s">
+        <v>3221</v>
+      </c>
+      <c r="C84" t="s">
+        <v>3222</v>
+      </c>
+      <c r="D84" t="s">
         <v>3223</v>
       </c>
-      <c r="C84" t="s">
+      <c r="E84" t="s">
         <v>3224</v>
       </c>
-      <c r="D84" t="s">
+      <c r="F84" t="s">
         <v>3225</v>
       </c>
-      <c r="E84" t="s">
+      <c r="G84" t="s">
         <v>3226</v>
       </c>
-      <c r="F84" t="s">
+      <c r="H84" t="s">
         <v>3227</v>
       </c>
-      <c r="G84" t="s">
+      <c r="I84" t="s">
         <v>3228</v>
-      </c>
-      <c r="H84" t="s">
-        <v>3229</v>
-      </c>
-      <c r="I84" t="s">
-        <v>3230</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="12.65" customHeight="1">
       <c r="A85" t="s">
-        <v>3236</v>
+        <v>3234</v>
       </c>
       <c r="B85">
         <v>6</v>
@@ -71585,7 +71582,7 @@
     </row>
     <row r="86" spans="1:9" ht="12.65" customHeight="1">
       <c r="A86" t="s">
-        <v>3237</v>
+        <v>3235</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -71614,7 +71611,7 @@
     </row>
     <row r="87" spans="1:9" ht="12.65" customHeight="1">
       <c r="A87" t="s">
-        <v>3238</v>
+        <v>3236</v>
       </c>
       <c r="B87">
         <v>3</v>
@@ -71643,7 +71640,7 @@
     </row>
     <row r="88" spans="1:9" ht="12.65" customHeight="1">
       <c r="A88" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B88">
         <v>11</v>
@@ -71673,33 +71670,33 @@
     <row r="89" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="90" spans="1:9" ht="12.65" customHeight="1">
       <c r="A90" s="260" t="s">
-        <v>3239</v>
+        <v>3237</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="12.65" customHeight="1">
       <c r="B91" t="s">
+        <v>3221</v>
+      </c>
+      <c r="C91" t="s">
+        <v>3222</v>
+      </c>
+      <c r="D91" t="s">
         <v>3223</v>
       </c>
-      <c r="C91" t="s">
+      <c r="E91" t="s">
         <v>3224</v>
       </c>
-      <c r="D91" t="s">
+      <c r="F91" t="s">
         <v>3225</v>
       </c>
-      <c r="E91" t="s">
+      <c r="G91" t="s">
         <v>3226</v>
       </c>
-      <c r="F91" t="s">
+      <c r="H91" t="s">
         <v>3227</v>
       </c>
-      <c r="G91" t="s">
+      <c r="I91" t="s">
         <v>3228</v>
-      </c>
-      <c r="H91" t="s">
-        <v>3229</v>
-      </c>
-      <c r="I91" t="s">
-        <v>3230</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="12.65" customHeight="1">
@@ -71762,7 +71759,7 @@
     </row>
     <row r="94" spans="1:9" ht="12.65" customHeight="1">
       <c r="A94" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B94">
         <v>11</v>
@@ -71792,33 +71789,33 @@
     <row r="95" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="96" spans="1:9" ht="12.65" customHeight="1">
       <c r="A96" s="260" t="s">
-        <v>3240</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="12.65" customHeight="1">
       <c r="B97" t="s">
+        <v>3221</v>
+      </c>
+      <c r="C97" t="s">
+        <v>3222</v>
+      </c>
+      <c r="D97" t="s">
         <v>3223</v>
       </c>
-      <c r="C97" t="s">
+      <c r="E97" t="s">
         <v>3224</v>
       </c>
-      <c r="D97" t="s">
+      <c r="F97" t="s">
         <v>3225</v>
       </c>
-      <c r="E97" t="s">
+      <c r="G97" t="s">
         <v>3226</v>
       </c>
-      <c r="F97" t="s">
+      <c r="H97" t="s">
         <v>3227</v>
       </c>
-      <c r="G97" t="s">
+      <c r="I97" t="s">
         <v>3228</v>
-      </c>
-      <c r="H97" t="s">
-        <v>3229</v>
-      </c>
-      <c r="I97" t="s">
-        <v>3230</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="12.65" customHeight="1">
@@ -72055,7 +72052,7 @@
     </row>
     <row r="106" spans="1:9" ht="12.65" customHeight="1">
       <c r="A106" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B106">
         <v>8</v>
@@ -72085,33 +72082,33 @@
     <row r="107" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="108" spans="1:9" ht="12.65" customHeight="1">
       <c r="A108" s="260" t="s">
-        <v>3241</v>
+        <v>3239</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="12.65" customHeight="1">
       <c r="B109" t="s">
+        <v>3221</v>
+      </c>
+      <c r="C109" t="s">
+        <v>3222</v>
+      </c>
+      <c r="D109" t="s">
         <v>3223</v>
       </c>
-      <c r="C109" t="s">
+      <c r="E109" t="s">
         <v>3224</v>
       </c>
-      <c r="D109" t="s">
+      <c r="F109" t="s">
         <v>3225</v>
       </c>
-      <c r="E109" t="s">
+      <c r="G109" t="s">
         <v>3226</v>
       </c>
-      <c r="F109" t="s">
+      <c r="H109" t="s">
         <v>3227</v>
       </c>
-      <c r="G109" t="s">
+      <c r="I109" t="s">
         <v>3228</v>
-      </c>
-      <c r="H109" t="s">
-        <v>3229</v>
-      </c>
-      <c r="I109" t="s">
-        <v>3230</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="12.65" customHeight="1">
@@ -72232,7 +72229,7 @@
     </row>
     <row r="114" spans="1:9" ht="12.65" customHeight="1">
       <c r="A114" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B114">
         <v>10</v>
@@ -72262,38 +72259,38 @@
     <row r="115" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="116" spans="1:9" ht="12.65" customHeight="1">
       <c r="A116" s="260" t="s">
-        <v>3242</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="12.65" customHeight="1">
       <c r="B117" t="s">
+        <v>3221</v>
+      </c>
+      <c r="C117" t="s">
+        <v>3222</v>
+      </c>
+      <c r="D117" t="s">
         <v>3223</v>
       </c>
-      <c r="C117" t="s">
+      <c r="E117" t="s">
         <v>3224</v>
       </c>
-      <c r="D117" t="s">
+      <c r="F117" t="s">
         <v>3225</v>
       </c>
-      <c r="E117" t="s">
+      <c r="G117" t="s">
         <v>3226</v>
       </c>
-      <c r="F117" t="s">
+      <c r="H117" t="s">
         <v>3227</v>
       </c>
-      <c r="G117" t="s">
+      <c r="I117" t="s">
         <v>3228</v>
-      </c>
-      <c r="H117" t="s">
-        <v>3229</v>
-      </c>
-      <c r="I117" t="s">
-        <v>3230</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="12.65" customHeight="1">
       <c r="A118" t="s">
-        <v>3243</v>
+        <v>3241</v>
       </c>
       <c r="B118">
         <v>2</v>
@@ -72322,7 +72319,7 @@
     </row>
     <row r="119" spans="1:9" ht="12.65" customHeight="1">
       <c r="A119" t="s">
-        <v>3244</v>
+        <v>3242</v>
       </c>
       <c r="B119">
         <v>6</v>
@@ -72351,7 +72348,7 @@
     </row>
     <row r="120" spans="1:9" ht="12.65" customHeight="1">
       <c r="A120" t="s">
-        <v>3228</v>
+        <v>3226</v>
       </c>
       <c r="B120">
         <v>8</v>
@@ -72381,106 +72378,106 @@
     <row r="121" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="122" spans="1:9" ht="12.65" customHeight="1">
       <c r="A122" s="260" t="s">
-        <v>3245</v>
+        <v>3243</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="124" spans="1:9" ht="12.65" customHeight="1">
       <c r="A124" s="260" t="s">
-        <v>3246</v>
+        <v>3244</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="12.65" customHeight="1">
       <c r="A125" s="260" t="s">
-        <v>3247</v>
+        <v>3245</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="12.65" customHeight="1"/>
     <row r="127" spans="1:9" ht="12.65" customHeight="1">
       <c r="A127" t="s">
-        <v>3248</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="12.65" customHeight="1">
       <c r="A128" t="s">
-        <v>3249</v>
+        <v>3247</v>
       </c>
     </row>
     <row r="129" spans="1:1" ht="12.65" customHeight="1">
       <c r="A129" t="s">
-        <v>3250</v>
+        <v>3248</v>
       </c>
     </row>
     <row r="130" spans="1:1" ht="12.65" customHeight="1">
       <c r="A130" t="s">
-        <v>3251</v>
+        <v>3249</v>
       </c>
     </row>
     <row r="131" spans="1:1" ht="12.65" customHeight="1">
       <c r="A131" t="s">
-        <v>3252</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="132" spans="1:1" ht="12.65" customHeight="1">
       <c r="A132" t="s">
-        <v>3253</v>
+        <v>3251</v>
       </c>
     </row>
     <row r="133" spans="1:1" ht="12.65" customHeight="1">
       <c r="A133" t="s">
-        <v>3254</v>
+        <v>3252</v>
       </c>
     </row>
     <row r="134" spans="1:1" ht="12.65" customHeight="1">
       <c r="A134" t="s">
-        <v>3255</v>
+        <v>3253</v>
       </c>
     </row>
     <row r="135" spans="1:1" ht="12.65" customHeight="1">
       <c r="A135" t="s">
-        <v>3256</v>
+        <v>3254</v>
       </c>
     </row>
     <row r="136" spans="1:1" ht="12.65" customHeight="1">
       <c r="A136" t="s">
-        <v>3257</v>
+        <v>3255</v>
       </c>
     </row>
     <row r="137" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="138" spans="1:1" ht="12.65" customHeight="1">
       <c r="A138" s="260" t="s">
-        <v>3258</v>
+        <v>3256</v>
       </c>
     </row>
     <row r="139" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="140" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="141" spans="1:1" ht="12.65" customHeight="1">
       <c r="A141" s="465" t="s">
-        <v>3259</v>
+        <v>3257</v>
       </c>
     </row>
     <row r="142" spans="1:1" ht="12.65" customHeight="1">
       <c r="A142" t="s">
-        <v>3260</v>
+        <v>3258</v>
       </c>
     </row>
     <row r="143" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="144" spans="1:1" ht="12.65" customHeight="1">
       <c r="A144" s="466" t="s">
-        <v>3261</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="145" spans="1:2" ht="12.65" customHeight="1">
       <c r="A145" t="s">
-        <v>3262</v>
+        <v>3260</v>
       </c>
       <c r="B145" t="s">
-        <v>3263</v>
+        <v>3261</v>
       </c>
     </row>
     <row r="146" spans="1:2" ht="12.65" customHeight="1">
       <c r="A146" t="s">
-        <v>3264</v>
+        <v>3262</v>
       </c>
       <c r="B146">
         <v>12</v>
@@ -72488,7 +72485,7 @@
     </row>
     <row r="147" spans="1:2" ht="12.65" customHeight="1">
       <c r="A147" t="s">
-        <v>3265</v>
+        <v>3263</v>
       </c>
       <c r="B147">
         <v>28</v>
@@ -72496,7 +72493,7 @@
     </row>
     <row r="148" spans="1:2" ht="12.65" customHeight="1">
       <c r="A148" t="s">
-        <v>3266</v>
+        <v>3264</v>
       </c>
       <c r="B148">
         <v>23</v>
@@ -72504,7 +72501,7 @@
     </row>
     <row r="149" spans="1:2" ht="12.65" customHeight="1">
       <c r="A149" t="s">
-        <v>3267</v>
+        <v>3265</v>
       </c>
       <c r="B149">
         <v>17</v>
@@ -72512,486 +72509,486 @@
     </row>
     <row r="150" spans="1:2" ht="12.65" customHeight="1">
       <c r="A150" t="s">
-        <v>3268</v>
+        <v>3266</v>
       </c>
       <c r="B150" t="s">
-        <v>3269</v>
+        <v>3267</v>
       </c>
     </row>
     <row r="151" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="152" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="153" spans="1:2" ht="12.65" customHeight="1">
       <c r="A153" s="467" t="s">
-        <v>3270</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="154" spans="1:2" ht="12.65" customHeight="1">
       <c r="A154" t="s">
-        <v>3271</v>
+        <v>3269</v>
       </c>
     </row>
     <row r="155" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="156" spans="1:2" ht="12.65" customHeight="1">
       <c r="A156" s="468" t="s">
-        <v>3272</v>
+        <v>3270</v>
       </c>
     </row>
     <row r="157" spans="1:2" ht="12.65" customHeight="1">
       <c r="A157" t="s">
-        <v>3273</v>
+        <v>3271</v>
       </c>
     </row>
     <row r="158" spans="1:2" ht="12.65" customHeight="1">
       <c r="A158" t="s">
-        <v>3274</v>
+        <v>3272</v>
       </c>
     </row>
     <row r="159" spans="1:2" ht="12.65" customHeight="1">
       <c r="A159" t="s">
-        <v>3275</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="160" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="161" spans="1:2" ht="12.65" customHeight="1">
       <c r="A161" s="468" t="s">
-        <v>3276</v>
+        <v>3274</v>
       </c>
     </row>
     <row r="162" spans="1:2" ht="12.65" customHeight="1">
       <c r="A162" t="s">
-        <v>3277</v>
+        <v>3275</v>
       </c>
     </row>
     <row r="163" spans="1:2" ht="12.65" customHeight="1">
       <c r="A163" t="s">
-        <v>3278</v>
+        <v>3276</v>
       </c>
       <c r="B163" t="s">
-        <v>3279</v>
+        <v>3277</v>
       </c>
     </row>
     <row r="164" spans="1:2" ht="12.65" customHeight="1">
       <c r="A164" t="s">
-        <v>3280</v>
+        <v>3278</v>
       </c>
       <c r="B164" t="s">
-        <v>3281</v>
+        <v>3279</v>
       </c>
     </row>
     <row r="165" spans="1:2" ht="12.65" customHeight="1">
       <c r="A165" t="s">
-        <v>3282</v>
+        <v>3280</v>
       </c>
       <c r="B165" t="s">
-        <v>3283</v>
+        <v>3281</v>
       </c>
     </row>
     <row r="166" spans="1:2" ht="12.65" customHeight="1">
       <c r="A166" t="s">
-        <v>3284</v>
+        <v>3282</v>
       </c>
       <c r="B166" t="s">
-        <v>3285</v>
+        <v>3283</v>
       </c>
     </row>
     <row r="167" spans="1:2" ht="12.65" customHeight="1">
       <c r="A167" t="s">
-        <v>3286</v>
+        <v>3284</v>
       </c>
       <c r="B167" t="s">
-        <v>3285</v>
+        <v>3283</v>
       </c>
     </row>
     <row r="168" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="169" spans="1:2" ht="12.65" customHeight="1">
       <c r="A169" t="s">
-        <v>3287</v>
+        <v>3285</v>
       </c>
     </row>
     <row r="170" spans="1:2" ht="12.65" customHeight="1">
       <c r="A170" t="s">
-        <v>3288</v>
+        <v>3286</v>
       </c>
     </row>
     <row r="171" spans="1:2" ht="12.65" customHeight="1">
       <c r="A171" t="s">
-        <v>3289</v>
+        <v>3287</v>
       </c>
     </row>
     <row r="172" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="173" spans="1:2" ht="12.65" customHeight="1">
       <c r="A173" s="468" t="s">
-        <v>3290</v>
+        <v>3288</v>
       </c>
     </row>
     <row r="174" spans="1:2" ht="12.65" customHeight="1">
       <c r="A174" t="s">
-        <v>3291</v>
+        <v>3289</v>
       </c>
     </row>
     <row r="175" spans="1:2" ht="12.65" customHeight="1">
       <c r="A175" t="s">
-        <v>3292</v>
+        <v>3290</v>
       </c>
     </row>
     <row r="176" spans="1:2" ht="12.65" customHeight="1">
       <c r="A176" t="s">
-        <v>3293</v>
+        <v>3291</v>
       </c>
     </row>
     <row r="177" spans="1:1" ht="12.65" customHeight="1">
       <c r="A177" t="s">
-        <v>3294</v>
+        <v>3292</v>
       </c>
     </row>
     <row r="178" spans="1:1" ht="12.65" customHeight="1">
       <c r="A178" t="s">
-        <v>3295</v>
+        <v>3293</v>
       </c>
     </row>
     <row r="179" spans="1:1" ht="12.65" customHeight="1">
       <c r="A179" t="s">
-        <v>3296</v>
+        <v>3294</v>
       </c>
     </row>
     <row r="180" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="181" spans="1:1" ht="12.65" customHeight="1">
       <c r="A181" s="469" t="s">
-        <v>3297</v>
+        <v>3295</v>
       </c>
     </row>
     <row r="182" spans="1:1" ht="12.65" customHeight="1">
       <c r="A182" t="s">
-        <v>3298</v>
+        <v>3296</v>
       </c>
     </row>
     <row r="183" spans="1:1" ht="12.65" customHeight="1">
       <c r="A183" t="s">
-        <v>3299</v>
+        <v>3297</v>
       </c>
     </row>
     <row r="184" spans="1:1" ht="12.65" customHeight="1">
       <c r="A184" t="s">
-        <v>3300</v>
+        <v>3298</v>
       </c>
     </row>
     <row r="185" spans="1:1" ht="12.65" customHeight="1">
       <c r="A185" t="s">
-        <v>3301</v>
+        <v>3299</v>
       </c>
     </row>
     <row r="186" spans="1:1" ht="12.65" customHeight="1">
       <c r="A186" t="s">
-        <v>3302</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="187" spans="1:1" ht="12.65" customHeight="1">
       <c r="A187" t="s">
-        <v>3303</v>
+        <v>3301</v>
       </c>
     </row>
     <row r="188" spans="1:1" ht="12.65" customHeight="1">
       <c r="A188" t="s">
-        <v>3304</v>
+        <v>3302</v>
       </c>
     </row>
     <row r="189" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="190" spans="1:1" ht="12.65" customHeight="1">
       <c r="A190" s="467" t="s">
-        <v>3305</v>
+        <v>3303</v>
       </c>
     </row>
     <row r="191" spans="1:1" ht="12.65" customHeight="1">
       <c r="A191" t="s">
-        <v>3306</v>
+        <v>3304</v>
       </c>
     </row>
     <row r="192" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="193" spans="1:1" ht="12.65" customHeight="1">
       <c r="A193" s="466" t="s">
-        <v>3307</v>
+        <v>3305</v>
       </c>
     </row>
     <row r="194" spans="1:1" ht="12.65" customHeight="1">
       <c r="A194" t="s">
-        <v>3308</v>
+        <v>3306</v>
       </c>
     </row>
     <row r="195" spans="1:1" ht="12.65" customHeight="1">
       <c r="A195" t="s">
-        <v>3309</v>
+        <v>3307</v>
       </c>
     </row>
     <row r="196" spans="1:1" ht="12.65" customHeight="1">
       <c r="A196" t="s">
-        <v>3310</v>
+        <v>3308</v>
       </c>
     </row>
     <row r="197" spans="1:1" ht="12.65" customHeight="1">
       <c r="A197" t="s">
-        <v>3311</v>
+        <v>3309</v>
       </c>
     </row>
     <row r="198" spans="1:1" ht="12.65" customHeight="1">
       <c r="A198" t="s">
-        <v>3312</v>
+        <v>3310</v>
       </c>
     </row>
     <row r="199" spans="1:1" ht="12.65" customHeight="1">
       <c r="A199" t="s">
-        <v>3313</v>
+        <v>3311</v>
       </c>
     </row>
     <row r="200" spans="1:1" ht="12.65" customHeight="1">
       <c r="A200" t="s">
-        <v>3314</v>
+        <v>3312</v>
       </c>
     </row>
     <row r="201" spans="1:1" ht="12.65" customHeight="1">
       <c r="A201" t="s">
-        <v>3315</v>
+        <v>3313</v>
       </c>
     </row>
     <row r="202" spans="1:1" ht="12.65" customHeight="1">
       <c r="A202" t="s">
-        <v>3316</v>
+        <v>3314</v>
       </c>
     </row>
     <row r="203" spans="1:1" ht="12.65" customHeight="1">
       <c r="A203" t="s">
-        <v>3317</v>
+        <v>3315</v>
       </c>
     </row>
     <row r="204" spans="1:1" ht="12.65" customHeight="1">
       <c r="A204" t="s">
-        <v>3318</v>
+        <v>3316</v>
       </c>
     </row>
     <row r="205" spans="1:1" ht="12.65" customHeight="1">
       <c r="A205" t="s">
-        <v>3319</v>
+        <v>3317</v>
       </c>
     </row>
     <row r="206" spans="1:1" ht="12.65" customHeight="1">
       <c r="A206" t="s">
-        <v>3320</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="207" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="208" spans="1:1" ht="12.65" customHeight="1">
       <c r="A208" s="466" t="s">
-        <v>3321</v>
+        <v>3319</v>
       </c>
     </row>
     <row r="209" spans="1:1" ht="12.65" customHeight="1">
       <c r="A209" t="s">
-        <v>3322</v>
+        <v>3320</v>
       </c>
     </row>
     <row r="210" spans="1:1" ht="12.65" customHeight="1">
       <c r="A210" t="s">
-        <v>3323</v>
+        <v>3321</v>
       </c>
     </row>
     <row r="211" spans="1:1" ht="12.65" customHeight="1">
       <c r="A211" t="s">
-        <v>3324</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="212" spans="1:1" ht="12.65" customHeight="1">
       <c r="A212" t="s">
-        <v>3325</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="213" spans="1:1" ht="12.65" customHeight="1">
       <c r="A213" t="s">
-        <v>3326</v>
+        <v>3324</v>
       </c>
     </row>
     <row r="214" spans="1:1" ht="12.65" customHeight="1">
       <c r="A214" t="s">
-        <v>3327</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="215" spans="1:1" ht="12.65" customHeight="1">
       <c r="A215" t="s">
-        <v>3328</v>
+        <v>3326</v>
       </c>
     </row>
     <row r="216" spans="1:1" ht="12.65" customHeight="1">
       <c r="A216" t="s">
-        <v>3329</v>
+        <v>3327</v>
       </c>
     </row>
     <row r="217" spans="1:1" ht="12.65" customHeight="1">
       <c r="A217" t="s">
-        <v>3330</v>
+        <v>3328</v>
       </c>
     </row>
     <row r="218" spans="1:1" ht="12.65" customHeight="1">
       <c r="A218" t="s">
-        <v>3331</v>
+        <v>3329</v>
       </c>
     </row>
     <row r="219" spans="1:1" ht="12.65" customHeight="1">
       <c r="A219" t="s">
-        <v>3332</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="220" spans="1:1" ht="12.65" customHeight="1">
       <c r="A220" t="s">
-        <v>3333</v>
+        <v>3331</v>
       </c>
     </row>
     <row r="221" spans="1:1" ht="12.65" customHeight="1">
       <c r="A221" t="s">
-        <v>3334</v>
+        <v>3332</v>
       </c>
     </row>
     <row r="222" spans="1:1" ht="12.65" customHeight="1">
       <c r="A222" t="s">
-        <v>3335</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="223" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="224" spans="1:1" ht="12.65" customHeight="1">
       <c r="A224" s="470" t="s">
-        <v>3336</v>
+        <v>3334</v>
       </c>
     </row>
     <row r="225" spans="1:2" ht="12.65" customHeight="1">
       <c r="A225" t="s">
-        <v>3337</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="226" spans="1:2" ht="12.65" customHeight="1">
       <c r="A226" t="s">
-        <v>3338</v>
+        <v>3336</v>
       </c>
     </row>
     <row r="227" spans="1:2" ht="12.65" customHeight="1">
       <c r="A227" t="s">
-        <v>3339</v>
+        <v>3337</v>
       </c>
     </row>
     <row r="228" spans="1:2" ht="12.65" customHeight="1">
       <c r="A228" t="s">
-        <v>3340</v>
+        <v>3338</v>
       </c>
     </row>
     <row r="229" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="230" spans="1:2" ht="12.65" customHeight="1">
       <c r="A230" s="467" t="s">
-        <v>3341</v>
+        <v>3339</v>
       </c>
     </row>
     <row r="231" spans="1:2" ht="12.65" customHeight="1">
       <c r="A231" t="s">
-        <v>3342</v>
+        <v>3340</v>
       </c>
     </row>
     <row r="232" spans="1:2" ht="12.65" customHeight="1"/>
     <row r="233" spans="1:2" ht="12.65" customHeight="1">
       <c r="A233" s="466" t="s">
-        <v>3343</v>
+        <v>3341</v>
       </c>
     </row>
     <row r="234" spans="1:2" ht="12.65" customHeight="1">
       <c r="A234" t="s">
-        <v>3132</v>
+        <v>3130</v>
       </c>
       <c r="B234" t="s">
-        <v>3344</v>
+        <v>3342</v>
       </c>
     </row>
     <row r="235" spans="1:2" ht="12.65" customHeight="1">
       <c r="A235" t="s">
-        <v>3345</v>
+        <v>3343</v>
       </c>
       <c r="B235" t="s">
-        <v>3346</v>
+        <v>3344</v>
       </c>
     </row>
     <row r="236" spans="1:2" ht="12.65" customHeight="1">
       <c r="A236" t="s">
-        <v>3347</v>
+        <v>3345</v>
       </c>
       <c r="B236" t="s">
-        <v>3137</v>
+        <v>3135</v>
       </c>
     </row>
     <row r="237" spans="1:2" ht="12.65" customHeight="1">
       <c r="A237" t="s">
-        <v>3348</v>
+        <v>3346</v>
       </c>
       <c r="B237" t="s">
-        <v>3139</v>
+        <v>3137</v>
       </c>
     </row>
     <row r="238" spans="1:2" ht="12.65" customHeight="1">
       <c r="A238" t="s">
-        <v>3349</v>
+        <v>3347</v>
       </c>
       <c r="B238" t="s">
-        <v>3141</v>
+        <v>3139</v>
       </c>
     </row>
     <row r="239" spans="1:2" ht="12.65" customHeight="1">
       <c r="A239" t="s">
-        <v>3142</v>
+        <v>3140</v>
       </c>
       <c r="B239" t="s">
-        <v>3143</v>
+        <v>3141</v>
       </c>
     </row>
     <row r="240" spans="1:2" ht="12.65" customHeight="1">
       <c r="A240" t="s">
-        <v>3144</v>
+        <v>3142</v>
       </c>
       <c r="B240" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="241" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="242" spans="1:1" ht="12.65" customHeight="1">
       <c r="A242" s="466" t="s">
-        <v>3350</v>
+        <v>3348</v>
       </c>
     </row>
     <row r="243" spans="1:1" ht="12.65" customHeight="1">
       <c r="A243" t="s">
-        <v>3351</v>
+        <v>3349</v>
       </c>
     </row>
     <row r="244" spans="1:1" ht="12.65" customHeight="1">
       <c r="A244" t="s">
-        <v>3352</v>
+        <v>3350</v>
       </c>
     </row>
     <row r="245" spans="1:1" ht="12.65" customHeight="1">
       <c r="A245" t="s">
-        <v>3353</v>
+        <v>3351</v>
       </c>
     </row>
     <row r="246" spans="1:1" ht="12.65" customHeight="1"/>
     <row r="247" spans="1:1" ht="12.65" customHeight="1">
       <c r="A247" s="466" t="s">
-        <v>3354</v>
+        <v>3352</v>
       </c>
     </row>
     <row r="248" spans="1:1" ht="12.65" customHeight="1">
       <c r="A248" t="s">
-        <v>3355</v>
+        <v>3353</v>
       </c>
     </row>
     <row r="249" spans="1:1" ht="12.65" customHeight="1">
       <c r="A249" t="s">
-        <v>3356</v>
+        <v>3354</v>
       </c>
     </row>
     <row r="250" spans="1:1" ht="12.65" customHeight="1">
       <c r="A250" t="s">
-        <v>3357</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="251" spans="1:1" ht="12.65" customHeight="1"/>
@@ -73764,199 +73761,199 @@
         <v>5</v>
       </c>
       <c r="B1" s="492" t="s">
+        <v>3356</v>
+      </c>
+      <c r="C1" s="492" t="s">
+        <v>3357</v>
+      </c>
+      <c r="D1" s="492" t="s">
         <v>3358</v>
       </c>
-      <c r="C1" s="492" t="s">
+      <c r="E1" s="492" t="s">
         <v>3359</v>
       </c>
-      <c r="D1" s="492" t="s">
+      <c r="F1" s="492" t="s">
         <v>3360</v>
-      </c>
-      <c r="E1" s="492" t="s">
-        <v>3361</v>
-      </c>
-      <c r="F1" s="492" t="s">
-        <v>3362</v>
       </c>
       <c r="G1" s="492" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="492" t="s">
-        <v>3363</v>
+        <v>3361</v>
       </c>
       <c r="I1" s="492" t="s">
-        <v>3364</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="37.5">
+        <v>3362</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="50">
       <c r="A2" s="496">
         <v>46238</v>
       </c>
       <c r="B2" t="s">
+        <v>3363</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3364</v>
+      </c>
+      <c r="E2" t="s">
         <v>3365</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" s="494" t="s">
         <v>3366</v>
-      </c>
-      <c r="E2" t="s">
-        <v>3367</v>
-      </c>
-      <c r="F2" s="494" t="s">
-        <v>3368</v>
       </c>
       <c r="G2" s="493"/>
       <c r="I2" s="494" t="s">
-        <v>3369</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="37.5">
+        <v>3367</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="50">
       <c r="B3" t="s">
-        <v>3370</v>
+        <v>3368</v>
       </c>
       <c r="C3">
         <v>7888</v>
       </c>
       <c r="D3" t="s">
+        <v>3369</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3370</v>
+      </c>
+      <c r="F3" s="494" t="s">
         <v>3371</v>
-      </c>
-      <c r="E3" t="s">
-        <v>3372</v>
-      </c>
-      <c r="F3" s="494" t="s">
-        <v>3373</v>
       </c>
       <c r="G3" s="493"/>
       <c r="I3" s="494" t="s">
-        <v>3374</v>
+        <v>3372</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="25">
       <c r="B4" t="s">
-        <v>3375</v>
+        <v>3373</v>
       </c>
       <c r="C4">
         <v>8981</v>
       </c>
       <c r="D4" t="s">
+        <v>3374</v>
+      </c>
+      <c r="E4" t="s">
+        <v>3375</v>
+      </c>
+      <c r="F4" s="494" t="s">
         <v>3376</v>
-      </c>
-      <c r="E4" t="s">
-        <v>3377</v>
-      </c>
-      <c r="F4" s="494" t="s">
-        <v>3378</v>
       </c>
       <c r="G4" s="493"/>
       <c r="I4" s="494" t="s">
-        <v>3379</v>
+        <v>3377</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="25">
       <c r="B5" t="s">
+        <v>3378</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3379</v>
+      </c>
+      <c r="E5" t="s">
         <v>3380</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" s="494" t="s">
         <v>3381</v>
-      </c>
-      <c r="E5" t="s">
-        <v>3382</v>
-      </c>
-      <c r="F5" s="494" t="s">
-        <v>3383</v>
       </c>
       <c r="G5" s="493"/>
       <c r="I5" s="494" t="s">
-        <v>3384</v>
+        <v>3382</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="25">
       <c r="B6" t="s">
+        <v>3383</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3384</v>
+      </c>
+      <c r="E6" t="s">
         <v>3385</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" s="494" t="s">
         <v>3386</v>
-      </c>
-      <c r="E6" t="s">
-        <v>3387</v>
-      </c>
-      <c r="F6" s="494" t="s">
-        <v>3388</v>
       </c>
       <c r="G6" s="493"/>
       <c r="I6" s="494" t="s">
-        <v>3389</v>
+        <v>3387</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="25">
       <c r="B7" t="s">
+        <v>3388</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3389</v>
+      </c>
+      <c r="E7" t="s">
         <v>3390</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" s="494" t="s">
         <v>3391</v>
-      </c>
-      <c r="E7" t="s">
-        <v>3392</v>
-      </c>
-      <c r="F7" s="494" t="s">
-        <v>3393</v>
       </c>
       <c r="G7" s="493"/>
       <c r="I7" s="494" t="s">
-        <v>3407</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="25">
       <c r="B8" t="s">
+        <v>3392</v>
+      </c>
+      <c r="D8" t="s">
+        <v>3393</v>
+      </c>
+      <c r="E8" t="s">
         <v>3394</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" s="494" t="s">
         <v>3395</v>
-      </c>
-      <c r="E8" t="s">
-        <v>3396</v>
-      </c>
-      <c r="F8" s="494" t="s">
-        <v>3397</v>
       </c>
       <c r="G8" s="493"/>
       <c r="I8" s="494" t="s">
-        <v>3408</v>
+        <v>3406</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="25">
       <c r="B9" t="s">
-        <v>3398</v>
+        <v>3396</v>
       </c>
       <c r="C9">
         <v>8609</v>
       </c>
       <c r="D9" t="s">
+        <v>3397</v>
+      </c>
+      <c r="E9" t="s">
+        <v>3398</v>
+      </c>
+      <c r="F9" s="494" t="s">
         <v>3399</v>
-      </c>
-      <c r="E9" t="s">
-        <v>3400</v>
-      </c>
-      <c r="F9" s="494" t="s">
-        <v>3401</v>
       </c>
       <c r="G9" s="493"/>
       <c r="I9" s="494" t="s">
-        <v>3409</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="25">
+        <v>3407</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="37.5">
       <c r="B10" t="s">
+        <v>3400</v>
+      </c>
+      <c r="E10" t="s">
+        <v>3401</v>
+      </c>
+      <c r="F10" s="494" t="s">
         <v>3402</v>
-      </c>
-      <c r="E10" t="s">
-        <v>3403</v>
-      </c>
-      <c r="F10" s="494" t="s">
-        <v>3404</v>
       </c>
       <c r="G10" s="493"/>
       <c r="I10" s="494" t="s">
-        <v>3405</v>
+        <v>3403</v>
       </c>
     </row>
   </sheetData>

--- a/j-busqueda clientes/j-clientes-gle.xlsx
+++ b/j-busqueda clientes/j-clientes-gle.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88153b17ae7a9f01/documentos/TRABAJOS AUTONOMOS/JURADA/j-busqueda clientes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="11_8D71D4E3FF54086EB3E5708B7890922AE0578CDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00EA212E-46F1-42D4-A663-893CCCCD5380}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="11_8D71D4E3FF54086EB3E5708B7890922AE0578CDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58D0681B-671C-4933-8668-5C1F50641B05}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="-110" windowWidth="24900" windowHeight="14500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10993,7 +10993,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="497">
+  <cellXfs count="498">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -12407,6 +12407,9 @@
     </xf>
     <xf numFmtId="166" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -22717,8 +22720,8 @@
         <v>46035</v>
       </c>
       <c r="C171" s="379"/>
-      <c r="D171" s="76" t="s">
-        <v>1014</v>
+      <c r="D171" s="497">
+        <v>46259</v>
       </c>
       <c r="E171" s="76" t="s">
         <v>64</v>
@@ -22726,7 +22729,9 @@
       <c r="F171" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="G171" s="76"/>
+      <c r="G171" s="450" t="s">
+        <v>149</v>
+      </c>
       <c r="H171" s="116" t="s">
         <v>1015</v>
       </c>

--- a/j-busqueda clientes/j-clientes-gle.xlsx
+++ b/j-busqueda clientes/j-clientes-gle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88153b17ae7a9f01/documentos/TRABAJOS AUTONOMOS/JURADA/j-busqueda clientes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="11_8D71D4E3FF54086EB3E5708B7890922AE0578CDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58D0681B-671C-4933-8668-5C1F50641B05}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="11_8D71D4E3FF54086EB3E5708B7890922AE0578CDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3F1861F-6894-4D77-9496-A1BDB532E311}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="-110" windowWidth="24900" windowHeight="14500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5708" uniqueCount="3410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5709" uniqueCount="3410">
   <si>
     <t>para día</t>
   </si>
@@ -34467,7 +34467,9 @@
       <c r="F364" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="G364" s="86"/>
+      <c r="G364" s="491" t="s">
+        <v>149</v>
+      </c>
       <c r="H364" s="120" t="s">
         <v>2343</v>
       </c>
